--- a/MAHINDRA_GROUP_Technical_Metrics.xlsx
+++ b/MAHINDRA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="80">
   <si>
     <t>Symbol</t>
   </si>
@@ -178,7 +178,49 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>Left 52W High Zone</t>
+  </si>
+  <si>
+    <t>0.0% → -3.3%</t>
+  </si>
+  <si>
+    <t>⚪ NEUTRAL</t>
+  </si>
+  <si>
+    <t>0.0%</t>
+  </si>
+  <si>
+    <t>-3.3%</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>54.5 → 49.1</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>54.5</t>
+  </si>
+  <si>
+    <t>49.1</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -230,7 +272,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -264,6 +306,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF1F4E79"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -277,7 +326,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -299,6 +348,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF4A6FA5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,21 +435,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -403,7 +460,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -902,10 +959,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>409.5</v>
+        <v>413</v>
       </c>
       <c r="D2">
-        <v>-0.24</v>
+        <v>0.85</v>
       </c>
       <c r="E2">
         <v>490.2</v>
@@ -914,46 +971,46 @@
         <v>379.2</v>
       </c>
       <c r="G2">
-        <v>-16.46</v>
+        <v>-15.75</v>
       </c>
       <c r="H2">
-        <v>7.99</v>
+        <v>8.91</v>
       </c>
       <c r="I2">
-        <v>-2.42</v>
+        <v>0.58</v>
       </c>
       <c r="J2">
-        <v>-11.8</v>
+        <v>-12.02</v>
       </c>
       <c r="K2">
-        <v>-11.5</v>
+        <v>-9.81</v>
       </c>
       <c r="L2">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="M2">
-        <v>11.87</v>
+        <v>11.98</v>
       </c>
       <c r="N2">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="O2">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="P2">
-        <v>411.19</v>
+        <v>411.67</v>
       </c>
       <c r="Q2">
-        <v>432.51</v>
+        <v>430.23</v>
       </c>
       <c r="R2">
-        <v>447.84</v>
+        <v>447.35</v>
       </c>
       <c r="S2">
-        <v>438.74</v>
+        <v>438.67</v>
       </c>
       <c r="T2">
-        <v>-6.66</v>
+        <v>-5.85</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -968,34 +1025,34 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>35.42</v>
+        <v>38.16</v>
       </c>
       <c r="Z2">
-        <v>-13.47</v>
+        <v>-12.9</v>
       </c>
       <c r="AA2">
-        <v>-12.1</v>
+        <v>-12.26</v>
       </c>
       <c r="AB2">
-        <v>-1.37</v>
+        <v>-0.64</v>
       </c>
       <c r="AC2">
-        <v>27.87</v>
+        <v>52.05</v>
       </c>
       <c r="AD2">
-        <v>28.74</v>
+        <v>36.65</v>
       </c>
       <c r="AE2">
-        <v>12.35</v>
+        <v>12.33</v>
       </c>
       <c r="AF2">
-        <v>-60.58</v>
+        <v>486.43</v>
       </c>
       <c r="AG2">
-        <v>488.66</v>
+        <v>485.62</v>
       </c>
       <c r="AH2">
-        <v>376.37</v>
+        <v>374.85</v>
       </c>
       <c r="AI2">
         <v>446.81</v>
@@ -1004,7 +1061,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>46.89</v>
+        <v>43.77</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1015,10 +1072,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>3517</v>
+        <v>3460.1</v>
       </c>
       <c r="D3">
-        <v>0.43</v>
+        <v>-1.62</v>
       </c>
       <c r="E3">
         <v>3802.4</v>
@@ -1027,46 +1084,46 @@
         <v>2931.1</v>
       </c>
       <c r="G3">
-        <v>-7.51</v>
+        <v>-9</v>
       </c>
       <c r="H3">
-        <v>19.99</v>
+        <v>18.05</v>
       </c>
       <c r="I3">
-        <v>2.58</v>
+        <v>0.79</v>
       </c>
       <c r="J3">
-        <v>12.39</v>
+        <v>9.48</v>
       </c>
       <c r="K3">
-        <v>10.74</v>
+        <v>11.19</v>
       </c>
       <c r="L3">
-        <v>9.9</v>
+        <v>7.72</v>
       </c>
       <c r="M3">
-        <v>35.91</v>
+        <v>35.73</v>
       </c>
       <c r="N3">
         <v>55</v>
       </c>
       <c r="O3">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="P3">
-        <v>3462.68</v>
+        <v>3468.1</v>
       </c>
       <c r="Q3">
-        <v>3278.13</v>
+        <v>3296.47</v>
       </c>
       <c r="R3">
-        <v>3159.23</v>
+        <v>3169.03</v>
       </c>
       <c r="S3">
-        <v>3360.04</v>
+        <v>3359.23</v>
       </c>
       <c r="T3">
-        <v>4.67</v>
+        <v>3</v>
       </c>
       <c r="U3" t="s">
         <v>48</v>
@@ -1081,34 +1138,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>69.52</v>
+        <v>63.49</v>
       </c>
       <c r="Z3">
-        <v>93.98999999999999</v>
+        <v>93.29000000000001</v>
       </c>
       <c r="AA3">
-        <v>69.34999999999999</v>
+        <v>74.14</v>
       </c>
       <c r="AB3">
-        <v>24.63</v>
+        <v>19.15</v>
       </c>
       <c r="AC3">
-        <v>88.68000000000001</v>
+        <v>87.81</v>
       </c>
       <c r="AD3">
-        <v>88.88</v>
+        <v>88.39</v>
       </c>
       <c r="AE3">
-        <v>79.45999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="AF3">
-        <v>-3.17</v>
+        <v>-10.8</v>
       </c>
       <c r="AG3">
-        <v>3558.63</v>
+        <v>3574.03</v>
       </c>
       <c r="AH3">
-        <v>2997.63</v>
+        <v>3018.91</v>
       </c>
       <c r="AI3">
         <v>3274.47</v>
@@ -1117,7 +1174,7 @@
         <v>50</v>
       </c>
       <c r="AK3">
-        <v>60.99</v>
+        <v>59.18</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1128,10 +1185,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>412.3</v>
+        <v>398.8</v>
       </c>
       <c r="D4">
-        <v>0.9399999999999999</v>
+        <v>-3.27</v>
       </c>
       <c r="E4">
         <v>412.3</v>
@@ -1140,46 +1197,46 @@
         <v>252.5</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>-3.27</v>
       </c>
       <c r="H4">
-        <v>63.29</v>
+        <v>57.94</v>
       </c>
       <c r="I4">
-        <v>1.68</v>
+        <v>0.05</v>
       </c>
       <c r="J4">
-        <v>20.96</v>
+        <v>19.87</v>
       </c>
       <c r="K4">
-        <v>26.1</v>
+        <v>24.59</v>
       </c>
       <c r="L4">
-        <v>59.53</v>
+        <v>55.51</v>
       </c>
       <c r="M4">
-        <v>23.92</v>
+        <v>22.92</v>
       </c>
       <c r="N4">
         <v>99</v>
       </c>
       <c r="O4">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P4">
-        <v>401.31</v>
+        <v>401.35</v>
       </c>
       <c r="Q4">
-        <v>369.71</v>
+        <v>373.39</v>
       </c>
       <c r="R4">
-        <v>331.5</v>
+        <v>333.57</v>
       </c>
       <c r="S4">
-        <v>337.33</v>
+        <v>337.82</v>
       </c>
       <c r="T4">
-        <v>22.22</v>
+        <v>18.05</v>
       </c>
       <c r="U4" t="s">
         <v>48</v>
@@ -1194,43 +1251,43 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>69.75</v>
+        <v>62.47</v>
       </c>
       <c r="Z4">
-        <v>21.77</v>
+        <v>20.9</v>
       </c>
       <c r="AA4">
-        <v>19.51</v>
+        <v>19.79</v>
       </c>
       <c r="AB4">
-        <v>2.26</v>
+        <v>1.11</v>
       </c>
       <c r="AC4">
-        <v>47.28</v>
+        <v>33.35</v>
       </c>
       <c r="AD4">
-        <v>52.91</v>
+        <v>44.23</v>
       </c>
       <c r="AE4">
-        <v>15.87</v>
+        <v>15.94</v>
       </c>
       <c r="AF4">
-        <v>-49.24</v>
+        <v>-76.97</v>
       </c>
       <c r="AG4">
-        <v>433.37</v>
+        <v>434.67</v>
       </c>
       <c r="AH4">
-        <v>306.04</v>
+        <v>312.11</v>
       </c>
       <c r="AI4">
-        <v>357.39</v>
+        <v>357.72</v>
       </c>
       <c r="AJ4" t="s">
         <v>50</v>
       </c>
       <c r="AK4">
-        <v>53.97</v>
+        <v>54.14</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1241,10 +1298,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>386.85</v>
+        <v>382.65</v>
       </c>
       <c r="D5">
-        <v>0.08</v>
+        <v>-1.09</v>
       </c>
       <c r="E5">
         <v>421.7</v>
@@ -1253,46 +1310,46 @@
         <v>294.25</v>
       </c>
       <c r="G5">
-        <v>-8.26</v>
+        <v>-9.26</v>
       </c>
       <c r="H5">
-        <v>31.47</v>
+        <v>30.04</v>
       </c>
       <c r="I5">
-        <v>-2.86</v>
+        <v>-3.75</v>
       </c>
       <c r="J5">
-        <v>2.1</v>
+        <v>1.07</v>
       </c>
       <c r="K5">
-        <v>19.44</v>
+        <v>17.54</v>
       </c>
       <c r="L5">
-        <v>6.81</v>
+        <v>7.43</v>
       </c>
       <c r="M5">
-        <v>9.5</v>
+        <v>9.69</v>
       </c>
       <c r="N5">
         <v>66</v>
       </c>
       <c r="O5">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P5">
-        <v>388.04</v>
+        <v>385.06</v>
       </c>
       <c r="Q5">
-        <v>381.39</v>
+        <v>381.9</v>
       </c>
       <c r="R5">
-        <v>363.9</v>
+        <v>364.84</v>
       </c>
       <c r="S5">
-        <v>365.05</v>
+        <v>365.01</v>
       </c>
       <c r="T5">
-        <v>5.97</v>
+        <v>4.83</v>
       </c>
       <c r="U5" t="s">
         <v>48</v>
@@ -1307,34 +1364,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>58.13</v>
+        <v>53.86</v>
       </c>
       <c r="Z5">
-        <v>6.87</v>
+        <v>6.12</v>
       </c>
       <c r="AA5">
-        <v>7.56</v>
+        <v>7.28</v>
       </c>
       <c r="AB5">
-        <v>-0.6899999999999999</v>
+        <v>-1.15</v>
       </c>
       <c r="AC5">
-        <v>16.27</v>
+        <v>11</v>
       </c>
       <c r="AD5">
-        <v>21.59</v>
+        <v>12.83</v>
       </c>
       <c r="AE5">
-        <v>11.61</v>
+        <v>11.48</v>
       </c>
       <c r="AF5">
-        <v>-66.05</v>
+        <v>-80.16</v>
       </c>
       <c r="AG5">
-        <v>398.52</v>
+        <v>398.51</v>
       </c>
       <c r="AH5">
-        <v>364.26</v>
+        <v>365.3</v>
       </c>
       <c r="AI5">
         <v>364.94</v>
@@ -1343,7 +1400,7 @@
         <v>50</v>
       </c>
       <c r="AK5">
-        <v>36.53</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1354,10 +1411,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>411.35</v>
+        <v>409.35</v>
       </c>
       <c r="D6">
-        <v>2.15</v>
+        <v>-0.49</v>
       </c>
       <c r="E6">
         <v>442.7</v>
@@ -1366,46 +1423,46 @@
         <v>279.55</v>
       </c>
       <c r="G6">
-        <v>-7.08</v>
+        <v>-7.53</v>
       </c>
       <c r="H6">
-        <v>47.15</v>
+        <v>46.43</v>
       </c>
       <c r="I6">
-        <v>-1.19</v>
+        <v>-2.77</v>
       </c>
       <c r="J6">
-        <v>6.24</v>
+        <v>6.95</v>
       </c>
       <c r="K6">
-        <v>9.74</v>
+        <v>9.92</v>
       </c>
       <c r="L6">
-        <v>27.93</v>
+        <v>30.01</v>
       </c>
       <c r="M6">
-        <v>-9.039999999999999</v>
+        <v>-8.720000000000001</v>
       </c>
       <c r="N6">
         <v>88</v>
       </c>
       <c r="O6">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P6">
-        <v>412.49</v>
+        <v>410.16</v>
       </c>
       <c r="Q6">
-        <v>404.12</v>
+        <v>404.91</v>
       </c>
       <c r="R6">
-        <v>379.87</v>
+        <v>381.11</v>
       </c>
       <c r="S6">
-        <v>362.75</v>
+        <v>362.97</v>
       </c>
       <c r="T6">
-        <v>13.4</v>
+        <v>12.78</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1420,34 +1477,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>56.66</v>
+        <v>55.39</v>
       </c>
       <c r="Z6">
-        <v>8.4</v>
+        <v>7.84</v>
       </c>
       <c r="AA6">
-        <v>9.43</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="AB6">
-        <v>-1.02</v>
+        <v>-1.27</v>
       </c>
       <c r="AC6">
-        <v>19.81</v>
+        <v>16.57</v>
       </c>
       <c r="AD6">
-        <v>28.03</v>
+        <v>18.7</v>
       </c>
       <c r="AE6">
-        <v>15.02</v>
+        <v>14.64</v>
       </c>
       <c r="AF6">
-        <v>-48.14</v>
+        <v>-69.63</v>
       </c>
       <c r="AG6">
-        <v>426.91</v>
+        <v>427.25</v>
       </c>
       <c r="AH6">
-        <v>381.34</v>
+        <v>382.56</v>
       </c>
       <c r="AI6">
         <v>371.16</v>
@@ -1456,7 +1513,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>33.5</v>
+        <v>29.24</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1467,10 +1524,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>607.85</v>
+        <v>595</v>
       </c>
       <c r="D7">
-        <v>3.08</v>
+        <v>-2.11</v>
       </c>
       <c r="E7">
         <v>681.5</v>
@@ -1479,46 +1536,46 @@
         <v>506.45</v>
       </c>
       <c r="G7">
-        <v>-10.81</v>
+        <v>-12.69</v>
       </c>
       <c r="H7">
-        <v>20.02</v>
+        <v>17.48</v>
       </c>
       <c r="I7">
-        <v>5.95</v>
+        <v>2.75</v>
       </c>
       <c r="J7">
-        <v>1.58</v>
+        <v>0.53</v>
       </c>
       <c r="K7">
-        <v>-5.23</v>
+        <v>-8.289999999999999</v>
       </c>
       <c r="L7">
-        <v>-8.51</v>
+        <v>-11.92</v>
       </c>
       <c r="M7">
-        <v>34.12</v>
+        <v>33.05</v>
       </c>
       <c r="N7">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="O7">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P7">
-        <v>588.61</v>
+        <v>591.79</v>
       </c>
       <c r="Q7">
-        <v>580.35</v>
+        <v>580.64</v>
       </c>
       <c r="R7">
-        <v>600.22</v>
+        <v>599.8200000000001</v>
       </c>
       <c r="S7">
-        <v>580.79</v>
+        <v>580.84</v>
       </c>
       <c r="T7">
-        <v>4.66</v>
+        <v>2.44</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1533,34 +1590,34 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>60.66</v>
+        <v>53.23</v>
       </c>
       <c r="Z7">
-        <v>-3.07</v>
+        <v>-2.02</v>
       </c>
       <c r="AA7">
-        <v>-7.47</v>
+        <v>-6.38</v>
       </c>
       <c r="AB7">
-        <v>4.4</v>
+        <v>4.36</v>
       </c>
       <c r="AC7">
-        <v>100</v>
+        <v>91.2</v>
       </c>
       <c r="AD7">
-        <v>100</v>
+        <v>97.06999999999999</v>
       </c>
       <c r="AE7">
-        <v>15.01</v>
+        <v>15.53</v>
       </c>
       <c r="AF7">
-        <v>413.42</v>
+        <v>69.17</v>
       </c>
       <c r="AG7">
-        <v>599.61</v>
+        <v>600.64</v>
       </c>
       <c r="AH7">
-        <v>561.09</v>
+        <v>560.65</v>
       </c>
       <c r="AI7">
         <v>558.51</v>
@@ -1569,7 +1626,7 @@
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>30.52</v>
+        <v>32.87</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1580,10 +1637,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>230.31</v>
+        <v>225.57</v>
       </c>
       <c r="D8">
-        <v>0.28</v>
+        <v>-2.06</v>
       </c>
       <c r="E8">
         <v>363.5</v>
@@ -1592,46 +1649,46 @@
         <v>210.4</v>
       </c>
       <c r="G8">
-        <v>-36.64</v>
+        <v>-37.94</v>
       </c>
       <c r="H8">
-        <v>9.460000000000001</v>
+        <v>7.21</v>
       </c>
       <c r="I8">
-        <v>5.18</v>
+        <v>-1.06</v>
       </c>
       <c r="J8">
-        <v>-1.46</v>
+        <v>-2.64</v>
       </c>
       <c r="K8">
-        <v>2.54</v>
+        <v>0.79</v>
       </c>
       <c r="L8">
-        <v>-35.3</v>
+        <v>-36.49</v>
       </c>
       <c r="M8">
-        <v>2.84</v>
+        <v>2.48</v>
       </c>
       <c r="N8">
         <v>12</v>
       </c>
       <c r="O8">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="P8">
-        <v>230.43</v>
+        <v>229.95</v>
       </c>
       <c r="Q8">
         <v>223.57</v>
       </c>
       <c r="R8">
-        <v>228.05</v>
+        <v>228.18</v>
       </c>
       <c r="S8">
-        <v>270.53</v>
+        <v>269.96</v>
       </c>
       <c r="T8">
-        <v>-14.87</v>
+        <v>-16.44</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1646,31 +1703,31 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>54.53</v>
+        <v>49.14</v>
       </c>
       <c r="Z8">
-        <v>-0.21</v>
+        <v>-0.23</v>
       </c>
       <c r="AA8">
-        <v>-1.85</v>
+        <v>-1.53</v>
       </c>
       <c r="AB8">
-        <v>1.64</v>
+        <v>1.29</v>
       </c>
       <c r="AC8">
-        <v>87.83</v>
+        <v>75.92</v>
       </c>
       <c r="AD8">
-        <v>92.23</v>
+        <v>85.23999999999999</v>
       </c>
       <c r="AE8">
-        <v>7.45</v>
+        <v>7.46</v>
       </c>
       <c r="AF8">
-        <v>-24.38</v>
+        <v>-69.34999999999999</v>
       </c>
       <c r="AG8">
-        <v>235.98</v>
+        <v>235.99</v>
       </c>
       <c r="AH8">
         <v>211.15</v>
@@ -1682,7 +1739,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>31.3</v>
+        <v>31.14</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1693,10 +1750,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>3602.3</v>
+        <v>3597.9</v>
       </c>
       <c r="D9">
-        <v>0.05</v>
+        <v>-0.12</v>
       </c>
       <c r="E9">
         <v>4497.5</v>
@@ -1705,46 +1762,46 @@
         <v>3308.9</v>
       </c>
       <c r="G9">
-        <v>-19.9</v>
+        <v>-20</v>
       </c>
       <c r="H9">
-        <v>8.869999999999999</v>
+        <v>8.73</v>
       </c>
       <c r="I9">
-        <v>-0.78</v>
+        <v>-0.02</v>
       </c>
       <c r="J9">
-        <v>-4.69</v>
+        <v>-5.06</v>
       </c>
       <c r="K9">
-        <v>-5.33</v>
+        <v>-5.16</v>
       </c>
       <c r="L9">
-        <v>-10.46</v>
+        <v>-10.1</v>
       </c>
       <c r="M9">
-        <v>18.29</v>
+        <v>18.43</v>
       </c>
       <c r="N9">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="O9">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="P9">
-        <v>3601.2</v>
+        <v>3601.06</v>
       </c>
       <c r="Q9">
-        <v>3629.35</v>
+        <v>3621.4</v>
       </c>
       <c r="R9">
-        <v>3759.08</v>
+        <v>3755.02</v>
       </c>
       <c r="S9">
-        <v>3725.71</v>
+        <v>3723.39</v>
       </c>
       <c r="T9">
-        <v>-3.31</v>
+        <v>-3.37</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1759,34 +1816,34 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>39.85</v>
+        <v>39.32</v>
       </c>
       <c r="Z9">
-        <v>-50.44</v>
+        <v>-48.05</v>
       </c>
       <c r="AA9">
-        <v>-57.04</v>
+        <v>-55.24</v>
       </c>
       <c r="AB9">
-        <v>6.6</v>
+        <v>7.19</v>
       </c>
       <c r="AC9">
-        <v>81.2</v>
+        <v>82.73</v>
       </c>
       <c r="AD9">
-        <v>80.73999999999999</v>
+        <v>81.93000000000001</v>
       </c>
       <c r="AE9">
-        <v>70.16</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="AF9">
-        <v>-61.06</v>
+        <v>-68.76000000000001</v>
       </c>
       <c r="AG9">
-        <v>3757.12</v>
+        <v>3734.69</v>
       </c>
       <c r="AH9">
-        <v>3501.58</v>
+        <v>3508.1</v>
       </c>
       <c r="AI9">
         <v>3794.41</v>
@@ -1795,7 +1852,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>13.6</v>
+        <v>13.08</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1806,10 +1863,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>1640</v>
+        <v>1643</v>
       </c>
       <c r="D10">
-        <v>0.31</v>
+        <v>0.18</v>
       </c>
       <c r="E10">
         <v>1768.4</v>
@@ -1818,46 +1875,46 @@
         <v>1326.2</v>
       </c>
       <c r="G10">
-        <v>-7.26</v>
+        <v>-7.09</v>
       </c>
       <c r="H10">
-        <v>23.66</v>
+        <v>23.89</v>
       </c>
       <c r="I10">
-        <v>-0.55</v>
+        <v>-0.33</v>
       </c>
       <c r="J10">
-        <v>12.73</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="K10">
-        <v>17.74</v>
+        <v>19.49</v>
       </c>
       <c r="L10">
-        <v>12.35</v>
+        <v>11.77</v>
       </c>
       <c r="M10">
-        <v>7.54</v>
+        <v>7.57</v>
       </c>
       <c r="N10">
         <v>77</v>
       </c>
       <c r="O10">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P10">
-        <v>1641.14</v>
+        <v>1640.04</v>
       </c>
       <c r="Q10">
-        <v>1596.21</v>
+        <v>1604.15</v>
       </c>
       <c r="R10">
-        <v>1508.97</v>
+        <v>1510.96</v>
       </c>
       <c r="S10">
-        <v>1499.61</v>
+        <v>1500.58</v>
       </c>
       <c r="T10">
-        <v>9.359999999999999</v>
+        <v>9.49</v>
       </c>
       <c r="U10" t="s">
         <v>48</v>
@@ -1872,34 +1929,34 @@
         <v>3</v>
       </c>
       <c r="Y10">
-        <v>65.33</v>
+        <v>65.81</v>
       </c>
       <c r="Z10">
-        <v>45.41</v>
+        <v>43.65</v>
       </c>
       <c r="AA10">
-        <v>46.18</v>
+        <v>45.67</v>
       </c>
       <c r="AB10">
-        <v>-0.77</v>
+        <v>-2.02</v>
       </c>
       <c r="AC10">
-        <v>26.29</v>
+        <v>30.94</v>
       </c>
       <c r="AD10">
-        <v>37.65</v>
+        <v>31.17</v>
       </c>
       <c r="AE10">
-        <v>43.01</v>
+        <v>41.39</v>
       </c>
       <c r="AF10">
-        <v>-9.02</v>
+        <v>-39.13</v>
       </c>
       <c r="AG10">
-        <v>1709.28</v>
+        <v>1705.85</v>
       </c>
       <c r="AH10">
-        <v>1483.14</v>
+        <v>1502.44</v>
       </c>
       <c r="AI10">
         <v>1527.05</v>
@@ -1908,7 +1965,7 @@
         <v>50</v>
       </c>
       <c r="AK10">
-        <v>40.45</v>
+        <v>39.96</v>
       </c>
     </row>
   </sheetData>
@@ -2049,7 +2106,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F83"/>
+  <dimension ref="A1:F82"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2069,1348 +2126,1369 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="D2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="A6" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-11.12</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C8" s="7">
         <v>-11.8</v>
       </c>
-      <c r="E7" s="6">
-        <v>-0.68</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="D8" s="7">
+        <v>-12.02</v>
+      </c>
+      <c r="E8" s="8">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>13.5</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C9" s="7">
         <v>12.39</v>
       </c>
-      <c r="E8" s="6">
-        <v>-1.11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="D9" s="7">
+        <v>9.48</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-2.91</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>21.29</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C10" s="7">
         <v>20.96</v>
       </c>
-      <c r="E9" s="6">
+      <c r="D10" s="7">
+        <v>19.87</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-1.09</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="7">
+        <v>2.1</v>
+      </c>
+      <c r="D11" s="7">
+        <v>1.07</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-1.03</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="7">
+        <v>6.24</v>
+      </c>
+      <c r="D12" s="7">
+        <v>6.95</v>
+      </c>
+      <c r="E12" s="9">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="7">
+        <v>1.58</v>
+      </c>
+      <c r="D13" s="7">
+        <v>0.53</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-1.05</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="7">
+        <v>-1.46</v>
+      </c>
+      <c r="D14" s="7">
+        <v>-2.64</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-1.18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="7">
+        <v>-4.69</v>
+      </c>
+      <c r="D15" s="7">
+        <v>-5.06</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-0.37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="7">
+        <v>12.73</v>
+      </c>
+      <c r="D16" s="7">
+        <v>9.210000000000001</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-3.52</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-2.42</v>
+      </c>
+      <c r="D17" s="7">
+        <v>0.58</v>
+      </c>
+      <c r="E17" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="7">
+        <v>2.58</v>
+      </c>
+      <c r="D18" s="7">
+        <v>0.79</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-1.79</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="7">
+        <v>1.68</v>
+      </c>
+      <c r="D19" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-1.63</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="7">
+        <v>-2.86</v>
+      </c>
+      <c r="D20" s="7">
+        <v>-3.75</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-0.89</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-1.19</v>
+      </c>
+      <c r="D21" s="7">
+        <v>-2.77</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-1.58</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="7">
+        <v>5.95</v>
+      </c>
+      <c r="D22" s="7">
+        <v>2.75</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-3.2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="7">
+        <v>5.18</v>
+      </c>
+      <c r="D23" s="7">
+        <v>-1.06</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-6.24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="7">
+        <v>-0.78</v>
+      </c>
+      <c r="D24" s="7">
+        <v>-0.02</v>
+      </c>
+      <c r="E24" s="9">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="7">
+        <v>-0.55</v>
+      </c>
+      <c r="D25" s="7">
         <v>-0.33</v>
       </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="E25" s="9">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="7">
+        <v>2.3</v>
+      </c>
+      <c r="D26" s="7">
+        <v>2.88</v>
+      </c>
+      <c r="E26" s="9">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="7">
+        <v>9.9</v>
+      </c>
+      <c r="D27" s="7">
+        <v>7.72</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-2.18</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="7">
+        <v>59.53</v>
+      </c>
+      <c r="D28" s="7">
+        <v>55.51</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-4.02</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="5">
-        <v>5.04</v>
-      </c>
-      <c r="D10" s="5">
-        <v>2.1</v>
-      </c>
-      <c r="E10" s="6">
-        <v>-2.94</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="B29" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="7">
+        <v>6.81</v>
+      </c>
+      <c r="D29" s="7">
+        <v>7.43</v>
+      </c>
+      <c r="E29" s="9">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="5">
-        <v>3.54</v>
-      </c>
-      <c r="D11" s="5">
-        <v>6.24</v>
-      </c>
-      <c r="E11" s="7">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="B30" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="7">
+        <v>27.93</v>
+      </c>
+      <c r="D30" s="7">
+        <v>30.01</v>
+      </c>
+      <c r="E30" s="9">
+        <v>2.08</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="5">
-        <v>-0.23</v>
-      </c>
-      <c r="D12" s="5">
-        <v>1.58</v>
-      </c>
-      <c r="E12" s="7">
-        <v>1.81</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="B31" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="7">
+        <v>-8.51</v>
+      </c>
+      <c r="D31" s="7">
+        <v>-11.92</v>
+      </c>
+      <c r="E31" s="8">
+        <v>-3.41</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="5">
-        <v>-0.89</v>
-      </c>
-      <c r="D13" s="5">
-        <v>-1.46</v>
-      </c>
-      <c r="E13" s="6">
-        <v>-0.57</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="B32" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="7">
+        <v>-35.3</v>
+      </c>
+      <c r="D32" s="7">
+        <v>-36.49</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-1.19</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="5">
-        <v>-3.53</v>
-      </c>
-      <c r="D14" s="5">
-        <v>-4.69</v>
-      </c>
-      <c r="E14" s="6">
-        <v>-1.16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="B33" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="7">
+        <v>-10.46</v>
+      </c>
+      <c r="D33" s="7">
+        <v>-10.1</v>
+      </c>
+      <c r="E33" s="9">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="5">
-        <v>14.63</v>
-      </c>
-      <c r="D15" s="5">
-        <v>12.73</v>
-      </c>
-      <c r="E15" s="6">
+      <c r="B34" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="7">
+        <v>12.35</v>
+      </c>
+      <c r="D34" s="7">
+        <v>11.77</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-0.58</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="7">
+        <v>-11.5</v>
+      </c>
+      <c r="D35" s="7">
+        <v>-9.81</v>
+      </c>
+      <c r="E35" s="9">
+        <v>1.69</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="7">
+        <v>10.74</v>
+      </c>
+      <c r="D36" s="7">
+        <v>11.19</v>
+      </c>
+      <c r="E36" s="9">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="7">
+        <v>26.1</v>
+      </c>
+      <c r="D37" s="7">
+        <v>24.59</v>
+      </c>
+      <c r="E37" s="8">
+        <v>-1.51</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="7">
+        <v>19.44</v>
+      </c>
+      <c r="D38" s="7">
+        <v>17.54</v>
+      </c>
+      <c r="E38" s="8">
         <v>-1.9</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="7">
+        <v>9.74</v>
+      </c>
+      <c r="D39" s="7">
+        <v>9.92</v>
+      </c>
+      <c r="E39" s="9">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="7">
+        <v>-5.23</v>
+      </c>
+      <c r="D40" s="7">
+        <v>-8.289999999999999</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-3.06</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="7">
+        <v>2.54</v>
+      </c>
+      <c r="D41" s="7">
+        <v>0.79</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-1.75</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="7">
+        <v>-5.33</v>
+      </c>
+      <c r="D42" s="7">
+        <v>-5.16</v>
+      </c>
+      <c r="E42" s="9">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="7">
+        <v>17.74</v>
+      </c>
+      <c r="D43" s="7">
+        <v>19.49</v>
+      </c>
+      <c r="E43" s="9">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="5">
-        <v>0.47</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-2.42</v>
-      </c>
-      <c r="E16" s="6">
-        <v>-2.89</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="B44" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="7">
+        <v>-16.46</v>
+      </c>
+      <c r="D44" s="7">
+        <v>-15.75</v>
+      </c>
+      <c r="E44" s="9">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="5">
-        <v>3.05</v>
-      </c>
-      <c r="D17" s="5">
-        <v>2.58</v>
-      </c>
-      <c r="E17" s="6">
-        <v>-0.47</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="B45" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="7">
+        <v>-7.51</v>
+      </c>
+      <c r="D45" s="7">
+        <v>-9</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-1.49</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="5">
-        <v>5.88</v>
-      </c>
-      <c r="D18" s="5">
-        <v>1.68</v>
-      </c>
-      <c r="E18" s="6">
+      <c r="B46" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="7">
+        <v>0</v>
+      </c>
+      <c r="D46" s="7">
+        <v>-3.27</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-3.27</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="7">
+        <v>-8.26</v>
+      </c>
+      <c r="D47" s="7">
+        <v>-9.26</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="7">
+        <v>-7.08</v>
+      </c>
+      <c r="D48" s="7">
+        <v>-7.53</v>
+      </c>
+      <c r="E48" s="8">
+        <v>-0.45</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="7">
+        <v>-10.81</v>
+      </c>
+      <c r="D49" s="7">
+        <v>-12.69</v>
+      </c>
+      <c r="E49" s="8">
+        <v>-1.88</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="7">
+        <v>-36.64</v>
+      </c>
+      <c r="D50" s="7">
+        <v>-37.94</v>
+      </c>
+      <c r="E50" s="8">
+        <v>-1.3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="7">
+        <v>-19.9</v>
+      </c>
+      <c r="D51" s="7">
+        <v>-20</v>
+      </c>
+      <c r="E51" s="8">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="7">
+        <v>-7.26</v>
+      </c>
+      <c r="D52" s="7">
+        <v>-7.09</v>
+      </c>
+      <c r="E52" s="9">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="7">
+        <v>409.5</v>
+      </c>
+      <c r="D53" s="7">
+        <v>413</v>
+      </c>
+      <c r="E53" s="9">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="7">
+        <v>3517</v>
+      </c>
+      <c r="D54" s="7">
+        <v>3460.1</v>
+      </c>
+      <c r="E54" s="8">
+        <v>-56.9</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="7">
+        <v>412.3</v>
+      </c>
+      <c r="D55" s="7">
+        <v>398.8</v>
+      </c>
+      <c r="E55" s="8">
+        <v>-13.5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="7">
+        <v>386.85</v>
+      </c>
+      <c r="D56" s="7">
+        <v>382.65</v>
+      </c>
+      <c r="E56" s="8">
         <v>-4.2</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+    <row r="57" spans="1:5">
+      <c r="A57" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="7">
+        <v>411.35</v>
+      </c>
+      <c r="D57" s="7">
+        <v>409.35</v>
+      </c>
+      <c r="E57" s="8">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="7">
+        <v>607.85</v>
+      </c>
+      <c r="D58" s="7">
+        <v>595</v>
+      </c>
+      <c r="E58" s="8">
+        <v>-12.85</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="7">
+        <v>230.31</v>
+      </c>
+      <c r="D59" s="7">
+        <v>225.57</v>
+      </c>
+      <c r="E59" s="8">
+        <v>-4.74</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="7">
+        <v>3602.3</v>
+      </c>
+      <c r="D60" s="7">
+        <v>3597.9</v>
+      </c>
+      <c r="E60" s="8">
+        <v>-4.4</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C61" s="7">
+        <v>1640</v>
+      </c>
+      <c r="D61" s="7">
+        <v>1643</v>
+      </c>
+      <c r="E61" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C62" s="7">
+        <v>34</v>
+      </c>
+      <c r="D62" s="7">
+        <v>45</v>
+      </c>
+      <c r="E62" s="9">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C63" s="7">
+        <v>45</v>
+      </c>
+      <c r="D63" s="7">
+        <v>23</v>
+      </c>
+      <c r="E63" s="8">
+        <v>-22</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C64" s="7">
+        <v>23</v>
+      </c>
+      <c r="D64" s="7">
+        <v>34</v>
+      </c>
+      <c r="E64" s="9">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="7">
+        <v>35.42</v>
+      </c>
+      <c r="D65" s="7">
+        <v>38.16</v>
+      </c>
+      <c r="E65" s="9">
+        <v>2.74</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="7">
+        <v>69.52</v>
+      </c>
+      <c r="D66" s="7">
+        <v>63.49</v>
+      </c>
+      <c r="E66" s="8">
+        <v>-6.03</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="7">
+        <v>69.75</v>
+      </c>
+      <c r="D67" s="7">
+        <v>62.47</v>
+      </c>
+      <c r="E67" s="8">
+        <v>-7.28</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="5">
-        <v>-1.55</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-2.86</v>
-      </c>
-      <c r="E19" s="6">
-        <v>-1.31</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="B68" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="7">
+        <v>58.13</v>
+      </c>
+      <c r="D68" s="7">
+        <v>53.86</v>
+      </c>
+      <c r="E68" s="8">
+        <v>-4.27</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="5">
-        <v>-1.66</v>
-      </c>
-      <c r="D20" s="5">
-        <v>-1.19</v>
-      </c>
-      <c r="E20" s="7">
-        <v>0.47</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="B69" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="7">
+        <v>56.66</v>
+      </c>
+      <c r="D69" s="7">
+        <v>55.39</v>
+      </c>
+      <c r="E69" s="8">
+        <v>-1.27</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="5">
-        <v>4.31</v>
-      </c>
-      <c r="D21" s="5">
-        <v>5.95</v>
-      </c>
-      <c r="E21" s="7">
-        <v>1.64</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="B70" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="7">
+        <v>60.66</v>
+      </c>
+      <c r="D70" s="7">
+        <v>53.23</v>
+      </c>
+      <c r="E70" s="8">
+        <v>-7.43</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="5">
-        <v>5.15</v>
-      </c>
-      <c r="D22" s="5">
-        <v>5.18</v>
-      </c>
-      <c r="E22" s="7">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="B71" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="7">
+        <v>54.53</v>
+      </c>
+      <c r="D71" s="7">
+        <v>49.14</v>
+      </c>
+      <c r="E71" s="8">
+        <v>-5.39</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C72" s="7">
+        <v>39.85</v>
+      </c>
+      <c r="D72" s="7">
+        <v>39.32</v>
+      </c>
+      <c r="E72" s="8">
+        <v>-0.53</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="5">
-        <v>-0.99</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-0.55</v>
-      </c>
-      <c r="E23" s="7">
-        <v>0.44</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="B73" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C73" s="7">
+        <v>65.33</v>
+      </c>
+      <c r="D73" s="7">
+        <v>65.81</v>
+      </c>
+      <c r="E73" s="9">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="5">
-        <v>2.71</v>
-      </c>
-      <c r="D24" s="5">
-        <v>2.3</v>
-      </c>
-      <c r="E24" s="6">
-        <v>-0.41</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="B74" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="7">
+        <v>-60.58</v>
+      </c>
+      <c r="D74" s="7">
+        <v>486.43</v>
+      </c>
+      <c r="E74" s="9">
+        <v>547.01</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="5">
-        <v>10.85</v>
-      </c>
-      <c r="D25" s="5">
-        <v>9.9</v>
-      </c>
-      <c r="E25" s="6">
-        <v>-0.95</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="B75" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="7">
+        <v>-3.17</v>
+      </c>
+      <c r="D75" s="7">
+        <v>-10.8</v>
+      </c>
+      <c r="E75" s="8">
+        <v>-7.63</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="5">
-        <v>58.01</v>
-      </c>
-      <c r="D26" s="5">
-        <v>59.53</v>
-      </c>
-      <c r="E26" s="7">
-        <v>1.52</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="B76" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="7">
+        <v>-49.24</v>
+      </c>
+      <c r="D76" s="7">
+        <v>-76.97</v>
+      </c>
+      <c r="E76" s="8">
+        <v>-27.73</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="5">
-        <v>4.97</v>
-      </c>
-      <c r="D27" s="5">
-        <v>6.81</v>
-      </c>
-      <c r="E27" s="7">
-        <v>1.84</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="B77" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="7">
+        <v>-66.05</v>
+      </c>
+      <c r="D77" s="7">
+        <v>-80.16</v>
+      </c>
+      <c r="E77" s="8">
+        <v>-14.11</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="5">
-        <v>22.98</v>
-      </c>
-      <c r="D28" s="5">
-        <v>27.93</v>
-      </c>
-      <c r="E28" s="7">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="B78" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="7">
+        <v>-48.14</v>
+      </c>
+      <c r="D78" s="7">
+        <v>-69.63</v>
+      </c>
+      <c r="E78" s="8">
+        <v>-21.49</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-10.86</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-8.51</v>
-      </c>
-      <c r="E29" s="7">
-        <v>2.35</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="B79" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="7">
+        <v>413.42</v>
+      </c>
+      <c r="D79" s="7">
+        <v>69.17</v>
+      </c>
+      <c r="E79" s="8">
+        <v>-344.25</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-35.45</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-35.3</v>
-      </c>
-      <c r="E30" s="7">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
+      <c r="B80" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="7">
+        <v>-24.38</v>
+      </c>
+      <c r="D80" s="7">
+        <v>-69.34999999999999</v>
+      </c>
+      <c r="E80" s="8">
+        <v>-44.97</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="5">
-        <v>-10.36</v>
-      </c>
-      <c r="D31" s="5">
-        <v>-10.46</v>
-      </c>
-      <c r="E31" s="6">
-        <v>-0.1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
+      <c r="B81" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81" s="7">
+        <v>-61.06</v>
+      </c>
+      <c r="D81" s="7">
+        <v>-68.76000000000001</v>
+      </c>
+      <c r="E81" s="8">
+        <v>-7.7</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="5">
-        <v>14.83</v>
-      </c>
-      <c r="D32" s="5">
-        <v>12.35</v>
-      </c>
-      <c r="E32" s="6">
-        <v>-2.48</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="5">
-        <v>-14.02</v>
-      </c>
-      <c r="D33" s="5">
-        <v>-11.5</v>
-      </c>
-      <c r="E33" s="7">
-        <v>2.52</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="5">
-        <v>7.89</v>
-      </c>
-      <c r="D34" s="5">
-        <v>10.74</v>
-      </c>
-      <c r="E34" s="7">
-        <v>2.85</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="5">
-        <v>21.18</v>
-      </c>
-      <c r="D35" s="5">
-        <v>26.1</v>
-      </c>
-      <c r="E35" s="7">
-        <v>4.92</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="5">
-        <v>16.1</v>
-      </c>
-      <c r="D36" s="5">
-        <v>19.44</v>
-      </c>
-      <c r="E36" s="7">
-        <v>3.34</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="5">
-        <v>4.57</v>
-      </c>
-      <c r="D37" s="5">
-        <v>9.74</v>
-      </c>
-      <c r="E37" s="7">
-        <v>5.17</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="5">
-        <v>-9.07</v>
-      </c>
-      <c r="D38" s="5">
-        <v>-5.23</v>
-      </c>
-      <c r="E38" s="7">
-        <v>3.84</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="5">
-        <v>-2.16</v>
-      </c>
-      <c r="D39" s="5">
-        <v>2.54</v>
-      </c>
-      <c r="E39" s="7">
-        <v>4.7</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="5">
-        <v>-7.84</v>
-      </c>
-      <c r="D40" s="5">
-        <v>-5.33</v>
-      </c>
-      <c r="E40" s="7">
-        <v>2.51</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="5">
-        <v>12.19</v>
-      </c>
-      <c r="D41" s="5">
-        <v>17.74</v>
-      </c>
-      <c r="E41" s="7">
-        <v>5.55</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="5">
-        <v>-16.26</v>
-      </c>
-      <c r="D42" s="5">
-        <v>-16.46</v>
-      </c>
-      <c r="E42" s="6">
-        <v>-0.2</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="5">
-        <v>-7.9</v>
-      </c>
-      <c r="D43" s="5">
-        <v>-7.51</v>
-      </c>
-      <c r="E43" s="7">
-        <v>0.39</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="5">
-        <v>-8.34</v>
-      </c>
-      <c r="D44" s="5">
-        <v>-8.26</v>
-      </c>
-      <c r="E44" s="7">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="5">
-        <v>-9.039999999999999</v>
-      </c>
-      <c r="D45" s="5">
-        <v>-7.08</v>
-      </c>
-      <c r="E45" s="7">
-        <v>1.96</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="5">
-        <v>-13.47</v>
-      </c>
-      <c r="D46" s="5">
-        <v>-10.81</v>
-      </c>
-      <c r="E46" s="7">
-        <v>2.66</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="5">
-        <v>-36.82</v>
-      </c>
-      <c r="D47" s="5">
-        <v>-36.64</v>
-      </c>
-      <c r="E47" s="7">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="5">
-        <v>-19.95</v>
-      </c>
-      <c r="D48" s="5">
-        <v>-19.9</v>
-      </c>
-      <c r="E48" s="7">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="5">
-        <v>-7.54</v>
-      </c>
-      <c r="D49" s="5">
-        <v>-7.26</v>
-      </c>
-      <c r="E49" s="7">
-        <v>0.28</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C50" s="5">
-        <v>410.5</v>
-      </c>
-      <c r="D50" s="5">
-        <v>409.5</v>
-      </c>
-      <c r="E50" s="6">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C51" s="5">
-        <v>3502</v>
-      </c>
-      <c r="D51" s="5">
-        <v>3517</v>
-      </c>
-      <c r="E51" s="7">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="5">
-        <v>408.45</v>
-      </c>
-      <c r="D52" s="5">
-        <v>412.3</v>
-      </c>
-      <c r="E52" s="7">
-        <v>3.85</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="5">
-        <v>386.55</v>
-      </c>
-      <c r="D53" s="5">
-        <v>386.85</v>
-      </c>
-      <c r="E53" s="7">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="5">
-        <v>402.7</v>
-      </c>
-      <c r="D54" s="5">
-        <v>411.35</v>
-      </c>
-      <c r="E54" s="7">
-        <v>8.65</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="5">
-        <v>589.7</v>
-      </c>
-      <c r="D55" s="5">
-        <v>607.85</v>
-      </c>
-      <c r="E55" s="7">
-        <v>18.15</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="5">
-        <v>229.66</v>
-      </c>
-      <c r="D56" s="5">
-        <v>230.31</v>
-      </c>
-      <c r="E56" s="7">
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="5">
-        <v>3600.4</v>
-      </c>
-      <c r="D57" s="5">
-        <v>3602.3</v>
-      </c>
-      <c r="E57" s="7">
-        <v>1.9</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="5">
-        <v>1635</v>
-      </c>
-      <c r="D58" s="5">
-        <v>1640</v>
-      </c>
-      <c r="E58" s="7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C59" s="5">
-        <v>45</v>
-      </c>
-      <c r="D59" s="5">
-        <v>34</v>
-      </c>
-      <c r="E59" s="6">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C60" s="5">
-        <v>66</v>
-      </c>
-      <c r="D60" s="5">
-        <v>55</v>
-      </c>
-      <c r="E60" s="6">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C61" s="5">
-        <v>55</v>
-      </c>
-      <c r="D61" s="5">
-        <v>66</v>
-      </c>
-      <c r="E61" s="7">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C62" s="5">
-        <v>77</v>
-      </c>
-      <c r="D62" s="5">
-        <v>88</v>
-      </c>
-      <c r="E62" s="7">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C63" s="5">
-        <v>23</v>
-      </c>
-      <c r="D63" s="5">
-        <v>45</v>
-      </c>
-      <c r="E63" s="7">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C64" s="5">
-        <v>34</v>
-      </c>
-      <c r="D64" s="5">
-        <v>23</v>
-      </c>
-      <c r="E64" s="6">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C65" s="5">
-        <v>88</v>
-      </c>
-      <c r="D65" s="5">
-        <v>77</v>
-      </c>
-      <c r="E65" s="6">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="5">
-        <v>35.84</v>
-      </c>
-      <c r="D66" s="5">
-        <v>35.42</v>
-      </c>
-      <c r="E66" s="6">
-        <v>-0.42</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="5">
-        <v>68.79000000000001</v>
-      </c>
-      <c r="D67" s="5">
-        <v>69.52</v>
-      </c>
-      <c r="E67" s="7">
-        <v>0.73</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="5">
-        <v>68.78</v>
-      </c>
-      <c r="D68" s="5">
-        <v>69.75</v>
-      </c>
-      <c r="E68" s="7">
-        <v>0.97</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="5">
-        <v>57.91</v>
-      </c>
-      <c r="D69" s="5">
-        <v>58.13</v>
-      </c>
-      <c r="E69" s="7">
-        <v>0.22</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="5">
-        <v>52.29</v>
-      </c>
-      <c r="D70" s="5">
-        <v>56.66</v>
-      </c>
-      <c r="E70" s="7">
-        <v>4.37</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="5">
-        <v>51.85</v>
-      </c>
-      <c r="D71" s="5">
-        <v>60.66</v>
-      </c>
-      <c r="E71" s="7">
-        <v>8.81</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C72" s="5">
-        <v>53.88</v>
-      </c>
-      <c r="D72" s="5">
-        <v>54.53</v>
-      </c>
-      <c r="E72" s="7">
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C73" s="5">
-        <v>39.52</v>
-      </c>
-      <c r="D73" s="5">
-        <v>39.85</v>
-      </c>
-      <c r="E73" s="7">
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C74" s="5">
-        <v>64.56</v>
-      </c>
-      <c r="D74" s="5">
-        <v>65.33</v>
-      </c>
-      <c r="E74" s="7">
-        <v>0.77</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B75" s="3" t="s">
+      <c r="B82" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C75" s="5">
-        <v>-44.88</v>
-      </c>
-      <c r="D75" s="5">
-        <v>-60.58</v>
-      </c>
-      <c r="E75" s="6">
-        <v>-15.7</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="5">
-        <v>32.11</v>
-      </c>
-      <c r="D76" s="5">
-        <v>-3.17</v>
-      </c>
-      <c r="E76" s="6">
-        <v>-35.28</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="5">
-        <v>-28.49</v>
-      </c>
-      <c r="D77" s="5">
-        <v>-49.24</v>
-      </c>
-      <c r="E77" s="6">
-        <v>-20.75</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="5">
-        <v>-75.17</v>
-      </c>
-      <c r="D78" s="5">
-        <v>-66.05</v>
-      </c>
-      <c r="E78" s="7">
-        <v>9.119999999999999</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="5">
-        <v>56.68</v>
-      </c>
-      <c r="D79" s="5">
-        <v>-48.14</v>
-      </c>
-      <c r="E79" s="6">
-        <v>-104.82</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="5">
-        <v>98.98</v>
-      </c>
-      <c r="D80" s="5">
-        <v>413.42</v>
-      </c>
-      <c r="E80" s="7">
-        <v>314.44</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="5">
-        <v>-62.86</v>
-      </c>
-      <c r="D81" s="5">
-        <v>-24.38</v>
-      </c>
-      <c r="E81" s="7">
-        <v>38.48</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C82" s="5">
-        <v>-65.81999999999999</v>
-      </c>
-      <c r="D82" s="5">
-        <v>-61.06</v>
-      </c>
-      <c r="E82" s="7">
-        <v>4.76</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="A83" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C83" s="5">
-        <v>111.31</v>
-      </c>
-      <c r="D83" s="5">
+      <c r="C82" s="7">
         <v>-9.02</v>
       </c>
-      <c r="E83" s="6">
-        <v>-120.33</v>
+      <c r="D82" s="7">
+        <v>-39.13</v>
+      </c>
+      <c r="E82" s="8">
+        <v>-30.11</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3430,60 +3508,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>65</v>
+      <c r="B1" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="12">
         <v>60.16</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="13">
         <v>9</v>
       </c>
-      <c r="D2" s="10">
-        <v>56.6</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="12">
+        <v>53.4</v>
+      </c>
+      <c r="E2" s="12">
         <v>70</v>
       </c>
-      <c r="F2" s="10">
-        <v>4.2</v>
-      </c>
-      <c r="G2" s="10">
-        <v>7.1</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="12">
+        <v>3</v>
+      </c>
+      <c r="G2" s="12">
+        <v>6.7</v>
+      </c>
+      <c r="H2" s="12">
         <v>55.4</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="12">
         <v>20</v>
       </c>
     </row>
@@ -3585,61 +3663,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="14" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="13">
-        <v>0.3591</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.3411999999999999</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.2392</v>
-      </c>
-      <c r="D2" s="13">
-        <v>0.1829</v>
-      </c>
-      <c r="E2" s="13">
-        <v>0.1187</v>
-      </c>
-      <c r="F2" s="13">
-        <v>0.095</v>
-      </c>
-      <c r="G2" s="13">
-        <v>0.07539999999999999</v>
-      </c>
-      <c r="H2" s="13">
-        <v>0.0284</v>
-      </c>
-      <c r="I2" s="13">
-        <v>-0.09039999999999999</v>
+      <c r="A2" s="15">
+        <v>0.3573</v>
+      </c>
+      <c r="B2" s="15">
+        <v>0.3305</v>
+      </c>
+      <c r="C2" s="15">
+        <v>0.2292</v>
+      </c>
+      <c r="D2" s="15">
+        <v>0.1843</v>
+      </c>
+      <c r="E2" s="15">
+        <v>0.1198</v>
+      </c>
+      <c r="F2" s="15">
+        <v>0.0969</v>
+      </c>
+      <c r="G2" s="15">
+        <v>0.0757</v>
+      </c>
+      <c r="H2" s="15">
+        <v>0.0248</v>
+      </c>
+      <c r="I2" s="15">
+        <v>-0.0872</v>
       </c>
     </row>
   </sheetData>

--- a/MAHINDRA_GROUP_Technical_Metrics.xlsx
+++ b/MAHINDRA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="74">
   <si>
     <t>Symbol</t>
   </si>
@@ -193,34 +193,16 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>Left 52W High Zone</t>
-  </si>
-  <si>
-    <t>0.0% → -3.3%</t>
-  </si>
-  <si>
-    <t>⚪ NEUTRAL</t>
-  </si>
-  <si>
-    <t>0.0%</t>
-  </si>
-  <si>
-    <t>-3.3%</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>54.5 → 49.1</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>54.5</t>
-  </si>
-  <si>
-    <t>49.1</t>
+    <t>50 DMA &gt; 200 DMA</t>
+  </si>
+  <si>
+    <t>No → Yes</t>
+  </si>
+  <si>
+    <t>🟢 GOLDEN CROSS</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -272,7 +254,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -306,7 +288,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF1F4E79"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -318,15 +300,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -353,19 +328,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -435,7 +404,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -443,15 +412,14 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -460,7 +428,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -959,10 +927,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>413</v>
+        <v>411.7</v>
       </c>
       <c r="D2">
-        <v>0.85</v>
+        <v>-0.31</v>
       </c>
       <c r="E2">
         <v>490.2</v>
@@ -971,46 +939,46 @@
         <v>379.2</v>
       </c>
       <c r="G2">
-        <v>-15.75</v>
+        <v>-16.01</v>
       </c>
       <c r="H2">
-        <v>8.91</v>
+        <v>8.57</v>
       </c>
       <c r="I2">
-        <v>0.58</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="J2">
-        <v>-12.02</v>
+        <v>-10.22</v>
       </c>
       <c r="K2">
-        <v>-9.81</v>
+        <v>-9.67</v>
       </c>
       <c r="L2">
-        <v>2.88</v>
+        <v>3.61</v>
       </c>
       <c r="M2">
-        <v>11.98</v>
+        <v>11.95</v>
       </c>
       <c r="N2">
         <v>45</v>
       </c>
       <c r="O2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="P2">
-        <v>411.67</v>
+        <v>411</v>
       </c>
       <c r="Q2">
-        <v>430.23</v>
+        <v>427.76</v>
       </c>
       <c r="R2">
-        <v>447.35</v>
+        <v>446.68</v>
       </c>
       <c r="S2">
-        <v>438.67</v>
+        <v>438.6</v>
       </c>
       <c r="T2">
-        <v>-5.85</v>
+        <v>-6.13</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1025,34 +993,34 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>38.16</v>
+        <v>37.52</v>
       </c>
       <c r="Z2">
-        <v>-12.9</v>
+        <v>-12.42</v>
       </c>
       <c r="AA2">
-        <v>-12.26</v>
+        <v>-12.29</v>
       </c>
       <c r="AB2">
-        <v>-0.64</v>
+        <v>-0.12</v>
       </c>
       <c r="AC2">
-        <v>52.05</v>
+        <v>73.73</v>
       </c>
       <c r="AD2">
-        <v>36.65</v>
+        <v>51.22</v>
       </c>
       <c r="AE2">
-        <v>12.33</v>
+        <v>12.31</v>
       </c>
       <c r="AF2">
-        <v>486.43</v>
+        <v>-31.88</v>
       </c>
       <c r="AG2">
-        <v>485.62</v>
+        <v>481.75</v>
       </c>
       <c r="AH2">
-        <v>374.85</v>
+        <v>373.78</v>
       </c>
       <c r="AI2">
         <v>446.81</v>
@@ -1061,7 +1029,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>43.77</v>
+        <v>39.15</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1072,10 +1040,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>3460.1</v>
+        <v>3403.6</v>
       </c>
       <c r="D3">
-        <v>-1.62</v>
+        <v>-1.63</v>
       </c>
       <c r="E3">
         <v>3802.4</v>
@@ -1084,46 +1052,46 @@
         <v>2931.1</v>
       </c>
       <c r="G3">
-        <v>-9</v>
+        <v>-10.49</v>
       </c>
       <c r="H3">
-        <v>18.05</v>
+        <v>16.12</v>
       </c>
       <c r="I3">
-        <v>0.79</v>
+        <v>-1.5</v>
       </c>
       <c r="J3">
-        <v>9.48</v>
+        <v>10.03</v>
       </c>
       <c r="K3">
-        <v>11.19</v>
+        <v>7.24</v>
       </c>
       <c r="L3">
-        <v>7.72</v>
+        <v>5.46</v>
       </c>
       <c r="M3">
-        <v>35.73</v>
+        <v>35.37</v>
       </c>
       <c r="N3">
         <v>55</v>
       </c>
       <c r="O3">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P3">
-        <v>3468.1</v>
+        <v>3457.74</v>
       </c>
       <c r="Q3">
-        <v>3296.47</v>
+        <v>3312.51</v>
       </c>
       <c r="R3">
-        <v>3169.03</v>
+        <v>3177.13</v>
       </c>
       <c r="S3">
-        <v>3359.23</v>
+        <v>3358.13</v>
       </c>
       <c r="T3">
-        <v>3</v>
+        <v>1.35</v>
       </c>
       <c r="U3" t="s">
         <v>48</v>
@@ -1138,34 +1106,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>63.49</v>
+        <v>58.1</v>
       </c>
       <c r="Z3">
-        <v>93.29000000000001</v>
+        <v>87.17</v>
       </c>
       <c r="AA3">
-        <v>74.14</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="AB3">
-        <v>19.15</v>
+        <v>10.42</v>
       </c>
       <c r="AC3">
-        <v>87.81</v>
+        <v>66.42</v>
       </c>
       <c r="AD3">
-        <v>88.39</v>
+        <v>80.97</v>
       </c>
       <c r="AE3">
-        <v>78.2</v>
+        <v>77.48999999999999</v>
       </c>
       <c r="AF3">
-        <v>-10.8</v>
+        <v>-28.7</v>
       </c>
       <c r="AG3">
-        <v>3574.03</v>
+        <v>3574.75</v>
       </c>
       <c r="AH3">
-        <v>3018.91</v>
+        <v>3050.26</v>
       </c>
       <c r="AI3">
         <v>3274.47</v>
@@ -1174,7 +1142,7 @@
         <v>50</v>
       </c>
       <c r="AK3">
-        <v>59.18</v>
+        <v>53.97</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1185,10 +1153,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>398.8</v>
+        <v>395.85</v>
       </c>
       <c r="D4">
-        <v>-3.27</v>
+        <v>-0.74</v>
       </c>
       <c r="E4">
         <v>412.3</v>
@@ -1197,46 +1165,46 @@
         <v>252.5</v>
       </c>
       <c r="G4">
-        <v>-3.27</v>
+        <v>-3.99</v>
       </c>
       <c r="H4">
-        <v>57.94</v>
+        <v>56.77</v>
       </c>
       <c r="I4">
-        <v>0.05</v>
+        <v>-0.64</v>
       </c>
       <c r="J4">
-        <v>19.87</v>
+        <v>21.76</v>
       </c>
       <c r="K4">
-        <v>24.59</v>
+        <v>23.36</v>
       </c>
       <c r="L4">
-        <v>55.51</v>
+        <v>56.25</v>
       </c>
       <c r="M4">
-        <v>22.92</v>
+        <v>22.54</v>
       </c>
       <c r="N4">
         <v>99</v>
       </c>
       <c r="O4">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P4">
-        <v>401.35</v>
+        <v>400.84</v>
       </c>
       <c r="Q4">
-        <v>373.39</v>
+        <v>376.93</v>
       </c>
       <c r="R4">
-        <v>333.57</v>
+        <v>335.6</v>
       </c>
       <c r="S4">
-        <v>337.82</v>
+        <v>338.31</v>
       </c>
       <c r="T4">
-        <v>18.05</v>
+        <v>17.01</v>
       </c>
       <c r="U4" t="s">
         <v>48</v>
@@ -1251,34 +1219,34 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>62.47</v>
+        <v>60.97</v>
       </c>
       <c r="Z4">
-        <v>20.9</v>
+        <v>19.74</v>
       </c>
       <c r="AA4">
-        <v>19.79</v>
+        <v>19.78</v>
       </c>
       <c r="AB4">
-        <v>1.11</v>
+        <v>-0.04</v>
       </c>
       <c r="AC4">
-        <v>33.35</v>
+        <v>18.04</v>
       </c>
       <c r="AD4">
-        <v>44.23</v>
+        <v>32.89</v>
       </c>
       <c r="AE4">
-        <v>15.94</v>
+        <v>16.05</v>
       </c>
       <c r="AF4">
-        <v>-76.97</v>
+        <v>-34.56</v>
       </c>
       <c r="AG4">
-        <v>434.67</v>
+        <v>434.51</v>
       </c>
       <c r="AH4">
-        <v>312.11</v>
+        <v>319.36</v>
       </c>
       <c r="AI4">
         <v>357.72</v>
@@ -1287,7 +1255,7 @@
         <v>50</v>
       </c>
       <c r="AK4">
-        <v>54.14</v>
+        <v>51.97</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1298,10 +1266,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>382.65</v>
+        <v>382.85</v>
       </c>
       <c r="D5">
-        <v>-1.09</v>
+        <v>0.05</v>
       </c>
       <c r="E5">
         <v>421.7</v>
@@ -1310,25 +1278,25 @@
         <v>294.25</v>
       </c>
       <c r="G5">
-        <v>-9.26</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="H5">
-        <v>30.04</v>
+        <v>30.11</v>
       </c>
       <c r="I5">
-        <v>-3.75</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>1.07</v>
+        <v>2.81</v>
       </c>
       <c r="K5">
-        <v>17.54</v>
+        <v>18.2</v>
       </c>
       <c r="L5">
-        <v>7.43</v>
+        <v>8.27</v>
       </c>
       <c r="M5">
-        <v>9.69</v>
+        <v>9.6</v>
       </c>
       <c r="N5">
         <v>66</v>
@@ -1340,58 +1308,58 @@
         <v>385.06</v>
       </c>
       <c r="Q5">
-        <v>381.9</v>
+        <v>382.46</v>
       </c>
       <c r="R5">
-        <v>364.84</v>
+        <v>365.75</v>
       </c>
       <c r="S5">
-        <v>365.01</v>
+        <v>364.99</v>
       </c>
       <c r="T5">
-        <v>4.83</v>
+        <v>4.89</v>
       </c>
       <c r="U5" t="s">
         <v>48</v>
       </c>
       <c r="V5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="W5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="X5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y5">
-        <v>53.86</v>
+        <v>54.03</v>
       </c>
       <c r="Z5">
-        <v>6.12</v>
+        <v>5.49</v>
       </c>
       <c r="AA5">
-        <v>7.28</v>
+        <v>6.92</v>
       </c>
       <c r="AB5">
-        <v>-1.15</v>
+        <v>-1.43</v>
       </c>
       <c r="AC5">
-        <v>11</v>
+        <v>5.85</v>
       </c>
       <c r="AD5">
-        <v>12.83</v>
+        <v>11.04</v>
       </c>
       <c r="AE5">
-        <v>11.48</v>
+        <v>11.21</v>
       </c>
       <c r="AF5">
-        <v>-80.16</v>
+        <v>-80.61</v>
       </c>
       <c r="AG5">
-        <v>398.51</v>
+        <v>398.35</v>
       </c>
       <c r="AH5">
-        <v>365.3</v>
+        <v>366.57</v>
       </c>
       <c r="AI5">
         <v>364.94</v>
@@ -1400,7 +1368,7 @@
         <v>50</v>
       </c>
       <c r="AK5">
-        <v>33.33</v>
+        <v>29.71</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1411,10 +1379,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>409.35</v>
+        <v>406.95</v>
       </c>
       <c r="D6">
-        <v>-0.49</v>
+        <v>-0.59</v>
       </c>
       <c r="E6">
         <v>442.7</v>
@@ -1423,46 +1391,46 @@
         <v>279.55</v>
       </c>
       <c r="G6">
-        <v>-7.53</v>
+        <v>-8.08</v>
       </c>
       <c r="H6">
-        <v>46.43</v>
+        <v>45.57</v>
       </c>
       <c r="I6">
-        <v>-2.77</v>
+        <v>-1.58</v>
       </c>
       <c r="J6">
-        <v>6.95</v>
+        <v>3.37</v>
       </c>
       <c r="K6">
-        <v>9.92</v>
+        <v>11.08</v>
       </c>
       <c r="L6">
-        <v>30.01</v>
+        <v>30.08</v>
       </c>
       <c r="M6">
-        <v>-8.720000000000001</v>
+        <v>-9.33</v>
       </c>
       <c r="N6">
         <v>88</v>
       </c>
       <c r="O6">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="P6">
-        <v>410.16</v>
+        <v>408.85</v>
       </c>
       <c r="Q6">
-        <v>404.91</v>
+        <v>405.84</v>
       </c>
       <c r="R6">
-        <v>381.11</v>
+        <v>382.28</v>
       </c>
       <c r="S6">
-        <v>362.97</v>
+        <v>363.19</v>
       </c>
       <c r="T6">
-        <v>12.78</v>
+        <v>12.05</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1477,34 +1445,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>55.39</v>
+        <v>53.84</v>
       </c>
       <c r="Z6">
-        <v>7.84</v>
+        <v>7.11</v>
       </c>
       <c r="AA6">
-        <v>9.109999999999999</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="AB6">
-        <v>-1.27</v>
+        <v>-1.6</v>
       </c>
       <c r="AC6">
-        <v>16.57</v>
+        <v>20.01</v>
       </c>
       <c r="AD6">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AE6">
-        <v>14.64</v>
+        <v>14.45</v>
       </c>
       <c r="AF6">
-        <v>-69.63</v>
+        <v>-64.93000000000001</v>
       </c>
       <c r="AG6">
-        <v>427.25</v>
+        <v>426.79</v>
       </c>
       <c r="AH6">
-        <v>382.56</v>
+        <v>384.88</v>
       </c>
       <c r="AI6">
         <v>371.16</v>
@@ -1513,7 +1481,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>29.24</v>
+        <v>27.73</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1524,10 +1492,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>595</v>
+        <v>609.95</v>
       </c>
       <c r="D7">
-        <v>-2.11</v>
+        <v>2.51</v>
       </c>
       <c r="E7">
         <v>681.5</v>
@@ -1536,46 +1504,46 @@
         <v>506.45</v>
       </c>
       <c r="G7">
-        <v>-12.69</v>
+        <v>-10.5</v>
       </c>
       <c r="H7">
-        <v>17.48</v>
+        <v>20.44</v>
       </c>
       <c r="I7">
-        <v>2.75</v>
+        <v>4.69</v>
       </c>
       <c r="J7">
-        <v>0.53</v>
+        <v>3.54</v>
       </c>
       <c r="K7">
-        <v>-8.289999999999999</v>
+        <v>-5.7</v>
       </c>
       <c r="L7">
-        <v>-11.92</v>
+        <v>-7.66</v>
       </c>
       <c r="M7">
-        <v>33.05</v>
+        <v>33.37</v>
       </c>
       <c r="N7">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="O7">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="P7">
-        <v>591.79</v>
+        <v>597.26</v>
       </c>
       <c r="Q7">
-        <v>580.64</v>
+        <v>581.7</v>
       </c>
       <c r="R7">
         <v>599.8200000000001</v>
       </c>
       <c r="S7">
-        <v>580.84</v>
+        <v>581.04</v>
       </c>
       <c r="T7">
-        <v>2.44</v>
+        <v>4.98</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1590,34 +1558,34 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>53.23</v>
+        <v>59.45</v>
       </c>
       <c r="Z7">
-        <v>-2.02</v>
+        <v>0.01</v>
       </c>
       <c r="AA7">
-        <v>-6.38</v>
+        <v>-5.1</v>
       </c>
       <c r="AB7">
-        <v>4.36</v>
+        <v>5.11</v>
       </c>
       <c r="AC7">
-        <v>91.2</v>
+        <v>89.5</v>
       </c>
       <c r="AD7">
-        <v>97.06999999999999</v>
+        <v>93.56999999999999</v>
       </c>
       <c r="AE7">
-        <v>15.53</v>
+        <v>15.79</v>
       </c>
       <c r="AF7">
-        <v>69.17</v>
+        <v>29.26</v>
       </c>
       <c r="AG7">
-        <v>600.64</v>
+        <v>605.41</v>
       </c>
       <c r="AH7">
-        <v>560.65</v>
+        <v>558</v>
       </c>
       <c r="AI7">
         <v>558.51</v>
@@ -1626,7 +1594,7 @@
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>32.87</v>
+        <v>34.59</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1637,10 +1605,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>225.57</v>
+        <v>224.88</v>
       </c>
       <c r="D8">
-        <v>-2.06</v>
+        <v>-0.31</v>
       </c>
       <c r="E8">
         <v>363.5</v>
@@ -1649,46 +1617,46 @@
         <v>210.4</v>
       </c>
       <c r="G8">
-        <v>-37.94</v>
+        <v>-38.13</v>
       </c>
       <c r="H8">
-        <v>7.21</v>
+        <v>6.88</v>
       </c>
       <c r="I8">
-        <v>-1.06</v>
+        <v>-3.58</v>
       </c>
       <c r="J8">
-        <v>-2.64</v>
+        <v>-0.25</v>
       </c>
       <c r="K8">
-        <v>0.79</v>
+        <v>-2.2</v>
       </c>
       <c r="L8">
-        <v>-36.49</v>
+        <v>-36.07</v>
       </c>
       <c r="M8">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="N8">
         <v>12</v>
       </c>
       <c r="O8">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P8">
-        <v>229.95</v>
+        <v>228.28</v>
       </c>
       <c r="Q8">
-        <v>223.57</v>
+        <v>223.52</v>
       </c>
       <c r="R8">
-        <v>228.18</v>
+        <v>228.39</v>
       </c>
       <c r="S8">
-        <v>269.96</v>
+        <v>269.4</v>
       </c>
       <c r="T8">
-        <v>-16.44</v>
+        <v>-16.52</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1703,34 +1671,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>49.14</v>
+        <v>48.39</v>
       </c>
       <c r="Z8">
-        <v>-0.23</v>
+        <v>-0.31</v>
       </c>
       <c r="AA8">
-        <v>-1.53</v>
+        <v>-1.28</v>
       </c>
       <c r="AB8">
-        <v>1.29</v>
+        <v>0.98</v>
       </c>
       <c r="AC8">
-        <v>75.92</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="AD8">
-        <v>85.23999999999999</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="AE8">
-        <v>7.46</v>
+        <v>7.2</v>
       </c>
       <c r="AF8">
-        <v>-69.34999999999999</v>
+        <v>-69.56999999999999</v>
       </c>
       <c r="AG8">
-        <v>235.99</v>
+        <v>235.91</v>
       </c>
       <c r="AH8">
-        <v>211.15</v>
+        <v>211.13</v>
       </c>
       <c r="AI8">
         <v>237.22</v>
@@ -1739,7 +1707,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>31.14</v>
+        <v>30.31</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1750,10 +1718,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>3597.9</v>
+        <v>3608.9</v>
       </c>
       <c r="D9">
-        <v>-0.12</v>
+        <v>0.31</v>
       </c>
       <c r="E9">
         <v>4497.5</v>
@@ -1762,46 +1730,46 @@
         <v>3308.9</v>
       </c>
       <c r="G9">
-        <v>-20</v>
+        <v>-19.76</v>
       </c>
       <c r="H9">
-        <v>8.73</v>
+        <v>9.07</v>
       </c>
       <c r="I9">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="J9">
-        <v>-5.06</v>
+        <v>-3.94</v>
       </c>
       <c r="K9">
-        <v>-5.16</v>
+        <v>-4.98</v>
       </c>
       <c r="L9">
-        <v>-10.1</v>
+        <v>-7.91</v>
       </c>
       <c r="M9">
-        <v>18.43</v>
+        <v>18.75</v>
       </c>
       <c r="N9">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="O9">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="P9">
         <v>3601.06</v>
       </c>
       <c r="Q9">
-        <v>3621.4</v>
+        <v>3613.38</v>
       </c>
       <c r="R9">
-        <v>3755.02</v>
+        <v>3751.24</v>
       </c>
       <c r="S9">
-        <v>3723.39</v>
+        <v>3721.14</v>
       </c>
       <c r="T9">
-        <v>-3.37</v>
+        <v>-3.02</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1816,34 +1784,34 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>39.32</v>
+        <v>41.42</v>
       </c>
       <c r="Z9">
-        <v>-48.05</v>
+        <v>-44.75</v>
       </c>
       <c r="AA9">
-        <v>-55.24</v>
+        <v>-53.15</v>
       </c>
       <c r="AB9">
-        <v>7.19</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="AC9">
-        <v>82.73</v>
+        <v>88.06999999999999</v>
       </c>
       <c r="AD9">
-        <v>81.93000000000001</v>
+        <v>84</v>
       </c>
       <c r="AE9">
-        <v>67.54000000000001</v>
+        <v>65</v>
       </c>
       <c r="AF9">
-        <v>-68.76000000000001</v>
+        <v>-53.15</v>
       </c>
       <c r="AG9">
-        <v>3734.69</v>
+        <v>3702.82</v>
       </c>
       <c r="AH9">
-        <v>3508.1</v>
+        <v>3523.94</v>
       </c>
       <c r="AI9">
         <v>3794.41</v>
@@ -1852,7 +1820,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>13.08</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1863,10 +1831,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>1643</v>
+        <v>1625</v>
       </c>
       <c r="D10">
-        <v>0.18</v>
+        <v>-1.1</v>
       </c>
       <c r="E10">
         <v>1768.4</v>
@@ -1875,46 +1843,46 @@
         <v>1326.2</v>
       </c>
       <c r="G10">
-        <v>-7.09</v>
+        <v>-8.109999999999999</v>
       </c>
       <c r="H10">
-        <v>23.89</v>
+        <v>22.53</v>
       </c>
       <c r="I10">
-        <v>-0.33</v>
+        <v>-1.52</v>
       </c>
       <c r="J10">
-        <v>9.210000000000001</v>
+        <v>9.48</v>
       </c>
       <c r="K10">
-        <v>19.49</v>
+        <v>20.96</v>
       </c>
       <c r="L10">
-        <v>11.77</v>
+        <v>12.54</v>
       </c>
       <c r="M10">
-        <v>7.57</v>
+        <v>6.34</v>
       </c>
       <c r="N10">
         <v>77</v>
       </c>
       <c r="O10">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="P10">
-        <v>1640.04</v>
+        <v>1635.04</v>
       </c>
       <c r="Q10">
-        <v>1604.15</v>
+        <v>1610.46</v>
       </c>
       <c r="R10">
-        <v>1510.96</v>
+        <v>1512.04</v>
       </c>
       <c r="S10">
-        <v>1500.58</v>
+        <v>1501.39</v>
       </c>
       <c r="T10">
-        <v>9.49</v>
+        <v>8.23</v>
       </c>
       <c r="U10" t="s">
         <v>48</v>
@@ -1929,34 +1897,34 @@
         <v>3</v>
       </c>
       <c r="Y10">
-        <v>65.81</v>
+        <v>60.38</v>
       </c>
       <c r="Z10">
-        <v>43.65</v>
+        <v>40.33</v>
       </c>
       <c r="AA10">
-        <v>45.67</v>
+        <v>44.61</v>
       </c>
       <c r="AB10">
-        <v>-2.02</v>
+        <v>-4.27</v>
       </c>
       <c r="AC10">
-        <v>30.94</v>
+        <v>22.51</v>
       </c>
       <c r="AD10">
-        <v>31.17</v>
+        <v>26.58</v>
       </c>
       <c r="AE10">
-        <v>41.39</v>
+        <v>40.92</v>
       </c>
       <c r="AF10">
-        <v>-39.13</v>
+        <v>19.28</v>
       </c>
       <c r="AG10">
-        <v>1705.85</v>
+        <v>1699.5</v>
       </c>
       <c r="AH10">
-        <v>1502.44</v>
+        <v>1521.42</v>
       </c>
       <c r="AI10">
         <v>1527.05</v>
@@ -1965,7 +1933,7 @@
         <v>50</v>
       </c>
       <c r="AK10">
-        <v>39.96</v>
+        <v>36.16</v>
       </c>
     </row>
   </sheetData>
@@ -2106,7 +2074,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F82"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2146,7 +2114,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2158,35 +2126,35 @@
         <v>59</v>
       </c>
       <c r="E3" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>66</v>
+      <c r="E4" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -2198,1291 +2166,1274 @@
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="7">
-        <v>-11.8</v>
-      </c>
-      <c r="D8" s="7">
+      <c r="C8" s="6">
         <v>-12.02</v>
       </c>
-      <c r="E8" s="8">
-        <v>-0.22</v>
+      <c r="D8" s="6">
+        <v>-10.22</v>
+      </c>
+      <c r="E8" s="7">
+        <v>1.8</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="7">
-        <v>12.39</v>
-      </c>
-      <c r="D9" s="7">
+      <c r="C9" s="6">
         <v>9.48</v>
       </c>
-      <c r="E9" s="8">
-        <v>-2.91</v>
+      <c r="D9" s="6">
+        <v>10.03</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0.55</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="6">
+        <v>19.87</v>
+      </c>
+      <c r="D10" s="6">
+        <v>21.76</v>
+      </c>
+      <c r="E10" s="7">
+        <v>1.89</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>1.07</v>
+      </c>
+      <c r="D11" s="6">
+        <v>2.81</v>
+      </c>
+      <c r="E11" s="7">
+        <v>1.74</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>6.95</v>
+      </c>
+      <c r="D12" s="6">
+        <v>3.37</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-3.58</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>0.53</v>
+      </c>
+      <c r="D13" s="6">
+        <v>3.54</v>
+      </c>
+      <c r="E13" s="7">
+        <v>3.01</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-2.64</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-0.25</v>
+      </c>
+      <c r="E14" s="7">
+        <v>2.39</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-5.06</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-3.94</v>
+      </c>
+      <c r="E15" s="7">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="6">
+        <v>9.210000000000001</v>
+      </c>
+      <c r="D16" s="6">
+        <v>9.48</v>
+      </c>
+      <c r="E16" s="7">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>0.58</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-1.39</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>0.79</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-1.5</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-2.29</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-0.64</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-3.75</v>
+      </c>
+      <c r="D20" s="6">
+        <v>0</v>
+      </c>
+      <c r="E20" s="7">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-2.77</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-1.58</v>
+      </c>
+      <c r="E21" s="7">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="6">
+        <v>2.75</v>
+      </c>
+      <c r="D22" s="6">
+        <v>4.69</v>
+      </c>
+      <c r="E22" s="7">
+        <v>1.94</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-1.06</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-3.58</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-2.52</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-0.02</v>
+      </c>
+      <c r="D24" s="6">
+        <v>0</v>
+      </c>
+      <c r="E24" s="7">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-0.33</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-1.52</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-1.19</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>2.88</v>
+      </c>
+      <c r="D26" s="6">
+        <v>3.61</v>
+      </c>
+      <c r="E26" s="7">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>7.72</v>
+      </c>
+      <c r="D27" s="6">
+        <v>5.46</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-2.26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="6">
+        <v>55.51</v>
+      </c>
+      <c r="D28" s="6">
+        <v>56.25</v>
+      </c>
+      <c r="E28" s="7">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="6">
+        <v>7.43</v>
+      </c>
+      <c r="D29" s="6">
+        <v>8.27</v>
+      </c>
+      <c r="E29" s="7">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="6">
+        <v>30.01</v>
+      </c>
+      <c r="D30" s="6">
+        <v>30.08</v>
+      </c>
+      <c r="E30" s="7">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-11.92</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-7.66</v>
+      </c>
+      <c r="E31" s="7">
+        <v>4.26</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-36.49</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-36.07</v>
+      </c>
+      <c r="E32" s="7">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="6">
+        <v>-10.1</v>
+      </c>
+      <c r="D33" s="6">
+        <v>-7.91</v>
+      </c>
+      <c r="E33" s="7">
+        <v>2.19</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="6">
+        <v>11.77</v>
+      </c>
+      <c r="D34" s="6">
+        <v>12.54</v>
+      </c>
+      <c r="E34" s="7">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-9.81</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-9.67</v>
+      </c>
+      <c r="E35" s="7">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="6">
+        <v>11.19</v>
+      </c>
+      <c r="D36" s="6">
+        <v>7.24</v>
+      </c>
+      <c r="E36" s="8">
+        <v>-3.95</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="6">
+        <v>24.59</v>
+      </c>
+      <c r="D37" s="6">
+        <v>23.36</v>
+      </c>
+      <c r="E37" s="8">
+        <v>-1.23</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="6">
+        <v>17.54</v>
+      </c>
+      <c r="D38" s="6">
+        <v>18.2</v>
+      </c>
+      <c r="E38" s="7">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="6">
+        <v>9.92</v>
+      </c>
+      <c r="D39" s="6">
+        <v>11.08</v>
+      </c>
+      <c r="E39" s="7">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-8.289999999999999</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-5.7</v>
+      </c>
+      <c r="E40" s="7">
+        <v>2.59</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="6">
+        <v>0.79</v>
+      </c>
+      <c r="D41" s="6">
+        <v>-2.2</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-2.99</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="6">
+        <v>-5.16</v>
+      </c>
+      <c r="D42" s="6">
+        <v>-4.98</v>
+      </c>
+      <c r="E42" s="7">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="6">
+        <v>19.49</v>
+      </c>
+      <c r="D43" s="6">
         <v>20.96</v>
       </c>
-      <c r="D10" s="7">
-        <v>19.87</v>
-      </c>
-      <c r="E10" s="8">
-        <v>-1.09</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7">
-        <v>2.1</v>
-      </c>
-      <c r="D11" s="7">
-        <v>1.07</v>
-      </c>
-      <c r="E11" s="8">
-        <v>-1.03</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7">
-        <v>6.24</v>
-      </c>
-      <c r="D12" s="7">
-        <v>6.95</v>
-      </c>
-      <c r="E12" s="9">
-        <v>0.71</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="7">
-        <v>1.58</v>
-      </c>
-      <c r="D13" s="7">
-        <v>0.53</v>
-      </c>
-      <c r="E13" s="8">
-        <v>-1.05</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="7">
-        <v>-1.46</v>
-      </c>
-      <c r="D14" s="7">
-        <v>-2.64</v>
-      </c>
-      <c r="E14" s="8">
-        <v>-1.18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="7">
-        <v>-4.69</v>
-      </c>
-      <c r="D15" s="7">
-        <v>-5.06</v>
-      </c>
-      <c r="E15" s="8">
-        <v>-0.37</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="7">
-        <v>12.73</v>
-      </c>
-      <c r="D16" s="7">
-        <v>9.210000000000001</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-3.52</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+      <c r="E43" s="7">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-2.42</v>
-      </c>
-      <c r="D17" s="7">
-        <v>0.58</v>
-      </c>
-      <c r="E17" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
+      <c r="B44" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="6">
+        <v>-15.75</v>
+      </c>
+      <c r="D44" s="6">
+        <v>-16.01</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-0.26</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="7">
-        <v>2.58</v>
-      </c>
-      <c r="D18" s="7">
-        <v>0.79</v>
-      </c>
-      <c r="E18" s="8">
-        <v>-1.79</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="7">
-        <v>1.68</v>
-      </c>
-      <c r="D19" s="7">
-        <v>0.05</v>
-      </c>
-      <c r="E19" s="8">
-        <v>-1.63</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="7">
-        <v>-2.86</v>
-      </c>
-      <c r="D20" s="7">
-        <v>-3.75</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-0.89</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-1.19</v>
-      </c>
-      <c r="D21" s="7">
-        <v>-2.77</v>
-      </c>
-      <c r="E21" s="8">
-        <v>-1.58</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="7">
-        <v>5.95</v>
-      </c>
-      <c r="D22" s="7">
-        <v>2.75</v>
-      </c>
-      <c r="E22" s="8">
-        <v>-3.2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="7">
-        <v>5.18</v>
-      </c>
-      <c r="D23" s="7">
-        <v>-1.06</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-6.24</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="7">
-        <v>-0.78</v>
-      </c>
-      <c r="D24" s="7">
-        <v>-0.02</v>
-      </c>
-      <c r="E24" s="9">
-        <v>0.76</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="7">
-        <v>-0.55</v>
-      </c>
-      <c r="D25" s="7">
-        <v>-0.33</v>
-      </c>
-      <c r="E25" s="9">
-        <v>0.22</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="7">
-        <v>2.3</v>
-      </c>
-      <c r="D26" s="7">
-        <v>2.88</v>
-      </c>
-      <c r="E26" s="9">
-        <v>0.58</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="7">
-        <v>9.9</v>
-      </c>
-      <c r="D27" s="7">
-        <v>7.72</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-2.18</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="7">
-        <v>59.53</v>
-      </c>
-      <c r="D28" s="7">
-        <v>55.51</v>
-      </c>
-      <c r="E28" s="8">
-        <v>-4.02</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="7">
-        <v>6.81</v>
-      </c>
-      <c r="D29" s="7">
-        <v>7.43</v>
-      </c>
-      <c r="E29" s="9">
-        <v>0.62</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="7">
-        <v>27.93</v>
-      </c>
-      <c r="D30" s="7">
-        <v>30.01</v>
-      </c>
-      <c r="E30" s="9">
-        <v>2.08</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="7">
-        <v>-8.51</v>
-      </c>
-      <c r="D31" s="7">
-        <v>-11.92</v>
-      </c>
-      <c r="E31" s="8">
-        <v>-3.41</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="7">
-        <v>-35.3</v>
-      </c>
-      <c r="D32" s="7">
-        <v>-36.49</v>
-      </c>
-      <c r="E32" s="8">
-        <v>-1.19</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="7">
-        <v>-10.46</v>
-      </c>
-      <c r="D33" s="7">
-        <v>-10.1</v>
-      </c>
-      <c r="E33" s="9">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="7">
-        <v>12.35</v>
-      </c>
-      <c r="D34" s="7">
-        <v>11.77</v>
-      </c>
-      <c r="E34" s="8">
-        <v>-0.58</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="7">
-        <v>-11.5</v>
-      </c>
-      <c r="D35" s="7">
-        <v>-9.81</v>
-      </c>
-      <c r="E35" s="9">
-        <v>1.69</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="7">
-        <v>10.74</v>
-      </c>
-      <c r="D36" s="7">
-        <v>11.19</v>
-      </c>
-      <c r="E36" s="9">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="7">
-        <v>26.1</v>
-      </c>
-      <c r="D37" s="7">
-        <v>24.59</v>
-      </c>
-      <c r="E37" s="8">
-        <v>-1.51</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="7">
-        <v>19.44</v>
-      </c>
-      <c r="D38" s="7">
-        <v>17.54</v>
-      </c>
-      <c r="E38" s="8">
-        <v>-1.9</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="7">
-        <v>9.74</v>
-      </c>
-      <c r="D39" s="7">
-        <v>9.92</v>
-      </c>
-      <c r="E39" s="9">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="7">
-        <v>-5.23</v>
-      </c>
-      <c r="D40" s="7">
-        <v>-8.289999999999999</v>
-      </c>
-      <c r="E40" s="8">
-        <v>-3.06</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="7">
-        <v>2.54</v>
-      </c>
-      <c r="D41" s="7">
-        <v>0.79</v>
-      </c>
-      <c r="E41" s="8">
-        <v>-1.75</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="7">
-        <v>-5.33</v>
-      </c>
-      <c r="D42" s="7">
-        <v>-5.16</v>
-      </c>
-      <c r="E42" s="9">
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="7">
-        <v>17.74</v>
-      </c>
-      <c r="D43" s="7">
-        <v>19.49</v>
-      </c>
-      <c r="E43" s="9">
-        <v>1.75</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="6" t="s">
+      <c r="B45" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C44" s="7">
-        <v>-16.46</v>
-      </c>
-      <c r="D44" s="7">
-        <v>-15.75</v>
-      </c>
-      <c r="E44" s="9">
-        <v>0.71</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="7">
-        <v>-7.51</v>
-      </c>
-      <c r="D45" s="7">
+      <c r="C45" s="6">
         <v>-9</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-10.49</v>
       </c>
       <c r="E45" s="8">
         <v>-1.49</v>
       </c>
     </row>
     <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
+      <c r="A46" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C46" s="7">
-        <v>0</v>
-      </c>
-      <c r="D46" s="7">
+      <c r="C46" s="6">
         <v>-3.27</v>
       </c>
+      <c r="D46" s="6">
+        <v>-3.99</v>
+      </c>
       <c r="E46" s="8">
-        <v>-3.27</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
+      <c r="A47" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B47" s="6" t="s">
+      <c r="B47" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C47" s="7">
-        <v>-8.26</v>
-      </c>
-      <c r="D47" s="7">
+      <c r="C47" s="6">
         <v>-9.26</v>
       </c>
-      <c r="E47" s="8">
-        <v>-1</v>
+      <c r="D47" s="6">
+        <v>-9.210000000000001</v>
+      </c>
+      <c r="E47" s="7">
+        <v>0.05</v>
       </c>
     </row>
     <row r="48" spans="1:5">
-      <c r="A48" s="6" t="s">
+      <c r="A48" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B48" s="6" t="s">
+      <c r="B48" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C48" s="7">
-        <v>-7.08</v>
-      </c>
-      <c r="D48" s="7">
+      <c r="C48" s="6">
         <v>-7.53</v>
       </c>
+      <c r="D48" s="6">
+        <v>-8.08</v>
+      </c>
       <c r="E48" s="8">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="6">
+        <v>-12.69</v>
+      </c>
+      <c r="D49" s="6">
+        <v>-10.5</v>
+      </c>
+      <c r="E49" s="7">
+        <v>2.19</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="6">
+        <v>-37.94</v>
+      </c>
+      <c r="D50" s="6">
+        <v>-38.13</v>
+      </c>
+      <c r="E50" s="8">
+        <v>-0.19</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="6">
+        <v>-20</v>
+      </c>
+      <c r="D51" s="6">
+        <v>-19.76</v>
+      </c>
+      <c r="E51" s="7">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="6">
+        <v>-7.09</v>
+      </c>
+      <c r="D52" s="6">
+        <v>-8.109999999999999</v>
+      </c>
+      <c r="E52" s="8">
+        <v>-1.02</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="6">
+        <v>413</v>
+      </c>
+      <c r="D53" s="6">
+        <v>411.7</v>
+      </c>
+      <c r="E53" s="8">
+        <v>-1.3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="6">
+        <v>3460.1</v>
+      </c>
+      <c r="D54" s="6">
+        <v>3403.6</v>
+      </c>
+      <c r="E54" s="8">
+        <v>-56.5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="6">
+        <v>398.8</v>
+      </c>
+      <c r="D55" s="6">
+        <v>395.85</v>
+      </c>
+      <c r="E55" s="8">
+        <v>-2.95</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="6">
+        <v>382.65</v>
+      </c>
+      <c r="D56" s="6">
+        <v>382.85</v>
+      </c>
+      <c r="E56" s="7">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="6">
+        <v>409.35</v>
+      </c>
+      <c r="D57" s="6">
+        <v>406.95</v>
+      </c>
+      <c r="E57" s="8">
+        <v>-2.4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="6">
+        <v>595</v>
+      </c>
+      <c r="D58" s="6">
+        <v>609.95</v>
+      </c>
+      <c r="E58" s="7">
+        <v>14.95</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="6">
+        <v>225.57</v>
+      </c>
+      <c r="D59" s="6">
+        <v>224.88</v>
+      </c>
+      <c r="E59" s="8">
+        <v>-0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="6">
+        <v>3597.9</v>
+      </c>
+      <c r="D60" s="6">
+        <v>3608.9</v>
+      </c>
+      <c r="E60" s="7">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C61" s="6">
+        <v>1643</v>
+      </c>
+      <c r="D61" s="6">
+        <v>1625</v>
+      </c>
+      <c r="E61" s="8">
+        <v>-18</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C62" s="6">
+        <v>23</v>
+      </c>
+      <c r="D62" s="6">
+        <v>34</v>
+      </c>
+      <c r="E62" s="7">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C63" s="6">
+        <v>34</v>
+      </c>
+      <c r="D63" s="6">
+        <v>23</v>
+      </c>
+      <c r="E63" s="8">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="6">
+        <v>38.16</v>
+      </c>
+      <c r="D64" s="6">
+        <v>37.52</v>
+      </c>
+      <c r="E64" s="8">
+        <v>-0.64</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="6">
+        <v>63.49</v>
+      </c>
+      <c r="D65" s="6">
+        <v>58.1</v>
+      </c>
+      <c r="E65" s="8">
+        <v>-5.39</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="6">
+        <v>62.47</v>
+      </c>
+      <c r="D66" s="6">
+        <v>60.97</v>
+      </c>
+      <c r="E66" s="8">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="6">
+        <v>53.86</v>
+      </c>
+      <c r="D67" s="6">
+        <v>54.03</v>
+      </c>
+      <c r="E67" s="7">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="6">
+        <v>55.39</v>
+      </c>
+      <c r="D68" s="6">
+        <v>53.84</v>
+      </c>
+      <c r="E68" s="8">
+        <v>-1.55</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="6">
+        <v>53.23</v>
+      </c>
+      <c r="D69" s="6">
+        <v>59.45</v>
+      </c>
+      <c r="E69" s="7">
+        <v>6.22</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="6">
+        <v>49.14</v>
+      </c>
+      <c r="D70" s="6">
+        <v>48.39</v>
+      </c>
+      <c r="E70" s="8">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="6">
+        <v>39.32</v>
+      </c>
+      <c r="D71" s="6">
+        <v>41.42</v>
+      </c>
+      <c r="E71" s="7">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C72" s="6">
+        <v>65.81</v>
+      </c>
+      <c r="D72" s="6">
+        <v>60.38</v>
+      </c>
+      <c r="E72" s="8">
+        <v>-5.43</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="6">
+        <v>486.43</v>
+      </c>
+      <c r="D73" s="6">
+        <v>-31.88</v>
+      </c>
+      <c r="E73" s="8">
+        <v>-518.3099999999999</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="6">
+        <v>-10.8</v>
+      </c>
+      <c r="D74" s="6">
+        <v>-28.7</v>
+      </c>
+      <c r="E74" s="8">
+        <v>-17.9</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="6">
+        <v>-76.97</v>
+      </c>
+      <c r="D75" s="6">
+        <v>-34.56</v>
+      </c>
+      <c r="E75" s="7">
+        <v>42.41</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="6">
+        <v>-80.16</v>
+      </c>
+      <c r="D76" s="6">
+        <v>-80.61</v>
+      </c>
+      <c r="E76" s="8">
         <v>-0.45</v>
       </c>
     </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="6" t="s">
+    <row r="77" spans="1:5">
+      <c r="A77" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="6">
+        <v>-69.63</v>
+      </c>
+      <c r="D77" s="6">
+        <v>-64.93000000000001</v>
+      </c>
+      <c r="E77" s="7">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B49" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="7">
-        <v>-10.81</v>
-      </c>
-      <c r="D49" s="7">
-        <v>-12.69</v>
-      </c>
-      <c r="E49" s="8">
-        <v>-1.88</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="6" t="s">
+      <c r="B78" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="6">
+        <v>69.17</v>
+      </c>
+      <c r="D78" s="6">
+        <v>29.26</v>
+      </c>
+      <c r="E78" s="8">
+        <v>-39.91</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B50" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="7">
-        <v>-36.64</v>
-      </c>
-      <c r="D50" s="7">
-        <v>-37.94</v>
-      </c>
-      <c r="E50" s="8">
-        <v>-1.3</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="6" t="s">
+      <c r="B79" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="6">
+        <v>-69.34999999999999</v>
+      </c>
+      <c r="D79" s="6">
+        <v>-69.56999999999999</v>
+      </c>
+      <c r="E79" s="8">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B51" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="7">
-        <v>-19.9</v>
-      </c>
-      <c r="D51" s="7">
-        <v>-20</v>
-      </c>
-      <c r="E51" s="8">
-        <v>-0.1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="6" t="s">
+      <c r="B80" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="6">
+        <v>-68.76000000000001</v>
+      </c>
+      <c r="D80" s="6">
+        <v>-53.15</v>
+      </c>
+      <c r="E80" s="7">
+        <v>15.61</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B52" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C52" s="7">
-        <v>-7.26</v>
-      </c>
-      <c r="D52" s="7">
-        <v>-7.09</v>
-      </c>
-      <c r="E52" s="9">
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="7">
-        <v>409.5</v>
-      </c>
-      <c r="D53" s="7">
-        <v>413</v>
-      </c>
-      <c r="E53" s="9">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="7">
-        <v>3517</v>
-      </c>
-      <c r="D54" s="7">
-        <v>3460.1</v>
-      </c>
-      <c r="E54" s="8">
-        <v>-56.9</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="7">
-        <v>412.3</v>
-      </c>
-      <c r="D55" s="7">
-        <v>398.8</v>
-      </c>
-      <c r="E55" s="8">
-        <v>-13.5</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="7">
-        <v>386.85</v>
-      </c>
-      <c r="D56" s="7">
-        <v>382.65</v>
-      </c>
-      <c r="E56" s="8">
-        <v>-4.2</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="7">
-        <v>411.35</v>
-      </c>
-      <c r="D57" s="7">
-        <v>409.35</v>
-      </c>
-      <c r="E57" s="8">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="7">
-        <v>607.85</v>
-      </c>
-      <c r="D58" s="7">
-        <v>595</v>
-      </c>
-      <c r="E58" s="8">
-        <v>-12.85</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="7">
-        <v>230.31</v>
-      </c>
-      <c r="D59" s="7">
-        <v>225.57</v>
-      </c>
-      <c r="E59" s="8">
-        <v>-4.74</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="7">
-        <v>3602.3</v>
-      </c>
-      <c r="D60" s="7">
-        <v>3597.9</v>
-      </c>
-      <c r="E60" s="8">
-        <v>-4.4</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C61" s="7">
-        <v>1640</v>
-      </c>
-      <c r="D61" s="7">
-        <v>1643</v>
-      </c>
-      <c r="E61" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C62" s="7">
-        <v>34</v>
-      </c>
-      <c r="D62" s="7">
-        <v>45</v>
-      </c>
-      <c r="E62" s="9">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C63" s="7">
-        <v>45</v>
-      </c>
-      <c r="D63" s="7">
-        <v>23</v>
-      </c>
-      <c r="E63" s="8">
-        <v>-22</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C64" s="7">
-        <v>23</v>
-      </c>
-      <c r="D64" s="7">
-        <v>34</v>
-      </c>
-      <c r="E64" s="9">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="7">
-        <v>35.42</v>
-      </c>
-      <c r="D65" s="7">
-        <v>38.16</v>
-      </c>
-      <c r="E65" s="9">
-        <v>2.74</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="7">
-        <v>69.52</v>
-      </c>
-      <c r="D66" s="7">
-        <v>63.49</v>
-      </c>
-      <c r="E66" s="8">
-        <v>-6.03</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="7">
-        <v>69.75</v>
-      </c>
-      <c r="D67" s="7">
-        <v>62.47</v>
-      </c>
-      <c r="E67" s="8">
-        <v>-7.28</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="7">
-        <v>58.13</v>
-      </c>
-      <c r="D68" s="7">
-        <v>53.86</v>
-      </c>
-      <c r="E68" s="8">
-        <v>-4.27</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="7">
-        <v>56.66</v>
-      </c>
-      <c r="D69" s="7">
-        <v>55.39</v>
-      </c>
-      <c r="E69" s="8">
-        <v>-1.27</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="7">
-        <v>60.66</v>
-      </c>
-      <c r="D70" s="7">
-        <v>53.23</v>
-      </c>
-      <c r="E70" s="8">
-        <v>-7.43</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B71" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="7">
-        <v>54.53</v>
-      </c>
-      <c r="D71" s="7">
-        <v>49.14</v>
-      </c>
-      <c r="E71" s="8">
-        <v>-5.39</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C72" s="7">
-        <v>39.85</v>
-      </c>
-      <c r="D72" s="7">
-        <v>39.32</v>
-      </c>
-      <c r="E72" s="8">
-        <v>-0.53</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C73" s="7">
-        <v>65.33</v>
-      </c>
-      <c r="D73" s="7">
-        <v>65.81</v>
-      </c>
-      <c r="E73" s="9">
-        <v>0.48</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B74" s="6" t="s">
+      <c r="B81" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C74" s="7">
-        <v>-60.58</v>
-      </c>
-      <c r="D74" s="7">
-        <v>486.43</v>
-      </c>
-      <c r="E74" s="9">
-        <v>547.01</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B75" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="7">
-        <v>-3.17</v>
-      </c>
-      <c r="D75" s="7">
-        <v>-10.8</v>
-      </c>
-      <c r="E75" s="8">
-        <v>-7.63</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B76" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="7">
-        <v>-49.24</v>
-      </c>
-      <c r="D76" s="7">
-        <v>-76.97</v>
-      </c>
-      <c r="E76" s="8">
-        <v>-27.73</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B77" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="7">
-        <v>-66.05</v>
-      </c>
-      <c r="D77" s="7">
-        <v>-80.16</v>
-      </c>
-      <c r="E77" s="8">
-        <v>-14.11</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B78" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="7">
-        <v>-48.14</v>
-      </c>
-      <c r="D78" s="7">
-        <v>-69.63</v>
-      </c>
-      <c r="E78" s="8">
-        <v>-21.49</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B79" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="7">
-        <v>413.42</v>
-      </c>
-      <c r="D79" s="7">
-        <v>69.17</v>
-      </c>
-      <c r="E79" s="8">
-        <v>-344.25</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B80" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="7">
-        <v>-24.38</v>
-      </c>
-      <c r="D80" s="7">
-        <v>-69.34999999999999</v>
-      </c>
-      <c r="E80" s="8">
-        <v>-44.97</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B81" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="7">
-        <v>-61.06</v>
-      </c>
-      <c r="D81" s="7">
-        <v>-68.76000000000001</v>
-      </c>
-      <c r="E81" s="8">
-        <v>-7.7</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B82" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C82" s="7">
-        <v>-9.02</v>
-      </c>
-      <c r="D82" s="7">
+      <c r="C81" s="6">
         <v>-39.13</v>
       </c>
-      <c r="E82" s="8">
-        <v>-30.11</v>
+      <c r="D81" s="6">
+        <v>19.28</v>
+      </c>
+      <c r="E81" s="7">
+        <v>58.41</v>
       </c>
     </row>
   </sheetData>
@@ -3508,61 +3459,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="H1" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="I1" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="D1" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>79</v>
-      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="11">
         <v>60.16</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="12">
         <v>9</v>
       </c>
-      <c r="D2" s="12">
-        <v>53.4</v>
-      </c>
-      <c r="E2" s="12">
+      <c r="D2" s="11">
+        <v>52.7</v>
+      </c>
+      <c r="E2" s="11">
         <v>70</v>
       </c>
-      <c r="F2" s="12">
-        <v>3</v>
-      </c>
-      <c r="G2" s="12">
-        <v>6.7</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="F2" s="11">
+        <v>4.1</v>
+      </c>
+      <c r="G2" s="11">
+        <v>6.5</v>
+      </c>
+      <c r="H2" s="11">
         <v>55.4</v>
       </c>
-      <c r="I2" s="12">
-        <v>20</v>
+      <c r="I2" s="11">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -3663,61 +3614,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="13" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="15">
-        <v>0.3573</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0.3305</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0.2292</v>
-      </c>
-      <c r="D2" s="15">
-        <v>0.1843</v>
-      </c>
-      <c r="E2" s="15">
-        <v>0.1198</v>
-      </c>
-      <c r="F2" s="15">
-        <v>0.0969</v>
-      </c>
-      <c r="G2" s="15">
-        <v>0.0757</v>
-      </c>
-      <c r="H2" s="15">
-        <v>0.0248</v>
-      </c>
-      <c r="I2" s="15">
-        <v>-0.0872</v>
+      <c r="A2" s="14">
+        <v>0.3537</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.3337</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.2254</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.1875</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.1195</v>
+      </c>
+      <c r="F2" s="14">
+        <v>0.096</v>
+      </c>
+      <c r="G2" s="14">
+        <v>0.0634</v>
+      </c>
+      <c r="H2" s="14">
+        <v>0.0252</v>
+      </c>
+      <c r="I2" s="14">
+        <v>-0.09329999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/MAHINDRA_GROUP_Technical_Metrics.xlsx
+++ b/MAHINDRA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="66">
   <si>
     <t>Symbol</t>
   </si>
@@ -178,31 +178,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>50 DMA &gt; 200 DMA</t>
-  </si>
-  <si>
-    <t>No → Yes</t>
-  </si>
-  <si>
-    <t>🟢 GOLDEN CROSS</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -288,14 +264,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -328,13 +304,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,15 +380,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -927,10 +902,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>411.7</v>
+        <v>408.6</v>
       </c>
       <c r="D2">
-        <v>-0.31</v>
+        <v>-0.75</v>
       </c>
       <c r="E2">
         <v>490.2</v>
@@ -939,46 +914,46 @@
         <v>379.2</v>
       </c>
       <c r="G2">
-        <v>-16.01</v>
+        <v>-16.65</v>
       </c>
       <c r="H2">
-        <v>8.57</v>
+        <v>7.75</v>
       </c>
       <c r="I2">
-        <v>-0.8100000000000001</v>
+        <v>-0.41</v>
       </c>
       <c r="J2">
-        <v>-10.22</v>
+        <v>-11.39</v>
       </c>
       <c r="K2">
-        <v>-9.67</v>
+        <v>-11.32</v>
       </c>
       <c r="L2">
-        <v>3.61</v>
+        <v>3.72</v>
       </c>
       <c r="M2">
-        <v>11.95</v>
+        <v>12.13</v>
       </c>
       <c r="N2">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="O2">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="P2">
-        <v>411</v>
+        <v>410.66</v>
       </c>
       <c r="Q2">
-        <v>427.76</v>
+        <v>424.56</v>
       </c>
       <c r="R2">
-        <v>446.68</v>
+        <v>445.81</v>
       </c>
       <c r="S2">
-        <v>438.6</v>
+        <v>438.55</v>
       </c>
       <c r="T2">
-        <v>-6.13</v>
+        <v>-6.83</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -993,34 +968,34 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>37.52</v>
+        <v>35.98</v>
       </c>
       <c r="Z2">
-        <v>-12.42</v>
+        <v>-12.14</v>
       </c>
       <c r="AA2">
-        <v>-12.29</v>
+        <v>-12.26</v>
       </c>
       <c r="AB2">
-        <v>-0.12</v>
+        <v>0.12</v>
       </c>
       <c r="AC2">
-        <v>73.73</v>
+        <v>90.87</v>
       </c>
       <c r="AD2">
-        <v>51.22</v>
+        <v>72.22</v>
       </c>
       <c r="AE2">
-        <v>12.31</v>
+        <v>11.94</v>
       </c>
       <c r="AF2">
-        <v>-31.88</v>
+        <v>-75.97</v>
       </c>
       <c r="AG2">
-        <v>481.75</v>
+        <v>474.81</v>
       </c>
       <c r="AH2">
-        <v>373.78</v>
+        <v>374.32</v>
       </c>
       <c r="AI2">
         <v>446.81</v>
@@ -1029,7 +1004,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>39.15</v>
+        <v>36.53</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1040,10 +1015,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>3403.6</v>
+        <v>3428.2</v>
       </c>
       <c r="D3">
-        <v>-1.63</v>
+        <v>0.72</v>
       </c>
       <c r="E3">
         <v>3802.4</v>
@@ -1052,46 +1027,46 @@
         <v>2931.1</v>
       </c>
       <c r="G3">
-        <v>-10.49</v>
+        <v>-9.84</v>
       </c>
       <c r="H3">
-        <v>16.12</v>
+        <v>16.96</v>
       </c>
       <c r="I3">
-        <v>-1.5</v>
+        <v>0.65</v>
       </c>
       <c r="J3">
-        <v>10.03</v>
+        <v>11.2</v>
       </c>
       <c r="K3">
-        <v>7.24</v>
+        <v>9.77</v>
       </c>
       <c r="L3">
-        <v>5.46</v>
+        <v>6.76</v>
       </c>
       <c r="M3">
-        <v>35.37</v>
+        <v>35.48</v>
       </c>
       <c r="N3">
         <v>55</v>
       </c>
       <c r="O3">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="P3">
-        <v>3457.74</v>
+        <v>3462.18</v>
       </c>
       <c r="Q3">
-        <v>3312.51</v>
+        <v>3328.02</v>
       </c>
       <c r="R3">
-        <v>3177.13</v>
+        <v>3185.47</v>
       </c>
       <c r="S3">
-        <v>3358.13</v>
+        <v>3357.15</v>
       </c>
       <c r="T3">
-        <v>1.35</v>
+        <v>2.12</v>
       </c>
       <c r="U3" t="s">
         <v>48</v>
@@ -1106,34 +1081,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>58.1</v>
+        <v>59.7</v>
       </c>
       <c r="Z3">
-        <v>87.17</v>
+        <v>83.34</v>
       </c>
       <c r="AA3">
-        <v>76.73999999999999</v>
+        <v>78.06</v>
       </c>
       <c r="AB3">
-        <v>10.42</v>
+        <v>5.28</v>
       </c>
       <c r="AC3">
-        <v>66.42</v>
+        <v>43.13</v>
       </c>
       <c r="AD3">
-        <v>80.97</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="AE3">
-        <v>77.48999999999999</v>
+        <v>75.06</v>
       </c>
       <c r="AF3">
-        <v>-28.7</v>
+        <v>-10.01</v>
       </c>
       <c r="AG3">
-        <v>3574.75</v>
+        <v>3578.22</v>
       </c>
       <c r="AH3">
-        <v>3050.26</v>
+        <v>3077.83</v>
       </c>
       <c r="AI3">
         <v>3274.47</v>
@@ -1142,7 +1117,7 @@
         <v>50</v>
       </c>
       <c r="AK3">
-        <v>53.97</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1153,10 +1128,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>395.85</v>
+        <v>396.4</v>
       </c>
       <c r="D4">
-        <v>-0.74</v>
+        <v>0.14</v>
       </c>
       <c r="E4">
         <v>412.3</v>
@@ -1165,46 +1140,46 @@
         <v>252.5</v>
       </c>
       <c r="G4">
-        <v>-3.99</v>
+        <v>-3.86</v>
       </c>
       <c r="H4">
-        <v>56.77</v>
+        <v>56.99</v>
       </c>
       <c r="I4">
-        <v>-0.64</v>
+        <v>1.95</v>
       </c>
       <c r="J4">
-        <v>21.76</v>
+        <v>21.99</v>
       </c>
       <c r="K4">
-        <v>23.36</v>
+        <v>23.62</v>
       </c>
       <c r="L4">
-        <v>56.25</v>
+        <v>56.31</v>
       </c>
       <c r="M4">
-        <v>22.54</v>
+        <v>23.2</v>
       </c>
       <c r="N4">
         <v>99</v>
       </c>
       <c r="O4">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="P4">
-        <v>400.84</v>
+        <v>402.36</v>
       </c>
       <c r="Q4">
-        <v>376.93</v>
+        <v>380.66</v>
       </c>
       <c r="R4">
-        <v>335.6</v>
+        <v>337.72</v>
       </c>
       <c r="S4">
-        <v>338.31</v>
+        <v>338.8</v>
       </c>
       <c r="T4">
-        <v>17.01</v>
+        <v>17</v>
       </c>
       <c r="U4" t="s">
         <v>48</v>
@@ -1219,34 +1194,34 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>60.97</v>
+        <v>61.16</v>
       </c>
       <c r="Z4">
-        <v>19.74</v>
+        <v>18.65</v>
       </c>
       <c r="AA4">
-        <v>19.78</v>
+        <v>19.56</v>
       </c>
       <c r="AB4">
-        <v>-0.04</v>
+        <v>-0.9</v>
       </c>
       <c r="AC4">
-        <v>18.04</v>
+        <v>0.97</v>
       </c>
       <c r="AD4">
-        <v>32.89</v>
+        <v>17.45</v>
       </c>
       <c r="AE4">
-        <v>16.05</v>
+        <v>15.8</v>
       </c>
       <c r="AF4">
-        <v>-34.56</v>
+        <v>-61.92</v>
       </c>
       <c r="AG4">
-        <v>434.51</v>
+        <v>432.6</v>
       </c>
       <c r="AH4">
-        <v>319.36</v>
+        <v>328.73</v>
       </c>
       <c r="AI4">
         <v>357.72</v>
@@ -1255,7 +1230,7 @@
         <v>50</v>
       </c>
       <c r="AK4">
-        <v>51.97</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1266,10 +1241,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>382.85</v>
+        <v>383.75</v>
       </c>
       <c r="D5">
-        <v>0.05</v>
+        <v>0.24</v>
       </c>
       <c r="E5">
         <v>421.7</v>
@@ -1278,46 +1253,46 @@
         <v>294.25</v>
       </c>
       <c r="G5">
-        <v>-9.210000000000001</v>
+        <v>-9</v>
       </c>
       <c r="H5">
-        <v>30.11</v>
+        <v>30.42</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="J5">
-        <v>2.81</v>
+        <v>3.26</v>
       </c>
       <c r="K5">
-        <v>18.2</v>
+        <v>17.55</v>
       </c>
       <c r="L5">
-        <v>8.27</v>
+        <v>10.64</v>
       </c>
       <c r="M5">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="N5">
         <v>66</v>
       </c>
       <c r="O5">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P5">
-        <v>385.06</v>
+        <v>384.53</v>
       </c>
       <c r="Q5">
-        <v>382.46</v>
+        <v>382.79</v>
       </c>
       <c r="R5">
-        <v>365.75</v>
+        <v>366.73</v>
       </c>
       <c r="S5">
         <v>364.99</v>
       </c>
       <c r="T5">
-        <v>4.89</v>
+        <v>5.14</v>
       </c>
       <c r="U5" t="s">
         <v>48</v>
@@ -1332,34 +1307,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>54.03</v>
+        <v>54.85</v>
       </c>
       <c r="Z5">
-        <v>5.49</v>
+        <v>5</v>
       </c>
       <c r="AA5">
-        <v>6.92</v>
+        <v>6.53</v>
       </c>
       <c r="AB5">
-        <v>-1.43</v>
+        <v>-1.54</v>
       </c>
       <c r="AC5">
-        <v>5.85</v>
+        <v>2.16</v>
       </c>
       <c r="AD5">
-        <v>11.04</v>
+        <v>6.34</v>
       </c>
       <c r="AE5">
-        <v>11.21</v>
+        <v>10.8</v>
       </c>
       <c r="AF5">
-        <v>-80.61</v>
+        <v>-72.97</v>
       </c>
       <c r="AG5">
-        <v>398.35</v>
+        <v>398.49</v>
       </c>
       <c r="AH5">
-        <v>366.57</v>
+        <v>367.08</v>
       </c>
       <c r="AI5">
         <v>364.94</v>
@@ -1368,7 +1343,7 @@
         <v>50</v>
       </c>
       <c r="AK5">
-        <v>29.71</v>
+        <v>26.67</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1379,10 +1354,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>406.95</v>
+        <v>406</v>
       </c>
       <c r="D6">
-        <v>-0.59</v>
+        <v>-0.23</v>
       </c>
       <c r="E6">
         <v>442.7</v>
@@ -1391,46 +1366,46 @@
         <v>279.55</v>
       </c>
       <c r="G6">
-        <v>-8.08</v>
+        <v>-8.289999999999999</v>
       </c>
       <c r="H6">
-        <v>45.57</v>
+        <v>45.23</v>
       </c>
       <c r="I6">
-        <v>-1.58</v>
+        <v>-1.91</v>
       </c>
       <c r="J6">
-        <v>3.37</v>
+        <v>4.53</v>
       </c>
       <c r="K6">
-        <v>11.08</v>
+        <v>12.45</v>
       </c>
       <c r="L6">
-        <v>30.08</v>
+        <v>27.79</v>
       </c>
       <c r="M6">
-        <v>-9.33</v>
+        <v>-9.81</v>
       </c>
       <c r="N6">
         <v>88</v>
       </c>
       <c r="O6">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="P6">
-        <v>408.85</v>
+        <v>407.27</v>
       </c>
       <c r="Q6">
-        <v>405.84</v>
+        <v>406.7</v>
       </c>
       <c r="R6">
-        <v>382.28</v>
+        <v>383.39</v>
       </c>
       <c r="S6">
-        <v>363.19</v>
+        <v>363.44</v>
       </c>
       <c r="T6">
-        <v>12.05</v>
+        <v>11.71</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1445,34 +1420,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>53.84</v>
+        <v>53.21</v>
       </c>
       <c r="Z6">
-        <v>7.11</v>
+        <v>6.39</v>
       </c>
       <c r="AA6">
-        <v>8.710000000000001</v>
+        <v>8.25</v>
       </c>
       <c r="AB6">
-        <v>-1.6</v>
+        <v>-1.86</v>
       </c>
       <c r="AC6">
-        <v>20.01</v>
+        <v>12.37</v>
       </c>
       <c r="AD6">
-        <v>18.8</v>
+        <v>16.31</v>
       </c>
       <c r="AE6">
-        <v>14.45</v>
+        <v>13.97</v>
       </c>
       <c r="AF6">
-        <v>-64.93000000000001</v>
+        <v>-74.70999999999999</v>
       </c>
       <c r="AG6">
-        <v>426.79</v>
+        <v>426.04</v>
       </c>
       <c r="AH6">
-        <v>384.88</v>
+        <v>387.37</v>
       </c>
       <c r="AI6">
         <v>371.16</v>
@@ -1481,7 +1456,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>27.73</v>
+        <v>26.42</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1492,10 +1467,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>609.95</v>
+        <v>612</v>
       </c>
       <c r="D7">
-        <v>2.51</v>
+        <v>0.34</v>
       </c>
       <c r="E7">
         <v>681.5</v>
@@ -1504,46 +1479,46 @@
         <v>506.45</v>
       </c>
       <c r="G7">
-        <v>-10.5</v>
+        <v>-10.2</v>
       </c>
       <c r="H7">
-        <v>20.44</v>
+        <v>20.84</v>
       </c>
       <c r="I7">
-        <v>4.69</v>
+        <v>4.83</v>
       </c>
       <c r="J7">
-        <v>3.54</v>
+        <v>3.95</v>
       </c>
       <c r="K7">
-        <v>-5.7</v>
+        <v>-5.08</v>
       </c>
       <c r="L7">
-        <v>-7.66</v>
+        <v>-6.63</v>
       </c>
       <c r="M7">
-        <v>33.37</v>
+        <v>32.17</v>
       </c>
       <c r="N7">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="O7">
         <v>42</v>
       </c>
       <c r="P7">
-        <v>597.26</v>
+        <v>602.9</v>
       </c>
       <c r="Q7">
-        <v>581.7</v>
+        <v>583.09</v>
       </c>
       <c r="R7">
-        <v>599.8200000000001</v>
+        <v>599.85</v>
       </c>
       <c r="S7">
-        <v>581.04</v>
+        <v>581.24</v>
       </c>
       <c r="T7">
-        <v>4.98</v>
+        <v>5.29</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1558,43 +1533,43 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>59.45</v>
+        <v>60.23</v>
       </c>
       <c r="Z7">
-        <v>0.01</v>
+        <v>1.77</v>
       </c>
       <c r="AA7">
-        <v>-5.1</v>
+        <v>-3.73</v>
       </c>
       <c r="AB7">
-        <v>5.11</v>
+        <v>5.5</v>
       </c>
       <c r="AC7">
-        <v>89.5</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="AD7">
-        <v>93.56999999999999</v>
+        <v>89.87</v>
       </c>
       <c r="AE7">
-        <v>15.79</v>
+        <v>16.13</v>
       </c>
       <c r="AF7">
-        <v>29.26</v>
+        <v>117.17</v>
       </c>
       <c r="AG7">
-        <v>605.41</v>
+        <v>610.4</v>
       </c>
       <c r="AH7">
-        <v>558</v>
+        <v>555.78</v>
       </c>
       <c r="AI7">
-        <v>558.51</v>
+        <v>568.8</v>
       </c>
       <c r="AJ7" t="s">
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>34.59</v>
+        <v>38.21</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1605,10 +1580,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>224.88</v>
+        <v>223.88</v>
       </c>
       <c r="D8">
-        <v>-0.31</v>
+        <v>-0.44</v>
       </c>
       <c r="E8">
         <v>363.5</v>
@@ -1617,25 +1592,25 @@
         <v>210.4</v>
       </c>
       <c r="G8">
-        <v>-38.13</v>
+        <v>-38.41</v>
       </c>
       <c r="H8">
-        <v>6.88</v>
+        <v>6.41</v>
       </c>
       <c r="I8">
-        <v>-3.58</v>
+        <v>-3.07</v>
       </c>
       <c r="J8">
-        <v>-0.25</v>
+        <v>-0.91</v>
       </c>
       <c r="K8">
-        <v>-2.2</v>
+        <v>-4.51</v>
       </c>
       <c r="L8">
-        <v>-36.07</v>
+        <v>-36.11</v>
       </c>
       <c r="M8">
-        <v>2.52</v>
+        <v>1.69</v>
       </c>
       <c r="N8">
         <v>12</v>
@@ -1644,19 +1619,19 @@
         <v>16</v>
       </c>
       <c r="P8">
-        <v>228.28</v>
+        <v>226.86</v>
       </c>
       <c r="Q8">
-        <v>223.52</v>
+        <v>223.22</v>
       </c>
       <c r="R8">
-        <v>228.39</v>
+        <v>228.63</v>
       </c>
       <c r="S8">
-        <v>269.4</v>
+        <v>268.85</v>
       </c>
       <c r="T8">
-        <v>-16.52</v>
+        <v>-16.73</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1671,34 +1646,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>48.39</v>
+        <v>47.27</v>
       </c>
       <c r="Z8">
-        <v>-0.31</v>
+        <v>-0.44</v>
       </c>
       <c r="AA8">
-        <v>-1.28</v>
+        <v>-1.12</v>
       </c>
       <c r="AB8">
-        <v>0.98</v>
+        <v>0.67</v>
       </c>
       <c r="AC8">
-        <v>64.54000000000001</v>
+        <v>50.43</v>
       </c>
       <c r="AD8">
-        <v>76.09999999999999</v>
+        <v>63.63</v>
       </c>
       <c r="AE8">
-        <v>7.2</v>
+        <v>6.91</v>
       </c>
       <c r="AF8">
-        <v>-69.56999999999999</v>
+        <v>-76.69</v>
       </c>
       <c r="AG8">
-        <v>235.91</v>
+        <v>235.23</v>
       </c>
       <c r="AH8">
-        <v>211.13</v>
+        <v>211.2</v>
       </c>
       <c r="AI8">
         <v>237.22</v>
@@ -1707,7 +1682,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>30.31</v>
+        <v>29.2</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1718,10 +1693,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>3608.9</v>
+        <v>3618.2</v>
       </c>
       <c r="D9">
-        <v>0.31</v>
+        <v>0.26</v>
       </c>
       <c r="E9">
         <v>4497.5</v>
@@ -1730,46 +1705,46 @@
         <v>3308.9</v>
       </c>
       <c r="G9">
-        <v>-19.76</v>
+        <v>-19.55</v>
       </c>
       <c r="H9">
-        <v>9.07</v>
+        <v>9.35</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="J9">
-        <v>-3.94</v>
+        <v>-4.01</v>
       </c>
       <c r="K9">
-        <v>-4.98</v>
+        <v>-3.79</v>
       </c>
       <c r="L9">
-        <v>-7.91</v>
+        <v>-8.48</v>
       </c>
       <c r="M9">
-        <v>18.75</v>
+        <v>18.64</v>
       </c>
       <c r="N9">
         <v>23</v>
       </c>
       <c r="O9">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P9">
-        <v>3601.06</v>
+        <v>3605.54</v>
       </c>
       <c r="Q9">
-        <v>3613.38</v>
+        <v>3607.71</v>
       </c>
       <c r="R9">
-        <v>3751.24</v>
+        <v>3748.04</v>
       </c>
       <c r="S9">
-        <v>3721.14</v>
+        <v>3719.07</v>
       </c>
       <c r="T9">
-        <v>-3.02</v>
+        <v>-2.71</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1784,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>41.42</v>
+        <v>43.21</v>
       </c>
       <c r="Z9">
-        <v>-44.75</v>
+        <v>-40.92</v>
       </c>
       <c r="AA9">
-        <v>-53.15</v>
+        <v>-50.7</v>
       </c>
       <c r="AB9">
-        <v>8.390000000000001</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="AC9">
-        <v>88.06999999999999</v>
+        <v>93.02</v>
       </c>
       <c r="AD9">
-        <v>84</v>
+        <v>87.94</v>
       </c>
       <c r="AE9">
-        <v>65</v>
+        <v>62.35</v>
       </c>
       <c r="AF9">
-        <v>-53.15</v>
+        <v>-69.2</v>
       </c>
       <c r="AG9">
-        <v>3702.82</v>
+        <v>3677.9</v>
       </c>
       <c r="AH9">
-        <v>3523.94</v>
+        <v>3537.52</v>
       </c>
       <c r="AI9">
         <v>3794.41</v>
@@ -1820,7 +1795,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>13.2</v>
+        <v>13.33</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1831,10 +1806,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>1625</v>
+        <v>1639</v>
       </c>
       <c r="D10">
-        <v>-1.1</v>
+        <v>0.86</v>
       </c>
       <c r="E10">
         <v>1768.4</v>
@@ -1843,46 +1818,46 @@
         <v>1326.2</v>
       </c>
       <c r="G10">
-        <v>-8.109999999999999</v>
+        <v>-7.32</v>
       </c>
       <c r="H10">
-        <v>22.53</v>
+        <v>23.59</v>
       </c>
       <c r="I10">
-        <v>-1.52</v>
+        <v>0.42</v>
       </c>
       <c r="J10">
-        <v>9.48</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="K10">
-        <v>20.96</v>
+        <v>19.59</v>
       </c>
       <c r="L10">
-        <v>12.54</v>
+        <v>11.75</v>
       </c>
       <c r="M10">
-        <v>6.34</v>
+        <v>6.58</v>
       </c>
       <c r="N10">
         <v>77</v>
       </c>
       <c r="O10">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="P10">
-        <v>1635.04</v>
+        <v>1636.4</v>
       </c>
       <c r="Q10">
-        <v>1610.46</v>
+        <v>1616.9</v>
       </c>
       <c r="R10">
-        <v>1512.04</v>
+        <v>1515.37</v>
       </c>
       <c r="S10">
-        <v>1501.39</v>
+        <v>1502.31</v>
       </c>
       <c r="T10">
-        <v>8.23</v>
+        <v>9.1</v>
       </c>
       <c r="U10" t="s">
         <v>48</v>
@@ -1897,34 +1872,34 @@
         <v>3</v>
       </c>
       <c r="Y10">
-        <v>60.38</v>
+        <v>62.94</v>
       </c>
       <c r="Z10">
-        <v>40.33</v>
+        <v>38.39</v>
       </c>
       <c r="AA10">
-        <v>44.61</v>
+        <v>43.36</v>
       </c>
       <c r="AB10">
-        <v>-4.27</v>
+        <v>-4.97</v>
       </c>
       <c r="AC10">
-        <v>22.51</v>
+        <v>18.42</v>
       </c>
       <c r="AD10">
-        <v>26.58</v>
+        <v>23.96</v>
       </c>
       <c r="AE10">
-        <v>40.92</v>
+        <v>39.99</v>
       </c>
       <c r="AF10">
-        <v>19.28</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="AG10">
-        <v>1699.5</v>
+        <v>1693.14</v>
       </c>
       <c r="AH10">
-        <v>1521.42</v>
+        <v>1540.65</v>
       </c>
       <c r="AI10">
         <v>1527.05</v>
@@ -1933,7 +1908,7 @@
         <v>50</v>
       </c>
       <c r="AK10">
-        <v>36.16</v>
+        <v>32.86</v>
       </c>
     </row>
   </sheetData>
@@ -2074,7 +2049,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2094,1352 +2069,1297 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>-10.22</v>
+      </c>
+      <c r="D7" s="5">
+        <v>-11.39</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-1.17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>10.03</v>
+      </c>
+      <c r="D8" s="5">
+        <v>11.2</v>
+      </c>
+      <c r="E8" s="7">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>21.76</v>
+      </c>
+      <c r="D9" s="5">
+        <v>21.99</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5">
+        <v>2.81</v>
+      </c>
+      <c r="D10" s="5">
+        <v>3.26</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>3.37</v>
+      </c>
+      <c r="D11" s="5">
+        <v>4.53</v>
+      </c>
+      <c r="E11" s="7">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="5">
+        <v>3.54</v>
+      </c>
+      <c r="D12" s="5">
+        <v>3.95</v>
+      </c>
+      <c r="E12" s="7">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="5">
+        <v>-0.25</v>
+      </c>
+      <c r="D13" s="5">
+        <v>-0.91</v>
+      </c>
+      <c r="E13" s="6">
+        <v>-0.66</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-3.94</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-4.01</v>
+      </c>
+      <c r="E14" s="6">
+        <v>-0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="5">
+        <v>9.48</v>
+      </c>
+      <c r="D15" s="5">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="E15" s="6">
+        <v>-0.12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-0.41</v>
+      </c>
+      <c r="E16" s="7">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-1.5</v>
+      </c>
+      <c r="D17" s="5">
+        <v>0.65</v>
+      </c>
+      <c r="E17" s="7">
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-0.64</v>
+      </c>
+      <c r="D18" s="5">
+        <v>1.95</v>
+      </c>
+      <c r="E18" s="7">
+        <v>2.59</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="5">
         <v>0</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="D19" s="5">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="E19" s="6">
+        <v>-0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-1.58</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-1.91</v>
+      </c>
+      <c r="E20" s="6">
+        <v>-0.33</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="5">
+        <v>4.69</v>
+      </c>
+      <c r="D21" s="5">
+        <v>4.83</v>
+      </c>
+      <c r="E21" s="7">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="5">
+        <v>-3.58</v>
+      </c>
+      <c r="D22" s="5">
+        <v>-3.07</v>
+      </c>
+      <c r="E22" s="7">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="5">
+        <v>0</v>
+      </c>
+      <c r="D23" s="5">
+        <v>0.62</v>
+      </c>
+      <c r="E23" s="7">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-1.52</v>
+      </c>
+      <c r="D24" s="5">
+        <v>0.42</v>
+      </c>
+      <c r="E24" s="7">
+        <v>1.94</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>-12.02</v>
-      </c>
-      <c r="D8" s="6">
-        <v>-10.22</v>
-      </c>
-      <c r="E8" s="7">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="B25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="5">
+        <v>3.61</v>
+      </c>
+      <c r="D25" s="5">
+        <v>3.72</v>
+      </c>
+      <c r="E25" s="7">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>9.48</v>
-      </c>
-      <c r="D9" s="6">
-        <v>10.03</v>
-      </c>
-      <c r="E9" s="7">
+      <c r="B26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="5">
+        <v>5.46</v>
+      </c>
+      <c r="D26" s="5">
+        <v>6.76</v>
+      </c>
+      <c r="E26" s="7">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="5">
+        <v>56.25</v>
+      </c>
+      <c r="D27" s="5">
+        <v>56.31</v>
+      </c>
+      <c r="E27" s="7">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="5">
+        <v>8.27</v>
+      </c>
+      <c r="D28" s="5">
+        <v>10.64</v>
+      </c>
+      <c r="E28" s="7">
+        <v>2.37</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="5">
+        <v>30.08</v>
+      </c>
+      <c r="D29" s="5">
+        <v>27.79</v>
+      </c>
+      <c r="E29" s="6">
+        <v>-2.29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-7.66</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-6.63</v>
+      </c>
+      <c r="E30" s="7">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-36.07</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-36.11</v>
+      </c>
+      <c r="E31" s="6">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="5">
+        <v>-7.91</v>
+      </c>
+      <c r="D32" s="5">
+        <v>-8.48</v>
+      </c>
+      <c r="E32" s="6">
+        <v>-0.57</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="5">
+        <v>12.54</v>
+      </c>
+      <c r="D33" s="5">
+        <v>11.75</v>
+      </c>
+      <c r="E33" s="6">
+        <v>-0.79</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="5">
+        <v>-9.67</v>
+      </c>
+      <c r="D34" s="5">
+        <v>-11.32</v>
+      </c>
+      <c r="E34" s="6">
+        <v>-1.65</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="5">
+        <v>7.24</v>
+      </c>
+      <c r="D35" s="5">
+        <v>9.77</v>
+      </c>
+      <c r="E35" s="7">
+        <v>2.53</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="5">
+        <v>23.36</v>
+      </c>
+      <c r="D36" s="5">
+        <v>23.62</v>
+      </c>
+      <c r="E36" s="7">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="5">
+        <v>18.2</v>
+      </c>
+      <c r="D37" s="5">
+        <v>17.55</v>
+      </c>
+      <c r="E37" s="6">
+        <v>-0.65</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="5">
+        <v>11.08</v>
+      </c>
+      <c r="D38" s="5">
+        <v>12.45</v>
+      </c>
+      <c r="E38" s="7">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="5">
+        <v>-5.7</v>
+      </c>
+      <c r="D39" s="5">
+        <v>-5.08</v>
+      </c>
+      <c r="E39" s="7">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="5">
+        <v>-2.2</v>
+      </c>
+      <c r="D40" s="5">
+        <v>-4.51</v>
+      </c>
+      <c r="E40" s="6">
+        <v>-2.31</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="5">
+        <v>-4.98</v>
+      </c>
+      <c r="D41" s="5">
+        <v>-3.79</v>
+      </c>
+      <c r="E41" s="7">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="5">
+        <v>20.96</v>
+      </c>
+      <c r="D42" s="5">
+        <v>19.59</v>
+      </c>
+      <c r="E42" s="6">
+        <v>-1.37</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="5">
+        <v>-16.01</v>
+      </c>
+      <c r="D43" s="5">
+        <v>-16.65</v>
+      </c>
+      <c r="E43" s="6">
+        <v>-0.64</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="5">
+        <v>-10.49</v>
+      </c>
+      <c r="D44" s="5">
+        <v>-9.84</v>
+      </c>
+      <c r="E44" s="7">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="5">
+        <v>-3.99</v>
+      </c>
+      <c r="D45" s="5">
+        <v>-3.86</v>
+      </c>
+      <c r="E45" s="7">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="5">
+        <v>-9.210000000000001</v>
+      </c>
+      <c r="D46" s="5">
+        <v>-9</v>
+      </c>
+      <c r="E46" s="7">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="5">
+        <v>-8.08</v>
+      </c>
+      <c r="D47" s="5">
+        <v>-8.289999999999999</v>
+      </c>
+      <c r="E47" s="6">
+        <v>-0.21</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="5">
+        <v>-10.5</v>
+      </c>
+      <c r="D48" s="5">
+        <v>-10.2</v>
+      </c>
+      <c r="E48" s="7">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="5">
+        <v>-38.13</v>
+      </c>
+      <c r="D49" s="5">
+        <v>-38.41</v>
+      </c>
+      <c r="E49" s="6">
+        <v>-0.28</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="5">
+        <v>-19.76</v>
+      </c>
+      <c r="D50" s="5">
+        <v>-19.55</v>
+      </c>
+      <c r="E50" s="7">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="5">
+        <v>-8.109999999999999</v>
+      </c>
+      <c r="D51" s="5">
+        <v>-7.32</v>
+      </c>
+      <c r="E51" s="7">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="5">
+        <v>411.7</v>
+      </c>
+      <c r="D52" s="5">
+        <v>408.6</v>
+      </c>
+      <c r="E52" s="6">
+        <v>-3.1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="5">
+        <v>3403.6</v>
+      </c>
+      <c r="D53" s="5">
+        <v>3428.2</v>
+      </c>
+      <c r="E53" s="7">
+        <v>24.6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="5">
+        <v>395.85</v>
+      </c>
+      <c r="D54" s="5">
+        <v>396.4</v>
+      </c>
+      <c r="E54" s="7">
         <v>0.55</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>19.87</v>
-      </c>
-      <c r="D10" s="6">
-        <v>21.76</v>
-      </c>
-      <c r="E10" s="7">
-        <v>1.89</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+    <row r="55" spans="1:5">
+      <c r="A55" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>1.07</v>
-      </c>
-      <c r="D11" s="6">
-        <v>2.81</v>
-      </c>
-      <c r="E11" s="7">
-        <v>1.74</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B55" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="5">
+        <v>382.85</v>
+      </c>
+      <c r="D55" s="5">
+        <v>383.75</v>
+      </c>
+      <c r="E55" s="7">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>6.95</v>
-      </c>
-      <c r="D12" s="6">
-        <v>3.37</v>
-      </c>
-      <c r="E12" s="8">
-        <v>-3.58</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B56" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="5">
+        <v>406.95</v>
+      </c>
+      <c r="D56" s="5">
+        <v>406</v>
+      </c>
+      <c r="E56" s="6">
+        <v>-0.95</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="6">
-        <v>0.53</v>
-      </c>
-      <c r="D13" s="6">
-        <v>3.54</v>
-      </c>
-      <c r="E13" s="7">
-        <v>3.01</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B57" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="5">
+        <v>609.95</v>
+      </c>
+      <c r="D57" s="5">
+        <v>612</v>
+      </c>
+      <c r="E57" s="7">
+        <v>2.05</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-2.64</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-0.25</v>
-      </c>
-      <c r="E14" s="7">
-        <v>2.39</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B58" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="5">
+        <v>224.88</v>
+      </c>
+      <c r="D58" s="5">
+        <v>223.88</v>
+      </c>
+      <c r="E58" s="6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-5.06</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-3.94</v>
-      </c>
-      <c r="E15" s="7">
-        <v>1.12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B59" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="5">
+        <v>3608.9</v>
+      </c>
+      <c r="D59" s="5">
+        <v>3618.2</v>
+      </c>
+      <c r="E59" s="7">
+        <v>9.300000000000001</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="6">
-        <v>9.210000000000001</v>
-      </c>
-      <c r="D16" s="6">
-        <v>9.48</v>
-      </c>
-      <c r="E16" s="7">
-        <v>0.27</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B60" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="5">
+        <v>1625</v>
+      </c>
+      <c r="D60" s="5">
+        <v>1639</v>
+      </c>
+      <c r="E60" s="7">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>0.58</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-0.8100000000000001</v>
-      </c>
-      <c r="E17" s="8">
-        <v>-1.39</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>0.79</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-1.5</v>
-      </c>
-      <c r="E18" s="8">
-        <v>-2.29</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>0.05</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-0.64</v>
-      </c>
-      <c r="E19" s="8">
-        <v>-0.6899999999999999</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-3.75</v>
-      </c>
-      <c r="D20" s="6">
-        <v>0</v>
-      </c>
-      <c r="E20" s="7">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-2.77</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-1.58</v>
-      </c>
-      <c r="E21" s="7">
-        <v>1.19</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B61" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C61" s="5">
+        <v>45</v>
+      </c>
+      <c r="D61" s="5">
+        <v>34</v>
+      </c>
+      <c r="E61" s="6">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="6">
-        <v>2.75</v>
-      </c>
-      <c r="D22" s="6">
-        <v>4.69</v>
-      </c>
-      <c r="E22" s="7">
-        <v>1.94</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-1.06</v>
-      </c>
-      <c r="D23" s="6">
-        <v>-3.58</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-2.52</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-0.02</v>
-      </c>
-      <c r="D24" s="6">
-        <v>0</v>
-      </c>
-      <c r="E24" s="7">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B62" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C62" s="5">
+        <v>34</v>
+      </c>
+      <c r="D62" s="5">
         <v>45</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-0.33</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-1.52</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-1.19</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>2.88</v>
-      </c>
-      <c r="D26" s="6">
-        <v>3.61</v>
-      </c>
-      <c r="E26" s="7">
-        <v>0.73</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>7.72</v>
-      </c>
-      <c r="D27" s="6">
-        <v>5.46</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-2.26</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="6">
-        <v>55.51</v>
-      </c>
-      <c r="D28" s="6">
-        <v>56.25</v>
-      </c>
-      <c r="E28" s="7">
-        <v>0.74</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="6">
-        <v>7.43</v>
-      </c>
-      <c r="D29" s="6">
-        <v>8.27</v>
-      </c>
-      <c r="E29" s="7">
-        <v>0.84</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="6">
-        <v>30.01</v>
-      </c>
-      <c r="D30" s="6">
-        <v>30.08</v>
-      </c>
-      <c r="E30" s="7">
-        <v>0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-11.92</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-7.66</v>
-      </c>
-      <c r="E31" s="7">
-        <v>4.26</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-36.49</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-36.07</v>
-      </c>
-      <c r="E32" s="7">
-        <v>0.42</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="6">
-        <v>-10.1</v>
-      </c>
-      <c r="D33" s="6">
-        <v>-7.91</v>
-      </c>
-      <c r="E33" s="7">
-        <v>2.19</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="6">
-        <v>11.77</v>
-      </c>
-      <c r="D34" s="6">
-        <v>12.54</v>
-      </c>
-      <c r="E34" s="7">
-        <v>0.77</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="6">
-        <v>-9.81</v>
-      </c>
-      <c r="D35" s="6">
-        <v>-9.67</v>
-      </c>
-      <c r="E35" s="7">
-        <v>0.14</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="6">
-        <v>11.19</v>
-      </c>
-      <c r="D36" s="6">
-        <v>7.24</v>
-      </c>
-      <c r="E36" s="8">
-        <v>-3.95</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="6">
-        <v>24.59</v>
-      </c>
-      <c r="D37" s="6">
-        <v>23.36</v>
-      </c>
-      <c r="E37" s="8">
-        <v>-1.23</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="6">
-        <v>17.54</v>
-      </c>
-      <c r="D38" s="6">
-        <v>18.2</v>
-      </c>
-      <c r="E38" s="7">
-        <v>0.66</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="6">
-        <v>9.92</v>
-      </c>
-      <c r="D39" s="6">
-        <v>11.08</v>
-      </c>
-      <c r="E39" s="7">
-        <v>1.16</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-8.289999999999999</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-5.7</v>
-      </c>
-      <c r="E40" s="7">
-        <v>2.59</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="6">
-        <v>0.79</v>
-      </c>
-      <c r="D41" s="6">
-        <v>-2.2</v>
-      </c>
-      <c r="E41" s="8">
-        <v>-2.99</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="6">
-        <v>-5.16</v>
-      </c>
-      <c r="D42" s="6">
-        <v>-4.98</v>
-      </c>
-      <c r="E42" s="7">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="6">
-        <v>19.49</v>
-      </c>
-      <c r="D43" s="6">
-        <v>20.96</v>
-      </c>
-      <c r="E43" s="7">
-        <v>1.47</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="6">
-        <v>-15.75</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-16.01</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-0.26</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-9</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-10.49</v>
-      </c>
-      <c r="E45" s="8">
-        <v>-1.49</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-3.27</v>
-      </c>
-      <c r="D46" s="6">
-        <v>-3.99</v>
-      </c>
-      <c r="E46" s="8">
-        <v>-0.72</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="6">
-        <v>-9.26</v>
-      </c>
-      <c r="D47" s="6">
-        <v>-9.210000000000001</v>
-      </c>
-      <c r="E47" s="7">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="6">
-        <v>-7.53</v>
-      </c>
-      <c r="D48" s="6">
-        <v>-8.08</v>
-      </c>
-      <c r="E48" s="8">
-        <v>-0.55</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="6">
-        <v>-12.69</v>
-      </c>
-      <c r="D49" s="6">
-        <v>-10.5</v>
-      </c>
-      <c r="E49" s="7">
-        <v>2.19</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="6">
-        <v>-37.94</v>
-      </c>
-      <c r="D50" s="6">
-        <v>-38.13</v>
-      </c>
-      <c r="E50" s="8">
-        <v>-0.19</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="6">
-        <v>-20</v>
-      </c>
-      <c r="D51" s="6">
-        <v>-19.76</v>
-      </c>
-      <c r="E51" s="7">
-        <v>0.24</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C52" s="6">
-        <v>-7.09</v>
-      </c>
-      <c r="D52" s="6">
-        <v>-8.109999999999999</v>
-      </c>
-      <c r="E52" s="8">
-        <v>-1.02</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="6">
-        <v>413</v>
-      </c>
-      <c r="D53" s="6">
-        <v>411.7</v>
-      </c>
-      <c r="E53" s="8">
-        <v>-1.3</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="6">
-        <v>3460.1</v>
-      </c>
-      <c r="D54" s="6">
-        <v>3403.6</v>
-      </c>
-      <c r="E54" s="8">
-        <v>-56.5</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="6">
-        <v>398.8</v>
-      </c>
-      <c r="D55" s="6">
-        <v>395.85</v>
-      </c>
-      <c r="E55" s="8">
-        <v>-2.95</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="6">
-        <v>382.65</v>
-      </c>
-      <c r="D56" s="6">
-        <v>382.85</v>
-      </c>
-      <c r="E56" s="7">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="6">
-        <v>409.35</v>
-      </c>
-      <c r="D57" s="6">
-        <v>406.95</v>
-      </c>
-      <c r="E57" s="8">
-        <v>-2.4</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="6">
-        <v>595</v>
-      </c>
-      <c r="D58" s="6">
-        <v>609.95</v>
-      </c>
-      <c r="E58" s="7">
-        <v>14.95</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="6">
-        <v>225.57</v>
-      </c>
-      <c r="D59" s="6">
-        <v>224.88</v>
-      </c>
-      <c r="E59" s="8">
-        <v>-0.6899999999999999</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="6">
-        <v>3597.9</v>
-      </c>
-      <c r="D60" s="6">
-        <v>3608.9</v>
-      </c>
-      <c r="E60" s="7">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C61" s="6">
-        <v>1643</v>
-      </c>
-      <c r="D61" s="6">
-        <v>1625</v>
-      </c>
-      <c r="E61" s="8">
-        <v>-18</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C62" s="6">
-        <v>23</v>
-      </c>
-      <c r="D62" s="6">
-        <v>34</v>
       </c>
       <c r="E62" s="7">
         <v>11</v>
       </c>
     </row>
     <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
+      <c r="A63" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="5">
+        <v>37.52</v>
+      </c>
+      <c r="D63" s="5">
+        <v>35.98</v>
+      </c>
+      <c r="E63" s="6">
+        <v>-1.54</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="5">
+        <v>58.1</v>
+      </c>
+      <c r="D64" s="5">
+        <v>59.7</v>
+      </c>
+      <c r="E64" s="7">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="5">
+        <v>60.97</v>
+      </c>
+      <c r="D65" s="5">
+        <v>61.16</v>
+      </c>
+      <c r="E65" s="7">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="5">
+        <v>54.03</v>
+      </c>
+      <c r="D66" s="5">
+        <v>54.85</v>
+      </c>
+      <c r="E66" s="7">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="5">
+        <v>53.84</v>
+      </c>
+      <c r="D67" s="5">
+        <v>53.21</v>
+      </c>
+      <c r="E67" s="6">
+        <v>-0.63</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="5">
+        <v>59.45</v>
+      </c>
+      <c r="D68" s="5">
+        <v>60.23</v>
+      </c>
+      <c r="E68" s="7">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="5">
+        <v>48.39</v>
+      </c>
+      <c r="D69" s="5">
+        <v>47.27</v>
+      </c>
+      <c r="E69" s="6">
+        <v>-1.12</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B63" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C63" s="6">
-        <v>34</v>
-      </c>
-      <c r="D63" s="6">
-        <v>23</v>
-      </c>
-      <c r="E63" s="8">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
+      <c r="B70" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="5">
+        <v>41.42</v>
+      </c>
+      <c r="D70" s="5">
+        <v>43.21</v>
+      </c>
+      <c r="E70" s="7">
+        <v>1.79</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="5">
+        <v>60.38</v>
+      </c>
+      <c r="D71" s="5">
+        <v>62.94</v>
+      </c>
+      <c r="E71" s="7">
+        <v>2.56</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B64" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="6">
-        <v>38.16</v>
-      </c>
-      <c r="D64" s="6">
-        <v>37.52</v>
-      </c>
-      <c r="E64" s="8">
-        <v>-0.64</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
+      <c r="B72" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C72" s="5">
+        <v>-31.88</v>
+      </c>
+      <c r="D72" s="5">
+        <v>-75.97</v>
+      </c>
+      <c r="E72" s="6">
+        <v>-44.09</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B65" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="6">
-        <v>63.49</v>
-      </c>
-      <c r="D65" s="6">
-        <v>58.1</v>
-      </c>
-      <c r="E65" s="8">
-        <v>-5.39</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="5" t="s">
+      <c r="B73" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="5">
+        <v>-28.7</v>
+      </c>
+      <c r="D73" s="5">
+        <v>-10.01</v>
+      </c>
+      <c r="E73" s="7">
+        <v>18.69</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B66" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="6">
-        <v>62.47</v>
-      </c>
-      <c r="D66" s="6">
-        <v>60.97</v>
-      </c>
-      <c r="E66" s="8">
-        <v>-1.5</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="5" t="s">
+      <c r="B74" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="5">
+        <v>-34.56</v>
+      </c>
+      <c r="D74" s="5">
+        <v>-61.92</v>
+      </c>
+      <c r="E74" s="6">
+        <v>-27.36</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B67" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="6">
-        <v>53.86</v>
-      </c>
-      <c r="D67" s="6">
-        <v>54.03</v>
-      </c>
-      <c r="E67" s="7">
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="5" t="s">
+      <c r="B75" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="5">
+        <v>-80.61</v>
+      </c>
+      <c r="D75" s="5">
+        <v>-72.97</v>
+      </c>
+      <c r="E75" s="7">
+        <v>7.64</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B68" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="6">
-        <v>55.39</v>
-      </c>
-      <c r="D68" s="6">
-        <v>53.84</v>
-      </c>
-      <c r="E68" s="8">
-        <v>-1.55</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="5" t="s">
+      <c r="B76" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="5">
+        <v>-64.93000000000001</v>
+      </c>
+      <c r="D76" s="5">
+        <v>-74.70999999999999</v>
+      </c>
+      <c r="E76" s="6">
+        <v>-9.779999999999999</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B69" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="6">
-        <v>53.23</v>
-      </c>
-      <c r="D69" s="6">
-        <v>59.45</v>
-      </c>
-      <c r="E69" s="7">
-        <v>6.22</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="5" t="s">
+      <c r="B77" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="5">
+        <v>29.26</v>
+      </c>
+      <c r="D77" s="5">
+        <v>117.17</v>
+      </c>
+      <c r="E77" s="7">
+        <v>87.91</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B70" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="6">
-        <v>49.14</v>
-      </c>
-      <c r="D70" s="6">
-        <v>48.39</v>
-      </c>
-      <c r="E70" s="8">
-        <v>-0.75</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="5" t="s">
+      <c r="B78" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="5">
+        <v>-69.56999999999999</v>
+      </c>
+      <c r="D78" s="5">
+        <v>-76.69</v>
+      </c>
+      <c r="E78" s="6">
+        <v>-7.12</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B71" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="6">
-        <v>39.32</v>
-      </c>
-      <c r="D71" s="6">
-        <v>41.42</v>
-      </c>
-      <c r="E71" s="7">
-        <v>2.1</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="5" t="s">
+      <c r="B79" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="5">
+        <v>-53.15</v>
+      </c>
+      <c r="D79" s="5">
+        <v>-69.2</v>
+      </c>
+      <c r="E79" s="6">
+        <v>-16.05</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B72" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C72" s="6">
-        <v>65.81</v>
-      </c>
-      <c r="D72" s="6">
-        <v>60.38</v>
-      </c>
-      <c r="E72" s="8">
-        <v>-5.43</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B73" s="5" t="s">
+      <c r="B80" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C73" s="6">
-        <v>486.43</v>
-      </c>
-      <c r="D73" s="6">
-        <v>-31.88</v>
-      </c>
-      <c r="E73" s="8">
-        <v>-518.3099999999999</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="6">
-        <v>-10.8</v>
-      </c>
-      <c r="D74" s="6">
-        <v>-28.7</v>
-      </c>
-      <c r="E74" s="8">
-        <v>-17.9</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="6">
-        <v>-76.97</v>
-      </c>
-      <c r="D75" s="6">
-        <v>-34.56</v>
-      </c>
-      <c r="E75" s="7">
-        <v>42.41</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="6">
-        <v>-80.16</v>
-      </c>
-      <c r="D76" s="6">
-        <v>-80.61</v>
-      </c>
-      <c r="E76" s="8">
-        <v>-0.45</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="6">
-        <v>-69.63</v>
-      </c>
-      <c r="D77" s="6">
-        <v>-64.93000000000001</v>
-      </c>
-      <c r="E77" s="7">
-        <v>4.7</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="6">
-        <v>69.17</v>
-      </c>
-      <c r="D78" s="6">
-        <v>29.26</v>
-      </c>
-      <c r="E78" s="8">
-        <v>-39.91</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="6">
-        <v>-69.34999999999999</v>
-      </c>
-      <c r="D79" s="6">
-        <v>-69.56999999999999</v>
-      </c>
-      <c r="E79" s="8">
-        <v>-0.22</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="6">
-        <v>-68.76000000000001</v>
-      </c>
-      <c r="D80" s="6">
-        <v>-53.15</v>
-      </c>
-      <c r="E80" s="7">
-        <v>15.61</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="6">
-        <v>-39.13</v>
-      </c>
-      <c r="D81" s="6">
+      <c r="C80" s="5">
         <v>19.28</v>
       </c>
-      <c r="E81" s="7">
-        <v>58.41</v>
+      <c r="D80" s="5">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="E80" s="6">
+        <v>-10.91</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3459,60 +3379,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="F1" s="9" t="s">
+      <c r="B1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" s="10">
+        <v>60.16</v>
+      </c>
+      <c r="C2" s="11">
+        <v>9</v>
+      </c>
+      <c r="D2" s="10">
+        <v>53.2</v>
+      </c>
+      <c r="E2" s="10">
         <v>70</v>
       </c>
-      <c r="G1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="B2" s="11">
-        <v>60.16</v>
-      </c>
-      <c r="C2" s="12">
-        <v>9</v>
-      </c>
-      <c r="D2" s="11">
-        <v>52.7</v>
-      </c>
-      <c r="E2" s="11">
-        <v>70</v>
-      </c>
-      <c r="F2" s="11">
-        <v>4.1</v>
-      </c>
-      <c r="G2" s="11">
+      <c r="F2" s="10">
+        <v>4.2</v>
+      </c>
+      <c r="G2" s="10">
         <v>6.5</v>
       </c>
-      <c r="H2" s="11">
+      <c r="H2" s="10">
         <v>55.4</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>30</v>
       </c>
     </row>
@@ -3614,61 +3534,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="12" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="14">
-        <v>0.3537</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.3337</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.2254</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.1875</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.1195</v>
-      </c>
-      <c r="F2" s="14">
-        <v>0.096</v>
-      </c>
-      <c r="G2" s="14">
-        <v>0.0634</v>
-      </c>
-      <c r="H2" s="14">
-        <v>0.0252</v>
-      </c>
-      <c r="I2" s="14">
-        <v>-0.09329999999999999</v>
+      <c r="A2" s="13">
+        <v>0.3547999999999999</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.3217</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.232</v>
+      </c>
+      <c r="D2" s="13">
+        <v>0.1864</v>
+      </c>
+      <c r="E2" s="13">
+        <v>0.1213</v>
+      </c>
+      <c r="F2" s="13">
+        <v>0.094</v>
+      </c>
+      <c r="G2" s="13">
+        <v>0.0658</v>
+      </c>
+      <c r="H2" s="13">
+        <v>0.0169</v>
+      </c>
+      <c r="I2" s="13">
+        <v>-0.09810000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/MAHINDRA_GROUP_Technical_Metrics.xlsx
+++ b/MAHINDRA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="78">
   <si>
     <t>Symbol</t>
   </si>
@@ -178,7 +178,43 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>50 DMA &gt; 200 DMA</t>
+  </si>
+  <si>
+    <t>No → Yes</t>
+  </si>
+  <si>
+    <t>🟢 GOLDEN CROSS</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>47.3 → 50.6</t>
+  </si>
+  <si>
+    <t>47.3</t>
+  </si>
+  <si>
+    <t>50.6</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -264,14 +300,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -304,13 +340,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,17 +416,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -902,10 +939,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>408.6</v>
+        <v>407.75</v>
       </c>
       <c r="D2">
-        <v>-0.75</v>
+        <v>-0.21</v>
       </c>
       <c r="E2">
         <v>490.2</v>
@@ -914,46 +951,46 @@
         <v>379.2</v>
       </c>
       <c r="G2">
-        <v>-16.65</v>
+        <v>-16.82</v>
       </c>
       <c r="H2">
-        <v>7.75</v>
+        <v>7.53</v>
       </c>
       <c r="I2">
-        <v>-0.41</v>
+        <v>-0.67</v>
       </c>
       <c r="J2">
-        <v>-11.39</v>
+        <v>-13.72</v>
       </c>
       <c r="K2">
-        <v>-11.32</v>
+        <v>-10.3</v>
       </c>
       <c r="L2">
-        <v>3.72</v>
+        <v>3.74</v>
       </c>
       <c r="M2">
-        <v>12.13</v>
+        <v>12.1</v>
       </c>
       <c r="N2">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="O2">
         <v>38</v>
       </c>
       <c r="P2">
-        <v>410.66</v>
+        <v>410.11</v>
       </c>
       <c r="Q2">
-        <v>424.56</v>
+        <v>421.27</v>
       </c>
       <c r="R2">
-        <v>445.81</v>
+        <v>444.85</v>
       </c>
       <c r="S2">
-        <v>438.55</v>
+        <v>438.45</v>
       </c>
       <c r="T2">
-        <v>-6.83</v>
+        <v>-7</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -968,43 +1005,43 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>35.98</v>
+        <v>35.55</v>
       </c>
       <c r="Z2">
-        <v>-12.14</v>
+        <v>-11.85</v>
       </c>
       <c r="AA2">
-        <v>-12.26</v>
+        <v>-12.18</v>
       </c>
       <c r="AB2">
-        <v>0.12</v>
+        <v>0.33</v>
       </c>
       <c r="AC2">
-        <v>90.87</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="AD2">
-        <v>72.22</v>
+        <v>82.33</v>
       </c>
       <c r="AE2">
-        <v>11.94</v>
+        <v>11.47</v>
       </c>
       <c r="AF2">
-        <v>-75.97</v>
+        <v>-77.08</v>
       </c>
       <c r="AG2">
-        <v>474.81</v>
+        <v>466.33</v>
       </c>
       <c r="AH2">
-        <v>374.32</v>
+        <v>376.21</v>
       </c>
       <c r="AI2">
-        <v>446.81</v>
+        <v>443.72</v>
       </c>
       <c r="AJ2" t="s">
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>36.53</v>
+        <v>34.78</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1015,10 +1052,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>3428.2</v>
+        <v>3428.3</v>
       </c>
       <c r="D3">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>3802.4</v>
@@ -1033,40 +1070,40 @@
         <v>16.96</v>
       </c>
       <c r="I3">
-        <v>0.65</v>
+        <v>-2.1</v>
       </c>
       <c r="J3">
-        <v>11.2</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="K3">
-        <v>9.77</v>
+        <v>11.17</v>
       </c>
       <c r="L3">
-        <v>6.76</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="M3">
-        <v>35.48</v>
+        <v>34.82</v>
       </c>
       <c r="N3">
         <v>55</v>
       </c>
       <c r="O3">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="P3">
-        <v>3462.18</v>
+        <v>3447.44</v>
       </c>
       <c r="Q3">
-        <v>3328.02</v>
+        <v>3340.48</v>
       </c>
       <c r="R3">
-        <v>3185.47</v>
+        <v>3193.72</v>
       </c>
       <c r="S3">
-        <v>3357.15</v>
+        <v>3356.23</v>
       </c>
       <c r="T3">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="U3" t="s">
         <v>48</v>
@@ -1081,34 +1118,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>59.7</v>
+        <v>59.71</v>
       </c>
       <c r="Z3">
-        <v>83.34</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="AA3">
-        <v>78.06</v>
+        <v>78.33</v>
       </c>
       <c r="AB3">
-        <v>5.28</v>
+        <v>1.07</v>
       </c>
       <c r="AC3">
-        <v>43.13</v>
+        <v>31.46</v>
       </c>
       <c r="AD3">
-        <v>65.79000000000001</v>
+        <v>47</v>
       </c>
       <c r="AE3">
-        <v>75.06</v>
+        <v>73.39</v>
       </c>
       <c r="AF3">
-        <v>-10.01</v>
+        <v>-59.3</v>
       </c>
       <c r="AG3">
-        <v>3578.22</v>
+        <v>3584.19</v>
       </c>
       <c r="AH3">
-        <v>3077.83</v>
+        <v>3096.77</v>
       </c>
       <c r="AI3">
         <v>3274.47</v>
@@ -1117,7 +1154,7 @@
         <v>50</v>
       </c>
       <c r="AK3">
-        <v>49</v>
+        <v>43.48</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1128,100 +1165,100 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>396.4</v>
+        <v>390.1</v>
       </c>
       <c r="D4">
-        <v>0.14</v>
+        <v>-1.59</v>
       </c>
       <c r="E4">
         <v>412.3</v>
       </c>
       <c r="F4">
-        <v>252.5</v>
+        <v>253.95</v>
       </c>
       <c r="G4">
-        <v>-3.86</v>
+        <v>-5.38</v>
       </c>
       <c r="H4">
-        <v>56.99</v>
+        <v>53.61</v>
       </c>
       <c r="I4">
-        <v>1.95</v>
+        <v>-4.49</v>
       </c>
       <c r="J4">
-        <v>21.99</v>
+        <v>21.21</v>
       </c>
       <c r="K4">
-        <v>23.62</v>
+        <v>22.96</v>
       </c>
       <c r="L4">
-        <v>56.31</v>
+        <v>54.5</v>
       </c>
       <c r="M4">
-        <v>23.2</v>
+        <v>22.92</v>
       </c>
       <c r="N4">
         <v>99</v>
       </c>
       <c r="O4">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="P4">
-        <v>402.36</v>
+        <v>398.69</v>
       </c>
       <c r="Q4">
-        <v>380.66</v>
+        <v>383.96</v>
       </c>
       <c r="R4">
-        <v>337.72</v>
+        <v>339.74</v>
       </c>
       <c r="S4">
-        <v>338.8</v>
+        <v>339.26</v>
       </c>
       <c r="T4">
-        <v>17</v>
+        <v>14.99</v>
       </c>
       <c r="U4" t="s">
         <v>48</v>
       </c>
       <c r="V4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="W4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="X4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y4">
-        <v>61.16</v>
+        <v>57.74</v>
       </c>
       <c r="Z4">
-        <v>18.65</v>
+        <v>17.09</v>
       </c>
       <c r="AA4">
-        <v>19.56</v>
+        <v>19.06</v>
       </c>
       <c r="AB4">
-        <v>-0.9</v>
+        <v>-1.98</v>
       </c>
       <c r="AC4">
-        <v>0.97</v>
+        <v>0.52</v>
       </c>
       <c r="AD4">
-        <v>17.45</v>
+        <v>6.51</v>
       </c>
       <c r="AE4">
-        <v>15.8</v>
+        <v>15.5</v>
       </c>
       <c r="AF4">
-        <v>-61.92</v>
+        <v>-73.81999999999999</v>
       </c>
       <c r="AG4">
-        <v>432.6</v>
+        <v>428.67</v>
       </c>
       <c r="AH4">
-        <v>328.73</v>
+        <v>339.24</v>
       </c>
       <c r="AI4">
         <v>357.72</v>
@@ -1230,7 +1267,7 @@
         <v>50</v>
       </c>
       <c r="AK4">
-        <v>50.09</v>
+        <v>45.65</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1241,10 +1278,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>383.75</v>
+        <v>384.9</v>
       </c>
       <c r="D5">
-        <v>0.24</v>
+        <v>0.3</v>
       </c>
       <c r="E5">
         <v>421.7</v>
@@ -1253,46 +1290,46 @@
         <v>294.25</v>
       </c>
       <c r="G5">
-        <v>-9</v>
+        <v>-8.73</v>
       </c>
       <c r="H5">
-        <v>30.42</v>
+        <v>30.81</v>
       </c>
       <c r="I5">
-        <v>-0.6899999999999999</v>
+        <v>-0.43</v>
       </c>
       <c r="J5">
-        <v>3.26</v>
+        <v>2.03</v>
       </c>
       <c r="K5">
-        <v>17.55</v>
+        <v>19</v>
       </c>
       <c r="L5">
-        <v>10.64</v>
+        <v>12.45</v>
       </c>
       <c r="M5">
-        <v>9.4</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="N5">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="O5">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="P5">
-        <v>384.53</v>
+        <v>384.2</v>
       </c>
       <c r="Q5">
-        <v>382.79</v>
+        <v>383.36</v>
       </c>
       <c r="R5">
-        <v>366.73</v>
+        <v>367.7</v>
       </c>
       <c r="S5">
-        <v>364.99</v>
+        <v>364.98</v>
       </c>
       <c r="T5">
-        <v>5.14</v>
+        <v>5.46</v>
       </c>
       <c r="U5" t="s">
         <v>48</v>
@@ -1307,34 +1344,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>54.85</v>
+        <v>55.93</v>
       </c>
       <c r="Z5">
-        <v>5</v>
+        <v>4.65</v>
       </c>
       <c r="AA5">
-        <v>6.53</v>
+        <v>6.16</v>
       </c>
       <c r="AB5">
-        <v>-1.54</v>
+        <v>-1.51</v>
       </c>
       <c r="AC5">
-        <v>2.16</v>
+        <v>6</v>
       </c>
       <c r="AD5">
-        <v>6.34</v>
+        <v>4.67</v>
       </c>
       <c r="AE5">
-        <v>10.8</v>
+        <v>10.27</v>
       </c>
       <c r="AF5">
-        <v>-72.97</v>
+        <v>-87.86</v>
       </c>
       <c r="AG5">
-        <v>398.49</v>
+        <v>398.46</v>
       </c>
       <c r="AH5">
-        <v>367.08</v>
+        <v>368.25</v>
       </c>
       <c r="AI5">
         <v>364.94</v>
@@ -1343,7 +1380,7 @@
         <v>50</v>
       </c>
       <c r="AK5">
-        <v>26.67</v>
+        <v>24.25</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1354,10 +1391,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>406</v>
+        <v>405.5</v>
       </c>
       <c r="D6">
-        <v>-0.23</v>
+        <v>-0.12</v>
       </c>
       <c r="E6">
         <v>442.7</v>
@@ -1366,46 +1403,46 @@
         <v>279.55</v>
       </c>
       <c r="G6">
-        <v>-8.289999999999999</v>
+        <v>-8.4</v>
       </c>
       <c r="H6">
-        <v>45.23</v>
+        <v>45.05</v>
       </c>
       <c r="I6">
-        <v>-1.91</v>
+        <v>0.7</v>
       </c>
       <c r="J6">
-        <v>4.53</v>
+        <v>4.34</v>
       </c>
       <c r="K6">
-        <v>12.45</v>
+        <v>12.53</v>
       </c>
       <c r="L6">
-        <v>27.79</v>
+        <v>25.93</v>
       </c>
       <c r="M6">
-        <v>-9.81</v>
+        <v>-9.94</v>
       </c>
       <c r="N6">
         <v>88</v>
       </c>
       <c r="O6">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="P6">
-        <v>407.27</v>
+        <v>407.83</v>
       </c>
       <c r="Q6">
-        <v>406.7</v>
+        <v>407.61</v>
       </c>
       <c r="R6">
-        <v>383.39</v>
+        <v>384.56</v>
       </c>
       <c r="S6">
-        <v>363.44</v>
+        <v>363.7</v>
       </c>
       <c r="T6">
-        <v>11.71</v>
+        <v>11.49</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1420,34 +1457,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>53.21</v>
+        <v>52.85</v>
       </c>
       <c r="Z6">
-        <v>6.39</v>
+        <v>5.71</v>
       </c>
       <c r="AA6">
-        <v>8.25</v>
+        <v>7.74</v>
       </c>
       <c r="AB6">
-        <v>-1.86</v>
+        <v>-2.03</v>
       </c>
       <c r="AC6">
-        <v>12.37</v>
+        <v>7.03</v>
       </c>
       <c r="AD6">
-        <v>16.31</v>
+        <v>13.14</v>
       </c>
       <c r="AE6">
-        <v>13.97</v>
+        <v>13.39</v>
       </c>
       <c r="AF6">
-        <v>-74.70999999999999</v>
+        <v>-86.01000000000001</v>
       </c>
       <c r="AG6">
-        <v>426.04</v>
+        <v>424.7</v>
       </c>
       <c r="AH6">
-        <v>387.37</v>
+        <v>390.52</v>
       </c>
       <c r="AI6">
         <v>371.16</v>
@@ -1456,7 +1493,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>26.42</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1467,10 +1504,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>612</v>
+        <v>612.45</v>
       </c>
       <c r="D7">
-        <v>0.34</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E7">
         <v>681.5</v>
@@ -1479,46 +1516,46 @@
         <v>506.45</v>
       </c>
       <c r="G7">
-        <v>-10.2</v>
+        <v>-10.13</v>
       </c>
       <c r="H7">
-        <v>20.84</v>
+        <v>20.93</v>
       </c>
       <c r="I7">
-        <v>4.83</v>
+        <v>3.86</v>
       </c>
       <c r="J7">
-        <v>3.95</v>
+        <v>4.82</v>
       </c>
       <c r="K7">
-        <v>-5.08</v>
+        <v>-3.79</v>
       </c>
       <c r="L7">
-        <v>-6.63</v>
+        <v>-5.77</v>
       </c>
       <c r="M7">
-        <v>32.17</v>
+        <v>30.9</v>
       </c>
       <c r="N7">
         <v>45</v>
       </c>
       <c r="O7">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="P7">
-        <v>602.9</v>
+        <v>607.45</v>
       </c>
       <c r="Q7">
-        <v>583.09</v>
+        <v>584.6900000000001</v>
       </c>
       <c r="R7">
-        <v>599.85</v>
+        <v>599.8</v>
       </c>
       <c r="S7">
-        <v>581.24</v>
+        <v>581.41</v>
       </c>
       <c r="T7">
-        <v>5.29</v>
+        <v>5.34</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1533,34 +1570,34 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>60.23</v>
+        <v>60.41</v>
       </c>
       <c r="Z7">
-        <v>1.77</v>
+        <v>3.16</v>
       </c>
       <c r="AA7">
-        <v>-3.73</v>
+        <v>-2.35</v>
       </c>
       <c r="AB7">
-        <v>5.5</v>
+        <v>5.51</v>
       </c>
       <c r="AC7">
-        <v>88.90000000000001</v>
+        <v>97.36</v>
       </c>
       <c r="AD7">
-        <v>89.87</v>
+        <v>91.92</v>
       </c>
       <c r="AE7">
-        <v>16.13</v>
+        <v>15.59</v>
       </c>
       <c r="AF7">
-        <v>117.17</v>
+        <v>-15.92</v>
       </c>
       <c r="AG7">
-        <v>610.4</v>
+        <v>614.9400000000001</v>
       </c>
       <c r="AH7">
-        <v>555.78</v>
+        <v>554.4400000000001</v>
       </c>
       <c r="AI7">
         <v>568.8</v>
@@ -1569,7 +1606,7 @@
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>38.21</v>
+        <v>41.17</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1580,10 +1617,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>223.88</v>
+        <v>226.62</v>
       </c>
       <c r="D8">
-        <v>-0.44</v>
+        <v>1.22</v>
       </c>
       <c r="E8">
         <v>363.5</v>
@@ -1592,46 +1629,46 @@
         <v>210.4</v>
       </c>
       <c r="G8">
-        <v>-38.41</v>
+        <v>-37.66</v>
       </c>
       <c r="H8">
-        <v>6.41</v>
+        <v>7.71</v>
       </c>
       <c r="I8">
-        <v>-3.07</v>
+        <v>-1.32</v>
       </c>
       <c r="J8">
-        <v>-0.91</v>
+        <v>-1.47</v>
       </c>
       <c r="K8">
-        <v>-4.51</v>
+        <v>-1.1</v>
       </c>
       <c r="L8">
-        <v>-36.11</v>
+        <v>-35.56</v>
       </c>
       <c r="M8">
-        <v>1.69</v>
+        <v>2.37</v>
       </c>
       <c r="N8">
         <v>12</v>
       </c>
       <c r="O8">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="P8">
-        <v>226.86</v>
+        <v>226.25</v>
       </c>
       <c r="Q8">
-        <v>223.22</v>
+        <v>223.33</v>
       </c>
       <c r="R8">
-        <v>228.63</v>
+        <v>228.82</v>
       </c>
       <c r="S8">
-        <v>268.85</v>
+        <v>268.32</v>
       </c>
       <c r="T8">
-        <v>-16.73</v>
+        <v>-15.54</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1646,34 +1683,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>47.27</v>
+        <v>50.65</v>
       </c>
       <c r="Z8">
-        <v>-0.44</v>
+        <v>-0.32</v>
       </c>
       <c r="AA8">
-        <v>-1.12</v>
+        <v>-0.96</v>
       </c>
       <c r="AB8">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="AC8">
-        <v>50.43</v>
+        <v>53.03</v>
       </c>
       <c r="AD8">
-        <v>63.63</v>
+        <v>56</v>
       </c>
       <c r="AE8">
-        <v>6.91</v>
+        <v>6.85</v>
       </c>
       <c r="AF8">
-        <v>-76.69</v>
+        <v>-49.09</v>
       </c>
       <c r="AG8">
-        <v>235.23</v>
+        <v>235.43</v>
       </c>
       <c r="AH8">
-        <v>211.2</v>
+        <v>211.23</v>
       </c>
       <c r="AI8">
         <v>237.22</v>
@@ -1682,7 +1719,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>29.2</v>
+        <v>30.26</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1693,10 +1730,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>3618.2</v>
+        <v>3638.2</v>
       </c>
       <c r="D9">
-        <v>0.26</v>
+        <v>0.55</v>
       </c>
       <c r="E9">
         <v>4497.5</v>
@@ -1705,46 +1742,46 @@
         <v>3308.9</v>
       </c>
       <c r="G9">
-        <v>-19.55</v>
+        <v>-19.11</v>
       </c>
       <c r="H9">
-        <v>9.35</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="I9">
-        <v>0.62</v>
+        <v>1.05</v>
       </c>
       <c r="J9">
-        <v>-4.01</v>
+        <v>-2.5</v>
       </c>
       <c r="K9">
-        <v>-3.79</v>
+        <v>-1.14</v>
       </c>
       <c r="L9">
-        <v>-8.48</v>
+        <v>-6.42</v>
       </c>
       <c r="M9">
-        <v>18.64</v>
+        <v>18.99</v>
       </c>
       <c r="N9">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="O9">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="P9">
-        <v>3605.54</v>
+        <v>3613.1</v>
       </c>
       <c r="Q9">
-        <v>3607.71</v>
+        <v>3604.15</v>
       </c>
       <c r="R9">
-        <v>3748.04</v>
+        <v>3745.38</v>
       </c>
       <c r="S9">
-        <v>3719.07</v>
+        <v>3717.06</v>
       </c>
       <c r="T9">
-        <v>-2.71</v>
+        <v>-2.12</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1759,34 +1796,34 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>43.21</v>
+        <v>46.97</v>
       </c>
       <c r="Z9">
-        <v>-40.92</v>
+        <v>-35.85</v>
       </c>
       <c r="AA9">
-        <v>-50.7</v>
+        <v>-47.73</v>
       </c>
       <c r="AB9">
-        <v>9.779999999999999</v>
+        <v>11.88</v>
       </c>
       <c r="AC9">
-        <v>93.02</v>
+        <v>99.45999999999999</v>
       </c>
       <c r="AD9">
-        <v>87.94</v>
+        <v>93.52</v>
       </c>
       <c r="AE9">
-        <v>62.35</v>
+        <v>61.59</v>
       </c>
       <c r="AF9">
-        <v>-69.2</v>
+        <v>-68.25</v>
       </c>
       <c r="AG9">
-        <v>3677.9</v>
+        <v>3657.97</v>
       </c>
       <c r="AH9">
-        <v>3537.52</v>
+        <v>3550.34</v>
       </c>
       <c r="AI9">
         <v>3794.41</v>
@@ -1795,7 +1832,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>13.33</v>
+        <v>15.85</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1806,10 +1843,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>1639</v>
+        <v>1632.8</v>
       </c>
       <c r="D10">
-        <v>0.86</v>
+        <v>-0.38</v>
       </c>
       <c r="E10">
         <v>1768.4</v>
@@ -1818,46 +1855,46 @@
         <v>1326.2</v>
       </c>
       <c r="G10">
-        <v>-7.32</v>
+        <v>-7.67</v>
       </c>
       <c r="H10">
-        <v>23.59</v>
+        <v>23.12</v>
       </c>
       <c r="I10">
-        <v>0.42</v>
+        <v>-0.13</v>
       </c>
       <c r="J10">
-        <v>9.359999999999999</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="K10">
-        <v>19.59</v>
+        <v>14.18</v>
       </c>
       <c r="L10">
-        <v>11.75</v>
+        <v>11.45</v>
       </c>
       <c r="M10">
-        <v>6.58</v>
+        <v>6.74</v>
       </c>
       <c r="N10">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="O10">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="P10">
-        <v>1636.4</v>
+        <v>1635.96</v>
       </c>
       <c r="Q10">
-        <v>1616.9</v>
+        <v>1619.89</v>
       </c>
       <c r="R10">
-        <v>1515.37</v>
+        <v>1518.28</v>
       </c>
       <c r="S10">
-        <v>1502.31</v>
+        <v>1503.16</v>
       </c>
       <c r="T10">
-        <v>9.1</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="U10" t="s">
         <v>48</v>
@@ -1872,34 +1909,34 @@
         <v>3</v>
       </c>
       <c r="Y10">
-        <v>62.94</v>
+        <v>61.06</v>
       </c>
       <c r="Z10">
-        <v>38.39</v>
+        <v>35.94</v>
       </c>
       <c r="AA10">
-        <v>43.36</v>
+        <v>41.88</v>
       </c>
       <c r="AB10">
-        <v>-4.97</v>
+        <v>-5.94</v>
       </c>
       <c r="AC10">
-        <v>18.42</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="AD10">
-        <v>23.96</v>
+        <v>16.39</v>
       </c>
       <c r="AE10">
-        <v>39.99</v>
+        <v>39.81</v>
       </c>
       <c r="AF10">
-        <v>8.369999999999999</v>
+        <v>2.9</v>
       </c>
       <c r="AG10">
-        <v>1693.14</v>
+        <v>1693.52</v>
       </c>
       <c r="AH10">
-        <v>1540.65</v>
+        <v>1546.26</v>
       </c>
       <c r="AI10">
         <v>1527.05</v>
@@ -1908,7 +1945,7 @@
         <v>50</v>
       </c>
       <c r="AK10">
-        <v>32.86</v>
+        <v>29.05</v>
       </c>
     </row>
   </sheetData>
@@ -2049,7 +2086,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F80"/>
+  <dimension ref="A1:F83"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2069,1297 +2106,1389 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>52</v>
       </c>
+      <c r="C2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>57</v>
+      <c r="A5" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="5">
-        <v>-10.22</v>
-      </c>
-      <c r="D7" s="5">
-        <v>-11.39</v>
-      </c>
-      <c r="E7" s="6">
-        <v>-1.17</v>
-      </c>
+      <c r="A7" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-11.39</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-13.72</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-2.33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>10.03</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C10" s="6">
         <v>11.2</v>
       </c>
-      <c r="E8" s="7">
-        <v>1.17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="D10" s="6">
+        <v>9.960000000000001</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-1.24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>21.76</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C11" s="6">
         <v>21.99</v>
       </c>
-      <c r="E9" s="7">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="D11" s="6">
+        <v>21.21</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-0.78</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>2.81</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C12" s="6">
         <v>3.26</v>
       </c>
-      <c r="E10" s="7">
+      <c r="D12" s="6">
+        <v>2.03</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-1.23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>4.53</v>
+      </c>
+      <c r="D13" s="6">
+        <v>4.34</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-0.19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="6">
+        <v>3.95</v>
+      </c>
+      <c r="D14" s="6">
+        <v>4.82</v>
+      </c>
+      <c r="E14" s="8">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-0.91</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-1.47</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-4.01</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-2.5</v>
+      </c>
+      <c r="E16" s="8">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="6">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="D17" s="6">
+        <v>8.109999999999999</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-1.25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-0.41</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-0.67</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-0.26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>0.65</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-2.1</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-2.75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>1.95</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-4.49</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-6.44</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-0.43</v>
+      </c>
+      <c r="E21" s="8">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="6">
+        <v>-1.91</v>
+      </c>
+      <c r="D22" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="E22" s="8">
+        <v>2.61</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="6">
+        <v>4.83</v>
+      </c>
+      <c r="D23" s="6">
+        <v>3.86</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-0.97</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-3.07</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-1.32</v>
+      </c>
+      <c r="E24" s="8">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="6">
+        <v>0.62</v>
+      </c>
+      <c r="D25" s="6">
+        <v>1.05</v>
+      </c>
+      <c r="E25" s="8">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="6">
+        <v>0.42</v>
+      </c>
+      <c r="D26" s="6">
+        <v>-0.13</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>3.72</v>
+      </c>
+      <c r="D27" s="6">
+        <v>3.74</v>
+      </c>
+      <c r="E27" s="8">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="6">
+        <v>6.76</v>
+      </c>
+      <c r="D28" s="6">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="E28" s="8">
+        <v>2.28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="6">
+        <v>56.31</v>
+      </c>
+      <c r="D29" s="6">
+        <v>54.5</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-1.81</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="6">
+        <v>10.64</v>
+      </c>
+      <c r="D30" s="6">
+        <v>12.45</v>
+      </c>
+      <c r="E30" s="8">
+        <v>1.81</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="6">
+        <v>27.79</v>
+      </c>
+      <c r="D31" s="6">
+        <v>25.93</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-1.86</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-6.63</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-5.77</v>
+      </c>
+      <c r="E32" s="8">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="6">
+        <v>-36.11</v>
+      </c>
+      <c r="D33" s="6">
+        <v>-35.56</v>
+      </c>
+      <c r="E33" s="8">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-8.48</v>
+      </c>
+      <c r="D34" s="6">
+        <v>-6.42</v>
+      </c>
+      <c r="E34" s="8">
+        <v>2.06</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" s="6">
+        <v>11.75</v>
+      </c>
+      <c r="D35" s="6">
+        <v>11.45</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-11.32</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-10.3</v>
+      </c>
+      <c r="E36" s="8">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="6">
+        <v>9.77</v>
+      </c>
+      <c r="D37" s="6">
+        <v>11.17</v>
+      </c>
+      <c r="E37" s="8">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="6">
+        <v>23.62</v>
+      </c>
+      <c r="D38" s="6">
+        <v>22.96</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-0.66</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="6">
+        <v>17.55</v>
+      </c>
+      <c r="D39" s="6">
+        <v>19</v>
+      </c>
+      <c r="E39" s="8">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="6">
+        <v>12.45</v>
+      </c>
+      <c r="D40" s="6">
+        <v>12.53</v>
+      </c>
+      <c r="E40" s="8">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-5.08</v>
+      </c>
+      <c r="D41" s="6">
+        <v>-3.79</v>
+      </c>
+      <c r="E41" s="8">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="6">
+        <v>-4.51</v>
+      </c>
+      <c r="D42" s="6">
+        <v>-1.1</v>
+      </c>
+      <c r="E42" s="8">
+        <v>3.41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="6">
+        <v>-3.79</v>
+      </c>
+      <c r="D43" s="6">
+        <v>-1.14</v>
+      </c>
+      <c r="E43" s="8">
+        <v>2.65</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="6">
+        <v>19.59</v>
+      </c>
+      <c r="D44" s="6">
+        <v>14.18</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-5.41</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-16.65</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-16.82</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-0.17</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="6">
+        <v>-3.86</v>
+      </c>
+      <c r="D46" s="6">
+        <v>-5.38</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-1.52</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="6">
+        <v>-9</v>
+      </c>
+      <c r="D47" s="6">
+        <v>-8.73</v>
+      </c>
+      <c r="E47" s="8">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="6">
+        <v>-8.289999999999999</v>
+      </c>
+      <c r="D48" s="6">
+        <v>-8.4</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-0.11</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="6">
+        <v>-10.2</v>
+      </c>
+      <c r="D49" s="6">
+        <v>-10.13</v>
+      </c>
+      <c r="E49" s="8">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="6">
+        <v>-38.41</v>
+      </c>
+      <c r="D50" s="6">
+        <v>-37.66</v>
+      </c>
+      <c r="E50" s="8">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="6">
+        <v>-19.55</v>
+      </c>
+      <c r="D51" s="6">
+        <v>-19.11</v>
+      </c>
+      <c r="E51" s="8">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="6">
+        <v>-7.32</v>
+      </c>
+      <c r="D52" s="6">
+        <v>-7.67</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-0.35</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="6">
+        <v>408.6</v>
+      </c>
+      <c r="D53" s="6">
+        <v>407.75</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-0.85</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="6">
+        <v>3428.2</v>
+      </c>
+      <c r="D54" s="6">
+        <v>3428.3</v>
+      </c>
+      <c r="E54" s="8">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="6">
+        <v>396.4</v>
+      </c>
+      <c r="D55" s="6">
+        <v>390.1</v>
+      </c>
+      <c r="E55" s="7">
+        <v>-6.3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="6">
+        <v>383.75</v>
+      </c>
+      <c r="D56" s="6">
+        <v>384.9</v>
+      </c>
+      <c r="E56" s="8">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="6">
+        <v>406</v>
+      </c>
+      <c r="D57" s="6">
+        <v>405.5</v>
+      </c>
+      <c r="E57" s="7">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="6">
+        <v>612</v>
+      </c>
+      <c r="D58" s="6">
+        <v>612.45</v>
+      </c>
+      <c r="E58" s="8">
         <v>0.45</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="6">
+        <v>223.88</v>
+      </c>
+      <c r="D59" s="6">
+        <v>226.62</v>
+      </c>
+      <c r="E59" s="8">
+        <v>2.74</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="6">
+        <v>3618.2</v>
+      </c>
+      <c r="D60" s="6">
+        <v>3638.2</v>
+      </c>
+      <c r="E60" s="8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C61" s="6">
+        <v>1639</v>
+      </c>
+      <c r="D61" s="6">
+        <v>1632.8</v>
+      </c>
+      <c r="E61" s="7">
+        <v>-6.2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C62" s="6">
+        <v>34</v>
+      </c>
+      <c r="D62" s="6">
+        <v>23</v>
+      </c>
+      <c r="E62" s="7">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C63" s="6">
+        <v>66</v>
+      </c>
+      <c r="D63" s="6">
+        <v>77</v>
+      </c>
+      <c r="E63" s="8">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C64" s="6">
+        <v>23</v>
+      </c>
+      <c r="D64" s="6">
+        <v>34</v>
+      </c>
+      <c r="E64" s="8">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C65" s="6">
+        <v>77</v>
+      </c>
+      <c r="D65" s="6">
+        <v>66</v>
+      </c>
+      <c r="E65" s="7">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="6">
+        <v>35.98</v>
+      </c>
+      <c r="D66" s="6">
+        <v>35.55</v>
+      </c>
+      <c r="E66" s="7">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="6">
+        <v>59.7</v>
+      </c>
+      <c r="D67" s="6">
+        <v>59.71</v>
+      </c>
+      <c r="E67" s="8">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="6">
+        <v>61.16</v>
+      </c>
+      <c r="D68" s="6">
+        <v>57.74</v>
+      </c>
+      <c r="E68" s="7">
+        <v>-3.42</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="6">
+        <v>54.85</v>
+      </c>
+      <c r="D69" s="6">
+        <v>55.93</v>
+      </c>
+      <c r="E69" s="8">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="5">
-        <v>3.37</v>
-      </c>
-      <c r="D11" s="5">
-        <v>4.53</v>
-      </c>
-      <c r="E11" s="7">
-        <v>1.16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="B70" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="6">
+        <v>53.21</v>
+      </c>
+      <c r="D70" s="6">
+        <v>52.85</v>
+      </c>
+      <c r="E70" s="7">
+        <v>-0.36</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="5">
-        <v>3.54</v>
-      </c>
-      <c r="D12" s="5">
-        <v>3.95</v>
-      </c>
-      <c r="E12" s="7">
-        <v>0.41</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="B71" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="6">
+        <v>60.23</v>
+      </c>
+      <c r="D71" s="6">
+        <v>60.41</v>
+      </c>
+      <c r="E71" s="8">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="5">
-        <v>-0.25</v>
-      </c>
-      <c r="D13" s="5">
-        <v>-0.91</v>
-      </c>
-      <c r="E13" s="6">
-        <v>-0.66</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="B72" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C72" s="6">
+        <v>47.27</v>
+      </c>
+      <c r="D72" s="6">
+        <v>50.65</v>
+      </c>
+      <c r="E72" s="8">
+        <v>3.38</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="5">
-        <v>-3.94</v>
-      </c>
-      <c r="D14" s="5">
-        <v>-4.01</v>
-      </c>
-      <c r="E14" s="6">
-        <v>-0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="B73" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C73" s="6">
+        <v>43.21</v>
+      </c>
+      <c r="D73" s="6">
+        <v>46.97</v>
+      </c>
+      <c r="E73" s="8">
+        <v>3.76</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="5">
-        <v>9.48</v>
-      </c>
-      <c r="D15" s="5">
-        <v>9.359999999999999</v>
-      </c>
-      <c r="E15" s="6">
-        <v>-0.12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="B74" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C74" s="6">
+        <v>62.94</v>
+      </c>
+      <c r="D74" s="6">
+        <v>61.06</v>
+      </c>
+      <c r="E74" s="7">
+        <v>-1.88</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="5">
-        <v>-0.8100000000000001</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-0.41</v>
-      </c>
-      <c r="E16" s="7">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="B75" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="6">
+        <v>-75.97</v>
+      </c>
+      <c r="D75" s="6">
+        <v>-77.08</v>
+      </c>
+      <c r="E75" s="7">
+        <v>-1.11</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="5">
-        <v>-1.5</v>
-      </c>
-      <c r="D17" s="5">
-        <v>0.65</v>
-      </c>
-      <c r="E17" s="7">
-        <v>2.15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="B76" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="6">
+        <v>-10.01</v>
+      </c>
+      <c r="D76" s="6">
+        <v>-59.3</v>
+      </c>
+      <c r="E76" s="7">
+        <v>-49.29</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="5">
-        <v>-0.64</v>
-      </c>
-      <c r="D18" s="5">
-        <v>1.95</v>
-      </c>
-      <c r="E18" s="7">
-        <v>2.59</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="B77" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="6">
+        <v>-61.92</v>
+      </c>
+      <c r="D77" s="6">
+        <v>-73.81999999999999</v>
+      </c>
+      <c r="E77" s="7">
+        <v>-11.9</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="5">
-        <v>0</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-0.6899999999999999</v>
-      </c>
-      <c r="E19" s="6">
-        <v>-0.6899999999999999</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="B78" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="6">
+        <v>-72.97</v>
+      </c>
+      <c r="D78" s="6">
+        <v>-87.86</v>
+      </c>
+      <c r="E78" s="7">
+        <v>-14.89</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="5">
-        <v>-1.58</v>
-      </c>
-      <c r="D20" s="5">
-        <v>-1.91</v>
-      </c>
-      <c r="E20" s="6">
-        <v>-0.33</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="B79" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="6">
+        <v>-74.70999999999999</v>
+      </c>
+      <c r="D79" s="6">
+        <v>-86.01000000000001</v>
+      </c>
+      <c r="E79" s="7">
+        <v>-11.3</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="5">
-        <v>4.69</v>
-      </c>
-      <c r="D21" s="5">
-        <v>4.83</v>
-      </c>
-      <c r="E21" s="7">
-        <v>0.14</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="B80" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="6">
+        <v>117.17</v>
+      </c>
+      <c r="D80" s="6">
+        <v>-15.92</v>
+      </c>
+      <c r="E80" s="7">
+        <v>-133.09</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="5">
-        <v>-3.58</v>
-      </c>
-      <c r="D22" s="5">
-        <v>-3.07</v>
-      </c>
-      <c r="E22" s="7">
-        <v>0.51</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="B81" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81" s="6">
+        <v>-76.69</v>
+      </c>
+      <c r="D81" s="6">
+        <v>-49.09</v>
+      </c>
+      <c r="E81" s="8">
+        <v>27.6</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="5">
-        <v>0</v>
-      </c>
-      <c r="D23" s="5">
-        <v>0.62</v>
-      </c>
-      <c r="E23" s="7">
-        <v>0.62</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="B82" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C82" s="6">
+        <v>-69.2</v>
+      </c>
+      <c r="D82" s="6">
+        <v>-68.25</v>
+      </c>
+      <c r="E82" s="8">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="5">
-        <v>-1.52</v>
-      </c>
-      <c r="D24" s="5">
-        <v>0.42</v>
-      </c>
-      <c r="E24" s="7">
-        <v>1.94</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="5">
-        <v>3.61</v>
-      </c>
-      <c r="D25" s="5">
-        <v>3.72</v>
-      </c>
-      <c r="E25" s="7">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="5">
-        <v>5.46</v>
-      </c>
-      <c r="D26" s="5">
-        <v>6.76</v>
-      </c>
-      <c r="E26" s="7">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="5">
-        <v>56.25</v>
-      </c>
-      <c r="D27" s="5">
-        <v>56.31</v>
-      </c>
-      <c r="E27" s="7">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="5">
-        <v>8.27</v>
-      </c>
-      <c r="D28" s="5">
-        <v>10.64</v>
-      </c>
-      <c r="E28" s="7">
-        <v>2.37</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="5">
-        <v>30.08</v>
-      </c>
-      <c r="D29" s="5">
-        <v>27.79</v>
-      </c>
-      <c r="E29" s="6">
-        <v>-2.29</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-7.66</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-6.63</v>
-      </c>
-      <c r="E30" s="7">
-        <v>1.03</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="5">
-        <v>-36.07</v>
-      </c>
-      <c r="D31" s="5">
-        <v>-36.11</v>
-      </c>
-      <c r="E31" s="6">
-        <v>-0.04</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="5">
-        <v>-7.91</v>
-      </c>
-      <c r="D32" s="5">
-        <v>-8.48</v>
-      </c>
-      <c r="E32" s="6">
-        <v>-0.57</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="5">
-        <v>12.54</v>
-      </c>
-      <c r="D33" s="5">
-        <v>11.75</v>
-      </c>
-      <c r="E33" s="6">
-        <v>-0.79</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="5">
-        <v>-9.67</v>
-      </c>
-      <c r="D34" s="5">
-        <v>-11.32</v>
-      </c>
-      <c r="E34" s="6">
-        <v>-1.65</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="5">
-        <v>7.24</v>
-      </c>
-      <c r="D35" s="5">
-        <v>9.77</v>
-      </c>
-      <c r="E35" s="7">
-        <v>2.53</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="5">
-        <v>23.36</v>
-      </c>
-      <c r="D36" s="5">
-        <v>23.62</v>
-      </c>
-      <c r="E36" s="7">
-        <v>0.26</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="5">
-        <v>18.2</v>
-      </c>
-      <c r="D37" s="5">
-        <v>17.55</v>
-      </c>
-      <c r="E37" s="6">
-        <v>-0.65</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="5">
-        <v>11.08</v>
-      </c>
-      <c r="D38" s="5">
-        <v>12.45</v>
-      </c>
-      <c r="E38" s="7">
-        <v>1.37</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="5">
-        <v>-5.7</v>
-      </c>
-      <c r="D39" s="5">
-        <v>-5.08</v>
-      </c>
-      <c r="E39" s="7">
-        <v>0.62</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="5">
-        <v>-2.2</v>
-      </c>
-      <c r="D40" s="5">
-        <v>-4.51</v>
-      </c>
-      <c r="E40" s="6">
-        <v>-2.31</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="5">
-        <v>-4.98</v>
-      </c>
-      <c r="D41" s="5">
-        <v>-3.79</v>
-      </c>
-      <c r="E41" s="7">
-        <v>1.19</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="5">
-        <v>20.96</v>
-      </c>
-      <c r="D42" s="5">
-        <v>19.59</v>
-      </c>
-      <c r="E42" s="6">
-        <v>-1.37</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="5">
-        <v>-16.01</v>
-      </c>
-      <c r="D43" s="5">
-        <v>-16.65</v>
-      </c>
-      <c r="E43" s="6">
-        <v>-0.64</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="5">
-        <v>-10.49</v>
-      </c>
-      <c r="D44" s="5">
-        <v>-9.84</v>
-      </c>
-      <c r="E44" s="7">
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="5">
-        <v>-3.99</v>
-      </c>
-      <c r="D45" s="5">
-        <v>-3.86</v>
-      </c>
-      <c r="E45" s="7">
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="5">
-        <v>-9.210000000000001</v>
-      </c>
-      <c r="D46" s="5">
-        <v>-9</v>
-      </c>
-      <c r="E46" s="7">
-        <v>0.21</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="5">
-        <v>-8.08</v>
-      </c>
-      <c r="D47" s="5">
-        <v>-8.289999999999999</v>
-      </c>
-      <c r="E47" s="6">
-        <v>-0.21</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="5">
-        <v>-10.5</v>
-      </c>
-      <c r="D48" s="5">
-        <v>-10.2</v>
-      </c>
-      <c r="E48" s="7">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="5">
-        <v>-38.13</v>
-      </c>
-      <c r="D49" s="5">
-        <v>-38.41</v>
-      </c>
-      <c r="E49" s="6">
-        <v>-0.28</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="5">
-        <v>-19.76</v>
-      </c>
-      <c r="D50" s="5">
-        <v>-19.55</v>
-      </c>
-      <c r="E50" s="7">
-        <v>0.21</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="5">
-        <v>-8.109999999999999</v>
-      </c>
-      <c r="D51" s="5">
-        <v>-7.32</v>
-      </c>
-      <c r="E51" s="7">
-        <v>0.79</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="5">
-        <v>411.7</v>
-      </c>
-      <c r="D52" s="5">
-        <v>408.6</v>
-      </c>
-      <c r="E52" s="6">
-        <v>-3.1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="5">
-        <v>3403.6</v>
-      </c>
-      <c r="D53" s="5">
-        <v>3428.2</v>
-      </c>
-      <c r="E53" s="7">
-        <v>24.6</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="5">
-        <v>395.85</v>
-      </c>
-      <c r="D54" s="5">
-        <v>396.4</v>
-      </c>
-      <c r="E54" s="7">
-        <v>0.55</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="5">
-        <v>382.85</v>
-      </c>
-      <c r="D55" s="5">
-        <v>383.75</v>
-      </c>
-      <c r="E55" s="7">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="5">
-        <v>406.95</v>
-      </c>
-      <c r="D56" s="5">
-        <v>406</v>
-      </c>
-      <c r="E56" s="6">
-        <v>-0.95</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="5">
-        <v>609.95</v>
-      </c>
-      <c r="D57" s="5">
-        <v>612</v>
-      </c>
-      <c r="E57" s="7">
-        <v>2.05</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="5">
-        <v>224.88</v>
-      </c>
-      <c r="D58" s="5">
-        <v>223.88</v>
-      </c>
-      <c r="E58" s="6">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="5">
-        <v>3608.9</v>
-      </c>
-      <c r="D59" s="5">
-        <v>3618.2</v>
-      </c>
-      <c r="E59" s="7">
-        <v>9.300000000000001</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="5">
-        <v>1625</v>
-      </c>
-      <c r="D60" s="5">
-        <v>1639</v>
-      </c>
-      <c r="E60" s="7">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C61" s="5">
-        <v>45</v>
-      </c>
-      <c r="D61" s="5">
-        <v>34</v>
-      </c>
-      <c r="E61" s="6">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C62" s="5">
-        <v>34</v>
-      </c>
-      <c r="D62" s="5">
-        <v>45</v>
-      </c>
-      <c r="E62" s="7">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C63" s="5">
-        <v>37.52</v>
-      </c>
-      <c r="D63" s="5">
-        <v>35.98</v>
-      </c>
-      <c r="E63" s="6">
-        <v>-1.54</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="5">
-        <v>58.1</v>
-      </c>
-      <c r="D64" s="5">
-        <v>59.7</v>
-      </c>
-      <c r="E64" s="7">
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="5">
-        <v>60.97</v>
-      </c>
-      <c r="D65" s="5">
-        <v>61.16</v>
-      </c>
-      <c r="E65" s="7">
-        <v>0.19</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="5">
-        <v>54.03</v>
-      </c>
-      <c r="D66" s="5">
-        <v>54.85</v>
-      </c>
-      <c r="E66" s="7">
-        <v>0.82</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="5">
-        <v>53.84</v>
-      </c>
-      <c r="D67" s="5">
-        <v>53.21</v>
-      </c>
-      <c r="E67" s="6">
-        <v>-0.63</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="5">
-        <v>59.45</v>
-      </c>
-      <c r="D68" s="5">
-        <v>60.23</v>
-      </c>
-      <c r="E68" s="7">
-        <v>0.78</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="5">
-        <v>48.39</v>
-      </c>
-      <c r="D69" s="5">
-        <v>47.27</v>
-      </c>
-      <c r="E69" s="6">
-        <v>-1.12</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="5">
-        <v>41.42</v>
-      </c>
-      <c r="D70" s="5">
-        <v>43.21</v>
-      </c>
-      <c r="E70" s="7">
-        <v>1.79</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="5">
-        <v>60.38</v>
-      </c>
-      <c r="D71" s="5">
-        <v>62.94</v>
-      </c>
-      <c r="E71" s="7">
-        <v>2.56</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B72" s="3" t="s">
+      <c r="B83" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C72" s="5">
-        <v>-31.88</v>
-      </c>
-      <c r="D72" s="5">
-        <v>-75.97</v>
-      </c>
-      <c r="E72" s="6">
-        <v>-44.09</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C73" s="5">
-        <v>-28.7</v>
-      </c>
-      <c r="D73" s="5">
-        <v>-10.01</v>
-      </c>
-      <c r="E73" s="7">
-        <v>18.69</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="5">
-        <v>-34.56</v>
-      </c>
-      <c r="D74" s="5">
-        <v>-61.92</v>
-      </c>
-      <c r="E74" s="6">
-        <v>-27.36</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="5">
-        <v>-80.61</v>
-      </c>
-      <c r="D75" s="5">
-        <v>-72.97</v>
-      </c>
-      <c r="E75" s="7">
-        <v>7.64</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="5">
-        <v>-64.93000000000001</v>
-      </c>
-      <c r="D76" s="5">
-        <v>-74.70999999999999</v>
-      </c>
-      <c r="E76" s="6">
-        <v>-9.779999999999999</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="5">
-        <v>29.26</v>
-      </c>
-      <c r="D77" s="5">
-        <v>117.17</v>
-      </c>
-      <c r="E77" s="7">
-        <v>87.91</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="5">
-        <v>-69.56999999999999</v>
-      </c>
-      <c r="D78" s="5">
-        <v>-76.69</v>
-      </c>
-      <c r="E78" s="6">
-        <v>-7.12</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="5">
-        <v>-53.15</v>
-      </c>
-      <c r="D79" s="5">
-        <v>-69.2</v>
-      </c>
-      <c r="E79" s="6">
-        <v>-16.05</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="5">
-        <v>19.28</v>
-      </c>
-      <c r="D80" s="5">
+      <c r="C83" s="6">
         <v>8.369999999999999</v>
       </c>
-      <c r="E80" s="6">
-        <v>-10.91</v>
+      <c r="D83" s="6">
+        <v>2.9</v>
+      </c>
+      <c r="E83" s="7">
+        <v>-5.47</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A7:E7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3379,61 +3508,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>65</v>
+      <c r="B1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>60.16</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>9</v>
       </c>
-      <c r="D2" s="10">
-        <v>53.2</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="11">
+        <v>53.4</v>
+      </c>
+      <c r="E2" s="11">
         <v>70</v>
       </c>
-      <c r="F2" s="10">
-        <v>4.2</v>
-      </c>
-      <c r="G2" s="10">
-        <v>6.5</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>3.6</v>
+      </c>
+      <c r="G2" s="11">
+        <v>7.1</v>
+      </c>
+      <c r="H2" s="11">
         <v>55.4</v>
       </c>
-      <c r="I2" s="10">
-        <v>30</v>
+      <c r="I2" s="11">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -3534,61 +3663,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="13" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="13">
-        <v>0.3547999999999999</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.3217</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.232</v>
-      </c>
-      <c r="D2" s="13">
-        <v>0.1864</v>
-      </c>
-      <c r="E2" s="13">
-        <v>0.1213</v>
-      </c>
-      <c r="F2" s="13">
-        <v>0.094</v>
-      </c>
-      <c r="G2" s="13">
-        <v>0.0658</v>
-      </c>
-      <c r="H2" s="13">
-        <v>0.0169</v>
-      </c>
-      <c r="I2" s="13">
-        <v>-0.09810000000000001</v>
+      <c r="A2" s="14">
+        <v>0.3482</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.309</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.2292</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.1899</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.121</v>
+      </c>
+      <c r="F2" s="14">
+        <v>0.0953</v>
+      </c>
+      <c r="G2" s="14">
+        <v>0.0674</v>
+      </c>
+      <c r="H2" s="14">
+        <v>0.0237</v>
+      </c>
+      <c r="I2" s="14">
+        <v>-0.09939999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/MAHINDRA_GROUP_Technical_Metrics.xlsx
+++ b/MAHINDRA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="66">
   <si>
     <t>Symbol</t>
   </si>
@@ -178,43 +178,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>50 DMA &gt; 200 DMA</t>
-  </si>
-  <si>
-    <t>No → Yes</t>
-  </si>
-  <si>
-    <t>🟢 GOLDEN CROSS</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>47.3 → 50.6</t>
-  </si>
-  <si>
-    <t>47.3</t>
-  </si>
-  <si>
-    <t>50.6</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -300,14 +264,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -340,13 +304,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,18 +380,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -942,7 +905,7 @@
         <v>407.75</v>
       </c>
       <c r="D2">
-        <v>-0.21</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>490.2</v>
@@ -957,40 +920,40 @@
         <v>7.53</v>
       </c>
       <c r="I2">
-        <v>-0.67</v>
+        <v>-0.43</v>
       </c>
       <c r="J2">
-        <v>-13.72</v>
+        <v>-13.92</v>
       </c>
       <c r="K2">
-        <v>-10.3</v>
+        <v>-12.23</v>
       </c>
       <c r="L2">
-        <v>3.74</v>
+        <v>4.11</v>
       </c>
       <c r="M2">
-        <v>12.1</v>
+        <v>11.95</v>
       </c>
       <c r="N2">
         <v>23</v>
       </c>
       <c r="O2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P2">
-        <v>410.11</v>
+        <v>409.76</v>
       </c>
       <c r="Q2">
-        <v>421.27</v>
+        <v>417.96</v>
       </c>
       <c r="R2">
-        <v>444.85</v>
+        <v>443.97</v>
       </c>
       <c r="S2">
-        <v>438.45</v>
+        <v>438.33</v>
       </c>
       <c r="T2">
-        <v>-7</v>
+        <v>-6.98</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1008,40 +971,40 @@
         <v>35.55</v>
       </c>
       <c r="Z2">
-        <v>-11.85</v>
+        <v>-11.49</v>
       </c>
       <c r="AA2">
-        <v>-12.18</v>
+        <v>-12.04</v>
       </c>
       <c r="AB2">
-        <v>0.33</v>
+        <v>0.55</v>
       </c>
       <c r="AC2">
-        <v>82.40000000000001</v>
+        <v>73.38</v>
       </c>
       <c r="AD2">
-        <v>82.33</v>
+        <v>82.22</v>
       </c>
       <c r="AE2">
-        <v>11.47</v>
+        <v>11.04</v>
       </c>
       <c r="AF2">
-        <v>-77.08</v>
+        <v>-78.34</v>
       </c>
       <c r="AG2">
-        <v>466.33</v>
+        <v>455.94</v>
       </c>
       <c r="AH2">
-        <v>376.21</v>
+        <v>379.99</v>
       </c>
       <c r="AI2">
-        <v>443.72</v>
+        <v>442.42</v>
       </c>
       <c r="AJ2" t="s">
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>34.78</v>
+        <v>33.27</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1052,10 +1015,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>3428.3</v>
+        <v>3390.4</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>-1.11</v>
       </c>
       <c r="E3">
         <v>3802.4</v>
@@ -1064,46 +1027,46 @@
         <v>2931.1</v>
       </c>
       <c r="G3">
-        <v>-9.84</v>
+        <v>-10.84</v>
       </c>
       <c r="H3">
-        <v>16.96</v>
+        <v>15.67</v>
       </c>
       <c r="I3">
-        <v>-2.1</v>
+        <v>-3.6</v>
       </c>
       <c r="J3">
-        <v>9.960000000000001</v>
+        <v>6.64</v>
       </c>
       <c r="K3">
-        <v>11.17</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="L3">
-        <v>9.039999999999999</v>
+        <v>6.41</v>
       </c>
       <c r="M3">
-        <v>34.82</v>
+        <v>34.77</v>
       </c>
       <c r="N3">
         <v>55</v>
       </c>
       <c r="O3">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P3">
-        <v>3447.44</v>
+        <v>3422.12</v>
       </c>
       <c r="Q3">
-        <v>3340.48</v>
+        <v>3351.72</v>
       </c>
       <c r="R3">
-        <v>3193.72</v>
+        <v>3200.72</v>
       </c>
       <c r="S3">
-        <v>3356.23</v>
+        <v>3355.29</v>
       </c>
       <c r="T3">
-        <v>2.15</v>
+        <v>1.05</v>
       </c>
       <c r="U3" t="s">
         <v>48</v>
@@ -1118,34 +1081,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>59.71</v>
+        <v>55.89</v>
       </c>
       <c r="Z3">
-        <v>79.40000000000001</v>
+        <v>72.39</v>
       </c>
       <c r="AA3">
-        <v>78.33</v>
+        <v>77.14</v>
       </c>
       <c r="AB3">
-        <v>1.07</v>
+        <v>-4.75</v>
       </c>
       <c r="AC3">
-        <v>31.46</v>
+        <v>21.09</v>
       </c>
       <c r="AD3">
-        <v>47</v>
+        <v>31.89</v>
       </c>
       <c r="AE3">
-        <v>73.39</v>
+        <v>72.69</v>
       </c>
       <c r="AF3">
-        <v>-59.3</v>
+        <v>-29.52</v>
       </c>
       <c r="AG3">
-        <v>3584.19</v>
+        <v>3581.82</v>
       </c>
       <c r="AH3">
-        <v>3096.77</v>
+        <v>3121.63</v>
       </c>
       <c r="AI3">
         <v>3274.47</v>
@@ -1154,7 +1117,7 @@
         <v>50</v>
       </c>
       <c r="AK3">
-        <v>43.48</v>
+        <v>39.9</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1165,10 +1128,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>390.1</v>
+        <v>388.9</v>
       </c>
       <c r="D4">
-        <v>-1.59</v>
+        <v>-0.31</v>
       </c>
       <c r="E4">
         <v>412.3</v>
@@ -1177,46 +1140,46 @@
         <v>253.95</v>
       </c>
       <c r="G4">
-        <v>-5.38</v>
+        <v>-5.68</v>
       </c>
       <c r="H4">
-        <v>53.61</v>
+        <v>53.14</v>
       </c>
       <c r="I4">
-        <v>-4.49</v>
+        <v>-5.68</v>
       </c>
       <c r="J4">
-        <v>21.21</v>
+        <v>19.96</v>
       </c>
       <c r="K4">
-        <v>22.96</v>
+        <v>21.66</v>
       </c>
       <c r="L4">
-        <v>54.5</v>
+        <v>52.54</v>
       </c>
       <c r="M4">
-        <v>22.92</v>
+        <v>23.2</v>
       </c>
       <c r="N4">
         <v>99</v>
       </c>
       <c r="O4">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P4">
-        <v>398.69</v>
+        <v>394.01</v>
       </c>
       <c r="Q4">
-        <v>383.96</v>
+        <v>387.27</v>
       </c>
       <c r="R4">
-        <v>339.74</v>
+        <v>341.72</v>
       </c>
       <c r="S4">
-        <v>339.26</v>
+        <v>339.7</v>
       </c>
       <c r="T4">
-        <v>14.99</v>
+        <v>14.48</v>
       </c>
       <c r="U4" t="s">
         <v>48</v>
@@ -1231,34 +1194,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>57.74</v>
+        <v>57.09</v>
       </c>
       <c r="Z4">
-        <v>17.09</v>
+        <v>15.57</v>
       </c>
       <c r="AA4">
-        <v>19.06</v>
+        <v>18.36</v>
       </c>
       <c r="AB4">
-        <v>-1.98</v>
+        <v>-2.8</v>
       </c>
       <c r="AC4">
         <v>0.52</v>
       </c>
       <c r="AD4">
-        <v>6.51</v>
+        <v>0.67</v>
       </c>
       <c r="AE4">
-        <v>15.5</v>
+        <v>14.99</v>
       </c>
       <c r="AF4">
-        <v>-73.81999999999999</v>
+        <v>-78.97</v>
       </c>
       <c r="AG4">
-        <v>428.67</v>
+        <v>421.4</v>
       </c>
       <c r="AH4">
-        <v>339.24</v>
+        <v>353.15</v>
       </c>
       <c r="AI4">
         <v>357.72</v>
@@ -1267,7 +1230,7 @@
         <v>50</v>
       </c>
       <c r="AK4">
-        <v>45.65</v>
+        <v>40.49</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1278,10 +1241,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>384.9</v>
+        <v>386.65</v>
       </c>
       <c r="D5">
-        <v>0.3</v>
+        <v>0.45</v>
       </c>
       <c r="E5">
         <v>421.7</v>
@@ -1290,46 +1253,46 @@
         <v>294.25</v>
       </c>
       <c r="G5">
-        <v>-8.73</v>
+        <v>-8.31</v>
       </c>
       <c r="H5">
-        <v>30.81</v>
+        <v>31.4</v>
       </c>
       <c r="I5">
-        <v>-0.43</v>
+        <v>-0.05</v>
       </c>
       <c r="J5">
-        <v>2.03</v>
+        <v>3.52</v>
       </c>
       <c r="K5">
-        <v>19</v>
+        <v>17.56</v>
       </c>
       <c r="L5">
-        <v>12.45</v>
+        <v>11.06</v>
       </c>
       <c r="M5">
-        <v>9.529999999999999</v>
+        <v>9.42</v>
       </c>
       <c r="N5">
         <v>77</v>
       </c>
       <c r="O5">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="P5">
-        <v>384.2</v>
+        <v>384.16</v>
       </c>
       <c r="Q5">
-        <v>383.36</v>
+        <v>384.03</v>
       </c>
       <c r="R5">
-        <v>367.7</v>
+        <v>368.67</v>
       </c>
       <c r="S5">
         <v>364.98</v>
       </c>
       <c r="T5">
-        <v>5.46</v>
+        <v>5.94</v>
       </c>
       <c r="U5" t="s">
         <v>48</v>
@@ -1344,34 +1307,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>55.93</v>
+        <v>57.6</v>
       </c>
       <c r="Z5">
-        <v>4.65</v>
+        <v>4.46</v>
       </c>
       <c r="AA5">
-        <v>6.16</v>
+        <v>5.82</v>
       </c>
       <c r="AB5">
-        <v>-1.51</v>
+        <v>-1.36</v>
       </c>
       <c r="AC5">
-        <v>6</v>
+        <v>12.6</v>
       </c>
       <c r="AD5">
-        <v>4.67</v>
+        <v>6.92</v>
       </c>
       <c r="AE5">
-        <v>10.27</v>
+        <v>10.61</v>
       </c>
       <c r="AF5">
-        <v>-87.86</v>
+        <v>-64.62</v>
       </c>
       <c r="AG5">
-        <v>398.46</v>
+        <v>398.41</v>
       </c>
       <c r="AH5">
-        <v>368.25</v>
+        <v>369.65</v>
       </c>
       <c r="AI5">
         <v>364.94</v>
@@ -1380,7 +1343,7 @@
         <v>50</v>
       </c>
       <c r="AK5">
-        <v>24.25</v>
+        <v>23.6</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1394,7 +1357,7 @@
         <v>405.5</v>
       </c>
       <c r="D6">
-        <v>-0.12</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>442.7</v>
@@ -1409,40 +1372,40 @@
         <v>45.05</v>
       </c>
       <c r="I6">
-        <v>0.7</v>
+        <v>-1.42</v>
       </c>
       <c r="J6">
-        <v>4.34</v>
+        <v>4.69</v>
       </c>
       <c r="K6">
-        <v>12.53</v>
+        <v>13.87</v>
       </c>
       <c r="L6">
-        <v>25.93</v>
+        <v>22.01</v>
       </c>
       <c r="M6">
-        <v>-9.94</v>
+        <v>-9.9</v>
       </c>
       <c r="N6">
         <v>88</v>
       </c>
       <c r="O6">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P6">
-        <v>407.83</v>
+        <v>406.66</v>
       </c>
       <c r="Q6">
-        <v>407.61</v>
+        <v>408.23</v>
       </c>
       <c r="R6">
-        <v>384.56</v>
+        <v>385.69</v>
       </c>
       <c r="S6">
-        <v>363.7</v>
+        <v>364</v>
       </c>
       <c r="T6">
-        <v>11.49</v>
+        <v>11.4</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1460,31 +1423,31 @@
         <v>52.85</v>
       </c>
       <c r="Z6">
-        <v>5.71</v>
+        <v>5.11</v>
       </c>
       <c r="AA6">
-        <v>7.74</v>
+        <v>7.21</v>
       </c>
       <c r="AB6">
-        <v>-2.03</v>
+        <v>-2.1</v>
       </c>
       <c r="AC6">
-        <v>7.03</v>
+        <v>5.14</v>
       </c>
       <c r="AD6">
-        <v>13.14</v>
+        <v>8.18</v>
       </c>
       <c r="AE6">
-        <v>13.39</v>
+        <v>12.85</v>
       </c>
       <c r="AF6">
-        <v>-86.01000000000001</v>
+        <v>-69.7</v>
       </c>
       <c r="AG6">
-        <v>424.7</v>
+        <v>423.94</v>
       </c>
       <c r="AH6">
-        <v>390.52</v>
+        <v>392.53</v>
       </c>
       <c r="AI6">
         <v>371.16</v>
@@ -1493,7 +1456,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>25.29</v>
+        <v>24.31</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1504,10 +1467,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>612.45</v>
+        <v>622</v>
       </c>
       <c r="D7">
-        <v>0.07000000000000001</v>
+        <v>1.56</v>
       </c>
       <c r="E7">
         <v>681.5</v>
@@ -1516,25 +1479,25 @@
         <v>506.45</v>
       </c>
       <c r="G7">
-        <v>-10.13</v>
+        <v>-8.73</v>
       </c>
       <c r="H7">
-        <v>20.93</v>
+        <v>22.82</v>
       </c>
       <c r="I7">
-        <v>3.86</v>
+        <v>2.33</v>
       </c>
       <c r="J7">
-        <v>4.82</v>
+        <v>7.16</v>
       </c>
       <c r="K7">
-        <v>-3.79</v>
+        <v>-2.09</v>
       </c>
       <c r="L7">
-        <v>-5.77</v>
+        <v>-3.48</v>
       </c>
       <c r="M7">
-        <v>30.9</v>
+        <v>31.92</v>
       </c>
       <c r="N7">
         <v>45</v>
@@ -1543,19 +1506,19 @@
         <v>44</v>
       </c>
       <c r="P7">
-        <v>607.45</v>
+        <v>610.28</v>
       </c>
       <c r="Q7">
-        <v>584.6900000000001</v>
+        <v>586.55</v>
       </c>
       <c r="R7">
-        <v>599.8</v>
+        <v>599.76</v>
       </c>
       <c r="S7">
-        <v>581.41</v>
+        <v>581.65</v>
       </c>
       <c r="T7">
-        <v>5.34</v>
+        <v>6.94</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1570,34 +1533,34 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>60.41</v>
+        <v>64.13</v>
       </c>
       <c r="Z7">
-        <v>3.16</v>
+        <v>4.98</v>
       </c>
       <c r="AA7">
-        <v>-2.35</v>
+        <v>-0.88</v>
       </c>
       <c r="AB7">
-        <v>5.51</v>
+        <v>5.86</v>
       </c>
       <c r="AC7">
-        <v>97.36</v>
+        <v>99.05</v>
       </c>
       <c r="AD7">
-        <v>91.92</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="AE7">
-        <v>15.59</v>
+        <v>15.68</v>
       </c>
       <c r="AF7">
-        <v>-15.92</v>
+        <v>3.95</v>
       </c>
       <c r="AG7">
-        <v>614.9400000000001</v>
+        <v>621.1</v>
       </c>
       <c r="AH7">
-        <v>554.4400000000001</v>
+        <v>552.01</v>
       </c>
       <c r="AI7">
         <v>568.8</v>
@@ -1606,7 +1569,7 @@
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>41.17</v>
+        <v>44.65</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1620,7 +1583,7 @@
         <v>226.62</v>
       </c>
       <c r="D8">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>363.5</v>
@@ -1635,40 +1598,40 @@
         <v>7.71</v>
       </c>
       <c r="I8">
-        <v>-1.32</v>
+        <v>-1.6</v>
       </c>
       <c r="J8">
-        <v>-1.47</v>
+        <v>1.02</v>
       </c>
       <c r="K8">
-        <v>-1.1</v>
+        <v>1.39</v>
       </c>
       <c r="L8">
-        <v>-35.56</v>
+        <v>-36.02</v>
       </c>
       <c r="M8">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="N8">
         <v>12</v>
       </c>
       <c r="O8">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="P8">
-        <v>226.25</v>
+        <v>225.51</v>
       </c>
       <c r="Q8">
         <v>223.33</v>
       </c>
       <c r="R8">
-        <v>228.82</v>
+        <v>229.04</v>
       </c>
       <c r="S8">
-        <v>268.32</v>
+        <v>267.79</v>
       </c>
       <c r="T8">
-        <v>-15.54</v>
+        <v>-15.37</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1686,25 +1649,25 @@
         <v>50.65</v>
       </c>
       <c r="Z8">
-        <v>-0.32</v>
+        <v>-0.23</v>
       </c>
       <c r="AA8">
-        <v>-0.96</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="AB8">
-        <v>0.63</v>
+        <v>0.58</v>
       </c>
       <c r="AC8">
-        <v>53.03</v>
+        <v>56.91</v>
       </c>
       <c r="AD8">
-        <v>56</v>
+        <v>53.46</v>
       </c>
       <c r="AE8">
-        <v>6.85</v>
+        <v>6.8</v>
       </c>
       <c r="AF8">
-        <v>-49.09</v>
+        <v>-61.63</v>
       </c>
       <c r="AG8">
         <v>235.43</v>
@@ -1719,7 +1682,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>30.26</v>
+        <v>31.17</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1733,7 +1696,7 @@
         <v>3638.2</v>
       </c>
       <c r="D9">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <v>4497.5</v>
@@ -1748,19 +1711,19 @@
         <v>9.949999999999999</v>
       </c>
       <c r="I9">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="J9">
-        <v>-2.5</v>
+        <v>-1.92</v>
       </c>
       <c r="K9">
-        <v>-1.14</v>
+        <v>-1.99</v>
       </c>
       <c r="L9">
-        <v>-6.42</v>
+        <v>-7.97</v>
       </c>
       <c r="M9">
-        <v>18.99</v>
+        <v>19.41</v>
       </c>
       <c r="N9">
         <v>34</v>
@@ -1769,19 +1732,19 @@
         <v>41</v>
       </c>
       <c r="P9">
-        <v>3613.1</v>
+        <v>3620.28</v>
       </c>
       <c r="Q9">
-        <v>3604.15</v>
+        <v>3602.26</v>
       </c>
       <c r="R9">
-        <v>3745.38</v>
+        <v>3743.47</v>
       </c>
       <c r="S9">
-        <v>3717.06</v>
+        <v>3715.19</v>
       </c>
       <c r="T9">
-        <v>-2.12</v>
+        <v>-2.07</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1799,31 +1762,31 @@
         <v>46.97</v>
       </c>
       <c r="Z9">
-        <v>-35.85</v>
+        <v>-31.48</v>
       </c>
       <c r="AA9">
-        <v>-47.73</v>
+        <v>-44.48</v>
       </c>
       <c r="AB9">
-        <v>11.88</v>
+        <v>13</v>
       </c>
       <c r="AC9">
-        <v>99.45999999999999</v>
+        <v>100</v>
       </c>
       <c r="AD9">
-        <v>93.52</v>
+        <v>97.48999999999999</v>
       </c>
       <c r="AE9">
-        <v>61.59</v>
+        <v>60.88</v>
       </c>
       <c r="AF9">
-        <v>-68.25</v>
+        <v>-45.29</v>
       </c>
       <c r="AG9">
-        <v>3657.97</v>
+        <v>3647.38</v>
       </c>
       <c r="AH9">
-        <v>3550.34</v>
+        <v>3557.14</v>
       </c>
       <c r="AI9">
         <v>3794.41</v>
@@ -1832,7 +1795,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>15.85</v>
+        <v>18.02</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1843,10 +1806,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>1632.8</v>
+        <v>1610</v>
       </c>
       <c r="D10">
-        <v>-0.38</v>
+        <v>-1.4</v>
       </c>
       <c r="E10">
         <v>1768.4</v>
@@ -1855,46 +1818,46 @@
         <v>1326.2</v>
       </c>
       <c r="G10">
-        <v>-7.67</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="H10">
-        <v>23.12</v>
+        <v>21.4</v>
       </c>
       <c r="I10">
-        <v>-0.13</v>
+        <v>-1.83</v>
       </c>
       <c r="J10">
-        <v>8.109999999999999</v>
+        <v>2.36</v>
       </c>
       <c r="K10">
-        <v>14.18</v>
+        <v>9.74</v>
       </c>
       <c r="L10">
-        <v>11.45</v>
+        <v>9.84</v>
       </c>
       <c r="M10">
-        <v>6.74</v>
+        <v>5.73</v>
       </c>
       <c r="N10">
         <v>66</v>
       </c>
       <c r="O10">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="P10">
-        <v>1635.96</v>
+        <v>1629.96</v>
       </c>
       <c r="Q10">
-        <v>1619.89</v>
+        <v>1621.57</v>
       </c>
       <c r="R10">
-        <v>1518.28</v>
+        <v>1520.81</v>
       </c>
       <c r="S10">
-        <v>1503.16</v>
+        <v>1503.98</v>
       </c>
       <c r="T10">
-        <v>8.619999999999999</v>
+        <v>7.05</v>
       </c>
       <c r="U10" t="s">
         <v>48</v>
@@ -1909,34 +1872,34 @@
         <v>3</v>
       </c>
       <c r="Y10">
-        <v>61.06</v>
+        <v>54.59</v>
       </c>
       <c r="Z10">
-        <v>35.94</v>
+        <v>31.79</v>
       </c>
       <c r="AA10">
-        <v>41.88</v>
+        <v>39.86</v>
       </c>
       <c r="AB10">
-        <v>-5.94</v>
+        <v>-8.07</v>
       </c>
       <c r="AC10">
         <v>8.220000000000001</v>
       </c>
       <c r="AD10">
-        <v>16.39</v>
+        <v>11.62</v>
       </c>
       <c r="AE10">
-        <v>39.81</v>
+        <v>39.45</v>
       </c>
       <c r="AF10">
-        <v>2.9</v>
+        <v>-54.71</v>
       </c>
       <c r="AG10">
-        <v>1693.52</v>
+        <v>1692.5</v>
       </c>
       <c r="AH10">
-        <v>1546.26</v>
+        <v>1550.64</v>
       </c>
       <c r="AI10">
         <v>1527.05</v>
@@ -1945,7 +1908,7 @@
         <v>50</v>
       </c>
       <c r="AK10">
-        <v>29.05</v>
+        <v>27.31</v>
       </c>
     </row>
   </sheetData>
@@ -2086,7 +2049,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F83"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2106,1389 +2069,1059 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>64</v>
-      </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
+      <c r="A7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>-13.72</v>
+      </c>
+      <c r="D7" s="5">
+        <v>-13.92</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-0.2</v>
+      </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="3" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>69</v>
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>9.960000000000001</v>
+      </c>
+      <c r="D8" s="5">
+        <v>6.64</v>
+      </c>
+      <c r="E8" s="6">
+        <v>-3.32</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>21.21</v>
+      </c>
+      <c r="D9" s="5">
+        <v>19.96</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-1.25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5">
+        <v>2.03</v>
+      </c>
+      <c r="D10" s="5">
+        <v>3.52</v>
+      </c>
+      <c r="E10" s="7">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>4.34</v>
+      </c>
+      <c r="D11" s="5">
+        <v>4.69</v>
+      </c>
+      <c r="E11" s="7">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="5">
+        <v>4.82</v>
+      </c>
+      <c r="D12" s="5">
+        <v>7.16</v>
+      </c>
+      <c r="E12" s="7">
+        <v>2.34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="5">
+        <v>-1.47</v>
+      </c>
+      <c r="D13" s="5">
+        <v>1.02</v>
+      </c>
+      <c r="E13" s="7">
+        <v>2.49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-2.5</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-1.92</v>
+      </c>
+      <c r="E14" s="7">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="5">
+        <v>8.109999999999999</v>
+      </c>
+      <c r="D15" s="5">
+        <v>2.36</v>
+      </c>
+      <c r="E15" s="6">
+        <v>-5.75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-11.39</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-13.72</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-2.33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>-0.67</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-0.43</v>
+      </c>
+      <c r="E16" s="7">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>11.2</v>
-      </c>
-      <c r="D10" s="6">
-        <v>9.960000000000001</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-1.24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-2.1</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-3.6</v>
+      </c>
+      <c r="E17" s="6">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>21.99</v>
-      </c>
-      <c r="D11" s="6">
-        <v>21.21</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-0.78</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-4.49</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-5.68</v>
+      </c>
+      <c r="E18" s="6">
+        <v>-1.19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>3.26</v>
-      </c>
-      <c r="D12" s="6">
-        <v>2.03</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-1.23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-0.43</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-0.05</v>
+      </c>
+      <c r="E19" s="7">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="6">
-        <v>4.53</v>
-      </c>
-      <c r="D13" s="6">
-        <v>4.34</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-0.19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="5">
+        <v>0.7</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-1.42</v>
+      </c>
+      <c r="E20" s="6">
+        <v>-2.12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="6">
+      <c r="B21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="5">
+        <v>3.86</v>
+      </c>
+      <c r="D21" s="5">
+        <v>2.33</v>
+      </c>
+      <c r="E21" s="6">
+        <v>-1.53</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="5">
+        <v>-1.32</v>
+      </c>
+      <c r="D22" s="5">
+        <v>-1.6</v>
+      </c>
+      <c r="E22" s="6">
+        <v>-0.28</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="5">
+        <v>1.05</v>
+      </c>
+      <c r="D23" s="5">
+        <v>1</v>
+      </c>
+      <c r="E23" s="6">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-0.13</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-1.83</v>
+      </c>
+      <c r="E24" s="6">
+        <v>-1.7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="5">
+        <v>3.74</v>
+      </c>
+      <c r="D25" s="5">
+        <v>4.11</v>
+      </c>
+      <c r="E25" s="7">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="5">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="D26" s="5">
+        <v>6.41</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-2.63</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="5">
+        <v>54.5</v>
+      </c>
+      <c r="D27" s="5">
+        <v>52.54</v>
+      </c>
+      <c r="E27" s="6">
+        <v>-1.96</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="5">
+        <v>12.45</v>
+      </c>
+      <c r="D28" s="5">
+        <v>11.06</v>
+      </c>
+      <c r="E28" s="6">
+        <v>-1.39</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="5">
+        <v>25.93</v>
+      </c>
+      <c r="D29" s="5">
+        <v>22.01</v>
+      </c>
+      <c r="E29" s="6">
+        <v>-3.92</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-5.77</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-3.48</v>
+      </c>
+      <c r="E30" s="7">
+        <v>2.29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-35.56</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-36.02</v>
+      </c>
+      <c r="E31" s="6">
+        <v>-0.46</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="5">
+        <v>-6.42</v>
+      </c>
+      <c r="D32" s="5">
+        <v>-7.97</v>
+      </c>
+      <c r="E32" s="6">
+        <v>-1.55</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="5">
+        <v>11.45</v>
+      </c>
+      <c r="D33" s="5">
+        <v>9.84</v>
+      </c>
+      <c r="E33" s="6">
+        <v>-1.61</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="5">
+        <v>-10.3</v>
+      </c>
+      <c r="D34" s="5">
+        <v>-12.23</v>
+      </c>
+      <c r="E34" s="6">
+        <v>-1.93</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="5">
+        <v>11.17</v>
+      </c>
+      <c r="D35" s="5">
+        <v>9.640000000000001</v>
+      </c>
+      <c r="E35" s="6">
+        <v>-1.53</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="5">
+        <v>22.96</v>
+      </c>
+      <c r="D36" s="5">
+        <v>21.66</v>
+      </c>
+      <c r="E36" s="6">
+        <v>-1.3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="5">
+        <v>19</v>
+      </c>
+      <c r="D37" s="5">
+        <v>17.56</v>
+      </c>
+      <c r="E37" s="6">
+        <v>-1.44</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="5">
+        <v>12.53</v>
+      </c>
+      <c r="D38" s="5">
+        <v>13.87</v>
+      </c>
+      <c r="E38" s="7">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="5">
+        <v>-3.79</v>
+      </c>
+      <c r="D39" s="5">
+        <v>-2.09</v>
+      </c>
+      <c r="E39" s="7">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="5">
+        <v>-1.1</v>
+      </c>
+      <c r="D40" s="5">
+        <v>1.39</v>
+      </c>
+      <c r="E40" s="7">
+        <v>2.49</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="5">
+        <v>-1.14</v>
+      </c>
+      <c r="D41" s="5">
+        <v>-1.99</v>
+      </c>
+      <c r="E41" s="6">
+        <v>-0.85</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="5">
+        <v>14.18</v>
+      </c>
+      <c r="D42" s="5">
+        <v>9.74</v>
+      </c>
+      <c r="E42" s="6">
+        <v>-4.44</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="5">
+        <v>-9.84</v>
+      </c>
+      <c r="D43" s="5">
+        <v>-10.84</v>
+      </c>
+      <c r="E43" s="6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="5">
+        <v>-5.38</v>
+      </c>
+      <c r="D44" s="5">
+        <v>-5.68</v>
+      </c>
+      <c r="E44" s="6">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="5">
+        <v>-8.73</v>
+      </c>
+      <c r="D45" s="5">
+        <v>-8.31</v>
+      </c>
+      <c r="E45" s="7">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="5">
+        <v>-10.13</v>
+      </c>
+      <c r="D46" s="5">
+        <v>-8.73</v>
+      </c>
+      <c r="E46" s="7">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="5">
+        <v>-7.67</v>
+      </c>
+      <c r="D47" s="5">
+        <v>-8.960000000000001</v>
+      </c>
+      <c r="E47" s="6">
+        <v>-1.29</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="5">
+        <v>3428.3</v>
+      </c>
+      <c r="D48" s="5">
+        <v>3390.4</v>
+      </c>
+      <c r="E48" s="6">
+        <v>-37.9</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" s="5">
+        <v>390.1</v>
+      </c>
+      <c r="D49" s="5">
+        <v>388.9</v>
+      </c>
+      <c r="E49" s="6">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C50" s="5">
+        <v>384.9</v>
+      </c>
+      <c r="D50" s="5">
+        <v>386.65</v>
+      </c>
+      <c r="E50" s="7">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C51" s="5">
+        <v>612.45</v>
+      </c>
+      <c r="D51" s="5">
+        <v>622</v>
+      </c>
+      <c r="E51" s="7">
+        <v>9.550000000000001</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="5">
+        <v>1632.8</v>
+      </c>
+      <c r="D52" s="5">
+        <v>1610</v>
+      </c>
+      <c r="E52" s="6">
+        <v>-22.8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="5">
+        <v>59.71</v>
+      </c>
+      <c r="D53" s="5">
+        <v>55.89</v>
+      </c>
+      <c r="E53" s="6">
+        <v>-3.82</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="5">
+        <v>57.74</v>
+      </c>
+      <c r="D54" s="5">
+        <v>57.09</v>
+      </c>
+      <c r="E54" s="6">
+        <v>-0.65</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="5">
+        <v>55.93</v>
+      </c>
+      <c r="D55" s="5">
+        <v>57.6</v>
+      </c>
+      <c r="E55" s="7">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="5">
+        <v>60.41</v>
+      </c>
+      <c r="D56" s="5">
+        <v>64.13</v>
+      </c>
+      <c r="E56" s="7">
+        <v>3.72</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="5">
+        <v>61.06</v>
+      </c>
+      <c r="D57" s="5">
+        <v>54.59</v>
+      </c>
+      <c r="E57" s="6">
+        <v>-6.47</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" s="5">
+        <v>-77.08</v>
+      </c>
+      <c r="D58" s="5">
+        <v>-78.34</v>
+      </c>
+      <c r="E58" s="6">
+        <v>-1.26</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="5">
+        <v>-59.3</v>
+      </c>
+      <c r="D59" s="5">
+        <v>-29.52</v>
+      </c>
+      <c r="E59" s="7">
+        <v>29.78</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="5">
+        <v>-73.81999999999999</v>
+      </c>
+      <c r="D60" s="5">
+        <v>-78.97</v>
+      </c>
+      <c r="E60" s="6">
+        <v>-5.15</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="5">
+        <v>-87.86</v>
+      </c>
+      <c r="D61" s="5">
+        <v>-64.62</v>
+      </c>
+      <c r="E61" s="7">
+        <v>23.24</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C62" s="5">
+        <v>-86.01000000000001</v>
+      </c>
+      <c r="D62" s="5">
+        <v>-69.7</v>
+      </c>
+      <c r="E62" s="7">
+        <v>16.31</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="5">
+        <v>-15.92</v>
+      </c>
+      <c r="D63" s="5">
         <v>3.95</v>
       </c>
-      <c r="D14" s="6">
-        <v>4.82</v>
-      </c>
-      <c r="E14" s="8">
-        <v>0.87</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="E63" s="7">
+        <v>19.87</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-0.91</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-1.47</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-0.5600000000000001</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B64" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" s="5">
+        <v>-49.09</v>
+      </c>
+      <c r="D64" s="5">
+        <v>-61.63</v>
+      </c>
+      <c r="E64" s="6">
+        <v>-12.54</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-4.01</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-2.5</v>
-      </c>
-      <c r="E16" s="8">
-        <v>1.51</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B65" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C65" s="5">
+        <v>-68.25</v>
+      </c>
+      <c r="D65" s="5">
+        <v>-45.29</v>
+      </c>
+      <c r="E65" s="7">
+        <v>22.96</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="6">
-        <v>9.359999999999999</v>
-      </c>
-      <c r="D17" s="6">
-        <v>8.109999999999999</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-1.25</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-0.41</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-0.67</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-0.26</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>0.65</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-2.1</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-2.75</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>1.95</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-4.49</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-6.44</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-0.6899999999999999</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-0.43</v>
-      </c>
-      <c r="E21" s="8">
-        <v>0.26</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-1.91</v>
-      </c>
-      <c r="D22" s="6">
-        <v>0.7</v>
-      </c>
-      <c r="E22" s="8">
-        <v>2.61</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="6">
-        <v>4.83</v>
-      </c>
-      <c r="D23" s="6">
-        <v>3.86</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-0.97</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-3.07</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-1.32</v>
-      </c>
-      <c r="E24" s="8">
-        <v>1.75</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="6">
-        <v>0.62</v>
-      </c>
-      <c r="D25" s="6">
-        <v>1.05</v>
-      </c>
-      <c r="E25" s="8">
-        <v>0.43</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C26" s="6">
-        <v>0.42</v>
-      </c>
-      <c r="D26" s="6">
-        <v>-0.13</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-0.55</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>3.72</v>
-      </c>
-      <c r="D27" s="6">
-        <v>3.74</v>
-      </c>
-      <c r="E27" s="8">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="6">
-        <v>6.76</v>
-      </c>
-      <c r="D28" s="6">
-        <v>9.039999999999999</v>
-      </c>
-      <c r="E28" s="8">
-        <v>2.28</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="6">
-        <v>56.31</v>
-      </c>
-      <c r="D29" s="6">
-        <v>54.5</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-1.81</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="6">
-        <v>10.64</v>
-      </c>
-      <c r="D30" s="6">
-        <v>12.45</v>
-      </c>
-      <c r="E30" s="8">
-        <v>1.81</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="6">
-        <v>27.79</v>
-      </c>
-      <c r="D31" s="6">
-        <v>25.93</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-1.86</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-6.63</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-5.77</v>
-      </c>
-      <c r="E32" s="8">
-        <v>0.86</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="6">
-        <v>-36.11</v>
-      </c>
-      <c r="D33" s="6">
-        <v>-35.56</v>
-      </c>
-      <c r="E33" s="8">
-        <v>0.55</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="6">
-        <v>-8.48</v>
-      </c>
-      <c r="D34" s="6">
-        <v>-6.42</v>
-      </c>
-      <c r="E34" s="8">
-        <v>2.06</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C35" s="6">
-        <v>11.75</v>
-      </c>
-      <c r="D35" s="6">
-        <v>11.45</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-0.3</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="6">
-        <v>-11.32</v>
-      </c>
-      <c r="D36" s="6">
-        <v>-10.3</v>
-      </c>
-      <c r="E36" s="8">
-        <v>1.02</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="6">
-        <v>9.77</v>
-      </c>
-      <c r="D37" s="6">
-        <v>11.17</v>
-      </c>
-      <c r="E37" s="8">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="6">
-        <v>23.62</v>
-      </c>
-      <c r="D38" s="6">
-        <v>22.96</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-0.66</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="6">
-        <v>17.55</v>
-      </c>
-      <c r="D39" s="6">
-        <v>19</v>
-      </c>
-      <c r="E39" s="8">
-        <v>1.45</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="6">
-        <v>12.45</v>
-      </c>
-      <c r="D40" s="6">
-        <v>12.53</v>
-      </c>
-      <c r="E40" s="8">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="6">
-        <v>-5.08</v>
-      </c>
-      <c r="D41" s="6">
-        <v>-3.79</v>
-      </c>
-      <c r="E41" s="8">
-        <v>1.29</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="6">
-        <v>-4.51</v>
-      </c>
-      <c r="D42" s="6">
-        <v>-1.1</v>
-      </c>
-      <c r="E42" s="8">
-        <v>3.41</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="6">
-        <v>-3.79</v>
-      </c>
-      <c r="D43" s="6">
-        <v>-1.14</v>
-      </c>
-      <c r="E43" s="8">
-        <v>2.65</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44" s="6">
-        <v>19.59</v>
-      </c>
-      <c r="D44" s="6">
-        <v>14.18</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-5.41</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-16.65</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-16.82</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-0.17</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-3.86</v>
-      </c>
-      <c r="D46" s="6">
-        <v>-5.38</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-1.52</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="6">
-        <v>-9</v>
-      </c>
-      <c r="D47" s="6">
-        <v>-8.73</v>
-      </c>
-      <c r="E47" s="8">
-        <v>0.27</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="6">
-        <v>-8.289999999999999</v>
-      </c>
-      <c r="D48" s="6">
-        <v>-8.4</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-0.11</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="6">
-        <v>-10.2</v>
-      </c>
-      <c r="D49" s="6">
-        <v>-10.13</v>
-      </c>
-      <c r="E49" s="8">
-        <v>0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="6">
-        <v>-38.41</v>
-      </c>
-      <c r="D50" s="6">
-        <v>-37.66</v>
-      </c>
-      <c r="E50" s="8">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="6">
-        <v>-19.55</v>
-      </c>
-      <c r="D51" s="6">
-        <v>-19.11</v>
-      </c>
-      <c r="E51" s="8">
-        <v>0.44</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C52" s="6">
-        <v>-7.32</v>
-      </c>
-      <c r="D52" s="6">
-        <v>-7.67</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-0.35</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="6">
-        <v>408.6</v>
-      </c>
-      <c r="D53" s="6">
-        <v>407.75</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-0.85</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="6">
-        <v>3428.2</v>
-      </c>
-      <c r="D54" s="6">
-        <v>3428.3</v>
-      </c>
-      <c r="E54" s="8">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="6">
-        <v>396.4</v>
-      </c>
-      <c r="D55" s="6">
-        <v>390.1</v>
-      </c>
-      <c r="E55" s="7">
-        <v>-6.3</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="6">
-        <v>383.75</v>
-      </c>
-      <c r="D56" s="6">
-        <v>384.9</v>
-      </c>
-      <c r="E56" s="8">
-        <v>1.15</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="6">
-        <v>406</v>
-      </c>
-      <c r="D57" s="6">
-        <v>405.5</v>
-      </c>
-      <c r="E57" s="7">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="6">
-        <v>612</v>
-      </c>
-      <c r="D58" s="6">
-        <v>612.45</v>
-      </c>
-      <c r="E58" s="8">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="6">
-        <v>223.88</v>
-      </c>
-      <c r="D59" s="6">
-        <v>226.62</v>
-      </c>
-      <c r="E59" s="8">
-        <v>2.74</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="6">
-        <v>3618.2</v>
-      </c>
-      <c r="D60" s="6">
-        <v>3638.2</v>
-      </c>
-      <c r="E60" s="8">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C61" s="6">
-        <v>1639</v>
-      </c>
-      <c r="D61" s="6">
-        <v>1632.8</v>
-      </c>
-      <c r="E61" s="7">
-        <v>-6.2</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C62" s="6">
-        <v>34</v>
-      </c>
-      <c r="D62" s="6">
-        <v>23</v>
-      </c>
-      <c r="E62" s="7">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C63" s="6">
-        <v>66</v>
-      </c>
-      <c r="D63" s="6">
-        <v>77</v>
-      </c>
-      <c r="E63" s="8">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C64" s="6">
-        <v>23</v>
-      </c>
-      <c r="D64" s="6">
-        <v>34</v>
-      </c>
-      <c r="E64" s="8">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C65" s="6">
-        <v>77</v>
-      </c>
-      <c r="D65" s="6">
-        <v>66</v>
-      </c>
-      <c r="E65" s="7">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="6">
-        <v>35.98</v>
-      </c>
-      <c r="D66" s="6">
-        <v>35.55</v>
-      </c>
-      <c r="E66" s="7">
-        <v>-0.43</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="6">
-        <v>59.7</v>
-      </c>
-      <c r="D67" s="6">
-        <v>59.71</v>
-      </c>
-      <c r="E67" s="8">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="6">
-        <v>61.16</v>
-      </c>
-      <c r="D68" s="6">
-        <v>57.74</v>
-      </c>
-      <c r="E68" s="7">
-        <v>-3.42</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="6">
-        <v>54.85</v>
-      </c>
-      <c r="D69" s="6">
-        <v>55.93</v>
-      </c>
-      <c r="E69" s="8">
-        <v>1.08</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="6">
-        <v>53.21</v>
-      </c>
-      <c r="D70" s="6">
-        <v>52.85</v>
-      </c>
-      <c r="E70" s="7">
-        <v>-0.36</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="6">
-        <v>60.23</v>
-      </c>
-      <c r="D71" s="6">
-        <v>60.41</v>
-      </c>
-      <c r="E71" s="8">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C72" s="6">
-        <v>47.27</v>
-      </c>
-      <c r="D72" s="6">
-        <v>50.65</v>
-      </c>
-      <c r="E72" s="8">
-        <v>3.38</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C73" s="6">
-        <v>43.21</v>
-      </c>
-      <c r="D73" s="6">
-        <v>46.97</v>
-      </c>
-      <c r="E73" s="8">
-        <v>3.76</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C74" s="6">
-        <v>62.94</v>
-      </c>
-      <c r="D74" s="6">
-        <v>61.06</v>
-      </c>
-      <c r="E74" s="7">
-        <v>-1.88</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B75" s="5" t="s">
+      <c r="B66" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C75" s="6">
-        <v>-75.97</v>
-      </c>
-      <c r="D75" s="6">
-        <v>-77.08</v>
-      </c>
-      <c r="E75" s="7">
-        <v>-1.11</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="6">
-        <v>-10.01</v>
-      </c>
-      <c r="D76" s="6">
-        <v>-59.3</v>
-      </c>
-      <c r="E76" s="7">
-        <v>-49.29</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="6">
-        <v>-61.92</v>
-      </c>
-      <c r="D77" s="6">
-        <v>-73.81999999999999</v>
-      </c>
-      <c r="E77" s="7">
-        <v>-11.9</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="6">
-        <v>-72.97</v>
-      </c>
-      <c r="D78" s="6">
-        <v>-87.86</v>
-      </c>
-      <c r="E78" s="7">
-        <v>-14.89</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="6">
-        <v>-74.70999999999999</v>
-      </c>
-      <c r="D79" s="6">
-        <v>-86.01000000000001</v>
-      </c>
-      <c r="E79" s="7">
-        <v>-11.3</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="6">
-        <v>117.17</v>
-      </c>
-      <c r="D80" s="6">
-        <v>-15.92</v>
-      </c>
-      <c r="E80" s="7">
-        <v>-133.09</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="6">
-        <v>-76.69</v>
-      </c>
-      <c r="D81" s="6">
-        <v>-49.09</v>
-      </c>
-      <c r="E81" s="8">
-        <v>27.6</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B82" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C82" s="6">
-        <v>-69.2</v>
-      </c>
-      <c r="D82" s="6">
-        <v>-68.25</v>
-      </c>
-      <c r="E82" s="8">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="A83" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B83" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C83" s="6">
-        <v>8.369999999999999</v>
-      </c>
-      <c r="D83" s="6">
+      <c r="C66" s="5">
         <v>2.9</v>
       </c>
-      <c r="E83" s="7">
-        <v>-5.47</v>
+      <c r="D66" s="5">
+        <v>-54.71</v>
+      </c>
+      <c r="E66" s="6">
+        <v>-57.61</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3508,60 +3141,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" s="10">
+        <v>60.16</v>
+      </c>
+      <c r="C2" s="11">
+        <v>9</v>
+      </c>
+      <c r="D2" s="10">
+        <v>52.8</v>
+      </c>
+      <c r="E2" s="10">
         <v>70</v>
       </c>
-      <c r="C1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="B2" s="11">
-        <v>60.16</v>
-      </c>
-      <c r="C2" s="12">
-        <v>9</v>
-      </c>
-      <c r="D2" s="11">
-        <v>53.4</v>
-      </c>
-      <c r="E2" s="11">
-        <v>70</v>
-      </c>
-      <c r="F2" s="11">
-        <v>3.6</v>
-      </c>
-      <c r="G2" s="11">
-        <v>7.1</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>3.3</v>
+      </c>
+      <c r="G2" s="10">
+        <v>6.4</v>
+      </c>
+      <c r="H2" s="10">
         <v>55.4</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>40</v>
       </c>
     </row>
@@ -3663,61 +3296,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="12" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="14">
-        <v>0.3482</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.309</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.2292</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.1899</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.121</v>
-      </c>
-      <c r="F2" s="14">
-        <v>0.0953</v>
-      </c>
-      <c r="G2" s="14">
-        <v>0.0674</v>
-      </c>
-      <c r="H2" s="14">
-        <v>0.0237</v>
-      </c>
-      <c r="I2" s="14">
-        <v>-0.09939999999999999</v>
+      <c r="A2" s="13">
+        <v>0.3477</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.3192</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.232</v>
+      </c>
+      <c r="D2" s="13">
+        <v>0.1941</v>
+      </c>
+      <c r="E2" s="13">
+        <v>0.1195</v>
+      </c>
+      <c r="F2" s="13">
+        <v>0.09420000000000001</v>
+      </c>
+      <c r="G2" s="13">
+        <v>0.0573</v>
+      </c>
+      <c r="H2" s="13">
+        <v>0.0245</v>
+      </c>
+      <c r="I2" s="13">
+        <v>-0.099</v>
       </c>
     </row>
   </sheetData>

--- a/MAHINDRA_GROUP_Technical_Metrics.xlsx
+++ b/MAHINDRA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="75">
   <si>
     <t>Symbol</t>
   </si>
@@ -178,7 +178,34 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>50.6 → 44.4</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>50.6</t>
+  </si>
+  <si>
+    <t>44.4</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -380,17 +407,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -902,10 +930,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>407.75</v>
+        <v>409.7</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="E2">
         <v>490.2</v>
@@ -914,46 +942,46 @@
         <v>379.2</v>
       </c>
       <c r="G2">
-        <v>-16.82</v>
+        <v>-16.42</v>
       </c>
       <c r="H2">
-        <v>7.53</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="I2">
-        <v>-0.43</v>
+        <v>-0.8</v>
       </c>
       <c r="J2">
-        <v>-13.92</v>
+        <v>-13.53</v>
       </c>
       <c r="K2">
-        <v>-12.23</v>
+        <v>-11.49</v>
       </c>
       <c r="L2">
-        <v>4.11</v>
+        <v>4.88</v>
       </c>
       <c r="M2">
-        <v>11.95</v>
+        <v>12.06</v>
       </c>
       <c r="N2">
         <v>23</v>
       </c>
       <c r="O2">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="P2">
-        <v>409.76</v>
+        <v>409.1</v>
       </c>
       <c r="Q2">
-        <v>417.96</v>
+        <v>414.81</v>
       </c>
       <c r="R2">
-        <v>443.97</v>
+        <v>443.4</v>
       </c>
       <c r="S2">
-        <v>438.33</v>
+        <v>438.21</v>
       </c>
       <c r="T2">
-        <v>-6.98</v>
+        <v>-6.51</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -968,43 +996,43 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>35.55</v>
+        <v>37.54</v>
       </c>
       <c r="Z2">
-        <v>-11.49</v>
+        <v>-10.92</v>
       </c>
       <c r="AA2">
-        <v>-12.04</v>
+        <v>-11.82</v>
       </c>
       <c r="AB2">
-        <v>0.55</v>
+        <v>0.9</v>
       </c>
       <c r="AC2">
-        <v>73.38</v>
+        <v>77.81</v>
       </c>
       <c r="AD2">
-        <v>82.22</v>
+        <v>77.86</v>
       </c>
       <c r="AE2">
-        <v>11.04</v>
+        <v>10.66</v>
       </c>
       <c r="AF2">
-        <v>-78.34</v>
+        <v>-68.75</v>
       </c>
       <c r="AG2">
-        <v>455.94</v>
+        <v>442.81</v>
       </c>
       <c r="AH2">
-        <v>379.99</v>
+        <v>386.82</v>
       </c>
       <c r="AI2">
-        <v>442.42</v>
+        <v>441.09</v>
       </c>
       <c r="AJ2" t="s">
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>33.27</v>
+        <v>32.16</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1015,10 +1043,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>3390.4</v>
+        <v>3421.5</v>
       </c>
       <c r="D3">
-        <v>-1.11</v>
+        <v>0.92</v>
       </c>
       <c r="E3">
         <v>3802.4</v>
@@ -1027,46 +1055,46 @@
         <v>2931.1</v>
       </c>
       <c r="G3">
-        <v>-10.84</v>
+        <v>-10.02</v>
       </c>
       <c r="H3">
-        <v>15.67</v>
+        <v>16.73</v>
       </c>
       <c r="I3">
-        <v>-3.6</v>
+        <v>-1.12</v>
       </c>
       <c r="J3">
-        <v>6.64</v>
+        <v>8.09</v>
       </c>
       <c r="K3">
-        <v>9.640000000000001</v>
+        <v>9.59</v>
       </c>
       <c r="L3">
-        <v>6.41</v>
+        <v>5.72</v>
       </c>
       <c r="M3">
-        <v>34.77</v>
+        <v>34.99</v>
       </c>
       <c r="N3">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="O3">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="P3">
-        <v>3422.12</v>
+        <v>3414.4</v>
       </c>
       <c r="Q3">
-        <v>3351.72</v>
+        <v>3362.72</v>
       </c>
       <c r="R3">
-        <v>3200.72</v>
+        <v>3209.83</v>
       </c>
       <c r="S3">
-        <v>3355.29</v>
+        <v>3354.72</v>
       </c>
       <c r="T3">
-        <v>1.05</v>
+        <v>1.99</v>
       </c>
       <c r="U3" t="s">
         <v>48</v>
@@ -1081,34 +1109,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>55.89</v>
+        <v>58.25</v>
       </c>
       <c r="Z3">
-        <v>72.39</v>
+        <v>68.55</v>
       </c>
       <c r="AA3">
-        <v>77.14</v>
+        <v>75.43000000000001</v>
       </c>
       <c r="AB3">
-        <v>-4.75</v>
+        <v>-6.87</v>
       </c>
       <c r="AC3">
-        <v>21.09</v>
+        <v>16.82</v>
       </c>
       <c r="AD3">
-        <v>31.89</v>
+        <v>23.12</v>
       </c>
       <c r="AE3">
-        <v>72.69</v>
+        <v>70.7</v>
       </c>
       <c r="AF3">
-        <v>-29.52</v>
+        <v>-45.11</v>
       </c>
       <c r="AG3">
-        <v>3581.82</v>
+        <v>3583.44</v>
       </c>
       <c r="AH3">
-        <v>3121.63</v>
+        <v>3141.99</v>
       </c>
       <c r="AI3">
         <v>3274.47</v>
@@ -1117,7 +1145,7 @@
         <v>50</v>
       </c>
       <c r="AK3">
-        <v>39.9</v>
+        <v>36.79</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1128,10 +1156,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>388.9</v>
+        <v>386.2</v>
       </c>
       <c r="D4">
-        <v>-0.31</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="E4">
         <v>412.3</v>
@@ -1140,46 +1168,46 @@
         <v>253.95</v>
       </c>
       <c r="G4">
-        <v>-5.68</v>
+        <v>-6.33</v>
       </c>
       <c r="H4">
-        <v>53.14</v>
+        <v>52.08</v>
       </c>
       <c r="I4">
-        <v>-5.68</v>
+        <v>-3.16</v>
       </c>
       <c r="J4">
-        <v>19.96</v>
+        <v>19.73</v>
       </c>
       <c r="K4">
-        <v>21.66</v>
+        <v>24.98</v>
       </c>
       <c r="L4">
-        <v>52.54</v>
+        <v>50.3</v>
       </c>
       <c r="M4">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="N4">
         <v>99</v>
       </c>
       <c r="O4">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P4">
-        <v>394.01</v>
+        <v>391.49</v>
       </c>
       <c r="Q4">
-        <v>387.27</v>
+        <v>389.09</v>
       </c>
       <c r="R4">
-        <v>341.72</v>
+        <v>343.83</v>
       </c>
       <c r="S4">
-        <v>339.7</v>
+        <v>340.05</v>
       </c>
       <c r="T4">
-        <v>14.48</v>
+        <v>13.57</v>
       </c>
       <c r="U4" t="s">
         <v>48</v>
@@ -1194,34 +1222,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>57.09</v>
+        <v>55.57</v>
       </c>
       <c r="Z4">
-        <v>15.57</v>
+        <v>13.98</v>
       </c>
       <c r="AA4">
-        <v>18.36</v>
+        <v>17.49</v>
       </c>
       <c r="AB4">
-        <v>-2.8</v>
+        <v>-3.5</v>
       </c>
       <c r="AC4">
-        <v>0.52</v>
+        <v>0</v>
       </c>
       <c r="AD4">
-        <v>0.67</v>
+        <v>0.35</v>
       </c>
       <c r="AE4">
-        <v>14.99</v>
+        <v>14.55</v>
       </c>
       <c r="AF4">
-        <v>-78.97</v>
+        <v>-79.59</v>
       </c>
       <c r="AG4">
-        <v>421.4</v>
+        <v>418.34</v>
       </c>
       <c r="AH4">
-        <v>353.15</v>
+        <v>359.84</v>
       </c>
       <c r="AI4">
         <v>357.72</v>
@@ -1230,7 +1258,7 @@
         <v>50</v>
       </c>
       <c r="AK4">
-        <v>40.49</v>
+        <v>35.75</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1241,10 +1269,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>386.65</v>
+        <v>384.15</v>
       </c>
       <c r="D5">
-        <v>0.45</v>
+        <v>-0.65</v>
       </c>
       <c r="E5">
         <v>421.7</v>
@@ -1253,46 +1281,46 @@
         <v>294.25</v>
       </c>
       <c r="G5">
-        <v>-8.31</v>
+        <v>-8.9</v>
       </c>
       <c r="H5">
-        <v>31.4</v>
+        <v>30.55</v>
       </c>
       <c r="I5">
-        <v>-0.05</v>
+        <v>0.39</v>
       </c>
       <c r="J5">
-        <v>3.52</v>
+        <v>2.93</v>
       </c>
       <c r="K5">
-        <v>17.56</v>
+        <v>17.58</v>
       </c>
       <c r="L5">
-        <v>11.06</v>
+        <v>12.55</v>
       </c>
       <c r="M5">
-        <v>9.42</v>
+        <v>9.31</v>
       </c>
       <c r="N5">
         <v>77</v>
       </c>
       <c r="O5">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="P5">
-        <v>384.16</v>
+        <v>384.46</v>
       </c>
       <c r="Q5">
-        <v>384.03</v>
+        <v>384.78</v>
       </c>
       <c r="R5">
-        <v>368.67</v>
+        <v>369.66</v>
       </c>
       <c r="S5">
-        <v>364.98</v>
+        <v>364.96</v>
       </c>
       <c r="T5">
-        <v>5.94</v>
+        <v>5.26</v>
       </c>
       <c r="U5" t="s">
         <v>48</v>
@@ -1307,34 +1335,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>57.6</v>
+        <v>54.43</v>
       </c>
       <c r="Z5">
-        <v>4.46</v>
+        <v>4.06</v>
       </c>
       <c r="AA5">
-        <v>5.82</v>
+        <v>5.47</v>
       </c>
       <c r="AB5">
-        <v>-1.36</v>
+        <v>-1.4</v>
       </c>
       <c r="AC5">
-        <v>12.6</v>
+        <v>11.83</v>
       </c>
       <c r="AD5">
-        <v>6.92</v>
+        <v>10.14</v>
       </c>
       <c r="AE5">
-        <v>10.61</v>
+        <v>10.55</v>
       </c>
       <c r="AF5">
-        <v>-64.62</v>
+        <v>-74.13</v>
       </c>
       <c r="AG5">
-        <v>398.41</v>
+        <v>397.35</v>
       </c>
       <c r="AH5">
-        <v>369.65</v>
+        <v>372.2</v>
       </c>
       <c r="AI5">
         <v>364.94</v>
@@ -1343,7 +1371,7 @@
         <v>50</v>
       </c>
       <c r="AK5">
-        <v>23.6</v>
+        <v>22.59</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1354,10 +1382,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>405.5</v>
+        <v>404.55</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
       <c r="E6">
         <v>442.7</v>
@@ -1366,46 +1394,46 @@
         <v>279.55</v>
       </c>
       <c r="G6">
-        <v>-8.4</v>
+        <v>-8.619999999999999</v>
       </c>
       <c r="H6">
-        <v>45.05</v>
+        <v>44.71</v>
       </c>
       <c r="I6">
-        <v>-1.42</v>
+        <v>-1.17</v>
       </c>
       <c r="J6">
-        <v>4.69</v>
+        <v>2.93</v>
       </c>
       <c r="K6">
-        <v>13.87</v>
+        <v>14.12</v>
       </c>
       <c r="L6">
-        <v>22.01</v>
+        <v>23.34</v>
       </c>
       <c r="M6">
-        <v>-9.9</v>
+        <v>-10.11</v>
       </c>
       <c r="N6">
         <v>88</v>
       </c>
       <c r="O6">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="P6">
-        <v>406.66</v>
+        <v>405.7</v>
       </c>
       <c r="Q6">
-        <v>408.23</v>
+        <v>408.9</v>
       </c>
       <c r="R6">
-        <v>385.69</v>
+        <v>387.02</v>
       </c>
       <c r="S6">
-        <v>364</v>
+        <v>364.24</v>
       </c>
       <c r="T6">
-        <v>11.4</v>
+        <v>11.07</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1420,34 +1448,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>52.85</v>
+        <v>52.09</v>
       </c>
       <c r="Z6">
-        <v>5.11</v>
+        <v>4.51</v>
       </c>
       <c r="AA6">
-        <v>7.21</v>
+        <v>6.67</v>
       </c>
       <c r="AB6">
-        <v>-2.1</v>
+        <v>-2.16</v>
       </c>
       <c r="AC6">
-        <v>5.14</v>
+        <v>3.1</v>
       </c>
       <c r="AD6">
-        <v>8.18</v>
+        <v>5.09</v>
       </c>
       <c r="AE6">
-        <v>12.85</v>
+        <v>12.58</v>
       </c>
       <c r="AF6">
-        <v>-69.7</v>
+        <v>-81.53</v>
       </c>
       <c r="AG6">
-        <v>423.94</v>
+        <v>422.54</v>
       </c>
       <c r="AH6">
-        <v>392.53</v>
+        <v>395.26</v>
       </c>
       <c r="AI6">
         <v>371.16</v>
@@ -1456,7 +1484,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>24.31</v>
+        <v>26.45</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1467,10 +1495,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>622</v>
+        <v>620.9</v>
       </c>
       <c r="D7">
-        <v>1.56</v>
+        <v>-0.18</v>
       </c>
       <c r="E7">
         <v>681.5</v>
@@ -1479,25 +1507,25 @@
         <v>506.45</v>
       </c>
       <c r="G7">
-        <v>-8.73</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="H7">
-        <v>22.82</v>
+        <v>22.6</v>
       </c>
       <c r="I7">
-        <v>2.33</v>
+        <v>4.35</v>
       </c>
       <c r="J7">
-        <v>7.16</v>
+        <v>6.19</v>
       </c>
       <c r="K7">
-        <v>-2.09</v>
+        <v>-3.09</v>
       </c>
       <c r="L7">
-        <v>-3.48</v>
+        <v>-7.33</v>
       </c>
       <c r="M7">
-        <v>31.92</v>
+        <v>31.89</v>
       </c>
       <c r="N7">
         <v>45</v>
@@ -1506,19 +1534,19 @@
         <v>44</v>
       </c>
       <c r="P7">
-        <v>610.28</v>
+        <v>615.46</v>
       </c>
       <c r="Q7">
-        <v>586.55</v>
+        <v>588.6</v>
       </c>
       <c r="R7">
-        <v>599.76</v>
+        <v>599.89</v>
       </c>
       <c r="S7">
-        <v>581.65</v>
+        <v>581.89</v>
       </c>
       <c r="T7">
-        <v>6.94</v>
+        <v>6.7</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1533,43 +1561,43 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>64.13</v>
+        <v>63.39</v>
       </c>
       <c r="Z7">
-        <v>4.98</v>
+        <v>6.26</v>
       </c>
       <c r="AA7">
-        <v>-0.88</v>
+        <v>0.55</v>
       </c>
       <c r="AB7">
-        <v>5.86</v>
+        <v>5.71</v>
       </c>
       <c r="AC7">
-        <v>99.05</v>
+        <v>98.75</v>
       </c>
       <c r="AD7">
-        <v>95.09999999999999</v>
+        <v>98.39</v>
       </c>
       <c r="AE7">
-        <v>15.68</v>
+        <v>15.41</v>
       </c>
       <c r="AF7">
-        <v>3.95</v>
+        <v>21.9</v>
       </c>
       <c r="AG7">
-        <v>621.1</v>
+        <v>626.22</v>
       </c>
       <c r="AH7">
-        <v>552.01</v>
+        <v>550.98</v>
       </c>
       <c r="AI7">
-        <v>568.8</v>
+        <v>575.79</v>
       </c>
       <c r="AJ7" t="s">
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>44.65</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1580,10 +1608,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>226.62</v>
+        <v>221.39</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>-2.31</v>
       </c>
       <c r="E8">
         <v>363.5</v>
@@ -1592,46 +1620,46 @@
         <v>210.4</v>
       </c>
       <c r="G8">
-        <v>-37.66</v>
+        <v>-39.09</v>
       </c>
       <c r="H8">
-        <v>7.71</v>
+        <v>5.22</v>
       </c>
       <c r="I8">
-        <v>-1.6</v>
+        <v>-1.85</v>
       </c>
       <c r="J8">
-        <v>1.02</v>
+        <v>-2.28</v>
       </c>
       <c r="K8">
-        <v>1.39</v>
+        <v>0.3</v>
       </c>
       <c r="L8">
-        <v>-36.02</v>
+        <v>-37.93</v>
       </c>
       <c r="M8">
-        <v>2.45</v>
+        <v>1.79</v>
       </c>
       <c r="N8">
         <v>12</v>
       </c>
       <c r="O8">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="P8">
-        <v>225.51</v>
+        <v>224.68</v>
       </c>
       <c r="Q8">
-        <v>223.33</v>
+        <v>223</v>
       </c>
       <c r="R8">
-        <v>229.04</v>
+        <v>229.26</v>
       </c>
       <c r="S8">
-        <v>267.79</v>
+        <v>267.22</v>
       </c>
       <c r="T8">
-        <v>-15.37</v>
+        <v>-17.15</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1646,34 +1674,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>50.65</v>
+        <v>44.35</v>
       </c>
       <c r="Z8">
-        <v>-0.23</v>
+        <v>-0.57</v>
       </c>
       <c r="AA8">
-        <v>-0.8100000000000001</v>
+        <v>-0.76</v>
       </c>
       <c r="AB8">
-        <v>0.58</v>
+        <v>0.2</v>
       </c>
       <c r="AC8">
-        <v>56.91</v>
+        <v>50.37</v>
       </c>
       <c r="AD8">
-        <v>53.46</v>
+        <v>53.44</v>
       </c>
       <c r="AE8">
-        <v>6.8</v>
+        <v>6.73</v>
       </c>
       <c r="AF8">
-        <v>-61.63</v>
+        <v>-70.52</v>
       </c>
       <c r="AG8">
-        <v>235.43</v>
+        <v>234.93</v>
       </c>
       <c r="AH8">
-        <v>211.23</v>
+        <v>211.08</v>
       </c>
       <c r="AI8">
         <v>237.22</v>
@@ -1682,7 +1710,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>31.17</v>
+        <v>28.99</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1693,10 +1721,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>3638.2</v>
+        <v>3594</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>-1.21</v>
       </c>
       <c r="E9">
         <v>4497.5</v>
@@ -1705,46 +1733,46 @@
         <v>3308.9</v>
       </c>
       <c r="G9">
-        <v>-19.11</v>
+        <v>-20.09</v>
       </c>
       <c r="H9">
-        <v>9.949999999999999</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="I9">
-        <v>1</v>
+        <v>-0.11</v>
       </c>
       <c r="J9">
-        <v>-1.92</v>
+        <v>-2.23</v>
       </c>
       <c r="K9">
-        <v>-1.99</v>
+        <v>-2.6</v>
       </c>
       <c r="L9">
-        <v>-7.97</v>
+        <v>-9.539999999999999</v>
       </c>
       <c r="M9">
-        <v>19.41</v>
+        <v>19.08</v>
       </c>
       <c r="N9">
         <v>34</v>
       </c>
       <c r="O9">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="P9">
-        <v>3620.28</v>
+        <v>3619.5</v>
       </c>
       <c r="Q9">
-        <v>3602.26</v>
+        <v>3601.62</v>
       </c>
       <c r="R9">
-        <v>3743.47</v>
+        <v>3740.7</v>
       </c>
       <c r="S9">
-        <v>3715.19</v>
+        <v>3713.03</v>
       </c>
       <c r="T9">
-        <v>-2.07</v>
+        <v>-3.21</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1759,43 +1787,43 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>46.97</v>
+        <v>40.16</v>
       </c>
       <c r="Z9">
-        <v>-31.48</v>
+        <v>-31.21</v>
       </c>
       <c r="AA9">
-        <v>-44.48</v>
+        <v>-41.83</v>
       </c>
       <c r="AB9">
-        <v>13</v>
+        <v>10.61</v>
       </c>
       <c r="AC9">
-        <v>100</v>
+        <v>72.98999999999999</v>
       </c>
       <c r="AD9">
-        <v>97.48999999999999</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="AE9">
-        <v>60.88</v>
+        <v>60.69</v>
       </c>
       <c r="AF9">
-        <v>-45.29</v>
+        <v>-66.06999999999999</v>
       </c>
       <c r="AG9">
-        <v>3647.38</v>
+        <v>3646.83</v>
       </c>
       <c r="AH9">
-        <v>3557.14</v>
+        <v>3556.42</v>
       </c>
       <c r="AI9">
-        <v>3794.41</v>
+        <v>3789.57</v>
       </c>
       <c r="AJ9" t="s">
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>18.02</v>
+        <v>16.23</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1806,10 +1834,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>1610</v>
+        <v>1592</v>
       </c>
       <c r="D10">
-        <v>-1.4</v>
+        <v>-1.12</v>
       </c>
       <c r="E10">
         <v>1768.4</v>
@@ -1818,46 +1846,46 @@
         <v>1326.2</v>
       </c>
       <c r="G10">
-        <v>-8.960000000000001</v>
+        <v>-9.98</v>
       </c>
       <c r="H10">
-        <v>21.4</v>
+        <v>20.04</v>
       </c>
       <c r="I10">
-        <v>-1.83</v>
+        <v>-3.1</v>
       </c>
       <c r="J10">
-        <v>2.36</v>
+        <v>0.99</v>
       </c>
       <c r="K10">
-        <v>9.74</v>
+        <v>10.63</v>
       </c>
       <c r="L10">
-        <v>9.84</v>
+        <v>6.58</v>
       </c>
       <c r="M10">
-        <v>5.73</v>
+        <v>5.51</v>
       </c>
       <c r="N10">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="O10">
         <v>65</v>
       </c>
       <c r="P10">
-        <v>1629.96</v>
+        <v>1619.76</v>
       </c>
       <c r="Q10">
-        <v>1621.57</v>
+        <v>1622.35</v>
       </c>
       <c r="R10">
-        <v>1520.81</v>
+        <v>1522.58</v>
       </c>
       <c r="S10">
-        <v>1503.98</v>
+        <v>1504.68</v>
       </c>
       <c r="T10">
-        <v>7.05</v>
+        <v>5.8</v>
       </c>
       <c r="U10" t="s">
         <v>48</v>
@@ -1872,34 +1900,34 @@
         <v>3</v>
       </c>
       <c r="Y10">
-        <v>54.59</v>
+        <v>50.08</v>
       </c>
       <c r="Z10">
-        <v>31.79</v>
+        <v>26.74</v>
       </c>
       <c r="AA10">
-        <v>39.86</v>
+        <v>37.24</v>
       </c>
       <c r="AB10">
-        <v>-8.07</v>
+        <v>-10.5</v>
       </c>
       <c r="AC10">
-        <v>8.220000000000001</v>
+        <v>1.72</v>
       </c>
       <c r="AD10">
-        <v>11.62</v>
+        <v>6.06</v>
       </c>
       <c r="AE10">
-        <v>39.45</v>
+        <v>38.78</v>
       </c>
       <c r="AF10">
-        <v>-54.71</v>
+        <v>-34.22</v>
       </c>
       <c r="AG10">
-        <v>1692.5</v>
+        <v>1691.5</v>
       </c>
       <c r="AH10">
-        <v>1550.64</v>
+        <v>1553.21</v>
       </c>
       <c r="AI10">
         <v>1527.05</v>
@@ -1908,7 +1936,7 @@
         <v>50</v>
       </c>
       <c r="AK10">
-        <v>27.31</v>
+        <v>28.62</v>
       </c>
     </row>
   </sheetData>
@@ -2049,7 +2077,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2069,12 +2097,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>52</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -2082,1040 +2145,1278 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C6" s="4" t="s">
+      <c r="B6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>-13.72</v>
+      </c>
+      <c r="D7" s="6">
+        <v>-13.53</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>9.960000000000001</v>
+      </c>
+      <c r="D8" s="6">
+        <v>8.09</v>
+      </c>
+      <c r="E8" s="8">
+        <v>-1.87</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>21.21</v>
+      </c>
+      <c r="D9" s="6">
+        <v>19.73</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-1.48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>2.03</v>
+      </c>
+      <c r="D10" s="6">
+        <v>2.93</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>4.34</v>
+      </c>
+      <c r="D11" s="6">
+        <v>2.93</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-1.41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>4.82</v>
+      </c>
+      <c r="D12" s="6">
+        <v>6.19</v>
+      </c>
+      <c r="E12" s="7">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-1.47</v>
+      </c>
+      <c r="D13" s="6">
+        <v>-2.28</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-2.5</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-2.23</v>
+      </c>
+      <c r="E14" s="7">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="6">
+        <v>8.109999999999999</v>
+      </c>
+      <c r="D15" s="6">
+        <v>0.99</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-7.12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-0.67</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-0.8</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-0.13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-2.1</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-1.12</v>
+      </c>
+      <c r="E17" s="7">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-4.49</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-3.16</v>
+      </c>
+      <c r="E18" s="7">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-0.43</v>
+      </c>
+      <c r="D19" s="6">
+        <v>0.39</v>
+      </c>
+      <c r="E19" s="7">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-1.17</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-1.87</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="6">
+        <v>3.86</v>
+      </c>
+      <c r="D21" s="6">
+        <v>4.35</v>
+      </c>
+      <c r="E21" s="7">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="6">
+        <v>-1.32</v>
+      </c>
+      <c r="D22" s="6">
+        <v>-1.85</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-0.53</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="6">
+        <v>1.05</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-0.11</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-1.16</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-0.13</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-3.1</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-2.97</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="6">
+        <v>3.74</v>
+      </c>
+      <c r="D25" s="6">
+        <v>4.88</v>
+      </c>
+      <c r="E25" s="7">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="D26" s="6">
+        <v>5.72</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-3.32</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>54.5</v>
+      </c>
+      <c r="D27" s="6">
+        <v>50.3</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-4.2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="6">
+        <v>12.45</v>
+      </c>
+      <c r="D28" s="6">
+        <v>12.55</v>
+      </c>
+      <c r="E28" s="7">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="6">
+        <v>25.93</v>
+      </c>
+      <c r="D29" s="6">
+        <v>23.34</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-2.59</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-5.77</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-7.33</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-1.56</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-35.56</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-37.93</v>
+      </c>
+      <c r="E31" s="8">
+        <v>-2.37</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-6.42</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-9.539999999999999</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-3.12</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="6">
+        <v>11.45</v>
+      </c>
+      <c r="D33" s="6">
+        <v>6.58</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-4.87</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-10.3</v>
+      </c>
+      <c r="D34" s="6">
+        <v>-11.49</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-1.19</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="6">
+        <v>11.17</v>
+      </c>
+      <c r="D35" s="6">
+        <v>9.59</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-1.58</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="6">
+        <v>22.96</v>
+      </c>
+      <c r="D36" s="6">
+        <v>24.98</v>
+      </c>
+      <c r="E36" s="7">
+        <v>2.02</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="6">
+        <v>19</v>
+      </c>
+      <c r="D37" s="6">
+        <v>17.58</v>
+      </c>
+      <c r="E37" s="8">
+        <v>-1.42</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="6">
+        <v>12.53</v>
+      </c>
+      <c r="D38" s="6">
+        <v>14.12</v>
+      </c>
+      <c r="E38" s="7">
+        <v>1.59</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-3.79</v>
+      </c>
+      <c r="D39" s="6">
+        <v>-3.09</v>
+      </c>
+      <c r="E39" s="7">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-1.1</v>
+      </c>
+      <c r="D40" s="6">
+        <v>0.3</v>
+      </c>
+      <c r="E40" s="7">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-1.14</v>
+      </c>
+      <c r="D41" s="6">
+        <v>-2.6</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-1.46</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="6">
+        <v>14.18</v>
+      </c>
+      <c r="D42" s="6">
+        <v>10.63</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-3.55</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="6">
+        <v>-16.82</v>
+      </c>
+      <c r="D43" s="6">
+        <v>-16.42</v>
+      </c>
+      <c r="E43" s="7">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="6">
+        <v>-9.84</v>
+      </c>
+      <c r="D44" s="6">
+        <v>-10.02</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-0.18</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-5.38</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-6.33</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-0.95</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="6">
+        <v>-8.73</v>
+      </c>
+      <c r="D46" s="6">
+        <v>-8.9</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-0.17</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="6">
+        <v>-8.4</v>
+      </c>
+      <c r="D47" s="6">
+        <v>-8.619999999999999</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="6">
+        <v>-10.13</v>
+      </c>
+      <c r="D48" s="6">
+        <v>-8.890000000000001</v>
+      </c>
+      <c r="E48" s="7">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="6">
+        <v>-37.66</v>
+      </c>
+      <c r="D49" s="6">
+        <v>-39.09</v>
+      </c>
+      <c r="E49" s="8">
+        <v>-1.43</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="6">
+        <v>-19.11</v>
+      </c>
+      <c r="D50" s="6">
+        <v>-20.09</v>
+      </c>
+      <c r="E50" s="8">
+        <v>-0.98</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="6">
+        <v>-7.67</v>
+      </c>
+      <c r="D51" s="6">
+        <v>-9.98</v>
+      </c>
+      <c r="E51" s="8">
+        <v>-2.31</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="6">
+        <v>407.75</v>
+      </c>
+      <c r="D52" s="6">
+        <v>409.7</v>
+      </c>
+      <c r="E52" s="7">
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="6">
+        <v>3428.3</v>
+      </c>
+      <c r="D53" s="6">
+        <v>3421.5</v>
+      </c>
+      <c r="E53" s="8">
+        <v>-6.8</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="6">
+        <v>390.1</v>
+      </c>
+      <c r="D54" s="6">
+        <v>386.2</v>
+      </c>
+      <c r="E54" s="8">
+        <v>-3.9</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="6">
+        <v>384.9</v>
+      </c>
+      <c r="D55" s="6">
+        <v>384.15</v>
+      </c>
+      <c r="E55" s="8">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="6">
+        <v>405.5</v>
+      </c>
+      <c r="D56" s="6">
+        <v>404.55</v>
+      </c>
+      <c r="E56" s="8">
+        <v>-0.95</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="6">
+        <v>612.45</v>
+      </c>
+      <c r="D57" s="6">
+        <v>620.9</v>
+      </c>
+      <c r="E57" s="7">
+        <v>8.449999999999999</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="6">
+        <v>226.62</v>
+      </c>
+      <c r="D58" s="6">
+        <v>221.39</v>
+      </c>
+      <c r="E58" s="8">
+        <v>-5.23</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="6">
+        <v>3638.2</v>
+      </c>
+      <c r="D59" s="6">
+        <v>3594</v>
+      </c>
+      <c r="E59" s="8">
+        <v>-44.2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="6">
+        <v>1632.8</v>
+      </c>
+      <c r="D60" s="6">
+        <v>1592</v>
+      </c>
+      <c r="E60" s="8">
+        <v>-40.8</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C61" s="6">
         <v>55</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="D61" s="6">
+        <v>66</v>
+      </c>
+      <c r="E61" s="7">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C62" s="6">
+        <v>66</v>
+      </c>
+      <c r="D62" s="6">
+        <v>55</v>
+      </c>
+      <c r="E62" s="8">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="5">
-        <v>-13.72</v>
-      </c>
-      <c r="D7" s="5">
-        <v>-13.92</v>
-      </c>
-      <c r="E7" s="6">
-        <v>-0.2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="B63" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="6">
+        <v>35.55</v>
+      </c>
+      <c r="D63" s="6">
+        <v>37.54</v>
+      </c>
+      <c r="E63" s="7">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="5">
-        <v>9.960000000000001</v>
-      </c>
-      <c r="D8" s="5">
-        <v>6.64</v>
-      </c>
-      <c r="E8" s="6">
-        <v>-3.32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="B64" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="6">
+        <v>59.71</v>
+      </c>
+      <c r="D64" s="6">
+        <v>58.25</v>
+      </c>
+      <c r="E64" s="8">
+        <v>-1.46</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="5">
-        <v>21.21</v>
-      </c>
-      <c r="D9" s="5">
-        <v>19.96</v>
-      </c>
-      <c r="E9" s="6">
-        <v>-1.25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="B65" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="6">
+        <v>57.74</v>
+      </c>
+      <c r="D65" s="6">
+        <v>55.57</v>
+      </c>
+      <c r="E65" s="8">
+        <v>-2.17</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="5">
-        <v>2.03</v>
-      </c>
-      <c r="D10" s="5">
-        <v>3.52</v>
-      </c>
-      <c r="E10" s="7">
-        <v>1.49</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="B66" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="6">
+        <v>55.93</v>
+      </c>
+      <c r="D66" s="6">
+        <v>54.43</v>
+      </c>
+      <c r="E66" s="8">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="5">
-        <v>4.34</v>
-      </c>
-      <c r="D11" s="5">
-        <v>4.69</v>
-      </c>
-      <c r="E11" s="7">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="B67" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="6">
+        <v>52.85</v>
+      </c>
+      <c r="D67" s="6">
+        <v>52.09</v>
+      </c>
+      <c r="E67" s="8">
+        <v>-0.76</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="5">
-        <v>4.82</v>
-      </c>
-      <c r="D12" s="5">
-        <v>7.16</v>
-      </c>
-      <c r="E12" s="7">
-        <v>2.34</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="B68" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="6">
+        <v>60.41</v>
+      </c>
+      <c r="D68" s="6">
+        <v>63.39</v>
+      </c>
+      <c r="E68" s="7">
+        <v>2.98</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="5">
-        <v>-1.47</v>
-      </c>
-      <c r="D13" s="5">
-        <v>1.02</v>
-      </c>
-      <c r="E13" s="7">
-        <v>2.49</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="B69" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="6">
+        <v>50.65</v>
+      </c>
+      <c r="D69" s="6">
+        <v>44.35</v>
+      </c>
+      <c r="E69" s="8">
+        <v>-6.3</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="5">
-        <v>-2.5</v>
-      </c>
-      <c r="D14" s="5">
-        <v>-1.92</v>
-      </c>
-      <c r="E14" s="7">
-        <v>0.58</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="B70" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="6">
+        <v>46.97</v>
+      </c>
+      <c r="D70" s="6">
+        <v>40.16</v>
+      </c>
+      <c r="E70" s="8">
+        <v>-6.81</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="5">
-        <v>8.109999999999999</v>
-      </c>
-      <c r="D15" s="5">
-        <v>2.36</v>
-      </c>
-      <c r="E15" s="6">
-        <v>-5.75</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="B71" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="6">
+        <v>61.06</v>
+      </c>
+      <c r="D71" s="6">
+        <v>50.08</v>
+      </c>
+      <c r="E71" s="8">
+        <v>-10.98</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="5">
-        <v>-0.67</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-0.43</v>
-      </c>
-      <c r="E16" s="7">
-        <v>0.24</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="B72" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C72" s="6">
+        <v>-77.08</v>
+      </c>
+      <c r="D72" s="6">
+        <v>-68.75</v>
+      </c>
+      <c r="E72" s="7">
+        <v>8.33</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="5">
-        <v>-2.1</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-3.6</v>
-      </c>
-      <c r="E17" s="6">
-        <v>-1.5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="B73" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="6">
+        <v>-59.3</v>
+      </c>
+      <c r="D73" s="6">
+        <v>-45.11</v>
+      </c>
+      <c r="E73" s="7">
+        <v>14.19</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="5">
-        <v>-4.49</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-5.68</v>
-      </c>
-      <c r="E18" s="6">
-        <v>-1.19</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="B74" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="6">
+        <v>-73.81999999999999</v>
+      </c>
+      <c r="D74" s="6">
+        <v>-79.59</v>
+      </c>
+      <c r="E74" s="8">
+        <v>-5.77</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="5">
-        <v>-0.43</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-0.05</v>
-      </c>
-      <c r="E19" s="7">
-        <v>0.38</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="B75" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="6">
+        <v>-87.86</v>
+      </c>
+      <c r="D75" s="6">
+        <v>-74.13</v>
+      </c>
+      <c r="E75" s="7">
+        <v>13.73</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="5">
-        <v>0.7</v>
-      </c>
-      <c r="D20" s="5">
-        <v>-1.42</v>
-      </c>
-      <c r="E20" s="6">
-        <v>-2.12</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="B76" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="6">
+        <v>-86.01000000000001</v>
+      </c>
+      <c r="D76" s="6">
+        <v>-81.53</v>
+      </c>
+      <c r="E76" s="7">
+        <v>4.48</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="5">
-        <v>3.86</v>
-      </c>
-      <c r="D21" s="5">
-        <v>2.33</v>
-      </c>
-      <c r="E21" s="6">
-        <v>-1.53</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="B77" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="6">
+        <v>-15.92</v>
+      </c>
+      <c r="D77" s="6">
+        <v>21.9</v>
+      </c>
+      <c r="E77" s="7">
+        <v>37.82</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="5">
-        <v>-1.32</v>
-      </c>
-      <c r="D22" s="5">
-        <v>-1.6</v>
-      </c>
-      <c r="E22" s="6">
-        <v>-0.28</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="B78" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="6">
+        <v>-49.09</v>
+      </c>
+      <c r="D78" s="6">
+        <v>-70.52</v>
+      </c>
+      <c r="E78" s="8">
+        <v>-21.43</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="5">
-        <v>1.05</v>
-      </c>
-      <c r="D23" s="5">
-        <v>1</v>
-      </c>
-      <c r="E23" s="6">
-        <v>-0.05</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="B79" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="6">
+        <v>-68.25</v>
+      </c>
+      <c r="D79" s="6">
+        <v>-66.06999999999999</v>
+      </c>
+      <c r="E79" s="7">
+        <v>2.18</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="5">
-        <v>-0.13</v>
-      </c>
-      <c r="D24" s="5">
-        <v>-1.83</v>
-      </c>
-      <c r="E24" s="6">
-        <v>-1.7</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="5">
-        <v>3.74</v>
-      </c>
-      <c r="D25" s="5">
-        <v>4.11</v>
-      </c>
-      <c r="E25" s="7">
-        <v>0.37</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="5">
-        <v>9.039999999999999</v>
-      </c>
-      <c r="D26" s="5">
-        <v>6.41</v>
-      </c>
-      <c r="E26" s="6">
-        <v>-2.63</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="5">
-        <v>54.5</v>
-      </c>
-      <c r="D27" s="5">
-        <v>52.54</v>
-      </c>
-      <c r="E27" s="6">
-        <v>-1.96</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="5">
-        <v>12.45</v>
-      </c>
-      <c r="D28" s="5">
-        <v>11.06</v>
-      </c>
-      <c r="E28" s="6">
-        <v>-1.39</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="5">
-        <v>25.93</v>
-      </c>
-      <c r="D29" s="5">
-        <v>22.01</v>
-      </c>
-      <c r="E29" s="6">
-        <v>-3.92</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-5.77</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-3.48</v>
-      </c>
-      <c r="E30" s="7">
-        <v>2.29</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="5">
-        <v>-35.56</v>
-      </c>
-      <c r="D31" s="5">
-        <v>-36.02</v>
-      </c>
-      <c r="E31" s="6">
-        <v>-0.46</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="5">
-        <v>-6.42</v>
-      </c>
-      <c r="D32" s="5">
-        <v>-7.97</v>
-      </c>
-      <c r="E32" s="6">
-        <v>-1.55</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="5">
-        <v>11.45</v>
-      </c>
-      <c r="D33" s="5">
-        <v>9.84</v>
-      </c>
-      <c r="E33" s="6">
-        <v>-1.61</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="5">
-        <v>-10.3</v>
-      </c>
-      <c r="D34" s="5">
-        <v>-12.23</v>
-      </c>
-      <c r="E34" s="6">
-        <v>-1.93</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="5">
-        <v>11.17</v>
-      </c>
-      <c r="D35" s="5">
-        <v>9.640000000000001</v>
-      </c>
-      <c r="E35" s="6">
-        <v>-1.53</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="5">
-        <v>22.96</v>
-      </c>
-      <c r="D36" s="5">
-        <v>21.66</v>
-      </c>
-      <c r="E36" s="6">
-        <v>-1.3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="5">
-        <v>19</v>
-      </c>
-      <c r="D37" s="5">
-        <v>17.56</v>
-      </c>
-      <c r="E37" s="6">
-        <v>-1.44</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="5">
-        <v>12.53</v>
-      </c>
-      <c r="D38" s="5">
-        <v>13.87</v>
-      </c>
-      <c r="E38" s="7">
-        <v>1.34</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="5">
-        <v>-3.79</v>
-      </c>
-      <c r="D39" s="5">
-        <v>-2.09</v>
-      </c>
-      <c r="E39" s="7">
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="5">
-        <v>-1.1</v>
-      </c>
-      <c r="D40" s="5">
-        <v>1.39</v>
-      </c>
-      <c r="E40" s="7">
-        <v>2.49</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="5">
-        <v>-1.14</v>
-      </c>
-      <c r="D41" s="5">
-        <v>-1.99</v>
-      </c>
-      <c r="E41" s="6">
-        <v>-0.85</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="5">
-        <v>14.18</v>
-      </c>
-      <c r="D42" s="5">
-        <v>9.74</v>
-      </c>
-      <c r="E42" s="6">
-        <v>-4.44</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="5">
-        <v>-9.84</v>
-      </c>
-      <c r="D43" s="5">
-        <v>-10.84</v>
-      </c>
-      <c r="E43" s="6">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="5">
-        <v>-5.38</v>
-      </c>
-      <c r="D44" s="5">
-        <v>-5.68</v>
-      </c>
-      <c r="E44" s="6">
-        <v>-0.3</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="5">
-        <v>-8.73</v>
-      </c>
-      <c r="D45" s="5">
-        <v>-8.31</v>
-      </c>
-      <c r="E45" s="7">
-        <v>0.42</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="5">
-        <v>-10.13</v>
-      </c>
-      <c r="D46" s="5">
-        <v>-8.73</v>
-      </c>
-      <c r="E46" s="7">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="5">
-        <v>-7.67</v>
-      </c>
-      <c r="D47" s="5">
-        <v>-8.960000000000001</v>
-      </c>
-      <c r="E47" s="6">
-        <v>-1.29</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="5">
-        <v>3428.3</v>
-      </c>
-      <c r="D48" s="5">
-        <v>3390.4</v>
-      </c>
-      <c r="E48" s="6">
-        <v>-37.9</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="5">
-        <v>390.1</v>
-      </c>
-      <c r="D49" s="5">
-        <v>388.9</v>
-      </c>
-      <c r="E49" s="6">
-        <v>-1.2</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C50" s="5">
-        <v>384.9</v>
-      </c>
-      <c r="D50" s="5">
-        <v>386.65</v>
-      </c>
-      <c r="E50" s="7">
-        <v>1.75</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C51" s="5">
-        <v>612.45</v>
-      </c>
-      <c r="D51" s="5">
-        <v>622</v>
-      </c>
-      <c r="E51" s="7">
-        <v>9.550000000000001</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="5">
-        <v>1632.8</v>
-      </c>
-      <c r="D52" s="5">
-        <v>1610</v>
-      </c>
-      <c r="E52" s="6">
-        <v>-22.8</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53" s="5">
-        <v>59.71</v>
-      </c>
-      <c r="D53" s="5">
-        <v>55.89</v>
-      </c>
-      <c r="E53" s="6">
-        <v>-3.82</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="5">
-        <v>57.74</v>
-      </c>
-      <c r="D54" s="5">
-        <v>57.09</v>
-      </c>
-      <c r="E54" s="6">
-        <v>-0.65</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="5">
-        <v>55.93</v>
-      </c>
-      <c r="D55" s="5">
-        <v>57.6</v>
-      </c>
-      <c r="E55" s="7">
-        <v>1.67</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="5">
-        <v>60.41</v>
-      </c>
-      <c r="D56" s="5">
-        <v>64.13</v>
-      </c>
-      <c r="E56" s="7">
-        <v>3.72</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="5">
-        <v>61.06</v>
-      </c>
-      <c r="D57" s="5">
-        <v>54.59</v>
-      </c>
-      <c r="E57" s="6">
-        <v>-6.47</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B58" s="3" t="s">
+      <c r="B80" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C58" s="5">
-        <v>-77.08</v>
-      </c>
-      <c r="D58" s="5">
-        <v>-78.34</v>
-      </c>
-      <c r="E58" s="6">
-        <v>-1.26</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C59" s="5">
-        <v>-59.3</v>
-      </c>
-      <c r="D59" s="5">
-        <v>-29.52</v>
-      </c>
-      <c r="E59" s="7">
-        <v>29.78</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C60" s="5">
-        <v>-73.81999999999999</v>
-      </c>
-      <c r="D60" s="5">
-        <v>-78.97</v>
-      </c>
-      <c r="E60" s="6">
-        <v>-5.15</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C61" s="5">
-        <v>-87.86</v>
-      </c>
-      <c r="D61" s="5">
-        <v>-64.62</v>
-      </c>
-      <c r="E61" s="7">
-        <v>23.24</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="5">
-        <v>-86.01000000000001</v>
-      </c>
-      <c r="D62" s="5">
-        <v>-69.7</v>
-      </c>
-      <c r="E62" s="7">
-        <v>16.31</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="5">
-        <v>-15.92</v>
-      </c>
-      <c r="D63" s="5">
-        <v>3.95</v>
-      </c>
-      <c r="E63" s="7">
-        <v>19.87</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="5">
-        <v>-49.09</v>
-      </c>
-      <c r="D64" s="5">
-        <v>-61.63</v>
-      </c>
-      <c r="E64" s="6">
-        <v>-12.54</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C65" s="5">
-        <v>-68.25</v>
-      </c>
-      <c r="D65" s="5">
-        <v>-45.29</v>
-      </c>
-      <c r="E65" s="7">
-        <v>22.96</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C66" s="5">
+      <c r="C80" s="6">
         <v>2.9</v>
       </c>
-      <c r="D66" s="5">
-        <v>-54.71</v>
-      </c>
-      <c r="E66" s="6">
-        <v>-57.61</v>
+      <c r="D80" s="6">
+        <v>-34.22</v>
+      </c>
+      <c r="E80" s="8">
+        <v>-37.12</v>
       </c>
     </row>
   </sheetData>
@@ -3141,60 +3442,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>65</v>
+      <c r="B1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>60.16</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>9</v>
       </c>
-      <c r="D2" s="10">
-        <v>52.8</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="11">
+        <v>50.7</v>
+      </c>
+      <c r="E2" s="11">
         <v>70</v>
       </c>
-      <c r="F2" s="10">
-        <v>3.3</v>
-      </c>
-      <c r="G2" s="10">
-        <v>6.4</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>2.5</v>
+      </c>
+      <c r="G2" s="11">
+        <v>6.7</v>
+      </c>
+      <c r="H2" s="11">
         <v>55.4</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>40</v>
       </c>
     </row>
@@ -3296,61 +3597,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="13" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="13">
-        <v>0.3477</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.3192</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.232</v>
-      </c>
-      <c r="D2" s="13">
-        <v>0.1941</v>
-      </c>
-      <c r="E2" s="13">
-        <v>0.1195</v>
-      </c>
-      <c r="F2" s="13">
-        <v>0.09420000000000001</v>
-      </c>
-      <c r="G2" s="13">
-        <v>0.0573</v>
-      </c>
-      <c r="H2" s="13">
-        <v>0.0245</v>
-      </c>
-      <c r="I2" s="13">
-        <v>-0.099</v>
+      <c r="A2" s="14">
+        <v>0.3499</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.3189</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.231</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.1908</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.1206</v>
+      </c>
+      <c r="F2" s="14">
+        <v>0.0931</v>
+      </c>
+      <c r="G2" s="14">
+        <v>0.0551</v>
+      </c>
+      <c r="H2" s="14">
+        <v>0.0179</v>
+      </c>
+      <c r="I2" s="14">
+        <v>-0.1011</v>
       </c>
     </row>
   </sheetData>

--- a/MAHINDRA_GROUP_Technical_Metrics.xlsx
+++ b/MAHINDRA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="78">
   <si>
     <t>Symbol</t>
   </si>
@@ -196,16 +196,25 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>50.6 → 44.4</t>
+    <t>54.4 → 43.6</t>
   </si>
   <si>
     <t>🔴 BEARISH</t>
   </si>
   <si>
-    <t>50.6</t>
-  </si>
-  <si>
-    <t>44.4</t>
+    <t>54.4</t>
+  </si>
+  <si>
+    <t>43.6</t>
+  </si>
+  <si>
+    <t>50.1 → 49.5</t>
+  </si>
+  <si>
+    <t>50.1</t>
+  </si>
+  <si>
+    <t>49.5</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -417,8 +426,8 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -930,10 +939,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>409.7</v>
+        <v>406.65</v>
       </c>
       <c r="D2">
-        <v>0.48</v>
+        <v>-0.74</v>
       </c>
       <c r="E2">
         <v>490.2</v>
@@ -942,46 +951,46 @@
         <v>379.2</v>
       </c>
       <c r="G2">
-        <v>-16.42</v>
+        <v>-17.04</v>
       </c>
       <c r="H2">
-        <v>8.039999999999999</v>
+        <v>7.24</v>
       </c>
       <c r="I2">
-        <v>-0.8</v>
+        <v>-1.23</v>
       </c>
       <c r="J2">
-        <v>-13.53</v>
+        <v>-13.97</v>
       </c>
       <c r="K2">
-        <v>-11.49</v>
+        <v>-12.13</v>
       </c>
       <c r="L2">
         <v>4.88</v>
       </c>
       <c r="M2">
-        <v>12.06</v>
+        <v>13.5</v>
       </c>
       <c r="N2">
         <v>23</v>
       </c>
       <c r="O2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P2">
-        <v>409.1</v>
+        <v>408.09</v>
       </c>
       <c r="Q2">
-        <v>414.81</v>
+        <v>411.52</v>
       </c>
       <c r="R2">
-        <v>443.4</v>
+        <v>442.73</v>
       </c>
       <c r="S2">
-        <v>438.21</v>
+        <v>438.07</v>
       </c>
       <c r="T2">
-        <v>-6.51</v>
+        <v>-7.17</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -996,43 +1005,43 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>37.54</v>
+        <v>35.69</v>
       </c>
       <c r="Z2">
-        <v>-10.92</v>
+        <v>-10.6</v>
       </c>
       <c r="AA2">
-        <v>-11.82</v>
+        <v>-11.57</v>
       </c>
       <c r="AB2">
-        <v>0.9</v>
+        <v>0.98</v>
       </c>
       <c r="AC2">
-        <v>77.81</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="AD2">
-        <v>77.86</v>
+        <v>75.65000000000001</v>
       </c>
       <c r="AE2">
-        <v>10.66</v>
+        <v>10.25</v>
       </c>
       <c r="AF2">
-        <v>-68.75</v>
+        <v>-81.08</v>
       </c>
       <c r="AG2">
-        <v>442.81</v>
+        <v>418.72</v>
       </c>
       <c r="AH2">
-        <v>386.82</v>
+        <v>404.32</v>
       </c>
       <c r="AI2">
-        <v>441.09</v>
+        <v>438.87</v>
       </c>
       <c r="AJ2" t="s">
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>32.16</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1043,10 +1052,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>3421.5</v>
+        <v>3415</v>
       </c>
       <c r="D3">
-        <v>0.92</v>
+        <v>-0.19</v>
       </c>
       <c r="E3">
         <v>3802.4</v>
@@ -1055,46 +1064,46 @@
         <v>2931.1</v>
       </c>
       <c r="G3">
-        <v>-10.02</v>
+        <v>-10.19</v>
       </c>
       <c r="H3">
-        <v>16.73</v>
+        <v>16.51</v>
       </c>
       <c r="I3">
-        <v>-1.12</v>
+        <v>0.33</v>
       </c>
       <c r="J3">
-        <v>8.09</v>
+        <v>6.66</v>
       </c>
       <c r="K3">
-        <v>9.59</v>
+        <v>10.2</v>
       </c>
       <c r="L3">
-        <v>5.72</v>
+        <v>4.05</v>
       </c>
       <c r="M3">
-        <v>34.99</v>
+        <v>35.16</v>
       </c>
       <c r="N3">
+        <v>55</v>
+      </c>
+      <c r="O3">
         <v>66</v>
       </c>
-      <c r="O3">
-        <v>65</v>
-      </c>
       <c r="P3">
-        <v>3414.4</v>
+        <v>3416.68</v>
       </c>
       <c r="Q3">
-        <v>3362.72</v>
+        <v>3374.7</v>
       </c>
       <c r="R3">
-        <v>3209.83</v>
+        <v>3218.32</v>
       </c>
       <c r="S3">
-        <v>3354.72</v>
+        <v>3354.29</v>
       </c>
       <c r="T3">
-        <v>1.99</v>
+        <v>1.81</v>
       </c>
       <c r="U3" t="s">
         <v>48</v>
@@ -1109,34 +1118,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>58.25</v>
+        <v>57.55</v>
       </c>
       <c r="Z3">
-        <v>68.55</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="AA3">
-        <v>75.43000000000001</v>
+        <v>73.19</v>
       </c>
       <c r="AB3">
-        <v>-6.87</v>
+        <v>-8.949999999999999</v>
       </c>
       <c r="AC3">
-        <v>16.82</v>
+        <v>10.84</v>
       </c>
       <c r="AD3">
-        <v>23.12</v>
+        <v>16.25</v>
       </c>
       <c r="AE3">
-        <v>70.7</v>
+        <v>69.54000000000001</v>
       </c>
       <c r="AF3">
-        <v>-45.11</v>
+        <v>-35.76</v>
       </c>
       <c r="AG3">
-        <v>3583.44</v>
+        <v>3577.92</v>
       </c>
       <c r="AH3">
-        <v>3141.99</v>
+        <v>3171.48</v>
       </c>
       <c r="AI3">
         <v>3274.47</v>
@@ -1145,7 +1154,7 @@
         <v>50</v>
       </c>
       <c r="AK3">
-        <v>36.79</v>
+        <v>32.52</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1156,10 +1165,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>386.2</v>
+        <v>389.6</v>
       </c>
       <c r="D4">
-        <v>-0.6899999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="E4">
         <v>412.3</v>
@@ -1168,46 +1177,46 @@
         <v>253.95</v>
       </c>
       <c r="G4">
-        <v>-6.33</v>
+        <v>-5.51</v>
       </c>
       <c r="H4">
-        <v>52.08</v>
+        <v>53.42</v>
       </c>
       <c r="I4">
-        <v>-3.16</v>
+        <v>-1.58</v>
       </c>
       <c r="J4">
-        <v>19.73</v>
+        <v>11.36</v>
       </c>
       <c r="K4">
-        <v>24.98</v>
+        <v>29.03</v>
       </c>
       <c r="L4">
-        <v>50.3</v>
+        <v>50.51</v>
       </c>
       <c r="M4">
-        <v>23.1</v>
+        <v>24.2</v>
       </c>
       <c r="N4">
         <v>99</v>
       </c>
       <c r="O4">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P4">
-        <v>391.49</v>
+        <v>390.24</v>
       </c>
       <c r="Q4">
-        <v>389.09</v>
+        <v>389.66</v>
       </c>
       <c r="R4">
-        <v>343.83</v>
+        <v>345.92</v>
       </c>
       <c r="S4">
-        <v>340.05</v>
+        <v>340.42</v>
       </c>
       <c r="T4">
-        <v>13.57</v>
+        <v>14.45</v>
       </c>
       <c r="U4" t="s">
         <v>48</v>
@@ -1222,34 +1231,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>55.57</v>
+        <v>57.12</v>
       </c>
       <c r="Z4">
-        <v>13.98</v>
+        <v>12.86</v>
       </c>
       <c r="AA4">
-        <v>17.49</v>
+        <v>16.56</v>
       </c>
       <c r="AB4">
-        <v>-3.5</v>
+        <v>-3.7</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AD4">
-        <v>0.35</v>
+        <v>1.17</v>
       </c>
       <c r="AE4">
-        <v>14.55</v>
+        <v>14.43</v>
       </c>
       <c r="AF4">
-        <v>-79.59</v>
+        <v>-67.16</v>
       </c>
       <c r="AG4">
-        <v>418.34</v>
+        <v>418.46</v>
       </c>
       <c r="AH4">
-        <v>359.84</v>
+        <v>360.87</v>
       </c>
       <c r="AI4">
         <v>357.72</v>
@@ -1258,7 +1267,7 @@
         <v>50</v>
       </c>
       <c r="AK4">
-        <v>35.75</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1269,10 +1278,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>384.15</v>
+        <v>373.7</v>
       </c>
       <c r="D5">
-        <v>-0.65</v>
+        <v>-2.72</v>
       </c>
       <c r="E5">
         <v>421.7</v>
@@ -1281,46 +1290,46 @@
         <v>294.25</v>
       </c>
       <c r="G5">
-        <v>-8.9</v>
+        <v>-11.38</v>
       </c>
       <c r="H5">
-        <v>30.55</v>
+        <v>27</v>
       </c>
       <c r="I5">
-        <v>0.39</v>
+        <v>-2.39</v>
       </c>
       <c r="J5">
-        <v>2.93</v>
+        <v>1.22</v>
       </c>
       <c r="K5">
-        <v>17.58</v>
+        <v>12.02</v>
       </c>
       <c r="L5">
-        <v>12.55</v>
+        <v>9.17</v>
       </c>
       <c r="M5">
-        <v>9.31</v>
+        <v>8.81</v>
       </c>
       <c r="N5">
         <v>77</v>
       </c>
       <c r="O5">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="P5">
-        <v>384.46</v>
+        <v>382.63</v>
       </c>
       <c r="Q5">
-        <v>384.78</v>
+        <v>384.76</v>
       </c>
       <c r="R5">
-        <v>369.66</v>
+        <v>370.44</v>
       </c>
       <c r="S5">
-        <v>364.96</v>
+        <v>364.91</v>
       </c>
       <c r="T5">
-        <v>5.26</v>
+        <v>2.41</v>
       </c>
       <c r="U5" t="s">
         <v>48</v>
@@ -1335,34 +1344,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>54.43</v>
+        <v>43.63</v>
       </c>
       <c r="Z5">
-        <v>4.06</v>
+        <v>2.87</v>
       </c>
       <c r="AA5">
-        <v>5.47</v>
+        <v>4.95</v>
       </c>
       <c r="AB5">
-        <v>-1.4</v>
+        <v>-2.08</v>
       </c>
       <c r="AC5">
-        <v>11.83</v>
+        <v>7.99</v>
       </c>
       <c r="AD5">
-        <v>10.14</v>
+        <v>10.8</v>
       </c>
       <c r="AE5">
-        <v>10.55</v>
+        <v>10.99</v>
       </c>
       <c r="AF5">
-        <v>-74.13</v>
+        <v>54.22</v>
       </c>
       <c r="AG5">
-        <v>397.35</v>
+        <v>397.41</v>
       </c>
       <c r="AH5">
-        <v>372.2</v>
+        <v>372.11</v>
       </c>
       <c r="AI5">
         <v>364.94</v>
@@ -1371,7 +1380,7 @@
         <v>50</v>
       </c>
       <c r="AK5">
-        <v>22.59</v>
+        <v>25.71</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1382,10 +1391,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>404.55</v>
+        <v>406.25</v>
       </c>
       <c r="D6">
-        <v>-0.23</v>
+        <v>0.42</v>
       </c>
       <c r="E6">
         <v>442.7</v>
@@ -1394,46 +1403,46 @@
         <v>279.55</v>
       </c>
       <c r="G6">
-        <v>-8.619999999999999</v>
+        <v>-8.23</v>
       </c>
       <c r="H6">
-        <v>44.71</v>
+        <v>45.32</v>
       </c>
       <c r="I6">
-        <v>-1.17</v>
+        <v>-0.17</v>
       </c>
       <c r="J6">
-        <v>2.93</v>
+        <v>3.86</v>
       </c>
       <c r="K6">
-        <v>14.12</v>
+        <v>14.16</v>
       </c>
       <c r="L6">
-        <v>23.34</v>
+        <v>21.5</v>
       </c>
       <c r="M6">
-        <v>-10.11</v>
+        <v>-10.42</v>
       </c>
       <c r="N6">
         <v>88</v>
       </c>
       <c r="O6">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="P6">
-        <v>405.7</v>
+        <v>405.56</v>
       </c>
       <c r="Q6">
-        <v>408.9</v>
+        <v>409.11</v>
       </c>
       <c r="R6">
-        <v>387.02</v>
+        <v>388.24</v>
       </c>
       <c r="S6">
-        <v>364.24</v>
+        <v>364.45</v>
       </c>
       <c r="T6">
-        <v>11.07</v>
+        <v>11.47</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1448,43 +1457,43 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>52.09</v>
+        <v>53.39</v>
       </c>
       <c r="Z6">
-        <v>4.51</v>
+        <v>4.12</v>
       </c>
       <c r="AA6">
-        <v>6.67</v>
+        <v>6.16</v>
       </c>
       <c r="AB6">
-        <v>-2.16</v>
+        <v>-2.04</v>
       </c>
       <c r="AC6">
-        <v>3.1</v>
+        <v>5.04</v>
       </c>
       <c r="AD6">
-        <v>5.09</v>
+        <v>4.43</v>
       </c>
       <c r="AE6">
-        <v>12.58</v>
+        <v>12.39</v>
       </c>
       <c r="AF6">
-        <v>-81.53</v>
+        <v>-57.13</v>
       </c>
       <c r="AG6">
-        <v>422.54</v>
+        <v>422.44</v>
       </c>
       <c r="AH6">
-        <v>395.26</v>
+        <v>395.77</v>
       </c>
       <c r="AI6">
-        <v>371.16</v>
+        <v>372.35</v>
       </c>
       <c r="AJ6" t="s">
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>26.45</v>
+        <v>23.09</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1495,10 +1504,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>620.9</v>
+        <v>613.9</v>
       </c>
       <c r="D7">
-        <v>-0.18</v>
+        <v>-1.13</v>
       </c>
       <c r="E7">
         <v>681.5</v>
@@ -1507,25 +1516,25 @@
         <v>506.45</v>
       </c>
       <c r="G7">
-        <v>-8.890000000000001</v>
+        <v>-9.92</v>
       </c>
       <c r="H7">
-        <v>22.6</v>
+        <v>21.22</v>
       </c>
       <c r="I7">
-        <v>4.35</v>
+        <v>0.65</v>
       </c>
       <c r="J7">
-        <v>6.19</v>
+        <v>5.84</v>
       </c>
       <c r="K7">
-        <v>-3.09</v>
+        <v>-3.9</v>
       </c>
       <c r="L7">
-        <v>-7.33</v>
+        <v>-9.07</v>
       </c>
       <c r="M7">
-        <v>31.89</v>
+        <v>31.85</v>
       </c>
       <c r="N7">
         <v>45</v>
@@ -1534,19 +1543,19 @@
         <v>44</v>
       </c>
       <c r="P7">
-        <v>615.46</v>
+        <v>616.25</v>
       </c>
       <c r="Q7">
-        <v>588.6</v>
+        <v>590.52</v>
       </c>
       <c r="R7">
-        <v>599.89</v>
+        <v>599.96</v>
       </c>
       <c r="S7">
-        <v>581.89</v>
+        <v>582.0700000000001</v>
       </c>
       <c r="T7">
-        <v>6.7</v>
+        <v>5.47</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1561,34 +1570,34 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>63.39</v>
+        <v>58.76</v>
       </c>
       <c r="Z7">
-        <v>6.26</v>
+        <v>6.63</v>
       </c>
       <c r="AA7">
-        <v>0.55</v>
+        <v>1.76</v>
       </c>
       <c r="AB7">
-        <v>5.71</v>
+        <v>4.87</v>
       </c>
       <c r="AC7">
-        <v>98.75</v>
+        <v>92.48999999999999</v>
       </c>
       <c r="AD7">
-        <v>98.39</v>
+        <v>96.76000000000001</v>
       </c>
       <c r="AE7">
-        <v>15.41</v>
+        <v>15.21</v>
       </c>
       <c r="AF7">
-        <v>21.9</v>
+        <v>37.53</v>
       </c>
       <c r="AG7">
-        <v>626.22</v>
+        <v>629.22</v>
       </c>
       <c r="AH7">
-        <v>550.98</v>
+        <v>551.8200000000001</v>
       </c>
       <c r="AI7">
         <v>575.79</v>
@@ -1597,7 +1606,7 @@
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>48.1</v>
+        <v>49.17</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1608,10 +1617,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>221.39</v>
+        <v>219.48</v>
       </c>
       <c r="D8">
-        <v>-2.31</v>
+        <v>-0.86</v>
       </c>
       <c r="E8">
         <v>363.5</v>
@@ -1620,25 +1629,25 @@
         <v>210.4</v>
       </c>
       <c r="G8">
-        <v>-39.09</v>
+        <v>-39.62</v>
       </c>
       <c r="H8">
-        <v>5.22</v>
+        <v>4.32</v>
       </c>
       <c r="I8">
-        <v>-1.85</v>
+        <v>-2.4</v>
       </c>
       <c r="J8">
-        <v>-2.28</v>
+        <v>-3.72</v>
       </c>
       <c r="K8">
-        <v>0.3</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L8">
-        <v>-37.93</v>
+        <v>-38.74</v>
       </c>
       <c r="M8">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="N8">
         <v>12</v>
@@ -1647,19 +1656,19 @@
         <v>18</v>
       </c>
       <c r="P8">
-        <v>224.68</v>
+        <v>223.6</v>
       </c>
       <c r="Q8">
-        <v>223</v>
+        <v>223.39</v>
       </c>
       <c r="R8">
-        <v>229.26</v>
+        <v>229.03</v>
       </c>
       <c r="S8">
-        <v>267.22</v>
+        <v>266.67</v>
       </c>
       <c r="T8">
-        <v>-17.15</v>
+        <v>-17.7</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1674,34 +1683,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>44.35</v>
+        <v>42.28</v>
       </c>
       <c r="Z8">
-        <v>-0.57</v>
+        <v>-0.98</v>
       </c>
       <c r="AA8">
-        <v>-0.76</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="AB8">
-        <v>0.2</v>
+        <v>-0.17</v>
       </c>
       <c r="AC8">
-        <v>50.37</v>
+        <v>29.46</v>
       </c>
       <c r="AD8">
-        <v>53.44</v>
+        <v>45.58</v>
       </c>
       <c r="AE8">
-        <v>6.73</v>
+        <v>6.52</v>
       </c>
       <c r="AF8">
-        <v>-70.52</v>
+        <v>-62.9</v>
       </c>
       <c r="AG8">
-        <v>234.93</v>
+        <v>234.23</v>
       </c>
       <c r="AH8">
-        <v>211.08</v>
+        <v>212.56</v>
       </c>
       <c r="AI8">
         <v>237.22</v>
@@ -1710,7 +1719,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>28.99</v>
+        <v>25.54</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1721,10 +1730,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>3594</v>
+        <v>3588.8</v>
       </c>
       <c r="D9">
-        <v>-1.21</v>
+        <v>-0.14</v>
       </c>
       <c r="E9">
         <v>4497.5</v>
@@ -1733,46 +1742,46 @@
         <v>3308.9</v>
       </c>
       <c r="G9">
-        <v>-20.09</v>
+        <v>-20.2</v>
       </c>
       <c r="H9">
-        <v>8.619999999999999</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="I9">
-        <v>-0.11</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="J9">
-        <v>-2.23</v>
+        <v>-0.5</v>
       </c>
       <c r="K9">
-        <v>-2.6</v>
+        <v>-2.42</v>
       </c>
       <c r="L9">
-        <v>-9.539999999999999</v>
+        <v>-10.21</v>
       </c>
       <c r="M9">
-        <v>19.08</v>
+        <v>19.68</v>
       </c>
       <c r="N9">
         <v>34</v>
       </c>
       <c r="O9">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="P9">
-        <v>3619.5</v>
+        <v>3615.48</v>
       </c>
       <c r="Q9">
-        <v>3601.62</v>
+        <v>3601.71</v>
       </c>
       <c r="R9">
-        <v>3740.7</v>
+        <v>3736.87</v>
       </c>
       <c r="S9">
-        <v>3713.03</v>
+        <v>3710.85</v>
       </c>
       <c r="T9">
-        <v>-3.21</v>
+        <v>-3.29</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1787,43 +1796,43 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>40.16</v>
+        <v>39.44</v>
       </c>
       <c r="Z9">
-        <v>-31.21</v>
+        <v>-31.07</v>
       </c>
       <c r="AA9">
-        <v>-41.83</v>
+        <v>-39.67</v>
       </c>
       <c r="AB9">
-        <v>10.61</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="AC9">
-        <v>72.98999999999999</v>
+        <v>43.11</v>
       </c>
       <c r="AD9">
-        <v>90.81999999999999</v>
+        <v>72.03</v>
       </c>
       <c r="AE9">
-        <v>60.69</v>
+        <v>59.75</v>
       </c>
       <c r="AF9">
-        <v>-66.06999999999999</v>
+        <v>-39.86</v>
       </c>
       <c r="AG9">
-        <v>3646.83</v>
+        <v>3646.81</v>
       </c>
       <c r="AH9">
-        <v>3556.42</v>
+        <v>3556.61</v>
       </c>
       <c r="AI9">
-        <v>3789.57</v>
+        <v>3764.06</v>
       </c>
       <c r="AJ9" t="s">
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>16.23</v>
+        <v>15.54</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1834,10 +1843,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>1592</v>
+        <v>1589.8</v>
       </c>
       <c r="D10">
-        <v>-1.12</v>
+        <v>-0.14</v>
       </c>
       <c r="E10">
         <v>1768.4</v>
@@ -1846,46 +1855,46 @@
         <v>1326.2</v>
       </c>
       <c r="G10">
-        <v>-9.98</v>
+        <v>-10.1</v>
       </c>
       <c r="H10">
-        <v>20.04</v>
+        <v>19.88</v>
       </c>
       <c r="I10">
-        <v>-3.1</v>
+        <v>-2.17</v>
       </c>
       <c r="J10">
-        <v>0.99</v>
+        <v>0.86</v>
       </c>
       <c r="K10">
-        <v>10.63</v>
+        <v>11.96</v>
       </c>
       <c r="L10">
-        <v>6.58</v>
+        <v>6.65</v>
       </c>
       <c r="M10">
-        <v>5.51</v>
+        <v>5.69</v>
       </c>
       <c r="N10">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="O10">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="P10">
-        <v>1619.76</v>
+        <v>1612.72</v>
       </c>
       <c r="Q10">
-        <v>1622.35</v>
+        <v>1623.82</v>
       </c>
       <c r="R10">
-        <v>1522.58</v>
+        <v>1524.7</v>
       </c>
       <c r="S10">
-        <v>1504.68</v>
+        <v>1505.46</v>
       </c>
       <c r="T10">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="U10" t="s">
         <v>48</v>
@@ -1900,34 +1909,34 @@
         <v>3</v>
       </c>
       <c r="Y10">
-        <v>50.08</v>
+        <v>49.54</v>
       </c>
       <c r="Z10">
-        <v>26.74</v>
+        <v>22.3</v>
       </c>
       <c r="AA10">
-        <v>37.24</v>
+        <v>34.25</v>
       </c>
       <c r="AB10">
-        <v>-10.5</v>
+        <v>-11.95</v>
       </c>
       <c r="AC10">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AD10">
-        <v>6.06</v>
+        <v>3.32</v>
       </c>
       <c r="AE10">
-        <v>38.78</v>
+        <v>38.5</v>
       </c>
       <c r="AF10">
-        <v>-34.22</v>
+        <v>-38.96</v>
       </c>
       <c r="AG10">
-        <v>1691.5</v>
+        <v>1688.57</v>
       </c>
       <c r="AH10">
-        <v>1553.21</v>
+        <v>1559.06</v>
       </c>
       <c r="AI10">
         <v>1527.05</v>
@@ -1936,7 +1945,7 @@
         <v>50</v>
       </c>
       <c r="AK10">
-        <v>28.62</v>
+        <v>30.15</v>
       </c>
     </row>
   </sheetData>
@@ -2117,7 +2126,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2135,353 +2144,356 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="D4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E6" s="3" t="s">
+      <c r="B7" s="3" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="6">
-        <v>-13.72</v>
-      </c>
-      <c r="D7" s="6">
-        <v>-13.53</v>
-      </c>
-      <c r="E7" s="7">
-        <v>0.19</v>
+      <c r="C7" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>9.960000000000001</v>
+        <v>-13.53</v>
       </c>
       <c r="D8" s="6">
-        <v>8.09</v>
-      </c>
-      <c r="E8" s="8">
-        <v>-1.87</v>
+        <v>-13.97</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-0.44</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>21.21</v>
+        <v>8.09</v>
       </c>
       <c r="D9" s="6">
-        <v>19.73</v>
-      </c>
-      <c r="E9" s="8">
-        <v>-1.48</v>
+        <v>6.66</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-1.43</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>2.03</v>
+        <v>19.73</v>
       </c>
       <c r="D10" s="6">
-        <v>2.93</v>
+        <v>11.36</v>
       </c>
       <c r="E10" s="7">
-        <v>0.9</v>
+        <v>-8.369999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>4.34</v>
+        <v>2.93</v>
       </c>
       <c r="D11" s="6">
-        <v>2.93</v>
-      </c>
-      <c r="E11" s="8">
-        <v>-1.41</v>
+        <v>1.22</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-1.71</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>4.82</v>
+        <v>2.93</v>
       </c>
       <c r="D12" s="6">
-        <v>6.19</v>
-      </c>
-      <c r="E12" s="7">
-        <v>1.37</v>
+        <v>3.86</v>
+      </c>
+      <c r="E12" s="8">
+        <v>0.93</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-1.47</v>
+        <v>6.19</v>
       </c>
       <c r="D13" s="6">
-        <v>-2.28</v>
-      </c>
-      <c r="E13" s="8">
-        <v>-0.8100000000000001</v>
+        <v>5.84</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-0.35</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>-2.5</v>
+        <v>-2.28</v>
       </c>
       <c r="D14" s="6">
-        <v>-2.23</v>
+        <v>-3.72</v>
       </c>
       <c r="E14" s="7">
-        <v>0.27</v>
+        <v>-1.44</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="6">
-        <v>8.109999999999999</v>
+        <v>-2.23</v>
       </c>
       <c r="D15" s="6">
-        <v>0.99</v>
+        <v>-0.5</v>
       </c>
       <c r="E15" s="8">
-        <v>-7.12</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C16" s="6">
-        <v>-0.67</v>
+        <v>0.99</v>
       </c>
       <c r="D16" s="6">
-        <v>-0.8</v>
-      </c>
-      <c r="E16" s="8">
+        <v>0.86</v>
+      </c>
+      <c r="E16" s="7">
         <v>-0.13</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>-2.1</v>
+        <v>-0.8</v>
       </c>
       <c r="D17" s="6">
-        <v>-1.12</v>
+        <v>-1.23</v>
       </c>
       <c r="E17" s="7">
-        <v>0.98</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>-4.49</v>
+        <v>-1.12</v>
       </c>
       <c r="D18" s="6">
-        <v>-3.16</v>
-      </c>
-      <c r="E18" s="7">
-        <v>1.33</v>
+        <v>0.33</v>
+      </c>
+      <c r="E18" s="8">
+        <v>1.45</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>-0.43</v>
+        <v>-3.16</v>
       </c>
       <c r="D19" s="6">
-        <v>0.39</v>
-      </c>
-      <c r="E19" s="7">
-        <v>0.82</v>
+        <v>-1.58</v>
+      </c>
+      <c r="E19" s="8">
+        <v>1.58</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>0.7</v>
+        <v>0.39</v>
       </c>
       <c r="D20" s="6">
-        <v>-1.17</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-1.87</v>
+        <v>-2.39</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-2.78</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="6">
-        <v>3.86</v>
+        <v>-1.17</v>
       </c>
       <c r="D21" s="6">
-        <v>4.35</v>
-      </c>
-      <c r="E21" s="7">
-        <v>0.49</v>
+        <v>-0.17</v>
+      </c>
+      <c r="E21" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="6">
-        <v>-1.32</v>
+        <v>4.35</v>
       </c>
       <c r="D22" s="6">
-        <v>-1.85</v>
-      </c>
-      <c r="E22" s="8">
-        <v>-0.53</v>
+        <v>0.65</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-3.7</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="6">
-        <v>1.05</v>
+        <v>-1.85</v>
       </c>
       <c r="D23" s="6">
-        <v>-0.11</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-1.16</v>
+        <v>-2.4</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-0.55</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="6">
-        <v>-0.13</v>
+        <v>-0.11</v>
       </c>
       <c r="D24" s="6">
-        <v>-3.1</v>
-      </c>
-      <c r="E24" s="8">
-        <v>-2.97</v>
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-0.45</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C25" s="6">
-        <v>3.74</v>
+        <v>-3.1</v>
       </c>
       <c r="D25" s="6">
-        <v>4.88</v>
-      </c>
-      <c r="E25" s="7">
-        <v>1.14</v>
+        <v>-2.17</v>
+      </c>
+      <c r="E25" s="8">
+        <v>0.93</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2492,13 +2504,13 @@
         <v>11</v>
       </c>
       <c r="C26" s="6">
-        <v>9.039999999999999</v>
+        <v>5.72</v>
       </c>
       <c r="D26" s="6">
-        <v>5.72</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-3.32</v>
+        <v>4.05</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-1.67</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2509,13 +2521,13 @@
         <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>54.5</v>
+        <v>50.3</v>
       </c>
       <c r="D27" s="6">
-        <v>50.3</v>
+        <v>50.51</v>
       </c>
       <c r="E27" s="8">
-        <v>-4.2</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2526,13 +2538,13 @@
         <v>11</v>
       </c>
       <c r="C28" s="6">
-        <v>12.45</v>
+        <v>12.55</v>
       </c>
       <c r="D28" s="6">
-        <v>12.55</v>
+        <v>9.17</v>
       </c>
       <c r="E28" s="7">
-        <v>0.1</v>
+        <v>-3.38</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2543,13 +2555,13 @@
         <v>11</v>
       </c>
       <c r="C29" s="6">
-        <v>25.93</v>
+        <v>23.34</v>
       </c>
       <c r="D29" s="6">
-        <v>23.34</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-2.59</v>
+        <v>21.5</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-1.84</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2560,13 +2572,13 @@
         <v>11</v>
       </c>
       <c r="C30" s="6">
-        <v>-5.77</v>
+        <v>-7.33</v>
       </c>
       <c r="D30" s="6">
-        <v>-7.33</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-1.56</v>
+        <v>-9.07</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-1.74</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2577,13 +2589,13 @@
         <v>11</v>
       </c>
       <c r="C31" s="6">
-        <v>-35.56</v>
+        <v>-37.93</v>
       </c>
       <c r="D31" s="6">
-        <v>-37.93</v>
-      </c>
-      <c r="E31" s="8">
-        <v>-2.37</v>
+        <v>-38.74</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2594,13 +2606,13 @@
         <v>11</v>
       </c>
       <c r="C32" s="6">
-        <v>-6.42</v>
+        <v>-9.539999999999999</v>
       </c>
       <c r="D32" s="6">
-        <v>-9.539999999999999</v>
-      </c>
-      <c r="E32" s="8">
-        <v>-3.12</v>
+        <v>-10.21</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-0.67</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2611,13 +2623,13 @@
         <v>11</v>
       </c>
       <c r="C33" s="6">
-        <v>11.45</v>
+        <v>6.58</v>
       </c>
       <c r="D33" s="6">
-        <v>6.58</v>
+        <v>6.65</v>
       </c>
       <c r="E33" s="8">
-        <v>-4.87</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2628,13 +2640,13 @@
         <v>10</v>
       </c>
       <c r="C34" s="6">
-        <v>-10.3</v>
+        <v>-11.49</v>
       </c>
       <c r="D34" s="6">
-        <v>-11.49</v>
-      </c>
-      <c r="E34" s="8">
-        <v>-1.19</v>
+        <v>-12.13</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-0.64</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2645,13 +2657,13 @@
         <v>10</v>
       </c>
       <c r="C35" s="6">
-        <v>11.17</v>
+        <v>9.59</v>
       </c>
       <c r="D35" s="6">
-        <v>9.59</v>
+        <v>10.2</v>
       </c>
       <c r="E35" s="8">
-        <v>-1.58</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2662,13 +2674,13 @@
         <v>10</v>
       </c>
       <c r="C36" s="6">
-        <v>22.96</v>
+        <v>24.98</v>
       </c>
       <c r="D36" s="6">
-        <v>24.98</v>
-      </c>
-      <c r="E36" s="7">
-        <v>2.02</v>
+        <v>29.03</v>
+      </c>
+      <c r="E36" s="8">
+        <v>4.05</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2679,13 +2691,13 @@
         <v>10</v>
       </c>
       <c r="C37" s="6">
-        <v>19</v>
+        <v>17.58</v>
       </c>
       <c r="D37" s="6">
-        <v>17.58</v>
-      </c>
-      <c r="E37" s="8">
-        <v>-1.42</v>
+        <v>12.02</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-5.56</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2696,13 +2708,13 @@
         <v>10</v>
       </c>
       <c r="C38" s="6">
-        <v>12.53</v>
+        <v>14.12</v>
       </c>
       <c r="D38" s="6">
-        <v>14.12</v>
-      </c>
-      <c r="E38" s="7">
-        <v>1.59</v>
+        <v>14.16</v>
+      </c>
+      <c r="E38" s="8">
+        <v>0.04</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2713,13 +2725,13 @@
         <v>10</v>
       </c>
       <c r="C39" s="6">
-        <v>-3.79</v>
+        <v>-3.09</v>
       </c>
       <c r="D39" s="6">
-        <v>-3.09</v>
+        <v>-3.9</v>
       </c>
       <c r="E39" s="7">
-        <v>0.7</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2730,13 +2742,13 @@
         <v>10</v>
       </c>
       <c r="C40" s="6">
-        <v>-1.1</v>
+        <v>0.3</v>
       </c>
       <c r="D40" s="6">
-        <v>0.3</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E40" s="7">
-        <v>1.4</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2747,13 +2759,13 @@
         <v>10</v>
       </c>
       <c r="C41" s="6">
-        <v>-1.14</v>
+        <v>-2.6</v>
       </c>
       <c r="D41" s="6">
-        <v>-2.6</v>
+        <v>-2.42</v>
       </c>
       <c r="E41" s="8">
-        <v>-1.46</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2764,13 +2776,13 @@
         <v>10</v>
       </c>
       <c r="C42" s="6">
-        <v>14.18</v>
+        <v>10.63</v>
       </c>
       <c r="D42" s="6">
-        <v>10.63</v>
+        <v>11.96</v>
       </c>
       <c r="E42" s="8">
-        <v>-3.55</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2781,13 +2793,13 @@
         <v>6</v>
       </c>
       <c r="C43" s="6">
-        <v>-16.82</v>
+        <v>-16.42</v>
       </c>
       <c r="D43" s="6">
-        <v>-16.42</v>
+        <v>-17.04</v>
       </c>
       <c r="E43" s="7">
-        <v>0.4</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2798,13 +2810,13 @@
         <v>6</v>
       </c>
       <c r="C44" s="6">
-        <v>-9.84</v>
+        <v>-10.02</v>
       </c>
       <c r="D44" s="6">
-        <v>-10.02</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-0.18</v>
+        <v>-10.19</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-0.17</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2815,13 +2827,13 @@
         <v>6</v>
       </c>
       <c r="C45" s="6">
-        <v>-5.38</v>
+        <v>-6.33</v>
       </c>
       <c r="D45" s="6">
-        <v>-6.33</v>
+        <v>-5.51</v>
       </c>
       <c r="E45" s="8">
-        <v>-0.95</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2832,13 +2844,13 @@
         <v>6</v>
       </c>
       <c r="C46" s="6">
-        <v>-8.73</v>
+        <v>-8.9</v>
       </c>
       <c r="D46" s="6">
-        <v>-8.9</v>
-      </c>
-      <c r="E46" s="8">
-        <v>-0.17</v>
+        <v>-11.38</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-2.48</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2849,13 +2861,13 @@
         <v>6</v>
       </c>
       <c r="C47" s="6">
-        <v>-8.4</v>
+        <v>-8.619999999999999</v>
       </c>
       <c r="D47" s="6">
-        <v>-8.619999999999999</v>
+        <v>-8.23</v>
       </c>
       <c r="E47" s="8">
-        <v>-0.22</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2866,13 +2878,13 @@
         <v>6</v>
       </c>
       <c r="C48" s="6">
-        <v>-10.13</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="D48" s="6">
-        <v>-8.890000000000001</v>
+        <v>-9.92</v>
       </c>
       <c r="E48" s="7">
-        <v>1.24</v>
+        <v>-1.03</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2883,13 +2895,13 @@
         <v>6</v>
       </c>
       <c r="C49" s="6">
-        <v>-37.66</v>
+        <v>-39.09</v>
       </c>
       <c r="D49" s="6">
-        <v>-39.09</v>
-      </c>
-      <c r="E49" s="8">
-        <v>-1.43</v>
+        <v>-39.62</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-0.53</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2900,13 +2912,13 @@
         <v>6</v>
       </c>
       <c r="C50" s="6">
-        <v>-19.11</v>
+        <v>-20.09</v>
       </c>
       <c r="D50" s="6">
-        <v>-20.09</v>
-      </c>
-      <c r="E50" s="8">
-        <v>-0.98</v>
+        <v>-20.2</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-0.11</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2917,13 +2929,13 @@
         <v>6</v>
       </c>
       <c r="C51" s="6">
-        <v>-7.67</v>
+        <v>-9.98</v>
       </c>
       <c r="D51" s="6">
-        <v>-9.98</v>
-      </c>
-      <c r="E51" s="8">
-        <v>-2.31</v>
+        <v>-10.1</v>
+      </c>
+      <c r="E51" s="7">
+        <v>-0.12</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2934,13 +2946,13 @@
         <v>2</v>
       </c>
       <c r="C52" s="6">
-        <v>407.75</v>
+        <v>409.7</v>
       </c>
       <c r="D52" s="6">
-        <v>409.7</v>
+        <v>406.65</v>
       </c>
       <c r="E52" s="7">
-        <v>1.95</v>
+        <v>-3.05</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2951,13 +2963,13 @@
         <v>2</v>
       </c>
       <c r="C53" s="6">
-        <v>3428.3</v>
+        <v>3421.5</v>
       </c>
       <c r="D53" s="6">
-        <v>3421.5</v>
-      </c>
-      <c r="E53" s="8">
-        <v>-6.8</v>
+        <v>3415</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-6.5</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2968,13 +2980,13 @@
         <v>2</v>
       </c>
       <c r="C54" s="6">
-        <v>390.1</v>
+        <v>386.2</v>
       </c>
       <c r="D54" s="6">
-        <v>386.2</v>
+        <v>389.6</v>
       </c>
       <c r="E54" s="8">
-        <v>-3.9</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -2985,13 +2997,13 @@
         <v>2</v>
       </c>
       <c r="C55" s="6">
-        <v>384.9</v>
+        <v>384.15</v>
       </c>
       <c r="D55" s="6">
-        <v>384.15</v>
-      </c>
-      <c r="E55" s="8">
-        <v>-0.75</v>
+        <v>373.7</v>
+      </c>
+      <c r="E55" s="7">
+        <v>-10.45</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -3002,13 +3014,13 @@
         <v>2</v>
       </c>
       <c r="C56" s="6">
-        <v>405.5</v>
+        <v>404.55</v>
       </c>
       <c r="D56" s="6">
-        <v>404.55</v>
+        <v>406.25</v>
       </c>
       <c r="E56" s="8">
-        <v>-0.95</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -3019,13 +3031,13 @@
         <v>2</v>
       </c>
       <c r="C57" s="6">
-        <v>612.45</v>
+        <v>620.9</v>
       </c>
       <c r="D57" s="6">
-        <v>620.9</v>
+        <v>613.9</v>
       </c>
       <c r="E57" s="7">
-        <v>8.449999999999999</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -3036,13 +3048,13 @@
         <v>2</v>
       </c>
       <c r="C58" s="6">
-        <v>226.62</v>
+        <v>221.39</v>
       </c>
       <c r="D58" s="6">
-        <v>221.39</v>
-      </c>
-      <c r="E58" s="8">
-        <v>-5.23</v>
+        <v>219.48</v>
+      </c>
+      <c r="E58" s="7">
+        <v>-1.91</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -3053,13 +3065,13 @@
         <v>2</v>
       </c>
       <c r="C59" s="6">
-        <v>3638.2</v>
+        <v>3594</v>
       </c>
       <c r="D59" s="6">
-        <v>3594</v>
-      </c>
-      <c r="E59" s="8">
-        <v>-44.2</v>
+        <v>3588.8</v>
+      </c>
+      <c r="E59" s="7">
+        <v>-5.2</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -3070,13 +3082,13 @@
         <v>2</v>
       </c>
       <c r="C60" s="6">
-        <v>1632.8</v>
+        <v>1592</v>
       </c>
       <c r="D60" s="6">
-        <v>1592</v>
-      </c>
-      <c r="E60" s="8">
-        <v>-40.8</v>
+        <v>1589.8</v>
+      </c>
+      <c r="E60" s="7">
+        <v>-2.2</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -3087,13 +3099,13 @@
         <v>13</v>
       </c>
       <c r="C61" s="6">
+        <v>66</v>
+      </c>
+      <c r="D61" s="6">
         <v>55</v>
       </c>
-      <c r="D61" s="6">
-        <v>66</v>
-      </c>
       <c r="E61" s="7">
-        <v>11</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -3104,13 +3116,13 @@
         <v>13</v>
       </c>
       <c r="C62" s="6">
+        <v>55</v>
+      </c>
+      <c r="D62" s="6">
         <v>66</v>
       </c>
-      <c r="D62" s="6">
-        <v>55</v>
-      </c>
       <c r="E62" s="8">
-        <v>-11</v>
+        <v>11</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -3121,13 +3133,13 @@
         <v>24</v>
       </c>
       <c r="C63" s="6">
-        <v>35.55</v>
+        <v>37.54</v>
       </c>
       <c r="D63" s="6">
-        <v>37.54</v>
+        <v>35.69</v>
       </c>
       <c r="E63" s="7">
-        <v>1.99</v>
+        <v>-1.85</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -3138,13 +3150,13 @@
         <v>24</v>
       </c>
       <c r="C64" s="6">
-        <v>59.71</v>
+        <v>58.25</v>
       </c>
       <c r="D64" s="6">
-        <v>58.25</v>
-      </c>
-      <c r="E64" s="8">
-        <v>-1.46</v>
+        <v>57.55</v>
+      </c>
+      <c r="E64" s="7">
+        <v>-0.7</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -3155,13 +3167,13 @@
         <v>24</v>
       </c>
       <c r="C65" s="6">
-        <v>57.74</v>
+        <v>55.57</v>
       </c>
       <c r="D65" s="6">
-        <v>55.57</v>
+        <v>57.12</v>
       </c>
       <c r="E65" s="8">
-        <v>-2.17</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -3172,13 +3184,13 @@
         <v>24</v>
       </c>
       <c r="C66" s="6">
-        <v>55.93</v>
+        <v>54.43</v>
       </c>
       <c r="D66" s="6">
-        <v>54.43</v>
-      </c>
-      <c r="E66" s="8">
-        <v>-1.5</v>
+        <v>43.63</v>
+      </c>
+      <c r="E66" s="7">
+        <v>-10.8</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -3189,13 +3201,13 @@
         <v>24</v>
       </c>
       <c r="C67" s="6">
-        <v>52.85</v>
+        <v>52.09</v>
       </c>
       <c r="D67" s="6">
-        <v>52.09</v>
+        <v>53.39</v>
       </c>
       <c r="E67" s="8">
-        <v>-0.76</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -3206,13 +3218,13 @@
         <v>24</v>
       </c>
       <c r="C68" s="6">
-        <v>60.41</v>
+        <v>63.39</v>
       </c>
       <c r="D68" s="6">
-        <v>63.39</v>
+        <v>58.76</v>
       </c>
       <c r="E68" s="7">
-        <v>2.98</v>
+        <v>-4.63</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -3223,13 +3235,13 @@
         <v>24</v>
       </c>
       <c r="C69" s="6">
-        <v>50.65</v>
+        <v>44.35</v>
       </c>
       <c r="D69" s="6">
-        <v>44.35</v>
-      </c>
-      <c r="E69" s="8">
-        <v>-6.3</v>
+        <v>42.28</v>
+      </c>
+      <c r="E69" s="7">
+        <v>-2.07</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -3240,13 +3252,13 @@
         <v>24</v>
       </c>
       <c r="C70" s="6">
-        <v>46.97</v>
+        <v>40.16</v>
       </c>
       <c r="D70" s="6">
-        <v>40.16</v>
-      </c>
-      <c r="E70" s="8">
-        <v>-6.81</v>
+        <v>39.44</v>
+      </c>
+      <c r="E70" s="7">
+        <v>-0.72</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -3257,13 +3269,13 @@
         <v>24</v>
       </c>
       <c r="C71" s="6">
-        <v>61.06</v>
+        <v>50.08</v>
       </c>
       <c r="D71" s="6">
-        <v>50.08</v>
-      </c>
-      <c r="E71" s="8">
-        <v>-10.98</v>
+        <v>49.54</v>
+      </c>
+      <c r="E71" s="7">
+        <v>-0.54</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -3274,13 +3286,13 @@
         <v>31</v>
       </c>
       <c r="C72" s="6">
-        <v>-77.08</v>
+        <v>-68.75</v>
       </c>
       <c r="D72" s="6">
-        <v>-68.75</v>
+        <v>-81.08</v>
       </c>
       <c r="E72" s="7">
-        <v>8.33</v>
+        <v>-12.33</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -3291,13 +3303,13 @@
         <v>31</v>
       </c>
       <c r="C73" s="6">
-        <v>-59.3</v>
+        <v>-45.11</v>
       </c>
       <c r="D73" s="6">
-        <v>-45.11</v>
-      </c>
-      <c r="E73" s="7">
-        <v>14.19</v>
+        <v>-35.76</v>
+      </c>
+      <c r="E73" s="8">
+        <v>9.35</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -3308,13 +3320,13 @@
         <v>31</v>
       </c>
       <c r="C74" s="6">
-        <v>-73.81999999999999</v>
+        <v>-79.59</v>
       </c>
       <c r="D74" s="6">
-        <v>-79.59</v>
+        <v>-67.16</v>
       </c>
       <c r="E74" s="8">
-        <v>-5.77</v>
+        <v>12.43</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -3325,13 +3337,13 @@
         <v>31</v>
       </c>
       <c r="C75" s="6">
-        <v>-87.86</v>
+        <v>-74.13</v>
       </c>
       <c r="D75" s="6">
-        <v>-74.13</v>
-      </c>
-      <c r="E75" s="7">
-        <v>13.73</v>
+        <v>54.22</v>
+      </c>
+      <c r="E75" s="8">
+        <v>128.35</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -3342,13 +3354,13 @@
         <v>31</v>
       </c>
       <c r="C76" s="6">
-        <v>-86.01000000000001</v>
+        <v>-81.53</v>
       </c>
       <c r="D76" s="6">
-        <v>-81.53</v>
-      </c>
-      <c r="E76" s="7">
-        <v>4.48</v>
+        <v>-57.13</v>
+      </c>
+      <c r="E76" s="8">
+        <v>24.4</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -3359,13 +3371,13 @@
         <v>31</v>
       </c>
       <c r="C77" s="6">
-        <v>-15.92</v>
+        <v>21.9</v>
       </c>
       <c r="D77" s="6">
-        <v>21.9</v>
-      </c>
-      <c r="E77" s="7">
-        <v>37.82</v>
+        <v>37.53</v>
+      </c>
+      <c r="E77" s="8">
+        <v>15.63</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -3376,13 +3388,13 @@
         <v>31</v>
       </c>
       <c r="C78" s="6">
-        <v>-49.09</v>
+        <v>-70.52</v>
       </c>
       <c r="D78" s="6">
-        <v>-70.52</v>
+        <v>-62.9</v>
       </c>
       <c r="E78" s="8">
-        <v>-21.43</v>
+        <v>7.62</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -3393,13 +3405,13 @@
         <v>31</v>
       </c>
       <c r="C79" s="6">
-        <v>-68.25</v>
+        <v>-66.06999999999999</v>
       </c>
       <c r="D79" s="6">
-        <v>-66.06999999999999</v>
-      </c>
-      <c r="E79" s="7">
-        <v>2.18</v>
+        <v>-39.86</v>
+      </c>
+      <c r="E79" s="8">
+        <v>26.21</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -3410,19 +3422,19 @@
         <v>31</v>
       </c>
       <c r="C80" s="6">
-        <v>2.9</v>
+        <v>-34.22</v>
       </c>
       <c r="D80" s="6">
-        <v>-34.22</v>
-      </c>
-      <c r="E80" s="8">
-        <v>-37.12</v>
+        <v>-38.96</v>
+      </c>
+      <c r="E80" s="7">
+        <v>-4.74</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3446,28 +3458,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3481,16 +3493,16 @@
         <v>9</v>
       </c>
       <c r="D2" s="11">
-        <v>50.7</v>
+        <v>48.6</v>
       </c>
       <c r="E2" s="11">
         <v>70</v>
       </c>
       <c r="F2" s="11">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="G2" s="11">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="H2" s="11">
         <v>55.4</v>
@@ -3627,31 +3639,31 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="14">
-        <v>0.3499</v>
+        <v>0.3516</v>
       </c>
       <c r="B2" s="14">
-        <v>0.3189</v>
+        <v>0.3185</v>
       </c>
       <c r="C2" s="14">
-        <v>0.231</v>
+        <v>0.242</v>
       </c>
       <c r="D2" s="14">
-        <v>0.1908</v>
+        <v>0.1968</v>
       </c>
       <c r="E2" s="14">
-        <v>0.1206</v>
+        <v>0.135</v>
       </c>
       <c r="F2" s="14">
-        <v>0.0931</v>
+        <v>0.08810000000000001</v>
       </c>
       <c r="G2" s="14">
-        <v>0.0551</v>
+        <v>0.05690000000000001</v>
       </c>
       <c r="H2" s="14">
-        <v>0.0179</v>
+        <v>0.0186</v>
       </c>
       <c r="I2" s="14">
-        <v>-0.1011</v>
+        <v>-0.1042</v>
       </c>
     </row>
   </sheetData>

--- a/MAHINDRA_GROUP_Technical_Metrics.xlsx
+++ b/MAHINDRA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="75">
   <si>
     <t>Symbol</t>
   </si>
@@ -196,25 +196,16 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>54.4 → 43.6</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>54.4</t>
-  </si>
-  <si>
-    <t>43.6</t>
-  </si>
-  <si>
-    <t>50.1 → 49.5</t>
+    <t>49.5 → 50.1</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>49.5</t>
   </si>
   <si>
     <t>50.1</t>
-  </si>
-  <si>
-    <t>49.5</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -300,14 +291,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -340,13 +331,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -426,8 +417,8 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -939,10 +930,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>406.65</v>
+        <v>403.8</v>
       </c>
       <c r="D2">
-        <v>-0.74</v>
+        <v>-0.7</v>
       </c>
       <c r="E2">
         <v>490.2</v>
@@ -951,46 +942,46 @@
         <v>379.2</v>
       </c>
       <c r="G2">
-        <v>-17.04</v>
+        <v>-17.63</v>
       </c>
       <c r="H2">
-        <v>7.24</v>
+        <v>6.49</v>
       </c>
       <c r="I2">
-        <v>-1.23</v>
+        <v>-1.17</v>
       </c>
       <c r="J2">
-        <v>-13.97</v>
+        <v>-14.54</v>
       </c>
       <c r="K2">
-        <v>-12.13</v>
+        <v>-10.5</v>
       </c>
       <c r="L2">
-        <v>4.88</v>
+        <v>3.62</v>
       </c>
       <c r="M2">
-        <v>13.5</v>
+        <v>13.33</v>
       </c>
       <c r="N2">
         <v>23</v>
       </c>
       <c r="O2">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P2">
-        <v>408.09</v>
+        <v>407.13</v>
       </c>
       <c r="Q2">
-        <v>411.52</v>
+        <v>410.76</v>
       </c>
       <c r="R2">
-        <v>442.73</v>
+        <v>442.1</v>
       </c>
       <c r="S2">
-        <v>438.07</v>
+        <v>437.96</v>
       </c>
       <c r="T2">
-        <v>-7.17</v>
+        <v>-7.8</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1005,43 +996,43 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>35.69</v>
+        <v>33.99</v>
       </c>
       <c r="Z2">
-        <v>-10.6</v>
+        <v>-10.45</v>
       </c>
       <c r="AA2">
-        <v>-11.57</v>
+        <v>-11.35</v>
       </c>
       <c r="AB2">
-        <v>0.98</v>
+        <v>0.9</v>
       </c>
       <c r="AC2">
-        <v>75.76000000000001</v>
+        <v>53.52</v>
       </c>
       <c r="AD2">
-        <v>75.65000000000001</v>
+        <v>69.03</v>
       </c>
       <c r="AE2">
-        <v>10.25</v>
+        <v>10.03</v>
       </c>
       <c r="AF2">
-        <v>-81.08</v>
+        <v>-57.92</v>
       </c>
       <c r="AG2">
-        <v>418.72</v>
+        <v>417.85</v>
       </c>
       <c r="AH2">
-        <v>404.32</v>
+        <v>403.68</v>
       </c>
       <c r="AI2">
-        <v>438.87</v>
+        <v>436.69</v>
       </c>
       <c r="AJ2" t="s">
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>31.5</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1052,10 +1043,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>3415</v>
+        <v>3424.8</v>
       </c>
       <c r="D3">
-        <v>-0.19</v>
+        <v>0.29</v>
       </c>
       <c r="E3">
         <v>3802.4</v>
@@ -1064,46 +1055,46 @@
         <v>2931.1</v>
       </c>
       <c r="G3">
-        <v>-10.19</v>
+        <v>-9.93</v>
       </c>
       <c r="H3">
-        <v>16.51</v>
+        <v>16.84</v>
       </c>
       <c r="I3">
-        <v>0.33</v>
+        <v>-0.1</v>
       </c>
       <c r="J3">
-        <v>6.66</v>
+        <v>7.86</v>
       </c>
       <c r="K3">
-        <v>10.2</v>
+        <v>11.15</v>
       </c>
       <c r="L3">
-        <v>4.05</v>
+        <v>4.88</v>
       </c>
       <c r="M3">
-        <v>35.16</v>
+        <v>35.21</v>
       </c>
       <c r="N3">
         <v>55</v>
       </c>
       <c r="O3">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="P3">
-        <v>3416.68</v>
+        <v>3416</v>
       </c>
       <c r="Q3">
-        <v>3374.7</v>
+        <v>3384.46</v>
       </c>
       <c r="R3">
-        <v>3218.32</v>
+        <v>3227.77</v>
       </c>
       <c r="S3">
-        <v>3354.29</v>
+        <v>3353.98</v>
       </c>
       <c r="T3">
-        <v>1.81</v>
+        <v>2.11</v>
       </c>
       <c r="U3" t="s">
         <v>48</v>
@@ -1118,34 +1109,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>57.55</v>
+        <v>58.36</v>
       </c>
       <c r="Z3">
-        <v>64.23999999999999</v>
+        <v>60.92</v>
       </c>
       <c r="AA3">
-        <v>73.19</v>
+        <v>70.73999999999999</v>
       </c>
       <c r="AB3">
-        <v>-8.949999999999999</v>
+        <v>-9.82</v>
       </c>
       <c r="AC3">
-        <v>10.84</v>
+        <v>15.9</v>
       </c>
       <c r="AD3">
-        <v>16.25</v>
+        <v>14.52</v>
       </c>
       <c r="AE3">
-        <v>69.54000000000001</v>
+        <v>68.53</v>
       </c>
       <c r="AF3">
-        <v>-35.76</v>
+        <v>-48.36</v>
       </c>
       <c r="AG3">
-        <v>3577.92</v>
+        <v>3576.8</v>
       </c>
       <c r="AH3">
-        <v>3171.48</v>
+        <v>3192.11</v>
       </c>
       <c r="AI3">
         <v>3274.47</v>
@@ -1154,7 +1145,7 @@
         <v>50</v>
       </c>
       <c r="AK3">
-        <v>32.52</v>
+        <v>30.84</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1165,10 +1156,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>389.6</v>
+        <v>382.45</v>
       </c>
       <c r="D4">
-        <v>0.88</v>
+        <v>-1.84</v>
       </c>
       <c r="E4">
         <v>412.3</v>
@@ -1177,46 +1168,46 @@
         <v>253.95</v>
       </c>
       <c r="G4">
-        <v>-5.51</v>
+        <v>-7.24</v>
       </c>
       <c r="H4">
-        <v>53.42</v>
+        <v>50.6</v>
       </c>
       <c r="I4">
-        <v>-1.58</v>
+        <v>-3.52</v>
       </c>
       <c r="J4">
-        <v>11.36</v>
+        <v>1.14</v>
       </c>
       <c r="K4">
-        <v>29.03</v>
+        <v>27.67</v>
       </c>
       <c r="L4">
-        <v>50.51</v>
+        <v>49.92</v>
       </c>
       <c r="M4">
-        <v>24.2</v>
+        <v>23.73</v>
       </c>
       <c r="N4">
         <v>99</v>
       </c>
       <c r="O4">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="P4">
-        <v>390.24</v>
+        <v>387.45</v>
       </c>
       <c r="Q4">
-        <v>389.66</v>
+        <v>390.27</v>
       </c>
       <c r="R4">
-        <v>345.92</v>
+        <v>348.03</v>
       </c>
       <c r="S4">
-        <v>340.42</v>
+        <v>340.75</v>
       </c>
       <c r="T4">
-        <v>14.45</v>
+        <v>12.24</v>
       </c>
       <c r="U4" t="s">
         <v>48</v>
@@ -1231,34 +1222,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>57.12</v>
+        <v>52.93</v>
       </c>
       <c r="Z4">
-        <v>12.86</v>
+        <v>11.26</v>
       </c>
       <c r="AA4">
-        <v>16.56</v>
+        <v>15.5</v>
       </c>
       <c r="AB4">
-        <v>-3.7</v>
+        <v>-4.24</v>
       </c>
       <c r="AC4">
         <v>2.99</v>
       </c>
       <c r="AD4">
-        <v>1.17</v>
+        <v>1.99</v>
       </c>
       <c r="AE4">
-        <v>14.43</v>
+        <v>14.68</v>
       </c>
       <c r="AF4">
-        <v>-67.16</v>
+        <v>-65.81</v>
       </c>
       <c r="AG4">
-        <v>418.46</v>
+        <v>417.84</v>
       </c>
       <c r="AH4">
-        <v>360.87</v>
+        <v>362.7</v>
       </c>
       <c r="AI4">
         <v>357.72</v>
@@ -1267,7 +1258,7 @@
         <v>50</v>
       </c>
       <c r="AK4">
-        <v>31.8</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1278,10 +1269,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>373.7</v>
+        <v>377.2</v>
       </c>
       <c r="D5">
-        <v>-2.72</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E5">
         <v>421.7</v>
@@ -1290,25 +1281,25 @@
         <v>294.25</v>
       </c>
       <c r="G5">
-        <v>-11.38</v>
+        <v>-10.55</v>
       </c>
       <c r="H5">
-        <v>27</v>
+        <v>28.19</v>
       </c>
       <c r="I5">
-        <v>-2.39</v>
+        <v>-1.71</v>
       </c>
       <c r="J5">
-        <v>1.22</v>
+        <v>0.83</v>
       </c>
       <c r="K5">
-        <v>12.02</v>
+        <v>10.62</v>
       </c>
       <c r="L5">
-        <v>9.17</v>
+        <v>10.65</v>
       </c>
       <c r="M5">
-        <v>8.81</v>
+        <v>9.01</v>
       </c>
       <c r="N5">
         <v>77</v>
@@ -1317,19 +1308,19 @@
         <v>67</v>
       </c>
       <c r="P5">
-        <v>382.63</v>
+        <v>381.32</v>
       </c>
       <c r="Q5">
-        <v>384.76</v>
+        <v>384.74</v>
       </c>
       <c r="R5">
-        <v>370.44</v>
+        <v>371.5</v>
       </c>
       <c r="S5">
-        <v>364.91</v>
+        <v>364.87</v>
       </c>
       <c r="T5">
-        <v>2.41</v>
+        <v>3.38</v>
       </c>
       <c r="U5" t="s">
         <v>48</v>
@@ -1344,34 +1335,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>43.63</v>
+        <v>47.39</v>
       </c>
       <c r="Z5">
-        <v>2.87</v>
+        <v>2.19</v>
       </c>
       <c r="AA5">
-        <v>4.95</v>
+        <v>4.4</v>
       </c>
       <c r="AB5">
-        <v>-2.08</v>
+        <v>-2.21</v>
       </c>
       <c r="AC5">
-        <v>7.99</v>
+        <v>5.51</v>
       </c>
       <c r="AD5">
-        <v>10.8</v>
+        <v>8.44</v>
       </c>
       <c r="AE5">
-        <v>10.99</v>
+        <v>10.82</v>
       </c>
       <c r="AF5">
-        <v>54.22</v>
+        <v>-84.66</v>
       </c>
       <c r="AG5">
-        <v>397.41</v>
+        <v>397.43</v>
       </c>
       <c r="AH5">
-        <v>372.11</v>
+        <v>372.06</v>
       </c>
       <c r="AI5">
         <v>364.94</v>
@@ -1380,7 +1371,7 @@
         <v>50</v>
       </c>
       <c r="AK5">
-        <v>25.71</v>
+        <v>28.42</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1391,10 +1382,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>406.25</v>
+        <v>406.65</v>
       </c>
       <c r="D6">
-        <v>0.42</v>
+        <v>0.1</v>
       </c>
       <c r="E6">
         <v>442.7</v>
@@ -1403,46 +1394,46 @@
         <v>279.55</v>
       </c>
       <c r="G6">
-        <v>-8.23</v>
+        <v>-8.140000000000001</v>
       </c>
       <c r="H6">
-        <v>45.32</v>
+        <v>45.47</v>
       </c>
       <c r="I6">
-        <v>-0.17</v>
+        <v>0.16</v>
       </c>
       <c r="J6">
-        <v>3.86</v>
+        <v>1.12</v>
       </c>
       <c r="K6">
-        <v>14.16</v>
+        <v>14.78</v>
       </c>
       <c r="L6">
-        <v>21.5</v>
+        <v>26.19</v>
       </c>
       <c r="M6">
-        <v>-10.42</v>
+        <v>-10.4</v>
       </c>
       <c r="N6">
         <v>88</v>
       </c>
       <c r="O6">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="P6">
-        <v>405.56</v>
+        <v>405.69</v>
       </c>
       <c r="Q6">
-        <v>409.11</v>
+        <v>409.85</v>
       </c>
       <c r="R6">
-        <v>388.24</v>
+        <v>389.61</v>
       </c>
       <c r="S6">
-        <v>364.45</v>
+        <v>364.71</v>
       </c>
       <c r="T6">
-        <v>11.47</v>
+        <v>11.5</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1457,34 +1448,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>53.39</v>
+        <v>53.7</v>
       </c>
       <c r="Z6">
-        <v>4.12</v>
+        <v>3.8</v>
       </c>
       <c r="AA6">
-        <v>6.16</v>
+        <v>5.69</v>
       </c>
       <c r="AB6">
-        <v>-2.04</v>
+        <v>-1.89</v>
       </c>
       <c r="AC6">
-        <v>5.04</v>
+        <v>7.83</v>
       </c>
       <c r="AD6">
-        <v>4.43</v>
+        <v>5.32</v>
       </c>
       <c r="AE6">
-        <v>12.39</v>
+        <v>12.07</v>
       </c>
       <c r="AF6">
-        <v>-57.13</v>
+        <v>-73.65000000000001</v>
       </c>
       <c r="AG6">
-        <v>422.44</v>
+        <v>420.53</v>
       </c>
       <c r="AH6">
-        <v>395.77</v>
+        <v>399.17</v>
       </c>
       <c r="AI6">
         <v>372.35</v>
@@ -1493,7 +1484,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>23.09</v>
+        <v>21.38</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1504,10 +1495,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>613.9</v>
+        <v>610.6</v>
       </c>
       <c r="D7">
-        <v>-1.13</v>
+        <v>-0.54</v>
       </c>
       <c r="E7">
         <v>681.5</v>
@@ -1516,46 +1507,46 @@
         <v>506.45</v>
       </c>
       <c r="G7">
-        <v>-9.92</v>
+        <v>-10.4</v>
       </c>
       <c r="H7">
-        <v>21.22</v>
+        <v>20.56</v>
       </c>
       <c r="I7">
-        <v>0.65</v>
+        <v>-0.23</v>
       </c>
       <c r="J7">
-        <v>5.84</v>
+        <v>6.11</v>
       </c>
       <c r="K7">
         <v>-3.9</v>
       </c>
       <c r="L7">
-        <v>-9.07</v>
+        <v>-9.470000000000001</v>
       </c>
       <c r="M7">
-        <v>31.85</v>
+        <v>31.69</v>
       </c>
       <c r="N7">
         <v>45</v>
       </c>
       <c r="O7">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P7">
-        <v>616.25</v>
+        <v>615.97</v>
       </c>
       <c r="Q7">
-        <v>590.52</v>
+        <v>592.79</v>
       </c>
       <c r="R7">
-        <v>599.96</v>
+        <v>600.2</v>
       </c>
       <c r="S7">
-        <v>582.0700000000001</v>
+        <v>582.28</v>
       </c>
       <c r="T7">
-        <v>5.47</v>
+        <v>4.86</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1570,34 +1561,34 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>58.76</v>
+        <v>56.65</v>
       </c>
       <c r="Z7">
-        <v>6.63</v>
+        <v>6.58</v>
       </c>
       <c r="AA7">
-        <v>1.76</v>
+        <v>2.73</v>
       </c>
       <c r="AB7">
-        <v>4.87</v>
+        <v>3.86</v>
       </c>
       <c r="AC7">
-        <v>92.48999999999999</v>
+        <v>81.04000000000001</v>
       </c>
       <c r="AD7">
-        <v>96.76000000000001</v>
+        <v>90.76000000000001</v>
       </c>
       <c r="AE7">
-        <v>15.21</v>
+        <v>14.87</v>
       </c>
       <c r="AF7">
-        <v>37.53</v>
+        <v>66.55</v>
       </c>
       <c r="AG7">
-        <v>629.22</v>
+        <v>630.54</v>
       </c>
       <c r="AH7">
-        <v>551.8200000000001</v>
+        <v>555.05</v>
       </c>
       <c r="AI7">
         <v>575.79</v>
@@ -1606,7 +1597,7 @@
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>49.17</v>
+        <v>48.01</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1617,10 +1608,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>219.48</v>
+        <v>221.05</v>
       </c>
       <c r="D8">
-        <v>-0.86</v>
+        <v>0.72</v>
       </c>
       <c r="E8">
         <v>363.5</v>
@@ -1629,46 +1620,46 @@
         <v>210.4</v>
       </c>
       <c r="G8">
-        <v>-39.62</v>
+        <v>-39.19</v>
       </c>
       <c r="H8">
-        <v>4.32</v>
+        <v>5.06</v>
       </c>
       <c r="I8">
-        <v>-2.4</v>
+        <v>-1.26</v>
       </c>
       <c r="J8">
-        <v>-3.72</v>
+        <v>4.42</v>
       </c>
       <c r="K8">
-        <v>0.07000000000000001</v>
+        <v>1</v>
       </c>
       <c r="L8">
-        <v>-38.74</v>
+        <v>-37.83</v>
       </c>
       <c r="M8">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="N8">
         <v>12</v>
       </c>
       <c r="O8">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="P8">
-        <v>223.6</v>
+        <v>223.03</v>
       </c>
       <c r="Q8">
-        <v>223.39</v>
+        <v>223.54</v>
       </c>
       <c r="R8">
-        <v>229.03</v>
+        <v>228.74</v>
       </c>
       <c r="S8">
-        <v>266.67</v>
+        <v>266.13</v>
       </c>
       <c r="T8">
-        <v>-17.7</v>
+        <v>-16.94</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1683,34 +1674,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>42.28</v>
+        <v>44.57</v>
       </c>
       <c r="Z8">
-        <v>-0.98</v>
+        <v>-1.16</v>
       </c>
       <c r="AA8">
-        <v>-0.8100000000000001</v>
+        <v>-0.88</v>
       </c>
       <c r="AB8">
-        <v>-0.17</v>
+        <v>-0.29</v>
       </c>
       <c r="AC8">
-        <v>29.46</v>
+        <v>13.44</v>
       </c>
       <c r="AD8">
-        <v>45.58</v>
+        <v>31.09</v>
       </c>
       <c r="AE8">
-        <v>6.52</v>
+        <v>6.8</v>
       </c>
       <c r="AF8">
-        <v>-62.9</v>
+        <v>-63.69</v>
       </c>
       <c r="AG8">
-        <v>234.23</v>
+        <v>234.15</v>
       </c>
       <c r="AH8">
-        <v>212.56</v>
+        <v>212.94</v>
       </c>
       <c r="AI8">
         <v>237.22</v>
@@ -1719,7 +1710,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>25.54</v>
+        <v>25.62</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1730,10 +1721,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>3588.8</v>
+        <v>3602.6</v>
       </c>
       <c r="D9">
-        <v>-0.14</v>
+        <v>0.38</v>
       </c>
       <c r="E9">
         <v>4497.5</v>
@@ -1742,46 +1733,46 @@
         <v>3308.9</v>
       </c>
       <c r="G9">
-        <v>-20.2</v>
+        <v>-19.9</v>
       </c>
       <c r="H9">
-        <v>8.460000000000001</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="I9">
-        <v>-0.5600000000000001</v>
+        <v>-0.43</v>
       </c>
       <c r="J9">
-        <v>-0.5</v>
+        <v>0.43</v>
       </c>
       <c r="K9">
-        <v>-2.42</v>
+        <v>-2.15</v>
       </c>
       <c r="L9">
-        <v>-10.21</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="M9">
-        <v>19.68</v>
+        <v>19.76</v>
       </c>
       <c r="N9">
         <v>34</v>
       </c>
       <c r="O9">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P9">
-        <v>3615.48</v>
+        <v>3612.36</v>
       </c>
       <c r="Q9">
-        <v>3601.71</v>
+        <v>3603.01</v>
       </c>
       <c r="R9">
-        <v>3736.87</v>
+        <v>3733.37</v>
       </c>
       <c r="S9">
-        <v>3710.85</v>
+        <v>3708.86</v>
       </c>
       <c r="T9">
-        <v>-3.29</v>
+        <v>-2.87</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1796,34 +1787,34 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>39.44</v>
+        <v>42.4</v>
       </c>
       <c r="Z9">
-        <v>-31.07</v>
+        <v>-29.5</v>
       </c>
       <c r="AA9">
-        <v>-39.67</v>
+        <v>-37.64</v>
       </c>
       <c r="AB9">
-        <v>8.609999999999999</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="AC9">
-        <v>43.11</v>
+        <v>25.01</v>
       </c>
       <c r="AD9">
-        <v>72.03</v>
+        <v>47.04</v>
       </c>
       <c r="AE9">
-        <v>59.75</v>
+        <v>59.69</v>
       </c>
       <c r="AF9">
-        <v>-39.86</v>
+        <v>-43.97</v>
       </c>
       <c r="AG9">
-        <v>3646.81</v>
+        <v>3646.53</v>
       </c>
       <c r="AH9">
-        <v>3556.61</v>
+        <v>3559.49</v>
       </c>
       <c r="AI9">
         <v>3764.06</v>
@@ -1832,7 +1823,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>15.54</v>
+        <v>14.85</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1843,10 +1834,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>1589.8</v>
+        <v>1592.1</v>
       </c>
       <c r="D10">
-        <v>-0.14</v>
+        <v>0.14</v>
       </c>
       <c r="E10">
         <v>1768.4</v>
@@ -1855,46 +1846,46 @@
         <v>1326.2</v>
       </c>
       <c r="G10">
-        <v>-10.1</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="H10">
-        <v>19.88</v>
+        <v>20.05</v>
       </c>
       <c r="I10">
-        <v>-2.17</v>
+        <v>-2.86</v>
       </c>
       <c r="J10">
-        <v>0.86</v>
+        <v>2.02</v>
       </c>
       <c r="K10">
-        <v>11.96</v>
+        <v>11.95</v>
       </c>
       <c r="L10">
-        <v>6.65</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="M10">
-        <v>5.69</v>
+        <v>5.71</v>
       </c>
       <c r="N10">
         <v>66</v>
       </c>
       <c r="O10">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="P10">
-        <v>1612.72</v>
+        <v>1603.34</v>
       </c>
       <c r="Q10">
-        <v>1623.82</v>
+        <v>1625.63</v>
       </c>
       <c r="R10">
-        <v>1524.7</v>
+        <v>1526.97</v>
       </c>
       <c r="S10">
-        <v>1505.46</v>
+        <v>1506.29</v>
       </c>
       <c r="T10">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="U10" t="s">
         <v>48</v>
@@ -1909,34 +1900,34 @@
         <v>3</v>
       </c>
       <c r="Y10">
-        <v>49.54</v>
+        <v>50.14</v>
       </c>
       <c r="Z10">
-        <v>22.3</v>
+        <v>18.76</v>
       </c>
       <c r="AA10">
-        <v>34.25</v>
+        <v>31.15</v>
       </c>
       <c r="AB10">
-        <v>-11.95</v>
+        <v>-12.39</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AD10">
-        <v>3.32</v>
+        <v>0.92</v>
       </c>
       <c r="AE10">
-        <v>38.5</v>
+        <v>37.28</v>
       </c>
       <c r="AF10">
-        <v>-38.96</v>
+        <v>-40.77</v>
       </c>
       <c r="AG10">
-        <v>1688.57</v>
+        <v>1684.08</v>
       </c>
       <c r="AH10">
-        <v>1559.06</v>
+        <v>1567.18</v>
       </c>
       <c r="AI10">
         <v>1527.05</v>
@@ -1945,7 +1936,7 @@
         <v>50</v>
       </c>
       <c r="AK10">
-        <v>30.15</v>
+        <v>31.47</v>
       </c>
     </row>
   </sheetData>
@@ -2086,7 +2077,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F80"/>
+  <dimension ref="A1:F77"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2126,7 +2117,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2144,217 +2135,214 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" s="4" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
+      <c r="E6" s="3" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>69</v>
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>-13.97</v>
+      </c>
+      <c r="D7" s="6">
+        <v>-14.54</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-0.57</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-13.53</v>
+        <v>6.66</v>
       </c>
       <c r="D8" s="6">
-        <v>-13.97</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-0.44</v>
+        <v>7.86</v>
+      </c>
+      <c r="E8" s="8">
+        <v>1.2</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>8.09</v>
+        <v>11.36</v>
       </c>
       <c r="D9" s="6">
-        <v>6.66</v>
+        <v>1.14</v>
       </c>
       <c r="E9" s="7">
-        <v>-1.43</v>
+        <v>-10.22</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>19.73</v>
+        <v>1.22</v>
       </c>
       <c r="D10" s="6">
-        <v>11.36</v>
+        <v>0.83</v>
       </c>
       <c r="E10" s="7">
-        <v>-8.369999999999999</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>2.93</v>
+        <v>3.86</v>
       </c>
       <c r="D11" s="6">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="E11" s="7">
-        <v>-1.71</v>
+        <v>-2.74</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>2.93</v>
+        <v>5.84</v>
       </c>
       <c r="D12" s="6">
-        <v>3.86</v>
+        <v>6.11</v>
       </c>
       <c r="E12" s="8">
-        <v>0.93</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>6.19</v>
+        <v>-3.72</v>
       </c>
       <c r="D13" s="6">
-        <v>5.84</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-0.35</v>
+        <v>4.42</v>
+      </c>
+      <c r="E13" s="8">
+        <v>8.140000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>-2.28</v>
+        <v>-0.5</v>
       </c>
       <c r="D14" s="6">
-        <v>-3.72</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-1.44</v>
+        <v>0.43</v>
+      </c>
+      <c r="E14" s="8">
+        <v>0.93</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="6">
-        <v>-2.23</v>
+        <v>0.86</v>
       </c>
       <c r="D15" s="6">
-        <v>-0.5</v>
+        <v>2.02</v>
       </c>
       <c r="E15" s="8">
-        <v>1.73</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>0.99</v>
+        <v>-1.23</v>
       </c>
       <c r="D16" s="6">
-        <v>0.86</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-0.13</v>
+        <v>-1.17</v>
+      </c>
+      <c r="E16" s="8">
+        <v>0.06</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>-0.8</v>
+        <v>0.33</v>
       </c>
       <c r="D17" s="6">
-        <v>-1.23</v>
+        <v>-0.1</v>
       </c>
       <c r="E17" s="7">
         <v>-0.43</v>
@@ -2362,138 +2350,138 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>-1.12</v>
+        <v>-1.58</v>
       </c>
       <c r="D18" s="6">
-        <v>0.33</v>
-      </c>
-      <c r="E18" s="8">
-        <v>1.45</v>
+        <v>-3.52</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-1.94</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>-3.16</v>
+        <v>-2.39</v>
       </c>
       <c r="D19" s="6">
-        <v>-1.58</v>
+        <v>-1.71</v>
       </c>
       <c r="E19" s="8">
-        <v>1.58</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>0.39</v>
+        <v>-0.17</v>
       </c>
       <c r="D20" s="6">
-        <v>-2.39</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-2.78</v>
+        <v>0.16</v>
+      </c>
+      <c r="E20" s="8">
+        <v>0.33</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="6">
-        <v>-1.17</v>
+        <v>0.65</v>
       </c>
       <c r="D21" s="6">
-        <v>-0.17</v>
-      </c>
-      <c r="E21" s="8">
-        <v>1</v>
+        <v>-0.23</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-0.88</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="6">
-        <v>4.35</v>
+        <v>-2.4</v>
       </c>
       <c r="D22" s="6">
-        <v>0.65</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-3.7</v>
+        <v>-1.26</v>
+      </c>
+      <c r="E22" s="8">
+        <v>1.14</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="6">
-        <v>-1.85</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="D23" s="6">
-        <v>-2.4</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-0.55</v>
+        <v>-0.43</v>
+      </c>
+      <c r="E23" s="8">
+        <v>0.13</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="6">
-        <v>-0.11</v>
+        <v>-2.17</v>
       </c>
       <c r="D24" s="6">
-        <v>-0.5600000000000001</v>
+        <v>-2.86</v>
       </c>
       <c r="E24" s="7">
-        <v>-0.45</v>
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C25" s="6">
-        <v>-3.1</v>
+        <v>4.88</v>
       </c>
       <c r="D25" s="6">
-        <v>-2.17</v>
-      </c>
-      <c r="E25" s="8">
-        <v>0.93</v>
+        <v>3.62</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-1.26</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2504,13 +2492,13 @@
         <v>11</v>
       </c>
       <c r="C26" s="6">
-        <v>5.72</v>
+        <v>4.05</v>
       </c>
       <c r="D26" s="6">
-        <v>4.05</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-1.67</v>
+        <v>4.88</v>
+      </c>
+      <c r="E26" s="8">
+        <v>0.83</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2521,13 +2509,13 @@
         <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>50.3</v>
+        <v>50.51</v>
       </c>
       <c r="D27" s="6">
-        <v>50.51</v>
-      </c>
-      <c r="E27" s="8">
-        <v>0.21</v>
+        <v>49.92</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-0.59</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2538,13 +2526,13 @@
         <v>11</v>
       </c>
       <c r="C28" s="6">
-        <v>12.55</v>
+        <v>9.17</v>
       </c>
       <c r="D28" s="6">
-        <v>9.17</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-3.38</v>
+        <v>10.65</v>
+      </c>
+      <c r="E28" s="8">
+        <v>1.48</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2555,13 +2543,13 @@
         <v>11</v>
       </c>
       <c r="C29" s="6">
-        <v>23.34</v>
+        <v>21.5</v>
       </c>
       <c r="D29" s="6">
-        <v>21.5</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-1.84</v>
+        <v>26.19</v>
+      </c>
+      <c r="E29" s="8">
+        <v>4.69</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2572,13 +2560,13 @@
         <v>11</v>
       </c>
       <c r="C30" s="6">
-        <v>-7.33</v>
+        <v>-9.07</v>
       </c>
       <c r="D30" s="6">
-        <v>-9.07</v>
+        <v>-9.470000000000001</v>
       </c>
       <c r="E30" s="7">
-        <v>-1.74</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2589,13 +2577,13 @@
         <v>11</v>
       </c>
       <c r="C31" s="6">
-        <v>-37.93</v>
+        <v>-38.74</v>
       </c>
       <c r="D31" s="6">
-        <v>-38.74</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-0.8100000000000001</v>
+        <v>-37.83</v>
+      </c>
+      <c r="E31" s="8">
+        <v>0.91</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2606,13 +2594,13 @@
         <v>11</v>
       </c>
       <c r="C32" s="6">
-        <v>-9.539999999999999</v>
+        <v>-10.21</v>
       </c>
       <c r="D32" s="6">
-        <v>-10.21</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-0.67</v>
+        <v>-9.970000000000001</v>
+      </c>
+      <c r="E32" s="8">
+        <v>0.24</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2623,13 +2611,13 @@
         <v>11</v>
       </c>
       <c r="C33" s="6">
-        <v>6.58</v>
+        <v>6.65</v>
       </c>
       <c r="D33" s="6">
-        <v>6.65</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="E33" s="8">
-        <v>0.07000000000000001</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2640,13 +2628,13 @@
         <v>10</v>
       </c>
       <c r="C34" s="6">
-        <v>-11.49</v>
+        <v>-12.13</v>
       </c>
       <c r="D34" s="6">
-        <v>-12.13</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-0.64</v>
+        <v>-10.5</v>
+      </c>
+      <c r="E34" s="8">
+        <v>1.63</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2657,13 +2645,13 @@
         <v>10</v>
       </c>
       <c r="C35" s="6">
-        <v>9.59</v>
+        <v>10.2</v>
       </c>
       <c r="D35" s="6">
-        <v>10.2</v>
+        <v>11.15</v>
       </c>
       <c r="E35" s="8">
-        <v>0.61</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2674,13 +2662,13 @@
         <v>10</v>
       </c>
       <c r="C36" s="6">
-        <v>24.98</v>
+        <v>29.03</v>
       </c>
       <c r="D36" s="6">
-        <v>29.03</v>
-      </c>
-      <c r="E36" s="8">
-        <v>4.05</v>
+        <v>27.67</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-1.36</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2691,13 +2679,13 @@
         <v>10</v>
       </c>
       <c r="C37" s="6">
-        <v>17.58</v>
+        <v>12.02</v>
       </c>
       <c r="D37" s="6">
-        <v>12.02</v>
+        <v>10.62</v>
       </c>
       <c r="E37" s="7">
-        <v>-5.56</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2708,387 +2696,387 @@
         <v>10</v>
       </c>
       <c r="C38" s="6">
-        <v>14.12</v>
+        <v>14.16</v>
       </c>
       <c r="D38" s="6">
-        <v>14.16</v>
+        <v>14.78</v>
       </c>
       <c r="E38" s="8">
-        <v>0.04</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C39" s="6">
-        <v>-3.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D39" s="6">
-        <v>-3.9</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-0.8100000000000001</v>
+        <v>1</v>
+      </c>
+      <c r="E39" s="8">
+        <v>0.93</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C40" s="6">
-        <v>0.3</v>
+        <v>-2.42</v>
       </c>
       <c r="D40" s="6">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-0.23</v>
+        <v>-2.15</v>
+      </c>
+      <c r="E40" s="8">
+        <v>0.27</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C41" s="6">
-        <v>-2.6</v>
+        <v>11.96</v>
       </c>
       <c r="D41" s="6">
-        <v>-2.42</v>
-      </c>
-      <c r="E41" s="8">
-        <v>0.18</v>
+        <v>11.95</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-0.01</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C42" s="6">
-        <v>10.63</v>
+        <v>-17.04</v>
       </c>
       <c r="D42" s="6">
-        <v>11.96</v>
-      </c>
-      <c r="E42" s="8">
-        <v>1.33</v>
+        <v>-17.63</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-0.59</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C43" s="6">
-        <v>-16.42</v>
+        <v>-10.19</v>
       </c>
       <c r="D43" s="6">
-        <v>-17.04</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-0.62</v>
+        <v>-9.93</v>
+      </c>
+      <c r="E43" s="8">
+        <v>0.26</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C44" s="6">
-        <v>-10.02</v>
+        <v>-5.51</v>
       </c>
       <c r="D44" s="6">
-        <v>-10.19</v>
+        <v>-7.24</v>
       </c>
       <c r="E44" s="7">
-        <v>-0.17</v>
+        <v>-1.73</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C45" s="6">
-        <v>-6.33</v>
+        <v>-11.38</v>
       </c>
       <c r="D45" s="6">
-        <v>-5.51</v>
+        <v>-10.55</v>
       </c>
       <c r="E45" s="8">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C46" s="6">
-        <v>-8.9</v>
+        <v>-8.23</v>
       </c>
       <c r="D46" s="6">
-        <v>-11.38</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-2.48</v>
+        <v>-8.140000000000001</v>
+      </c>
+      <c r="E46" s="8">
+        <v>0.09</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C47" s="6">
-        <v>-8.619999999999999</v>
+        <v>-9.92</v>
       </c>
       <c r="D47" s="6">
-        <v>-8.23</v>
-      </c>
-      <c r="E47" s="8">
-        <v>0.39</v>
+        <v>-10.4</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-0.48</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C48" s="6">
-        <v>-8.890000000000001</v>
+        <v>-39.62</v>
       </c>
       <c r="D48" s="6">
-        <v>-9.92</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-1.03</v>
+        <v>-39.19</v>
+      </c>
+      <c r="E48" s="8">
+        <v>0.43</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C49" s="6">
-        <v>-39.09</v>
+        <v>-20.2</v>
       </c>
       <c r="D49" s="6">
-        <v>-39.62</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-0.53</v>
+        <v>-19.9</v>
+      </c>
+      <c r="E49" s="8">
+        <v>0.3</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C50" s="6">
-        <v>-20.09</v>
+        <v>-10.1</v>
       </c>
       <c r="D50" s="6">
-        <v>-20.2</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-0.11</v>
+        <v>-9.970000000000001</v>
+      </c>
+      <c r="E50" s="8">
+        <v>0.13</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C51" s="6">
-        <v>-9.98</v>
+        <v>406.65</v>
       </c>
       <c r="D51" s="6">
-        <v>-10.1</v>
+        <v>403.8</v>
       </c>
       <c r="E51" s="7">
-        <v>-0.12</v>
+        <v>-2.85</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C52" s="6">
-        <v>409.7</v>
+        <v>3415</v>
       </c>
       <c r="D52" s="6">
-        <v>406.65</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-3.05</v>
+        <v>3424.8</v>
+      </c>
+      <c r="E52" s="8">
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C53" s="6">
-        <v>3421.5</v>
+        <v>389.6</v>
       </c>
       <c r="D53" s="6">
-        <v>3415</v>
+        <v>382.45</v>
       </c>
       <c r="E53" s="7">
-        <v>-6.5</v>
+        <v>-7.15</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C54" s="6">
-        <v>386.2</v>
+        <v>373.7</v>
       </c>
       <c r="D54" s="6">
-        <v>389.6</v>
+        <v>377.2</v>
       </c>
       <c r="E54" s="8">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C55" s="6">
-        <v>384.15</v>
+        <v>406.25</v>
       </c>
       <c r="D55" s="6">
-        <v>373.7</v>
-      </c>
-      <c r="E55" s="7">
-        <v>-10.45</v>
+        <v>406.65</v>
+      </c>
+      <c r="E55" s="8">
+        <v>0.4</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C56" s="6">
-        <v>404.55</v>
+        <v>613.9</v>
       </c>
       <c r="D56" s="6">
-        <v>406.25</v>
-      </c>
-      <c r="E56" s="8">
-        <v>1.7</v>
+        <v>610.6</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-3.3</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C57" s="6">
-        <v>620.9</v>
+        <v>219.48</v>
       </c>
       <c r="D57" s="6">
-        <v>613.9</v>
-      </c>
-      <c r="E57" s="7">
-        <v>-7</v>
+        <v>221.05</v>
+      </c>
+      <c r="E57" s="8">
+        <v>1.57</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C58" s="6">
-        <v>221.39</v>
+        <v>3588.8</v>
       </c>
       <c r="D58" s="6">
-        <v>219.48</v>
-      </c>
-      <c r="E58" s="7">
-        <v>-1.91</v>
+        <v>3602.6</v>
+      </c>
+      <c r="E58" s="8">
+        <v>13.8</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C59" s="6">
-        <v>3594</v>
+        <v>1589.8</v>
       </c>
       <c r="D59" s="6">
-        <v>3588.8</v>
-      </c>
-      <c r="E59" s="7">
-        <v>-5.2</v>
+        <v>1592.1</v>
+      </c>
+      <c r="E59" s="8">
+        <v>2.3</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C60" s="6">
-        <v>1592</v>
+        <v>35.69</v>
       </c>
       <c r="D60" s="6">
-        <v>1589.8</v>
+        <v>33.99</v>
       </c>
       <c r="E60" s="7">
-        <v>-2.2</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -3096,345 +3084,294 @@
         <v>38</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C61" s="6">
-        <v>66</v>
+        <v>57.55</v>
       </c>
       <c r="D61" s="6">
-        <v>55</v>
-      </c>
-      <c r="E61" s="7">
-        <v>-11</v>
+        <v>58.36</v>
+      </c>
+      <c r="E61" s="8">
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C62" s="6">
-        <v>55</v>
+        <v>57.12</v>
       </c>
       <c r="D62" s="6">
-        <v>66</v>
-      </c>
-      <c r="E62" s="8">
-        <v>11</v>
+        <v>52.93</v>
+      </c>
+      <c r="E62" s="7">
+        <v>-4.19</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C63" s="6">
-        <v>37.54</v>
+        <v>43.63</v>
       </c>
       <c r="D63" s="6">
-        <v>35.69</v>
-      </c>
-      <c r="E63" s="7">
-        <v>-1.85</v>
+        <v>47.39</v>
+      </c>
+      <c r="E63" s="8">
+        <v>3.76</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C64" s="6">
-        <v>58.25</v>
+        <v>53.39</v>
       </c>
       <c r="D64" s="6">
-        <v>57.55</v>
-      </c>
-      <c r="E64" s="7">
-        <v>-0.7</v>
+        <v>53.7</v>
+      </c>
+      <c r="E64" s="8">
+        <v>0.31</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C65" s="6">
-        <v>55.57</v>
+        <v>58.76</v>
       </c>
       <c r="D65" s="6">
-        <v>57.12</v>
-      </c>
-      <c r="E65" s="8">
-        <v>1.55</v>
+        <v>56.65</v>
+      </c>
+      <c r="E65" s="7">
+        <v>-2.11</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C66" s="6">
-        <v>54.43</v>
+        <v>42.28</v>
       </c>
       <c r="D66" s="6">
-        <v>43.63</v>
-      </c>
-      <c r="E66" s="7">
-        <v>-10.8</v>
+        <v>44.57</v>
+      </c>
+      <c r="E66" s="8">
+        <v>2.29</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C67" s="6">
-        <v>52.09</v>
+        <v>39.44</v>
       </c>
       <c r="D67" s="6">
-        <v>53.39</v>
+        <v>42.4</v>
       </c>
       <c r="E67" s="8">
-        <v>1.3</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C68" s="6">
-        <v>63.39</v>
+        <v>49.54</v>
       </c>
       <c r="D68" s="6">
-        <v>58.76</v>
-      </c>
-      <c r="E68" s="7">
-        <v>-4.63</v>
+        <v>50.14</v>
+      </c>
+      <c r="E68" s="8">
+        <v>0.6</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C69" s="6">
-        <v>44.35</v>
+        <v>-81.08</v>
       </c>
       <c r="D69" s="6">
-        <v>42.28</v>
-      </c>
-      <c r="E69" s="7">
-        <v>-2.07</v>
+        <v>-57.92</v>
+      </c>
+      <c r="E69" s="8">
+        <v>23.16</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C70" s="6">
-        <v>40.16</v>
+        <v>-35.76</v>
       </c>
       <c r="D70" s="6">
-        <v>39.44</v>
+        <v>-48.36</v>
       </c>
       <c r="E70" s="7">
-        <v>-0.72</v>
+        <v>-12.6</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C71" s="6">
-        <v>50.08</v>
+        <v>-67.16</v>
       </c>
       <c r="D71" s="6">
-        <v>49.54</v>
-      </c>
-      <c r="E71" s="7">
-        <v>-0.54</v>
+        <v>-65.81</v>
+      </c>
+      <c r="E71" s="8">
+        <v>1.35</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C72" s="6">
-        <v>-68.75</v>
+        <v>54.22</v>
       </c>
       <c r="D72" s="6">
-        <v>-81.08</v>
+        <v>-84.66</v>
       </c>
       <c r="E72" s="7">
-        <v>-12.33</v>
+        <v>-138.88</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C73" s="6">
-        <v>-45.11</v>
+        <v>-57.13</v>
       </c>
       <c r="D73" s="6">
-        <v>-35.76</v>
-      </c>
-      <c r="E73" s="8">
-        <v>9.35</v>
+        <v>-73.65000000000001</v>
+      </c>
+      <c r="E73" s="7">
+        <v>-16.52</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C74" s="6">
-        <v>-79.59</v>
+        <v>37.53</v>
       </c>
       <c r="D74" s="6">
-        <v>-67.16</v>
+        <v>66.55</v>
       </c>
       <c r="E74" s="8">
-        <v>12.43</v>
+        <v>29.02</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C75" s="6">
-        <v>-74.13</v>
+        <v>-62.9</v>
       </c>
       <c r="D75" s="6">
-        <v>54.22</v>
-      </c>
-      <c r="E75" s="8">
-        <v>128.35</v>
+        <v>-63.69</v>
+      </c>
+      <c r="E75" s="7">
+        <v>-0.79</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C76" s="6">
-        <v>-81.53</v>
+        <v>-39.86</v>
       </c>
       <c r="D76" s="6">
-        <v>-57.13</v>
-      </c>
-      <c r="E76" s="8">
-        <v>24.4</v>
+        <v>-43.97</v>
+      </c>
+      <c r="E76" s="7">
+        <v>-4.11</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C77" s="6">
-        <v>21.9</v>
+        <v>-38.96</v>
       </c>
       <c r="D77" s="6">
-        <v>37.53</v>
-      </c>
-      <c r="E77" s="8">
-        <v>15.63</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="6">
-        <v>-70.52</v>
-      </c>
-      <c r="D78" s="6">
-        <v>-62.9</v>
-      </c>
-      <c r="E78" s="8">
-        <v>7.62</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="6">
-        <v>-66.06999999999999</v>
-      </c>
-      <c r="D79" s="6">
-        <v>-39.86</v>
-      </c>
-      <c r="E79" s="8">
-        <v>26.21</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="6">
-        <v>-34.22</v>
-      </c>
-      <c r="D80" s="6">
-        <v>-38.96</v>
-      </c>
-      <c r="E80" s="7">
-        <v>-4.74</v>
+        <v>-40.77</v>
+      </c>
+      <c r="E77" s="7">
+        <v>-1.81</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3458,28 +3395,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="F1" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>74</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3493,16 +3430,16 @@
         <v>9</v>
       </c>
       <c r="D2" s="11">
-        <v>48.6</v>
+        <v>48.9</v>
       </c>
       <c r="E2" s="11">
         <v>70</v>
       </c>
       <c r="F2" s="11">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="G2" s="11">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="H2" s="11">
         <v>55.4</v>
@@ -3639,31 +3576,31 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="14">
-        <v>0.3516</v>
+        <v>0.3521</v>
       </c>
       <c r="B2" s="14">
-        <v>0.3185</v>
+        <v>0.3169</v>
       </c>
       <c r="C2" s="14">
-        <v>0.242</v>
+        <v>0.2373</v>
       </c>
       <c r="D2" s="14">
-        <v>0.1968</v>
+        <v>0.1976</v>
       </c>
       <c r="E2" s="14">
-        <v>0.135</v>
+        <v>0.1333</v>
       </c>
       <c r="F2" s="14">
-        <v>0.08810000000000001</v>
+        <v>0.0901</v>
       </c>
       <c r="G2" s="14">
-        <v>0.05690000000000001</v>
+        <v>0.0571</v>
       </c>
       <c r="H2" s="14">
-        <v>0.0186</v>
+        <v>0.02</v>
       </c>
       <c r="I2" s="14">
-        <v>-0.1042</v>
+        <v>-0.104</v>
       </c>
     </row>
   </sheetData>

--- a/MAHINDRA_GROUP_Technical_Metrics.xlsx
+++ b/MAHINDRA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="79">
   <si>
     <t>Symbol</t>
   </si>
@@ -196,16 +196,28 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>49.5 → 50.1</t>
+    <t>48.8 → 50.5</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>49.5</t>
+    <t>48.8</t>
+  </si>
+  <si>
+    <t>50.5</t>
+  </si>
+  <si>
+    <t>50.1 → 49.4</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
   </si>
   <si>
     <t>50.1</t>
+  </si>
+  <si>
+    <t>49.4</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -407,7 +419,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -415,10 +427,11 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -930,10 +943,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>403.8</v>
+        <v>399.35</v>
       </c>
       <c r="D2">
-        <v>-0.7</v>
+        <v>-0.42</v>
       </c>
       <c r="E2">
         <v>490.2</v>
@@ -942,46 +955,46 @@
         <v>379.2</v>
       </c>
       <c r="G2">
-        <v>-17.63</v>
+        <v>-18.53</v>
       </c>
       <c r="H2">
-        <v>6.49</v>
+        <v>5.31</v>
       </c>
       <c r="I2">
-        <v>-1.17</v>
+        <v>-2.06</v>
       </c>
       <c r="J2">
-        <v>-14.54</v>
+        <v>-3.48</v>
       </c>
       <c r="K2">
-        <v>-10.5</v>
+        <v>-12.65</v>
       </c>
       <c r="L2">
-        <v>3.62</v>
+        <v>0.11</v>
       </c>
       <c r="M2">
-        <v>13.33</v>
+        <v>13.97</v>
       </c>
       <c r="N2">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="O2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P2">
-        <v>407.13</v>
+        <v>404.11</v>
       </c>
       <c r="Q2">
-        <v>410.76</v>
+        <v>409.42</v>
       </c>
       <c r="R2">
-        <v>442.1</v>
+        <v>440.37</v>
       </c>
       <c r="S2">
-        <v>437.96</v>
+        <v>437.68</v>
       </c>
       <c r="T2">
-        <v>-7.8</v>
+        <v>-8.76</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -996,43 +1009,43 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>33.99</v>
+        <v>31.42</v>
       </c>
       <c r="Z2">
-        <v>-10.45</v>
+        <v>-10.43</v>
       </c>
       <c r="AA2">
-        <v>-11.35</v>
+        <v>-11.02</v>
       </c>
       <c r="AB2">
-        <v>0.9</v>
+        <v>0.59</v>
       </c>
       <c r="AC2">
-        <v>53.52</v>
+        <v>0</v>
       </c>
       <c r="AD2">
-        <v>69.03</v>
+        <v>25.44</v>
       </c>
       <c r="AE2">
-        <v>10.03</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="AF2">
-        <v>-57.92</v>
+        <v>-47.59</v>
       </c>
       <c r="AG2">
-        <v>417.85</v>
+        <v>418.73</v>
       </c>
       <c r="AH2">
-        <v>403.68</v>
+        <v>400.12</v>
       </c>
       <c r="AI2">
-        <v>436.69</v>
+        <v>428.63</v>
       </c>
       <c r="AJ2" t="s">
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>32.4</v>
+        <v>37.2</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1043,10 +1056,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>3424.8</v>
+        <v>3414.1</v>
       </c>
       <c r="D3">
-        <v>0.29</v>
+        <v>0.06</v>
       </c>
       <c r="E3">
         <v>3802.4</v>
@@ -1055,46 +1068,46 @@
         <v>2931.1</v>
       </c>
       <c r="G3">
-        <v>-9.93</v>
+        <v>-10.21</v>
       </c>
       <c r="H3">
-        <v>16.84</v>
+        <v>16.48</v>
       </c>
       <c r="I3">
-        <v>-0.1</v>
+        <v>0.7</v>
       </c>
       <c r="J3">
-        <v>7.86</v>
+        <v>7.99</v>
       </c>
       <c r="K3">
-        <v>11.15</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="L3">
-        <v>4.88</v>
+        <v>1.79</v>
       </c>
       <c r="M3">
-        <v>35.21</v>
+        <v>35.39</v>
       </c>
       <c r="N3">
         <v>55</v>
       </c>
       <c r="O3">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="P3">
-        <v>3416</v>
+        <v>3417.52</v>
       </c>
       <c r="Q3">
-        <v>3384.46</v>
+        <v>3405.77</v>
       </c>
       <c r="R3">
-        <v>3227.77</v>
+        <v>3243.42</v>
       </c>
       <c r="S3">
-        <v>3353.98</v>
+        <v>3352.46</v>
       </c>
       <c r="T3">
-        <v>2.11</v>
+        <v>1.84</v>
       </c>
       <c r="U3" t="s">
         <v>48</v>
@@ -1109,34 +1122,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>58.36</v>
+        <v>57.05</v>
       </c>
       <c r="Z3">
-        <v>60.92</v>
+        <v>52.75</v>
       </c>
       <c r="AA3">
-        <v>70.73999999999999</v>
+        <v>64.88</v>
       </c>
       <c r="AB3">
-        <v>-9.82</v>
+        <v>-12.13</v>
       </c>
       <c r="AC3">
-        <v>15.9</v>
+        <v>11.28</v>
       </c>
       <c r="AD3">
-        <v>14.52</v>
+        <v>13.23</v>
       </c>
       <c r="AE3">
-        <v>68.53</v>
+        <v>65.05</v>
       </c>
       <c r="AF3">
-        <v>-48.36</v>
+        <v>-51.31</v>
       </c>
       <c r="AG3">
-        <v>3576.8</v>
+        <v>3548.87</v>
       </c>
       <c r="AH3">
-        <v>3192.11</v>
+        <v>3262.67</v>
       </c>
       <c r="AI3">
         <v>3274.47</v>
@@ -1145,7 +1158,7 @@
         <v>50</v>
       </c>
       <c r="AK3">
-        <v>30.84</v>
+        <v>26.88</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1156,10 +1169,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>382.45</v>
+        <v>378.7</v>
       </c>
       <c r="D4">
-        <v>-1.84</v>
+        <v>-0.76</v>
       </c>
       <c r="E4">
         <v>412.3</v>
@@ -1168,46 +1181,46 @@
         <v>253.95</v>
       </c>
       <c r="G4">
-        <v>-7.24</v>
+        <v>-8.15</v>
       </c>
       <c r="H4">
-        <v>50.6</v>
+        <v>49.12</v>
       </c>
       <c r="I4">
-        <v>-3.52</v>
+        <v>-2.62</v>
       </c>
       <c r="J4">
-        <v>1.14</v>
+        <v>6.23</v>
       </c>
       <c r="K4">
-        <v>27.67</v>
+        <v>24.12</v>
       </c>
       <c r="L4">
-        <v>49.92</v>
+        <v>43.99</v>
       </c>
       <c r="M4">
-        <v>23.73</v>
+        <v>22.91</v>
       </c>
       <c r="N4">
         <v>99</v>
       </c>
       <c r="O4">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P4">
-        <v>387.45</v>
+        <v>383.71</v>
       </c>
       <c r="Q4">
-        <v>390.27</v>
+        <v>392.31</v>
       </c>
       <c r="R4">
-        <v>348.03</v>
+        <v>351.9</v>
       </c>
       <c r="S4">
-        <v>340.75</v>
+        <v>341.37</v>
       </c>
       <c r="T4">
-        <v>12.24</v>
+        <v>10.94</v>
       </c>
       <c r="U4" t="s">
         <v>48</v>
@@ -1222,34 +1235,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>52.93</v>
+        <v>50.71</v>
       </c>
       <c r="Z4">
-        <v>11.26</v>
+        <v>8.33</v>
       </c>
       <c r="AA4">
-        <v>15.5</v>
+        <v>13.15</v>
       </c>
       <c r="AB4">
-        <v>-4.24</v>
+        <v>-4.83</v>
       </c>
       <c r="AC4">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="AD4">
         <v>1.99</v>
       </c>
       <c r="AE4">
-        <v>14.68</v>
+        <v>13.61</v>
       </c>
       <c r="AF4">
-        <v>-65.81</v>
+        <v>-54.04</v>
       </c>
       <c r="AG4">
-        <v>417.84</v>
+        <v>412.05</v>
       </c>
       <c r="AH4">
-        <v>362.7</v>
+        <v>372.57</v>
       </c>
       <c r="AI4">
         <v>357.72</v>
@@ -1258,7 +1271,7 @@
         <v>50</v>
       </c>
       <c r="AK4">
-        <v>29.6</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1269,10 +1282,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>377.2</v>
+        <v>379.15</v>
       </c>
       <c r="D5">
-        <v>0.9399999999999999</v>
+        <v>-0.17</v>
       </c>
       <c r="E5">
         <v>421.7</v>
@@ -1281,46 +1294,46 @@
         <v>294.25</v>
       </c>
       <c r="G5">
-        <v>-10.55</v>
+        <v>-10.09</v>
       </c>
       <c r="H5">
-        <v>28.19</v>
+        <v>28.85</v>
       </c>
       <c r="I5">
-        <v>-1.71</v>
+        <v>-1.94</v>
       </c>
       <c r="J5">
-        <v>0.83</v>
+        <v>1.2</v>
       </c>
       <c r="K5">
-        <v>10.62</v>
+        <v>11.09</v>
       </c>
       <c r="L5">
-        <v>10.65</v>
+        <v>7.33</v>
       </c>
       <c r="M5">
-        <v>9.01</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="N5">
         <v>77</v>
       </c>
       <c r="O5">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="P5">
-        <v>381.32</v>
+        <v>378.8</v>
       </c>
       <c r="Q5">
-        <v>384.74</v>
+        <v>384.94</v>
       </c>
       <c r="R5">
-        <v>371.5</v>
+        <v>373.73</v>
       </c>
       <c r="S5">
-        <v>364.87</v>
+        <v>364.59</v>
       </c>
       <c r="T5">
-        <v>3.38</v>
+        <v>3.99</v>
       </c>
       <c r="U5" t="s">
         <v>48</v>
@@ -1335,34 +1348,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>47.39</v>
+        <v>49.39</v>
       </c>
       <c r="Z5">
-        <v>2.19</v>
+        <v>1.48</v>
       </c>
       <c r="AA5">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="AB5">
-        <v>-2.21</v>
+        <v>-1.92</v>
       </c>
       <c r="AC5">
-        <v>5.51</v>
+        <v>25.52</v>
       </c>
       <c r="AD5">
-        <v>8.44</v>
+        <v>14.43</v>
       </c>
       <c r="AE5">
-        <v>10.82</v>
+        <v>10.76</v>
       </c>
       <c r="AF5">
-        <v>-84.66</v>
+        <v>-46.89</v>
       </c>
       <c r="AG5">
-        <v>397.43</v>
+        <v>397.06</v>
       </c>
       <c r="AH5">
-        <v>372.06</v>
+        <v>372.83</v>
       </c>
       <c r="AI5">
         <v>364.94</v>
@@ -1371,7 +1384,7 @@
         <v>50</v>
       </c>
       <c r="AK5">
-        <v>28.42</v>
+        <v>28.05</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1382,10 +1395,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>406.65</v>
+        <v>403.1</v>
       </c>
       <c r="D6">
-        <v>0.1</v>
+        <v>0.49</v>
       </c>
       <c r="E6">
         <v>442.7</v>
@@ -1394,25 +1407,25 @@
         <v>279.55</v>
       </c>
       <c r="G6">
-        <v>-8.140000000000001</v>
+        <v>-8.949999999999999</v>
       </c>
       <c r="H6">
-        <v>45.47</v>
+        <v>44.2</v>
       </c>
       <c r="I6">
-        <v>0.16</v>
+        <v>-0.59</v>
       </c>
       <c r="J6">
-        <v>1.12</v>
+        <v>-3.18</v>
       </c>
       <c r="K6">
-        <v>14.78</v>
+        <v>13.93</v>
       </c>
       <c r="L6">
-        <v>26.19</v>
+        <v>22.86</v>
       </c>
       <c r="M6">
-        <v>-10.4</v>
+        <v>-11.13</v>
       </c>
       <c r="N6">
         <v>88</v>
@@ -1421,19 +1434,19 @@
         <v>75</v>
       </c>
       <c r="P6">
-        <v>405.69</v>
+        <v>404.34</v>
       </c>
       <c r="Q6">
-        <v>409.85</v>
+        <v>408.29</v>
       </c>
       <c r="R6">
-        <v>389.61</v>
+        <v>392.3</v>
       </c>
       <c r="S6">
-        <v>364.71</v>
+        <v>365.31</v>
       </c>
       <c r="T6">
-        <v>11.5</v>
+        <v>10.34</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1448,34 +1461,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>53.7</v>
+        <v>50.52</v>
       </c>
       <c r="Z6">
-        <v>3.8</v>
+        <v>2.62</v>
       </c>
       <c r="AA6">
-        <v>5.69</v>
+        <v>4.66</v>
       </c>
       <c r="AB6">
-        <v>-1.89</v>
+        <v>-2.04</v>
       </c>
       <c r="AC6">
-        <v>7.83</v>
+        <v>9.73</v>
       </c>
       <c r="AD6">
-        <v>5.32</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="AE6">
-        <v>12.07</v>
+        <v>11.72</v>
       </c>
       <c r="AF6">
-        <v>-73.65000000000001</v>
+        <v>-69.33</v>
       </c>
       <c r="AG6">
-        <v>420.53</v>
+        <v>418.41</v>
       </c>
       <c r="AH6">
-        <v>399.17</v>
+        <v>398.17</v>
       </c>
       <c r="AI6">
         <v>372.35</v>
@@ -1484,7 +1497,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>21.38</v>
+        <v>19.23</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1495,10 +1508,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>610.6</v>
+        <v>634.75</v>
       </c>
       <c r="D7">
-        <v>-0.54</v>
+        <v>0.09</v>
       </c>
       <c r="E7">
         <v>681.5</v>
@@ -1507,46 +1520,46 @@
         <v>506.45</v>
       </c>
       <c r="G7">
-        <v>-10.4</v>
+        <v>-6.86</v>
       </c>
       <c r="H7">
-        <v>20.56</v>
+        <v>25.33</v>
       </c>
       <c r="I7">
-        <v>-0.23</v>
+        <v>2.05</v>
       </c>
       <c r="J7">
-        <v>6.11</v>
+        <v>11.06</v>
       </c>
       <c r="K7">
-        <v>-3.9</v>
+        <v>0.66</v>
       </c>
       <c r="L7">
-        <v>-9.470000000000001</v>
+        <v>-6.26</v>
       </c>
       <c r="M7">
-        <v>31.69</v>
+        <v>33.34</v>
       </c>
       <c r="N7">
         <v>45</v>
       </c>
       <c r="O7">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="P7">
-        <v>615.97</v>
+        <v>622.86</v>
       </c>
       <c r="Q7">
-        <v>592.79</v>
+        <v>598.8200000000001</v>
       </c>
       <c r="R7">
-        <v>600.2</v>
+        <v>601.35</v>
       </c>
       <c r="S7">
-        <v>582.28</v>
+        <v>582.85</v>
       </c>
       <c r="T7">
-        <v>4.86</v>
+        <v>8.9</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1561,43 +1574,43 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>56.65</v>
+        <v>66.2</v>
       </c>
       <c r="Z7">
-        <v>6.58</v>
+        <v>9.69</v>
       </c>
       <c r="AA7">
-        <v>2.73</v>
+        <v>5.02</v>
       </c>
       <c r="AB7">
-        <v>3.86</v>
+        <v>4.67</v>
       </c>
       <c r="AC7">
-        <v>81.04000000000001</v>
+        <v>88.55</v>
       </c>
       <c r="AD7">
-        <v>90.76000000000001</v>
+        <v>83.84</v>
       </c>
       <c r="AE7">
-        <v>14.87</v>
+        <v>16.94</v>
       </c>
       <c r="AF7">
-        <v>66.55</v>
+        <v>19.52</v>
       </c>
       <c r="AG7">
-        <v>630.54</v>
+        <v>641.88</v>
       </c>
       <c r="AH7">
-        <v>555.05</v>
+        <v>555.76</v>
       </c>
       <c r="AI7">
-        <v>575.79</v>
+        <v>588.5599999999999</v>
       </c>
       <c r="AJ7" t="s">
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>48.01</v>
+        <v>53.92</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1611,7 +1624,7 @@
         <v>221.05</v>
       </c>
       <c r="D8">
-        <v>0.72</v>
+        <v>-0.33</v>
       </c>
       <c r="E8">
         <v>363.5</v>
@@ -1626,19 +1639,19 @@
         <v>5.06</v>
       </c>
       <c r="I8">
-        <v>-1.26</v>
+        <v>-2.46</v>
       </c>
       <c r="J8">
-        <v>4.42</v>
+        <v>1.01</v>
       </c>
       <c r="K8">
-        <v>1</v>
+        <v>0.14</v>
       </c>
       <c r="L8">
-        <v>-37.83</v>
+        <v>-37.54</v>
       </c>
       <c r="M8">
-        <v>2</v>
+        <v>1.22</v>
       </c>
       <c r="N8">
         <v>12</v>
@@ -1647,19 +1660,19 @@
         <v>20</v>
       </c>
       <c r="P8">
-        <v>223.03</v>
+        <v>220.95</v>
       </c>
       <c r="Q8">
-        <v>223.54</v>
+        <v>223.55</v>
       </c>
       <c r="R8">
-        <v>228.74</v>
+        <v>228.27</v>
       </c>
       <c r="S8">
-        <v>266.13</v>
+        <v>265.03</v>
       </c>
       <c r="T8">
-        <v>-16.94</v>
+        <v>-16.6</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1674,34 +1687,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>44.57</v>
+        <v>44.71</v>
       </c>
       <c r="Z8">
-        <v>-1.16</v>
+        <v>-1.34</v>
       </c>
       <c r="AA8">
-        <v>-0.88</v>
+        <v>-1.03</v>
       </c>
       <c r="AB8">
-        <v>-0.29</v>
+        <v>-0.31</v>
       </c>
       <c r="AC8">
-        <v>13.44</v>
+        <v>17.31</v>
       </c>
       <c r="AD8">
-        <v>31.09</v>
+        <v>14.29</v>
       </c>
       <c r="AE8">
-        <v>6.8</v>
+        <v>6.55</v>
       </c>
       <c r="AF8">
-        <v>-63.69</v>
+        <v>-44.95</v>
       </c>
       <c r="AG8">
-        <v>234.15</v>
+        <v>234.03</v>
       </c>
       <c r="AH8">
-        <v>212.94</v>
+        <v>213.07</v>
       </c>
       <c r="AI8">
         <v>237.22</v>
@@ -1710,7 +1723,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>25.62</v>
+        <v>22.72</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1721,10 +1734,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>3602.6</v>
+        <v>3558.9</v>
       </c>
       <c r="D9">
-        <v>0.38</v>
+        <v>-0.31</v>
       </c>
       <c r="E9">
         <v>4497.5</v>
@@ -1733,46 +1746,46 @@
         <v>3308.9</v>
       </c>
       <c r="G9">
-        <v>-19.9</v>
+        <v>-20.87</v>
       </c>
       <c r="H9">
-        <v>8.880000000000001</v>
+        <v>7.56</v>
       </c>
       <c r="I9">
-        <v>-0.43</v>
+        <v>-2.18</v>
       </c>
       <c r="J9">
-        <v>0.43</v>
+        <v>-0.28</v>
       </c>
       <c r="K9">
-        <v>-2.15</v>
+        <v>-5.42</v>
       </c>
       <c r="L9">
-        <v>-9.970000000000001</v>
+        <v>-12.24</v>
       </c>
       <c r="M9">
-        <v>19.76</v>
+        <v>19.93</v>
       </c>
       <c r="N9">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="O9">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="P9">
-        <v>3612.36</v>
+        <v>3582.82</v>
       </c>
       <c r="Q9">
-        <v>3603.01</v>
+        <v>3600.72</v>
       </c>
       <c r="R9">
-        <v>3733.37</v>
+        <v>3728.14</v>
       </c>
       <c r="S9">
-        <v>3708.86</v>
+        <v>3704.87</v>
       </c>
       <c r="T9">
-        <v>-2.87</v>
+        <v>-3.94</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1787,43 +1800,43 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>42.4</v>
+        <v>36.23</v>
       </c>
       <c r="Z9">
-        <v>-29.5</v>
+        <v>-31.89</v>
       </c>
       <c r="AA9">
-        <v>-37.64</v>
+        <v>-35.35</v>
       </c>
       <c r="AB9">
-        <v>8.140000000000001</v>
+        <v>3.46</v>
       </c>
       <c r="AC9">
-        <v>25.01</v>
+        <v>15.23</v>
       </c>
       <c r="AD9">
-        <v>47.04</v>
+        <v>19.64</v>
       </c>
       <c r="AE9">
-        <v>59.69</v>
+        <v>55.75</v>
       </c>
       <c r="AF9">
-        <v>-43.97</v>
+        <v>-26.98</v>
       </c>
       <c r="AG9">
-        <v>3646.53</v>
+        <v>3648.36</v>
       </c>
       <c r="AH9">
-        <v>3559.49</v>
+        <v>3553.09</v>
       </c>
       <c r="AI9">
-        <v>3764.06</v>
+        <v>3727.81</v>
       </c>
       <c r="AJ9" t="s">
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>14.85</v>
+        <v>12.88</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1834,10 +1847,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>1592.1</v>
+        <v>1584</v>
       </c>
       <c r="D10">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="E10">
         <v>1768.4</v>
@@ -1846,46 +1859,46 @@
         <v>1326.2</v>
       </c>
       <c r="G10">
-        <v>-9.970000000000001</v>
+        <v>-10.43</v>
       </c>
       <c r="H10">
-        <v>20.05</v>
+        <v>19.44</v>
       </c>
       <c r="I10">
-        <v>-2.86</v>
+        <v>-1.61</v>
       </c>
       <c r="J10">
-        <v>2.02</v>
+        <v>1.57</v>
       </c>
       <c r="K10">
-        <v>11.95</v>
+        <v>8.59</v>
       </c>
       <c r="L10">
-        <v>8.210000000000001</v>
+        <v>6.94</v>
       </c>
       <c r="M10">
-        <v>5.71</v>
+        <v>4.66</v>
       </c>
       <c r="N10">
         <v>66</v>
       </c>
       <c r="O10">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="P10">
-        <v>1603.34</v>
+        <v>1588.38</v>
       </c>
       <c r="Q10">
-        <v>1625.63</v>
+        <v>1627.3</v>
       </c>
       <c r="R10">
-        <v>1526.97</v>
+        <v>1532.44</v>
       </c>
       <c r="S10">
-        <v>1506.29</v>
+        <v>1507.99</v>
       </c>
       <c r="T10">
-        <v>5.7</v>
+        <v>5.04</v>
       </c>
       <c r="U10" t="s">
         <v>48</v>
@@ -1900,34 +1913,34 @@
         <v>3</v>
       </c>
       <c r="Y10">
-        <v>50.14</v>
+        <v>47.96</v>
       </c>
       <c r="Z10">
-        <v>18.76</v>
+        <v>12.1</v>
       </c>
       <c r="AA10">
-        <v>31.15</v>
+        <v>24.77</v>
       </c>
       <c r="AB10">
-        <v>-12.39</v>
+        <v>-12.68</v>
       </c>
       <c r="AC10">
         <v>1.04</v>
       </c>
       <c r="AD10">
-        <v>0.92</v>
+        <v>1.04</v>
       </c>
       <c r="AE10">
-        <v>37.28</v>
+        <v>35.61</v>
       </c>
       <c r="AF10">
-        <v>-40.77</v>
+        <v>-21.82</v>
       </c>
       <c r="AG10">
-        <v>1684.08</v>
+        <v>1679.02</v>
       </c>
       <c r="AH10">
-        <v>1567.18</v>
+        <v>1575.59</v>
       </c>
       <c r="AI10">
         <v>1527.05</v>
@@ -1936,7 +1949,7 @@
         <v>50</v>
       </c>
       <c r="AK10">
-        <v>31.47</v>
+        <v>36.17</v>
       </c>
     </row>
   </sheetData>
@@ -2077,7 +2090,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F77"/>
+  <dimension ref="A1:F76"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2117,7 +2130,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2135,1243 +2148,1229 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+    <row r="4" spans="1:6">
+      <c r="A4" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="D4" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E6" s="3" t="s">
+      <c r="B7" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="7">
+        <v>-4.28</v>
+      </c>
+      <c r="D8" s="7">
+        <v>-3.48</v>
+      </c>
+      <c r="E8" s="8">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="7">
+        <v>5.65</v>
+      </c>
+      <c r="D9" s="7">
+        <v>7.99</v>
+      </c>
+      <c r="E9" s="8">
+        <v>2.34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="7">
+        <v>3.04</v>
+      </c>
+      <c r="D10" s="7">
+        <v>6.23</v>
+      </c>
+      <c r="E10" s="8">
+        <v>3.19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="7">
+        <v>0.61</v>
+      </c>
+      <c r="D11" s="7">
+        <v>1.2</v>
+      </c>
+      <c r="E11" s="8">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="7">
+        <v>2.37</v>
+      </c>
+      <c r="D12" s="7">
+        <v>-3.18</v>
+      </c>
+      <c r="E12" s="9">
+        <v>-5.55</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="7">
+        <v>12.22</v>
+      </c>
+      <c r="D13" s="7">
+        <v>11.06</v>
+      </c>
+      <c r="E13" s="9">
+        <v>-1.16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="7">
+        <v>1.71</v>
+      </c>
+      <c r="D14" s="7">
+        <v>1.01</v>
+      </c>
+      <c r="E14" s="9">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="7">
+        <v>-0.19</v>
+      </c>
+      <c r="D15" s="7">
+        <v>-0.28</v>
+      </c>
+      <c r="E15" s="9">
+        <v>-0.09</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="7">
+        <v>1.81</v>
+      </c>
+      <c r="D16" s="7">
+        <v>1.57</v>
+      </c>
+      <c r="E16" s="9">
+        <v>-0.24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-1.64</v>
+      </c>
+      <c r="D17" s="7">
+        <v>-2.06</v>
+      </c>
+      <c r="E17" s="9">
+        <v>-0.42</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-0.47</v>
+      </c>
+      <c r="D18" s="7">
+        <v>0.7</v>
+      </c>
+      <c r="E18" s="8">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="7">
+        <v>-2.18</v>
+      </c>
+      <c r="D19" s="7">
+        <v>-2.62</v>
+      </c>
+      <c r="E19" s="9">
+        <v>-0.44</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="7">
+        <v>-1.33</v>
+      </c>
+      <c r="D20" s="7">
+        <v>-1.94</v>
+      </c>
+      <c r="E20" s="9">
+        <v>-0.61</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-1.07</v>
+      </c>
+      <c r="D21" s="7">
+        <v>-0.59</v>
+      </c>
+      <c r="E21" s="8">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="7">
+        <v>3.54</v>
+      </c>
+      <c r="D22" s="7">
+        <v>2.05</v>
+      </c>
+      <c r="E22" s="9">
+        <v>-1.49</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="7">
+        <v>-2.13</v>
+      </c>
+      <c r="D23" s="7">
+        <v>-2.46</v>
+      </c>
+      <c r="E23" s="9">
+        <v>-0.33</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="7">
+        <v>-1.88</v>
+      </c>
+      <c r="D24" s="7">
+        <v>-2.18</v>
+      </c>
+      <c r="E24" s="9">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="7">
+        <v>-2.99</v>
+      </c>
+      <c r="D25" s="7">
+        <v>-1.61</v>
+      </c>
+      <c r="E25" s="8">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="7">
+        <v>2.11</v>
+      </c>
+      <c r="D26" s="7">
+        <v>0.11</v>
+      </c>
+      <c r="E26" s="9">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="7">
+        <v>0.86</v>
+      </c>
+      <c r="D27" s="7">
+        <v>1.79</v>
+      </c>
+      <c r="E27" s="8">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="7">
+        <v>43.24</v>
+      </c>
+      <c r="D28" s="7">
+        <v>43.99</v>
+      </c>
+      <c r="E28" s="8">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="7">
+        <v>11.18</v>
+      </c>
+      <c r="D29" s="7">
+        <v>7.33</v>
+      </c>
+      <c r="E29" s="9">
+        <v>-3.85</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="7">
+        <v>23.6</v>
+      </c>
+      <c r="D30" s="7">
+        <v>22.86</v>
+      </c>
+      <c r="E30" s="9">
+        <v>-0.74</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="7">
+        <v>-6.34</v>
+      </c>
+      <c r="D31" s="7">
+        <v>-6.26</v>
+      </c>
+      <c r="E31" s="8">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="7">
+        <v>-37.42</v>
+      </c>
+      <c r="D32" s="7">
+        <v>-37.54</v>
+      </c>
+      <c r="E32" s="9">
+        <v>-0.12</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="7">
+        <v>-13.39</v>
+      </c>
+      <c r="D33" s="7">
+        <v>-12.24</v>
+      </c>
+      <c r="E33" s="8">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="7">
+        <v>8.789999999999999</v>
+      </c>
+      <c r="D34" s="7">
+        <v>6.94</v>
+      </c>
+      <c r="E34" s="9">
+        <v>-1.85</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="7">
+        <v>-13.09</v>
+      </c>
+      <c r="D35" s="7">
+        <v>-12.65</v>
+      </c>
+      <c r="E35" s="8">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="7">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="D36" s="7">
+        <v>9.869999999999999</v>
+      </c>
+      <c r="E36" s="8">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="7">
+        <v>23.68</v>
+      </c>
+      <c r="D37" s="7">
+        <v>24.12</v>
+      </c>
+      <c r="E37" s="8">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="7">
+        <v>12.93</v>
+      </c>
+      <c r="D38" s="7">
+        <v>11.09</v>
+      </c>
+      <c r="E38" s="9">
+        <v>-1.84</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="7">
+        <v>12.43</v>
+      </c>
+      <c r="D39" s="7">
+        <v>13.93</v>
+      </c>
+      <c r="E39" s="8">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="7">
+        <v>1.29</v>
+      </c>
+      <c r="D40" s="7">
+        <v>0.66</v>
+      </c>
+      <c r="E40" s="9">
+        <v>-0.63</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="7">
+        <v>-0.06</v>
+      </c>
+      <c r="D41" s="7">
+        <v>0.14</v>
+      </c>
+      <c r="E41" s="8">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="7">
+        <v>-4.58</v>
+      </c>
+      <c r="D42" s="7">
+        <v>-5.42</v>
+      </c>
+      <c r="E42" s="9">
+        <v>-0.84</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="7">
+        <v>10.34</v>
+      </c>
+      <c r="D43" s="7">
+        <v>8.59</v>
+      </c>
+      <c r="E43" s="9">
+        <v>-1.75</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="7">
+        <v>-18.19</v>
+      </c>
+      <c r="D44" s="7">
+        <v>-18.53</v>
+      </c>
+      <c r="E44" s="9">
+        <v>-0.34</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="7">
+        <v>-10.26</v>
+      </c>
+      <c r="D45" s="7">
+        <v>-10.21</v>
+      </c>
+      <c r="E45" s="8">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="7">
+        <v>-7.45</v>
+      </c>
+      <c r="D46" s="7">
+        <v>-8.15</v>
+      </c>
+      <c r="E46" s="9">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="7">
+        <v>-9.94</v>
+      </c>
+      <c r="D47" s="7">
+        <v>-10.09</v>
+      </c>
+      <c r="E47" s="9">
+        <v>-0.15</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="7">
+        <v>-9.390000000000001</v>
+      </c>
+      <c r="D48" s="7">
+        <v>-8.949999999999999</v>
+      </c>
+      <c r="E48" s="8">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="7">
+        <v>-6.95</v>
+      </c>
+      <c r="D49" s="7">
+        <v>-6.86</v>
+      </c>
+      <c r="E49" s="8">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="7">
+        <v>-38.98</v>
+      </c>
+      <c r="D50" s="7">
+        <v>-39.19</v>
+      </c>
+      <c r="E50" s="9">
+        <v>-0.21</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="7">
+        <v>-20.63</v>
+      </c>
+      <c r="D51" s="7">
+        <v>-20.87</v>
+      </c>
+      <c r="E51" s="9">
+        <v>-0.24</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="7">
+        <v>401.05</v>
+      </c>
+      <c r="D52" s="7">
+        <v>399.35</v>
+      </c>
+      <c r="E52" s="9">
+        <v>-1.7</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="7">
+        <v>3412.2</v>
+      </c>
+      <c r="D53" s="7">
+        <v>3414.1</v>
+      </c>
+      <c r="E53" s="8">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="7">
+        <v>381.6</v>
+      </c>
+      <c r="D54" s="7">
+        <v>378.7</v>
+      </c>
+      <c r="E54" s="9">
+        <v>-2.9</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="7">
+        <v>379.8</v>
+      </c>
+      <c r="D55" s="7">
+        <v>379.15</v>
+      </c>
+      <c r="E55" s="9">
+        <v>-0.65</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="7">
+        <v>401.15</v>
+      </c>
+      <c r="D56" s="7">
+        <v>403.1</v>
+      </c>
+      <c r="E56" s="8">
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="7">
+        <v>634.15</v>
+      </c>
+      <c r="D57" s="7">
+        <v>634.75</v>
+      </c>
+      <c r="E57" s="8">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="7">
+        <v>221.79</v>
+      </c>
+      <c r="D58" s="7">
+        <v>221.05</v>
+      </c>
+      <c r="E58" s="9">
+        <v>-0.74</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="7">
+        <v>3569.8</v>
+      </c>
+      <c r="D59" s="7">
+        <v>3558.9</v>
+      </c>
+      <c r="E59" s="9">
+        <v>-10.9</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C60" s="7">
+        <v>32.4</v>
+      </c>
+      <c r="D60" s="7">
+        <v>31.42</v>
+      </c>
+      <c r="E60" s="9">
+        <v>-0.98</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" s="7">
+        <v>56.87</v>
+      </c>
+      <c r="D61" s="7">
+        <v>57.05</v>
+      </c>
+      <c r="E61" s="8">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" s="7">
+        <v>52.44</v>
+      </c>
+      <c r="D62" s="7">
+        <v>50.71</v>
+      </c>
+      <c r="E62" s="9">
+        <v>-1.73</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="7">
+        <v>50.06</v>
+      </c>
+      <c r="D63" s="7">
+        <v>49.39</v>
+      </c>
+      <c r="E63" s="9">
+        <v>-0.67</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="7">
+        <v>48.79</v>
+      </c>
+      <c r="D64" s="7">
+        <v>50.52</v>
+      </c>
+      <c r="E64" s="8">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="7">
         <v>66</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="D65" s="7">
+        <v>66.2</v>
+      </c>
+      <c r="E65" s="8">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="7">
+        <v>45.66</v>
+      </c>
+      <c r="D66" s="7">
+        <v>44.71</v>
+      </c>
+      <c r="E66" s="9">
+        <v>-0.95</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="7">
+        <v>37.68</v>
+      </c>
+      <c r="D67" s="7">
+        <v>36.23</v>
+      </c>
+      <c r="E67" s="9">
+        <v>-1.45</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="6">
-        <v>-13.97</v>
-      </c>
-      <c r="D7" s="6">
-        <v>-14.54</v>
-      </c>
-      <c r="E7" s="7">
-        <v>-0.57</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="B68" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C68" s="7">
+        <v>-66.62</v>
+      </c>
+      <c r="D68" s="7">
+        <v>-47.59</v>
+      </c>
+      <c r="E68" s="8">
+        <v>19.03</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>6.66</v>
-      </c>
-      <c r="D8" s="6">
-        <v>7.86</v>
-      </c>
-      <c r="E8" s="8">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="B69" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C69" s="7">
+        <v>-29.3</v>
+      </c>
+      <c r="D69" s="7">
+        <v>-51.31</v>
+      </c>
+      <c r="E69" s="9">
+        <v>-22.01</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>11.36</v>
-      </c>
-      <c r="D9" s="6">
-        <v>1.14</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-10.22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="B70" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="7">
+        <v>-64.51000000000001</v>
+      </c>
+      <c r="D70" s="7">
+        <v>-54.04</v>
+      </c>
+      <c r="E70" s="8">
+        <v>10.47</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>1.22</v>
-      </c>
-      <c r="D10" s="6">
-        <v>0.83</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-0.39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B71" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C71" s="7">
+        <v>-77.36</v>
+      </c>
+      <c r="D71" s="7">
+        <v>-46.89</v>
+      </c>
+      <c r="E71" s="8">
+        <v>30.47</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>3.86</v>
-      </c>
-      <c r="D11" s="6">
-        <v>1.12</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-2.74</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B72" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C72" s="7">
+        <v>-65.34</v>
+      </c>
+      <c r="D72" s="7">
+        <v>-69.33</v>
+      </c>
+      <c r="E72" s="9">
+        <v>-3.99</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>5.84</v>
-      </c>
-      <c r="D12" s="6">
-        <v>6.11</v>
-      </c>
-      <c r="E12" s="8">
-        <v>0.27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B73" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="7">
+        <v>739.46</v>
+      </c>
+      <c r="D73" s="7">
+        <v>19.52</v>
+      </c>
+      <c r="E73" s="9">
+        <v>-719.9400000000001</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-3.72</v>
-      </c>
-      <c r="D13" s="6">
-        <v>4.42</v>
-      </c>
-      <c r="E13" s="8">
-        <v>8.140000000000001</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B74" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="7">
+        <v>-50.76</v>
+      </c>
+      <c r="D74" s="7">
+        <v>-44.95</v>
+      </c>
+      <c r="E74" s="8">
+        <v>5.81</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-0.5</v>
-      </c>
-      <c r="D14" s="6">
-        <v>0.43</v>
-      </c>
-      <c r="E14" s="8">
-        <v>0.93</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B75" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="7">
+        <v>-30.95</v>
+      </c>
+      <c r="D75" s="7">
+        <v>-26.98</v>
+      </c>
+      <c r="E75" s="8">
+        <v>3.97</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="6">
-        <v>0.86</v>
-      </c>
-      <c r="D15" s="6">
-        <v>2.02</v>
-      </c>
-      <c r="E15" s="8">
-        <v>1.16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-1.23</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-1.17</v>
-      </c>
-      <c r="E16" s="8">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>0.33</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-0.1</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-0.43</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-1.58</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-3.52</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-1.94</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-2.39</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-1.71</v>
-      </c>
-      <c r="E19" s="8">
-        <v>0.68</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-0.17</v>
-      </c>
-      <c r="D20" s="6">
-        <v>0.16</v>
-      </c>
-      <c r="E20" s="8">
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6">
-        <v>0.65</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-0.23</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-0.88</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-2.4</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-1.26</v>
-      </c>
-      <c r="E22" s="8">
-        <v>1.14</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-0.5600000000000001</v>
-      </c>
-      <c r="D23" s="6">
-        <v>-0.43</v>
-      </c>
-      <c r="E23" s="8">
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-2.17</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-2.86</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-0.6899999999999999</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="6">
-        <v>4.88</v>
-      </c>
-      <c r="D25" s="6">
-        <v>3.62</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-1.26</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>4.05</v>
-      </c>
-      <c r="D26" s="6">
-        <v>4.88</v>
-      </c>
-      <c r="E26" s="8">
-        <v>0.83</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>50.51</v>
-      </c>
-      <c r="D27" s="6">
-        <v>49.92</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-0.59</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="6">
-        <v>9.17</v>
-      </c>
-      <c r="D28" s="6">
-        <v>10.65</v>
-      </c>
-      <c r="E28" s="8">
-        <v>1.48</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="6">
-        <v>21.5</v>
-      </c>
-      <c r="D29" s="6">
-        <v>26.19</v>
-      </c>
-      <c r="E29" s="8">
-        <v>4.69</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-9.07</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-9.470000000000001</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-0.4</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-38.74</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-37.83</v>
-      </c>
-      <c r="E31" s="8">
-        <v>0.91</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-10.21</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-9.970000000000001</v>
-      </c>
-      <c r="E32" s="8">
-        <v>0.24</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="6">
-        <v>6.65</v>
-      </c>
-      <c r="D33" s="6">
-        <v>8.210000000000001</v>
-      </c>
-      <c r="E33" s="8">
-        <v>1.56</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="6">
-        <v>-12.13</v>
-      </c>
-      <c r="D34" s="6">
-        <v>-10.5</v>
-      </c>
-      <c r="E34" s="8">
-        <v>1.63</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="6">
-        <v>10.2</v>
-      </c>
-      <c r="D35" s="6">
-        <v>11.15</v>
-      </c>
-      <c r="E35" s="8">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="6">
-        <v>29.03</v>
-      </c>
-      <c r="D36" s="6">
-        <v>27.67</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-1.36</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="6">
-        <v>12.02</v>
-      </c>
-      <c r="D37" s="6">
-        <v>10.62</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-1.4</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="6">
-        <v>14.16</v>
-      </c>
-      <c r="D38" s="6">
-        <v>14.78</v>
-      </c>
-      <c r="E38" s="8">
-        <v>0.62</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="6">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="D39" s="6">
-        <v>1</v>
-      </c>
-      <c r="E39" s="8">
-        <v>0.93</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-2.42</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-2.15</v>
-      </c>
-      <c r="E40" s="8">
-        <v>0.27</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="6">
-        <v>11.96</v>
-      </c>
-      <c r="D41" s="6">
-        <v>11.95</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-0.01</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="6">
-        <v>-17.04</v>
-      </c>
-      <c r="D42" s="6">
-        <v>-17.63</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-0.59</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="6">
-        <v>-10.19</v>
-      </c>
-      <c r="D43" s="6">
-        <v>-9.93</v>
-      </c>
-      <c r="E43" s="8">
-        <v>0.26</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="6">
-        <v>-5.51</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-7.24</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-1.73</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-11.38</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-10.55</v>
-      </c>
-      <c r="E45" s="8">
-        <v>0.83</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-8.23</v>
-      </c>
-      <c r="D46" s="6">
-        <v>-8.140000000000001</v>
-      </c>
-      <c r="E46" s="8">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="6">
-        <v>-9.92</v>
-      </c>
-      <c r="D47" s="6">
-        <v>-10.4</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-0.48</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="6">
-        <v>-39.62</v>
-      </c>
-      <c r="D48" s="6">
-        <v>-39.19</v>
-      </c>
-      <c r="E48" s="8">
-        <v>0.43</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="6">
-        <v>-20.2</v>
-      </c>
-      <c r="D49" s="6">
-        <v>-19.9</v>
-      </c>
-      <c r="E49" s="8">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="6">
-        <v>-10.1</v>
-      </c>
-      <c r="D50" s="6">
-        <v>-9.970000000000001</v>
-      </c>
-      <c r="E50" s="8">
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C51" s="6">
-        <v>406.65</v>
-      </c>
-      <c r="D51" s="6">
-        <v>403.8</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-2.85</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="6">
-        <v>3415</v>
-      </c>
-      <c r="D52" s="6">
-        <v>3424.8</v>
-      </c>
-      <c r="E52" s="8">
-        <v>9.800000000000001</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="6">
-        <v>389.6</v>
-      </c>
-      <c r="D53" s="6">
-        <v>382.45</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-7.15</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="6">
-        <v>373.7</v>
-      </c>
-      <c r="D54" s="6">
-        <v>377.2</v>
-      </c>
-      <c r="E54" s="8">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="6">
-        <v>406.25</v>
-      </c>
-      <c r="D55" s="6">
-        <v>406.65</v>
-      </c>
-      <c r="E55" s="8">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="6">
-        <v>613.9</v>
-      </c>
-      <c r="D56" s="6">
-        <v>610.6</v>
-      </c>
-      <c r="E56" s="7">
-        <v>-3.3</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="6">
-        <v>219.48</v>
-      </c>
-      <c r="D57" s="6">
-        <v>221.05</v>
-      </c>
-      <c r="E57" s="8">
-        <v>1.57</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="6">
-        <v>3588.8</v>
-      </c>
-      <c r="D58" s="6">
-        <v>3602.6</v>
-      </c>
-      <c r="E58" s="8">
-        <v>13.8</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="6">
-        <v>1589.8</v>
-      </c>
-      <c r="D59" s="6">
-        <v>1592.1</v>
-      </c>
-      <c r="E59" s="8">
-        <v>2.3</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C60" s="6">
-        <v>35.69</v>
-      </c>
-      <c r="D60" s="6">
-        <v>33.99</v>
-      </c>
-      <c r="E60" s="7">
-        <v>-1.7</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C61" s="6">
-        <v>57.55</v>
-      </c>
-      <c r="D61" s="6">
-        <v>58.36</v>
-      </c>
-      <c r="E61" s="8">
-        <v>0.8100000000000001</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C62" s="6">
-        <v>57.12</v>
-      </c>
-      <c r="D62" s="6">
-        <v>52.93</v>
-      </c>
-      <c r="E62" s="7">
-        <v>-4.19</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C63" s="6">
-        <v>43.63</v>
-      </c>
-      <c r="D63" s="6">
-        <v>47.39</v>
-      </c>
-      <c r="E63" s="8">
-        <v>3.76</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="6">
-        <v>53.39</v>
-      </c>
-      <c r="D64" s="6">
-        <v>53.7</v>
-      </c>
-      <c r="E64" s="8">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="6">
-        <v>58.76</v>
-      </c>
-      <c r="D65" s="6">
-        <v>56.65</v>
-      </c>
-      <c r="E65" s="7">
-        <v>-2.11</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="6">
-        <v>42.28</v>
-      </c>
-      <c r="D66" s="6">
-        <v>44.57</v>
-      </c>
-      <c r="E66" s="8">
-        <v>2.29</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="6">
-        <v>39.44</v>
-      </c>
-      <c r="D67" s="6">
-        <v>42.4</v>
-      </c>
-      <c r="E67" s="8">
-        <v>2.96</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="6">
-        <v>49.54</v>
-      </c>
-      <c r="D68" s="6">
-        <v>50.14</v>
-      </c>
-      <c r="E68" s="8">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B69" s="5" t="s">
+      <c r="B76" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C69" s="6">
-        <v>-81.08</v>
-      </c>
-      <c r="D69" s="6">
-        <v>-57.92</v>
-      </c>
-      <c r="E69" s="8">
-        <v>23.16</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C70" s="6">
-        <v>-35.76</v>
-      </c>
-      <c r="D70" s="6">
-        <v>-48.36</v>
-      </c>
-      <c r="E70" s="7">
-        <v>-12.6</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C71" s="6">
-        <v>-67.16</v>
-      </c>
-      <c r="D71" s="6">
-        <v>-65.81</v>
-      </c>
-      <c r="E71" s="8">
-        <v>1.35</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C72" s="6">
-        <v>54.22</v>
-      </c>
-      <c r="D72" s="6">
-        <v>-84.66</v>
-      </c>
-      <c r="E72" s="7">
-        <v>-138.88</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C73" s="6">
-        <v>-57.13</v>
-      </c>
-      <c r="D73" s="6">
-        <v>-73.65000000000001</v>
-      </c>
-      <c r="E73" s="7">
-        <v>-16.52</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="6">
-        <v>37.53</v>
-      </c>
-      <c r="D74" s="6">
-        <v>66.55</v>
-      </c>
-      <c r="E74" s="8">
-        <v>29.02</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="6">
-        <v>-62.9</v>
-      </c>
-      <c r="D75" s="6">
-        <v>-63.69</v>
-      </c>
-      <c r="E75" s="7">
-        <v>-0.79</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="6">
-        <v>-39.86</v>
-      </c>
-      <c r="D76" s="6">
-        <v>-43.97</v>
-      </c>
-      <c r="E76" s="7">
-        <v>-4.11</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="6">
-        <v>-38.96</v>
-      </c>
-      <c r="D77" s="6">
-        <v>-40.77</v>
-      </c>
-      <c r="E77" s="7">
-        <v>-1.81</v>
+      <c r="C76" s="7">
+        <v>-53.73</v>
+      </c>
+      <c r="D76" s="7">
+        <v>-21.82</v>
+      </c>
+      <c r="E76" s="8">
+        <v>31.91</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3391,60 +3390,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E1" s="9" t="s">
+      <c r="B1" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" s="12">
+        <v>60.16</v>
+      </c>
+      <c r="C2" s="13">
+        <v>9</v>
+      </c>
+      <c r="D2" s="12">
+        <v>48.2</v>
+      </c>
+      <c r="E2" s="12">
         <v>70</v>
       </c>
-      <c r="F1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="B2" s="11">
-        <v>60.16</v>
-      </c>
-      <c r="C2" s="12">
-        <v>9</v>
-      </c>
-      <c r="D2" s="11">
-        <v>48.9</v>
-      </c>
-      <c r="E2" s="11">
-        <v>70</v>
-      </c>
-      <c r="F2" s="11">
-        <v>1</v>
-      </c>
-      <c r="G2" s="11">
-        <v>6.7</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="12">
+        <v>2.5</v>
+      </c>
+      <c r="G2" s="12">
+        <v>5.6</v>
+      </c>
+      <c r="H2" s="12">
         <v>55.4</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="12">
         <v>40</v>
       </c>
     </row>
@@ -3546,61 +3545,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="14" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="14">
-        <v>0.3521</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.3169</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.2373</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.1976</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.1333</v>
-      </c>
-      <c r="F2" s="14">
-        <v>0.0901</v>
-      </c>
-      <c r="G2" s="14">
-        <v>0.0571</v>
-      </c>
-      <c r="H2" s="14">
-        <v>0.02</v>
-      </c>
-      <c r="I2" s="14">
-        <v>-0.104</v>
+      <c r="A2" s="15">
+        <v>0.3539</v>
+      </c>
+      <c r="B2" s="15">
+        <v>0.3334</v>
+      </c>
+      <c r="C2" s="15">
+        <v>0.2291</v>
+      </c>
+      <c r="D2" s="15">
+        <v>0.1993</v>
+      </c>
+      <c r="E2" s="15">
+        <v>0.1397</v>
+      </c>
+      <c r="F2" s="15">
+        <v>0.0922</v>
+      </c>
+      <c r="G2" s="15">
+        <v>0.0466</v>
+      </c>
+      <c r="H2" s="15">
+        <v>0.0122</v>
+      </c>
+      <c r="I2" s="15">
+        <v>-0.1113</v>
       </c>
     </row>
   </sheetData>

--- a/MAHINDRA_GROUP_Technical_Metrics.xlsx
+++ b/MAHINDRA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="81">
   <si>
     <t>Symbol</t>
   </si>
@@ -193,31 +193,37 @@
     <t>Curr Value</t>
   </si>
   <si>
+    <t>No → Yes</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
+  </si>
+  <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>48.8 → 50.5</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>48.8</t>
+    <t>48.0 → 52.6</t>
+  </si>
+  <si>
+    <t>48.0</t>
+  </si>
+  <si>
+    <t>52.6</t>
+  </si>
+  <si>
+    <t>50.5 → 47.5</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
   </si>
   <si>
     <t>50.5</t>
   </si>
   <si>
-    <t>50.1 → 49.4</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>50.1</t>
-  </si>
-  <si>
-    <t>49.4</t>
+    <t>47.5</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -430,8 +436,8 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -943,10 +949,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>399.35</v>
+        <v>395.95</v>
       </c>
       <c r="D2">
-        <v>-0.42</v>
+        <v>-0.85</v>
       </c>
       <c r="E2">
         <v>490.2</v>
@@ -955,25 +961,25 @@
         <v>379.2</v>
       </c>
       <c r="G2">
-        <v>-18.53</v>
+        <v>-19.23</v>
       </c>
       <c r="H2">
-        <v>5.31</v>
+        <v>4.42</v>
       </c>
       <c r="I2">
-        <v>-2.06</v>
+        <v>-3.36</v>
       </c>
       <c r="J2">
-        <v>-3.48</v>
+        <v>-4.22</v>
       </c>
       <c r="K2">
-        <v>-12.65</v>
+        <v>-13.5</v>
       </c>
       <c r="L2">
-        <v>0.11</v>
+        <v>-0.37</v>
       </c>
       <c r="M2">
-        <v>13.97</v>
+        <v>13.3</v>
       </c>
       <c r="N2">
         <v>34</v>
@@ -982,19 +988,19 @@
         <v>40</v>
       </c>
       <c r="P2">
-        <v>404.11</v>
+        <v>401.36</v>
       </c>
       <c r="Q2">
-        <v>409.42</v>
+        <v>408.81</v>
       </c>
       <c r="R2">
-        <v>440.37</v>
+        <v>438.99</v>
       </c>
       <c r="S2">
-        <v>437.68</v>
+        <v>437.53</v>
       </c>
       <c r="T2">
-        <v>-8.76</v>
+        <v>-9.5</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1009,43 +1015,43 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>31.42</v>
+        <v>29.49</v>
       </c>
       <c r="Z2">
-        <v>-10.43</v>
+        <v>-10.59</v>
       </c>
       <c r="AA2">
-        <v>-11.02</v>
+        <v>-10.93</v>
       </c>
       <c r="AB2">
-        <v>0.59</v>
+        <v>0.34</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>25.44</v>
+        <v>7.6</v>
       </c>
       <c r="AE2">
-        <v>9.390000000000001</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="AF2">
-        <v>-47.59</v>
+        <v>-15.16</v>
       </c>
       <c r="AG2">
-        <v>418.73</v>
+        <v>419.89</v>
       </c>
       <c r="AH2">
-        <v>400.12</v>
+        <v>397.72</v>
       </c>
       <c r="AI2">
-        <v>428.63</v>
+        <v>426.18</v>
       </c>
       <c r="AJ2" t="s">
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>37.2</v>
+        <v>41.04</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1056,10 +1062,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>3414.1</v>
+        <v>3443</v>
       </c>
       <c r="D3">
-        <v>0.06</v>
+        <v>0.85</v>
       </c>
       <c r="E3">
         <v>3802.4</v>
@@ -1068,46 +1074,46 @@
         <v>2931.1</v>
       </c>
       <c r="G3">
-        <v>-10.21</v>
+        <v>-9.449999999999999</v>
       </c>
       <c r="H3">
-        <v>16.48</v>
+        <v>17.46</v>
       </c>
       <c r="I3">
-        <v>0.7</v>
+        <v>0.63</v>
       </c>
       <c r="J3">
-        <v>7.99</v>
+        <v>6.31</v>
       </c>
       <c r="K3">
-        <v>9.869999999999999</v>
+        <v>10.3</v>
       </c>
       <c r="L3">
-        <v>1.79</v>
+        <v>1.4</v>
       </c>
       <c r="M3">
-        <v>35.39</v>
+        <v>35.83</v>
       </c>
       <c r="N3">
         <v>55</v>
       </c>
       <c r="O3">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="P3">
-        <v>3417.52</v>
+        <v>3421.82</v>
       </c>
       <c r="Q3">
-        <v>3405.77</v>
+        <v>3414.36</v>
       </c>
       <c r="R3">
-        <v>3243.42</v>
+        <v>3249.59</v>
       </c>
       <c r="S3">
-        <v>3352.46</v>
+        <v>3351.58</v>
       </c>
       <c r="T3">
-        <v>1.84</v>
+        <v>2.73</v>
       </c>
       <c r="U3" t="s">
         <v>48</v>
@@ -1122,34 +1128,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>57.05</v>
+        <v>59.77</v>
       </c>
       <c r="Z3">
-        <v>52.75</v>
+        <v>51.42</v>
       </c>
       <c r="AA3">
-        <v>64.88</v>
+        <v>62.19</v>
       </c>
       <c r="AB3">
-        <v>-12.13</v>
+        <v>-10.76</v>
       </c>
       <c r="AC3">
-        <v>11.28</v>
+        <v>14.73</v>
       </c>
       <c r="AD3">
-        <v>13.23</v>
+        <v>12.84</v>
       </c>
       <c r="AE3">
-        <v>65.05</v>
+        <v>63.71</v>
       </c>
       <c r="AF3">
-        <v>-51.31</v>
+        <v>-54.24</v>
       </c>
       <c r="AG3">
-        <v>3548.87</v>
+        <v>3543.39</v>
       </c>
       <c r="AH3">
-        <v>3262.67</v>
+        <v>3285.33</v>
       </c>
       <c r="AI3">
         <v>3274.47</v>
@@ -1158,7 +1164,7 @@
         <v>50</v>
       </c>
       <c r="AK3">
-        <v>26.88</v>
+        <v>24.37</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1169,10 +1175,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>378.7</v>
+        <v>381.45</v>
       </c>
       <c r="D4">
-        <v>-0.76</v>
+        <v>0.73</v>
       </c>
       <c r="E4">
         <v>412.3</v>
@@ -1181,46 +1187,46 @@
         <v>253.95</v>
       </c>
       <c r="G4">
-        <v>-8.15</v>
+        <v>-7.48</v>
       </c>
       <c r="H4">
-        <v>49.12</v>
+        <v>50.21</v>
       </c>
       <c r="I4">
-        <v>-2.62</v>
+        <v>-1.23</v>
       </c>
       <c r="J4">
-        <v>6.23</v>
+        <v>5.08</v>
       </c>
       <c r="K4">
-        <v>24.12</v>
+        <v>24.98</v>
       </c>
       <c r="L4">
-        <v>43.99</v>
+        <v>42.73</v>
       </c>
       <c r="M4">
-        <v>22.91</v>
+        <v>22.99</v>
       </c>
       <c r="N4">
         <v>99</v>
       </c>
       <c r="O4">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P4">
-        <v>383.71</v>
+        <v>382.76</v>
       </c>
       <c r="Q4">
-        <v>392.31</v>
+        <v>392.71</v>
       </c>
       <c r="R4">
-        <v>351.9</v>
+        <v>353.57</v>
       </c>
       <c r="S4">
-        <v>341.37</v>
+        <v>341.71</v>
       </c>
       <c r="T4">
-        <v>10.94</v>
+        <v>11.63</v>
       </c>
       <c r="U4" t="s">
         <v>48</v>
@@ -1235,34 +1241,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>50.71</v>
+        <v>52.32</v>
       </c>
       <c r="Z4">
-        <v>8.33</v>
+        <v>7.29</v>
       </c>
       <c r="AA4">
-        <v>13.15</v>
+        <v>11.98</v>
       </c>
       <c r="AB4">
-        <v>-4.83</v>
+        <v>-4.69</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AD4">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="AE4">
-        <v>13.61</v>
+        <v>13.22</v>
       </c>
       <c r="AF4">
-        <v>-54.04</v>
+        <v>-40</v>
       </c>
       <c r="AG4">
-        <v>412.05</v>
+        <v>411.13</v>
       </c>
       <c r="AH4">
-        <v>372.57</v>
+        <v>374.28</v>
       </c>
       <c r="AI4">
         <v>357.72</v>
@@ -1271,7 +1277,7 @@
         <v>50</v>
       </c>
       <c r="AK4">
-        <v>24.5</v>
+        <v>23.1</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1282,10 +1288,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>379.15</v>
+        <v>376.55</v>
       </c>
       <c r="D5">
-        <v>-0.17</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="E5">
         <v>421.7</v>
@@ -1294,46 +1300,46 @@
         <v>294.25</v>
       </c>
       <c r="G5">
-        <v>-10.09</v>
+        <v>-10.71</v>
       </c>
       <c r="H5">
-        <v>28.85</v>
+        <v>27.97</v>
       </c>
       <c r="I5">
-        <v>-1.94</v>
+        <v>-1.98</v>
       </c>
       <c r="J5">
-        <v>1.2</v>
+        <v>-0.97</v>
       </c>
       <c r="K5">
-        <v>11.09</v>
+        <v>10.07</v>
       </c>
       <c r="L5">
-        <v>7.33</v>
+        <v>6.24</v>
       </c>
       <c r="M5">
-        <v>9.220000000000001</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="N5">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="O5">
         <v>65</v>
       </c>
       <c r="P5">
-        <v>378.8</v>
+        <v>377.28</v>
       </c>
       <c r="Q5">
-        <v>384.94</v>
+        <v>384.76</v>
       </c>
       <c r="R5">
-        <v>373.73</v>
+        <v>374.59</v>
       </c>
       <c r="S5">
-        <v>364.59</v>
+        <v>364.47</v>
       </c>
       <c r="T5">
-        <v>3.99</v>
+        <v>3.31</v>
       </c>
       <c r="U5" t="s">
         <v>48</v>
@@ -1348,34 +1354,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>49.39</v>
+        <v>46.68</v>
       </c>
       <c r="Z5">
-        <v>1.48</v>
+        <v>0.98</v>
       </c>
       <c r="AA5">
-        <v>3.4</v>
+        <v>2.92</v>
       </c>
       <c r="AB5">
-        <v>-1.92</v>
+        <v>-1.94</v>
       </c>
       <c r="AC5">
-        <v>25.52</v>
+        <v>28.09</v>
       </c>
       <c r="AD5">
-        <v>14.43</v>
+        <v>21.96</v>
       </c>
       <c r="AE5">
-        <v>10.76</v>
+        <v>10.56</v>
       </c>
       <c r="AF5">
-        <v>-46.89</v>
+        <v>-48.79</v>
       </c>
       <c r="AG5">
-        <v>397.06</v>
+        <v>397.28</v>
       </c>
       <c r="AH5">
-        <v>372.83</v>
+        <v>372.24</v>
       </c>
       <c r="AI5">
         <v>364.94</v>
@@ -1384,7 +1390,7 @@
         <v>50</v>
       </c>
       <c r="AK5">
-        <v>28.05</v>
+        <v>26.67</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1395,10 +1401,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>403.1</v>
+        <v>399.7</v>
       </c>
       <c r="D6">
-        <v>0.49</v>
+        <v>-0.84</v>
       </c>
       <c r="E6">
         <v>442.7</v>
@@ -1407,46 +1413,46 @@
         <v>279.55</v>
       </c>
       <c r="G6">
-        <v>-8.949999999999999</v>
+        <v>-9.710000000000001</v>
       </c>
       <c r="H6">
-        <v>44.2</v>
+        <v>42.98</v>
       </c>
       <c r="I6">
-        <v>-0.59</v>
+        <v>-1.2</v>
       </c>
       <c r="J6">
-        <v>-3.18</v>
+        <v>-4.63</v>
       </c>
       <c r="K6">
-        <v>13.93</v>
+        <v>14.53</v>
       </c>
       <c r="L6">
-        <v>22.86</v>
+        <v>24.36</v>
       </c>
       <c r="M6">
-        <v>-11.13</v>
+        <v>-11.05</v>
       </c>
       <c r="N6">
         <v>88</v>
       </c>
       <c r="O6">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="P6">
-        <v>404.34</v>
+        <v>403.37</v>
       </c>
       <c r="Q6">
-        <v>408.29</v>
+        <v>407.75</v>
       </c>
       <c r="R6">
-        <v>392.3</v>
+        <v>393.32</v>
       </c>
       <c r="S6">
-        <v>365.31</v>
+        <v>365.6</v>
       </c>
       <c r="T6">
-        <v>10.34</v>
+        <v>9.33</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1461,34 +1467,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>50.52</v>
+        <v>47.5</v>
       </c>
       <c r="Z6">
-        <v>2.62</v>
+        <v>1.96</v>
       </c>
       <c r="AA6">
-        <v>4.66</v>
+        <v>4.12</v>
       </c>
       <c r="AB6">
-        <v>-2.04</v>
+        <v>-2.16</v>
       </c>
       <c r="AC6">
-        <v>9.73</v>
+        <v>5.38</v>
       </c>
       <c r="AD6">
-        <v>8.460000000000001</v>
+        <v>7.65</v>
       </c>
       <c r="AE6">
-        <v>11.72</v>
+        <v>11.58</v>
       </c>
       <c r="AF6">
-        <v>-69.33</v>
+        <v>-57.86</v>
       </c>
       <c r="AG6">
-        <v>418.41</v>
+        <v>418.51</v>
       </c>
       <c r="AH6">
-        <v>398.17</v>
+        <v>396.99</v>
       </c>
       <c r="AI6">
         <v>372.35</v>
@@ -1497,7 +1503,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>19.23</v>
+        <v>18.97</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1508,109 +1514,109 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>634.75</v>
+        <v>636.55</v>
       </c>
       <c r="D7">
-        <v>0.09</v>
+        <v>0.28</v>
       </c>
       <c r="E7">
-        <v>681.5</v>
+        <v>675.05</v>
       </c>
       <c r="F7">
         <v>506.45</v>
       </c>
       <c r="G7">
-        <v>-6.86</v>
+        <v>-5.7</v>
       </c>
       <c r="H7">
-        <v>25.33</v>
+        <v>25.69</v>
       </c>
       <c r="I7">
-        <v>2.05</v>
+        <v>2.52</v>
       </c>
       <c r="J7">
-        <v>11.06</v>
+        <v>10.35</v>
       </c>
       <c r="K7">
-        <v>0.66</v>
+        <v>0.21</v>
       </c>
       <c r="L7">
-        <v>-6.26</v>
+        <v>-6.6</v>
       </c>
       <c r="M7">
-        <v>33.34</v>
+        <v>33.76</v>
       </c>
       <c r="N7">
         <v>45</v>
       </c>
       <c r="O7">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="P7">
-        <v>622.86</v>
+        <v>625.99</v>
       </c>
       <c r="Q7">
-        <v>598.8200000000001</v>
+        <v>601.9400000000001</v>
       </c>
       <c r="R7">
-        <v>601.35</v>
+        <v>601.48</v>
       </c>
       <c r="S7">
-        <v>582.85</v>
+        <v>583.3</v>
       </c>
       <c r="T7">
-        <v>8.9</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="U7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V7" t="s">
         <v>48</v>
       </c>
       <c r="W7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="X7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y7">
-        <v>66.2</v>
+        <v>66.84</v>
       </c>
       <c r="Z7">
-        <v>9.69</v>
+        <v>10.77</v>
       </c>
       <c r="AA7">
-        <v>5.02</v>
+        <v>6.17</v>
       </c>
       <c r="AB7">
-        <v>4.67</v>
+        <v>4.6</v>
       </c>
       <c r="AC7">
-        <v>88.55</v>
+        <v>100</v>
       </c>
       <c r="AD7">
-        <v>83.84</v>
+        <v>90.16</v>
       </c>
       <c r="AE7">
-        <v>16.94</v>
+        <v>17.44</v>
       </c>
       <c r="AF7">
-        <v>19.52</v>
+        <v>80.22</v>
       </c>
       <c r="AG7">
-        <v>641.88</v>
+        <v>646.49</v>
       </c>
       <c r="AH7">
-        <v>555.76</v>
+        <v>557.4</v>
       </c>
       <c r="AI7">
-        <v>588.5599999999999</v>
+        <v>591.65</v>
       </c>
       <c r="AJ7" t="s">
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>53.92</v>
+        <v>56.86</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1621,58 +1627,58 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>221.05</v>
+        <v>219.1</v>
       </c>
       <c r="D8">
-        <v>-0.33</v>
+        <v>-0.88</v>
       </c>
       <c r="E8">
-        <v>363.5</v>
+        <v>362.35</v>
       </c>
       <c r="F8">
         <v>210.4</v>
       </c>
       <c r="G8">
-        <v>-39.19</v>
+        <v>-39.53</v>
       </c>
       <c r="H8">
-        <v>5.06</v>
+        <v>4.13</v>
       </c>
       <c r="I8">
-        <v>-2.46</v>
+        <v>-1.03</v>
       </c>
       <c r="J8">
-        <v>1.01</v>
+        <v>-2.11</v>
       </c>
       <c r="K8">
-        <v>0.14</v>
+        <v>-0.04</v>
       </c>
       <c r="L8">
-        <v>-37.54</v>
+        <v>-39.72</v>
       </c>
       <c r="M8">
-        <v>1.22</v>
+        <v>0.87</v>
       </c>
       <c r="N8">
         <v>12</v>
       </c>
       <c r="O8">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P8">
-        <v>220.95</v>
+        <v>220.49</v>
       </c>
       <c r="Q8">
-        <v>223.55</v>
+        <v>223.59</v>
       </c>
       <c r="R8">
-        <v>228.27</v>
+        <v>228</v>
       </c>
       <c r="S8">
-        <v>265.03</v>
+        <v>264.5</v>
       </c>
       <c r="T8">
-        <v>-16.6</v>
+        <v>-17.17</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1687,34 +1693,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>44.71</v>
+        <v>42.22</v>
       </c>
       <c r="Z8">
-        <v>-1.34</v>
+        <v>-1.56</v>
       </c>
       <c r="AA8">
-        <v>-1.03</v>
+        <v>-1.13</v>
       </c>
       <c r="AB8">
-        <v>-0.31</v>
+        <v>-0.43</v>
       </c>
       <c r="AC8">
-        <v>17.31</v>
+        <v>12.42</v>
       </c>
       <c r="AD8">
-        <v>14.29</v>
+        <v>13.95</v>
       </c>
       <c r="AE8">
-        <v>6.55</v>
+        <v>6.42</v>
       </c>
       <c r="AF8">
-        <v>-44.95</v>
+        <v>-18.78</v>
       </c>
       <c r="AG8">
-        <v>234.03</v>
+        <v>233.99</v>
       </c>
       <c r="AH8">
-        <v>213.07</v>
+        <v>213.19</v>
       </c>
       <c r="AI8">
         <v>237.22</v>
@@ -1723,7 +1729,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>22.72</v>
+        <v>22.35</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1734,10 +1740,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>3558.9</v>
+        <v>3551.7</v>
       </c>
       <c r="D9">
-        <v>-0.31</v>
+        <v>-0.2</v>
       </c>
       <c r="E9">
         <v>4497.5</v>
@@ -1746,46 +1752,46 @@
         <v>3308.9</v>
       </c>
       <c r="G9">
-        <v>-20.87</v>
+        <v>-21.03</v>
       </c>
       <c r="H9">
-        <v>7.56</v>
+        <v>7.34</v>
       </c>
       <c r="I9">
-        <v>-2.18</v>
+        <v>-1.18</v>
       </c>
       <c r="J9">
-        <v>-0.28</v>
+        <v>-1.49</v>
       </c>
       <c r="K9">
-        <v>-5.42</v>
+        <v>-5.87</v>
       </c>
       <c r="L9">
-        <v>-12.24</v>
+        <v>-12.72</v>
       </c>
       <c r="M9">
-        <v>19.93</v>
+        <v>19.94</v>
       </c>
       <c r="N9">
         <v>23</v>
       </c>
       <c r="O9">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P9">
-        <v>3582.82</v>
+        <v>3574.36</v>
       </c>
       <c r="Q9">
-        <v>3600.72</v>
+        <v>3600.39</v>
       </c>
       <c r="R9">
-        <v>3728.14</v>
+        <v>3722.65</v>
       </c>
       <c r="S9">
-        <v>3704.87</v>
+        <v>3703.21</v>
       </c>
       <c r="T9">
-        <v>-3.94</v>
+        <v>-4.09</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1800,43 +1806,43 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>36.23</v>
+        <v>35.27</v>
       </c>
       <c r="Z9">
-        <v>-31.89</v>
+        <v>-33.15</v>
       </c>
       <c r="AA9">
-        <v>-35.35</v>
+        <v>-34.91</v>
       </c>
       <c r="AB9">
-        <v>3.46</v>
+        <v>1.76</v>
       </c>
       <c r="AC9">
-        <v>15.23</v>
+        <v>0</v>
       </c>
       <c r="AD9">
-        <v>19.64</v>
+        <v>11.3</v>
       </c>
       <c r="AE9">
-        <v>55.75</v>
+        <v>53.07</v>
       </c>
       <c r="AF9">
-        <v>-26.98</v>
+        <v>-47.39</v>
       </c>
       <c r="AG9">
-        <v>3648.36</v>
+        <v>3649.36</v>
       </c>
       <c r="AH9">
-        <v>3553.09</v>
+        <v>3551.42</v>
       </c>
       <c r="AI9">
-        <v>3727.81</v>
+        <v>3713.31</v>
       </c>
       <c r="AJ9" t="s">
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>12.88</v>
+        <v>13.07</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1847,10 +1853,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>1584</v>
+        <v>1599.9</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10">
         <v>1768.4</v>
@@ -1859,46 +1865,46 @@
         <v>1326.2</v>
       </c>
       <c r="G10">
-        <v>-10.43</v>
+        <v>-9.529999999999999</v>
       </c>
       <c r="H10">
-        <v>19.44</v>
+        <v>20.64</v>
       </c>
       <c r="I10">
-        <v>-1.61</v>
+        <v>0.5</v>
       </c>
       <c r="J10">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="K10">
-        <v>8.59</v>
+        <v>9.91</v>
       </c>
       <c r="L10">
-        <v>6.94</v>
+        <v>6.07</v>
       </c>
       <c r="M10">
-        <v>4.66</v>
+        <v>4.88</v>
       </c>
       <c r="N10">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="O10">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="P10">
-        <v>1588.38</v>
+        <v>1589.96</v>
       </c>
       <c r="Q10">
-        <v>1627.3</v>
+        <v>1625.54</v>
       </c>
       <c r="R10">
-        <v>1532.44</v>
+        <v>1535.93</v>
       </c>
       <c r="S10">
-        <v>1507.99</v>
+        <v>1508.92</v>
       </c>
       <c r="T10">
-        <v>5.04</v>
+        <v>6.03</v>
       </c>
       <c r="U10" t="s">
         <v>48</v>
@@ -1913,34 +1919,34 @@
         <v>3</v>
       </c>
       <c r="Y10">
-        <v>47.96</v>
+        <v>52.65</v>
       </c>
       <c r="Z10">
-        <v>12.1</v>
+        <v>10.86</v>
       </c>
       <c r="AA10">
-        <v>24.77</v>
+        <v>21.99</v>
       </c>
       <c r="AB10">
-        <v>-12.68</v>
+        <v>-11.13</v>
       </c>
       <c r="AC10">
-        <v>1.04</v>
+        <v>8.74</v>
       </c>
       <c r="AD10">
-        <v>1.04</v>
+        <v>3.61</v>
       </c>
       <c r="AE10">
-        <v>35.61</v>
+        <v>35.77</v>
       </c>
       <c r="AF10">
-        <v>-21.82</v>
+        <v>-51.59</v>
       </c>
       <c r="AG10">
-        <v>1679.02</v>
+        <v>1678.51</v>
       </c>
       <c r="AH10">
-        <v>1575.59</v>
+        <v>1572.57</v>
       </c>
       <c r="AI10">
         <v>1527.05</v>
@@ -1949,7 +1955,7 @@
         <v>50</v>
       </c>
       <c r="AK10">
-        <v>36.17</v>
+        <v>39.25</v>
       </c>
     </row>
   </sheetData>
@@ -2090,7 +2096,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F76"/>
+  <dimension ref="A1:F83"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2130,1247 +2136,1372 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E3" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="E4" s="5" t="s">
+      <c r="C6" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="D6" s="5" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
+      <c r="E6" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="F6" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D7" s="3" t="s">
+      <c r="B9" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="7">
-        <v>-4.28</v>
-      </c>
-      <c r="D8" s="7">
-        <v>-3.48</v>
-      </c>
-      <c r="E8" s="8">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="7">
-        <v>5.65</v>
-      </c>
-      <c r="D9" s="7">
-        <v>7.99</v>
-      </c>
-      <c r="E9" s="8">
-        <v>2.34</v>
+      <c r="D9" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="7">
-        <v>3.04</v>
+        <v>-3.48</v>
       </c>
       <c r="D10" s="7">
-        <v>6.23</v>
+        <v>-4.22</v>
       </c>
       <c r="E10" s="8">
-        <v>3.19</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="7">
-        <v>0.61</v>
+        <v>7.99</v>
       </c>
       <c r="D11" s="7">
-        <v>1.2</v>
+        <v>6.31</v>
       </c>
       <c r="E11" s="8">
-        <v>0.59</v>
+        <v>-1.68</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="7">
-        <v>2.37</v>
+        <v>6.23</v>
       </c>
       <c r="D12" s="7">
-        <v>-3.18</v>
-      </c>
-      <c r="E12" s="9">
-        <v>-5.55</v>
+        <v>5.08</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-1.15</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="7">
-        <v>12.22</v>
+        <v>1.2</v>
       </c>
       <c r="D13" s="7">
-        <v>11.06</v>
-      </c>
-      <c r="E13" s="9">
-        <v>-1.16</v>
+        <v>-0.97</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-2.17</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="7">
-        <v>1.71</v>
+        <v>-3.18</v>
       </c>
       <c r="D14" s="7">
-        <v>1.01</v>
-      </c>
-      <c r="E14" s="9">
-        <v>-0.7</v>
+        <v>-4.63</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-1.45</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="7">
-        <v>-0.19</v>
+        <v>11.06</v>
       </c>
       <c r="D15" s="7">
-        <v>-0.28</v>
-      </c>
-      <c r="E15" s="9">
-        <v>-0.09</v>
+        <v>10.35</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-0.71</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="7">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="D16" s="7">
-        <v>1.57</v>
-      </c>
-      <c r="E16" s="9">
-        <v>-0.24</v>
+        <v>-2.11</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-3.12</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="6" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C17" s="7">
-        <v>-1.64</v>
+        <v>-0.28</v>
       </c>
       <c r="D17" s="7">
-        <v>-2.06</v>
-      </c>
-      <c r="E17" s="9">
-        <v>-0.42</v>
+        <v>-1.49</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-1.21</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="6" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C18" s="7">
-        <v>-0.47</v>
+        <v>1.57</v>
       </c>
       <c r="D18" s="7">
-        <v>0.7</v>
-      </c>
-      <c r="E18" s="8">
-        <v>1.17</v>
+        <v>1.58</v>
+      </c>
+      <c r="E18" s="9">
+        <v>0.01</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="7">
-        <v>-2.18</v>
+        <v>-2.06</v>
       </c>
       <c r="D19" s="7">
-        <v>-2.62</v>
-      </c>
-      <c r="E19" s="9">
-        <v>-0.44</v>
+        <v>-3.36</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-1.3</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="7">
-        <v>-1.33</v>
+        <v>0.7</v>
       </c>
       <c r="D20" s="7">
-        <v>-1.94</v>
-      </c>
-      <c r="E20" s="9">
-        <v>-0.61</v>
+        <v>0.63</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="7">
-        <v>-1.07</v>
+        <v>-2.62</v>
       </c>
       <c r="D21" s="7">
-        <v>-0.59</v>
-      </c>
-      <c r="E21" s="8">
-        <v>0.48</v>
+        <v>-1.23</v>
+      </c>
+      <c r="E21" s="9">
+        <v>1.39</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="7">
-        <v>3.54</v>
+        <v>-1.94</v>
       </c>
       <c r="D22" s="7">
-        <v>2.05</v>
-      </c>
-      <c r="E22" s="9">
-        <v>-1.49</v>
+        <v>-1.98</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-0.04</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="7">
-        <v>-2.13</v>
+        <v>-0.59</v>
       </c>
       <c r="D23" s="7">
-        <v>-2.46</v>
-      </c>
-      <c r="E23" s="9">
-        <v>-0.33</v>
+        <v>-1.2</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-0.61</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="7">
-        <v>-1.88</v>
+        <v>2.05</v>
       </c>
       <c r="D24" s="7">
-        <v>-2.18</v>
+        <v>2.52</v>
       </c>
       <c r="E24" s="9">
-        <v>-0.3</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C25" s="7">
-        <v>-2.99</v>
+        <v>-2.46</v>
       </c>
       <c r="D25" s="7">
-        <v>-1.61</v>
-      </c>
-      <c r="E25" s="8">
-        <v>1.38</v>
+        <v>-1.03</v>
+      </c>
+      <c r="E25" s="9">
+        <v>1.43</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="6" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C26" s="7">
-        <v>2.11</v>
+        <v>-2.18</v>
       </c>
       <c r="D26" s="7">
-        <v>0.11</v>
+        <v>-1.18</v>
       </c>
       <c r="E26" s="9">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="6" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C27" s="7">
-        <v>0.86</v>
+        <v>-1.61</v>
       </c>
       <c r="D27" s="7">
-        <v>1.79</v>
-      </c>
-      <c r="E27" s="8">
-        <v>0.93</v>
+        <v>0.5</v>
+      </c>
+      <c r="E27" s="9">
+        <v>2.11</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="7">
-        <v>43.24</v>
+        <v>0.11</v>
       </c>
       <c r="D28" s="7">
-        <v>43.99</v>
+        <v>-0.37</v>
       </c>
       <c r="E28" s="8">
-        <v>0.75</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C29" s="7">
-        <v>11.18</v>
+        <v>1.79</v>
       </c>
       <c r="D29" s="7">
-        <v>7.33</v>
-      </c>
-      <c r="E29" s="9">
-        <v>-3.85</v>
+        <v>1.4</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-0.39</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C30" s="7">
-        <v>23.6</v>
+        <v>43.99</v>
       </c>
       <c r="D30" s="7">
-        <v>22.86</v>
-      </c>
-      <c r="E30" s="9">
-        <v>-0.74</v>
+        <v>42.73</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-1.26</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C31" s="7">
-        <v>-6.34</v>
+        <v>7.33</v>
       </c>
       <c r="D31" s="7">
-        <v>-6.26</v>
+        <v>6.24</v>
       </c>
       <c r="E31" s="8">
-        <v>0.08</v>
+        <v>-1.09</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C32" s="7">
-        <v>-37.42</v>
+        <v>22.86</v>
       </c>
       <c r="D32" s="7">
-        <v>-37.54</v>
+        <v>24.36</v>
       </c>
       <c r="E32" s="9">
-        <v>-0.12</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C33" s="7">
-        <v>-13.39</v>
+        <v>-6.26</v>
       </c>
       <c r="D33" s="7">
-        <v>-12.24</v>
+        <v>-6.6</v>
       </c>
       <c r="E33" s="8">
-        <v>1.15</v>
+        <v>-0.34</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C34" s="7">
-        <v>8.789999999999999</v>
+        <v>-37.54</v>
       </c>
       <c r="D34" s="7">
-        <v>6.94</v>
-      </c>
-      <c r="E34" s="9">
-        <v>-1.85</v>
+        <v>-39.72</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-2.18</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="6" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C35" s="7">
-        <v>-13.09</v>
+        <v>-12.24</v>
       </c>
       <c r="D35" s="7">
-        <v>-12.65</v>
+        <v>-12.72</v>
       </c>
       <c r="E35" s="8">
-        <v>0.44</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="6" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C36" s="7">
-        <v>8.699999999999999</v>
+        <v>6.94</v>
       </c>
       <c r="D36" s="7">
-        <v>9.869999999999999</v>
+        <v>6.07</v>
       </c>
       <c r="E36" s="8">
-        <v>1.17</v>
+        <v>-0.87</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C37" s="7">
-        <v>23.68</v>
+        <v>-12.65</v>
       </c>
       <c r="D37" s="7">
-        <v>24.12</v>
+        <v>-13.5</v>
       </c>
       <c r="E37" s="8">
-        <v>0.44</v>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C38" s="7">
-        <v>12.93</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="D38" s="7">
-        <v>11.09</v>
+        <v>10.3</v>
       </c>
       <c r="E38" s="9">
-        <v>-1.84</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C39" s="7">
-        <v>12.43</v>
+        <v>24.12</v>
       </c>
       <c r="D39" s="7">
-        <v>13.93</v>
-      </c>
-      <c r="E39" s="8">
-        <v>1.5</v>
+        <v>24.98</v>
+      </c>
+      <c r="E39" s="9">
+        <v>0.86</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C40" s="7">
-        <v>1.29</v>
+        <v>11.09</v>
       </c>
       <c r="D40" s="7">
-        <v>0.66</v>
-      </c>
-      <c r="E40" s="9">
-        <v>-0.63</v>
+        <v>10.07</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-1.02</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C41" s="7">
-        <v>-0.06</v>
+        <v>13.93</v>
       </c>
       <c r="D41" s="7">
-        <v>0.14</v>
-      </c>
-      <c r="E41" s="8">
-        <v>0.2</v>
+        <v>14.53</v>
+      </c>
+      <c r="E41" s="9">
+        <v>0.6</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C42" s="7">
-        <v>-4.58</v>
+        <v>0.66</v>
       </c>
       <c r="D42" s="7">
-        <v>-5.42</v>
-      </c>
-      <c r="E42" s="9">
-        <v>-0.84</v>
+        <v>0.21</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-0.45</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C43" s="7">
-        <v>10.34</v>
+        <v>0.14</v>
       </c>
       <c r="D43" s="7">
-        <v>8.59</v>
-      </c>
-      <c r="E43" s="9">
-        <v>-1.75</v>
+        <v>-0.04</v>
+      </c>
+      <c r="E43" s="8">
+        <v>-0.18</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="6" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C44" s="7">
-        <v>-18.19</v>
+        <v>-5.42</v>
       </c>
       <c r="D44" s="7">
-        <v>-18.53</v>
-      </c>
-      <c r="E44" s="9">
-        <v>-0.34</v>
+        <v>-5.87</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-0.45</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="6" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C45" s="7">
-        <v>-10.26</v>
+        <v>8.59</v>
       </c>
       <c r="D45" s="7">
-        <v>-10.21</v>
-      </c>
-      <c r="E45" s="8">
-        <v>0.05</v>
+        <v>9.91</v>
+      </c>
+      <c r="E45" s="9">
+        <v>1.32</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C46" s="7">
-        <v>-7.45</v>
+        <v>-18.53</v>
       </c>
       <c r="D46" s="7">
-        <v>-8.15</v>
-      </c>
-      <c r="E46" s="9">
+        <v>-19.23</v>
+      </c>
+      <c r="E46" s="8">
         <v>-0.7</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C47" s="7">
-        <v>-9.94</v>
+        <v>-10.21</v>
       </c>
       <c r="D47" s="7">
-        <v>-10.09</v>
+        <v>-9.449999999999999</v>
       </c>
       <c r="E47" s="9">
-        <v>-0.15</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C48" s="7">
-        <v>-9.390000000000001</v>
+        <v>-8.15</v>
       </c>
       <c r="D48" s="7">
-        <v>-8.949999999999999</v>
-      </c>
-      <c r="E48" s="8">
-        <v>0.44</v>
+        <v>-7.48</v>
+      </c>
+      <c r="E48" s="9">
+        <v>0.67</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C49" s="7">
-        <v>-6.95</v>
+        <v>-10.09</v>
       </c>
       <c r="D49" s="7">
-        <v>-6.86</v>
+        <v>-10.71</v>
       </c>
       <c r="E49" s="8">
-        <v>0.09</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C50" s="7">
-        <v>-38.98</v>
+        <v>-8.949999999999999</v>
       </c>
       <c r="D50" s="7">
-        <v>-39.19</v>
-      </c>
-      <c r="E50" s="9">
-        <v>-0.21</v>
+        <v>-9.710000000000001</v>
+      </c>
+      <c r="E50" s="8">
+        <v>-0.76</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C51" s="7">
-        <v>-20.63</v>
+        <v>-6.86</v>
       </c>
       <c r="D51" s="7">
-        <v>-20.87</v>
+        <v>-5.7</v>
       </c>
       <c r="E51" s="9">
-        <v>-0.24</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="6" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C52" s="7">
-        <v>401.05</v>
+        <v>-39.19</v>
       </c>
       <c r="D52" s="7">
-        <v>399.35</v>
-      </c>
-      <c r="E52" s="9">
-        <v>-1.7</v>
+        <v>-39.53</v>
+      </c>
+      <c r="E52" s="8">
+        <v>-0.34</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="6" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C53" s="7">
-        <v>3412.2</v>
+        <v>-20.87</v>
       </c>
       <c r="D53" s="7">
-        <v>3414.1</v>
+        <v>-21.03</v>
       </c>
       <c r="E53" s="8">
-        <v>1.9</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="6" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C54" s="7">
-        <v>381.6</v>
+        <v>-10.43</v>
       </c>
       <c r="D54" s="7">
-        <v>378.7</v>
+        <v>-9.529999999999999</v>
       </c>
       <c r="E54" s="9">
-        <v>-2.9</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="6" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C55" s="7">
-        <v>379.8</v>
+        <v>399.35</v>
       </c>
       <c r="D55" s="7">
-        <v>379.15</v>
-      </c>
-      <c r="E55" s="9">
-        <v>-0.65</v>
+        <v>395.95</v>
+      </c>
+      <c r="E55" s="8">
+        <v>-3.4</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="6" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C56" s="7">
-        <v>401.15</v>
+        <v>3414.1</v>
       </c>
       <c r="D56" s="7">
-        <v>403.1</v>
-      </c>
-      <c r="E56" s="8">
-        <v>1.95</v>
+        <v>3443</v>
+      </c>
+      <c r="E56" s="9">
+        <v>28.9</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="6" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C57" s="7">
-        <v>634.15</v>
+        <v>378.7</v>
       </c>
       <c r="D57" s="7">
-        <v>634.75</v>
-      </c>
-      <c r="E57" s="8">
-        <v>0.6</v>
+        <v>381.45</v>
+      </c>
+      <c r="E57" s="9">
+        <v>2.75</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C58" s="7">
-        <v>221.79</v>
+        <v>379.15</v>
       </c>
       <c r="D58" s="7">
-        <v>221.05</v>
-      </c>
-      <c r="E58" s="9">
-        <v>-0.74</v>
+        <v>376.55</v>
+      </c>
+      <c r="E58" s="8">
+        <v>-2.6</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="6" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C59" s="7">
-        <v>3569.8</v>
+        <v>403.1</v>
       </c>
       <c r="D59" s="7">
-        <v>3558.9</v>
-      </c>
-      <c r="E59" s="9">
-        <v>-10.9</v>
+        <v>399.7</v>
+      </c>
+      <c r="E59" s="8">
+        <v>-3.4</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="6" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C60" s="7">
-        <v>32.4</v>
+        <v>634.75</v>
       </c>
       <c r="D60" s="7">
-        <v>31.42</v>
+        <v>636.55</v>
       </c>
       <c r="E60" s="9">
-        <v>-0.98</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="6" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C61" s="7">
-        <v>56.87</v>
+        <v>221.05</v>
       </c>
       <c r="D61" s="7">
-        <v>57.05</v>
+        <v>219.1</v>
       </c>
       <c r="E61" s="8">
-        <v>0.18</v>
+        <v>-1.95</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="6" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C62" s="7">
-        <v>52.44</v>
+        <v>3558.9</v>
       </c>
       <c r="D62" s="7">
-        <v>50.71</v>
-      </c>
-      <c r="E62" s="9">
-        <v>-1.73</v>
+        <v>3551.7</v>
+      </c>
+      <c r="E62" s="8">
+        <v>-7.2</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="6" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C63" s="7">
-        <v>50.06</v>
+        <v>1584</v>
       </c>
       <c r="D63" s="7">
-        <v>49.39</v>
+        <v>1599.9</v>
       </c>
       <c r="E63" s="9">
-        <v>-0.67</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C64" s="7">
-        <v>48.79</v>
+        <v>77</v>
       </c>
       <c r="D64" s="7">
-        <v>50.52</v>
+        <v>66</v>
       </c>
       <c r="E64" s="8">
-        <v>1.73</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C65" s="7">
         <v>66</v>
       </c>
       <c r="D65" s="7">
-        <v>66.2</v>
-      </c>
-      <c r="E65" s="8">
-        <v>0.2</v>
+        <v>77</v>
+      </c>
+      <c r="E65" s="9">
+        <v>11</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B66" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C66" s="7">
-        <v>45.66</v>
+        <v>31.42</v>
       </c>
       <c r="D66" s="7">
-        <v>44.71</v>
-      </c>
-      <c r="E66" s="9">
-        <v>-0.95</v>
+        <v>29.49</v>
+      </c>
+      <c r="E66" s="8">
+        <v>-1.93</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="6" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B67" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C67" s="7">
-        <v>37.68</v>
+        <v>57.05</v>
       </c>
       <c r="D67" s="7">
-        <v>36.23</v>
+        <v>59.77</v>
       </c>
       <c r="E67" s="9">
-        <v>-1.45</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C68" s="7">
-        <v>-66.62</v>
+        <v>50.71</v>
       </c>
       <c r="D68" s="7">
-        <v>-47.59</v>
-      </c>
-      <c r="E68" s="8">
-        <v>19.03</v>
+        <v>52.32</v>
+      </c>
+      <c r="E68" s="9">
+        <v>1.61</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C69" s="7">
-        <v>-29.3</v>
+        <v>49.39</v>
       </c>
       <c r="D69" s="7">
-        <v>-51.31</v>
-      </c>
-      <c r="E69" s="9">
-        <v>-22.01</v>
+        <v>46.68</v>
+      </c>
+      <c r="E69" s="8">
+        <v>-2.71</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C70" s="7">
-        <v>-64.51000000000001</v>
+        <v>50.52</v>
       </c>
       <c r="D70" s="7">
-        <v>-54.04</v>
+        <v>47.5</v>
       </c>
       <c r="E70" s="8">
-        <v>10.47</v>
+        <v>-3.02</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C71" s="7">
-        <v>-77.36</v>
+        <v>66.2</v>
       </c>
       <c r="D71" s="7">
-        <v>-46.89</v>
-      </c>
-      <c r="E71" s="8">
-        <v>30.47</v>
+        <v>66.84</v>
+      </c>
+      <c r="E71" s="9">
+        <v>0.64</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C72" s="7">
-        <v>-65.34</v>
+        <v>44.71</v>
       </c>
       <c r="D72" s="7">
-        <v>-69.33</v>
-      </c>
-      <c r="E72" s="9">
-        <v>-3.99</v>
+        <v>42.22</v>
+      </c>
+      <c r="E72" s="8">
+        <v>-2.49</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C73" s="7">
-        <v>739.46</v>
+        <v>36.23</v>
       </c>
       <c r="D73" s="7">
-        <v>19.52</v>
-      </c>
-      <c r="E73" s="9">
-        <v>-719.9400000000001</v>
+        <v>35.27</v>
+      </c>
+      <c r="E73" s="8">
+        <v>-0.96</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C74" s="7">
-        <v>-50.76</v>
+        <v>47.96</v>
       </c>
       <c r="D74" s="7">
-        <v>-44.95</v>
-      </c>
-      <c r="E74" s="8">
-        <v>5.81</v>
+        <v>52.65</v>
+      </c>
+      <c r="E74" s="9">
+        <v>4.69</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="6" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B75" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C75" s="7">
-        <v>-30.95</v>
+        <v>-47.59</v>
       </c>
       <c r="D75" s="7">
-        <v>-26.98</v>
-      </c>
-      <c r="E75" s="8">
-        <v>3.97</v>
+        <v>-15.16</v>
+      </c>
+      <c r="E75" s="9">
+        <v>32.43</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="6" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C76" s="7">
-        <v>-53.73</v>
+        <v>-51.31</v>
       </c>
       <c r="D76" s="7">
+        <v>-54.24</v>
+      </c>
+      <c r="E76" s="8">
+        <v>-2.93</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B77" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="7">
+        <v>-54.04</v>
+      </c>
+      <c r="D77" s="7">
+        <v>-40</v>
+      </c>
+      <c r="E77" s="9">
+        <v>14.04</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B78" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="7">
+        <v>-46.89</v>
+      </c>
+      <c r="D78" s="7">
+        <v>-48.79</v>
+      </c>
+      <c r="E78" s="8">
+        <v>-1.9</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B79" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="7">
+        <v>-69.33</v>
+      </c>
+      <c r="D79" s="7">
+        <v>-57.86</v>
+      </c>
+      <c r="E79" s="9">
+        <v>11.47</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B80" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="7">
+        <v>19.52</v>
+      </c>
+      <c r="D80" s="7">
+        <v>80.22</v>
+      </c>
+      <c r="E80" s="9">
+        <v>60.7</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B81" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81" s="7">
+        <v>-44.95</v>
+      </c>
+      <c r="D81" s="7">
+        <v>-18.78</v>
+      </c>
+      <c r="E81" s="9">
+        <v>26.17</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C82" s="7">
+        <v>-26.98</v>
+      </c>
+      <c r="D82" s="7">
+        <v>-47.39</v>
+      </c>
+      <c r="E82" s="8">
+        <v>-20.41</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B83" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C83" s="7">
         <v>-21.82</v>
       </c>
-      <c r="E76" s="8">
-        <v>31.91</v>
+      <c r="D83" s="7">
+        <v>-51.59</v>
+      </c>
+      <c r="E83" s="8">
+        <v>-29.77</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A8:E8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3394,28 +3525,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3429,13 +3560,13 @@
         <v>9</v>
       </c>
       <c r="D2" s="12">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
       <c r="E2" s="12">
         <v>70</v>
       </c>
       <c r="F2" s="12">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="G2" s="12">
         <v>5.6</v>
@@ -3444,7 +3575,7 @@
         <v>55.4</v>
       </c>
       <c r="I2" s="12">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -3575,31 +3706,31 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="15">
-        <v>0.3539</v>
+        <v>0.3583</v>
       </c>
       <c r="B2" s="15">
-        <v>0.3334</v>
+        <v>0.3376</v>
       </c>
       <c r="C2" s="15">
-        <v>0.2291</v>
+        <v>0.2299</v>
       </c>
       <c r="D2" s="15">
-        <v>0.1993</v>
+        <v>0.1994</v>
       </c>
       <c r="E2" s="15">
-        <v>0.1397</v>
+        <v>0.133</v>
       </c>
       <c r="F2" s="15">
-        <v>0.0922</v>
+        <v>0.09119999999999999</v>
       </c>
       <c r="G2" s="15">
-        <v>0.0466</v>
+        <v>0.0488</v>
       </c>
       <c r="H2" s="15">
-        <v>0.0122</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="I2" s="15">
-        <v>-0.1113</v>
+        <v>-0.1105</v>
       </c>
     </row>
   </sheetData>

--- a/MAHINDRA_GROUP_Technical_Metrics.xlsx
+++ b/MAHINDRA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="80">
   <si>
     <t>Symbol</t>
   </si>
@@ -193,37 +193,34 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>No → Yes</t>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>29.5 → 30.9</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>20 DMA &gt; 50 DMA</t>
+    <t>29.5</t>
+  </si>
+  <si>
+    <t>30.9</t>
   </si>
   <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>48.0 → 52.6</t>
-  </si>
-  <si>
-    <t>48.0</t>
+    <t>52.6 → 44.8</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
   </si>
   <si>
     <t>52.6</t>
   </si>
   <si>
-    <t>50.5 → 47.5</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>50.5</t>
-  </si>
-  <si>
-    <t>47.5</t>
+    <t>44.8</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -436,8 +433,8 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -949,10 +946,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>395.95</v>
+        <v>397</v>
       </c>
       <c r="D2">
-        <v>-0.85</v>
+        <v>0.27</v>
       </c>
       <c r="E2">
         <v>490.2</v>
@@ -961,25 +958,25 @@
         <v>379.2</v>
       </c>
       <c r="G2">
-        <v>-19.23</v>
+        <v>-19.01</v>
       </c>
       <c r="H2">
-        <v>4.42</v>
+        <v>4.69</v>
       </c>
       <c r="I2">
-        <v>-3.36</v>
+        <v>-2.37</v>
       </c>
       <c r="J2">
-        <v>-4.22</v>
+        <v>-2.77</v>
       </c>
       <c r="K2">
-        <v>-13.5</v>
+        <v>-13.27</v>
       </c>
       <c r="L2">
-        <v>-0.37</v>
+        <v>0.38</v>
       </c>
       <c r="M2">
-        <v>13.3</v>
+        <v>12.64</v>
       </c>
       <c r="N2">
         <v>34</v>
@@ -988,19 +985,19 @@
         <v>40</v>
       </c>
       <c r="P2">
-        <v>401.36</v>
+        <v>399.43</v>
       </c>
       <c r="Q2">
-        <v>408.81</v>
+        <v>407.92</v>
       </c>
       <c r="R2">
-        <v>438.99</v>
+        <v>437.55</v>
       </c>
       <c r="S2">
-        <v>437.53</v>
+        <v>437.39</v>
       </c>
       <c r="T2">
-        <v>-9.5</v>
+        <v>-9.23</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1015,43 +1012,43 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>29.49</v>
+        <v>30.9</v>
       </c>
       <c r="Z2">
-        <v>-10.59</v>
+        <v>-10.51</v>
       </c>
       <c r="AA2">
-        <v>-10.93</v>
+        <v>-10.85</v>
       </c>
       <c r="AB2">
         <v>0.34</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>5.41</v>
       </c>
       <c r="AD2">
-        <v>7.6</v>
+        <v>1.8</v>
       </c>
       <c r="AE2">
-        <v>9.470000000000001</v>
+        <v>9.24</v>
       </c>
       <c r="AF2">
-        <v>-15.16</v>
+        <v>-28.21</v>
       </c>
       <c r="AG2">
-        <v>419.89</v>
+        <v>419.82</v>
       </c>
       <c r="AH2">
-        <v>397.72</v>
+        <v>396.02</v>
       </c>
       <c r="AI2">
-        <v>426.18</v>
+        <v>423.49</v>
       </c>
       <c r="AJ2" t="s">
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>41.04</v>
+        <v>44.37</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1062,10 +1059,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>3443</v>
+        <v>3398.2</v>
       </c>
       <c r="D3">
-        <v>0.85</v>
+        <v>-1.3</v>
       </c>
       <c r="E3">
         <v>3802.4</v>
@@ -1074,46 +1071,46 @@
         <v>2931.1</v>
       </c>
       <c r="G3">
-        <v>-9.449999999999999</v>
+        <v>-10.63</v>
       </c>
       <c r="H3">
-        <v>17.46</v>
+        <v>15.94</v>
       </c>
       <c r="I3">
-        <v>0.63</v>
+        <v>-0.49</v>
       </c>
       <c r="J3">
-        <v>6.31</v>
+        <v>3.88</v>
       </c>
       <c r="K3">
-        <v>10.3</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="L3">
-        <v>1.4</v>
+        <v>0.68</v>
       </c>
       <c r="M3">
-        <v>35.83</v>
+        <v>35.15</v>
       </c>
       <c r="N3">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="O3">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="P3">
-        <v>3421.82</v>
+        <v>3418.46</v>
       </c>
       <c r="Q3">
-        <v>3414.36</v>
+        <v>3423.18</v>
       </c>
       <c r="R3">
-        <v>3249.59</v>
+        <v>3254.8</v>
       </c>
       <c r="S3">
-        <v>3351.58</v>
+        <v>3350.12</v>
       </c>
       <c r="T3">
-        <v>2.73</v>
+        <v>1.44</v>
       </c>
       <c r="U3" t="s">
         <v>48</v>
@@ -1128,34 +1125,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>59.77</v>
+        <v>54.04</v>
       </c>
       <c r="Z3">
-        <v>51.42</v>
+        <v>46.23</v>
       </c>
       <c r="AA3">
-        <v>62.19</v>
+        <v>59</v>
       </c>
       <c r="AB3">
-        <v>-10.76</v>
+        <v>-12.77</v>
       </c>
       <c r="AC3">
-        <v>14.73</v>
+        <v>12.33</v>
       </c>
       <c r="AD3">
-        <v>12.84</v>
+        <v>12.78</v>
       </c>
       <c r="AE3">
-        <v>63.71</v>
+        <v>62.7</v>
       </c>
       <c r="AF3">
-        <v>-54.24</v>
+        <v>-70.08</v>
       </c>
       <c r="AG3">
-        <v>3543.39</v>
+        <v>3515.75</v>
       </c>
       <c r="AH3">
-        <v>3285.33</v>
+        <v>3330.61</v>
       </c>
       <c r="AI3">
         <v>3274.47</v>
@@ -1164,7 +1161,7 @@
         <v>50</v>
       </c>
       <c r="AK3">
-        <v>24.37</v>
+        <v>22.68</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1175,10 +1172,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>381.45</v>
+        <v>385.35</v>
       </c>
       <c r="D4">
-        <v>0.73</v>
+        <v>1.02</v>
       </c>
       <c r="E4">
         <v>412.3</v>
@@ -1187,25 +1184,25 @@
         <v>253.95</v>
       </c>
       <c r="G4">
-        <v>-7.48</v>
+        <v>-6.54</v>
       </c>
       <c r="H4">
-        <v>50.21</v>
+        <v>51.74</v>
       </c>
       <c r="I4">
-        <v>-1.23</v>
+        <v>-1.09</v>
       </c>
       <c r="J4">
-        <v>5.08</v>
+        <v>3.17</v>
       </c>
       <c r="K4">
-        <v>24.98</v>
+        <v>26.26</v>
       </c>
       <c r="L4">
-        <v>42.73</v>
+        <v>47.79</v>
       </c>
       <c r="M4">
-        <v>22.99</v>
+        <v>21.91</v>
       </c>
       <c r="N4">
         <v>99</v>
@@ -1214,19 +1211,19 @@
         <v>87</v>
       </c>
       <c r="P4">
-        <v>382.76</v>
+        <v>381.91</v>
       </c>
       <c r="Q4">
-        <v>392.71</v>
+        <v>392.29</v>
       </c>
       <c r="R4">
-        <v>353.57</v>
+        <v>355.32</v>
       </c>
       <c r="S4">
-        <v>341.71</v>
+        <v>342.07</v>
       </c>
       <c r="T4">
-        <v>11.63</v>
+        <v>12.65</v>
       </c>
       <c r="U4" t="s">
         <v>48</v>
@@ -1241,34 +1238,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>52.32</v>
+        <v>54.58</v>
       </c>
       <c r="Z4">
-        <v>7.29</v>
+        <v>6.71</v>
       </c>
       <c r="AA4">
-        <v>11.98</v>
+        <v>10.93</v>
       </c>
       <c r="AB4">
-        <v>-4.69</v>
+        <v>-4.22</v>
       </c>
       <c r="AC4">
-        <v>2.82</v>
+        <v>9.6</v>
       </c>
       <c r="AD4">
-        <v>1.94</v>
+        <v>4.14</v>
       </c>
       <c r="AE4">
-        <v>13.22</v>
+        <v>12.84</v>
       </c>
       <c r="AF4">
-        <v>-40</v>
+        <v>-36.87</v>
       </c>
       <c r="AG4">
-        <v>411.13</v>
+        <v>410.99</v>
       </c>
       <c r="AH4">
-        <v>374.28</v>
+        <v>373.58</v>
       </c>
       <c r="AI4">
         <v>357.72</v>
@@ -1277,7 +1274,7 @@
         <v>50</v>
       </c>
       <c r="AK4">
-        <v>23.1</v>
+        <v>23.46</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1288,10 +1285,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>376.55</v>
+        <v>371.25</v>
       </c>
       <c r="D5">
-        <v>-0.6899999999999999</v>
+        <v>-1.41</v>
       </c>
       <c r="E5">
         <v>421.7</v>
@@ -1300,46 +1297,46 @@
         <v>294.25</v>
       </c>
       <c r="G5">
-        <v>-10.71</v>
+        <v>-11.96</v>
       </c>
       <c r="H5">
-        <v>27.97</v>
+        <v>26.17</v>
       </c>
       <c r="I5">
-        <v>-1.98</v>
+        <v>-0.66</v>
       </c>
       <c r="J5">
-        <v>-0.97</v>
+        <v>-2.37</v>
       </c>
       <c r="K5">
-        <v>10.07</v>
+        <v>8.52</v>
       </c>
       <c r="L5">
-        <v>6.24</v>
+        <v>6.73</v>
       </c>
       <c r="M5">
-        <v>9.119999999999999</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="N5">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="O5">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="P5">
-        <v>377.28</v>
+        <v>376.79</v>
       </c>
       <c r="Q5">
-        <v>384.76</v>
+        <v>383.95</v>
       </c>
       <c r="R5">
-        <v>374.59</v>
+        <v>375.16</v>
       </c>
       <c r="S5">
-        <v>364.47</v>
+        <v>364.34</v>
       </c>
       <c r="T5">
-        <v>3.31</v>
+        <v>1.9</v>
       </c>
       <c r="U5" t="s">
         <v>48</v>
@@ -1354,34 +1351,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>46.68</v>
+        <v>41.66</v>
       </c>
       <c r="Z5">
-        <v>0.98</v>
+        <v>0.15</v>
       </c>
       <c r="AA5">
-        <v>2.92</v>
+        <v>2.36</v>
       </c>
       <c r="AB5">
-        <v>-1.94</v>
+        <v>-2.21</v>
       </c>
       <c r="AC5">
-        <v>28.09</v>
+        <v>20.26</v>
       </c>
       <c r="AD5">
-        <v>21.96</v>
+        <v>24.62</v>
       </c>
       <c r="AE5">
-        <v>10.56</v>
+        <v>10.69</v>
       </c>
       <c r="AF5">
-        <v>-48.79</v>
+        <v>-32.18</v>
       </c>
       <c r="AG5">
-        <v>397.28</v>
+        <v>397.78</v>
       </c>
       <c r="AH5">
-        <v>372.24</v>
+        <v>370.13</v>
       </c>
       <c r="AI5">
         <v>364.94</v>
@@ -1390,7 +1387,7 @@
         <v>50</v>
       </c>
       <c r="AK5">
-        <v>26.67</v>
+        <v>28.01</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1401,10 +1398,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>399.7</v>
+        <v>399.4</v>
       </c>
       <c r="D6">
-        <v>-0.84</v>
+        <v>-0.08</v>
       </c>
       <c r="E6">
         <v>442.7</v>
@@ -1413,46 +1410,46 @@
         <v>279.55</v>
       </c>
       <c r="G6">
-        <v>-9.710000000000001</v>
+        <v>-9.779999999999999</v>
       </c>
       <c r="H6">
-        <v>42.98</v>
+        <v>42.87</v>
       </c>
       <c r="I6">
-        <v>-1.2</v>
+        <v>-1.69</v>
       </c>
       <c r="J6">
-        <v>-4.63</v>
+        <v>-2.68</v>
       </c>
       <c r="K6">
-        <v>14.53</v>
+        <v>14.44</v>
       </c>
       <c r="L6">
-        <v>24.36</v>
+        <v>22.8</v>
       </c>
       <c r="M6">
-        <v>-11.05</v>
+        <v>-11.07</v>
       </c>
       <c r="N6">
         <v>88</v>
       </c>
       <c r="O6">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P6">
-        <v>403.37</v>
+        <v>402</v>
       </c>
       <c r="Q6">
-        <v>407.75</v>
+        <v>407.25</v>
       </c>
       <c r="R6">
-        <v>393.32</v>
+        <v>394.42</v>
       </c>
       <c r="S6">
-        <v>365.6</v>
+        <v>365.89</v>
       </c>
       <c r="T6">
-        <v>9.33</v>
+        <v>9.16</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1467,34 +1464,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>47.5</v>
+        <v>47.24</v>
       </c>
       <c r="Z6">
-        <v>1.96</v>
+        <v>1.4</v>
       </c>
       <c r="AA6">
-        <v>4.12</v>
+        <v>3.57</v>
       </c>
       <c r="AB6">
-        <v>-2.16</v>
+        <v>-2.17</v>
       </c>
       <c r="AC6">
         <v>5.38</v>
       </c>
       <c r="AD6">
-        <v>7.65</v>
+        <v>6.83</v>
       </c>
       <c r="AE6">
-        <v>11.58</v>
+        <v>11.99</v>
       </c>
       <c r="AF6">
-        <v>-57.86</v>
+        <v>3.22</v>
       </c>
       <c r="AG6">
-        <v>418.51</v>
+        <v>418.6</v>
       </c>
       <c r="AH6">
-        <v>396.99</v>
+        <v>395.9</v>
       </c>
       <c r="AI6">
         <v>372.35</v>
@@ -1503,7 +1500,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>18.97</v>
+        <v>17.42</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1517,55 +1514,55 @@
         <v>636.55</v>
       </c>
       <c r="D7">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>675.05</v>
+        <v>668</v>
       </c>
       <c r="F7">
         <v>506.45</v>
       </c>
       <c r="G7">
-        <v>-5.7</v>
+        <v>-4.71</v>
       </c>
       <c r="H7">
         <v>25.69</v>
       </c>
       <c r="I7">
-        <v>2.52</v>
+        <v>3.69</v>
       </c>
       <c r="J7">
-        <v>10.35</v>
+        <v>10.88</v>
       </c>
       <c r="K7">
         <v>0.21</v>
       </c>
       <c r="L7">
-        <v>-6.6</v>
+        <v>-5.7</v>
       </c>
       <c r="M7">
-        <v>33.76</v>
+        <v>33.83</v>
       </c>
       <c r="N7">
         <v>45</v>
       </c>
       <c r="O7">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="P7">
-        <v>625.99</v>
+        <v>630.52</v>
       </c>
       <c r="Q7">
-        <v>601.9400000000001</v>
+        <v>604.67</v>
       </c>
       <c r="R7">
-        <v>601.48</v>
+        <v>601.73</v>
       </c>
       <c r="S7">
-        <v>583.3</v>
+        <v>583.74</v>
       </c>
       <c r="T7">
-        <v>9.130000000000001</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="U7" t="s">
         <v>48</v>
@@ -1583,31 +1580,31 @@
         <v>66.84</v>
       </c>
       <c r="Z7">
-        <v>10.77</v>
+        <v>11.49</v>
       </c>
       <c r="AA7">
-        <v>6.17</v>
+        <v>7.23</v>
       </c>
       <c r="AB7">
-        <v>4.6</v>
+        <v>4.26</v>
       </c>
       <c r="AC7">
         <v>100</v>
       </c>
       <c r="AD7">
-        <v>90.16</v>
+        <v>96.18000000000001</v>
       </c>
       <c r="AE7">
-        <v>17.44</v>
+        <v>17.1</v>
       </c>
       <c r="AF7">
-        <v>80.22</v>
+        <v>21.31</v>
       </c>
       <c r="AG7">
-        <v>646.49</v>
+        <v>650.72</v>
       </c>
       <c r="AH7">
-        <v>557.4</v>
+        <v>558.62</v>
       </c>
       <c r="AI7">
         <v>591.65</v>
@@ -1616,7 +1613,7 @@
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>56.86</v>
+        <v>59.41</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1627,58 +1624,58 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>219.1</v>
+        <v>218.19</v>
       </c>
       <c r="D8">
-        <v>-0.88</v>
+        <v>-0.42</v>
       </c>
       <c r="E8">
-        <v>362.35</v>
+        <v>362.05</v>
       </c>
       <c r="F8">
         <v>210.4</v>
       </c>
       <c r="G8">
-        <v>-39.53</v>
+        <v>-39.73</v>
       </c>
       <c r="H8">
-        <v>4.13</v>
+        <v>3.7</v>
       </c>
       <c r="I8">
-        <v>-1.03</v>
+        <v>-0.59</v>
       </c>
       <c r="J8">
-        <v>-2.11</v>
+        <v>-0.04</v>
       </c>
       <c r="K8">
-        <v>-0.04</v>
+        <v>-0.45</v>
       </c>
       <c r="L8">
-        <v>-39.72</v>
+        <v>-39.78</v>
       </c>
       <c r="M8">
-        <v>0.87</v>
+        <v>1.31</v>
       </c>
       <c r="N8">
         <v>12</v>
       </c>
       <c r="O8">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P8">
-        <v>220.49</v>
+        <v>220.24</v>
       </c>
       <c r="Q8">
-        <v>223.59</v>
+        <v>223.75</v>
       </c>
       <c r="R8">
-        <v>228</v>
+        <v>227.74</v>
       </c>
       <c r="S8">
-        <v>264.5</v>
+        <v>264</v>
       </c>
       <c r="T8">
-        <v>-17.17</v>
+        <v>-17.35</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1693,34 +1690,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>42.22</v>
+        <v>41.07</v>
       </c>
       <c r="Z8">
-        <v>-1.56</v>
+        <v>-1.79</v>
       </c>
       <c r="AA8">
-        <v>-1.13</v>
+        <v>-1.26</v>
       </c>
       <c r="AB8">
-        <v>-0.43</v>
+        <v>-0.52</v>
       </c>
       <c r="AC8">
-        <v>12.42</v>
+        <v>5.2</v>
       </c>
       <c r="AD8">
-        <v>13.95</v>
+        <v>11.65</v>
       </c>
       <c r="AE8">
-        <v>6.42</v>
+        <v>6.39</v>
       </c>
       <c r="AF8">
-        <v>-18.78</v>
+        <v>-2.37</v>
       </c>
       <c r="AG8">
-        <v>233.99</v>
+        <v>233.67</v>
       </c>
       <c r="AH8">
-        <v>213.19</v>
+        <v>213.84</v>
       </c>
       <c r="AI8">
         <v>237.22</v>
@@ -1729,7 +1726,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>22.35</v>
+        <v>22.59</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1740,10 +1737,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>3551.7</v>
+        <v>3549</v>
       </c>
       <c r="D9">
-        <v>-0.2</v>
+        <v>-0.08</v>
       </c>
       <c r="E9">
         <v>4497.5</v>
@@ -1752,25 +1749,25 @@
         <v>3308.9</v>
       </c>
       <c r="G9">
-        <v>-21.03</v>
+        <v>-21.09</v>
       </c>
       <c r="H9">
-        <v>7.34</v>
+        <v>7.26</v>
       </c>
       <c r="I9">
-        <v>-1.18</v>
+        <v>-1.11</v>
       </c>
       <c r="J9">
-        <v>-1.49</v>
+        <v>-0.26</v>
       </c>
       <c r="K9">
-        <v>-5.87</v>
+        <v>-5.94</v>
       </c>
       <c r="L9">
-        <v>-12.72</v>
+        <v>-13.9</v>
       </c>
       <c r="M9">
-        <v>19.94</v>
+        <v>19.93</v>
       </c>
       <c r="N9">
         <v>23</v>
@@ -1779,19 +1776,19 @@
         <v>36</v>
       </c>
       <c r="P9">
-        <v>3574.36</v>
+        <v>3566.4</v>
       </c>
       <c r="Q9">
-        <v>3600.39</v>
+        <v>3599.45</v>
       </c>
       <c r="R9">
-        <v>3722.65</v>
+        <v>3716.49</v>
       </c>
       <c r="S9">
-        <v>3703.21</v>
+        <v>3701.49</v>
       </c>
       <c r="T9">
-        <v>-4.09</v>
+        <v>-4.12</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1806,43 +1803,43 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>35.27</v>
+        <v>34.89</v>
       </c>
       <c r="Z9">
-        <v>-33.15</v>
+        <v>-33.98</v>
       </c>
       <c r="AA9">
-        <v>-34.91</v>
+        <v>-34.73</v>
       </c>
       <c r="AB9">
-        <v>1.76</v>
+        <v>0.75</v>
       </c>
       <c r="AC9">
         <v>0</v>
       </c>
       <c r="AD9">
-        <v>11.3</v>
+        <v>5.08</v>
       </c>
       <c r="AE9">
-        <v>53.07</v>
+        <v>51.37</v>
       </c>
       <c r="AF9">
-        <v>-47.39</v>
+        <v>-28.48</v>
       </c>
       <c r="AG9">
-        <v>3649.36</v>
+        <v>3651.67</v>
       </c>
       <c r="AH9">
-        <v>3551.42</v>
+        <v>3547.23</v>
       </c>
       <c r="AI9">
-        <v>3713.31</v>
+        <v>3708.5</v>
       </c>
       <c r="AJ9" t="s">
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>13.07</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1853,10 +1850,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>1599.9</v>
+        <v>1571</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>-1.81</v>
       </c>
       <c r="E10">
         <v>1768.4</v>
@@ -1865,46 +1862,46 @@
         <v>1326.2</v>
       </c>
       <c r="G10">
-        <v>-9.529999999999999</v>
+        <v>-11.16</v>
       </c>
       <c r="H10">
-        <v>20.64</v>
+        <v>18.46</v>
       </c>
       <c r="I10">
-        <v>0.5</v>
+        <v>-1.18</v>
       </c>
       <c r="J10">
-        <v>1.58</v>
+        <v>-3.93</v>
       </c>
       <c r="K10">
-        <v>9.91</v>
+        <v>7.93</v>
       </c>
       <c r="L10">
-        <v>6.07</v>
+        <v>4.35</v>
       </c>
       <c r="M10">
-        <v>4.88</v>
+        <v>4.69</v>
       </c>
       <c r="N10">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="O10">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="P10">
-        <v>1589.96</v>
+        <v>1586.2</v>
       </c>
       <c r="Q10">
-        <v>1625.54</v>
+        <v>1621.88</v>
       </c>
       <c r="R10">
-        <v>1535.93</v>
+        <v>1538.41</v>
       </c>
       <c r="S10">
-        <v>1508.92</v>
+        <v>1509.84</v>
       </c>
       <c r="T10">
-        <v>6.03</v>
+        <v>4.05</v>
       </c>
       <c r="U10" t="s">
         <v>48</v>
@@ -1919,34 +1916,34 @@
         <v>3</v>
       </c>
       <c r="Y10">
-        <v>52.65</v>
+        <v>44.76</v>
       </c>
       <c r="Z10">
-        <v>10.86</v>
+        <v>7.46</v>
       </c>
       <c r="AA10">
-        <v>21.99</v>
+        <v>19.08</v>
       </c>
       <c r="AB10">
-        <v>-11.13</v>
+        <v>-11.63</v>
       </c>
       <c r="AC10">
         <v>8.74</v>
       </c>
       <c r="AD10">
-        <v>3.61</v>
+        <v>6.18</v>
       </c>
       <c r="AE10">
-        <v>35.77</v>
+        <v>36.73</v>
       </c>
       <c r="AF10">
-        <v>-51.59</v>
+        <v>-42.47</v>
       </c>
       <c r="AG10">
-        <v>1678.51</v>
+        <v>1679.35</v>
       </c>
       <c r="AH10">
-        <v>1572.57</v>
+        <v>1564.41</v>
       </c>
       <c r="AI10">
         <v>1527.05</v>
@@ -1955,7 +1952,7 @@
         <v>50</v>
       </c>
       <c r="AK10">
-        <v>39.25</v>
+        <v>37.85</v>
       </c>
     </row>
   </sheetData>
@@ -2096,7 +2093,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F83"/>
+  <dimension ref="A1:F79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2136,1372 +2133,1298 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="4" t="s">
+      <c r="A4" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E5" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>63</v>
       </c>
+      <c r="D4" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="F6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>67</v>
       </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
+      <c r="A8" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="7">
+        <v>-4.22</v>
+      </c>
+      <c r="D8" s="7">
+        <v>-2.77</v>
+      </c>
+      <c r="E8" s="8">
+        <v>1.45</v>
+      </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>72</v>
+      <c r="A9" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="7">
+        <v>6.31</v>
+      </c>
+      <c r="D9" s="7">
+        <v>3.88</v>
+      </c>
+      <c r="E9" s="9">
+        <v>-2.43</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="7">
-        <v>-3.48</v>
+        <v>5.08</v>
       </c>
       <c r="D10" s="7">
-        <v>-4.22</v>
-      </c>
-      <c r="E10" s="8">
-        <v>-0.74</v>
+        <v>3.17</v>
+      </c>
+      <c r="E10" s="9">
+        <v>-1.91</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="7">
-        <v>7.99</v>
+        <v>-0.97</v>
       </c>
       <c r="D11" s="7">
-        <v>6.31</v>
-      </c>
-      <c r="E11" s="8">
-        <v>-1.68</v>
+        <v>-2.37</v>
+      </c>
+      <c r="E11" s="9">
+        <v>-1.4</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="7">
-        <v>6.23</v>
+        <v>-4.63</v>
       </c>
       <c r="D12" s="7">
-        <v>5.08</v>
+        <v>-2.68</v>
       </c>
       <c r="E12" s="8">
-        <v>-1.15</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="7">
-        <v>1.2</v>
+        <v>10.35</v>
       </c>
       <c r="D13" s="7">
-        <v>-0.97</v>
+        <v>10.88</v>
       </c>
       <c r="E13" s="8">
-        <v>-2.17</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="7">
-        <v>-3.18</v>
+        <v>-2.11</v>
       </c>
       <c r="D14" s="7">
-        <v>-4.63</v>
+        <v>-0.04</v>
       </c>
       <c r="E14" s="8">
-        <v>-1.45</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="7">
-        <v>11.06</v>
+        <v>-1.49</v>
       </c>
       <c r="D15" s="7">
-        <v>10.35</v>
+        <v>-0.26</v>
       </c>
       <c r="E15" s="8">
-        <v>-0.71</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="7">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="D16" s="7">
-        <v>-2.11</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-3.12</v>
+        <v>-3.93</v>
+      </c>
+      <c r="E16" s="9">
+        <v>-5.51</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="6" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C17" s="7">
-        <v>-0.28</v>
+        <v>-3.36</v>
       </c>
       <c r="D17" s="7">
-        <v>-1.49</v>
+        <v>-2.37</v>
       </c>
       <c r="E17" s="8">
-        <v>-1.21</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="6" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" s="7">
-        <v>1.57</v>
+        <v>0.63</v>
       </c>
       <c r="D18" s="7">
-        <v>1.58</v>
+        <v>-0.49</v>
       </c>
       <c r="E18" s="9">
-        <v>0.01</v>
+        <v>-1.12</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="7">
-        <v>-2.06</v>
+        <v>-1.23</v>
       </c>
       <c r="D19" s="7">
-        <v>-3.36</v>
+        <v>-1.09</v>
       </c>
       <c r="E19" s="8">
-        <v>-1.3</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="7">
-        <v>0.7</v>
+        <v>-1.98</v>
       </c>
       <c r="D20" s="7">
-        <v>0.63</v>
+        <v>-0.66</v>
       </c>
       <c r="E20" s="8">
-        <v>-0.07000000000000001</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="7">
-        <v>-2.62</v>
+        <v>-1.2</v>
       </c>
       <c r="D21" s="7">
-        <v>-1.23</v>
+        <v>-1.69</v>
       </c>
       <c r="E21" s="9">
-        <v>1.39</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="7">
-        <v>-1.94</v>
+        <v>2.52</v>
       </c>
       <c r="D22" s="7">
-        <v>-1.98</v>
+        <v>3.69</v>
       </c>
       <c r="E22" s="8">
-        <v>-0.04</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="7">
+        <v>-1.03</v>
+      </c>
+      <c r="D23" s="7">
         <v>-0.59</v>
       </c>
-      <c r="D23" s="7">
-        <v>-1.2</v>
-      </c>
       <c r="E23" s="8">
-        <v>-0.61</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="7">
-        <v>2.05</v>
+        <v>-1.18</v>
       </c>
       <c r="D24" s="7">
-        <v>2.52</v>
-      </c>
-      <c r="E24" s="9">
-        <v>0.47</v>
+        <v>-1.11</v>
+      </c>
+      <c r="E24" s="8">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C25" s="7">
-        <v>-2.46</v>
+        <v>0.5</v>
       </c>
       <c r="D25" s="7">
-        <v>-1.03</v>
+        <v>-1.18</v>
       </c>
       <c r="E25" s="9">
-        <v>1.43</v>
+        <v>-1.68</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="6" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C26" s="7">
-        <v>-2.18</v>
+        <v>-0.37</v>
       </c>
       <c r="D26" s="7">
-        <v>-1.18</v>
-      </c>
-      <c r="E26" s="9">
-        <v>1</v>
+        <v>0.38</v>
+      </c>
+      <c r="E26" s="8">
+        <v>0.75</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="6" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C27" s="7">
-        <v>-1.61</v>
+        <v>1.4</v>
       </c>
       <c r="D27" s="7">
-        <v>0.5</v>
+        <v>0.68</v>
       </c>
       <c r="E27" s="9">
-        <v>2.11</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="7">
-        <v>0.11</v>
+        <v>42.73</v>
       </c>
       <c r="D28" s="7">
-        <v>-0.37</v>
+        <v>47.79</v>
       </c>
       <c r="E28" s="8">
-        <v>-0.48</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C29" s="7">
-        <v>1.79</v>
+        <v>6.24</v>
       </c>
       <c r="D29" s="7">
-        <v>1.4</v>
+        <v>6.73</v>
       </c>
       <c r="E29" s="8">
-        <v>-0.39</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C30" s="7">
-        <v>43.99</v>
+        <v>24.36</v>
       </c>
       <c r="D30" s="7">
-        <v>42.73</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-1.26</v>
+        <v>22.8</v>
+      </c>
+      <c r="E30" s="9">
+        <v>-1.56</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C31" s="7">
-        <v>7.33</v>
+        <v>-6.6</v>
       </c>
       <c r="D31" s="7">
-        <v>6.24</v>
+        <v>-5.7</v>
       </c>
       <c r="E31" s="8">
-        <v>-1.09</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C32" s="7">
-        <v>22.86</v>
+        <v>-39.72</v>
       </c>
       <c r="D32" s="7">
-        <v>24.36</v>
+        <v>-39.78</v>
       </c>
       <c r="E32" s="9">
-        <v>1.5</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C33" s="7">
-        <v>-6.26</v>
+        <v>-12.72</v>
       </c>
       <c r="D33" s="7">
-        <v>-6.6</v>
-      </c>
-      <c r="E33" s="8">
-        <v>-0.34</v>
+        <v>-13.9</v>
+      </c>
+      <c r="E33" s="9">
+        <v>-1.18</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C34" s="7">
-        <v>-37.54</v>
+        <v>6.07</v>
       </c>
       <c r="D34" s="7">
-        <v>-39.72</v>
-      </c>
-      <c r="E34" s="8">
-        <v>-2.18</v>
+        <v>4.35</v>
+      </c>
+      <c r="E34" s="9">
+        <v>-1.72</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="6" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C35" s="7">
-        <v>-12.24</v>
+        <v>-13.5</v>
       </c>
       <c r="D35" s="7">
-        <v>-12.72</v>
+        <v>-13.27</v>
       </c>
       <c r="E35" s="8">
-        <v>-0.48</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="6" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C36" s="7">
-        <v>6.94</v>
+        <v>10.3</v>
       </c>
       <c r="D36" s="7">
-        <v>6.07</v>
-      </c>
-      <c r="E36" s="8">
-        <v>-0.87</v>
+        <v>8.859999999999999</v>
+      </c>
+      <c r="E36" s="9">
+        <v>-1.44</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C37" s="7">
-        <v>-12.65</v>
+        <v>24.98</v>
       </c>
       <c r="D37" s="7">
-        <v>-13.5</v>
+        <v>26.26</v>
       </c>
       <c r="E37" s="8">
-        <v>-0.85</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C38" s="7">
-        <v>9.869999999999999</v>
+        <v>10.07</v>
       </c>
       <c r="D38" s="7">
-        <v>10.3</v>
+        <v>8.52</v>
       </c>
       <c r="E38" s="9">
-        <v>0.43</v>
+        <v>-1.55</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C39" s="7">
-        <v>24.12</v>
+        <v>14.53</v>
       </c>
       <c r="D39" s="7">
-        <v>24.98</v>
+        <v>14.44</v>
       </c>
       <c r="E39" s="9">
-        <v>0.86</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C40" s="7">
-        <v>11.09</v>
+        <v>-0.04</v>
       </c>
       <c r="D40" s="7">
-        <v>10.07</v>
-      </c>
-      <c r="E40" s="8">
-        <v>-1.02</v>
+        <v>-0.45</v>
+      </c>
+      <c r="E40" s="9">
+        <v>-0.41</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="6" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C41" s="7">
-        <v>13.93</v>
+        <v>-5.87</v>
       </c>
       <c r="D41" s="7">
-        <v>14.53</v>
+        <v>-5.94</v>
       </c>
       <c r="E41" s="9">
-        <v>0.6</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C42" s="7">
-        <v>0.66</v>
+        <v>9.91</v>
       </c>
       <c r="D42" s="7">
-        <v>0.21</v>
-      </c>
-      <c r="E42" s="8">
-        <v>-0.45</v>
+        <v>7.93</v>
+      </c>
+      <c r="E42" s="9">
+        <v>-1.98</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C43" s="7">
-        <v>0.14</v>
+        <v>-19.23</v>
       </c>
       <c r="D43" s="7">
-        <v>-0.04</v>
+        <v>-19.01</v>
       </c>
       <c r="E43" s="8">
-        <v>-0.18</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="6" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C44" s="7">
-        <v>-5.42</v>
+        <v>-9.449999999999999</v>
       </c>
       <c r="D44" s="7">
-        <v>-5.87</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-0.45</v>
+        <v>-10.63</v>
+      </c>
+      <c r="E44" s="9">
+        <v>-1.18</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="6" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C45" s="7">
-        <v>8.59</v>
+        <v>-7.48</v>
       </c>
       <c r="D45" s="7">
-        <v>9.91</v>
-      </c>
-      <c r="E45" s="9">
-        <v>1.32</v>
+        <v>-6.54</v>
+      </c>
+      <c r="E45" s="8">
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="6" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C46" s="7">
-        <v>-18.53</v>
+        <v>-10.71</v>
       </c>
       <c r="D46" s="7">
-        <v>-19.23</v>
-      </c>
-      <c r="E46" s="8">
-        <v>-0.7</v>
+        <v>-11.96</v>
+      </c>
+      <c r="E46" s="9">
+        <v>-1.25</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C47" s="7">
-        <v>-10.21</v>
+        <v>-9.710000000000001</v>
       </c>
       <c r="D47" s="7">
-        <v>-9.449999999999999</v>
+        <v>-9.779999999999999</v>
       </c>
       <c r="E47" s="9">
-        <v>0.76</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="6" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C48" s="7">
-        <v>-8.15</v>
+        <v>-5.7</v>
       </c>
       <c r="D48" s="7">
-        <v>-7.48</v>
-      </c>
-      <c r="E48" s="9">
-        <v>0.67</v>
+        <v>-4.71</v>
+      </c>
+      <c r="E48" s="8">
+        <v>0.99</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C49" s="7">
-        <v>-10.09</v>
+        <v>-39.53</v>
       </c>
       <c r="D49" s="7">
-        <v>-10.71</v>
-      </c>
-      <c r="E49" s="8">
-        <v>-0.62</v>
+        <v>-39.73</v>
+      </c>
+      <c r="E49" s="9">
+        <v>-0.2</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="6" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C50" s="7">
-        <v>-8.949999999999999</v>
+        <v>-21.03</v>
       </c>
       <c r="D50" s="7">
-        <v>-9.710000000000001</v>
-      </c>
-      <c r="E50" s="8">
-        <v>-0.76</v>
+        <v>-21.09</v>
+      </c>
+      <c r="E50" s="9">
+        <v>-0.06</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C51" s="7">
-        <v>-6.86</v>
+        <v>-9.529999999999999</v>
       </c>
       <c r="D51" s="7">
-        <v>-5.7</v>
+        <v>-11.16</v>
       </c>
       <c r="E51" s="9">
-        <v>1.16</v>
+        <v>-1.63</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C52" s="7">
-        <v>-39.19</v>
+        <v>395.95</v>
       </c>
       <c r="D52" s="7">
-        <v>-39.53</v>
+        <v>397</v>
       </c>
       <c r="E52" s="8">
-        <v>-0.34</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="6" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C53" s="7">
-        <v>-20.87</v>
+        <v>3443</v>
       </c>
       <c r="D53" s="7">
-        <v>-21.03</v>
-      </c>
-      <c r="E53" s="8">
-        <v>-0.16</v>
+        <v>3398.2</v>
+      </c>
+      <c r="E53" s="9">
+        <v>-44.8</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="6" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C54" s="7">
-        <v>-10.43</v>
+        <v>381.45</v>
       </c>
       <c r="D54" s="7">
-        <v>-9.529999999999999</v>
-      </c>
-      <c r="E54" s="9">
-        <v>0.9</v>
+        <v>385.35</v>
+      </c>
+      <c r="E54" s="8">
+        <v>3.9</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="6" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C55" s="7">
-        <v>399.35</v>
+        <v>376.55</v>
       </c>
       <c r="D55" s="7">
-        <v>395.95</v>
-      </c>
-      <c r="E55" s="8">
-        <v>-3.4</v>
+        <v>371.25</v>
+      </c>
+      <c r="E55" s="9">
+        <v>-5.3</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C56" s="7">
-        <v>3414.1</v>
+        <v>399.7</v>
       </c>
       <c r="D56" s="7">
-        <v>3443</v>
+        <v>399.4</v>
       </c>
       <c r="E56" s="9">
-        <v>28.9</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C57" s="7">
-        <v>378.7</v>
+        <v>219.1</v>
       </c>
       <c r="D57" s="7">
-        <v>381.45</v>
+        <v>218.19</v>
       </c>
       <c r="E57" s="9">
-        <v>2.75</v>
+        <v>-0.91</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="6" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C58" s="7">
-        <v>379.15</v>
+        <v>3551.7</v>
       </c>
       <c r="D58" s="7">
-        <v>376.55</v>
-      </c>
-      <c r="E58" s="8">
-        <v>-2.6</v>
+        <v>3549</v>
+      </c>
+      <c r="E58" s="9">
+        <v>-2.7</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="6" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C59" s="7">
-        <v>403.1</v>
+        <v>1599.9</v>
       </c>
       <c r="D59" s="7">
-        <v>399.7</v>
-      </c>
-      <c r="E59" s="8">
-        <v>-3.4</v>
+        <v>1571</v>
+      </c>
+      <c r="E59" s="9">
+        <v>-28.9</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="6" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C60" s="7">
-        <v>634.75</v>
+        <v>55</v>
       </c>
       <c r="D60" s="7">
-        <v>636.55</v>
-      </c>
-      <c r="E60" s="9">
-        <v>1.8</v>
+        <v>66</v>
+      </c>
+      <c r="E60" s="8">
+        <v>11</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C61" s="7">
-        <v>221.05</v>
+        <v>66</v>
       </c>
       <c r="D61" s="7">
-        <v>219.1</v>
+        <v>77</v>
       </c>
       <c r="E61" s="8">
-        <v>-1.95</v>
+        <v>11</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C62" s="7">
-        <v>3558.9</v>
+        <v>77</v>
       </c>
       <c r="D62" s="7">
-        <v>3551.7</v>
-      </c>
-      <c r="E62" s="8">
-        <v>-7.2</v>
+        <v>55</v>
+      </c>
+      <c r="E62" s="9">
+        <v>-22</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="6" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C63" s="7">
-        <v>1584</v>
+        <v>29.49</v>
       </c>
       <c r="D63" s="7">
-        <v>1599.9</v>
-      </c>
-      <c r="E63" s="9">
-        <v>15.9</v>
+        <v>30.9</v>
+      </c>
+      <c r="E63" s="8">
+        <v>1.41</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C64" s="7">
-        <v>77</v>
+        <v>59.77</v>
       </c>
       <c r="D64" s="7">
-        <v>66</v>
-      </c>
-      <c r="E64" s="8">
-        <v>-11</v>
+        <v>54.04</v>
+      </c>
+      <c r="E64" s="9">
+        <v>-5.73</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="6" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C65" s="7">
-        <v>66</v>
+        <v>52.32</v>
       </c>
       <c r="D65" s="7">
-        <v>77</v>
-      </c>
-      <c r="E65" s="9">
-        <v>11</v>
+        <v>54.58</v>
+      </c>
+      <c r="E65" s="8">
+        <v>2.26</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="6" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B66" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C66" s="7">
-        <v>31.42</v>
+        <v>46.68</v>
       </c>
       <c r="D66" s="7">
-        <v>29.49</v>
-      </c>
-      <c r="E66" s="8">
-        <v>-1.93</v>
+        <v>41.66</v>
+      </c>
+      <c r="E66" s="9">
+        <v>-5.02</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B67" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C67" s="7">
-        <v>57.05</v>
+        <v>47.5</v>
       </c>
       <c r="D67" s="7">
-        <v>59.77</v>
+        <v>47.24</v>
       </c>
       <c r="E67" s="9">
-        <v>2.72</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C68" s="7">
-        <v>50.71</v>
+        <v>42.22</v>
       </c>
       <c r="D68" s="7">
-        <v>52.32</v>
+        <v>41.07</v>
       </c>
       <c r="E68" s="9">
-        <v>1.61</v>
+        <v>-1.15</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="6" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B69" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C69" s="7">
-        <v>49.39</v>
+        <v>35.27</v>
       </c>
       <c r="D69" s="7">
-        <v>46.68</v>
-      </c>
-      <c r="E69" s="8">
-        <v>-2.71</v>
+        <v>34.89</v>
+      </c>
+      <c r="E69" s="9">
+        <v>-0.38</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="6" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B70" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C70" s="7">
-        <v>50.52</v>
+        <v>52.65</v>
       </c>
       <c r="D70" s="7">
-        <v>47.5</v>
-      </c>
-      <c r="E70" s="8">
-        <v>-3.02</v>
+        <v>44.76</v>
+      </c>
+      <c r="E70" s="9">
+        <v>-7.89</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="6" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C71" s="7">
-        <v>66.2</v>
+        <v>-15.16</v>
       </c>
       <c r="D71" s="7">
-        <v>66.84</v>
+        <v>-28.21</v>
       </c>
       <c r="E71" s="9">
-        <v>0.64</v>
+        <v>-13.05</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C72" s="7">
-        <v>44.71</v>
+        <v>-54.24</v>
       </c>
       <c r="D72" s="7">
-        <v>42.22</v>
-      </c>
-      <c r="E72" s="8">
-        <v>-2.49</v>
+        <v>-70.08</v>
+      </c>
+      <c r="E72" s="9">
+        <v>-15.84</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="6" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C73" s="7">
-        <v>36.23</v>
+        <v>-40</v>
       </c>
       <c r="D73" s="7">
-        <v>35.27</v>
+        <v>-36.87</v>
       </c>
       <c r="E73" s="8">
-        <v>-0.96</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="6" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C74" s="7">
-        <v>47.96</v>
+        <v>-48.79</v>
       </c>
       <c r="D74" s="7">
-        <v>52.65</v>
-      </c>
-      <c r="E74" s="9">
-        <v>4.69</v>
+        <v>-32.18</v>
+      </c>
+      <c r="E74" s="8">
+        <v>16.61</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="6" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B75" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C75" s="7">
-        <v>-47.59</v>
+        <v>-57.86</v>
       </c>
       <c r="D75" s="7">
-        <v>-15.16</v>
-      </c>
-      <c r="E75" s="9">
-        <v>32.43</v>
+        <v>3.22</v>
+      </c>
+      <c r="E75" s="8">
+        <v>61.08</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="6" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C76" s="7">
-        <v>-51.31</v>
+        <v>80.22</v>
       </c>
       <c r="D76" s="7">
-        <v>-54.24</v>
-      </c>
-      <c r="E76" s="8">
-        <v>-2.93</v>
+        <v>21.31</v>
+      </c>
+      <c r="E76" s="9">
+        <v>-58.91</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B77" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C77" s="7">
-        <v>-54.04</v>
+        <v>-18.78</v>
       </c>
       <c r="D77" s="7">
-        <v>-40</v>
-      </c>
-      <c r="E77" s="9">
-        <v>14.04</v>
+        <v>-2.37</v>
+      </c>
+      <c r="E77" s="8">
+        <v>16.41</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="6" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B78" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C78" s="7">
-        <v>-46.89</v>
+        <v>-47.39</v>
       </c>
       <c r="D78" s="7">
-        <v>-48.79</v>
+        <v>-28.48</v>
       </c>
       <c r="E78" s="8">
-        <v>-1.9</v>
+        <v>18.91</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="6" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B79" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C79" s="7">
-        <v>-69.33</v>
+        <v>-51.59</v>
       </c>
       <c r="D79" s="7">
-        <v>-57.86</v>
-      </c>
-      <c r="E79" s="9">
-        <v>11.47</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B80" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="7">
-        <v>19.52</v>
-      </c>
-      <c r="D80" s="7">
-        <v>80.22</v>
-      </c>
-      <c r="E80" s="9">
-        <v>60.7</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B81" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="7">
-        <v>-44.95</v>
-      </c>
-      <c r="D81" s="7">
-        <v>-18.78</v>
-      </c>
-      <c r="E81" s="9">
-        <v>26.17</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B82" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C82" s="7">
-        <v>-26.98</v>
-      </c>
-      <c r="D82" s="7">
-        <v>-47.39</v>
-      </c>
-      <c r="E82" s="8">
-        <v>-20.41</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="A83" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B83" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C83" s="7">
-        <v>-21.82</v>
-      </c>
-      <c r="D83" s="7">
-        <v>-51.59</v>
-      </c>
-      <c r="E83" s="8">
-        <v>-29.77</v>
+        <v>-42.47</v>
+      </c>
+      <c r="E79" s="8">
+        <v>9.119999999999999</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3525,28 +3448,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C1" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="D1" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="E1" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="F1" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="G1" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="H1" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="I1" s="10" t="s">
         <v>79</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3560,16 +3483,16 @@
         <v>9</v>
       </c>
       <c r="D2" s="12">
-        <v>48.1</v>
+        <v>46.2</v>
       </c>
       <c r="E2" s="12">
         <v>70</v>
       </c>
       <c r="F2" s="12">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="G2" s="12">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="H2" s="12">
         <v>55.4</v>
@@ -3706,31 +3629,31 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="15">
-        <v>0.3583</v>
+        <v>0.3515</v>
       </c>
       <c r="B2" s="15">
-        <v>0.3376</v>
+        <v>0.3383</v>
       </c>
       <c r="C2" s="15">
-        <v>0.2299</v>
+        <v>0.2191</v>
       </c>
       <c r="D2" s="15">
-        <v>0.1994</v>
+        <v>0.1993</v>
       </c>
       <c r="E2" s="15">
-        <v>0.133</v>
+        <v>0.1264</v>
       </c>
       <c r="F2" s="15">
-        <v>0.09119999999999999</v>
+        <v>0.0839</v>
       </c>
       <c r="G2" s="15">
-        <v>0.0488</v>
+        <v>0.0469</v>
       </c>
       <c r="H2" s="15">
-        <v>0.008699999999999999</v>
+        <v>0.0131</v>
       </c>
       <c r="I2" s="15">
-        <v>-0.1105</v>
+        <v>-0.1107</v>
       </c>
     </row>
   </sheetData>

--- a/MAHINDRA_GROUP_Technical_Metrics.xlsx
+++ b/MAHINDRA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="78">
   <si>
     <t>Symbol</t>
   </si>
@@ -193,34 +193,28 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>29.5 → 30.9</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>29.5</t>
-  </si>
-  <si>
-    <t>30.9</t>
-  </si>
-  <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>52.6 → 44.8</t>
+    <t>54.0 → 46.7</t>
   </si>
   <si>
     <t>🔴 BEARISH</t>
   </si>
   <si>
-    <t>52.6</t>
-  </si>
-  <si>
-    <t>44.8</t>
+    <t>54.0</t>
+  </si>
+  <si>
+    <t>46.7</t>
+  </si>
+  <si>
+    <t>50 DMA &gt; 200 DMA</t>
+  </si>
+  <si>
+    <t>Yes → No</t>
+  </si>
+  <si>
+    <t>🔴 DEATH CROSS</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -306,14 +300,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -346,13 +340,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,7 +416,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -430,7 +424,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -946,10 +939,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>397</v>
+        <v>394.5</v>
       </c>
       <c r="D2">
-        <v>0.27</v>
+        <v>-0.63</v>
       </c>
       <c r="E2">
         <v>490.2</v>
@@ -958,25 +951,25 @@
         <v>379.2</v>
       </c>
       <c r="G2">
-        <v>-19.01</v>
+        <v>-19.52</v>
       </c>
       <c r="H2">
-        <v>4.69</v>
+        <v>4.03</v>
       </c>
       <c r="I2">
-        <v>-2.37</v>
+        <v>-2.3</v>
       </c>
       <c r="J2">
-        <v>-2.77</v>
+        <v>-4.88</v>
       </c>
       <c r="K2">
-        <v>-13.27</v>
+        <v>-11.64</v>
       </c>
       <c r="L2">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="M2">
-        <v>12.64</v>
+        <v>13.07</v>
       </c>
       <c r="N2">
         <v>34</v>
@@ -985,61 +978,61 @@
         <v>40</v>
       </c>
       <c r="P2">
-        <v>399.43</v>
+        <v>397.57</v>
       </c>
       <c r="Q2">
-        <v>407.92</v>
+        <v>407.05</v>
       </c>
       <c r="R2">
-        <v>437.55</v>
+        <v>436.29</v>
       </c>
       <c r="S2">
-        <v>437.39</v>
+        <v>437.21</v>
       </c>
       <c r="T2">
-        <v>-9.23</v>
+        <v>-9.77</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
       </c>
       <c r="V2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="W2" t="s">
         <v>47</v>
       </c>
       <c r="X2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y2">
-        <v>30.9</v>
+        <v>29.39</v>
       </c>
       <c r="Z2">
-        <v>-10.51</v>
+        <v>-10.52</v>
       </c>
       <c r="AA2">
-        <v>-10.85</v>
+        <v>-10.78</v>
       </c>
       <c r="AB2">
-        <v>0.34</v>
+        <v>0.26</v>
       </c>
       <c r="AC2">
         <v>5.41</v>
       </c>
       <c r="AD2">
-        <v>1.8</v>
+        <v>3.61</v>
       </c>
       <c r="AE2">
-        <v>9.24</v>
+        <v>9.01</v>
       </c>
       <c r="AF2">
-        <v>-28.21</v>
+        <v>-82.26000000000001</v>
       </c>
       <c r="AG2">
-        <v>419.82</v>
+        <v>420.2</v>
       </c>
       <c r="AH2">
-        <v>396.02</v>
+        <v>393.9</v>
       </c>
       <c r="AI2">
         <v>423.49</v>
@@ -1048,7 +1041,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>44.37</v>
+        <v>45.81</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1059,10 +1052,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>3398.2</v>
+        <v>3330</v>
       </c>
       <c r="D3">
-        <v>-1.3</v>
+        <v>-2.01</v>
       </c>
       <c r="E3">
         <v>3802.4</v>
@@ -1071,46 +1064,46 @@
         <v>2931.1</v>
       </c>
       <c r="G3">
-        <v>-10.63</v>
+        <v>-12.42</v>
       </c>
       <c r="H3">
-        <v>15.94</v>
+        <v>13.61</v>
       </c>
       <c r="I3">
-        <v>-0.49</v>
+        <v>-2.77</v>
       </c>
       <c r="J3">
-        <v>3.88</v>
+        <v>3.36</v>
       </c>
       <c r="K3">
-        <v>8.859999999999999</v>
+        <v>9.34</v>
       </c>
       <c r="L3">
-        <v>0.68</v>
+        <v>-2.15</v>
       </c>
       <c r="M3">
-        <v>35.15</v>
+        <v>34.82</v>
       </c>
       <c r="N3">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="O3">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="P3">
-        <v>3418.46</v>
+        <v>3399.5</v>
       </c>
       <c r="Q3">
-        <v>3423.18</v>
+        <v>3425.5</v>
       </c>
       <c r="R3">
-        <v>3254.8</v>
+        <v>3258.74</v>
       </c>
       <c r="S3">
-        <v>3350.12</v>
+        <v>3348.45</v>
       </c>
       <c r="T3">
-        <v>1.44</v>
+        <v>-0.55</v>
       </c>
       <c r="U3" t="s">
         <v>48</v>
@@ -1122,37 +1115,37 @@
         <v>47</v>
       </c>
       <c r="X3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y3">
-        <v>54.04</v>
+        <v>46.71</v>
       </c>
       <c r="Z3">
-        <v>46.23</v>
+        <v>36.19</v>
       </c>
       <c r="AA3">
-        <v>59</v>
+        <v>54.43</v>
       </c>
       <c r="AB3">
-        <v>-12.77</v>
+        <v>-18.25</v>
       </c>
       <c r="AC3">
-        <v>12.33</v>
+        <v>9.5</v>
       </c>
       <c r="AD3">
-        <v>12.78</v>
+        <v>12.19</v>
       </c>
       <c r="AE3">
-        <v>62.7</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="AF3">
-        <v>-70.08</v>
+        <v>-16.79</v>
       </c>
       <c r="AG3">
-        <v>3515.75</v>
+        <v>3504.73</v>
       </c>
       <c r="AH3">
-        <v>3330.61</v>
+        <v>3346.26</v>
       </c>
       <c r="AI3">
         <v>3274.47</v>
@@ -1161,7 +1154,7 @@
         <v>50</v>
       </c>
       <c r="AK3">
-        <v>22.68</v>
+        <v>23.83</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1172,10 +1165,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>385.35</v>
+        <v>383.35</v>
       </c>
       <c r="D4">
-        <v>1.02</v>
+        <v>-0.52</v>
       </c>
       <c r="E4">
         <v>412.3</v>
@@ -1184,46 +1177,46 @@
         <v>253.95</v>
       </c>
       <c r="G4">
-        <v>-6.54</v>
+        <v>-7.02</v>
       </c>
       <c r="H4">
-        <v>51.74</v>
+        <v>50.95</v>
       </c>
       <c r="I4">
-        <v>-1.09</v>
+        <v>0.24</v>
       </c>
       <c r="J4">
-        <v>3.17</v>
+        <v>-2.64</v>
       </c>
       <c r="K4">
-        <v>26.26</v>
+        <v>26.25</v>
       </c>
       <c r="L4">
-        <v>47.79</v>
+        <v>45.76</v>
       </c>
       <c r="M4">
-        <v>21.91</v>
+        <v>21.71</v>
       </c>
       <c r="N4">
         <v>99</v>
       </c>
       <c r="O4">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="P4">
-        <v>381.91</v>
+        <v>382.09</v>
       </c>
       <c r="Q4">
-        <v>392.29</v>
+        <v>391.83</v>
       </c>
       <c r="R4">
-        <v>355.32</v>
+        <v>357.04</v>
       </c>
       <c r="S4">
-        <v>342.07</v>
+        <v>342.42</v>
       </c>
       <c r="T4">
-        <v>12.65</v>
+        <v>11.95</v>
       </c>
       <c r="U4" t="s">
         <v>48</v>
@@ -1238,34 +1231,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>54.58</v>
+        <v>53.19</v>
       </c>
       <c r="Z4">
-        <v>6.71</v>
+        <v>6.02</v>
       </c>
       <c r="AA4">
-        <v>10.93</v>
+        <v>9.94</v>
       </c>
       <c r="AB4">
-        <v>-4.22</v>
+        <v>-3.93</v>
       </c>
       <c r="AC4">
-        <v>9.6</v>
+        <v>13.93</v>
       </c>
       <c r="AD4">
-        <v>4.14</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="AE4">
-        <v>12.84</v>
+        <v>12.51</v>
       </c>
       <c r="AF4">
-        <v>-36.87</v>
+        <v>-54.21</v>
       </c>
       <c r="AG4">
-        <v>410.99</v>
+        <v>410.95</v>
       </c>
       <c r="AH4">
-        <v>373.58</v>
+        <v>372.7</v>
       </c>
       <c r="AI4">
         <v>357.72</v>
@@ -1274,7 +1267,7 @@
         <v>50</v>
       </c>
       <c r="AK4">
-        <v>23.46</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1285,10 +1278,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>371.25</v>
+        <v>368.65</v>
       </c>
       <c r="D5">
-        <v>-1.41</v>
+        <v>-0.7</v>
       </c>
       <c r="E5">
         <v>421.7</v>
@@ -1297,46 +1290,46 @@
         <v>294.25</v>
       </c>
       <c r="G5">
-        <v>-11.96</v>
+        <v>-12.58</v>
       </c>
       <c r="H5">
-        <v>26.17</v>
+        <v>25.28</v>
       </c>
       <c r="I5">
-        <v>-0.66</v>
+        <v>-2.27</v>
       </c>
       <c r="J5">
-        <v>-2.37</v>
+        <v>-4.83</v>
       </c>
       <c r="K5">
-        <v>8.52</v>
+        <v>10.81</v>
       </c>
       <c r="L5">
-        <v>6.73</v>
+        <v>6.3</v>
       </c>
       <c r="M5">
-        <v>8.390000000000001</v>
+        <v>8.15</v>
       </c>
       <c r="N5">
         <v>77</v>
       </c>
       <c r="O5">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="P5">
-        <v>376.79</v>
+        <v>375.08</v>
       </c>
       <c r="Q5">
-        <v>383.95</v>
+        <v>383.12</v>
       </c>
       <c r="R5">
-        <v>375.16</v>
+        <v>375.6</v>
       </c>
       <c r="S5">
-        <v>364.34</v>
+        <v>364.19</v>
       </c>
       <c r="T5">
-        <v>1.9</v>
+        <v>1.22</v>
       </c>
       <c r="U5" t="s">
         <v>48</v>
@@ -1351,34 +1344,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>41.66</v>
+        <v>39.42</v>
       </c>
       <c r="Z5">
-        <v>0.15</v>
+        <v>-0.7</v>
       </c>
       <c r="AA5">
-        <v>2.36</v>
+        <v>1.75</v>
       </c>
       <c r="AB5">
-        <v>-2.21</v>
+        <v>-2.45</v>
       </c>
       <c r="AC5">
-        <v>20.26</v>
+        <v>7.01</v>
       </c>
       <c r="AD5">
-        <v>24.62</v>
+        <v>18.46</v>
       </c>
       <c r="AE5">
-        <v>10.69</v>
+        <v>10.53</v>
       </c>
       <c r="AF5">
-        <v>-32.18</v>
+        <v>-53.73</v>
       </c>
       <c r="AG5">
-        <v>397.78</v>
+        <v>398.51</v>
       </c>
       <c r="AH5">
-        <v>370.13</v>
+        <v>367.72</v>
       </c>
       <c r="AI5">
         <v>364.94</v>
@@ -1387,7 +1380,7 @@
         <v>50</v>
       </c>
       <c r="AK5">
-        <v>28.01</v>
+        <v>29.34</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1398,10 +1391,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>399.4</v>
+        <v>391.6</v>
       </c>
       <c r="D6">
-        <v>-0.08</v>
+        <v>-1.95</v>
       </c>
       <c r="E6">
         <v>442.7</v>
@@ -1410,46 +1403,46 @@
         <v>279.55</v>
       </c>
       <c r="G6">
-        <v>-9.779999999999999</v>
+        <v>-11.54</v>
       </c>
       <c r="H6">
-        <v>42.87</v>
+        <v>40.08</v>
       </c>
       <c r="I6">
-        <v>-1.69</v>
+        <v>-3.7</v>
       </c>
       <c r="J6">
-        <v>-2.68</v>
+        <v>-4.36</v>
       </c>
       <c r="K6">
-        <v>14.44</v>
+        <v>14.45</v>
       </c>
       <c r="L6">
-        <v>22.8</v>
+        <v>19.68</v>
       </c>
       <c r="M6">
-        <v>-11.07</v>
+        <v>-12.21</v>
       </c>
       <c r="N6">
         <v>88</v>
       </c>
       <c r="O6">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="P6">
-        <v>402</v>
+        <v>398.99</v>
       </c>
       <c r="Q6">
-        <v>407.25</v>
+        <v>406.7</v>
       </c>
       <c r="R6">
-        <v>394.42</v>
+        <v>395.35</v>
       </c>
       <c r="S6">
-        <v>365.89</v>
+        <v>366.16</v>
       </c>
       <c r="T6">
-        <v>9.16</v>
+        <v>6.95</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1464,34 +1457,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>47.24</v>
+        <v>40.8</v>
       </c>
       <c r="Z6">
-        <v>1.4</v>
+        <v>0.33</v>
       </c>
       <c r="AA6">
-        <v>3.57</v>
+        <v>2.93</v>
       </c>
       <c r="AB6">
-        <v>-2.17</v>
+        <v>-2.6</v>
       </c>
       <c r="AC6">
-        <v>5.38</v>
+        <v>0</v>
       </c>
       <c r="AD6">
-        <v>6.83</v>
+        <v>3.59</v>
       </c>
       <c r="AE6">
-        <v>11.99</v>
+        <v>12.05</v>
       </c>
       <c r="AF6">
-        <v>3.22</v>
+        <v>-45.65</v>
       </c>
       <c r="AG6">
-        <v>418.6</v>
+        <v>419.91</v>
       </c>
       <c r="AH6">
-        <v>395.9</v>
+        <v>393.48</v>
       </c>
       <c r="AI6">
         <v>372.35</v>
@@ -1500,7 +1493,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>17.42</v>
+        <v>16.04</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1511,58 +1504,58 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>636.55</v>
+        <v>642.05</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="E7">
-        <v>668</v>
+        <v>665.3</v>
       </c>
       <c r="F7">
         <v>506.45</v>
       </c>
       <c r="G7">
-        <v>-4.71</v>
+        <v>-3.49</v>
       </c>
       <c r="H7">
-        <v>25.69</v>
+        <v>26.77</v>
       </c>
       <c r="I7">
-        <v>3.69</v>
+        <v>5.15</v>
       </c>
       <c r="J7">
-        <v>10.88</v>
+        <v>10.33</v>
       </c>
       <c r="K7">
-        <v>0.21</v>
+        <v>3.29</v>
       </c>
       <c r="L7">
-        <v>-5.7</v>
+        <v>-3.88</v>
       </c>
       <c r="M7">
-        <v>33.83</v>
+        <v>34.1</v>
       </c>
       <c r="N7">
         <v>45</v>
       </c>
       <c r="O7">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="P7">
-        <v>630.52</v>
+        <v>636.8099999999999</v>
       </c>
       <c r="Q7">
-        <v>604.67</v>
+        <v>608.15</v>
       </c>
       <c r="R7">
-        <v>601.73</v>
+        <v>602.27</v>
       </c>
       <c r="S7">
-        <v>583.74</v>
+        <v>584.2</v>
       </c>
       <c r="T7">
-        <v>9.050000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="U7" t="s">
         <v>48</v>
@@ -1577,43 +1570,43 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>66.84</v>
+        <v>68.89</v>
       </c>
       <c r="Z7">
-        <v>11.49</v>
+        <v>12.37</v>
       </c>
       <c r="AA7">
-        <v>7.23</v>
+        <v>8.26</v>
       </c>
       <c r="AB7">
-        <v>4.26</v>
+        <v>4.11</v>
       </c>
       <c r="AC7">
         <v>100</v>
       </c>
       <c r="AD7">
-        <v>96.18000000000001</v>
+        <v>100</v>
       </c>
       <c r="AE7">
-        <v>17.1</v>
+        <v>17.14</v>
       </c>
       <c r="AF7">
-        <v>21.31</v>
+        <v>58.55</v>
       </c>
       <c r="AG7">
-        <v>650.72</v>
+        <v>654.48</v>
       </c>
       <c r="AH7">
-        <v>558.62</v>
+        <v>561.8099999999999</v>
       </c>
       <c r="AI7">
-        <v>591.65</v>
+        <v>592.37</v>
       </c>
       <c r="AJ7" t="s">
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>59.41</v>
+        <v>62.04</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1624,10 +1617,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>218.19</v>
+        <v>211.23</v>
       </c>
       <c r="D8">
-        <v>-0.42</v>
+        <v>-3.19</v>
       </c>
       <c r="E8">
         <v>362.05</v>
@@ -1636,46 +1629,46 @@
         <v>210.4</v>
       </c>
       <c r="G8">
-        <v>-39.73</v>
+        <v>-41.66</v>
       </c>
       <c r="H8">
-        <v>3.7</v>
+        <v>0.39</v>
       </c>
       <c r="I8">
-        <v>-0.59</v>
+        <v>-4.44</v>
       </c>
       <c r="J8">
-        <v>-0.04</v>
+        <v>-1.72</v>
       </c>
       <c r="K8">
-        <v>-0.45</v>
+        <v>-3.3</v>
       </c>
       <c r="L8">
-        <v>-39.78</v>
+        <v>-41.65</v>
       </c>
       <c r="M8">
-        <v>1.31</v>
+        <v>0.52</v>
       </c>
       <c r="N8">
         <v>12</v>
       </c>
       <c r="O8">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="P8">
-        <v>220.24</v>
+        <v>218.27</v>
       </c>
       <c r="Q8">
-        <v>223.75</v>
+        <v>223.52</v>
       </c>
       <c r="R8">
-        <v>227.74</v>
+        <v>227.34</v>
       </c>
       <c r="S8">
-        <v>264</v>
+        <v>263.47</v>
       </c>
       <c r="T8">
-        <v>-17.35</v>
+        <v>-19.83</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1690,43 +1683,43 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>41.07</v>
+        <v>33.54</v>
       </c>
       <c r="Z8">
-        <v>-1.79</v>
+        <v>-2.5</v>
       </c>
       <c r="AA8">
-        <v>-1.26</v>
+        <v>-1.51</v>
       </c>
       <c r="AB8">
-        <v>-0.52</v>
+        <v>-0.99</v>
       </c>
       <c r="AC8">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AD8">
-        <v>11.65</v>
+        <v>5.87</v>
       </c>
       <c r="AE8">
-        <v>6.39</v>
+        <v>6.68</v>
       </c>
       <c r="AF8">
-        <v>-2.37</v>
+        <v>311.95</v>
       </c>
       <c r="AG8">
-        <v>233.67</v>
+        <v>234.39</v>
       </c>
       <c r="AH8">
-        <v>213.84</v>
+        <v>212.65</v>
       </c>
       <c r="AI8">
-        <v>237.22</v>
+        <v>234.44</v>
       </c>
       <c r="AJ8" t="s">
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>22.59</v>
+        <v>26.34</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1737,10 +1730,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>3549</v>
+        <v>3548.3</v>
       </c>
       <c r="D9">
-        <v>-0.08</v>
+        <v>-0.02</v>
       </c>
       <c r="E9">
         <v>4497.5</v>
@@ -1749,46 +1742,46 @@
         <v>3308.9</v>
       </c>
       <c r="G9">
-        <v>-21.09</v>
+        <v>-21.11</v>
       </c>
       <c r="H9">
-        <v>7.26</v>
+        <v>7.24</v>
       </c>
       <c r="I9">
-        <v>-1.11</v>
+        <v>-1.51</v>
       </c>
       <c r="J9">
-        <v>-0.26</v>
+        <v>-0.55</v>
       </c>
       <c r="K9">
-        <v>-5.94</v>
+        <v>-7.26</v>
       </c>
       <c r="L9">
-        <v>-13.9</v>
+        <v>-14.12</v>
       </c>
       <c r="M9">
-        <v>19.93</v>
+        <v>20.18</v>
       </c>
       <c r="N9">
         <v>23</v>
       </c>
       <c r="O9">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="P9">
-        <v>3566.4</v>
+        <v>3555.54</v>
       </c>
       <c r="Q9">
-        <v>3599.45</v>
+        <v>3596.49</v>
       </c>
       <c r="R9">
-        <v>3716.49</v>
+        <v>3710.23</v>
       </c>
       <c r="S9">
-        <v>3701.49</v>
+        <v>3699.63</v>
       </c>
       <c r="T9">
-        <v>-4.12</v>
+        <v>-4.09</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1803,43 +1796,43 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>34.89</v>
+        <v>34.79</v>
       </c>
       <c r="Z9">
-        <v>-33.98</v>
+        <v>-34.3</v>
       </c>
       <c r="AA9">
-        <v>-34.73</v>
+        <v>-34.64</v>
       </c>
       <c r="AB9">
-        <v>0.75</v>
+        <v>0.34</v>
       </c>
       <c r="AC9">
         <v>0</v>
       </c>
       <c r="AD9">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="AE9">
-        <v>51.37</v>
+        <v>50.68</v>
       </c>
       <c r="AF9">
-        <v>-28.48</v>
+        <v>-28.18</v>
       </c>
       <c r="AG9">
-        <v>3651.67</v>
+        <v>3653.3</v>
       </c>
       <c r="AH9">
-        <v>3547.23</v>
+        <v>3539.68</v>
       </c>
       <c r="AI9">
-        <v>3708.5</v>
+        <v>3707.95</v>
       </c>
       <c r="AJ9" t="s">
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>12.4</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1850,10 +1843,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>1571</v>
+        <v>1585</v>
       </c>
       <c r="D10">
-        <v>-1.81</v>
+        <v>0.89</v>
       </c>
       <c r="E10">
         <v>1768.4</v>
@@ -1862,46 +1855,46 @@
         <v>1326.2</v>
       </c>
       <c r="G10">
-        <v>-11.16</v>
+        <v>-10.37</v>
       </c>
       <c r="H10">
-        <v>18.46</v>
+        <v>19.51</v>
       </c>
       <c r="I10">
-        <v>-1.18</v>
+        <v>-0.45</v>
       </c>
       <c r="J10">
-        <v>-3.93</v>
+        <v>-3.6</v>
       </c>
       <c r="K10">
-        <v>7.93</v>
+        <v>6.81</v>
       </c>
       <c r="L10">
-        <v>4.35</v>
+        <v>6.42</v>
       </c>
       <c r="M10">
-        <v>4.69</v>
+        <v>4.94</v>
       </c>
       <c r="N10">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="O10">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="P10">
-        <v>1586.2</v>
+        <v>1584.78</v>
       </c>
       <c r="Q10">
-        <v>1621.88</v>
+        <v>1617.68</v>
       </c>
       <c r="R10">
-        <v>1538.41</v>
+        <v>1540.86</v>
       </c>
       <c r="S10">
-        <v>1509.84</v>
+        <v>1510.78</v>
       </c>
       <c r="T10">
-        <v>4.05</v>
+        <v>4.91</v>
       </c>
       <c r="U10" t="s">
         <v>48</v>
@@ -1916,34 +1909,34 @@
         <v>3</v>
       </c>
       <c r="Y10">
-        <v>44.76</v>
+        <v>48.76</v>
       </c>
       <c r="Z10">
-        <v>7.46</v>
+        <v>5.83</v>
       </c>
       <c r="AA10">
-        <v>19.08</v>
+        <v>16.43</v>
       </c>
       <c r="AB10">
-        <v>-11.63</v>
+        <v>-10.61</v>
       </c>
       <c r="AC10">
-        <v>8.74</v>
+        <v>15.08</v>
       </c>
       <c r="AD10">
-        <v>6.18</v>
+        <v>10.86</v>
       </c>
       <c r="AE10">
-        <v>36.73</v>
+        <v>36.17</v>
       </c>
       <c r="AF10">
-        <v>-42.47</v>
+        <v>-26.32</v>
       </c>
       <c r="AG10">
-        <v>1679.35</v>
+        <v>1672.88</v>
       </c>
       <c r="AH10">
-        <v>1564.41</v>
+        <v>1562.48</v>
       </c>
       <c r="AI10">
         <v>1527.05</v>
@@ -1952,7 +1945,7 @@
         <v>50</v>
       </c>
       <c r="AK10">
-        <v>37.85</v>
+        <v>36.63</v>
       </c>
     </row>
   </sheetData>
@@ -2093,7 +2086,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F79"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2133,7 +2126,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2152,28 +2145,28 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B4" s="5" t="s">
+      <c r="A4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>66</v>
+      <c r="E4" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -2185,1240 +2178,1274 @@
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="E7" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>71</v>
-      </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="7">
-        <v>-4.22</v>
-      </c>
-      <c r="D8" s="7">
+      <c r="C8" s="6">
         <v>-2.77</v>
       </c>
-      <c r="E8" s="8">
-        <v>1.45</v>
+      <c r="D8" s="6">
+        <v>-4.88</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-2.11</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="7">
-        <v>6.31</v>
-      </c>
-      <c r="D9" s="7">
+      <c r="C9" s="6">
         <v>3.88</v>
       </c>
-      <c r="E9" s="9">
-        <v>-2.43</v>
+      <c r="D9" s="6">
+        <v>3.36</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-0.52</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="7">
-        <v>5.08</v>
-      </c>
-      <c r="D10" s="7">
+      <c r="C10" s="6">
         <v>3.17</v>
       </c>
-      <c r="E10" s="9">
-        <v>-1.91</v>
+      <c r="D10" s="6">
+        <v>-2.64</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-5.81</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="7">
-        <v>-0.97</v>
-      </c>
-      <c r="D11" s="7">
+      <c r="C11" s="6">
         <v>-2.37</v>
       </c>
-      <c r="E11" s="9">
-        <v>-1.4</v>
+      <c r="D11" s="6">
+        <v>-4.83</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-2.46</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="7">
-        <v>-4.63</v>
-      </c>
-      <c r="D12" s="7">
+      <c r="C12" s="6">
         <v>-2.68</v>
       </c>
-      <c r="E12" s="8">
-        <v>1.95</v>
+      <c r="D12" s="6">
+        <v>-4.36</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-1.68</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="7">
-        <v>10.35</v>
-      </c>
-      <c r="D13" s="7">
+      <c r="C13" s="6">
         <v>10.88</v>
       </c>
-      <c r="E13" s="8">
-        <v>0.53</v>
+      <c r="D13" s="6">
+        <v>10.33</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-0.55</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="7">
-        <v>-2.11</v>
-      </c>
-      <c r="D14" s="7">
+      <c r="C14" s="6">
         <v>-0.04</v>
       </c>
-      <c r="E14" s="8">
+      <c r="D14" s="6">
+        <v>-1.72</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-1.68</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-0.26</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-0.55</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-0.29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-3.93</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-3.6</v>
+      </c>
+      <c r="E16" s="8">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-2.37</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-2.3</v>
+      </c>
+      <c r="E17" s="8">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-0.49</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-2.77</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-2.28</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-1.09</v>
+      </c>
+      <c r="D19" s="6">
+        <v>0.24</v>
+      </c>
+      <c r="E19" s="8">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-0.66</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-2.27</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-1.61</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-1.69</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-3.7</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-2.01</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="6">
+        <v>3.69</v>
+      </c>
+      <c r="D22" s="6">
+        <v>5.15</v>
+      </c>
+      <c r="E22" s="8">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-0.59</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-4.44</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-3.85</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-1.11</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-1.51</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-1.18</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-0.45</v>
+      </c>
+      <c r="E25" s="8">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>0.38</v>
+      </c>
+      <c r="D26" s="6">
+        <v>0.41</v>
+      </c>
+      <c r="E26" s="8">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>0.68</v>
+      </c>
+      <c r="D27" s="6">
+        <v>-2.15</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-2.83</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="6">
+        <v>47.79</v>
+      </c>
+      <c r="D28" s="6">
+        <v>45.76</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-2.03</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="6">
+        <v>6.73</v>
+      </c>
+      <c r="D29" s="6">
+        <v>6.3</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="6">
+        <v>22.8</v>
+      </c>
+      <c r="D30" s="6">
+        <v>19.68</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-3.12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-5.7</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-3.88</v>
+      </c>
+      <c r="E31" s="8">
+        <v>1.82</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-39.78</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-41.65</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-1.87</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="6">
+        <v>-13.9</v>
+      </c>
+      <c r="D33" s="6">
+        <v>-14.12</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="6">
+        <v>4.35</v>
+      </c>
+      <c r="D34" s="6">
+        <v>6.42</v>
+      </c>
+      <c r="E34" s="8">
         <v>2.07</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-13.27</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-11.64</v>
+      </c>
+      <c r="E35" s="8">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="6">
+        <v>8.859999999999999</v>
+      </c>
+      <c r="D36" s="6">
+        <v>9.34</v>
+      </c>
+      <c r="E36" s="8">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="6">
+        <v>26.26</v>
+      </c>
+      <c r="D37" s="6">
+        <v>26.25</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="6">
+        <v>8.52</v>
+      </c>
+      <c r="D38" s="6">
+        <v>10.81</v>
+      </c>
+      <c r="E38" s="8">
+        <v>2.29</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="6">
+        <v>14.44</v>
+      </c>
+      <c r="D39" s="6">
+        <v>14.45</v>
+      </c>
+      <c r="E39" s="8">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="6">
+        <v>0.21</v>
+      </c>
+      <c r="D40" s="6">
+        <v>3.29</v>
+      </c>
+      <c r="E40" s="8">
+        <v>3.08</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-0.45</v>
+      </c>
+      <c r="D41" s="6">
+        <v>-3.3</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-2.85</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="7">
-        <v>-1.49</v>
-      </c>
-      <c r="D15" s="7">
-        <v>-0.26</v>
-      </c>
-      <c r="E15" s="8">
-        <v>1.23</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="B42" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="6">
+        <v>-5.94</v>
+      </c>
+      <c r="D42" s="6">
+        <v>-7.26</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-1.32</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="7">
-        <v>1.58</v>
-      </c>
-      <c r="D16" s="7">
-        <v>-3.93</v>
-      </c>
-      <c r="E16" s="9">
-        <v>-5.51</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+      <c r="B43" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="6">
+        <v>7.93</v>
+      </c>
+      <c r="D43" s="6">
+        <v>6.81</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-1.12</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-3.36</v>
-      </c>
-      <c r="D17" s="7">
+      <c r="B44" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="6">
+        <v>-19.01</v>
+      </c>
+      <c r="D44" s="6">
+        <v>-19.52</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-0.51</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-10.63</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-12.42</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-1.79</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="6">
+        <v>-6.54</v>
+      </c>
+      <c r="D46" s="6">
+        <v>-7.02</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-0.48</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="6">
+        <v>-11.96</v>
+      </c>
+      <c r="D47" s="6">
+        <v>-12.58</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-0.62</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="6">
+        <v>-9.779999999999999</v>
+      </c>
+      <c r="D48" s="6">
+        <v>-11.54</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-1.76</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="6">
+        <v>-4.71</v>
+      </c>
+      <c r="D49" s="6">
+        <v>-3.49</v>
+      </c>
+      <c r="E49" s="8">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="6">
+        <v>-39.73</v>
+      </c>
+      <c r="D50" s="6">
+        <v>-41.66</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-1.93</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="6">
+        <v>-21.09</v>
+      </c>
+      <c r="D51" s="6">
+        <v>-21.11</v>
+      </c>
+      <c r="E51" s="7">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="6">
+        <v>-11.16</v>
+      </c>
+      <c r="D52" s="6">
+        <v>-10.37</v>
+      </c>
+      <c r="E52" s="8">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="6">
+        <v>397</v>
+      </c>
+      <c r="D53" s="6">
+        <v>394.5</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-2.5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="6">
+        <v>3398.2</v>
+      </c>
+      <c r="D54" s="6">
+        <v>3330</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-68.2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="6">
+        <v>385.35</v>
+      </c>
+      <c r="D55" s="6">
+        <v>383.35</v>
+      </c>
+      <c r="E55" s="7">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="6">
+        <v>371.25</v>
+      </c>
+      <c r="D56" s="6">
+        <v>368.65</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-2.6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="6">
+        <v>399.4</v>
+      </c>
+      <c r="D57" s="6">
+        <v>391.6</v>
+      </c>
+      <c r="E57" s="7">
+        <v>-7.8</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="6">
+        <v>636.55</v>
+      </c>
+      <c r="D58" s="6">
+        <v>642.05</v>
+      </c>
+      <c r="E58" s="8">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="6">
+        <v>218.19</v>
+      </c>
+      <c r="D59" s="6">
+        <v>211.23</v>
+      </c>
+      <c r="E59" s="7">
+        <v>-6.96</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="6">
+        <v>3549</v>
+      </c>
+      <c r="D60" s="6">
+        <v>3548.3</v>
+      </c>
+      <c r="E60" s="7">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C61" s="6">
+        <v>1571</v>
+      </c>
+      <c r="D61" s="6">
+        <v>1585</v>
+      </c>
+      <c r="E61" s="8">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C62" s="6">
+        <v>66</v>
+      </c>
+      <c r="D62" s="6">
+        <v>55</v>
+      </c>
+      <c r="E62" s="7">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C63" s="6">
+        <v>55</v>
+      </c>
+      <c r="D63" s="6">
+        <v>66</v>
+      </c>
+      <c r="E63" s="8">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="6">
+        <v>30.9</v>
+      </c>
+      <c r="D64" s="6">
+        <v>29.39</v>
+      </c>
+      <c r="E64" s="7">
+        <v>-1.51</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="6">
+        <v>54.04</v>
+      </c>
+      <c r="D65" s="6">
+        <v>46.71</v>
+      </c>
+      <c r="E65" s="7">
+        <v>-7.33</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="6">
+        <v>54.58</v>
+      </c>
+      <c r="D66" s="6">
+        <v>53.19</v>
+      </c>
+      <c r="E66" s="7">
+        <v>-1.39</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="6">
+        <v>41.66</v>
+      </c>
+      <c r="D67" s="6">
+        <v>39.42</v>
+      </c>
+      <c r="E67" s="7">
+        <v>-2.24</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="6">
+        <v>47.24</v>
+      </c>
+      <c r="D68" s="6">
+        <v>40.8</v>
+      </c>
+      <c r="E68" s="7">
+        <v>-6.44</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="6">
+        <v>66.84</v>
+      </c>
+      <c r="D69" s="6">
+        <v>68.89</v>
+      </c>
+      <c r="E69" s="8">
+        <v>2.05</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="6">
+        <v>41.07</v>
+      </c>
+      <c r="D70" s="6">
+        <v>33.54</v>
+      </c>
+      <c r="E70" s="7">
+        <v>-7.53</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="6">
+        <v>34.89</v>
+      </c>
+      <c r="D71" s="6">
+        <v>34.79</v>
+      </c>
+      <c r="E71" s="7">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C72" s="6">
+        <v>44.76</v>
+      </c>
+      <c r="D72" s="6">
+        <v>48.76</v>
+      </c>
+      <c r="E72" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="6">
+        <v>-28.21</v>
+      </c>
+      <c r="D73" s="6">
+        <v>-82.26000000000001</v>
+      </c>
+      <c r="E73" s="7">
+        <v>-54.05</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="6">
+        <v>-70.08</v>
+      </c>
+      <c r="D74" s="6">
+        <v>-16.79</v>
+      </c>
+      <c r="E74" s="8">
+        <v>53.29</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="6">
+        <v>-36.87</v>
+      </c>
+      <c r="D75" s="6">
+        <v>-54.21</v>
+      </c>
+      <c r="E75" s="7">
+        <v>-17.34</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="6">
+        <v>-32.18</v>
+      </c>
+      <c r="D76" s="6">
+        <v>-53.73</v>
+      </c>
+      <c r="E76" s="7">
+        <v>-21.55</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="6">
+        <v>3.22</v>
+      </c>
+      <c r="D77" s="6">
+        <v>-45.65</v>
+      </c>
+      <c r="E77" s="7">
+        <v>-48.87</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="6">
+        <v>21.31</v>
+      </c>
+      <c r="D78" s="6">
+        <v>58.55</v>
+      </c>
+      <c r="E78" s="8">
+        <v>37.24</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="6">
         <v>-2.37</v>
       </c>
-      <c r="E17" s="8">
-        <v>0.99</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="7">
-        <v>0.63</v>
-      </c>
-      <c r="D18" s="7">
-        <v>-0.49</v>
-      </c>
-      <c r="E18" s="9">
-        <v>-1.12</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="7">
-        <v>-1.23</v>
-      </c>
-      <c r="D19" s="7">
-        <v>-1.09</v>
-      </c>
-      <c r="E19" s="8">
-        <v>0.14</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="7">
-        <v>-1.98</v>
-      </c>
-      <c r="D20" s="7">
-        <v>-0.66</v>
-      </c>
-      <c r="E20" s="8">
-        <v>1.32</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-1.2</v>
-      </c>
-      <c r="D21" s="7">
-        <v>-1.69</v>
-      </c>
-      <c r="E21" s="9">
-        <v>-0.49</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="7">
-        <v>2.52</v>
-      </c>
-      <c r="D22" s="7">
-        <v>3.69</v>
-      </c>
-      <c r="E22" s="8">
-        <v>1.17</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="7">
-        <v>-1.03</v>
-      </c>
-      <c r="D23" s="7">
-        <v>-0.59</v>
-      </c>
-      <c r="E23" s="8">
-        <v>0.44</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
+      <c r="D79" s="6">
+        <v>311.95</v>
+      </c>
+      <c r="E79" s="8">
+        <v>314.32</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="7">
-        <v>-1.18</v>
-      </c>
-      <c r="D24" s="7">
-        <v>-1.11</v>
-      </c>
-      <c r="E24" s="8">
-        <v>0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
+      <c r="B80" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="6">
+        <v>-28.48</v>
+      </c>
+      <c r="D80" s="6">
+        <v>-28.18</v>
+      </c>
+      <c r="E80" s="8">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="D25" s="7">
-        <v>-1.18</v>
-      </c>
-      <c r="E25" s="9">
-        <v>-1.68</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="7">
-        <v>-0.37</v>
-      </c>
-      <c r="D26" s="7">
-        <v>0.38</v>
-      </c>
-      <c r="E26" s="8">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="7">
-        <v>1.4</v>
-      </c>
-      <c r="D27" s="7">
-        <v>0.68</v>
-      </c>
-      <c r="E27" s="9">
-        <v>-0.72</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="7">
-        <v>42.73</v>
-      </c>
-      <c r="D28" s="7">
-        <v>47.79</v>
-      </c>
-      <c r="E28" s="8">
-        <v>5.06</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="7">
-        <v>6.24</v>
-      </c>
-      <c r="D29" s="7">
-        <v>6.73</v>
-      </c>
-      <c r="E29" s="8">
-        <v>0.49</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="7">
-        <v>24.36</v>
-      </c>
-      <c r="D30" s="7">
-        <v>22.8</v>
-      </c>
-      <c r="E30" s="9">
-        <v>-1.56</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="7">
-        <v>-6.6</v>
-      </c>
-      <c r="D31" s="7">
-        <v>-5.7</v>
-      </c>
-      <c r="E31" s="8">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="7">
-        <v>-39.72</v>
-      </c>
-      <c r="D32" s="7">
-        <v>-39.78</v>
-      </c>
-      <c r="E32" s="9">
-        <v>-0.06</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="7">
-        <v>-12.72</v>
-      </c>
-      <c r="D33" s="7">
-        <v>-13.9</v>
-      </c>
-      <c r="E33" s="9">
-        <v>-1.18</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="7">
-        <v>6.07</v>
-      </c>
-      <c r="D34" s="7">
-        <v>4.35</v>
-      </c>
-      <c r="E34" s="9">
-        <v>-1.72</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="7">
-        <v>-13.5</v>
-      </c>
-      <c r="D35" s="7">
-        <v>-13.27</v>
-      </c>
-      <c r="E35" s="8">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="7">
-        <v>10.3</v>
-      </c>
-      <c r="D36" s="7">
-        <v>8.859999999999999</v>
-      </c>
-      <c r="E36" s="9">
-        <v>-1.44</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="7">
-        <v>24.98</v>
-      </c>
-      <c r="D37" s="7">
-        <v>26.26</v>
-      </c>
-      <c r="E37" s="8">
-        <v>1.28</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="7">
-        <v>10.07</v>
-      </c>
-      <c r="D38" s="7">
-        <v>8.52</v>
-      </c>
-      <c r="E38" s="9">
-        <v>-1.55</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="7">
-        <v>14.53</v>
-      </c>
-      <c r="D39" s="7">
-        <v>14.44</v>
-      </c>
-      <c r="E39" s="9">
-        <v>-0.09</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="7">
-        <v>-0.04</v>
-      </c>
-      <c r="D40" s="7">
-        <v>-0.45</v>
-      </c>
-      <c r="E40" s="9">
-        <v>-0.41</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="7">
-        <v>-5.87</v>
-      </c>
-      <c r="D41" s="7">
-        <v>-5.94</v>
-      </c>
-      <c r="E41" s="9">
-        <v>-0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="7">
-        <v>9.91</v>
-      </c>
-      <c r="D42" s="7">
-        <v>7.93</v>
-      </c>
-      <c r="E42" s="9">
-        <v>-1.98</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="7">
-        <v>-19.23</v>
-      </c>
-      <c r="D43" s="7">
-        <v>-19.01</v>
-      </c>
-      <c r="E43" s="8">
-        <v>0.22</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="7">
-        <v>-9.449999999999999</v>
-      </c>
-      <c r="D44" s="7">
-        <v>-10.63</v>
-      </c>
-      <c r="E44" s="9">
-        <v>-1.18</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="7">
-        <v>-7.48</v>
-      </c>
-      <c r="D45" s="7">
-        <v>-6.54</v>
-      </c>
-      <c r="E45" s="8">
-        <v>0.9399999999999999</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="7">
-        <v>-10.71</v>
-      </c>
-      <c r="D46" s="7">
-        <v>-11.96</v>
-      </c>
-      <c r="E46" s="9">
-        <v>-1.25</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="7">
-        <v>-9.710000000000001</v>
-      </c>
-      <c r="D47" s="7">
-        <v>-9.779999999999999</v>
-      </c>
-      <c r="E47" s="9">
-        <v>-0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="7">
-        <v>-5.7</v>
-      </c>
-      <c r="D48" s="7">
-        <v>-4.71</v>
-      </c>
-      <c r="E48" s="8">
-        <v>0.99</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="7">
-        <v>-39.53</v>
-      </c>
-      <c r="D49" s="7">
-        <v>-39.73</v>
-      </c>
-      <c r="E49" s="9">
-        <v>-0.2</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="7">
-        <v>-21.03</v>
-      </c>
-      <c r="D50" s="7">
-        <v>-21.09</v>
-      </c>
-      <c r="E50" s="9">
-        <v>-0.06</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="7">
-        <v>-9.529999999999999</v>
-      </c>
-      <c r="D51" s="7">
-        <v>-11.16</v>
-      </c>
-      <c r="E51" s="9">
-        <v>-1.63</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="7">
-        <v>395.95</v>
-      </c>
-      <c r="D52" s="7">
-        <v>397</v>
-      </c>
-      <c r="E52" s="8">
-        <v>1.05</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="7">
-        <v>3443</v>
-      </c>
-      <c r="D53" s="7">
-        <v>3398.2</v>
-      </c>
-      <c r="E53" s="9">
-        <v>-44.8</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="7">
-        <v>381.45</v>
-      </c>
-      <c r="D54" s="7">
-        <v>385.35</v>
-      </c>
-      <c r="E54" s="8">
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="7">
-        <v>376.55</v>
-      </c>
-      <c r="D55" s="7">
-        <v>371.25</v>
-      </c>
-      <c r="E55" s="9">
-        <v>-5.3</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="7">
-        <v>399.7</v>
-      </c>
-      <c r="D56" s="7">
-        <v>399.4</v>
-      </c>
-      <c r="E56" s="9">
-        <v>-0.3</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="7">
-        <v>219.1</v>
-      </c>
-      <c r="D57" s="7">
-        <v>218.19</v>
-      </c>
-      <c r="E57" s="9">
-        <v>-0.91</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="7">
-        <v>3551.7</v>
-      </c>
-      <c r="D58" s="7">
-        <v>3549</v>
-      </c>
-      <c r="E58" s="9">
-        <v>-2.7</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="7">
-        <v>1599.9</v>
-      </c>
-      <c r="D59" s="7">
-        <v>1571</v>
-      </c>
-      <c r="E59" s="9">
-        <v>-28.9</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C60" s="7">
-        <v>55</v>
-      </c>
-      <c r="D60" s="7">
-        <v>66</v>
-      </c>
-      <c r="E60" s="8">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C61" s="7">
-        <v>66</v>
-      </c>
-      <c r="D61" s="7">
-        <v>77</v>
-      </c>
-      <c r="E61" s="8">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C62" s="7">
-        <v>77</v>
-      </c>
-      <c r="D62" s="7">
-        <v>55</v>
-      </c>
-      <c r="E62" s="9">
-        <v>-22</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C63" s="7">
-        <v>29.49</v>
-      </c>
-      <c r="D63" s="7">
-        <v>30.9</v>
-      </c>
-      <c r="E63" s="8">
-        <v>1.41</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="7">
-        <v>59.77</v>
-      </c>
-      <c r="D64" s="7">
-        <v>54.04</v>
-      </c>
-      <c r="E64" s="9">
-        <v>-5.73</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="7">
-        <v>52.32</v>
-      </c>
-      <c r="D65" s="7">
-        <v>54.58</v>
-      </c>
-      <c r="E65" s="8">
-        <v>2.26</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="7">
-        <v>46.68</v>
-      </c>
-      <c r="D66" s="7">
-        <v>41.66</v>
-      </c>
-      <c r="E66" s="9">
-        <v>-5.02</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="7">
-        <v>47.5</v>
-      </c>
-      <c r="D67" s="7">
-        <v>47.24</v>
-      </c>
-      <c r="E67" s="9">
-        <v>-0.26</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="7">
-        <v>42.22</v>
-      </c>
-      <c r="D68" s="7">
-        <v>41.07</v>
-      </c>
-      <c r="E68" s="9">
-        <v>-1.15</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="7">
-        <v>35.27</v>
-      </c>
-      <c r="D69" s="7">
-        <v>34.89</v>
-      </c>
-      <c r="E69" s="9">
-        <v>-0.38</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="7">
-        <v>52.65</v>
-      </c>
-      <c r="D70" s="7">
-        <v>44.76</v>
-      </c>
-      <c r="E70" s="9">
-        <v>-7.89</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B71" s="6" t="s">
+      <c r="B81" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C71" s="7">
-        <v>-15.16</v>
-      </c>
-      <c r="D71" s="7">
-        <v>-28.21</v>
-      </c>
-      <c r="E71" s="9">
-        <v>-13.05</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C72" s="7">
-        <v>-54.24</v>
-      </c>
-      <c r="D72" s="7">
-        <v>-70.08</v>
-      </c>
-      <c r="E72" s="9">
-        <v>-15.84</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C73" s="7">
-        <v>-40</v>
-      </c>
-      <c r="D73" s="7">
-        <v>-36.87</v>
-      </c>
-      <c r="E73" s="8">
-        <v>3.13</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B74" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="7">
-        <v>-48.79</v>
-      </c>
-      <c r="D74" s="7">
-        <v>-32.18</v>
-      </c>
-      <c r="E74" s="8">
-        <v>16.61</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B75" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="7">
-        <v>-57.86</v>
-      </c>
-      <c r="D75" s="7">
-        <v>3.22</v>
-      </c>
-      <c r="E75" s="8">
-        <v>61.08</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B76" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="7">
-        <v>80.22</v>
-      </c>
-      <c r="D76" s="7">
-        <v>21.31</v>
-      </c>
-      <c r="E76" s="9">
-        <v>-58.91</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B77" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="7">
-        <v>-18.78</v>
-      </c>
-      <c r="D77" s="7">
-        <v>-2.37</v>
-      </c>
-      <c r="E77" s="8">
-        <v>16.41</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B78" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="7">
-        <v>-47.39</v>
-      </c>
-      <c r="D78" s="7">
-        <v>-28.48</v>
-      </c>
-      <c r="E78" s="8">
-        <v>18.91</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B79" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="7">
-        <v>-51.59</v>
-      </c>
-      <c r="D79" s="7">
+      <c r="C81" s="6">
         <v>-42.47</v>
       </c>
-      <c r="E79" s="8">
-        <v>9.119999999999999</v>
+      <c r="D81" s="6">
+        <v>-26.32</v>
+      </c>
+      <c r="E81" s="8">
+        <v>16.15</v>
       </c>
     </row>
   </sheetData>
@@ -3444,60 +3471,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="E1" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="F1" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="G1" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="H1" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="I1" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="H1" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>79</v>
-      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="12">
-        <v>60.16</v>
-      </c>
-      <c r="C2" s="13">
+      <c r="B2" s="11">
+        <v>56.16</v>
+      </c>
+      <c r="C2" s="12">
         <v>9</v>
       </c>
-      <c r="D2" s="12">
-        <v>46.2</v>
-      </c>
-      <c r="E2" s="12">
-        <v>70</v>
-      </c>
-      <c r="F2" s="12">
-        <v>0.7</v>
-      </c>
-      <c r="G2" s="12">
-        <v>5.2</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="D2" s="11">
+        <v>43.9</v>
+      </c>
+      <c r="E2" s="11">
+        <v>60</v>
+      </c>
+      <c r="F2" s="11">
+        <v>-1</v>
+      </c>
+      <c r="G2" s="11">
+        <v>5.4</v>
+      </c>
+      <c r="H2" s="11">
         <v>55.4</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="11">
         <v>60</v>
       </c>
     </row>
@@ -3599,61 +3626,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="13" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="15">
-        <v>0.3515</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0.3383</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0.2191</v>
-      </c>
-      <c r="D2" s="15">
-        <v>0.1993</v>
-      </c>
-      <c r="E2" s="15">
-        <v>0.1264</v>
-      </c>
-      <c r="F2" s="15">
-        <v>0.0839</v>
-      </c>
-      <c r="G2" s="15">
-        <v>0.0469</v>
-      </c>
-      <c r="H2" s="15">
-        <v>0.0131</v>
-      </c>
-      <c r="I2" s="15">
-        <v>-0.1107</v>
+      <c r="A2" s="14">
+        <v>0.3482</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.341</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.2171</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.2018</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.1307</v>
+      </c>
+      <c r="F2" s="14">
+        <v>0.0815</v>
+      </c>
+      <c r="G2" s="14">
+        <v>0.04940000000000001</v>
+      </c>
+      <c r="H2" s="14">
+        <v>0.0052</v>
+      </c>
+      <c r="I2" s="14">
+        <v>-0.1221</v>
       </c>
     </row>
   </sheetData>

--- a/MAHINDRA_GROUP_Technical_Metrics.xlsx
+++ b/MAHINDRA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="89">
   <si>
     <t>Symbol</t>
   </si>
@@ -193,28 +193,61 @@
     <t>Curr Value</t>
   </si>
   <si>
+    <t>Near 52W High</t>
+  </si>
+  <si>
+    <t>-3.5% → -0.4%</t>
+  </si>
+  <si>
+    <t>🟢 BREAKOUT WATCH</t>
+  </si>
+  <si>
+    <t>-3.5%</t>
+  </si>
+  <si>
+    <t>-0.4%</t>
+  </si>
+  <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>54.0 → 46.7</t>
+    <t>48.8 → 60.9</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>48.8</t>
+  </si>
+  <si>
+    <t>60.9</t>
+  </si>
+  <si>
+    <t>RSI Overbought Entry</t>
+  </si>
+  <si>
+    <t>68.9 → 74.9</t>
+  </si>
+  <si>
+    <t>⚠️ CAUTION</t>
+  </si>
+  <si>
+    <t>68.9</t>
+  </si>
+  <si>
+    <t>74.9</t>
+  </si>
+  <si>
+    <t>53.2 → 48.7</t>
   </si>
   <si>
     <t>🔴 BEARISH</t>
   </si>
   <si>
-    <t>54.0</t>
-  </si>
-  <si>
-    <t>46.7</t>
-  </si>
-  <si>
-    <t>50 DMA &gt; 200 DMA</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
-  </si>
-  <si>
-    <t>🔴 DEATH CROSS</t>
+    <t>53.2</t>
+  </si>
+  <si>
+    <t>48.7</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -266,7 +299,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -300,20 +333,27 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -340,13 +380,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,7 +462,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -424,14 +470,16 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -440,7 +488,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -939,10 +987,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>394.5</v>
+        <v>389.95</v>
       </c>
       <c r="D2">
-        <v>-0.63</v>
+        <v>-1.15</v>
       </c>
       <c r="E2">
         <v>490.2</v>
@@ -951,46 +999,46 @@
         <v>379.2</v>
       </c>
       <c r="G2">
-        <v>-19.52</v>
+        <v>-20.45</v>
       </c>
       <c r="H2">
-        <v>4.03</v>
+        <v>2.83</v>
       </c>
       <c r="I2">
-        <v>-2.3</v>
+        <v>-2.77</v>
       </c>
       <c r="J2">
-        <v>-4.88</v>
+        <v>-5.33</v>
       </c>
       <c r="K2">
-        <v>-11.64</v>
+        <v>-10.85</v>
       </c>
       <c r="L2">
-        <v>0.41</v>
+        <v>-0.85</v>
       </c>
       <c r="M2">
-        <v>13.07</v>
+        <v>13.08</v>
       </c>
       <c r="N2">
         <v>34</v>
       </c>
       <c r="O2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="P2">
-        <v>397.57</v>
+        <v>395.35</v>
       </c>
       <c r="Q2">
-        <v>407.05</v>
+        <v>406.12</v>
       </c>
       <c r="R2">
-        <v>436.29</v>
+        <v>434.97</v>
       </c>
       <c r="S2">
-        <v>437.21</v>
+        <v>437.01</v>
       </c>
       <c r="T2">
-        <v>-9.77</v>
+        <v>-10.77</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1005,43 +1053,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>29.39</v>
+        <v>26.83</v>
       </c>
       <c r="Z2">
-        <v>-10.52</v>
+        <v>-10.78</v>
       </c>
       <c r="AA2">
         <v>-10.78</v>
       </c>
       <c r="AB2">
-        <v>0.26</v>
+        <v>0.01</v>
       </c>
       <c r="AC2">
         <v>5.41</v>
       </c>
       <c r="AD2">
-        <v>3.61</v>
+        <v>5.41</v>
       </c>
       <c r="AE2">
-        <v>9.01</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="AF2">
-        <v>-82.26000000000001</v>
+        <v>-41.98</v>
       </c>
       <c r="AG2">
-        <v>420.2</v>
+        <v>421.29</v>
       </c>
       <c r="AH2">
-        <v>393.9</v>
+        <v>390.94</v>
       </c>
       <c r="AI2">
-        <v>423.49</v>
+        <v>420.15</v>
       </c>
       <c r="AJ2" t="s">
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>45.81</v>
+        <v>48.56</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1052,10 +1100,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>3330</v>
+        <v>3334</v>
       </c>
       <c r="D3">
-        <v>-2.01</v>
+        <v>0.12</v>
       </c>
       <c r="E3">
         <v>3802.4</v>
@@ -1064,46 +1112,46 @@
         <v>2931.1</v>
       </c>
       <c r="G3">
-        <v>-12.42</v>
+        <v>-12.32</v>
       </c>
       <c r="H3">
-        <v>13.61</v>
+        <v>13.75</v>
       </c>
       <c r="I3">
-        <v>-2.77</v>
+        <v>-2.29</v>
       </c>
       <c r="J3">
-        <v>3.36</v>
+        <v>1.53</v>
       </c>
       <c r="K3">
-        <v>9.34</v>
+        <v>12.25</v>
       </c>
       <c r="L3">
-        <v>-2.15</v>
+        <v>-1.91</v>
       </c>
       <c r="M3">
-        <v>34.82</v>
+        <v>34.33</v>
       </c>
       <c r="N3">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="O3">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="P3">
-        <v>3399.5</v>
+        <v>3383.86</v>
       </c>
       <c r="Q3">
-        <v>3425.5</v>
+        <v>3422.27</v>
       </c>
       <c r="R3">
-        <v>3258.74</v>
+        <v>3262.69</v>
       </c>
       <c r="S3">
-        <v>3348.45</v>
+        <v>3346.37</v>
       </c>
       <c r="T3">
-        <v>-0.55</v>
+        <v>-0.37</v>
       </c>
       <c r="U3" t="s">
         <v>48</v>
@@ -1118,34 +1166,34 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>46.71</v>
+        <v>47.16</v>
       </c>
       <c r="Z3">
-        <v>36.19</v>
+        <v>28.23</v>
       </c>
       <c r="AA3">
-        <v>54.43</v>
+        <v>49.19</v>
       </c>
       <c r="AB3">
-        <v>-18.25</v>
+        <v>-20.97</v>
       </c>
       <c r="AC3">
-        <v>9.5</v>
+        <v>0.9</v>
       </c>
       <c r="AD3">
-        <v>12.19</v>
+        <v>7.58</v>
       </c>
       <c r="AE3">
-        <v>64.65000000000001</v>
+        <v>63.59</v>
       </c>
       <c r="AF3">
-        <v>-16.79</v>
+        <v>-18.42</v>
       </c>
       <c r="AG3">
-        <v>3504.73</v>
+        <v>3510.83</v>
       </c>
       <c r="AH3">
-        <v>3346.26</v>
+        <v>3333.71</v>
       </c>
       <c r="AI3">
         <v>3274.47</v>
@@ -1154,7 +1202,7 @@
         <v>50</v>
       </c>
       <c r="AK3">
-        <v>23.83</v>
+        <v>26.23</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1165,10 +1213,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>383.35</v>
+        <v>376.6</v>
       </c>
       <c r="D4">
-        <v>-0.52</v>
+        <v>-1.76</v>
       </c>
       <c r="E4">
         <v>412.3</v>
@@ -1177,46 +1225,46 @@
         <v>253.95</v>
       </c>
       <c r="G4">
-        <v>-7.02</v>
+        <v>-8.66</v>
       </c>
       <c r="H4">
-        <v>50.95</v>
+        <v>48.3</v>
       </c>
       <c r="I4">
-        <v>0.24</v>
+        <v>-1.31</v>
       </c>
       <c r="J4">
-        <v>-2.64</v>
+        <v>-4.06</v>
       </c>
       <c r="K4">
-        <v>26.25</v>
+        <v>27.62</v>
       </c>
       <c r="L4">
-        <v>45.76</v>
+        <v>41.55</v>
       </c>
       <c r="M4">
-        <v>21.71</v>
+        <v>20.67</v>
       </c>
       <c r="N4">
         <v>99</v>
       </c>
       <c r="O4">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="P4">
-        <v>382.09</v>
+        <v>381.09</v>
       </c>
       <c r="Q4">
-        <v>391.83</v>
+        <v>391.37</v>
       </c>
       <c r="R4">
-        <v>357.04</v>
+        <v>358.65</v>
       </c>
       <c r="S4">
-        <v>342.42</v>
+        <v>342.72</v>
       </c>
       <c r="T4">
-        <v>11.95</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="U4" t="s">
         <v>48</v>
@@ -1231,34 +1279,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>53.19</v>
+        <v>48.67</v>
       </c>
       <c r="Z4">
-        <v>6.02</v>
+        <v>4.87</v>
       </c>
       <c r="AA4">
-        <v>9.94</v>
+        <v>8.93</v>
       </c>
       <c r="AB4">
-        <v>-3.93</v>
+        <v>-4.06</v>
       </c>
       <c r="AC4">
-        <v>13.93</v>
+        <v>11.12</v>
       </c>
       <c r="AD4">
-        <v>8.779999999999999</v>
+        <v>11.55</v>
       </c>
       <c r="AE4">
-        <v>12.51</v>
+        <v>12.27</v>
       </c>
       <c r="AF4">
-        <v>-54.21</v>
+        <v>-67.16</v>
       </c>
       <c r="AG4">
-        <v>410.95</v>
+        <v>411.52</v>
       </c>
       <c r="AH4">
-        <v>372.7</v>
+        <v>371.22</v>
       </c>
       <c r="AI4">
         <v>357.72</v>
@@ -1267,7 +1315,7 @@
         <v>50</v>
       </c>
       <c r="AK4">
-        <v>21.6</v>
+        <v>20.27</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1278,10 +1326,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>368.65</v>
+        <v>367.55</v>
       </c>
       <c r="D5">
-        <v>-0.7</v>
+        <v>-0.3</v>
       </c>
       <c r="E5">
         <v>421.7</v>
@@ -1290,46 +1338,46 @@
         <v>294.25</v>
       </c>
       <c r="G5">
-        <v>-12.58</v>
+        <v>-12.84</v>
       </c>
       <c r="H5">
-        <v>25.28</v>
+        <v>24.91</v>
       </c>
       <c r="I5">
-        <v>-2.27</v>
+        <v>-3.23</v>
       </c>
       <c r="J5">
-        <v>-4.83</v>
+        <v>-4.63</v>
       </c>
       <c r="K5">
-        <v>10.81</v>
+        <v>9.5</v>
       </c>
       <c r="L5">
-        <v>6.3</v>
+        <v>5.95</v>
       </c>
       <c r="M5">
-        <v>8.15</v>
+        <v>7.85</v>
       </c>
       <c r="N5">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="O5">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="P5">
-        <v>375.08</v>
+        <v>372.63</v>
       </c>
       <c r="Q5">
-        <v>383.12</v>
+        <v>381.86</v>
       </c>
       <c r="R5">
-        <v>375.6</v>
+        <v>375.95</v>
       </c>
       <c r="S5">
-        <v>364.19</v>
+        <v>364.06</v>
       </c>
       <c r="T5">
-        <v>1.22</v>
+        <v>0.96</v>
       </c>
       <c r="U5" t="s">
         <v>48</v>
@@ -1344,34 +1392,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>39.42</v>
+        <v>38.48</v>
       </c>
       <c r="Z5">
-        <v>-0.7</v>
+        <v>-1.45</v>
       </c>
       <c r="AA5">
-        <v>1.75</v>
+        <v>1.11</v>
       </c>
       <c r="AB5">
-        <v>-2.45</v>
+        <v>-2.56</v>
       </c>
       <c r="AC5">
-        <v>7.01</v>
+        <v>0</v>
       </c>
       <c r="AD5">
-        <v>18.46</v>
+        <v>9.09</v>
       </c>
       <c r="AE5">
-        <v>10.53</v>
+        <v>10.12</v>
       </c>
       <c r="AF5">
-        <v>-53.73</v>
+        <v>-79.37</v>
       </c>
       <c r="AG5">
-        <v>398.51</v>
+        <v>398.06</v>
       </c>
       <c r="AH5">
-        <v>367.72</v>
+        <v>365.67</v>
       </c>
       <c r="AI5">
         <v>364.94</v>
@@ -1380,7 +1428,7 @@
         <v>50</v>
       </c>
       <c r="AK5">
-        <v>29.34</v>
+        <v>30.86</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1391,10 +1439,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>391.6</v>
+        <v>392.75</v>
       </c>
       <c r="D6">
-        <v>-1.95</v>
+        <v>0.29</v>
       </c>
       <c r="E6">
         <v>442.7</v>
@@ -1403,25 +1451,25 @@
         <v>279.55</v>
       </c>
       <c r="G6">
-        <v>-11.54</v>
+        <v>-11.28</v>
       </c>
       <c r="H6">
-        <v>40.08</v>
+        <v>40.49</v>
       </c>
       <c r="I6">
-        <v>-3.7</v>
+        <v>-2.09</v>
       </c>
       <c r="J6">
-        <v>-4.36</v>
+        <v>-2.46</v>
       </c>
       <c r="K6">
-        <v>14.45</v>
+        <v>13.05</v>
       </c>
       <c r="L6">
-        <v>19.68</v>
+        <v>20.33</v>
       </c>
       <c r="M6">
-        <v>-12.21</v>
+        <v>-12.59</v>
       </c>
       <c r="N6">
         <v>88</v>
@@ -1430,19 +1478,19 @@
         <v>72</v>
       </c>
       <c r="P6">
-        <v>398.99</v>
+        <v>397.31</v>
       </c>
       <c r="Q6">
-        <v>406.7</v>
+        <v>405.86</v>
       </c>
       <c r="R6">
-        <v>395.35</v>
+        <v>396.12</v>
       </c>
       <c r="S6">
-        <v>366.16</v>
+        <v>366.46</v>
       </c>
       <c r="T6">
-        <v>6.95</v>
+        <v>7.17</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1457,34 +1505,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>40.8</v>
+        <v>42.05</v>
       </c>
       <c r="Z6">
-        <v>0.33</v>
+        <v>-0.43</v>
       </c>
       <c r="AA6">
-        <v>2.93</v>
+        <v>2.25</v>
       </c>
       <c r="AB6">
-        <v>-2.6</v>
+        <v>-2.68</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AD6">
-        <v>3.59</v>
+        <v>2.75</v>
       </c>
       <c r="AE6">
-        <v>12.05</v>
+        <v>11.69</v>
       </c>
       <c r="AF6">
-        <v>-45.65</v>
+        <v>-53.23</v>
       </c>
       <c r="AG6">
-        <v>419.91</v>
+        <v>420.39</v>
       </c>
       <c r="AH6">
-        <v>393.48</v>
+        <v>391.33</v>
       </c>
       <c r="AI6">
         <v>372.35</v>
@@ -1493,7 +1541,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>16.04</v>
+        <v>15.84</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1504,58 +1552,58 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>642.05</v>
+        <v>661.7</v>
       </c>
       <c r="D7">
-        <v>0.86</v>
+        <v>3.06</v>
       </c>
       <c r="E7">
-        <v>665.3</v>
+        <v>664.6</v>
       </c>
       <c r="F7">
         <v>506.45</v>
       </c>
       <c r="G7">
-        <v>-3.49</v>
+        <v>-0.44</v>
       </c>
       <c r="H7">
-        <v>26.77</v>
+        <v>30.65</v>
       </c>
       <c r="I7">
-        <v>5.15</v>
+        <v>4.34</v>
       </c>
       <c r="J7">
-        <v>10.33</v>
+        <v>15.57</v>
       </c>
       <c r="K7">
-        <v>3.29</v>
+        <v>7.61</v>
       </c>
       <c r="L7">
-        <v>-3.88</v>
+        <v>-0.54</v>
       </c>
       <c r="M7">
-        <v>34.1</v>
+        <v>34.94</v>
       </c>
       <c r="N7">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="O7">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="P7">
-        <v>636.8099999999999</v>
+        <v>642.3200000000001</v>
       </c>
       <c r="Q7">
-        <v>608.15</v>
+        <v>612.96</v>
       </c>
       <c r="R7">
-        <v>602.27</v>
+        <v>602.85</v>
       </c>
       <c r="S7">
-        <v>584.2</v>
+        <v>584.74</v>
       </c>
       <c r="T7">
-        <v>9.9</v>
+        <v>13.16</v>
       </c>
       <c r="U7" t="s">
         <v>48</v>
@@ -1570,16 +1618,16 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>68.89</v>
+        <v>74.88</v>
       </c>
       <c r="Z7">
-        <v>12.37</v>
+        <v>14.48</v>
       </c>
       <c r="AA7">
-        <v>8.26</v>
+        <v>9.5</v>
       </c>
       <c r="AB7">
-        <v>4.11</v>
+        <v>4.98</v>
       </c>
       <c r="AC7">
         <v>100</v>
@@ -1588,25 +1636,25 @@
         <v>100</v>
       </c>
       <c r="AE7">
-        <v>17.14</v>
+        <v>17.76</v>
       </c>
       <c r="AF7">
-        <v>58.55</v>
+        <v>170.65</v>
       </c>
       <c r="AG7">
-        <v>654.48</v>
+        <v>660.58</v>
       </c>
       <c r="AH7">
-        <v>561.8099999999999</v>
+        <v>565.35</v>
       </c>
       <c r="AI7">
-        <v>592.37</v>
+        <v>602.11</v>
       </c>
       <c r="AJ7" t="s">
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>62.04</v>
+        <v>64.95</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1617,10 +1665,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>211.23</v>
+        <v>211.39</v>
       </c>
       <c r="D8">
-        <v>-3.19</v>
+        <v>0.08</v>
       </c>
       <c r="E8">
         <v>362.05</v>
@@ -1629,46 +1677,46 @@
         <v>210.4</v>
       </c>
       <c r="G8">
-        <v>-41.66</v>
+        <v>-41.61</v>
       </c>
       <c r="H8">
-        <v>0.39</v>
+        <v>0.47</v>
       </c>
       <c r="I8">
-        <v>-4.44</v>
+        <v>-4.69</v>
       </c>
       <c r="J8">
-        <v>-1.72</v>
+        <v>-2.09</v>
       </c>
       <c r="K8">
-        <v>-3.3</v>
+        <v>-3.47</v>
       </c>
       <c r="L8">
-        <v>-41.65</v>
+        <v>-41.31</v>
       </c>
       <c r="M8">
-        <v>0.52</v>
+        <v>0.15</v>
       </c>
       <c r="N8">
         <v>12</v>
       </c>
       <c r="O8">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="P8">
-        <v>218.27</v>
+        <v>216.19</v>
       </c>
       <c r="Q8">
-        <v>223.52</v>
+        <v>223.17</v>
       </c>
       <c r="R8">
-        <v>227.34</v>
+        <v>226.91</v>
       </c>
       <c r="S8">
-        <v>263.47</v>
+        <v>262.96</v>
       </c>
       <c r="T8">
-        <v>-19.83</v>
+        <v>-19.61</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1683,43 +1731,43 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>33.54</v>
+        <v>33.84</v>
       </c>
       <c r="Z8">
-        <v>-2.5</v>
+        <v>-3.02</v>
       </c>
       <c r="AA8">
-        <v>-1.51</v>
+        <v>-1.81</v>
       </c>
       <c r="AB8">
-        <v>-0.99</v>
+        <v>-1.21</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>0.59</v>
       </c>
       <c r="AD8">
-        <v>5.87</v>
+        <v>1.93</v>
       </c>
       <c r="AE8">
-        <v>6.68</v>
+        <v>6.62</v>
       </c>
       <c r="AF8">
-        <v>311.95</v>
+        <v>37.35</v>
       </c>
       <c r="AG8">
-        <v>234.39</v>
+        <v>235.13</v>
       </c>
       <c r="AH8">
-        <v>212.65</v>
+        <v>211.21</v>
       </c>
       <c r="AI8">
-        <v>234.44</v>
+        <v>232.72</v>
       </c>
       <c r="AJ8" t="s">
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>26.34</v>
+        <v>29.59</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1730,10 +1778,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>3548.3</v>
+        <v>3544.8</v>
       </c>
       <c r="D9">
-        <v>-0.02</v>
+        <v>-0.1</v>
       </c>
       <c r="E9">
         <v>4497.5</v>
@@ -1742,46 +1790,46 @@
         <v>3308.9</v>
       </c>
       <c r="G9">
-        <v>-21.11</v>
+        <v>-21.18</v>
       </c>
       <c r="H9">
-        <v>7.24</v>
+        <v>7.13</v>
       </c>
       <c r="I9">
-        <v>-1.51</v>
+        <v>-0.7</v>
       </c>
       <c r="J9">
-        <v>-0.55</v>
+        <v>-1.74</v>
       </c>
       <c r="K9">
-        <v>-7.26</v>
+        <v>-6.74</v>
       </c>
       <c r="L9">
-        <v>-14.12</v>
+        <v>-13.93</v>
       </c>
       <c r="M9">
-        <v>20.18</v>
+        <v>19.78</v>
       </c>
       <c r="N9">
         <v>23</v>
       </c>
       <c r="O9">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="P9">
-        <v>3555.54</v>
+        <v>3550.54</v>
       </c>
       <c r="Q9">
-        <v>3596.49</v>
+        <v>3592.29</v>
       </c>
       <c r="R9">
-        <v>3710.23</v>
+        <v>3703.68</v>
       </c>
       <c r="S9">
-        <v>3699.63</v>
+        <v>3697.74</v>
       </c>
       <c r="T9">
-        <v>-4.09</v>
+        <v>-4.14</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1796,16 +1844,16 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>34.79</v>
+        <v>34.25</v>
       </c>
       <c r="Z9">
-        <v>-34.3</v>
+        <v>-34.44</v>
       </c>
       <c r="AA9">
-        <v>-34.64</v>
+        <v>-34.6</v>
       </c>
       <c r="AB9">
-        <v>0.34</v>
+        <v>0.16</v>
       </c>
       <c r="AC9">
         <v>0</v>
@@ -1814,25 +1862,25 @@
         <v>0</v>
       </c>
       <c r="AE9">
-        <v>50.68</v>
+        <v>48.85</v>
       </c>
       <c r="AF9">
-        <v>-28.18</v>
+        <v>-45.14</v>
       </c>
       <c r="AG9">
-        <v>3653.3</v>
+        <v>3651.43</v>
       </c>
       <c r="AH9">
-        <v>3539.68</v>
+        <v>3533.16</v>
       </c>
       <c r="AI9">
-        <v>3707.95</v>
+        <v>3694.04</v>
       </c>
       <c r="AJ9" t="s">
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>10.81</v>
+        <v>9.43</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1843,10 +1891,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>1585</v>
+        <v>1640.9</v>
       </c>
       <c r="D10">
-        <v>0.89</v>
+        <v>3.53</v>
       </c>
       <c r="E10">
         <v>1768.4</v>
@@ -1855,46 +1903,46 @@
         <v>1326.2</v>
       </c>
       <c r="G10">
-        <v>-10.37</v>
+        <v>-7.21</v>
       </c>
       <c r="H10">
-        <v>19.51</v>
+        <v>23.73</v>
       </c>
       <c r="I10">
-        <v>-0.45</v>
+        <v>3.59</v>
       </c>
       <c r="J10">
-        <v>-3.6</v>
+        <v>-1.68</v>
       </c>
       <c r="K10">
-        <v>6.81</v>
+        <v>6.33</v>
       </c>
       <c r="L10">
-        <v>6.42</v>
+        <v>8.58</v>
       </c>
       <c r="M10">
-        <v>4.94</v>
+        <v>6.06</v>
       </c>
       <c r="N10">
         <v>66</v>
       </c>
       <c r="O10">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="P10">
-        <v>1584.78</v>
+        <v>1596.16</v>
       </c>
       <c r="Q10">
-        <v>1617.68</v>
+        <v>1617.16</v>
       </c>
       <c r="R10">
-        <v>1540.86</v>
+        <v>1544.73</v>
       </c>
       <c r="S10">
-        <v>1510.78</v>
+        <v>1511.94</v>
       </c>
       <c r="T10">
-        <v>4.91</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="U10" t="s">
         <v>48</v>
@@ -1909,34 +1957,34 @@
         <v>3</v>
       </c>
       <c r="Y10">
-        <v>48.76</v>
+        <v>60.94</v>
       </c>
       <c r="Z10">
-        <v>5.83</v>
+        <v>8.94</v>
       </c>
       <c r="AA10">
-        <v>16.43</v>
+        <v>14.94</v>
       </c>
       <c r="AB10">
-        <v>-10.61</v>
+        <v>-5.99</v>
       </c>
       <c r="AC10">
-        <v>15.08</v>
+        <v>31.95</v>
       </c>
       <c r="AD10">
-        <v>10.86</v>
+        <v>18.59</v>
       </c>
       <c r="AE10">
-        <v>36.17</v>
+        <v>37.66</v>
       </c>
       <c r="AF10">
-        <v>-26.32</v>
+        <v>27.61</v>
       </c>
       <c r="AG10">
-        <v>1672.88</v>
+        <v>1671.21</v>
       </c>
       <c r="AH10">
-        <v>1562.48</v>
+        <v>1563.11</v>
       </c>
       <c r="AI10">
         <v>1527.05</v>
@@ -1945,7 +1993,7 @@
         <v>50</v>
       </c>
       <c r="AK10">
-        <v>36.63</v>
+        <v>35.08</v>
       </c>
     </row>
   </sheetData>
@@ -2086,7 +2134,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:F84"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2126,7 +2174,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2146,7 +2194,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>62</v>
@@ -2158,1300 +2206,1357 @@
         <v>64</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>47</v>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A6" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="B9" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B10" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C10" s="8">
+        <v>-4.88</v>
+      </c>
+      <c r="D10" s="8">
+        <v>-5.33</v>
+      </c>
+      <c r="E10" s="9">
+        <v>-0.45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="8">
+        <v>3.36</v>
+      </c>
+      <c r="D11" s="8">
+        <v>1.53</v>
+      </c>
+      <c r="E11" s="9">
+        <v>-1.83</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="8">
+        <v>-2.64</v>
+      </c>
+      <c r="D12" s="8">
+        <v>-4.06</v>
+      </c>
+      <c r="E12" s="9">
+        <v>-1.42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="8">
+        <v>-4.83</v>
+      </c>
+      <c r="D13" s="8">
+        <v>-4.63</v>
+      </c>
+      <c r="E13" s="10">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="8">
+        <v>-4.36</v>
+      </c>
+      <c r="D14" s="8">
+        <v>-2.46</v>
+      </c>
+      <c r="E14" s="10">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="8">
+        <v>10.33</v>
+      </c>
+      <c r="D15" s="8">
+        <v>15.57</v>
+      </c>
+      <c r="E15" s="10">
+        <v>5.24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="8">
+        <v>-1.72</v>
+      </c>
+      <c r="D16" s="8">
+        <v>-2.09</v>
+      </c>
+      <c r="E16" s="9">
+        <v>-0.37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="8">
+        <v>-0.55</v>
+      </c>
+      <c r="D17" s="8">
+        <v>-1.74</v>
+      </c>
+      <c r="E17" s="9">
+        <v>-1.19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="8">
+        <v>-3.6</v>
+      </c>
+      <c r="D18" s="8">
+        <v>-1.68</v>
+      </c>
+      <c r="E18" s="10">
+        <v>1.92</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="8">
+        <v>-2.3</v>
+      </c>
+      <c r="D19" s="8">
         <v>-2.77</v>
       </c>
-      <c r="D8" s="6">
-        <v>-4.88</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-2.11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="E19" s="9">
+        <v>-0.47</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>3.88</v>
-      </c>
-      <c r="D9" s="6">
-        <v>3.36</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-0.52</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="B20" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="8">
+        <v>-2.77</v>
+      </c>
+      <c r="D20" s="8">
+        <v>-2.29</v>
+      </c>
+      <c r="E20" s="10">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>3.17</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-2.64</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-5.81</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B21" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="8">
+        <v>0.24</v>
+      </c>
+      <c r="D21" s="8">
+        <v>-1.31</v>
+      </c>
+      <c r="E21" s="9">
+        <v>-1.55</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-2.37</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-4.83</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-2.46</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B22" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="8">
+        <v>-2.27</v>
+      </c>
+      <c r="D22" s="8">
+        <v>-3.23</v>
+      </c>
+      <c r="E22" s="9">
+        <v>-0.96</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>-2.68</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-4.36</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-1.68</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B23" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="8">
+        <v>-3.7</v>
+      </c>
+      <c r="D23" s="8">
+        <v>-2.09</v>
+      </c>
+      <c r="E23" s="10">
+        <v>1.61</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="6">
-        <v>10.88</v>
-      </c>
-      <c r="D13" s="6">
-        <v>10.33</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-0.55</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B24" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="8">
+        <v>5.15</v>
+      </c>
+      <c r="D24" s="8">
+        <v>4.34</v>
+      </c>
+      <c r="E24" s="9">
+        <v>-0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-0.04</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-1.72</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-1.68</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B25" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="8">
+        <v>-4.44</v>
+      </c>
+      <c r="D25" s="8">
+        <v>-4.69</v>
+      </c>
+      <c r="E25" s="9">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="6">
+      <c r="B26" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="8">
+        <v>-1.51</v>
+      </c>
+      <c r="D26" s="8">
+        <v>-0.7</v>
+      </c>
+      <c r="E26" s="10">
+        <v>0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="8">
+        <v>-0.45</v>
+      </c>
+      <c r="D27" s="8">
+        <v>3.59</v>
+      </c>
+      <c r="E27" s="10">
+        <v>4.04</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="8">
+        <v>0.41</v>
+      </c>
+      <c r="D28" s="8">
+        <v>-0.85</v>
+      </c>
+      <c r="E28" s="9">
+        <v>-1.26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="8">
+        <v>-2.15</v>
+      </c>
+      <c r="D29" s="8">
+        <v>-1.91</v>
+      </c>
+      <c r="E29" s="10">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="8">
+        <v>45.76</v>
+      </c>
+      <c r="D30" s="8">
+        <v>41.55</v>
+      </c>
+      <c r="E30" s="9">
+        <v>-4.21</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="8">
+        <v>6.3</v>
+      </c>
+      <c r="D31" s="8">
+        <v>5.95</v>
+      </c>
+      <c r="E31" s="9">
+        <v>-0.35</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="8">
+        <v>19.68</v>
+      </c>
+      <c r="D32" s="8">
+        <v>20.33</v>
+      </c>
+      <c r="E32" s="10">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="8">
+        <v>-3.88</v>
+      </c>
+      <c r="D33" s="8">
+        <v>-0.54</v>
+      </c>
+      <c r="E33" s="10">
+        <v>3.34</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="8">
+        <v>-41.65</v>
+      </c>
+      <c r="D34" s="8">
+        <v>-41.31</v>
+      </c>
+      <c r="E34" s="10">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" s="8">
+        <v>-14.12</v>
+      </c>
+      <c r="D35" s="8">
+        <v>-13.93</v>
+      </c>
+      <c r="E35" s="10">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36" s="8">
+        <v>6.42</v>
+      </c>
+      <c r="D36" s="8">
+        <v>8.58</v>
+      </c>
+      <c r="E36" s="10">
+        <v>2.16</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="8">
+        <v>-11.64</v>
+      </c>
+      <c r="D37" s="8">
+        <v>-10.85</v>
+      </c>
+      <c r="E37" s="10">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="8">
+        <v>9.34</v>
+      </c>
+      <c r="D38" s="8">
+        <v>12.25</v>
+      </c>
+      <c r="E38" s="10">
+        <v>2.91</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="8">
+        <v>26.25</v>
+      </c>
+      <c r="D39" s="8">
+        <v>27.62</v>
+      </c>
+      <c r="E39" s="10">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="8">
+        <v>10.81</v>
+      </c>
+      <c r="D40" s="8">
+        <v>9.5</v>
+      </c>
+      <c r="E40" s="9">
+        <v>-1.31</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="8">
+        <v>14.45</v>
+      </c>
+      <c r="D41" s="8">
+        <v>13.05</v>
+      </c>
+      <c r="E41" s="9">
+        <v>-1.4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="8">
+        <v>3.29</v>
+      </c>
+      <c r="D42" s="8">
+        <v>7.61</v>
+      </c>
+      <c r="E42" s="10">
+        <v>4.32</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="8">
+        <v>-3.3</v>
+      </c>
+      <c r="D43" s="8">
+        <v>-3.47</v>
+      </c>
+      <c r="E43" s="9">
+        <v>-0.17</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="8">
+        <v>-7.26</v>
+      </c>
+      <c r="D44" s="8">
+        <v>-6.74</v>
+      </c>
+      <c r="E44" s="10">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="8">
+        <v>6.81</v>
+      </c>
+      <c r="D45" s="8">
+        <v>6.33</v>
+      </c>
+      <c r="E45" s="9">
+        <v>-0.48</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="8">
+        <v>-19.52</v>
+      </c>
+      <c r="D46" s="8">
+        <v>-20.45</v>
+      </c>
+      <c r="E46" s="9">
+        <v>-0.93</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="8">
+        <v>-12.42</v>
+      </c>
+      <c r="D47" s="8">
+        <v>-12.32</v>
+      </c>
+      <c r="E47" s="10">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="8">
+        <v>-7.02</v>
+      </c>
+      <c r="D48" s="8">
+        <v>-8.66</v>
+      </c>
+      <c r="E48" s="9">
+        <v>-1.64</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="8">
+        <v>-12.58</v>
+      </c>
+      <c r="D49" s="8">
+        <v>-12.84</v>
+      </c>
+      <c r="E49" s="9">
         <v>-0.26</v>
       </c>
-      <c r="D15" s="6">
-        <v>-0.55</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-0.29</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="8">
+        <v>-11.54</v>
+      </c>
+      <c r="D50" s="8">
+        <v>-11.28</v>
+      </c>
+      <c r="E50" s="10">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="8">
+        <v>-3.49</v>
+      </c>
+      <c r="D51" s="8">
+        <v>-0.44</v>
+      </c>
+      <c r="E51" s="10">
+        <v>3.05</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="8">
+        <v>-41.66</v>
+      </c>
+      <c r="D52" s="8">
+        <v>-41.61</v>
+      </c>
+      <c r="E52" s="10">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53" s="8">
+        <v>-21.11</v>
+      </c>
+      <c r="D53" s="8">
+        <v>-21.18</v>
+      </c>
+      <c r="E53" s="9">
+        <v>-0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-3.93</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-3.6</v>
-      </c>
-      <c r="E16" s="8">
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B54" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54" s="8">
+        <v>-10.37</v>
+      </c>
+      <c r="D54" s="8">
+        <v>-7.21</v>
+      </c>
+      <c r="E54" s="10">
+        <v>3.16</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-2.37</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-2.3</v>
-      </c>
-      <c r="E17" s="8">
-        <v>0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B55" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="8">
+        <v>394.5</v>
+      </c>
+      <c r="D55" s="8">
+        <v>389.95</v>
+      </c>
+      <c r="E55" s="9">
+        <v>-4.55</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-0.49</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-2.77</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-2.28</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B56" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="8">
+        <v>3330</v>
+      </c>
+      <c r="D56" s="8">
+        <v>3334</v>
+      </c>
+      <c r="E56" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-1.09</v>
-      </c>
-      <c r="D19" s="6">
-        <v>0.24</v>
-      </c>
-      <c r="E19" s="8">
-        <v>1.33</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B57" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="8">
+        <v>383.35</v>
+      </c>
+      <c r="D57" s="8">
+        <v>376.6</v>
+      </c>
+      <c r="E57" s="9">
+        <v>-6.75</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-0.66</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-2.27</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-1.61</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B58" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="8">
+        <v>368.65</v>
+      </c>
+      <c r="D58" s="8">
+        <v>367.55</v>
+      </c>
+      <c r="E58" s="9">
+        <v>-1.1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-1.69</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-3.7</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-2.01</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B59" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="8">
+        <v>391.6</v>
+      </c>
+      <c r="D59" s="8">
+        <v>392.75</v>
+      </c>
+      <c r="E59" s="10">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="6">
-        <v>3.69</v>
-      </c>
-      <c r="D22" s="6">
-        <v>5.15</v>
-      </c>
-      <c r="E22" s="8">
-        <v>1.46</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B60" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="8">
+        <v>642.05</v>
+      </c>
+      <c r="D60" s="8">
+        <v>661.7</v>
+      </c>
+      <c r="E60" s="10">
+        <v>19.65</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-0.59</v>
-      </c>
-      <c r="D23" s="6">
-        <v>-4.44</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-3.85</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B61" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C61" s="8">
+        <v>211.23</v>
+      </c>
+      <c r="D61" s="8">
+        <v>211.39</v>
+      </c>
+      <c r="E61" s="10">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-1.11</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-1.51</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-0.4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B62" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C62" s="8">
+        <v>3548.3</v>
+      </c>
+      <c r="D62" s="8">
+        <v>3544.8</v>
+      </c>
+      <c r="E62" s="9">
+        <v>-3.5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-1.18</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-0.45</v>
-      </c>
-      <c r="E25" s="8">
-        <v>0.73</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="B63" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C63" s="8">
+        <v>1585</v>
+      </c>
+      <c r="D63" s="8">
+        <v>1640.9</v>
+      </c>
+      <c r="E63" s="10">
+        <v>55.9</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C64" s="8">
+        <v>55</v>
+      </c>
+      <c r="D64" s="8">
+        <v>45</v>
+      </c>
+      <c r="E64" s="9">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B65" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C65" s="8">
+        <v>77</v>
+      </c>
+      <c r="D65" s="8">
+        <v>55</v>
+      </c>
+      <c r="E65" s="9">
+        <v>-22</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C66" s="8">
+        <v>45</v>
+      </c>
+      <c r="D66" s="8">
+        <v>77</v>
+      </c>
+      <c r="E66" s="10">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>0.38</v>
-      </c>
-      <c r="D26" s="6">
-        <v>0.41</v>
-      </c>
-      <c r="E26" s="8">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B67" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="8">
+        <v>29.39</v>
+      </c>
+      <c r="D67" s="8">
+        <v>26.83</v>
+      </c>
+      <c r="E67" s="9">
+        <v>-2.56</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>0.68</v>
-      </c>
-      <c r="D27" s="6">
-        <v>-2.15</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-2.83</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="B68" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="8">
+        <v>46.71</v>
+      </c>
+      <c r="D68" s="8">
+        <v>47.16</v>
+      </c>
+      <c r="E68" s="10">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="6">
-        <v>47.79</v>
-      </c>
-      <c r="D28" s="6">
-        <v>45.76</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-2.03</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="B69" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="8">
+        <v>53.19</v>
+      </c>
+      <c r="D69" s="8">
+        <v>48.67</v>
+      </c>
+      <c r="E69" s="9">
+        <v>-4.52</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="6">
-        <v>6.73</v>
-      </c>
-      <c r="D29" s="6">
-        <v>6.3</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-0.43</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="B70" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="8">
+        <v>39.42</v>
+      </c>
+      <c r="D70" s="8">
+        <v>38.48</v>
+      </c>
+      <c r="E70" s="9">
+        <v>-0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="6">
-        <v>22.8</v>
-      </c>
-      <c r="D30" s="6">
-        <v>19.68</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-3.12</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
+      <c r="B71" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="8">
+        <v>40.8</v>
+      </c>
+      <c r="D71" s="8">
+        <v>42.05</v>
+      </c>
+      <c r="E71" s="10">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-5.7</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-3.88</v>
-      </c>
-      <c r="E31" s="8">
-        <v>1.82</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
+      <c r="B72" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C72" s="8">
+        <v>68.89</v>
+      </c>
+      <c r="D72" s="8">
+        <v>74.88</v>
+      </c>
+      <c r="E72" s="10">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-39.78</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-41.65</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-1.87</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
+      <c r="B73" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C73" s="8">
+        <v>33.54</v>
+      </c>
+      <c r="D73" s="8">
+        <v>33.84</v>
+      </c>
+      <c r="E73" s="10">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="6">
-        <v>-13.9</v>
-      </c>
-      <c r="D33" s="6">
-        <v>-14.12</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-0.22</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
+      <c r="B74" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C74" s="8">
+        <v>34.79</v>
+      </c>
+      <c r="D74" s="8">
+        <v>34.25</v>
+      </c>
+      <c r="E74" s="9">
+        <v>-0.54</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="6">
-        <v>4.35</v>
-      </c>
-      <c r="D34" s="6">
-        <v>6.42</v>
-      </c>
-      <c r="E34" s="8">
-        <v>2.07</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
+      <c r="B75" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C75" s="8">
+        <v>48.76</v>
+      </c>
+      <c r="D75" s="8">
+        <v>60.94</v>
+      </c>
+      <c r="E75" s="10">
+        <v>12.18</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="6">
-        <v>-13.27</v>
-      </c>
-      <c r="D35" s="6">
-        <v>-11.64</v>
-      </c>
-      <c r="E35" s="8">
-        <v>1.63</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
+      <c r="B76" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="8">
+        <v>-82.26000000000001</v>
+      </c>
+      <c r="D76" s="8">
+        <v>-41.98</v>
+      </c>
+      <c r="E76" s="10">
+        <v>40.28</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="6">
-        <v>8.859999999999999</v>
-      </c>
-      <c r="D36" s="6">
-        <v>9.34</v>
-      </c>
-      <c r="E36" s="8">
-        <v>0.48</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
+      <c r="B77" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="8">
+        <v>-16.79</v>
+      </c>
+      <c r="D77" s="8">
+        <v>-18.42</v>
+      </c>
+      <c r="E77" s="9">
+        <v>-1.63</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="6">
-        <v>26.26</v>
-      </c>
-      <c r="D37" s="6">
-        <v>26.25</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-0.01</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
+      <c r="B78" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="8">
+        <v>-54.21</v>
+      </c>
+      <c r="D78" s="8">
+        <v>-67.16</v>
+      </c>
+      <c r="E78" s="9">
+        <v>-12.95</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="6">
-        <v>8.52</v>
-      </c>
-      <c r="D38" s="6">
-        <v>10.81</v>
-      </c>
-      <c r="E38" s="8">
-        <v>2.29</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
+      <c r="B79" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="8">
+        <v>-53.73</v>
+      </c>
+      <c r="D79" s="8">
+        <v>-79.37</v>
+      </c>
+      <c r="E79" s="9">
+        <v>-25.64</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B39" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="6">
-        <v>14.44</v>
-      </c>
-      <c r="D39" s="6">
-        <v>14.45</v>
-      </c>
-      <c r="E39" s="8">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
+      <c r="B80" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="8">
+        <v>-45.65</v>
+      </c>
+      <c r="D80" s="8">
+        <v>-53.23</v>
+      </c>
+      <c r="E80" s="9">
+        <v>-7.58</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B40" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="6">
-        <v>0.21</v>
-      </c>
-      <c r="D40" s="6">
-        <v>3.29</v>
-      </c>
-      <c r="E40" s="8">
-        <v>3.08</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
+      <c r="B81" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81" s="8">
+        <v>58.55</v>
+      </c>
+      <c r="D81" s="8">
+        <v>170.65</v>
+      </c>
+      <c r="E81" s="10">
+        <v>112.1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B41" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="6">
-        <v>-0.45</v>
-      </c>
-      <c r="D41" s="6">
-        <v>-3.3</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-2.85</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
+      <c r="B82" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C82" s="8">
+        <v>311.95</v>
+      </c>
+      <c r="D82" s="8">
+        <v>37.35</v>
+      </c>
+      <c r="E82" s="9">
+        <v>-274.6</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B42" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="6">
-        <v>-5.94</v>
-      </c>
-      <c r="D42" s="6">
-        <v>-7.26</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-1.32</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
+      <c r="B83" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C83" s="8">
+        <v>-28.18</v>
+      </c>
+      <c r="D83" s="8">
+        <v>-45.14</v>
+      </c>
+      <c r="E83" s="9">
+        <v>-16.96</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B43" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="6">
-        <v>7.93</v>
-      </c>
-      <c r="D43" s="6">
-        <v>6.81</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-1.12</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="6">
-        <v>-19.01</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-19.52</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-0.51</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-10.63</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-12.42</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-1.79</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-6.54</v>
-      </c>
-      <c r="D46" s="6">
-        <v>-7.02</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-0.48</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="6">
-        <v>-11.96</v>
-      </c>
-      <c r="D47" s="6">
-        <v>-12.58</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-0.62</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="6">
-        <v>-9.779999999999999</v>
-      </c>
-      <c r="D48" s="6">
-        <v>-11.54</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-1.76</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="6">
-        <v>-4.71</v>
-      </c>
-      <c r="D49" s="6">
-        <v>-3.49</v>
-      </c>
-      <c r="E49" s="8">
-        <v>1.22</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="6">
-        <v>-39.73</v>
-      </c>
-      <c r="D50" s="6">
-        <v>-41.66</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-1.93</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="6">
-        <v>-21.09</v>
-      </c>
-      <c r="D51" s="6">
-        <v>-21.11</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-0.02</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C52" s="6">
-        <v>-11.16</v>
-      </c>
-      <c r="D52" s="6">
-        <v>-10.37</v>
-      </c>
-      <c r="E52" s="8">
-        <v>0.79</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="6">
-        <v>397</v>
-      </c>
-      <c r="D53" s="6">
-        <v>394.5</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-2.5</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="6">
-        <v>3398.2</v>
-      </c>
-      <c r="D54" s="6">
-        <v>3330</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-68.2</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="6">
-        <v>385.35</v>
-      </c>
-      <c r="D55" s="6">
-        <v>383.35</v>
-      </c>
-      <c r="E55" s="7">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="6">
-        <v>371.25</v>
-      </c>
-      <c r="D56" s="6">
-        <v>368.65</v>
-      </c>
-      <c r="E56" s="7">
-        <v>-2.6</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="6">
-        <v>399.4</v>
-      </c>
-      <c r="D57" s="6">
-        <v>391.6</v>
-      </c>
-      <c r="E57" s="7">
-        <v>-7.8</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="6">
-        <v>636.55</v>
-      </c>
-      <c r="D58" s="6">
-        <v>642.05</v>
-      </c>
-      <c r="E58" s="8">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="6">
-        <v>218.19</v>
-      </c>
-      <c r="D59" s="6">
-        <v>211.23</v>
-      </c>
-      <c r="E59" s="7">
-        <v>-6.96</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="6">
-        <v>3549</v>
-      </c>
-      <c r="D60" s="6">
-        <v>3548.3</v>
-      </c>
-      <c r="E60" s="7">
-        <v>-0.7</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C61" s="6">
-        <v>1571</v>
-      </c>
-      <c r="D61" s="6">
-        <v>1585</v>
-      </c>
-      <c r="E61" s="8">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C62" s="6">
-        <v>66</v>
-      </c>
-      <c r="D62" s="6">
-        <v>55</v>
-      </c>
-      <c r="E62" s="7">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C63" s="6">
-        <v>55</v>
-      </c>
-      <c r="D63" s="6">
-        <v>66</v>
-      </c>
-      <c r="E63" s="8">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="6">
-        <v>30.9</v>
-      </c>
-      <c r="D64" s="6">
-        <v>29.39</v>
-      </c>
-      <c r="E64" s="7">
-        <v>-1.51</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="6">
-        <v>54.04</v>
-      </c>
-      <c r="D65" s="6">
-        <v>46.71</v>
-      </c>
-      <c r="E65" s="7">
-        <v>-7.33</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="6">
-        <v>54.58</v>
-      </c>
-      <c r="D66" s="6">
-        <v>53.19</v>
-      </c>
-      <c r="E66" s="7">
-        <v>-1.39</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="6">
-        <v>41.66</v>
-      </c>
-      <c r="D67" s="6">
-        <v>39.42</v>
-      </c>
-      <c r="E67" s="7">
-        <v>-2.24</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="6">
-        <v>47.24</v>
-      </c>
-      <c r="D68" s="6">
-        <v>40.8</v>
-      </c>
-      <c r="E68" s="7">
-        <v>-6.44</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="6">
-        <v>66.84</v>
-      </c>
-      <c r="D69" s="6">
-        <v>68.89</v>
-      </c>
-      <c r="E69" s="8">
-        <v>2.05</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="6">
-        <v>41.07</v>
-      </c>
-      <c r="D70" s="6">
-        <v>33.54</v>
-      </c>
-      <c r="E70" s="7">
-        <v>-7.53</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="6">
-        <v>34.89</v>
-      </c>
-      <c r="D71" s="6">
-        <v>34.79</v>
-      </c>
-      <c r="E71" s="7">
-        <v>-0.1</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C72" s="6">
-        <v>44.76</v>
-      </c>
-      <c r="D72" s="6">
-        <v>48.76</v>
-      </c>
-      <c r="E72" s="8">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B73" s="5" t="s">
+      <c r="B84" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C73" s="6">
-        <v>-28.21</v>
-      </c>
-      <c r="D73" s="6">
-        <v>-82.26000000000001</v>
-      </c>
-      <c r="E73" s="7">
-        <v>-54.05</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="6">
-        <v>-70.08</v>
-      </c>
-      <c r="D74" s="6">
-        <v>-16.79</v>
-      </c>
-      <c r="E74" s="8">
-        <v>53.29</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="6">
-        <v>-36.87</v>
-      </c>
-      <c r="D75" s="6">
-        <v>-54.21</v>
-      </c>
-      <c r="E75" s="7">
-        <v>-17.34</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="6">
-        <v>-32.18</v>
-      </c>
-      <c r="D76" s="6">
-        <v>-53.73</v>
-      </c>
-      <c r="E76" s="7">
-        <v>-21.55</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="6">
-        <v>3.22</v>
-      </c>
-      <c r="D77" s="6">
-        <v>-45.65</v>
-      </c>
-      <c r="E77" s="7">
-        <v>-48.87</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="6">
-        <v>21.31</v>
-      </c>
-      <c r="D78" s="6">
-        <v>58.55</v>
-      </c>
-      <c r="E78" s="8">
-        <v>37.24</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="6">
-        <v>-2.37</v>
-      </c>
-      <c r="D79" s="6">
-        <v>311.95</v>
-      </c>
-      <c r="E79" s="8">
-        <v>314.32</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="6">
-        <v>-28.48</v>
-      </c>
-      <c r="D80" s="6">
-        <v>-28.18</v>
-      </c>
-      <c r="E80" s="8">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="6">
-        <v>-42.47</v>
-      </c>
-      <c r="D81" s="6">
+      <c r="C84" s="8">
         <v>-26.32</v>
       </c>
-      <c r="E81" s="8">
-        <v>16.15</v>
+      <c r="D84" s="8">
+        <v>27.61</v>
+      </c>
+      <c r="E84" s="10">
+        <v>53.93</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A8:E8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3471,60 +3576,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>77</v>
+      <c r="B1" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="13">
         <v>56.16</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="14">
         <v>9</v>
       </c>
-      <c r="D2" s="11">
-        <v>43.9</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="13">
+        <v>45.2</v>
+      </c>
+      <c r="E2" s="13">
         <v>60</v>
       </c>
-      <c r="F2" s="11">
-        <v>-1</v>
-      </c>
-      <c r="G2" s="11">
-        <v>5.4</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="13">
+        <v>-0.5</v>
+      </c>
+      <c r="G2" s="13">
+        <v>6.1</v>
+      </c>
+      <c r="H2" s="13">
         <v>55.4</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="13">
         <v>60</v>
       </c>
     </row>
@@ -3626,61 +3731,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="15" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="14">
-        <v>0.3482</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.341</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.2171</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.2018</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.1307</v>
-      </c>
-      <c r="F2" s="14">
-        <v>0.0815</v>
-      </c>
-      <c r="G2" s="14">
-        <v>0.04940000000000001</v>
-      </c>
-      <c r="H2" s="14">
-        <v>0.0052</v>
-      </c>
-      <c r="I2" s="14">
-        <v>-0.1221</v>
+      <c r="A2" s="16">
+        <v>0.3494</v>
+      </c>
+      <c r="B2" s="16">
+        <v>0.3433</v>
+      </c>
+      <c r="C2" s="16">
+        <v>0.2067</v>
+      </c>
+      <c r="D2" s="16">
+        <v>0.1978</v>
+      </c>
+      <c r="E2" s="16">
+        <v>0.1308</v>
+      </c>
+      <c r="F2" s="16">
+        <v>0.0785</v>
+      </c>
+      <c r="G2" s="16">
+        <v>0.06059999999999999</v>
+      </c>
+      <c r="H2" s="16">
+        <v>0.0015</v>
+      </c>
+      <c r="I2" s="16">
+        <v>-0.1259</v>
       </c>
     </row>
   </sheetData>

--- a/MAHINDRA_GROUP_Technical_Metrics.xlsx
+++ b/MAHINDRA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="66">
   <si>
     <t>Symbol</t>
   </si>
@@ -178,76 +178,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>Near 52W High</t>
-  </si>
-  <si>
-    <t>-3.5% → -0.4%</t>
-  </si>
-  <si>
-    <t>🟢 BREAKOUT WATCH</t>
-  </si>
-  <si>
-    <t>-3.5%</t>
-  </si>
-  <si>
-    <t>-0.4%</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>48.8 → 60.9</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>48.8</t>
-  </si>
-  <si>
-    <t>60.9</t>
-  </si>
-  <si>
-    <t>RSI Overbought Entry</t>
-  </si>
-  <si>
-    <t>68.9 → 74.9</t>
-  </si>
-  <si>
-    <t>⚠️ CAUTION</t>
-  </si>
-  <si>
-    <t>68.9</t>
-  </si>
-  <si>
-    <t>74.9</t>
-  </si>
-  <si>
-    <t>53.2 → 48.7</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>53.2</t>
-  </si>
-  <si>
-    <t>48.7</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -299,7 +230,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -340,20 +271,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -381,12 +305,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -462,24 +380,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -488,7 +403,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -987,10 +902,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>389.95</v>
+        <v>391.05</v>
       </c>
       <c r="D2">
-        <v>-1.15</v>
+        <v>0.28</v>
       </c>
       <c r="E2">
         <v>490.2</v>
@@ -999,46 +914,46 @@
         <v>379.2</v>
       </c>
       <c r="G2">
-        <v>-20.45</v>
+        <v>-20.23</v>
       </c>
       <c r="H2">
-        <v>2.83</v>
+        <v>3.12</v>
       </c>
       <c r="I2">
-        <v>-2.77</v>
+        <v>-2.08</v>
       </c>
       <c r="J2">
-        <v>-5.33</v>
+        <v>-4.3</v>
       </c>
       <c r="K2">
-        <v>-10.85</v>
+        <v>-12.16</v>
       </c>
       <c r="L2">
-        <v>-0.85</v>
+        <v>2.55</v>
       </c>
       <c r="M2">
-        <v>13.08</v>
+        <v>11.45</v>
       </c>
       <c r="N2">
         <v>34</v>
       </c>
       <c r="O2">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P2">
-        <v>395.35</v>
+        <v>393.69</v>
       </c>
       <c r="Q2">
-        <v>406.12</v>
+        <v>404.69</v>
       </c>
       <c r="R2">
-        <v>434.97</v>
+        <v>433.51</v>
       </c>
       <c r="S2">
-        <v>437.01</v>
+        <v>436.83</v>
       </c>
       <c r="T2">
-        <v>-10.77</v>
+        <v>-10.48</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1053,10 +968,10 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>26.83</v>
+        <v>28.46</v>
       </c>
       <c r="Z2">
-        <v>-10.78</v>
+        <v>-10.76</v>
       </c>
       <c r="AA2">
         <v>-10.78</v>
@@ -1065,31 +980,31 @@
         <v>0.01</v>
       </c>
       <c r="AC2">
-        <v>5.41</v>
+        <v>5.05</v>
       </c>
       <c r="AD2">
-        <v>5.41</v>
+        <v>5.29</v>
       </c>
       <c r="AE2">
-        <v>8.970000000000001</v>
+        <v>8.92</v>
       </c>
       <c r="AF2">
-        <v>-41.98</v>
+        <v>-30.4</v>
       </c>
       <c r="AG2">
-        <v>421.29</v>
+        <v>419.88</v>
       </c>
       <c r="AH2">
-        <v>390.94</v>
+        <v>389.49</v>
       </c>
       <c r="AI2">
-        <v>420.15</v>
+        <v>417.67</v>
       </c>
       <c r="AJ2" t="s">
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>48.56</v>
+        <v>51.44</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1100,10 +1015,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>3334</v>
+        <v>3282</v>
       </c>
       <c r="D3">
-        <v>0.12</v>
+        <v>-1.56</v>
       </c>
       <c r="E3">
         <v>3802.4</v>
@@ -1112,46 +1027,46 @@
         <v>2931.1</v>
       </c>
       <c r="G3">
-        <v>-12.32</v>
+        <v>-13.69</v>
       </c>
       <c r="H3">
-        <v>13.75</v>
+        <v>11.97</v>
       </c>
       <c r="I3">
-        <v>-2.29</v>
+        <v>-3.87</v>
       </c>
       <c r="J3">
-        <v>1.53</v>
+        <v>-3.43</v>
       </c>
       <c r="K3">
-        <v>12.25</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="L3">
-        <v>-1.91</v>
+        <v>-1.47</v>
       </c>
       <c r="M3">
-        <v>34.33</v>
+        <v>33.81</v>
       </c>
       <c r="N3">
         <v>45</v>
       </c>
       <c r="O3">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="P3">
-        <v>3383.86</v>
+        <v>3357.44</v>
       </c>
       <c r="Q3">
-        <v>3422.27</v>
+        <v>3414.94</v>
       </c>
       <c r="R3">
-        <v>3262.69</v>
+        <v>3266.84</v>
       </c>
       <c r="S3">
-        <v>3346.37</v>
+        <v>3344.01</v>
       </c>
       <c r="T3">
-        <v>-0.37</v>
+        <v>-1.85</v>
       </c>
       <c r="U3" t="s">
         <v>48</v>
@@ -1166,34 +1081,34 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>47.16</v>
+        <v>42.14</v>
       </c>
       <c r="Z3">
-        <v>28.23</v>
+        <v>17.52</v>
       </c>
       <c r="AA3">
-        <v>49.19</v>
+        <v>42.86</v>
       </c>
       <c r="AB3">
-        <v>-20.97</v>
+        <v>-25.34</v>
       </c>
       <c r="AC3">
         <v>0.9</v>
       </c>
       <c r="AD3">
-        <v>7.58</v>
+        <v>3.77</v>
       </c>
       <c r="AE3">
-        <v>63.59</v>
+        <v>64.97</v>
       </c>
       <c r="AF3">
-        <v>-18.42</v>
+        <v>81.48999999999999</v>
       </c>
       <c r="AG3">
-        <v>3510.83</v>
+        <v>3523.34</v>
       </c>
       <c r="AH3">
-        <v>3333.71</v>
+        <v>3306.54</v>
       </c>
       <c r="AI3">
         <v>3274.47</v>
@@ -1202,7 +1117,7 @@
         <v>50</v>
       </c>
       <c r="AK3">
-        <v>26.23</v>
+        <v>29.19</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1213,10 +1128,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>376.6</v>
+        <v>373</v>
       </c>
       <c r="D4">
-        <v>-1.76</v>
+        <v>-0.96</v>
       </c>
       <c r="E4">
         <v>412.3</v>
@@ -1225,25 +1140,25 @@
         <v>253.95</v>
       </c>
       <c r="G4">
-        <v>-8.66</v>
+        <v>-9.529999999999999</v>
       </c>
       <c r="H4">
-        <v>48.3</v>
+        <v>46.88</v>
       </c>
       <c r="I4">
-        <v>-1.31</v>
+        <v>-1.51</v>
       </c>
       <c r="J4">
-        <v>-4.06</v>
+        <v>-3.31</v>
       </c>
       <c r="K4">
-        <v>27.62</v>
+        <v>26.74</v>
       </c>
       <c r="L4">
-        <v>41.55</v>
+        <v>43.19</v>
       </c>
       <c r="M4">
-        <v>20.67</v>
+        <v>20.34</v>
       </c>
       <c r="N4">
         <v>99</v>
@@ -1252,19 +1167,19 @@
         <v>85</v>
       </c>
       <c r="P4">
-        <v>381.09</v>
+        <v>379.95</v>
       </c>
       <c r="Q4">
-        <v>391.37</v>
+        <v>389.75</v>
       </c>
       <c r="R4">
-        <v>358.65</v>
+        <v>360.23</v>
       </c>
       <c r="S4">
-        <v>342.72</v>
+        <v>343.04</v>
       </c>
       <c r="T4">
-        <v>9.890000000000001</v>
+        <v>8.74</v>
       </c>
       <c r="U4" t="s">
         <v>48</v>
@@ -1279,34 +1194,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>48.67</v>
+        <v>46.4</v>
       </c>
       <c r="Z4">
-        <v>4.87</v>
+        <v>3.62</v>
       </c>
       <c r="AA4">
-        <v>8.93</v>
+        <v>7.87</v>
       </c>
       <c r="AB4">
-        <v>-4.06</v>
+        <v>-4.24</v>
       </c>
       <c r="AC4">
-        <v>11.12</v>
+        <v>4.34</v>
       </c>
       <c r="AD4">
-        <v>11.55</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE4">
-        <v>12.27</v>
+        <v>12.1</v>
       </c>
       <c r="AF4">
-        <v>-67.16</v>
+        <v>-36.46</v>
       </c>
       <c r="AG4">
-        <v>411.52</v>
+        <v>410.33</v>
       </c>
       <c r="AH4">
-        <v>371.22</v>
+        <v>369.16</v>
       </c>
       <c r="AI4">
         <v>357.72</v>
@@ -1315,7 +1230,7 @@
         <v>50</v>
       </c>
       <c r="AK4">
-        <v>20.27</v>
+        <v>21.77</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1326,10 +1241,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>367.55</v>
+        <v>365.65</v>
       </c>
       <c r="D5">
-        <v>-0.3</v>
+        <v>-0.52</v>
       </c>
       <c r="E5">
         <v>421.7</v>
@@ -1338,46 +1253,46 @@
         <v>294.25</v>
       </c>
       <c r="G5">
-        <v>-12.84</v>
+        <v>-13.29</v>
       </c>
       <c r="H5">
-        <v>24.91</v>
+        <v>24.27</v>
       </c>
       <c r="I5">
-        <v>-3.23</v>
+        <v>-3.56</v>
       </c>
       <c r="J5">
-        <v>-4.63</v>
+        <v>-6.88</v>
       </c>
       <c r="K5">
-        <v>9.5</v>
+        <v>8.44</v>
       </c>
       <c r="L5">
-        <v>5.95</v>
+        <v>3.33</v>
       </c>
       <c r="M5">
-        <v>7.85</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="N5">
         <v>55</v>
       </c>
       <c r="O5">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="P5">
-        <v>372.63</v>
+        <v>369.93</v>
       </c>
       <c r="Q5">
-        <v>381.86</v>
+        <v>380.23</v>
       </c>
       <c r="R5">
-        <v>375.95</v>
+        <v>376.22</v>
       </c>
       <c r="S5">
-        <v>364.06</v>
+        <v>363.95</v>
       </c>
       <c r="T5">
-        <v>0.96</v>
+        <v>0.47</v>
       </c>
       <c r="U5" t="s">
         <v>48</v>
@@ -1392,34 +1307,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>38.48</v>
+        <v>36.84</v>
       </c>
       <c r="Z5">
-        <v>-1.45</v>
+        <v>-2.17</v>
       </c>
       <c r="AA5">
-        <v>1.11</v>
+        <v>0.45</v>
       </c>
       <c r="AB5">
-        <v>-2.56</v>
+        <v>-2.63</v>
       </c>
       <c r="AC5">
         <v>0</v>
       </c>
       <c r="AD5">
-        <v>9.09</v>
+        <v>2.34</v>
       </c>
       <c r="AE5">
-        <v>10.12</v>
+        <v>10</v>
       </c>
       <c r="AF5">
-        <v>-79.37</v>
+        <v>-15.16</v>
       </c>
       <c r="AG5">
-        <v>398.06</v>
+        <v>396.04</v>
       </c>
       <c r="AH5">
-        <v>365.67</v>
+        <v>364.42</v>
       </c>
       <c r="AI5">
         <v>364.94</v>
@@ -1428,7 +1343,7 @@
         <v>50</v>
       </c>
       <c r="AK5">
-        <v>30.86</v>
+        <v>34.12</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1439,10 +1354,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>392.75</v>
+        <v>391.45</v>
       </c>
       <c r="D6">
-        <v>0.29</v>
+        <v>-0.33</v>
       </c>
       <c r="E6">
         <v>442.7</v>
@@ -1451,25 +1366,25 @@
         <v>279.55</v>
       </c>
       <c r="G6">
-        <v>-11.28</v>
+        <v>-11.58</v>
       </c>
       <c r="H6">
-        <v>40.49</v>
+        <v>40.03</v>
       </c>
       <c r="I6">
-        <v>-2.09</v>
+        <v>-2.89</v>
       </c>
       <c r="J6">
-        <v>-2.46</v>
+        <v>-4.41</v>
       </c>
       <c r="K6">
-        <v>13.05</v>
+        <v>12.29</v>
       </c>
       <c r="L6">
-        <v>20.33</v>
+        <v>21.62</v>
       </c>
       <c r="M6">
-        <v>-12.59</v>
+        <v>-12.22</v>
       </c>
       <c r="N6">
         <v>88</v>
@@ -1478,19 +1393,19 @@
         <v>72</v>
       </c>
       <c r="P6">
-        <v>397.31</v>
+        <v>394.98</v>
       </c>
       <c r="Q6">
-        <v>405.86</v>
+        <v>404.62</v>
       </c>
       <c r="R6">
-        <v>396.12</v>
+        <v>396.85</v>
       </c>
       <c r="S6">
-        <v>366.46</v>
+        <v>366.72</v>
       </c>
       <c r="T6">
-        <v>7.17</v>
+        <v>6.74</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1505,34 +1420,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>42.05</v>
+        <v>41</v>
       </c>
       <c r="Z6">
-        <v>-0.43</v>
+        <v>-1.12</v>
       </c>
       <c r="AA6">
-        <v>2.25</v>
+        <v>1.58</v>
       </c>
       <c r="AB6">
-        <v>-2.68</v>
+        <v>-2.7</v>
       </c>
       <c r="AC6">
-        <v>2.86</v>
+        <v>3.37</v>
       </c>
       <c r="AD6">
-        <v>2.75</v>
+        <v>2.08</v>
       </c>
       <c r="AE6">
-        <v>11.69</v>
+        <v>11.45</v>
       </c>
       <c r="AF6">
-        <v>-53.23</v>
+        <v>-28.42</v>
       </c>
       <c r="AG6">
-        <v>420.39</v>
+        <v>419.63</v>
       </c>
       <c r="AH6">
-        <v>391.33</v>
+        <v>389.61</v>
       </c>
       <c r="AI6">
         <v>372.35</v>
@@ -1541,7 +1456,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>15.84</v>
+        <v>16.65</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1552,10 +1467,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>661.7</v>
+        <v>663.2</v>
       </c>
       <c r="D7">
-        <v>3.06</v>
+        <v>0.23</v>
       </c>
       <c r="E7">
         <v>664.6</v>
@@ -1564,46 +1479,46 @@
         <v>506.45</v>
       </c>
       <c r="G7">
-        <v>-0.44</v>
+        <v>-0.21</v>
       </c>
       <c r="H7">
-        <v>30.65</v>
+        <v>30.95</v>
       </c>
       <c r="I7">
-        <v>4.34</v>
+        <v>4.48</v>
       </c>
       <c r="J7">
-        <v>15.57</v>
+        <v>17.31</v>
       </c>
       <c r="K7">
-        <v>7.61</v>
+        <v>8.76</v>
       </c>
       <c r="L7">
-        <v>-0.54</v>
+        <v>0.96</v>
       </c>
       <c r="M7">
-        <v>34.94</v>
+        <v>34.9</v>
       </c>
       <c r="N7">
         <v>77</v>
       </c>
       <c r="O7">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="P7">
-        <v>642.3200000000001</v>
+        <v>648.01</v>
       </c>
       <c r="Q7">
-        <v>612.96</v>
+        <v>617.4400000000001</v>
       </c>
       <c r="R7">
-        <v>602.85</v>
+        <v>603.5</v>
       </c>
       <c r="S7">
-        <v>584.74</v>
+        <v>585.24</v>
       </c>
       <c r="T7">
-        <v>13.16</v>
+        <v>13.32</v>
       </c>
       <c r="U7" t="s">
         <v>48</v>
@@ -1618,16 +1533,16 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>74.88</v>
+        <v>75.28</v>
       </c>
       <c r="Z7">
-        <v>14.48</v>
+        <v>16.09</v>
       </c>
       <c r="AA7">
-        <v>9.5</v>
+        <v>10.82</v>
       </c>
       <c r="AB7">
-        <v>4.98</v>
+        <v>5.27</v>
       </c>
       <c r="AC7">
         <v>100</v>
@@ -1636,25 +1551,25 @@
         <v>100</v>
       </c>
       <c r="AE7">
-        <v>17.76</v>
+        <v>17.82</v>
       </c>
       <c r="AF7">
-        <v>170.65</v>
+        <v>73.02</v>
       </c>
       <c r="AG7">
-        <v>660.58</v>
+        <v>666.3200000000001</v>
       </c>
       <c r="AH7">
-        <v>565.35</v>
+        <v>568.5599999999999</v>
       </c>
       <c r="AI7">
-        <v>602.11</v>
+        <v>605.9</v>
       </c>
       <c r="AJ7" t="s">
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>64.95</v>
+        <v>67.51000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1665,37 +1580,37 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>211.39</v>
+        <v>209.65</v>
       </c>
       <c r="D8">
-        <v>0.08</v>
+        <v>-0.82</v>
       </c>
       <c r="E8">
         <v>362.05</v>
       </c>
       <c r="F8">
-        <v>210.4</v>
+        <v>209.65</v>
       </c>
       <c r="G8">
-        <v>-41.61</v>
+        <v>-42.09</v>
       </c>
       <c r="H8">
-        <v>0.47</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <v>-4.69</v>
+        <v>-5.16</v>
       </c>
       <c r="J8">
-        <v>-2.09</v>
+        <v>-4.01</v>
       </c>
       <c r="K8">
-        <v>-3.47</v>
+        <v>-2.28</v>
       </c>
       <c r="L8">
-        <v>-41.31</v>
+        <v>-40.19</v>
       </c>
       <c r="M8">
-        <v>0.15</v>
+        <v>-0.16</v>
       </c>
       <c r="N8">
         <v>12</v>
@@ -1704,19 +1619,19 @@
         <v>15</v>
       </c>
       <c r="P8">
-        <v>216.19</v>
+        <v>213.91</v>
       </c>
       <c r="Q8">
-        <v>223.17</v>
+        <v>222.7</v>
       </c>
       <c r="R8">
-        <v>226.91</v>
+        <v>226.4</v>
       </c>
       <c r="S8">
-        <v>262.96</v>
+        <v>262.45</v>
       </c>
       <c r="T8">
-        <v>-19.61</v>
+        <v>-20.12</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1731,43 +1646,43 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>33.84</v>
+        <v>32.14</v>
       </c>
       <c r="Z8">
-        <v>-3.02</v>
+        <v>-3.53</v>
       </c>
       <c r="AA8">
-        <v>-1.81</v>
+        <v>-2.16</v>
       </c>
       <c r="AB8">
-        <v>-1.21</v>
+        <v>-1.37</v>
       </c>
       <c r="AC8">
         <v>0.59</v>
       </c>
       <c r="AD8">
-        <v>1.93</v>
+        <v>0.39</v>
       </c>
       <c r="AE8">
-        <v>6.62</v>
+        <v>6.43</v>
       </c>
       <c r="AF8">
-        <v>37.35</v>
+        <v>13.11</v>
       </c>
       <c r="AG8">
-        <v>235.13</v>
+        <v>236</v>
       </c>
       <c r="AH8">
-        <v>211.21</v>
+        <v>209.4</v>
       </c>
       <c r="AI8">
-        <v>232.72</v>
+        <v>230.39</v>
       </c>
       <c r="AJ8" t="s">
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>29.59</v>
+        <v>32.7</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1778,10 +1693,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>3544.8</v>
+        <v>3569.3</v>
       </c>
       <c r="D9">
-        <v>-0.1</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E9">
         <v>4497.5</v>
@@ -1790,46 +1705,46 @@
         <v>3308.9</v>
       </c>
       <c r="G9">
-        <v>-21.18</v>
+        <v>-20.64</v>
       </c>
       <c r="H9">
-        <v>7.13</v>
+        <v>7.87</v>
       </c>
       <c r="I9">
-        <v>-0.7</v>
+        <v>0.29</v>
       </c>
       <c r="J9">
-        <v>-1.74</v>
+        <v>-1.64</v>
       </c>
       <c r="K9">
-        <v>-6.74</v>
+        <v>-6.02</v>
       </c>
       <c r="L9">
-        <v>-13.93</v>
+        <v>-11.21</v>
       </c>
       <c r="M9">
-        <v>19.78</v>
+        <v>19.89</v>
       </c>
       <c r="N9">
         <v>23</v>
       </c>
       <c r="O9">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="P9">
-        <v>3550.54</v>
+        <v>3552.62</v>
       </c>
       <c r="Q9">
-        <v>3592.29</v>
+        <v>3589.23</v>
       </c>
       <c r="R9">
-        <v>3703.68</v>
+        <v>3696.52</v>
       </c>
       <c r="S9">
-        <v>3697.74</v>
+        <v>3695.87</v>
       </c>
       <c r="T9">
-        <v>-4.14</v>
+        <v>-3.42</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1844,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>34.25</v>
+        <v>41.19</v>
       </c>
       <c r="Z9">
-        <v>-34.44</v>
+        <v>-32.2</v>
       </c>
       <c r="AA9">
-        <v>-34.6</v>
+        <v>-34.12</v>
       </c>
       <c r="AB9">
-        <v>0.16</v>
+        <v>1.92</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>18.19</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>6.06</v>
       </c>
       <c r="AE9">
-        <v>48.85</v>
+        <v>51.99</v>
       </c>
       <c r="AF9">
-        <v>-45.14</v>
+        <v>193.19</v>
       </c>
       <c r="AG9">
-        <v>3651.43</v>
+        <v>3646.32</v>
       </c>
       <c r="AH9">
-        <v>3533.16</v>
+        <v>3532.14</v>
       </c>
       <c r="AI9">
         <v>3694.04</v>
@@ -1880,7 +1795,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>9.43</v>
+        <v>14.42</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1891,10 +1806,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>1640.9</v>
+        <v>1628</v>
       </c>
       <c r="D10">
-        <v>3.53</v>
+        <v>-0.79</v>
       </c>
       <c r="E10">
         <v>1768.4</v>
@@ -1903,46 +1818,46 @@
         <v>1326.2</v>
       </c>
       <c r="G10">
-        <v>-7.21</v>
+        <v>-7.94</v>
       </c>
       <c r="H10">
-        <v>23.73</v>
+        <v>22.76</v>
       </c>
       <c r="I10">
-        <v>3.59</v>
+        <v>2.78</v>
       </c>
       <c r="J10">
-        <v>-1.68</v>
+        <v>-1.41</v>
       </c>
       <c r="K10">
-        <v>6.33</v>
+        <v>3.6</v>
       </c>
       <c r="L10">
-        <v>8.58</v>
+        <v>9.51</v>
       </c>
       <c r="M10">
-        <v>6.06</v>
+        <v>5.47</v>
       </c>
       <c r="N10">
         <v>66</v>
       </c>
       <c r="O10">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="P10">
-        <v>1596.16</v>
+        <v>1604.96</v>
       </c>
       <c r="Q10">
-        <v>1617.16</v>
+        <v>1616.11</v>
       </c>
       <c r="R10">
-        <v>1544.73</v>
+        <v>1549.09</v>
       </c>
       <c r="S10">
-        <v>1511.94</v>
+        <v>1512.8</v>
       </c>
       <c r="T10">
-        <v>8.529999999999999</v>
+        <v>7.61</v>
       </c>
       <c r="U10" t="s">
         <v>48</v>
@@ -1957,34 +1872,34 @@
         <v>3</v>
       </c>
       <c r="Y10">
-        <v>60.94</v>
+        <v>57.54</v>
       </c>
       <c r="Z10">
-        <v>8.94</v>
+        <v>10.25</v>
       </c>
       <c r="AA10">
-        <v>14.94</v>
+        <v>14</v>
       </c>
       <c r="AB10">
-        <v>-5.99</v>
+        <v>-3.75</v>
       </c>
       <c r="AC10">
-        <v>31.95</v>
+        <v>55.38</v>
       </c>
       <c r="AD10">
-        <v>18.59</v>
+        <v>34.14</v>
       </c>
       <c r="AE10">
-        <v>37.66</v>
+        <v>37.24</v>
       </c>
       <c r="AF10">
-        <v>27.61</v>
+        <v>12.68</v>
       </c>
       <c r="AG10">
-        <v>1671.21</v>
+        <v>1668.34</v>
       </c>
       <c r="AH10">
-        <v>1563.11</v>
+        <v>1563.88</v>
       </c>
       <c r="AI10">
         <v>1527.05</v>
@@ -1993,7 +1908,7 @@
         <v>50</v>
       </c>
       <c r="AK10">
-        <v>35.08</v>
+        <v>33.73</v>
       </c>
     </row>
   </sheetData>
@@ -2134,7 +2049,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F84"/>
+  <dimension ref="A1:F78"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2154,1409 +2069,1263 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>75</v>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>-5.33</v>
+      </c>
+      <c r="D7" s="5">
+        <v>-4.3</v>
+      </c>
+      <c r="E7" s="6">
+        <v>1.03</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
+      <c r="A8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>1.53</v>
+      </c>
+      <c r="D8" s="5">
+        <v>-3.43</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-4.96</v>
+      </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="3" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>80</v>
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>-4.06</v>
+      </c>
+      <c r="D9" s="5">
+        <v>-3.31</v>
+      </c>
+      <c r="E9" s="6">
+        <v>0.75</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5">
+        <v>-4.63</v>
+      </c>
+      <c r="D10" s="5">
+        <v>-6.88</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-2.25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-2.46</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-4.41</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-1.95</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="5">
+        <v>15.57</v>
+      </c>
+      <c r="D12" s="5">
+        <v>17.31</v>
+      </c>
+      <c r="E12" s="6">
+        <v>1.74</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="5">
+        <v>-2.09</v>
+      </c>
+      <c r="D13" s="5">
+        <v>-4.01</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-1.92</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-1.74</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-1.64</v>
+      </c>
+      <c r="E14" s="6">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-1.68</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-1.41</v>
+      </c>
+      <c r="E15" s="6">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="8">
-        <v>-4.88</v>
-      </c>
-      <c r="D10" s="8">
-        <v>-5.33</v>
-      </c>
-      <c r="E10" s="9">
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>-2.77</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-2.08</v>
+      </c>
+      <c r="E16" s="6">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-2.29</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-3.87</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-1.58</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-1.31</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-1.51</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-3.23</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-3.56</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-0.33</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-2.09</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-2.89</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-0.8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="5">
+        <v>4.34</v>
+      </c>
+      <c r="D21" s="5">
+        <v>4.48</v>
+      </c>
+      <c r="E21" s="6">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="5">
+        <v>-4.69</v>
+      </c>
+      <c r="D22" s="5">
+        <v>-5.16</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-0.47</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="5">
+        <v>-0.7</v>
+      </c>
+      <c r="D23" s="5">
+        <v>0.29</v>
+      </c>
+      <c r="E23" s="6">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="5">
+        <v>3.59</v>
+      </c>
+      <c r="D24" s="5">
+        <v>2.78</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="5">
+        <v>-0.85</v>
+      </c>
+      <c r="D25" s="5">
+        <v>2.55</v>
+      </c>
+      <c r="E25" s="6">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="5">
+        <v>-1.91</v>
+      </c>
+      <c r="D26" s="5">
+        <v>-1.47</v>
+      </c>
+      <c r="E26" s="6">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="5">
+        <v>41.55</v>
+      </c>
+      <c r="D27" s="5">
+        <v>43.19</v>
+      </c>
+      <c r="E27" s="6">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="5">
+        <v>5.95</v>
+      </c>
+      <c r="D28" s="5">
+        <v>3.33</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-2.62</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="5">
+        <v>20.33</v>
+      </c>
+      <c r="D29" s="5">
+        <v>21.62</v>
+      </c>
+      <c r="E29" s="6">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-0.54</v>
+      </c>
+      <c r="D30" s="5">
+        <v>0.96</v>
+      </c>
+      <c r="E30" s="6">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-41.31</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-40.19</v>
+      </c>
+      <c r="E31" s="6">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="5">
+        <v>-13.93</v>
+      </c>
+      <c r="D32" s="5">
+        <v>-11.21</v>
+      </c>
+      <c r="E32" s="6">
+        <v>2.72</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="5">
+        <v>8.58</v>
+      </c>
+      <c r="D33" s="5">
+        <v>9.51</v>
+      </c>
+      <c r="E33" s="6">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="5">
+        <v>-10.85</v>
+      </c>
+      <c r="D34" s="5">
+        <v>-12.16</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-1.31</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="5">
+        <v>12.25</v>
+      </c>
+      <c r="D35" s="5">
+        <v>9.460000000000001</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-2.79</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="5">
+        <v>27.62</v>
+      </c>
+      <c r="D36" s="5">
+        <v>26.74</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-0.88</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="5">
+        <v>9.5</v>
+      </c>
+      <c r="D37" s="5">
+        <v>8.44</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-1.06</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="5">
+        <v>13.05</v>
+      </c>
+      <c r="D38" s="5">
+        <v>12.29</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-0.76</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="5">
+        <v>7.61</v>
+      </c>
+      <c r="D39" s="5">
+        <v>8.76</v>
+      </c>
+      <c r="E39" s="6">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="5">
+        <v>-3.47</v>
+      </c>
+      <c r="D40" s="5">
+        <v>-2.28</v>
+      </c>
+      <c r="E40" s="6">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="5">
+        <v>-6.74</v>
+      </c>
+      <c r="D41" s="5">
+        <v>-6.02</v>
+      </c>
+      <c r="E41" s="6">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="5">
+        <v>6.33</v>
+      </c>
+      <c r="D42" s="5">
+        <v>3.6</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-2.73</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="5">
+        <v>-20.45</v>
+      </c>
+      <c r="D43" s="5">
+        <v>-20.23</v>
+      </c>
+      <c r="E43" s="6">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="5">
+        <v>-12.32</v>
+      </c>
+      <c r="D44" s="5">
+        <v>-13.69</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-1.37</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="5">
+        <v>-8.66</v>
+      </c>
+      <c r="D45" s="5">
+        <v>-9.529999999999999</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-0.87</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="5">
+        <v>-12.84</v>
+      </c>
+      <c r="D46" s="5">
+        <v>-13.29</v>
+      </c>
+      <c r="E46" s="7">
         <v>-0.45</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="7" t="s">
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="5">
+        <v>-11.28</v>
+      </c>
+      <c r="D47" s="5">
+        <v>-11.58</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="5">
+        <v>-0.44</v>
+      </c>
+      <c r="D48" s="5">
+        <v>-0.21</v>
+      </c>
+      <c r="E48" s="6">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="5">
+        <v>-41.61</v>
+      </c>
+      <c r="D49" s="5">
+        <v>-42.09</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-0.48</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="5">
+        <v>-21.18</v>
+      </c>
+      <c r="D50" s="5">
+        <v>-20.64</v>
+      </c>
+      <c r="E50" s="6">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="5">
+        <v>-7.21</v>
+      </c>
+      <c r="D51" s="5">
+        <v>-7.94</v>
+      </c>
+      <c r="E51" s="7">
+        <v>-0.73</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="5">
+        <v>389.95</v>
+      </c>
+      <c r="D52" s="5">
+        <v>391.05</v>
+      </c>
+      <c r="E52" s="6">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="8">
-        <v>3.36</v>
-      </c>
-      <c r="D11" s="8">
-        <v>1.53</v>
-      </c>
-      <c r="E11" s="9">
-        <v>-1.83</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="7" t="s">
+      <c r="B53" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="5">
+        <v>3334</v>
+      </c>
+      <c r="D53" s="5">
+        <v>3282</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-52</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="8">
-        <v>-2.64</v>
-      </c>
-      <c r="D12" s="8">
-        <v>-4.06</v>
-      </c>
-      <c r="E12" s="9">
-        <v>-1.42</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="7" t="s">
+      <c r="B54" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="5">
+        <v>376.6</v>
+      </c>
+      <c r="D54" s="5">
+        <v>373</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-3.6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="8">
-        <v>-4.83</v>
-      </c>
-      <c r="D13" s="8">
-        <v>-4.63</v>
-      </c>
-      <c r="E13" s="10">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="7" t="s">
+      <c r="B55" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="5">
+        <v>367.55</v>
+      </c>
+      <c r="D55" s="5">
+        <v>365.65</v>
+      </c>
+      <c r="E55" s="7">
+        <v>-1.9</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="8">
-        <v>-4.36</v>
-      </c>
-      <c r="D14" s="8">
-        <v>-2.46</v>
-      </c>
-      <c r="E14" s="10">
-        <v>1.9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="7" t="s">
+      <c r="B56" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="5">
+        <v>392.75</v>
+      </c>
+      <c r="D56" s="5">
+        <v>391.45</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-1.3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="8">
-        <v>10.33</v>
-      </c>
-      <c r="D15" s="8">
-        <v>15.57</v>
-      </c>
-      <c r="E15" s="10">
-        <v>5.24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="7" t="s">
+      <c r="B57" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="5">
+        <v>661.7</v>
+      </c>
+      <c r="D57" s="5">
+        <v>663.2</v>
+      </c>
+      <c r="E57" s="6">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="8">
-        <v>-1.72</v>
-      </c>
-      <c r="D16" s="8">
-        <v>-2.09</v>
-      </c>
-      <c r="E16" s="9">
-        <v>-0.37</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="7" t="s">
+      <c r="B58" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="5">
+        <v>211.39</v>
+      </c>
+      <c r="D58" s="5">
+        <v>209.65</v>
+      </c>
+      <c r="E58" s="7">
+        <v>-1.74</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B17" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="8">
-        <v>-0.55</v>
-      </c>
-      <c r="D17" s="8">
-        <v>-1.74</v>
-      </c>
-      <c r="E17" s="9">
-        <v>-1.19</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="7" t="s">
+      <c r="B59" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="5">
+        <v>3544.8</v>
+      </c>
+      <c r="D59" s="5">
+        <v>3569.3</v>
+      </c>
+      <c r="E59" s="6">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B18" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="8">
-        <v>-3.6</v>
-      </c>
-      <c r="D18" s="8">
-        <v>-1.68</v>
-      </c>
-      <c r="E18" s="10">
-        <v>1.92</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="7" t="s">
+      <c r="B60" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="5">
+        <v>1640.9</v>
+      </c>
+      <c r="D60" s="5">
+        <v>1628</v>
+      </c>
+      <c r="E60" s="7">
+        <v>-12.9</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="8">
-        <v>-2.3</v>
-      </c>
-      <c r="D19" s="8">
-        <v>-2.77</v>
-      </c>
-      <c r="E19" s="9">
-        <v>-0.47</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="7" t="s">
+      <c r="B61" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" s="5">
+        <v>26.83</v>
+      </c>
+      <c r="D61" s="5">
+        <v>28.46</v>
+      </c>
+      <c r="E61" s="6">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="8">
-        <v>-2.77</v>
-      </c>
-      <c r="D20" s="8">
-        <v>-2.29</v>
-      </c>
-      <c r="E20" s="10">
-        <v>0.48</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="7" t="s">
+      <c r="B62" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" s="5">
+        <v>47.16</v>
+      </c>
+      <c r="D62" s="5">
+        <v>42.14</v>
+      </c>
+      <c r="E62" s="7">
+        <v>-5.02</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="8">
-        <v>0.24</v>
-      </c>
-      <c r="D21" s="8">
-        <v>-1.31</v>
-      </c>
-      <c r="E21" s="9">
-        <v>-1.55</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="7" t="s">
+      <c r="B63" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="5">
+        <v>48.67</v>
+      </c>
+      <c r="D63" s="5">
+        <v>46.4</v>
+      </c>
+      <c r="E63" s="7">
+        <v>-2.27</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="8">
-        <v>-2.27</v>
-      </c>
-      <c r="D22" s="8">
-        <v>-3.23</v>
-      </c>
-      <c r="E22" s="9">
-        <v>-0.96</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="7" t="s">
+      <c r="B64" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="5">
+        <v>38.48</v>
+      </c>
+      <c r="D64" s="5">
+        <v>36.84</v>
+      </c>
+      <c r="E64" s="7">
+        <v>-1.64</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B23" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="8">
-        <v>-3.7</v>
-      </c>
-      <c r="D23" s="8">
-        <v>-2.09</v>
-      </c>
-      <c r="E23" s="10">
-        <v>1.61</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="7" t="s">
+      <c r="B65" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="5">
+        <v>42.05</v>
+      </c>
+      <c r="D65" s="5">
+        <v>41</v>
+      </c>
+      <c r="E65" s="7">
+        <v>-1.05</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B24" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="8">
-        <v>5.15</v>
-      </c>
-      <c r="D24" s="8">
-        <v>4.34</v>
-      </c>
-      <c r="E24" s="9">
-        <v>-0.8100000000000001</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="7" t="s">
+      <c r="B66" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="5">
+        <v>74.88</v>
+      </c>
+      <c r="D66" s="5">
+        <v>75.28</v>
+      </c>
+      <c r="E66" s="6">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B25" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="8">
-        <v>-4.44</v>
-      </c>
-      <c r="D25" s="8">
-        <v>-4.69</v>
-      </c>
-      <c r="E25" s="9">
-        <v>-0.25</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="7" t="s">
+      <c r="B67" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="5">
+        <v>33.84</v>
+      </c>
+      <c r="D67" s="5">
+        <v>32.14</v>
+      </c>
+      <c r="E67" s="7">
+        <v>-1.7</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B26" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C26" s="8">
-        <v>-1.51</v>
-      </c>
-      <c r="D26" s="8">
-        <v>-0.7</v>
-      </c>
-      <c r="E26" s="10">
-        <v>0.8100000000000001</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="7" t="s">
+      <c r="B68" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="5">
+        <v>34.25</v>
+      </c>
+      <c r="D68" s="5">
+        <v>41.19</v>
+      </c>
+      <c r="E68" s="6">
+        <v>6.94</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B27" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C27" s="8">
-        <v>-0.45</v>
-      </c>
-      <c r="D27" s="8">
-        <v>3.59</v>
-      </c>
-      <c r="E27" s="10">
-        <v>4.04</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="7" t="s">
+      <c r="B69" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="5">
+        <v>60.94</v>
+      </c>
+      <c r="D69" s="5">
+        <v>57.54</v>
+      </c>
+      <c r="E69" s="7">
+        <v>-3.4</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="8">
-        <v>0.41</v>
-      </c>
-      <c r="D28" s="8">
-        <v>-0.85</v>
-      </c>
-      <c r="E28" s="9">
-        <v>-1.26</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="7" t="s">
+      <c r="B70" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="5">
+        <v>-41.98</v>
+      </c>
+      <c r="D70" s="5">
+        <v>-30.4</v>
+      </c>
+      <c r="E70" s="6">
+        <v>11.58</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="8">
-        <v>-2.15</v>
-      </c>
-      <c r="D29" s="8">
-        <v>-1.91</v>
-      </c>
-      <c r="E29" s="10">
-        <v>0.24</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="7" t="s">
+      <c r="B71" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C71" s="5">
+        <v>-18.42</v>
+      </c>
+      <c r="D71" s="5">
+        <v>81.48999999999999</v>
+      </c>
+      <c r="E71" s="6">
+        <v>99.91</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="8">
-        <v>45.76</v>
-      </c>
-      <c r="D30" s="8">
-        <v>41.55</v>
-      </c>
-      <c r="E30" s="9">
-        <v>-4.21</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="7" t="s">
+      <c r="B72" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C72" s="5">
+        <v>-67.16</v>
+      </c>
+      <c r="D72" s="5">
+        <v>-36.46</v>
+      </c>
+      <c r="E72" s="6">
+        <v>30.7</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B31" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="8">
-        <v>6.3</v>
-      </c>
-      <c r="D31" s="8">
-        <v>5.95</v>
-      </c>
-      <c r="E31" s="9">
-        <v>-0.35</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="7" t="s">
+      <c r="B73" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="5">
+        <v>-79.37</v>
+      </c>
+      <c r="D73" s="5">
+        <v>-15.16</v>
+      </c>
+      <c r="E73" s="6">
+        <v>64.20999999999999</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="8">
-        <v>19.68</v>
-      </c>
-      <c r="D32" s="8">
-        <v>20.33</v>
-      </c>
-      <c r="E32" s="10">
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="7" t="s">
+      <c r="B74" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="5">
+        <v>-53.23</v>
+      </c>
+      <c r="D74" s="5">
+        <v>-28.42</v>
+      </c>
+      <c r="E74" s="6">
+        <v>24.81</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B33" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="8">
-        <v>-3.88</v>
-      </c>
-      <c r="D33" s="8">
-        <v>-0.54</v>
-      </c>
-      <c r="E33" s="10">
-        <v>3.34</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="7" t="s">
+      <c r="B75" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="5">
+        <v>170.65</v>
+      </c>
+      <c r="D75" s="5">
+        <v>73.02</v>
+      </c>
+      <c r="E75" s="7">
+        <v>-97.63</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B34" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="8">
-        <v>-41.65</v>
-      </c>
-      <c r="D34" s="8">
-        <v>-41.31</v>
-      </c>
-      <c r="E34" s="10">
-        <v>0.34</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="7" t="s">
+      <c r="B76" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="5">
+        <v>37.35</v>
+      </c>
+      <c r="D76" s="5">
+        <v>13.11</v>
+      </c>
+      <c r="E76" s="7">
+        <v>-24.24</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B35" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C35" s="8">
-        <v>-14.12</v>
-      </c>
-      <c r="D35" s="8">
-        <v>-13.93</v>
-      </c>
-      <c r="E35" s="10">
-        <v>0.19</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="7" t="s">
+      <c r="B77" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="5">
+        <v>-45.14</v>
+      </c>
+      <c r="D77" s="5">
+        <v>193.19</v>
+      </c>
+      <c r="E77" s="6">
+        <v>238.33</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B36" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C36" s="8">
-        <v>6.42</v>
-      </c>
-      <c r="D36" s="8">
-        <v>8.58</v>
-      </c>
-      <c r="E36" s="10">
-        <v>2.16</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="8">
-        <v>-11.64</v>
-      </c>
-      <c r="D37" s="8">
-        <v>-10.85</v>
-      </c>
-      <c r="E37" s="10">
-        <v>0.79</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="8">
-        <v>9.34</v>
-      </c>
-      <c r="D38" s="8">
-        <v>12.25</v>
-      </c>
-      <c r="E38" s="10">
-        <v>2.91</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="8">
-        <v>26.25</v>
-      </c>
-      <c r="D39" s="8">
-        <v>27.62</v>
-      </c>
-      <c r="E39" s="10">
-        <v>1.37</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="8">
-        <v>10.81</v>
-      </c>
-      <c r="D40" s="8">
-        <v>9.5</v>
-      </c>
-      <c r="E40" s="9">
-        <v>-1.31</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="8">
-        <v>14.45</v>
-      </c>
-      <c r="D41" s="8">
-        <v>13.05</v>
-      </c>
-      <c r="E41" s="9">
-        <v>-1.4</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B42" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="8">
-        <v>3.29</v>
-      </c>
-      <c r="D42" s="8">
-        <v>7.61</v>
-      </c>
-      <c r="E42" s="10">
-        <v>4.32</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="8">
-        <v>-3.3</v>
-      </c>
-      <c r="D43" s="8">
-        <v>-3.47</v>
-      </c>
-      <c r="E43" s="9">
-        <v>-0.17</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B44" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44" s="8">
-        <v>-7.26</v>
-      </c>
-      <c r="D44" s="8">
-        <v>-6.74</v>
-      </c>
-      <c r="E44" s="10">
-        <v>0.52</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C45" s="8">
-        <v>6.81</v>
-      </c>
-      <c r="D45" s="8">
-        <v>6.33</v>
-      </c>
-      <c r="E45" s="9">
-        <v>-0.48</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B46" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="8">
-        <v>-19.52</v>
-      </c>
-      <c r="D46" s="8">
-        <v>-20.45</v>
-      </c>
-      <c r="E46" s="9">
-        <v>-0.93</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B47" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="8">
-        <v>-12.42</v>
-      </c>
-      <c r="D47" s="8">
-        <v>-12.32</v>
-      </c>
-      <c r="E47" s="10">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B48" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="8">
-        <v>-7.02</v>
-      </c>
-      <c r="D48" s="8">
-        <v>-8.66</v>
-      </c>
-      <c r="E48" s="9">
-        <v>-1.64</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B49" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="8">
-        <v>-12.58</v>
-      </c>
-      <c r="D49" s="8">
-        <v>-12.84</v>
-      </c>
-      <c r="E49" s="9">
-        <v>-0.26</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B50" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="8">
-        <v>-11.54</v>
-      </c>
-      <c r="D50" s="8">
-        <v>-11.28</v>
-      </c>
-      <c r="E50" s="10">
-        <v>0.26</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B51" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="8">
-        <v>-3.49</v>
-      </c>
-      <c r="D51" s="8">
-        <v>-0.44</v>
-      </c>
-      <c r="E51" s="10">
-        <v>3.05</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B52" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C52" s="8">
-        <v>-41.66</v>
-      </c>
-      <c r="D52" s="8">
-        <v>-41.61</v>
-      </c>
-      <c r="E52" s="10">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B53" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C53" s="8">
-        <v>-21.11</v>
-      </c>
-      <c r="D53" s="8">
-        <v>-21.18</v>
-      </c>
-      <c r="E53" s="9">
-        <v>-0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B54" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C54" s="8">
-        <v>-10.37</v>
-      </c>
-      <c r="D54" s="8">
-        <v>-7.21</v>
-      </c>
-      <c r="E54" s="10">
-        <v>3.16</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B55" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="8">
-        <v>394.5</v>
-      </c>
-      <c r="D55" s="8">
-        <v>389.95</v>
-      </c>
-      <c r="E55" s="9">
-        <v>-4.55</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B56" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="8">
-        <v>3330</v>
-      </c>
-      <c r="D56" s="8">
-        <v>3334</v>
-      </c>
-      <c r="E56" s="10">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B57" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="8">
-        <v>383.35</v>
-      </c>
-      <c r="D57" s="8">
-        <v>376.6</v>
-      </c>
-      <c r="E57" s="9">
-        <v>-6.75</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B58" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="8">
-        <v>368.65</v>
-      </c>
-      <c r="D58" s="8">
-        <v>367.55</v>
-      </c>
-      <c r="E58" s="9">
-        <v>-1.1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B59" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="8">
-        <v>391.6</v>
-      </c>
-      <c r="D59" s="8">
-        <v>392.75</v>
-      </c>
-      <c r="E59" s="10">
-        <v>1.15</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B60" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="8">
-        <v>642.05</v>
-      </c>
-      <c r="D60" s="8">
-        <v>661.7</v>
-      </c>
-      <c r="E60" s="10">
-        <v>19.65</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B61" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C61" s="8">
-        <v>211.23</v>
-      </c>
-      <c r="D61" s="8">
-        <v>211.39</v>
-      </c>
-      <c r="E61" s="10">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B62" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C62" s="8">
-        <v>3548.3</v>
-      </c>
-      <c r="D62" s="8">
-        <v>3544.8</v>
-      </c>
-      <c r="E62" s="9">
-        <v>-3.5</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B63" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C63" s="8">
-        <v>1585</v>
-      </c>
-      <c r="D63" s="8">
-        <v>1640.9</v>
-      </c>
-      <c r="E63" s="10">
-        <v>55.9</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B64" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C64" s="8">
-        <v>55</v>
-      </c>
-      <c r="D64" s="8">
-        <v>45</v>
-      </c>
-      <c r="E64" s="9">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B65" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C65" s="8">
-        <v>77</v>
-      </c>
-      <c r="D65" s="8">
-        <v>55</v>
-      </c>
-      <c r="E65" s="9">
-        <v>-22</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B66" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C66" s="8">
-        <v>45</v>
-      </c>
-      <c r="D66" s="8">
-        <v>77</v>
-      </c>
-      <c r="E66" s="10">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B67" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="8">
-        <v>29.39</v>
-      </c>
-      <c r="D67" s="8">
-        <v>26.83</v>
-      </c>
-      <c r="E67" s="9">
-        <v>-2.56</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B68" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="8">
-        <v>46.71</v>
-      </c>
-      <c r="D68" s="8">
-        <v>47.16</v>
-      </c>
-      <c r="E68" s="10">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B69" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="8">
-        <v>53.19</v>
-      </c>
-      <c r="D69" s="8">
-        <v>48.67</v>
-      </c>
-      <c r="E69" s="9">
-        <v>-4.52</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B70" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="8">
-        <v>39.42</v>
-      </c>
-      <c r="D70" s="8">
-        <v>38.48</v>
-      </c>
-      <c r="E70" s="9">
-        <v>-0.9399999999999999</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B71" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="8">
-        <v>40.8</v>
-      </c>
-      <c r="D71" s="8">
-        <v>42.05</v>
-      </c>
-      <c r="E71" s="10">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B72" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C72" s="8">
-        <v>68.89</v>
-      </c>
-      <c r="D72" s="8">
-        <v>74.88</v>
-      </c>
-      <c r="E72" s="10">
-        <v>5.99</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B73" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C73" s="8">
-        <v>33.54</v>
-      </c>
-      <c r="D73" s="8">
-        <v>33.84</v>
-      </c>
-      <c r="E73" s="10">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B74" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C74" s="8">
-        <v>34.79</v>
-      </c>
-      <c r="D74" s="8">
-        <v>34.25</v>
-      </c>
-      <c r="E74" s="9">
-        <v>-0.54</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B75" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C75" s="8">
-        <v>48.76</v>
-      </c>
-      <c r="D75" s="8">
-        <v>60.94</v>
-      </c>
-      <c r="E75" s="10">
-        <v>12.18</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B76" s="7" t="s">
+      <c r="B78" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C76" s="8">
-        <v>-82.26000000000001</v>
-      </c>
-      <c r="D76" s="8">
-        <v>-41.98</v>
-      </c>
-      <c r="E76" s="10">
-        <v>40.28</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B77" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="8">
-        <v>-16.79</v>
-      </c>
-      <c r="D77" s="8">
-        <v>-18.42</v>
-      </c>
-      <c r="E77" s="9">
-        <v>-1.63</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B78" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="8">
-        <v>-54.21</v>
-      </c>
-      <c r="D78" s="8">
-        <v>-67.16</v>
-      </c>
-      <c r="E78" s="9">
-        <v>-12.95</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B79" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="8">
-        <v>-53.73</v>
-      </c>
-      <c r="D79" s="8">
-        <v>-79.37</v>
-      </c>
-      <c r="E79" s="9">
-        <v>-25.64</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B80" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="8">
-        <v>-45.65</v>
-      </c>
-      <c r="D80" s="8">
-        <v>-53.23</v>
-      </c>
-      <c r="E80" s="9">
-        <v>-7.58</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B81" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="8">
-        <v>58.55</v>
-      </c>
-      <c r="D81" s="8">
-        <v>170.65</v>
-      </c>
-      <c r="E81" s="10">
-        <v>112.1</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B82" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C82" s="8">
-        <v>311.95</v>
-      </c>
-      <c r="D82" s="8">
-        <v>37.35</v>
-      </c>
-      <c r="E82" s="9">
-        <v>-274.6</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="A83" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B83" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C83" s="8">
-        <v>-28.18</v>
-      </c>
-      <c r="D83" s="8">
-        <v>-45.14</v>
-      </c>
-      <c r="E83" s="9">
-        <v>-16.96</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5">
-      <c r="A84" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B84" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C84" s="8">
-        <v>-26.32</v>
-      </c>
-      <c r="D84" s="8">
+      <c r="C78" s="5">
         <v>27.61</v>
       </c>
-      <c r="E84" s="10">
-        <v>53.93</v>
+      <c r="D78" s="5">
+        <v>12.68</v>
+      </c>
+      <c r="E78" s="7">
+        <v>-14.93</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3576,60 +3345,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="G1" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="H1" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="I1" s="11" t="s">
-        <v>88</v>
+      <c r="B1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="13">
+      <c r="B2" s="10">
         <v>56.16</v>
       </c>
-      <c r="C2" s="14">
+      <c r="C2" s="11">
         <v>9</v>
       </c>
-      <c r="D2" s="13">
-        <v>45.2</v>
-      </c>
-      <c r="E2" s="13">
+      <c r="D2" s="10">
+        <v>44.6</v>
+      </c>
+      <c r="E2" s="10">
         <v>60</v>
       </c>
-      <c r="F2" s="13">
-        <v>-0.5</v>
-      </c>
-      <c r="G2" s="13">
-        <v>6.1</v>
-      </c>
-      <c r="H2" s="13">
+      <c r="F2" s="10">
+        <v>-1.3</v>
+      </c>
+      <c r="G2" s="10">
+        <v>5.4</v>
+      </c>
+      <c r="H2" s="10">
         <v>55.4</v>
       </c>
-      <c r="I2" s="13">
+      <c r="I2" s="10">
         <v>60</v>
       </c>
     </row>
@@ -3731,61 +3500,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G1" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="H1" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="I1" s="12" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="16">
-        <v>0.3494</v>
-      </c>
-      <c r="B2" s="16">
-        <v>0.3433</v>
-      </c>
-      <c r="C2" s="16">
-        <v>0.2067</v>
-      </c>
-      <c r="D2" s="16">
-        <v>0.1978</v>
-      </c>
-      <c r="E2" s="16">
-        <v>0.1308</v>
-      </c>
-      <c r="F2" s="16">
-        <v>0.0785</v>
-      </c>
-      <c r="G2" s="16">
-        <v>0.06059999999999999</v>
-      </c>
-      <c r="H2" s="16">
-        <v>0.0015</v>
-      </c>
-      <c r="I2" s="16">
-        <v>-0.1259</v>
+      <c r="A2" s="13">
+        <v>0.349</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.3381</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.2034</v>
+      </c>
+      <c r="D2" s="13">
+        <v>0.1989</v>
+      </c>
+      <c r="E2" s="13">
+        <v>0.1145</v>
+      </c>
+      <c r="F2" s="13">
+        <v>0.08039999999999999</v>
+      </c>
+      <c r="G2" s="13">
+        <v>0.0547</v>
+      </c>
+      <c r="H2" s="13">
+        <v>-0.0016</v>
+      </c>
+      <c r="I2" s="13">
+        <v>-0.1222</v>
       </c>
     </row>
   </sheetData>

--- a/MAHINDRA_GROUP_Technical_Metrics.xlsx
+++ b/MAHINDRA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="83">
   <si>
     <t>Symbol</t>
   </si>
@@ -178,7 +178,58 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Overbought Exit</t>
+  </si>
+  <si>
+    <t>75.3 → 65.3</t>
+  </si>
+  <si>
+    <t>🔵 COOLING</t>
+  </si>
+  <si>
+    <t>75.3</t>
+  </si>
+  <si>
+    <t>65.3</t>
+  </si>
+  <si>
+    <t>Left 52W High Zone</t>
+  </si>
+  <si>
+    <t>-0.2% → -2.3%</t>
+  </si>
+  <si>
+    <t>⚪ NEUTRAL</t>
+  </si>
+  <si>
+    <t>-0.2%</t>
+  </si>
+  <si>
+    <t>-2.3%</t>
+  </si>
+  <si>
+    <t>50 DMA &gt; 200 DMA</t>
+  </si>
+  <si>
+    <t>Yes → No</t>
+  </si>
+  <si>
+    <t>🔴 DEATH CROSS</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -230,7 +281,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -264,7 +315,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF1F4E79"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -276,8 +327,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -304,13 +362,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,21 +444,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -403,7 +469,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -902,10 +968,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>391.05</v>
+        <v>390.85</v>
       </c>
       <c r="D2">
-        <v>0.28</v>
+        <v>-0.05</v>
       </c>
       <c r="E2">
         <v>490.2</v>
@@ -914,46 +980,46 @@
         <v>379.2</v>
       </c>
       <c r="G2">
-        <v>-20.23</v>
+        <v>-20.27</v>
       </c>
       <c r="H2">
-        <v>3.12</v>
+        <v>3.07</v>
       </c>
       <c r="I2">
-        <v>-2.08</v>
+        <v>-1.29</v>
       </c>
       <c r="J2">
-        <v>-4.3</v>
+        <v>-6.86</v>
       </c>
       <c r="K2">
-        <v>-12.16</v>
+        <v>-13.53</v>
       </c>
       <c r="L2">
-        <v>2.55</v>
+        <v>2.03</v>
       </c>
       <c r="M2">
-        <v>11.45</v>
+        <v>12.22</v>
       </c>
       <c r="N2">
         <v>34</v>
       </c>
       <c r="O2">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="P2">
-        <v>393.69</v>
+        <v>392.67</v>
       </c>
       <c r="Q2">
-        <v>404.69</v>
+        <v>403.7</v>
       </c>
       <c r="R2">
-        <v>433.51</v>
+        <v>431.85</v>
       </c>
       <c r="S2">
-        <v>436.83</v>
+        <v>436.66</v>
       </c>
       <c r="T2">
-        <v>-10.48</v>
+        <v>-10.49</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -968,43 +1034,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>28.46</v>
+        <v>28.33</v>
       </c>
       <c r="Z2">
-        <v>-10.76</v>
+        <v>-10.65</v>
       </c>
       <c r="AA2">
-        <v>-10.78</v>
+        <v>-10.75</v>
       </c>
       <c r="AB2">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="AC2">
-        <v>5.05</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="AD2">
-        <v>5.29</v>
+        <v>6.73</v>
       </c>
       <c r="AE2">
-        <v>8.92</v>
+        <v>8.68</v>
       </c>
       <c r="AF2">
-        <v>-30.4</v>
+        <v>-39.5</v>
       </c>
       <c r="AG2">
-        <v>419.88</v>
+        <v>419.82</v>
       </c>
       <c r="AH2">
-        <v>389.49</v>
+        <v>387.58</v>
       </c>
       <c r="AI2">
-        <v>417.67</v>
+        <v>416.42</v>
       </c>
       <c r="AJ2" t="s">
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>51.44</v>
+        <v>53.95</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1015,10 +1081,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>3282</v>
+        <v>3259</v>
       </c>
       <c r="D3">
-        <v>-1.56</v>
+        <v>-0.7</v>
       </c>
       <c r="E3">
         <v>3802.4</v>
@@ -1027,46 +1093,46 @@
         <v>2931.1</v>
       </c>
       <c r="G3">
-        <v>-13.69</v>
+        <v>-14.29</v>
       </c>
       <c r="H3">
-        <v>11.97</v>
+        <v>11.19</v>
       </c>
       <c r="I3">
-        <v>-3.87</v>
+        <v>-5.34</v>
       </c>
       <c r="J3">
-        <v>-3.43</v>
+        <v>-4.95</v>
       </c>
       <c r="K3">
-        <v>9.460000000000001</v>
+        <v>8.23</v>
       </c>
       <c r="L3">
-        <v>-1.47</v>
+        <v>-1.1</v>
       </c>
       <c r="M3">
-        <v>33.81</v>
+        <v>34.42</v>
       </c>
       <c r="N3">
         <v>45</v>
       </c>
       <c r="O3">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="P3">
-        <v>3357.44</v>
+        <v>3320.64</v>
       </c>
       <c r="Q3">
-        <v>3414.94</v>
+        <v>3406.24</v>
       </c>
       <c r="R3">
-        <v>3266.84</v>
+        <v>3270.75</v>
       </c>
       <c r="S3">
-        <v>3344.01</v>
+        <v>3341.81</v>
       </c>
       <c r="T3">
-        <v>-1.85</v>
+        <v>-2.48</v>
       </c>
       <c r="U3" t="s">
         <v>48</v>
@@ -1081,43 +1147,43 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>42.14</v>
+        <v>40.11</v>
       </c>
       <c r="Z3">
-        <v>17.52</v>
+        <v>7.1</v>
       </c>
       <c r="AA3">
-        <v>42.86</v>
+        <v>35.71</v>
       </c>
       <c r="AB3">
-        <v>-25.34</v>
+        <v>-28.61</v>
       </c>
       <c r="AC3">
         <v>0.9</v>
       </c>
       <c r="AD3">
-        <v>3.77</v>
+        <v>0.9</v>
       </c>
       <c r="AE3">
-        <v>64.97</v>
+        <v>70.69</v>
       </c>
       <c r="AF3">
-        <v>81.48999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="AG3">
-        <v>3523.34</v>
+        <v>3534.63</v>
       </c>
       <c r="AH3">
-        <v>3306.54</v>
+        <v>3277.85</v>
       </c>
       <c r="AI3">
-        <v>3274.47</v>
+        <v>3507.57</v>
       </c>
       <c r="AJ3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AK3">
-        <v>29.19</v>
+        <v>33.66</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1128,10 +1194,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>373</v>
+        <v>364.4</v>
       </c>
       <c r="D4">
-        <v>-0.96</v>
+        <v>-2.31</v>
       </c>
       <c r="E4">
         <v>412.3</v>
@@ -1140,46 +1206,46 @@
         <v>253.95</v>
       </c>
       <c r="G4">
-        <v>-9.529999999999999</v>
+        <v>-11.62</v>
       </c>
       <c r="H4">
-        <v>46.88</v>
+        <v>43.49</v>
       </c>
       <c r="I4">
-        <v>-1.51</v>
+        <v>-4.47</v>
       </c>
       <c r="J4">
-        <v>-3.31</v>
+        <v>-10.14</v>
       </c>
       <c r="K4">
-        <v>26.74</v>
+        <v>25.42</v>
       </c>
       <c r="L4">
-        <v>43.19</v>
+        <v>40.64</v>
       </c>
       <c r="M4">
-        <v>20.34</v>
+        <v>19.5</v>
       </c>
       <c r="N4">
         <v>99</v>
       </c>
       <c r="O4">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P4">
-        <v>379.95</v>
+        <v>376.54</v>
       </c>
       <c r="Q4">
-        <v>389.75</v>
+        <v>388.04</v>
       </c>
       <c r="R4">
-        <v>360.23</v>
+        <v>361.64</v>
       </c>
       <c r="S4">
-        <v>343.04</v>
+        <v>343.31</v>
       </c>
       <c r="T4">
-        <v>8.74</v>
+        <v>6.14</v>
       </c>
       <c r="U4" t="s">
         <v>48</v>
@@ -1194,34 +1260,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>46.4</v>
+        <v>41.44</v>
       </c>
       <c r="Z4">
-        <v>3.62</v>
+        <v>1.92</v>
       </c>
       <c r="AA4">
-        <v>7.87</v>
+        <v>6.68</v>
       </c>
       <c r="AB4">
-        <v>-4.24</v>
+        <v>-4.76</v>
       </c>
       <c r="AC4">
-        <v>4.34</v>
+        <v>0</v>
       </c>
       <c r="AD4">
-        <v>9.800000000000001</v>
+        <v>5.15</v>
       </c>
       <c r="AE4">
-        <v>12.1</v>
+        <v>12.17</v>
       </c>
       <c r="AF4">
-        <v>-36.46</v>
+        <v>-39.82</v>
       </c>
       <c r="AG4">
-        <v>410.33</v>
+        <v>411.06</v>
       </c>
       <c r="AH4">
-        <v>369.16</v>
+        <v>365.01</v>
       </c>
       <c r="AI4">
         <v>357.72</v>
@@ -1230,7 +1296,7 @@
         <v>50</v>
       </c>
       <c r="AK4">
-        <v>21.77</v>
+        <v>24.61</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1241,10 +1307,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>365.65</v>
+        <v>356.95</v>
       </c>
       <c r="D5">
-        <v>-0.52</v>
+        <v>-2.38</v>
       </c>
       <c r="E5">
         <v>421.7</v>
@@ -1253,46 +1319,46 @@
         <v>294.25</v>
       </c>
       <c r="G5">
-        <v>-13.29</v>
+        <v>-15.35</v>
       </c>
       <c r="H5">
-        <v>24.27</v>
+        <v>21.31</v>
       </c>
       <c r="I5">
-        <v>-3.56</v>
+        <v>-5.21</v>
       </c>
       <c r="J5">
-        <v>-6.88</v>
+        <v>-10.37</v>
       </c>
       <c r="K5">
-        <v>8.44</v>
+        <v>6.65</v>
       </c>
       <c r="L5">
-        <v>3.33</v>
+        <v>3.58</v>
       </c>
       <c r="M5">
-        <v>8.039999999999999</v>
+        <v>6.78</v>
       </c>
       <c r="N5">
         <v>55</v>
       </c>
       <c r="O5">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="P5">
-        <v>369.93</v>
+        <v>366.01</v>
       </c>
       <c r="Q5">
-        <v>380.23</v>
+        <v>378.2</v>
       </c>
       <c r="R5">
-        <v>376.22</v>
+        <v>376.15</v>
       </c>
       <c r="S5">
-        <v>363.95</v>
+        <v>363.8</v>
       </c>
       <c r="T5">
-        <v>0.47</v>
+        <v>-1.88</v>
       </c>
       <c r="U5" t="s">
         <v>48</v>
@@ -1304,46 +1370,46 @@
         <v>48</v>
       </c>
       <c r="X5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y5">
-        <v>36.84</v>
+        <v>30.45</v>
       </c>
       <c r="Z5">
-        <v>-2.17</v>
+        <v>-3.41</v>
       </c>
       <c r="AA5">
-        <v>0.45</v>
+        <v>-0.32</v>
       </c>
       <c r="AB5">
-        <v>-2.63</v>
+        <v>-3.09</v>
       </c>
       <c r="AC5">
         <v>0</v>
       </c>
       <c r="AD5">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AE5">
-        <v>10</v>
+        <v>10.14</v>
       </c>
       <c r="AF5">
-        <v>-15.16</v>
+        <v>-17.99</v>
       </c>
       <c r="AG5">
-        <v>396.04</v>
+        <v>395.04</v>
       </c>
       <c r="AH5">
-        <v>364.42</v>
+        <v>361.36</v>
       </c>
       <c r="AI5">
-        <v>364.94</v>
+        <v>391.46</v>
       </c>
       <c r="AJ5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AK5">
-        <v>34.12</v>
+        <v>38.13</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1354,10 +1420,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>391.45</v>
+        <v>387.2</v>
       </c>
       <c r="D6">
-        <v>-0.33</v>
+        <v>-1.09</v>
       </c>
       <c r="E6">
         <v>442.7</v>
@@ -1366,46 +1432,46 @@
         <v>279.55</v>
       </c>
       <c r="G6">
-        <v>-11.58</v>
+        <v>-12.54</v>
       </c>
       <c r="H6">
-        <v>40.03</v>
+        <v>38.51</v>
       </c>
       <c r="I6">
-        <v>-2.89</v>
+        <v>-3.13</v>
       </c>
       <c r="J6">
-        <v>-4.41</v>
+        <v>-6.99</v>
       </c>
       <c r="K6">
-        <v>12.29</v>
+        <v>10.5</v>
       </c>
       <c r="L6">
-        <v>21.62</v>
+        <v>23.29</v>
       </c>
       <c r="M6">
-        <v>-12.22</v>
+        <v>-11.89</v>
       </c>
       <c r="N6">
         <v>88</v>
       </c>
       <c r="O6">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P6">
-        <v>394.98</v>
+        <v>392.48</v>
       </c>
       <c r="Q6">
-        <v>404.62</v>
+        <v>402.93</v>
       </c>
       <c r="R6">
-        <v>396.85</v>
+        <v>397.2</v>
       </c>
       <c r="S6">
-        <v>366.72</v>
+        <v>366.97</v>
       </c>
       <c r="T6">
-        <v>6.74</v>
+        <v>5.51</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1420,34 +1486,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>41</v>
+        <v>37.66</v>
       </c>
       <c r="Z6">
-        <v>-1.12</v>
+        <v>-1.99</v>
       </c>
       <c r="AA6">
-        <v>1.58</v>
+        <v>0.87</v>
       </c>
       <c r="AB6">
-        <v>-2.7</v>
+        <v>-2.85</v>
       </c>
       <c r="AC6">
         <v>3.37</v>
       </c>
       <c r="AD6">
-        <v>2.08</v>
+        <v>3.2</v>
       </c>
       <c r="AE6">
-        <v>11.45</v>
+        <v>11.46</v>
       </c>
       <c r="AF6">
-        <v>-28.42</v>
+        <v>-31.7</v>
       </c>
       <c r="AG6">
-        <v>419.63</v>
+        <v>417.78</v>
       </c>
       <c r="AH6">
-        <v>389.61</v>
+        <v>388.08</v>
       </c>
       <c r="AI6">
         <v>372.35</v>
@@ -1456,7 +1522,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>16.65</v>
+        <v>19.4</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1467,10 +1533,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>663.2</v>
+        <v>649.6</v>
       </c>
       <c r="D7">
-        <v>0.23</v>
+        <v>-2.05</v>
       </c>
       <c r="E7">
         <v>664.6</v>
@@ -1479,46 +1545,46 @@
         <v>506.45</v>
       </c>
       <c r="G7">
-        <v>-0.21</v>
+        <v>-2.26</v>
       </c>
       <c r="H7">
-        <v>30.95</v>
+        <v>28.27</v>
       </c>
       <c r="I7">
-        <v>4.48</v>
+        <v>2.05</v>
       </c>
       <c r="J7">
-        <v>17.31</v>
+        <v>13.23</v>
       </c>
       <c r="K7">
-        <v>8.76</v>
+        <v>6.39</v>
       </c>
       <c r="L7">
-        <v>0.96</v>
+        <v>-0.8</v>
       </c>
       <c r="M7">
-        <v>34.9</v>
+        <v>34.6</v>
       </c>
       <c r="N7">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="O7">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="P7">
-        <v>648.01</v>
+        <v>650.62</v>
       </c>
       <c r="Q7">
-        <v>617.4400000000001</v>
+        <v>620.96</v>
       </c>
       <c r="R7">
-        <v>603.5</v>
+        <v>603.64</v>
       </c>
       <c r="S7">
-        <v>585.24</v>
+        <v>585.67</v>
       </c>
       <c r="T7">
-        <v>13.32</v>
+        <v>10.91</v>
       </c>
       <c r="U7" t="s">
         <v>48</v>
@@ -1533,34 +1599,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>75.28</v>
+        <v>65.33</v>
       </c>
       <c r="Z7">
-        <v>16.09</v>
+        <v>16.08</v>
       </c>
       <c r="AA7">
-        <v>10.82</v>
+        <v>11.87</v>
       </c>
       <c r="AB7">
-        <v>5.27</v>
+        <v>4.21</v>
       </c>
       <c r="AC7">
-        <v>100</v>
+        <v>82.2</v>
       </c>
       <c r="AD7">
-        <v>100</v>
+        <v>94.06999999999999</v>
       </c>
       <c r="AE7">
-        <v>17.82</v>
+        <v>18</v>
       </c>
       <c r="AF7">
-        <v>73.02</v>
+        <v>-3.7</v>
       </c>
       <c r="AG7">
-        <v>666.3200000000001</v>
+        <v>668.35</v>
       </c>
       <c r="AH7">
-        <v>568.5599999999999</v>
+        <v>573.58</v>
       </c>
       <c r="AI7">
         <v>605.9</v>
@@ -1569,7 +1635,7 @@
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>67.51000000000001</v>
+        <v>67.06999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1580,58 +1646,58 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>209.65</v>
+        <v>208.31</v>
       </c>
       <c r="D8">
-        <v>-0.82</v>
+        <v>-0.64</v>
       </c>
       <c r="E8">
         <v>362.05</v>
       </c>
       <c r="F8">
-        <v>209.65</v>
+        <v>208.31</v>
       </c>
       <c r="G8">
-        <v>-42.09</v>
+        <v>-42.46</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
       <c r="I8">
-        <v>-5.16</v>
+        <v>-4.92</v>
       </c>
       <c r="J8">
-        <v>-4.01</v>
+        <v>-4.86</v>
       </c>
       <c r="K8">
-        <v>-2.28</v>
+        <v>-1.73</v>
       </c>
       <c r="L8">
-        <v>-40.19</v>
+        <v>-40.8</v>
       </c>
       <c r="M8">
-        <v>-0.16</v>
+        <v>-0.34</v>
       </c>
       <c r="N8">
         <v>12</v>
       </c>
       <c r="O8">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P8">
-        <v>213.91</v>
+        <v>211.75</v>
       </c>
       <c r="Q8">
-        <v>222.7</v>
+        <v>221.72</v>
       </c>
       <c r="R8">
-        <v>226.4</v>
+        <v>225.71</v>
       </c>
       <c r="S8">
-        <v>262.45</v>
+        <v>261.93</v>
       </c>
       <c r="T8">
-        <v>-20.12</v>
+        <v>-20.47</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1646,43 +1712,43 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>32.14</v>
+        <v>30.85</v>
       </c>
       <c r="Z8">
-        <v>-3.53</v>
+        <v>-3.99</v>
       </c>
       <c r="AA8">
-        <v>-2.16</v>
+        <v>-2.52</v>
       </c>
       <c r="AB8">
-        <v>-1.37</v>
+        <v>-1.47</v>
       </c>
       <c r="AC8">
         <v>0.59</v>
       </c>
       <c r="AD8">
-        <v>0.39</v>
+        <v>0.59</v>
       </c>
       <c r="AE8">
-        <v>6.43</v>
+        <v>6.35</v>
       </c>
       <c r="AF8">
-        <v>13.11</v>
+        <v>7.18</v>
       </c>
       <c r="AG8">
-        <v>236</v>
+        <v>236.23</v>
       </c>
       <c r="AH8">
-        <v>209.4</v>
+        <v>207.21</v>
       </c>
       <c r="AI8">
-        <v>230.39</v>
+        <v>228.5</v>
       </c>
       <c r="AJ8" t="s">
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>32.7</v>
+        <v>36.21</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1693,10 +1759,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>3569.3</v>
+        <v>3537.7</v>
       </c>
       <c r="D9">
-        <v>0.6899999999999999</v>
+        <v>-0.89</v>
       </c>
       <c r="E9">
         <v>4497.5</v>
@@ -1705,88 +1771,88 @@
         <v>3308.9</v>
       </c>
       <c r="G9">
-        <v>-20.64</v>
+        <v>-21.34</v>
       </c>
       <c r="H9">
-        <v>7.87</v>
+        <v>6.91</v>
       </c>
       <c r="I9">
-        <v>0.29</v>
+        <v>-0.39</v>
       </c>
       <c r="J9">
-        <v>-1.64</v>
+        <v>-2.56</v>
       </c>
       <c r="K9">
-        <v>-6.02</v>
+        <v>-6.37</v>
       </c>
       <c r="L9">
-        <v>-11.21</v>
+        <v>-12.27</v>
       </c>
       <c r="M9">
-        <v>19.89</v>
+        <v>19.88</v>
       </c>
       <c r="N9">
         <v>23</v>
       </c>
       <c r="O9">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P9">
-        <v>3552.62</v>
+        <v>3549.82</v>
       </c>
       <c r="Q9">
-        <v>3589.23</v>
+        <v>3586.18</v>
       </c>
       <c r="R9">
-        <v>3696.52</v>
+        <v>3687.97</v>
       </c>
       <c r="S9">
-        <v>3695.87</v>
+        <v>3693.9</v>
       </c>
       <c r="T9">
-        <v>-3.42</v>
+        <v>-4.23</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
       </c>
       <c r="V9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="W9" t="s">
         <v>47</v>
       </c>
       <c r="X9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y9">
-        <v>41.19</v>
+        <v>35.92</v>
       </c>
       <c r="Z9">
-        <v>-32.2</v>
+        <v>-32.6</v>
       </c>
       <c r="AA9">
-        <v>-34.12</v>
+        <v>-33.82</v>
       </c>
       <c r="AB9">
-        <v>1.92</v>
+        <v>1.22</v>
       </c>
       <c r="AC9">
-        <v>18.19</v>
+        <v>22.58</v>
       </c>
       <c r="AD9">
-        <v>6.06</v>
+        <v>13.59</v>
       </c>
       <c r="AE9">
-        <v>51.99</v>
+        <v>52.33</v>
       </c>
       <c r="AF9">
-        <v>193.19</v>
+        <v>107.68</v>
       </c>
       <c r="AG9">
-        <v>3646.32</v>
+        <v>3647.51</v>
       </c>
       <c r="AH9">
-        <v>3532.14</v>
+        <v>3524.86</v>
       </c>
       <c r="AI9">
         <v>3694.04</v>
@@ -1795,7 +1861,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>14.42</v>
+        <v>18.41</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1806,10 +1872,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>1628</v>
+        <v>1638</v>
       </c>
       <c r="D10">
-        <v>-0.79</v>
+        <v>0.61</v>
       </c>
       <c r="E10">
         <v>1768.4</v>
@@ -1818,46 +1884,46 @@
         <v>1326.2</v>
       </c>
       <c r="G10">
-        <v>-7.94</v>
+        <v>-7.37</v>
       </c>
       <c r="H10">
-        <v>22.76</v>
+        <v>23.51</v>
       </c>
       <c r="I10">
-        <v>2.78</v>
+        <v>2.38</v>
       </c>
       <c r="J10">
-        <v>-1.41</v>
+        <v>-0.67</v>
       </c>
       <c r="K10">
-        <v>3.6</v>
+        <v>11.25</v>
       </c>
       <c r="L10">
-        <v>9.51</v>
+        <v>10.67</v>
       </c>
       <c r="M10">
-        <v>5.47</v>
+        <v>5.76</v>
       </c>
       <c r="N10">
+        <v>77</v>
+      </c>
+      <c r="O10">
         <v>66</v>
       </c>
-      <c r="O10">
-        <v>64</v>
-      </c>
       <c r="P10">
-        <v>1604.96</v>
+        <v>1612.58</v>
       </c>
       <c r="Q10">
-        <v>1616.11</v>
+        <v>1615.59</v>
       </c>
       <c r="R10">
-        <v>1549.09</v>
+        <v>1553.15</v>
       </c>
       <c r="S10">
-        <v>1512.8</v>
+        <v>1513.74</v>
       </c>
       <c r="T10">
-        <v>7.61</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="U10" t="s">
         <v>48</v>
@@ -1872,34 +1938,34 @@
         <v>3</v>
       </c>
       <c r="Y10">
-        <v>57.54</v>
+        <v>59.43</v>
       </c>
       <c r="Z10">
-        <v>10.25</v>
+        <v>11.96</v>
       </c>
       <c r="AA10">
-        <v>14</v>
+        <v>13.59</v>
       </c>
       <c r="AB10">
-        <v>-3.75</v>
+        <v>-1.63</v>
       </c>
       <c r="AC10">
-        <v>55.38</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="AD10">
-        <v>34.14</v>
+        <v>54.42</v>
       </c>
       <c r="AE10">
-        <v>37.24</v>
+        <v>37.1</v>
       </c>
       <c r="AF10">
-        <v>12.68</v>
+        <v>-8.02</v>
       </c>
       <c r="AG10">
-        <v>1668.34</v>
+        <v>1666.65</v>
       </c>
       <c r="AH10">
-        <v>1563.88</v>
+        <v>1564.52</v>
       </c>
       <c r="AI10">
         <v>1527.05</v>
@@ -1908,7 +1974,7 @@
         <v>50</v>
       </c>
       <c r="AK10">
-        <v>33.73</v>
+        <v>33.53</v>
       </c>
     </row>
   </sheetData>
@@ -2049,7 +2115,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:F82"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2069,1263 +2135,1372 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>52</v>
       </c>
+      <c r="C2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>57</v>
+      <c r="A5" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="5">
-        <v>-5.33</v>
-      </c>
-      <c r="D7" s="5">
-        <v>-4.3</v>
-      </c>
-      <c r="E7" s="6">
-        <v>1.03</v>
-      </c>
+      <c r="A7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-4.3</v>
+      </c>
+      <c r="D9" s="7">
+        <v>-6.86</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-2.56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>1.53</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C10" s="7">
         <v>-3.43</v>
       </c>
-      <c r="E8" s="7">
+      <c r="D10" s="7">
+        <v>-4.95</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-1.52</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="7">
+        <v>-3.31</v>
+      </c>
+      <c r="D11" s="7">
+        <v>-10.14</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-6.83</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="7">
+        <v>-6.88</v>
+      </c>
+      <c r="D12" s="7">
+        <v>-10.37</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-3.49</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="7">
+        <v>-4.41</v>
+      </c>
+      <c r="D13" s="7">
+        <v>-6.99</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-2.58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="7">
+        <v>17.31</v>
+      </c>
+      <c r="D14" s="7">
+        <v>13.23</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-4.08</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="7">
+        <v>-4.01</v>
+      </c>
+      <c r="D15" s="7">
+        <v>-4.86</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-0.85</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-1.64</v>
+      </c>
+      <c r="D16" s="7">
+        <v>-2.56</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-0.92</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-1.41</v>
+      </c>
+      <c r="D17" s="7">
+        <v>-0.67</v>
+      </c>
+      <c r="E17" s="9">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-2.08</v>
+      </c>
+      <c r="D18" s="7">
+        <v>-1.29</v>
+      </c>
+      <c r="E18" s="9">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="7">
+        <v>-3.87</v>
+      </c>
+      <c r="D19" s="7">
+        <v>-5.34</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-1.47</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="7">
+        <v>-1.51</v>
+      </c>
+      <c r="D20" s="7">
+        <v>-4.47</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-2.96</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-3.56</v>
+      </c>
+      <c r="D21" s="7">
+        <v>-5.21</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-1.65</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="7">
+        <v>-2.89</v>
+      </c>
+      <c r="D22" s="7">
+        <v>-3.13</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-0.24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="7">
+        <v>4.48</v>
+      </c>
+      <c r="D23" s="7">
+        <v>2.05</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-2.43</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="7">
+        <v>-5.16</v>
+      </c>
+      <c r="D24" s="7">
+        <v>-4.92</v>
+      </c>
+      <c r="E24" s="9">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="7">
+        <v>0.29</v>
+      </c>
+      <c r="D25" s="7">
+        <v>-0.39</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-0.68</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="7">
+        <v>2.78</v>
+      </c>
+      <c r="D26" s="7">
+        <v>2.38</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="7">
+        <v>2.55</v>
+      </c>
+      <c r="D27" s="7">
+        <v>2.03</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-0.52</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="7">
+        <v>-1.47</v>
+      </c>
+      <c r="D28" s="7">
+        <v>-1.1</v>
+      </c>
+      <c r="E28" s="9">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="7">
+        <v>43.19</v>
+      </c>
+      <c r="D29" s="7">
+        <v>40.64</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-2.55</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="7">
+        <v>3.33</v>
+      </c>
+      <c r="D30" s="7">
+        <v>3.58</v>
+      </c>
+      <c r="E30" s="9">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="7">
+        <v>21.62</v>
+      </c>
+      <c r="D31" s="7">
+        <v>23.29</v>
+      </c>
+      <c r="E31" s="9">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="7">
+        <v>0.96</v>
+      </c>
+      <c r="D32" s="7">
+        <v>-0.8</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-1.76</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="7">
+        <v>-40.19</v>
+      </c>
+      <c r="D33" s="7">
+        <v>-40.8</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-0.61</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="7">
+        <v>-11.21</v>
+      </c>
+      <c r="D34" s="7">
+        <v>-12.27</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-1.06</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" s="7">
+        <v>9.51</v>
+      </c>
+      <c r="D35" s="7">
+        <v>10.67</v>
+      </c>
+      <c r="E35" s="9">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="7">
+        <v>-12.16</v>
+      </c>
+      <c r="D36" s="7">
+        <v>-13.53</v>
+      </c>
+      <c r="E36" s="8">
+        <v>-1.37</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="7">
+        <v>9.460000000000001</v>
+      </c>
+      <c r="D37" s="7">
+        <v>8.23</v>
+      </c>
+      <c r="E37" s="8">
+        <v>-1.23</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="7">
+        <v>26.74</v>
+      </c>
+      <c r="D38" s="7">
+        <v>25.42</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-1.32</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="7">
+        <v>8.44</v>
+      </c>
+      <c r="D39" s="7">
+        <v>6.65</v>
+      </c>
+      <c r="E39" s="8">
+        <v>-1.79</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="7">
+        <v>12.29</v>
+      </c>
+      <c r="D40" s="7">
+        <v>10.5</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-1.79</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="7">
+        <v>8.76</v>
+      </c>
+      <c r="D41" s="7">
+        <v>6.39</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-2.37</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="7">
+        <v>-2.28</v>
+      </c>
+      <c r="D42" s="7">
+        <v>-1.73</v>
+      </c>
+      <c r="E42" s="9">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="7">
+        <v>-6.02</v>
+      </c>
+      <c r="D43" s="7">
+        <v>-6.37</v>
+      </c>
+      <c r="E43" s="8">
+        <v>-0.35</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="7">
+        <v>3.6</v>
+      </c>
+      <c r="D44" s="7">
+        <v>11.25</v>
+      </c>
+      <c r="E44" s="9">
+        <v>7.65</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="7">
+        <v>-20.23</v>
+      </c>
+      <c r="D45" s="7">
+        <v>-20.27</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="7">
+        <v>-13.69</v>
+      </c>
+      <c r="D46" s="7">
+        <v>-14.29</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="7">
+        <v>-9.529999999999999</v>
+      </c>
+      <c r="D47" s="7">
+        <v>-11.62</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-2.09</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="7">
+        <v>-13.29</v>
+      </c>
+      <c r="D48" s="7">
+        <v>-15.35</v>
+      </c>
+      <c r="E48" s="8">
+        <v>-2.06</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="7">
+        <v>-11.58</v>
+      </c>
+      <c r="D49" s="7">
+        <v>-12.54</v>
+      </c>
+      <c r="E49" s="8">
+        <v>-0.96</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="7">
+        <v>-0.21</v>
+      </c>
+      <c r="D50" s="7">
+        <v>-2.26</v>
+      </c>
+      <c r="E50" s="8">
+        <v>-2.05</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="7">
+        <v>-42.09</v>
+      </c>
+      <c r="D51" s="7">
+        <v>-42.46</v>
+      </c>
+      <c r="E51" s="8">
+        <v>-0.37</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="7">
+        <v>-20.64</v>
+      </c>
+      <c r="D52" s="7">
+        <v>-21.34</v>
+      </c>
+      <c r="E52" s="8">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53" s="7">
+        <v>-7.94</v>
+      </c>
+      <c r="D53" s="7">
+        <v>-7.37</v>
+      </c>
+      <c r="E53" s="9">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="7">
+        <v>391.05</v>
+      </c>
+      <c r="D54" s="7">
+        <v>390.85</v>
+      </c>
+      <c r="E54" s="8">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="7">
+        <v>3282</v>
+      </c>
+      <c r="D55" s="7">
+        <v>3259</v>
+      </c>
+      <c r="E55" s="8">
+        <v>-23</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="7">
+        <v>373</v>
+      </c>
+      <c r="D56" s="7">
+        <v>364.4</v>
+      </c>
+      <c r="E56" s="8">
+        <v>-8.6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="7">
+        <v>365.65</v>
+      </c>
+      <c r="D57" s="7">
+        <v>356.95</v>
+      </c>
+      <c r="E57" s="8">
+        <v>-8.699999999999999</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="7">
+        <v>391.45</v>
+      </c>
+      <c r="D58" s="7">
+        <v>387.2</v>
+      </c>
+      <c r="E58" s="8">
+        <v>-4.25</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="7">
+        <v>663.2</v>
+      </c>
+      <c r="D59" s="7">
+        <v>649.6</v>
+      </c>
+      <c r="E59" s="8">
+        <v>-13.6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="7">
+        <v>209.65</v>
+      </c>
+      <c r="D60" s="7">
+        <v>208.31</v>
+      </c>
+      <c r="E60" s="8">
+        <v>-1.34</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C61" s="7">
+        <v>3569.3</v>
+      </c>
+      <c r="D61" s="7">
+        <v>3537.7</v>
+      </c>
+      <c r="E61" s="8">
+        <v>-31.6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C62" s="7">
+        <v>1628</v>
+      </c>
+      <c r="D62" s="7">
+        <v>1638</v>
+      </c>
+      <c r="E62" s="9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C63" s="7">
+        <v>77</v>
+      </c>
+      <c r="D63" s="7">
+        <v>66</v>
+      </c>
+      <c r="E63" s="8">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C64" s="7">
+        <v>66</v>
+      </c>
+      <c r="D64" s="7">
+        <v>77</v>
+      </c>
+      <c r="E64" s="9">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="7">
+        <v>28.46</v>
+      </c>
+      <c r="D65" s="7">
+        <v>28.33</v>
+      </c>
+      <c r="E65" s="8">
+        <v>-0.13</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="7">
+        <v>42.14</v>
+      </c>
+      <c r="D66" s="7">
+        <v>40.11</v>
+      </c>
+      <c r="E66" s="8">
+        <v>-2.03</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="7">
+        <v>46.4</v>
+      </c>
+      <c r="D67" s="7">
+        <v>41.44</v>
+      </c>
+      <c r="E67" s="8">
         <v>-4.96</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+    <row r="68" spans="1:5">
+      <c r="A68" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="7">
+        <v>36.84</v>
+      </c>
+      <c r="D68" s="7">
+        <v>30.45</v>
+      </c>
+      <c r="E68" s="8">
+        <v>-6.39</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="7">
+        <v>41</v>
+      </c>
+      <c r="D69" s="7">
+        <v>37.66</v>
+      </c>
+      <c r="E69" s="8">
+        <v>-3.34</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="7">
+        <v>75.28</v>
+      </c>
+      <c r="D70" s="7">
+        <v>65.33</v>
+      </c>
+      <c r="E70" s="8">
+        <v>-9.949999999999999</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="7">
+        <v>32.14</v>
+      </c>
+      <c r="D71" s="7">
+        <v>30.85</v>
+      </c>
+      <c r="E71" s="8">
+        <v>-1.29</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C72" s="7">
+        <v>41.19</v>
+      </c>
+      <c r="D72" s="7">
+        <v>35.92</v>
+      </c>
+      <c r="E72" s="8">
+        <v>-5.27</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B73" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C73" s="7">
+        <v>57.54</v>
+      </c>
+      <c r="D73" s="7">
+        <v>59.43</v>
+      </c>
+      <c r="E73" s="9">
+        <v>1.89</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="7">
+        <v>-30.4</v>
+      </c>
+      <c r="D74" s="7">
+        <v>-39.5</v>
+      </c>
+      <c r="E74" s="8">
+        <v>-9.1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B75" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="7">
+        <v>81.48999999999999</v>
+      </c>
+      <c r="D75" s="7">
+        <v>0.93</v>
+      </c>
+      <c r="E75" s="8">
+        <v>-80.56</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="5">
-        <v>-4.06</v>
-      </c>
-      <c r="D9" s="5">
-        <v>-3.31</v>
-      </c>
-      <c r="E9" s="6">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="B76" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="7">
+        <v>-36.46</v>
+      </c>
+      <c r="D76" s="7">
+        <v>-39.82</v>
+      </c>
+      <c r="E76" s="8">
+        <v>-3.36</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="5">
-        <v>-4.63</v>
-      </c>
-      <c r="D10" s="5">
-        <v>-6.88</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-2.25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="B77" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="7">
+        <v>-15.16</v>
+      </c>
+      <c r="D77" s="7">
+        <v>-17.99</v>
+      </c>
+      <c r="E77" s="8">
+        <v>-2.83</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="5">
-        <v>-2.46</v>
-      </c>
-      <c r="D11" s="5">
-        <v>-4.41</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-1.95</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="B78" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="7">
+        <v>-28.42</v>
+      </c>
+      <c r="D78" s="7">
+        <v>-31.7</v>
+      </c>
+      <c r="E78" s="8">
+        <v>-3.28</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="5">
-        <v>15.57</v>
-      </c>
-      <c r="D12" s="5">
-        <v>17.31</v>
-      </c>
-      <c r="E12" s="6">
-        <v>1.74</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="B79" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="7">
+        <v>73.02</v>
+      </c>
+      <c r="D79" s="7">
+        <v>-3.7</v>
+      </c>
+      <c r="E79" s="8">
+        <v>-76.72</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="5">
-        <v>-2.09</v>
-      </c>
-      <c r="D13" s="5">
-        <v>-4.01</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-1.92</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="B80" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="7">
+        <v>13.11</v>
+      </c>
+      <c r="D80" s="7">
+        <v>7.18</v>
+      </c>
+      <c r="E80" s="8">
+        <v>-5.93</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="5">
-        <v>-1.74</v>
-      </c>
-      <c r="D14" s="5">
-        <v>-1.64</v>
-      </c>
-      <c r="E14" s="6">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="B81" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81" s="7">
+        <v>193.19</v>
+      </c>
+      <c r="D81" s="7">
+        <v>107.68</v>
+      </c>
+      <c r="E81" s="8">
+        <v>-85.51000000000001</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="5">
-        <v>-1.68</v>
-      </c>
-      <c r="D15" s="5">
-        <v>-1.41</v>
-      </c>
-      <c r="E15" s="6">
-        <v>0.27</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="5">
-        <v>-2.77</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-2.08</v>
-      </c>
-      <c r="E16" s="6">
-        <v>0.6899999999999999</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="5">
-        <v>-2.29</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-3.87</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-1.58</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="5">
-        <v>-1.31</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-1.51</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-0.2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="5">
-        <v>-3.23</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-3.56</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-0.33</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="5">
-        <v>-2.09</v>
-      </c>
-      <c r="D20" s="5">
-        <v>-2.89</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-0.8</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="5">
-        <v>4.34</v>
-      </c>
-      <c r="D21" s="5">
-        <v>4.48</v>
-      </c>
-      <c r="E21" s="6">
-        <v>0.14</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="5">
-        <v>-4.69</v>
-      </c>
-      <c r="D22" s="5">
-        <v>-5.16</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-0.47</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="5">
-        <v>-0.7</v>
-      </c>
-      <c r="D23" s="5">
-        <v>0.29</v>
-      </c>
-      <c r="E23" s="6">
-        <v>0.99</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="5">
-        <v>3.59</v>
-      </c>
-      <c r="D24" s="5">
-        <v>2.78</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-0.8100000000000001</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="5">
-        <v>-0.85</v>
-      </c>
-      <c r="D25" s="5">
-        <v>2.55</v>
-      </c>
-      <c r="E25" s="6">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="5">
-        <v>-1.91</v>
-      </c>
-      <c r="D26" s="5">
-        <v>-1.47</v>
-      </c>
-      <c r="E26" s="6">
-        <v>0.44</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="5">
-        <v>41.55</v>
-      </c>
-      <c r="D27" s="5">
-        <v>43.19</v>
-      </c>
-      <c r="E27" s="6">
-        <v>1.64</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="5">
-        <v>5.95</v>
-      </c>
-      <c r="D28" s="5">
-        <v>3.33</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-2.62</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="5">
-        <v>20.33</v>
-      </c>
-      <c r="D29" s="5">
-        <v>21.62</v>
-      </c>
-      <c r="E29" s="6">
-        <v>1.29</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-0.54</v>
-      </c>
-      <c r="D30" s="5">
-        <v>0.96</v>
-      </c>
-      <c r="E30" s="6">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="5">
-        <v>-41.31</v>
-      </c>
-      <c r="D31" s="5">
-        <v>-40.19</v>
-      </c>
-      <c r="E31" s="6">
-        <v>1.12</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="5">
-        <v>-13.93</v>
-      </c>
-      <c r="D32" s="5">
-        <v>-11.21</v>
-      </c>
-      <c r="E32" s="6">
-        <v>2.72</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="5">
-        <v>8.58</v>
-      </c>
-      <c r="D33" s="5">
-        <v>9.51</v>
-      </c>
-      <c r="E33" s="6">
-        <v>0.93</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="5">
-        <v>-10.85</v>
-      </c>
-      <c r="D34" s="5">
-        <v>-12.16</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-1.31</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="5">
-        <v>12.25</v>
-      </c>
-      <c r="D35" s="5">
-        <v>9.460000000000001</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-2.79</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="5">
-        <v>27.62</v>
-      </c>
-      <c r="D36" s="5">
-        <v>26.74</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-0.88</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="5">
-        <v>9.5</v>
-      </c>
-      <c r="D37" s="5">
-        <v>8.44</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-1.06</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="5">
-        <v>13.05</v>
-      </c>
-      <c r="D38" s="5">
-        <v>12.29</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-0.76</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="5">
-        <v>7.61</v>
-      </c>
-      <c r="D39" s="5">
-        <v>8.76</v>
-      </c>
-      <c r="E39" s="6">
-        <v>1.15</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="5">
-        <v>-3.47</v>
-      </c>
-      <c r="D40" s="5">
-        <v>-2.28</v>
-      </c>
-      <c r="E40" s="6">
-        <v>1.19</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="5">
-        <v>-6.74</v>
-      </c>
-      <c r="D41" s="5">
-        <v>-6.02</v>
-      </c>
-      <c r="E41" s="6">
-        <v>0.72</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="5">
-        <v>6.33</v>
-      </c>
-      <c r="D42" s="5">
-        <v>3.6</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-2.73</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="5">
-        <v>-20.45</v>
-      </c>
-      <c r="D43" s="5">
-        <v>-20.23</v>
-      </c>
-      <c r="E43" s="6">
-        <v>0.22</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="5">
-        <v>-12.32</v>
-      </c>
-      <c r="D44" s="5">
-        <v>-13.69</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-1.37</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="5">
-        <v>-8.66</v>
-      </c>
-      <c r="D45" s="5">
-        <v>-9.529999999999999</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-0.87</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="5">
-        <v>-12.84</v>
-      </c>
-      <c r="D46" s="5">
-        <v>-13.29</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-0.45</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="5">
-        <v>-11.28</v>
-      </c>
-      <c r="D47" s="5">
-        <v>-11.58</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-0.3</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="5">
-        <v>-0.44</v>
-      </c>
-      <c r="D48" s="5">
-        <v>-0.21</v>
-      </c>
-      <c r="E48" s="6">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="5">
-        <v>-41.61</v>
-      </c>
-      <c r="D49" s="5">
-        <v>-42.09</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-0.48</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="5">
-        <v>-21.18</v>
-      </c>
-      <c r="D50" s="5">
-        <v>-20.64</v>
-      </c>
-      <c r="E50" s="6">
-        <v>0.54</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="5">
-        <v>-7.21</v>
-      </c>
-      <c r="D51" s="5">
-        <v>-7.94</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-0.73</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="5">
-        <v>389.95</v>
-      </c>
-      <c r="D52" s="5">
-        <v>391.05</v>
-      </c>
-      <c r="E52" s="6">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="5">
-        <v>3334</v>
-      </c>
-      <c r="D53" s="5">
-        <v>3282</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-52</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="5">
-        <v>376.6</v>
-      </c>
-      <c r="D54" s="5">
-        <v>373</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-3.6</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="5">
-        <v>367.55</v>
-      </c>
-      <c r="D55" s="5">
-        <v>365.65</v>
-      </c>
-      <c r="E55" s="7">
-        <v>-1.9</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="5">
-        <v>392.75</v>
-      </c>
-      <c r="D56" s="5">
-        <v>391.45</v>
-      </c>
-      <c r="E56" s="7">
-        <v>-1.3</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="5">
-        <v>661.7</v>
-      </c>
-      <c r="D57" s="5">
-        <v>663.2</v>
-      </c>
-      <c r="E57" s="6">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="5">
-        <v>211.39</v>
-      </c>
-      <c r="D58" s="5">
-        <v>209.65</v>
-      </c>
-      <c r="E58" s="7">
-        <v>-1.74</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="5">
-        <v>3544.8</v>
-      </c>
-      <c r="D59" s="5">
-        <v>3569.3</v>
-      </c>
-      <c r="E59" s="6">
-        <v>24.5</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="5">
-        <v>1640.9</v>
-      </c>
-      <c r="D60" s="5">
-        <v>1628</v>
-      </c>
-      <c r="E60" s="7">
-        <v>-12.9</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C61" s="5">
-        <v>26.83</v>
-      </c>
-      <c r="D61" s="5">
-        <v>28.46</v>
-      </c>
-      <c r="E61" s="6">
-        <v>1.63</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C62" s="5">
-        <v>47.16</v>
-      </c>
-      <c r="D62" s="5">
-        <v>42.14</v>
-      </c>
-      <c r="E62" s="7">
-        <v>-5.02</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C63" s="5">
-        <v>48.67</v>
-      </c>
-      <c r="D63" s="5">
-        <v>46.4</v>
-      </c>
-      <c r="E63" s="7">
-        <v>-2.27</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="5">
-        <v>38.48</v>
-      </c>
-      <c r="D64" s="5">
-        <v>36.84</v>
-      </c>
-      <c r="E64" s="7">
-        <v>-1.64</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="5">
-        <v>42.05</v>
-      </c>
-      <c r="D65" s="5">
-        <v>41</v>
-      </c>
-      <c r="E65" s="7">
-        <v>-1.05</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="5">
-        <v>74.88</v>
-      </c>
-      <c r="D66" s="5">
-        <v>75.28</v>
-      </c>
-      <c r="E66" s="6">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="5">
-        <v>33.84</v>
-      </c>
-      <c r="D67" s="5">
-        <v>32.14</v>
-      </c>
-      <c r="E67" s="7">
-        <v>-1.7</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="5">
-        <v>34.25</v>
-      </c>
-      <c r="D68" s="5">
-        <v>41.19</v>
-      </c>
-      <c r="E68" s="6">
-        <v>6.94</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="5">
-        <v>60.94</v>
-      </c>
-      <c r="D69" s="5">
-        <v>57.54</v>
-      </c>
-      <c r="E69" s="7">
-        <v>-3.4</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B70" s="3" t="s">
+      <c r="B82" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C70" s="5">
-        <v>-41.98</v>
-      </c>
-      <c r="D70" s="5">
-        <v>-30.4</v>
-      </c>
-      <c r="E70" s="6">
-        <v>11.58</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C71" s="5">
-        <v>-18.42</v>
-      </c>
-      <c r="D71" s="5">
-        <v>81.48999999999999</v>
-      </c>
-      <c r="E71" s="6">
-        <v>99.91</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C72" s="5">
-        <v>-67.16</v>
-      </c>
-      <c r="D72" s="5">
-        <v>-36.46</v>
-      </c>
-      <c r="E72" s="6">
-        <v>30.7</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C73" s="5">
-        <v>-79.37</v>
-      </c>
-      <c r="D73" s="5">
-        <v>-15.16</v>
-      </c>
-      <c r="E73" s="6">
-        <v>64.20999999999999</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="5">
-        <v>-53.23</v>
-      </c>
-      <c r="D74" s="5">
-        <v>-28.42</v>
-      </c>
-      <c r="E74" s="6">
-        <v>24.81</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="5">
-        <v>170.65</v>
-      </c>
-      <c r="D75" s="5">
-        <v>73.02</v>
-      </c>
-      <c r="E75" s="7">
-        <v>-97.63</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="5">
-        <v>37.35</v>
-      </c>
-      <c r="D76" s="5">
-        <v>13.11</v>
-      </c>
-      <c r="E76" s="7">
-        <v>-24.24</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="5">
-        <v>-45.14</v>
-      </c>
-      <c r="D77" s="5">
-        <v>193.19</v>
-      </c>
-      <c r="E77" s="6">
-        <v>238.33</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="5">
-        <v>27.61</v>
-      </c>
-      <c r="D78" s="5">
+      <c r="C82" s="7">
         <v>12.68</v>
       </c>
-      <c r="E78" s="7">
-        <v>-14.93</v>
+      <c r="D82" s="7">
+        <v>-8.02</v>
+      </c>
+      <c r="E82" s="8">
+        <v>-20.7</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A7:E7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3345,60 +3520,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>65</v>
+      <c r="B1" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="10">
-        <v>56.16</v>
-      </c>
-      <c r="C2" s="11">
+      <c r="B2" s="12">
+        <v>48.16</v>
+      </c>
+      <c r="C2" s="13">
         <v>9</v>
       </c>
-      <c r="D2" s="10">
-        <v>44.6</v>
-      </c>
-      <c r="E2" s="10">
-        <v>60</v>
-      </c>
-      <c r="F2" s="10">
-        <v>-1.3</v>
-      </c>
-      <c r="G2" s="10">
-        <v>5.4</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="D2" s="12">
+        <v>41.1</v>
+      </c>
+      <c r="E2" s="12">
+        <v>40</v>
+      </c>
+      <c r="F2" s="12">
+        <v>-3.8</v>
+      </c>
+      <c r="G2" s="12">
+        <v>5.2</v>
+      </c>
+      <c r="H2" s="12">
         <v>55.4</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="12">
         <v>60</v>
       </c>
     </row>
@@ -3500,61 +3675,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="14" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="13">
-        <v>0.349</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.3381</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.2034</v>
-      </c>
-      <c r="D2" s="13">
-        <v>0.1989</v>
-      </c>
-      <c r="E2" s="13">
-        <v>0.1145</v>
-      </c>
-      <c r="F2" s="13">
-        <v>0.08039999999999999</v>
-      </c>
-      <c r="G2" s="13">
-        <v>0.0547</v>
-      </c>
-      <c r="H2" s="13">
-        <v>-0.0016</v>
-      </c>
-      <c r="I2" s="13">
-        <v>-0.1222</v>
+      <c r="A2" s="15">
+        <v>0.346</v>
+      </c>
+      <c r="B2" s="15">
+        <v>0.3442</v>
+      </c>
+      <c r="C2" s="15">
+        <v>0.1988</v>
+      </c>
+      <c r="D2" s="15">
+        <v>0.195</v>
+      </c>
+      <c r="E2" s="15">
+        <v>0.1222</v>
+      </c>
+      <c r="F2" s="15">
+        <v>0.0678</v>
+      </c>
+      <c r="G2" s="15">
+        <v>0.0576</v>
+      </c>
+      <c r="H2" s="15">
+        <v>-0.0034</v>
+      </c>
+      <c r="I2" s="15">
+        <v>-0.1189</v>
       </c>
     </row>
   </sheetData>

--- a/MAHINDRA_GROUP_Technical_Metrics.xlsx
+++ b/MAHINDRA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="80">
   <si>
     <t>Symbol</t>
   </si>
@@ -193,43 +193,34 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Overbought Exit</t>
-  </si>
-  <si>
-    <t>75.3 → 65.3</t>
-  </si>
-  <si>
-    <t>🔵 COOLING</t>
-  </si>
-  <si>
-    <t>75.3</t>
+    <t>Near 52W High</t>
+  </si>
+  <si>
+    <t>-2.3% → 0.0%</t>
+  </si>
+  <si>
+    <t>🟢 BREAKOUT WATCH</t>
+  </si>
+  <si>
+    <t>-2.3%</t>
+  </si>
+  <si>
+    <t>0.0%</t>
+  </si>
+  <si>
+    <t>RSI Overbought Entry</t>
+  </si>
+  <si>
+    <t>65.3 → 70.2</t>
+  </si>
+  <si>
+    <t>⚠️ CAUTION</t>
   </si>
   <si>
     <t>65.3</t>
   </si>
   <si>
-    <t>Left 52W High Zone</t>
-  </si>
-  <si>
-    <t>-0.2% → -2.3%</t>
-  </si>
-  <si>
-    <t>⚪ NEUTRAL</t>
-  </si>
-  <si>
-    <t>-0.2%</t>
-  </si>
-  <si>
-    <t>-2.3%</t>
-  </si>
-  <si>
-    <t>50 DMA &gt; 200 DMA</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
-  </si>
-  <si>
-    <t>🔴 DEATH CROSS</t>
+    <t>70.2</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -315,7 +306,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF1F4E79"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -323,13 +321,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -362,19 +353,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -455,7 +446,7 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -968,58 +959,58 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>390.85</v>
+        <v>385</v>
       </c>
       <c r="D2">
-        <v>-0.05</v>
+        <v>-1.5</v>
       </c>
       <c r="E2">
         <v>490.2</v>
       </c>
       <c r="F2">
-        <v>379.2</v>
+        <v>381.66</v>
       </c>
       <c r="G2">
-        <v>-20.27</v>
+        <v>-21.46</v>
       </c>
       <c r="H2">
-        <v>3.07</v>
+        <v>0.88</v>
       </c>
       <c r="I2">
-        <v>-1.29</v>
+        <v>-3.02</v>
       </c>
       <c r="J2">
-        <v>-6.86</v>
+        <v>-6.23</v>
       </c>
       <c r="K2">
-        <v>-13.53</v>
+        <v>-15.55</v>
       </c>
       <c r="L2">
-        <v>2.03</v>
+        <v>1.53</v>
       </c>
       <c r="M2">
-        <v>12.22</v>
+        <v>12.24</v>
       </c>
       <c r="N2">
         <v>34</v>
       </c>
       <c r="O2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P2">
-        <v>392.67</v>
+        <v>390.27</v>
       </c>
       <c r="Q2">
-        <v>403.7</v>
+        <v>402.2</v>
       </c>
       <c r="R2">
-        <v>431.85</v>
+        <v>430.17</v>
       </c>
       <c r="S2">
-        <v>436.66</v>
+        <v>436.47</v>
       </c>
       <c r="T2">
-        <v>-10.49</v>
+        <v>-11.79</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1034,43 +1025,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>28.33</v>
+        <v>24.93</v>
       </c>
       <c r="Z2">
-        <v>-10.65</v>
+        <v>-10.9</v>
       </c>
       <c r="AA2">
-        <v>-10.75</v>
+        <v>-10.78</v>
       </c>
       <c r="AB2">
-        <v>0.1</v>
+        <v>-0.12</v>
       </c>
       <c r="AC2">
         <v>9.720000000000001</v>
       </c>
       <c r="AD2">
-        <v>6.73</v>
+        <v>8.17</v>
       </c>
       <c r="AE2">
-        <v>8.68</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="AF2">
-        <v>-39.5</v>
+        <v>-55.81</v>
       </c>
       <c r="AG2">
-        <v>419.82</v>
+        <v>419.43</v>
       </c>
       <c r="AH2">
-        <v>387.58</v>
+        <v>384.97</v>
       </c>
       <c r="AI2">
-        <v>416.42</v>
+        <v>413.86</v>
       </c>
       <c r="AJ2" t="s">
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>53.95</v>
+        <v>56.93</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1081,10 +1072,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>3259</v>
+        <v>3190</v>
       </c>
       <c r="D3">
-        <v>-0.7</v>
+        <v>-2.12</v>
       </c>
       <c r="E3">
         <v>3802.4</v>
@@ -1093,46 +1084,46 @@
         <v>2931.1</v>
       </c>
       <c r="G3">
-        <v>-14.29</v>
+        <v>-16.11</v>
       </c>
       <c r="H3">
-        <v>11.19</v>
+        <v>8.83</v>
       </c>
       <c r="I3">
-        <v>-5.34</v>
+        <v>-6.13</v>
       </c>
       <c r="J3">
-        <v>-4.95</v>
+        <v>-7.08</v>
       </c>
       <c r="K3">
-        <v>8.23</v>
+        <v>5.77</v>
       </c>
       <c r="L3">
-        <v>-1.1</v>
+        <v>-0.3</v>
       </c>
       <c r="M3">
-        <v>34.42</v>
+        <v>34.46</v>
       </c>
       <c r="N3">
         <v>45</v>
       </c>
       <c r="O3">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="P3">
-        <v>3320.64</v>
+        <v>3279</v>
       </c>
       <c r="Q3">
-        <v>3406.24</v>
+        <v>3392.97</v>
       </c>
       <c r="R3">
-        <v>3270.75</v>
+        <v>3273.8</v>
       </c>
       <c r="S3">
-        <v>3341.81</v>
+        <v>3339.27</v>
       </c>
       <c r="T3">
-        <v>-2.48</v>
+        <v>-4.47</v>
       </c>
       <c r="U3" t="s">
         <v>48</v>
@@ -1147,43 +1138,43 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>40.11</v>
+        <v>34.71</v>
       </c>
       <c r="Z3">
-        <v>7.1</v>
+        <v>-6.65</v>
       </c>
       <c r="AA3">
-        <v>35.71</v>
+        <v>27.23</v>
       </c>
       <c r="AB3">
-        <v>-28.61</v>
+        <v>-33.89</v>
       </c>
       <c r="AC3">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="AD3">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="AE3">
-        <v>70.69</v>
+        <v>73.95999999999999</v>
       </c>
       <c r="AF3">
-        <v>0.93</v>
+        <v>55.3</v>
       </c>
       <c r="AG3">
-        <v>3534.63</v>
+        <v>3551.33</v>
       </c>
       <c r="AH3">
-        <v>3277.85</v>
+        <v>3234.61</v>
       </c>
       <c r="AI3">
-        <v>3507.57</v>
+        <v>3407.93</v>
       </c>
       <c r="AJ3" t="s">
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>33.66</v>
+        <v>39.05</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1194,58 +1185,58 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>364.4</v>
+        <v>368.85</v>
       </c>
       <c r="D4">
-        <v>-2.31</v>
+        <v>1.22</v>
       </c>
       <c r="E4">
         <v>412.3</v>
       </c>
       <c r="F4">
-        <v>253.95</v>
+        <v>257.5</v>
       </c>
       <c r="G4">
-        <v>-11.62</v>
+        <v>-10.54</v>
       </c>
       <c r="H4">
-        <v>43.49</v>
+        <v>43.24</v>
       </c>
       <c r="I4">
-        <v>-4.47</v>
+        <v>-4.28</v>
       </c>
       <c r="J4">
-        <v>-10.14</v>
+        <v>-7.46</v>
       </c>
       <c r="K4">
-        <v>25.42</v>
+        <v>27.61</v>
       </c>
       <c r="L4">
-        <v>40.64</v>
+        <v>45.25</v>
       </c>
       <c r="M4">
-        <v>19.5</v>
+        <v>19.17</v>
       </c>
       <c r="N4">
         <v>99</v>
       </c>
       <c r="O4">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="P4">
-        <v>376.54</v>
+        <v>373.24</v>
       </c>
       <c r="Q4">
-        <v>388.04</v>
+        <v>386.56</v>
       </c>
       <c r="R4">
-        <v>361.64</v>
+        <v>363.19</v>
       </c>
       <c r="S4">
-        <v>343.31</v>
+        <v>343.61</v>
       </c>
       <c r="T4">
-        <v>6.14</v>
+        <v>7.35</v>
       </c>
       <c r="U4" t="s">
         <v>48</v>
@@ -1260,34 +1251,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>41.44</v>
+        <v>44.73</v>
       </c>
       <c r="Z4">
-        <v>1.92</v>
+        <v>0.92</v>
       </c>
       <c r="AA4">
-        <v>6.68</v>
+        <v>5.53</v>
       </c>
       <c r="AB4">
-        <v>-4.76</v>
+        <v>-4.61</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>6.73</v>
       </c>
       <c r="AD4">
-        <v>5.15</v>
+        <v>3.69</v>
       </c>
       <c r="AE4">
-        <v>12.17</v>
+        <v>12.04</v>
       </c>
       <c r="AF4">
-        <v>-39.82</v>
+        <v>-44.01</v>
       </c>
       <c r="AG4">
-        <v>411.06</v>
+        <v>410.56</v>
       </c>
       <c r="AH4">
-        <v>365.01</v>
+        <v>362.56</v>
       </c>
       <c r="AI4">
         <v>357.72</v>
@@ -1296,7 +1287,7 @@
         <v>50</v>
       </c>
       <c r="AK4">
-        <v>24.61</v>
+        <v>27.78</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1307,10 +1298,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>356.95</v>
+        <v>359</v>
       </c>
       <c r="D5">
-        <v>-2.38</v>
+        <v>0.57</v>
       </c>
       <c r="E5">
         <v>421.7</v>
@@ -1319,46 +1310,46 @@
         <v>294.25</v>
       </c>
       <c r="G5">
-        <v>-15.35</v>
+        <v>-14.87</v>
       </c>
       <c r="H5">
-        <v>21.31</v>
+        <v>22.01</v>
       </c>
       <c r="I5">
-        <v>-5.21</v>
+        <v>-3.3</v>
       </c>
       <c r="J5">
-        <v>-10.37</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="K5">
-        <v>6.65</v>
+        <v>6.72</v>
       </c>
       <c r="L5">
-        <v>3.58</v>
+        <v>2.59</v>
       </c>
       <c r="M5">
-        <v>6.78</v>
+        <v>6.95</v>
       </c>
       <c r="N5">
         <v>55</v>
       </c>
       <c r="O5">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="P5">
-        <v>366.01</v>
+        <v>363.56</v>
       </c>
       <c r="Q5">
-        <v>378.2</v>
+        <v>377.01</v>
       </c>
       <c r="R5">
-        <v>376.15</v>
+        <v>376.13</v>
       </c>
       <c r="S5">
-        <v>363.8</v>
+        <v>363.64</v>
       </c>
       <c r="T5">
-        <v>-1.88</v>
+        <v>-1.28</v>
       </c>
       <c r="U5" t="s">
         <v>48</v>
@@ -1373,43 +1364,43 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>30.45</v>
+        <v>33.38</v>
       </c>
       <c r="Z5">
-        <v>-3.41</v>
+        <v>-4.17</v>
       </c>
       <c r="AA5">
-        <v>-0.32</v>
+        <v>-1.09</v>
       </c>
       <c r="AB5">
         <v>-3.09</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE5">
-        <v>10.14</v>
+        <v>10.06</v>
       </c>
       <c r="AF5">
-        <v>-17.99</v>
+        <v>-41.47</v>
       </c>
       <c r="AG5">
-        <v>395.04</v>
+        <v>395.73</v>
       </c>
       <c r="AH5">
-        <v>361.36</v>
+        <v>358.29</v>
       </c>
       <c r="AI5">
-        <v>391.46</v>
+        <v>386.7</v>
       </c>
       <c r="AJ5" t="s">
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>38.13</v>
+        <v>42.13</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1420,10 +1411,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>387.2</v>
+        <v>392.45</v>
       </c>
       <c r="D6">
-        <v>-1.09</v>
+        <v>1.36</v>
       </c>
       <c r="E6">
         <v>442.7</v>
@@ -1432,46 +1423,46 @@
         <v>279.55</v>
       </c>
       <c r="G6">
-        <v>-12.54</v>
+        <v>-11.35</v>
       </c>
       <c r="H6">
-        <v>38.51</v>
+        <v>40.39</v>
       </c>
       <c r="I6">
-        <v>-3.13</v>
+        <v>-1.74</v>
       </c>
       <c r="J6">
-        <v>-6.99</v>
+        <v>-6.78</v>
       </c>
       <c r="K6">
-        <v>10.5</v>
+        <v>13.1</v>
       </c>
       <c r="L6">
-        <v>23.29</v>
+        <v>23.86</v>
       </c>
       <c r="M6">
-        <v>-11.89</v>
+        <v>-11.49</v>
       </c>
       <c r="N6">
         <v>88</v>
       </c>
       <c r="O6">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="P6">
-        <v>392.48</v>
+        <v>391.09</v>
       </c>
       <c r="Q6">
-        <v>402.93</v>
+        <v>401.88</v>
       </c>
       <c r="R6">
-        <v>397.2</v>
+        <v>397.38</v>
       </c>
       <c r="S6">
-        <v>366.97</v>
+        <v>367.23</v>
       </c>
       <c r="T6">
-        <v>5.51</v>
+        <v>6.87</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1486,34 +1477,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>37.66</v>
+        <v>43.75</v>
       </c>
       <c r="Z6">
-        <v>-1.99</v>
+        <v>-2.23</v>
       </c>
       <c r="AA6">
-        <v>0.87</v>
+        <v>0.25</v>
       </c>
       <c r="AB6">
-        <v>-2.85</v>
+        <v>-2.47</v>
       </c>
       <c r="AC6">
-        <v>3.37</v>
+        <v>13.15</v>
       </c>
       <c r="AD6">
-        <v>3.2</v>
+        <v>6.63</v>
       </c>
       <c r="AE6">
-        <v>11.46</v>
+        <v>11.64</v>
       </c>
       <c r="AF6">
-        <v>-31.7</v>
+        <v>-37.04</v>
       </c>
       <c r="AG6">
-        <v>417.78</v>
+        <v>416.56</v>
       </c>
       <c r="AH6">
-        <v>388.08</v>
+        <v>387.19</v>
       </c>
       <c r="AI6">
         <v>372.35</v>
@@ -1522,7 +1513,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>19.4</v>
+        <v>20.76</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1533,58 +1524,58 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>649.6</v>
+        <v>665.05</v>
       </c>
       <c r="D7">
-        <v>-2.05</v>
+        <v>2.38</v>
       </c>
       <c r="E7">
-        <v>664.6</v>
+        <v>665.05</v>
       </c>
       <c r="F7">
         <v>506.45</v>
       </c>
       <c r="G7">
-        <v>-2.26</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>28.27</v>
+        <v>31.32</v>
       </c>
       <c r="I7">
-        <v>2.05</v>
+        <v>4.48</v>
       </c>
       <c r="J7">
-        <v>13.23</v>
+        <v>14.84</v>
       </c>
       <c r="K7">
-        <v>6.39</v>
+        <v>8.16</v>
       </c>
       <c r="L7">
-        <v>-0.8</v>
+        <v>3.68</v>
       </c>
       <c r="M7">
-        <v>34.6</v>
+        <v>34.98</v>
       </c>
       <c r="N7">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="O7">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="P7">
-        <v>650.62</v>
+        <v>656.3200000000001</v>
       </c>
       <c r="Q7">
-        <v>620.96</v>
+        <v>625.09</v>
       </c>
       <c r="R7">
-        <v>603.64</v>
+        <v>603.96</v>
       </c>
       <c r="S7">
-        <v>585.67</v>
+        <v>586.1799999999999</v>
       </c>
       <c r="T7">
-        <v>10.91</v>
+        <v>13.45</v>
       </c>
       <c r="U7" t="s">
         <v>48</v>
@@ -1599,34 +1590,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>65.33</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="Z7">
-        <v>16.08</v>
+        <v>17.13</v>
       </c>
       <c r="AA7">
-        <v>11.87</v>
+        <v>12.92</v>
       </c>
       <c r="AB7">
-        <v>4.21</v>
+        <v>4.2</v>
       </c>
       <c r="AC7">
-        <v>82.2</v>
+        <v>73.03</v>
       </c>
       <c r="AD7">
-        <v>94.06999999999999</v>
+        <v>85.08</v>
       </c>
       <c r="AE7">
-        <v>18</v>
+        <v>18.78</v>
       </c>
       <c r="AF7">
-        <v>-3.7</v>
+        <v>104.96</v>
       </c>
       <c r="AG7">
-        <v>668.35</v>
+        <v>672.77</v>
       </c>
       <c r="AH7">
-        <v>573.58</v>
+        <v>577.41</v>
       </c>
       <c r="AI7">
         <v>605.9</v>
@@ -1635,7 +1626,7 @@
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>67.06999999999999</v>
+        <v>67.45999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1646,58 +1637,58 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>208.31</v>
+        <v>206.59</v>
       </c>
       <c r="D8">
-        <v>-0.64</v>
+        <v>-0.83</v>
       </c>
       <c r="E8">
         <v>362.05</v>
       </c>
       <c r="F8">
-        <v>208.31</v>
+        <v>206.59</v>
       </c>
       <c r="G8">
-        <v>-42.46</v>
+        <v>-42.94</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
       <c r="I8">
-        <v>-4.92</v>
+        <v>-5.32</v>
       </c>
       <c r="J8">
-        <v>-4.86</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="K8">
-        <v>-1.73</v>
+        <v>-4.83</v>
       </c>
       <c r="L8">
-        <v>-40.8</v>
+        <v>-40.96</v>
       </c>
       <c r="M8">
-        <v>-0.34</v>
+        <v>-1.52</v>
       </c>
       <c r="N8">
         <v>12</v>
       </c>
       <c r="O8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P8">
-        <v>211.75</v>
+        <v>209.43</v>
       </c>
       <c r="Q8">
-        <v>221.72</v>
+        <v>220.39</v>
       </c>
       <c r="R8">
-        <v>225.71</v>
+        <v>225.04</v>
       </c>
       <c r="S8">
-        <v>261.93</v>
+        <v>261.39</v>
       </c>
       <c r="T8">
-        <v>-20.47</v>
+        <v>-20.97</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1712,43 +1703,43 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>30.85</v>
+        <v>29.23</v>
       </c>
       <c r="Z8">
-        <v>-3.99</v>
+        <v>-4.45</v>
       </c>
       <c r="AA8">
-        <v>-2.52</v>
+        <v>-2.91</v>
       </c>
       <c r="AB8">
-        <v>-1.47</v>
+        <v>-1.54</v>
       </c>
       <c r="AC8">
-        <v>0.59</v>
+        <v>0</v>
       </c>
       <c r="AD8">
-        <v>0.59</v>
+        <v>0.39</v>
       </c>
       <c r="AE8">
-        <v>6.35</v>
+        <v>6.24</v>
       </c>
       <c r="AF8">
-        <v>7.18</v>
+        <v>-19.98</v>
       </c>
       <c r="AG8">
-        <v>236.23</v>
+        <v>235.33</v>
       </c>
       <c r="AH8">
-        <v>207.21</v>
+        <v>205.44</v>
       </c>
       <c r="AI8">
-        <v>228.5</v>
+        <v>226.32</v>
       </c>
       <c r="AJ8" t="s">
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>36.21</v>
+        <v>39.77</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1759,10 +1750,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>3537.7</v>
+        <v>3540.9</v>
       </c>
       <c r="D9">
-        <v>-0.89</v>
+        <v>0.09</v>
       </c>
       <c r="E9">
         <v>4497.5</v>
@@ -1771,46 +1762,46 @@
         <v>3308.9</v>
       </c>
       <c r="G9">
-        <v>-21.34</v>
+        <v>-21.27</v>
       </c>
       <c r="H9">
-        <v>6.91</v>
+        <v>7.01</v>
       </c>
       <c r="I9">
-        <v>-0.39</v>
+        <v>-0.23</v>
       </c>
       <c r="J9">
-        <v>-2.56</v>
+        <v>-1.6</v>
       </c>
       <c r="K9">
-        <v>-6.37</v>
+        <v>-6.1</v>
       </c>
       <c r="L9">
-        <v>-12.27</v>
+        <v>-11.73</v>
       </c>
       <c r="M9">
-        <v>19.88</v>
+        <v>19.91</v>
       </c>
       <c r="N9">
         <v>23</v>
       </c>
       <c r="O9">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="P9">
-        <v>3549.82</v>
+        <v>3548.2</v>
       </c>
       <c r="Q9">
-        <v>3586.18</v>
+        <v>3582.78</v>
       </c>
       <c r="R9">
-        <v>3687.97</v>
+        <v>3680.45</v>
       </c>
       <c r="S9">
-        <v>3693.9</v>
+        <v>3691.52</v>
       </c>
       <c r="T9">
-        <v>-4.23</v>
+        <v>-4.08</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1825,43 +1816,43 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>35.92</v>
+        <v>36.8</v>
       </c>
       <c r="Z9">
-        <v>-32.6</v>
+        <v>-32.28</v>
       </c>
       <c r="AA9">
-        <v>-33.82</v>
+        <v>-33.51</v>
       </c>
       <c r="AB9">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AC9">
-        <v>22.58</v>
+        <v>29.28</v>
       </c>
       <c r="AD9">
-        <v>13.59</v>
+        <v>23.35</v>
       </c>
       <c r="AE9">
-        <v>52.33</v>
+        <v>52.37</v>
       </c>
       <c r="AF9">
-        <v>107.68</v>
+        <v>21.59</v>
       </c>
       <c r="AG9">
-        <v>3647.51</v>
+        <v>3646.31</v>
       </c>
       <c r="AH9">
-        <v>3524.86</v>
+        <v>3519.26</v>
       </c>
       <c r="AI9">
-        <v>3694.04</v>
+        <v>3684.57</v>
       </c>
       <c r="AJ9" t="s">
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>18.41</v>
+        <v>17.74</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1872,10 +1863,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>1638</v>
+        <v>1623</v>
       </c>
       <c r="D10">
-        <v>0.61</v>
+        <v>-0.92</v>
       </c>
       <c r="E10">
         <v>1768.4</v>
@@ -1884,46 +1875,46 @@
         <v>1326.2</v>
       </c>
       <c r="G10">
-        <v>-7.37</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="H10">
-        <v>23.51</v>
+        <v>22.38</v>
       </c>
       <c r="I10">
-        <v>2.38</v>
+        <v>3.31</v>
       </c>
       <c r="J10">
-        <v>-0.67</v>
+        <v>-1.55</v>
       </c>
       <c r="K10">
-        <v>11.25</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="L10">
-        <v>10.67</v>
+        <v>10.71</v>
       </c>
       <c r="M10">
-        <v>5.76</v>
+        <v>5.55</v>
       </c>
       <c r="N10">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="O10">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P10">
-        <v>1612.58</v>
+        <v>1622.98</v>
       </c>
       <c r="Q10">
-        <v>1615.59</v>
+        <v>1614.24</v>
       </c>
       <c r="R10">
-        <v>1553.15</v>
+        <v>1557.3</v>
       </c>
       <c r="S10">
-        <v>1513.74</v>
+        <v>1514.65</v>
       </c>
       <c r="T10">
-        <v>8.210000000000001</v>
+        <v>7.15</v>
       </c>
       <c r="U10" t="s">
         <v>48</v>
@@ -1938,34 +1929,34 @@
         <v>3</v>
       </c>
       <c r="Y10">
-        <v>59.43</v>
+        <v>55.44</v>
       </c>
       <c r="Z10">
         <v>11.96</v>
       </c>
       <c r="AA10">
-        <v>13.59</v>
+        <v>13.26</v>
       </c>
       <c r="AB10">
-        <v>-1.63</v>
+        <v>-1.3</v>
       </c>
       <c r="AC10">
-        <v>75.93000000000001</v>
+        <v>72.17</v>
       </c>
       <c r="AD10">
-        <v>54.42</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="AE10">
-        <v>37.1</v>
+        <v>36.85</v>
       </c>
       <c r="AF10">
-        <v>-8.02</v>
+        <v>-40.6</v>
       </c>
       <c r="AG10">
-        <v>1666.65</v>
+        <v>1662.83</v>
       </c>
       <c r="AH10">
-        <v>1564.52</v>
+        <v>1565.64</v>
       </c>
       <c r="AI10">
         <v>1527.05</v>
@@ -1974,7 +1965,7 @@
         <v>50</v>
       </c>
       <c r="AK10">
-        <v>33.53</v>
+        <v>31.37</v>
       </c>
     </row>
   </sheetData>
@@ -2115,7 +2106,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F82"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2174,992 +2165,989 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="5" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B5" s="5" t="s">
+    <row r="6" spans="1:6">
+      <c r="A6" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="C7" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="2" t="s">
+      <c r="D7" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
+      <c r="E7" s="3" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>74</v>
+      <c r="A8" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="7">
+        <v>-6.86</v>
+      </c>
+      <c r="D8" s="7">
+        <v>-6.23</v>
+      </c>
+      <c r="E8" s="8">
+        <v>0.63</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="7">
-        <v>-4.3</v>
+        <v>-4.95</v>
       </c>
       <c r="D9" s="7">
-        <v>-6.86</v>
-      </c>
-      <c r="E9" s="8">
-        <v>-2.56</v>
+        <v>-7.08</v>
+      </c>
+      <c r="E9" s="9">
+        <v>-2.13</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="7">
-        <v>-3.43</v>
+        <v>-10.14</v>
       </c>
       <c r="D10" s="7">
-        <v>-4.95</v>
+        <v>-7.46</v>
       </c>
       <c r="E10" s="8">
-        <v>-1.52</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="7">
-        <v>-3.31</v>
+        <v>-10.37</v>
       </c>
       <c r="D11" s="7">
-        <v>-10.14</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="E11" s="8">
-        <v>-6.83</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="7">
-        <v>-6.88</v>
+        <v>-6.99</v>
       </c>
       <c r="D12" s="7">
-        <v>-10.37</v>
+        <v>-6.78</v>
       </c>
       <c r="E12" s="8">
-        <v>-3.49</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="7">
-        <v>-4.41</v>
+        <v>13.23</v>
       </c>
       <c r="D13" s="7">
-        <v>-6.99</v>
+        <v>14.84</v>
       </c>
       <c r="E13" s="8">
-        <v>-2.58</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="7">
-        <v>17.31</v>
+        <v>-4.86</v>
       </c>
       <c r="D14" s="7">
-        <v>13.23</v>
-      </c>
-      <c r="E14" s="8">
-        <v>-4.08</v>
+        <v>-9.380000000000001</v>
+      </c>
+      <c r="E14" s="9">
+        <v>-4.52</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="7">
-        <v>-4.01</v>
+        <v>-2.56</v>
       </c>
       <c r="D15" s="7">
-        <v>-4.86</v>
+        <v>-1.6</v>
       </c>
       <c r="E15" s="8">
-        <v>-0.85</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="7">
-        <v>-1.64</v>
+        <v>-0.67</v>
       </c>
       <c r="D16" s="7">
-        <v>-2.56</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-0.92</v>
+        <v>-1.55</v>
+      </c>
+      <c r="E16" s="9">
+        <v>-0.88</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="6" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C17" s="7">
-        <v>-1.41</v>
+        <v>-1.29</v>
       </c>
       <c r="D17" s="7">
-        <v>-0.67</v>
+        <v>-3.02</v>
       </c>
       <c r="E17" s="9">
-        <v>0.74</v>
+        <v>-1.73</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="7">
-        <v>-2.08</v>
+        <v>-5.34</v>
       </c>
       <c r="D18" s="7">
-        <v>-1.29</v>
+        <v>-6.13</v>
       </c>
       <c r="E18" s="9">
-        <v>0.79</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="7">
-        <v>-3.87</v>
+        <v>-4.47</v>
       </c>
       <c r="D19" s="7">
-        <v>-5.34</v>
+        <v>-4.28</v>
       </c>
       <c r="E19" s="8">
-        <v>-1.47</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="7">
-        <v>-1.51</v>
+        <v>-5.21</v>
       </c>
       <c r="D20" s="7">
-        <v>-4.47</v>
+        <v>-3.3</v>
       </c>
       <c r="E20" s="8">
-        <v>-2.96</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="7">
-        <v>-3.56</v>
+        <v>-3.13</v>
       </c>
       <c r="D21" s="7">
-        <v>-5.21</v>
+        <v>-1.74</v>
       </c>
       <c r="E21" s="8">
-        <v>-1.65</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="7">
-        <v>-2.89</v>
+        <v>2.05</v>
       </c>
       <c r="D22" s="7">
-        <v>-3.13</v>
+        <v>4.48</v>
       </c>
       <c r="E22" s="8">
-        <v>-0.24</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="7">
-        <v>4.48</v>
+        <v>-4.92</v>
       </c>
       <c r="D23" s="7">
-        <v>2.05</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-2.43</v>
+        <v>-5.32</v>
+      </c>
+      <c r="E23" s="9">
+        <v>-0.4</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="7">
-        <v>-5.16</v>
+        <v>-0.39</v>
       </c>
       <c r="D24" s="7">
-        <v>-4.92</v>
-      </c>
-      <c r="E24" s="9">
-        <v>0.24</v>
+        <v>-0.23</v>
+      </c>
+      <c r="E24" s="8">
+        <v>0.16</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C25" s="7">
-        <v>0.29</v>
+        <v>2.38</v>
       </c>
       <c r="D25" s="7">
-        <v>-0.39</v>
+        <v>3.31</v>
       </c>
       <c r="E25" s="8">
-        <v>-0.68</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="6" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C26" s="7">
-        <v>2.78</v>
+        <v>2.03</v>
       </c>
       <c r="D26" s="7">
-        <v>2.38</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-0.4</v>
+        <v>1.53</v>
+      </c>
+      <c r="E26" s="9">
+        <v>-0.5</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C27" s="7">
-        <v>2.55</v>
+        <v>-1.1</v>
       </c>
       <c r="D27" s="7">
-        <v>2.03</v>
+        <v>-0.3</v>
       </c>
       <c r="E27" s="8">
-        <v>-0.52</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="7">
-        <v>-1.47</v>
+        <v>40.64</v>
       </c>
       <c r="D28" s="7">
-        <v>-1.1</v>
-      </c>
-      <c r="E28" s="9">
-        <v>0.37</v>
+        <v>45.25</v>
+      </c>
+      <c r="E28" s="8">
+        <v>4.61</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C29" s="7">
-        <v>43.19</v>
+        <v>3.58</v>
       </c>
       <c r="D29" s="7">
-        <v>40.64</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-2.55</v>
+        <v>2.59</v>
+      </c>
+      <c r="E29" s="9">
+        <v>-0.99</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C30" s="7">
-        <v>3.33</v>
+        <v>23.29</v>
       </c>
       <c r="D30" s="7">
-        <v>3.58</v>
-      </c>
-      <c r="E30" s="9">
-        <v>0.25</v>
+        <v>23.86</v>
+      </c>
+      <c r="E30" s="8">
+        <v>0.57</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C31" s="7">
-        <v>21.62</v>
+        <v>-0.8</v>
       </c>
       <c r="D31" s="7">
-        <v>23.29</v>
-      </c>
-      <c r="E31" s="9">
-        <v>1.67</v>
+        <v>3.68</v>
+      </c>
+      <c r="E31" s="8">
+        <v>4.48</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C32" s="7">
-        <v>0.96</v>
+        <v>-40.8</v>
       </c>
       <c r="D32" s="7">
-        <v>-0.8</v>
-      </c>
-      <c r="E32" s="8">
-        <v>-1.76</v>
+        <v>-40.96</v>
+      </c>
+      <c r="E32" s="9">
+        <v>-0.16</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C33" s="7">
-        <v>-40.19</v>
+        <v>-12.27</v>
       </c>
       <c r="D33" s="7">
-        <v>-40.8</v>
+        <v>-11.73</v>
       </c>
       <c r="E33" s="8">
-        <v>-0.61</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C34" s="7">
-        <v>-11.21</v>
+        <v>10.67</v>
       </c>
       <c r="D34" s="7">
-        <v>-12.27</v>
+        <v>10.71</v>
       </c>
       <c r="E34" s="8">
-        <v>-1.06</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="6" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C35" s="7">
-        <v>9.51</v>
+        <v>-13.53</v>
       </c>
       <c r="D35" s="7">
-        <v>10.67</v>
+        <v>-15.55</v>
       </c>
       <c r="E35" s="9">
-        <v>1.16</v>
+        <v>-2.02</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C36" s="7">
-        <v>-12.16</v>
+        <v>8.23</v>
       </c>
       <c r="D36" s="7">
-        <v>-13.53</v>
-      </c>
-      <c r="E36" s="8">
-        <v>-1.37</v>
+        <v>5.77</v>
+      </c>
+      <c r="E36" s="9">
+        <v>-2.46</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C37" s="7">
-        <v>9.460000000000001</v>
+        <v>25.42</v>
       </c>
       <c r="D37" s="7">
-        <v>8.23</v>
+        <v>27.61</v>
       </c>
       <c r="E37" s="8">
-        <v>-1.23</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C38" s="7">
-        <v>26.74</v>
+        <v>6.65</v>
       </c>
       <c r="D38" s="7">
-        <v>25.42</v>
+        <v>6.72</v>
       </c>
       <c r="E38" s="8">
-        <v>-1.32</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C39" s="7">
-        <v>8.44</v>
+        <v>10.5</v>
       </c>
       <c r="D39" s="7">
-        <v>6.65</v>
+        <v>13.1</v>
       </c>
       <c r="E39" s="8">
-        <v>-1.79</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C40" s="7">
-        <v>12.29</v>
+        <v>6.39</v>
       </c>
       <c r="D40" s="7">
-        <v>10.5</v>
+        <v>8.16</v>
       </c>
       <c r="E40" s="8">
-        <v>-1.79</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C41" s="7">
-        <v>8.76</v>
+        <v>-1.73</v>
       </c>
       <c r="D41" s="7">
-        <v>6.39</v>
-      </c>
-      <c r="E41" s="8">
-        <v>-2.37</v>
+        <v>-4.83</v>
+      </c>
+      <c r="E41" s="9">
+        <v>-3.1</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C42" s="7">
-        <v>-2.28</v>
+        <v>-6.37</v>
       </c>
       <c r="D42" s="7">
-        <v>-1.73</v>
-      </c>
-      <c r="E42" s="9">
-        <v>0.55</v>
+        <v>-6.1</v>
+      </c>
+      <c r="E42" s="8">
+        <v>0.27</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C43" s="7">
-        <v>-6.02</v>
+        <v>11.25</v>
       </c>
       <c r="D43" s="7">
-        <v>-6.37</v>
-      </c>
-      <c r="E43" s="8">
-        <v>-0.35</v>
+        <v>9.119999999999999</v>
+      </c>
+      <c r="E43" s="9">
+        <v>-2.13</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="6" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C44" s="7">
-        <v>3.6</v>
+        <v>-20.27</v>
       </c>
       <c r="D44" s="7">
-        <v>11.25</v>
+        <v>-21.46</v>
       </c>
       <c r="E44" s="9">
-        <v>7.65</v>
+        <v>-1.19</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C45" s="7">
-        <v>-20.23</v>
+        <v>-14.29</v>
       </c>
       <c r="D45" s="7">
-        <v>-20.27</v>
-      </c>
-      <c r="E45" s="8">
-        <v>-0.04</v>
+        <v>-16.11</v>
+      </c>
+      <c r="E45" s="9">
+        <v>-1.82</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C46" s="7">
-        <v>-13.69</v>
+        <v>-11.62</v>
       </c>
       <c r="D46" s="7">
-        <v>-14.29</v>
+        <v>-10.54</v>
       </c>
       <c r="E46" s="8">
-        <v>-0.6</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C47" s="7">
-        <v>-9.529999999999999</v>
+        <v>-15.35</v>
       </c>
       <c r="D47" s="7">
-        <v>-11.62</v>
+        <v>-14.87</v>
       </c>
       <c r="E47" s="8">
-        <v>-2.09</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C48" s="7">
-        <v>-13.29</v>
+        <v>-12.54</v>
       </c>
       <c r="D48" s="7">
-        <v>-15.35</v>
+        <v>-11.35</v>
       </c>
       <c r="E48" s="8">
-        <v>-2.06</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C49" s="7">
-        <v>-11.58</v>
+        <v>-2.26</v>
       </c>
       <c r="D49" s="7">
-        <v>-12.54</v>
+        <v>0</v>
       </c>
       <c r="E49" s="8">
-        <v>-0.96</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C50" s="7">
-        <v>-0.21</v>
+        <v>-42.46</v>
       </c>
       <c r="D50" s="7">
-        <v>-2.26</v>
-      </c>
-      <c r="E50" s="8">
-        <v>-2.05</v>
+        <v>-42.94</v>
+      </c>
+      <c r="E50" s="9">
+        <v>-0.48</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C51" s="7">
-        <v>-42.09</v>
+        <v>-21.34</v>
       </c>
       <c r="D51" s="7">
-        <v>-42.46</v>
+        <v>-21.27</v>
       </c>
       <c r="E51" s="8">
-        <v>-0.37</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C52" s="7">
-        <v>-20.64</v>
+        <v>-7.37</v>
       </c>
       <c r="D52" s="7">
-        <v>-21.34</v>
-      </c>
-      <c r="E52" s="8">
-        <v>-0.7</v>
+        <v>-8.220000000000001</v>
+      </c>
+      <c r="E52" s="9">
+        <v>-0.85</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="6" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C53" s="7">
-        <v>-7.94</v>
+        <v>390.85</v>
       </c>
       <c r="D53" s="7">
-        <v>-7.37</v>
+        <v>385</v>
       </c>
       <c r="E53" s="9">
-        <v>0.57</v>
+        <v>-5.85</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C54" s="7">
-        <v>391.05</v>
+        <v>3259</v>
       </c>
       <c r="D54" s="7">
-        <v>390.85</v>
-      </c>
-      <c r="E54" s="8">
-        <v>-0.2</v>
+        <v>3190</v>
+      </c>
+      <c r="E54" s="9">
+        <v>-69</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C55" s="7">
-        <v>3282</v>
+        <v>364.4</v>
       </c>
       <c r="D55" s="7">
-        <v>3259</v>
+        <v>368.85</v>
       </c>
       <c r="E55" s="8">
-        <v>-23</v>
+        <v>4.45</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C56" s="7">
-        <v>373</v>
+        <v>356.95</v>
       </c>
       <c r="D56" s="7">
-        <v>364.4</v>
+        <v>359</v>
       </c>
       <c r="E56" s="8">
-        <v>-8.6</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C57" s="7">
-        <v>365.65</v>
+        <v>387.2</v>
       </c>
       <c r="D57" s="7">
-        <v>356.95</v>
+        <v>392.45</v>
       </c>
       <c r="E57" s="8">
-        <v>-8.699999999999999</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C58" s="7">
-        <v>391.45</v>
+        <v>649.6</v>
       </c>
       <c r="D58" s="7">
-        <v>387.2</v>
+        <v>665.05</v>
       </c>
       <c r="E58" s="8">
-        <v>-4.25</v>
+        <v>15.45</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C59" s="7">
-        <v>663.2</v>
+        <v>208.31</v>
       </c>
       <c r="D59" s="7">
-        <v>649.6</v>
-      </c>
-      <c r="E59" s="8">
-        <v>-13.6</v>
+        <v>206.59</v>
+      </c>
+      <c r="E59" s="9">
+        <v>-1.72</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C60" s="7">
-        <v>209.65</v>
+        <v>3537.7</v>
       </c>
       <c r="D60" s="7">
-        <v>208.31</v>
+        <v>3540.9</v>
       </c>
       <c r="E60" s="8">
-        <v>-1.34</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C61" s="7">
-        <v>3569.3</v>
+        <v>1638</v>
       </c>
       <c r="D61" s="7">
-        <v>3537.7</v>
-      </c>
-      <c r="E61" s="8">
-        <v>-31.6</v>
+        <v>1623</v>
+      </c>
+      <c r="E61" s="9">
+        <v>-15</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="6" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C62" s="7">
-        <v>1628</v>
+        <v>66</v>
       </c>
       <c r="D62" s="7">
-        <v>1638</v>
-      </c>
-      <c r="E62" s="9">
-        <v>10</v>
+        <v>77</v>
+      </c>
+      <c r="E62" s="8">
+        <v>11</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B63" s="6" t="s">
         <v>13</v>
@@ -3170,337 +3158,320 @@
       <c r="D63" s="7">
         <v>66</v>
       </c>
-      <c r="E63" s="8">
+      <c r="E63" s="9">
         <v>-11</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="6" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C64" s="7">
-        <v>66</v>
+        <v>28.33</v>
       </c>
       <c r="D64" s="7">
-        <v>77</v>
+        <v>24.93</v>
       </c>
       <c r="E64" s="9">
-        <v>11</v>
+        <v>-3.4</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B65" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C65" s="7">
-        <v>28.46</v>
+        <v>40.11</v>
       </c>
       <c r="D65" s="7">
-        <v>28.33</v>
-      </c>
-      <c r="E65" s="8">
-        <v>-0.13</v>
+        <v>34.71</v>
+      </c>
+      <c r="E65" s="9">
+        <v>-5.4</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B66" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C66" s="7">
-        <v>42.14</v>
+        <v>41.44</v>
       </c>
       <c r="D66" s="7">
-        <v>40.11</v>
+        <v>44.73</v>
       </c>
       <c r="E66" s="8">
-        <v>-2.03</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B67" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C67" s="7">
-        <v>46.4</v>
+        <v>30.45</v>
       </c>
       <c r="D67" s="7">
-        <v>41.44</v>
+        <v>33.38</v>
       </c>
       <c r="E67" s="8">
-        <v>-4.96</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C68" s="7">
-        <v>36.84</v>
+        <v>37.66</v>
       </c>
       <c r="D68" s="7">
-        <v>30.45</v>
+        <v>43.75</v>
       </c>
       <c r="E68" s="8">
-        <v>-6.39</v>
+        <v>6.09</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B69" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C69" s="7">
-        <v>41</v>
+        <v>65.33</v>
       </c>
       <c r="D69" s="7">
-        <v>37.66</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="E69" s="8">
-        <v>-3.34</v>
+        <v>4.82</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B70" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C70" s="7">
-        <v>75.28</v>
+        <v>30.85</v>
       </c>
       <c r="D70" s="7">
-        <v>65.33</v>
-      </c>
-      <c r="E70" s="8">
-        <v>-9.949999999999999</v>
+        <v>29.23</v>
+      </c>
+      <c r="E70" s="9">
+        <v>-1.62</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B71" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C71" s="7">
-        <v>32.14</v>
+        <v>35.92</v>
       </c>
       <c r="D71" s="7">
-        <v>30.85</v>
+        <v>36.8</v>
       </c>
       <c r="E71" s="8">
-        <v>-1.29</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B72" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C72" s="7">
-        <v>41.19</v>
+        <v>59.43</v>
       </c>
       <c r="D72" s="7">
-        <v>35.92</v>
-      </c>
-      <c r="E72" s="8">
-        <v>-5.27</v>
+        <v>55.44</v>
+      </c>
+      <c r="E72" s="9">
+        <v>-3.99</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="6" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C73" s="7">
-        <v>57.54</v>
+        <v>-39.5</v>
       </c>
       <c r="D73" s="7">
-        <v>59.43</v>
+        <v>-55.81</v>
       </c>
       <c r="E73" s="9">
-        <v>1.89</v>
+        <v>-16.31</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B74" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C74" s="7">
-        <v>-30.4</v>
+        <v>0.93</v>
       </c>
       <c r="D74" s="7">
-        <v>-39.5</v>
+        <v>55.3</v>
       </c>
       <c r="E74" s="8">
-        <v>-9.1</v>
+        <v>54.37</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B75" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C75" s="7">
-        <v>81.48999999999999</v>
+        <v>-39.82</v>
       </c>
       <c r="D75" s="7">
-        <v>0.93</v>
-      </c>
-      <c r="E75" s="8">
-        <v>-80.56</v>
+        <v>-44.01</v>
+      </c>
+      <c r="E75" s="9">
+        <v>-4.19</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C76" s="7">
-        <v>-36.46</v>
+        <v>-17.99</v>
       </c>
       <c r="D76" s="7">
-        <v>-39.82</v>
-      </c>
-      <c r="E76" s="8">
-        <v>-3.36</v>
+        <v>-41.47</v>
+      </c>
+      <c r="E76" s="9">
+        <v>-23.48</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B77" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C77" s="7">
-        <v>-15.16</v>
+        <v>-31.7</v>
       </c>
       <c r="D77" s="7">
-        <v>-17.99</v>
-      </c>
-      <c r="E77" s="8">
-        <v>-2.83</v>
+        <v>-37.04</v>
+      </c>
+      <c r="E77" s="9">
+        <v>-5.34</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B78" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C78" s="7">
-        <v>-28.42</v>
+        <v>-3.7</v>
       </c>
       <c r="D78" s="7">
-        <v>-31.7</v>
+        <v>104.96</v>
       </c>
       <c r="E78" s="8">
-        <v>-3.28</v>
+        <v>108.66</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B79" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C79" s="7">
-        <v>73.02</v>
+        <v>7.18</v>
       </c>
       <c r="D79" s="7">
-        <v>-3.7</v>
-      </c>
-      <c r="E79" s="8">
-        <v>-76.72</v>
+        <v>-19.98</v>
+      </c>
+      <c r="E79" s="9">
+        <v>-27.16</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B80" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C80" s="7">
-        <v>13.11</v>
+        <v>107.68</v>
       </c>
       <c r="D80" s="7">
-        <v>7.18</v>
-      </c>
-      <c r="E80" s="8">
-        <v>-5.93</v>
+        <v>21.59</v>
+      </c>
+      <c r="E80" s="9">
+        <v>-86.09</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B81" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C81" s="7">
-        <v>193.19</v>
+        <v>-8.02</v>
       </c>
       <c r="D81" s="7">
-        <v>107.68</v>
-      </c>
-      <c r="E81" s="8">
-        <v>-85.51000000000001</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B82" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C82" s="7">
-        <v>12.68</v>
-      </c>
-      <c r="D82" s="7">
-        <v>-8.02</v>
-      </c>
-      <c r="E82" s="8">
-        <v>-20.7</v>
+        <v>-40.6</v>
+      </c>
+      <c r="E81" s="9">
+        <v>-32.58</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3524,28 +3495,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="F1" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="G1" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="H1" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="I1" s="10" t="s">
         <v>79</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3559,16 +3530,16 @@
         <v>9</v>
       </c>
       <c r="D2" s="12">
-        <v>41.1</v>
+        <v>41.5</v>
       </c>
       <c r="E2" s="12">
         <v>40</v>
       </c>
       <c r="F2" s="12">
-        <v>-3.8</v>
+        <v>-3.9</v>
       </c>
       <c r="G2" s="12">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="H2" s="12">
         <v>55.4</v>
@@ -3705,31 +3676,31 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="15">
-        <v>0.346</v>
+        <v>0.3497999999999999</v>
       </c>
       <c r="B2" s="15">
-        <v>0.3442</v>
+        <v>0.3446</v>
       </c>
       <c r="C2" s="15">
-        <v>0.1988</v>
+        <v>0.1991</v>
       </c>
       <c r="D2" s="15">
-        <v>0.195</v>
+        <v>0.1917</v>
       </c>
       <c r="E2" s="15">
-        <v>0.1222</v>
+        <v>0.1224</v>
       </c>
       <c r="F2" s="15">
-        <v>0.0678</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="G2" s="15">
-        <v>0.0576</v>
+        <v>0.0555</v>
       </c>
       <c r="H2" s="15">
-        <v>-0.0034</v>
+        <v>-0.0152</v>
       </c>
       <c r="I2" s="15">
-        <v>-0.1189</v>
+        <v>-0.1149</v>
       </c>
     </row>
   </sheetData>

--- a/MAHINDRA_GROUP_Technical_Metrics.xlsx
+++ b/MAHINDRA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="90">
   <si>
     <t>Symbol</t>
   </si>
@@ -193,34 +193,64 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>Near 52W High</t>
-  </si>
-  <si>
-    <t>-2.3% → 0.0%</t>
-  </si>
-  <si>
-    <t>🟢 BREAKOUT WATCH</t>
-  </si>
-  <si>
-    <t>-2.3%</t>
-  </si>
-  <si>
-    <t>0.0%</t>
-  </si>
-  <si>
-    <t>RSI Overbought Entry</t>
-  </si>
-  <si>
-    <t>65.3 → 70.2</t>
-  </si>
-  <si>
-    <t>⚠️ CAUTION</t>
-  </si>
-  <si>
-    <t>65.3</t>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>43.8 → 51.4</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>43.8</t>
+  </si>
+  <si>
+    <t>51.4</t>
+  </si>
+  <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>29.2 → 32.2</t>
+  </si>
+  <si>
+    <t>29.2</t>
+  </si>
+  <si>
+    <t>32.2</t>
+  </si>
+  <si>
+    <t>RSI Overbought Exit</t>
+  </si>
+  <si>
+    <t>70.2 → 63.1</t>
+  </si>
+  <si>
+    <t>🔵 COOLING</t>
   </si>
   <si>
     <t>70.2</t>
+  </si>
+  <si>
+    <t>63.1</t>
+  </si>
+  <si>
+    <t>Yes → No</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
+  </si>
+  <si>
+    <t>55.4 → 49.5</t>
+  </si>
+  <si>
+    <t>55.4</t>
+  </si>
+  <si>
+    <t>49.5</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -313,7 +343,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF1F4E79"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -359,7 +389,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -435,7 +465,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -444,10 +474,11 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -959,58 +990,58 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>385</v>
+        <v>383.95</v>
       </c>
       <c r="D2">
-        <v>-1.5</v>
+        <v>-0.27</v>
       </c>
       <c r="E2">
         <v>490.2</v>
       </c>
       <c r="F2">
-        <v>381.66</v>
+        <v>381.86</v>
       </c>
       <c r="G2">
-        <v>-21.46</v>
+        <v>-21.67</v>
       </c>
       <c r="H2">
-        <v>0.88</v>
+        <v>0.55</v>
       </c>
       <c r="I2">
-        <v>-3.02</v>
+        <v>-2.67</v>
       </c>
       <c r="J2">
-        <v>-6.23</v>
+        <v>-7.49</v>
       </c>
       <c r="K2">
-        <v>-15.55</v>
+        <v>-15.06</v>
       </c>
       <c r="L2">
-        <v>1.53</v>
+        <v>0.6</v>
       </c>
       <c r="M2">
-        <v>12.24</v>
+        <v>12.46</v>
       </c>
       <c r="N2">
         <v>34</v>
       </c>
       <c r="O2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P2">
-        <v>390.27</v>
+        <v>388.16</v>
       </c>
       <c r="Q2">
-        <v>402.2</v>
+        <v>400.88</v>
       </c>
       <c r="R2">
-        <v>430.17</v>
+        <v>428.45</v>
       </c>
       <c r="S2">
-        <v>436.47</v>
+        <v>436.26</v>
       </c>
       <c r="T2">
-        <v>-11.79</v>
+        <v>-11.99</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1025,43 +1056,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>24.93</v>
+        <v>24.37</v>
       </c>
       <c r="Z2">
-        <v>-10.9</v>
+        <v>-11.06</v>
       </c>
       <c r="AA2">
-        <v>-10.78</v>
+        <v>-10.84</v>
       </c>
       <c r="AB2">
-        <v>-0.12</v>
+        <v>-0.22</v>
       </c>
       <c r="AC2">
-        <v>9.720000000000001</v>
+        <v>4.67</v>
       </c>
       <c r="AD2">
-        <v>8.17</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="AE2">
-        <v>8.640000000000001</v>
+        <v>8.51</v>
       </c>
       <c r="AF2">
-        <v>-55.81</v>
+        <v>-24.05</v>
       </c>
       <c r="AG2">
-        <v>419.43</v>
+        <v>419.47</v>
       </c>
       <c r="AH2">
-        <v>384.97</v>
+        <v>382.29</v>
       </c>
       <c r="AI2">
-        <v>413.86</v>
+        <v>411.17</v>
       </c>
       <c r="AJ2" t="s">
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>56.93</v>
+        <v>59.8</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1072,10 +1103,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>3190</v>
+        <v>3150</v>
       </c>
       <c r="D3">
-        <v>-2.12</v>
+        <v>-1.25</v>
       </c>
       <c r="E3">
         <v>3802.4</v>
@@ -1084,25 +1115,25 @@
         <v>2931.1</v>
       </c>
       <c r="G3">
-        <v>-16.11</v>
+        <v>-17.16</v>
       </c>
       <c r="H3">
-        <v>8.83</v>
+        <v>7.47</v>
       </c>
       <c r="I3">
-        <v>-6.13</v>
+        <v>-5.41</v>
       </c>
       <c r="J3">
-        <v>-7.08</v>
+        <v>-8.84</v>
       </c>
       <c r="K3">
-        <v>5.77</v>
+        <v>3.6</v>
       </c>
       <c r="L3">
-        <v>-0.3</v>
+        <v>-4.99</v>
       </c>
       <c r="M3">
-        <v>34.46</v>
+        <v>34.21</v>
       </c>
       <c r="N3">
         <v>45</v>
@@ -1111,19 +1142,19 @@
         <v>51</v>
       </c>
       <c r="P3">
-        <v>3279</v>
+        <v>3243</v>
       </c>
       <c r="Q3">
-        <v>3392.97</v>
+        <v>3380.17</v>
       </c>
       <c r="R3">
-        <v>3273.8</v>
+        <v>3275.51</v>
       </c>
       <c r="S3">
-        <v>3339.27</v>
+        <v>3336.34</v>
       </c>
       <c r="T3">
-        <v>-4.47</v>
+        <v>-5.59</v>
       </c>
       <c r="U3" t="s">
         <v>48</v>
@@ -1138,43 +1169,43 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>34.71</v>
+        <v>32.01</v>
       </c>
       <c r="Z3">
-        <v>-6.65</v>
+        <v>-20.54</v>
       </c>
       <c r="AA3">
-        <v>27.23</v>
+        <v>17.68</v>
       </c>
       <c r="AB3">
-        <v>-33.89</v>
+        <v>-38.22</v>
       </c>
       <c r="AC3">
         <v>0</v>
       </c>
       <c r="AD3">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="AE3">
-        <v>73.95999999999999</v>
+        <v>72.95999999999999</v>
       </c>
       <c r="AF3">
-        <v>55.3</v>
+        <v>-2.75</v>
       </c>
       <c r="AG3">
-        <v>3551.33</v>
+        <v>3571.95</v>
       </c>
       <c r="AH3">
-        <v>3234.61</v>
+        <v>3188.39</v>
       </c>
       <c r="AI3">
-        <v>3407.93</v>
+        <v>3398.89</v>
       </c>
       <c r="AJ3" t="s">
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>39.05</v>
+        <v>43.71</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1185,58 +1216,58 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>368.85</v>
+        <v>376.05</v>
       </c>
       <c r="D4">
-        <v>1.22</v>
+        <v>1.95</v>
       </c>
       <c r="E4">
         <v>412.3</v>
       </c>
       <c r="F4">
-        <v>257.5</v>
+        <v>259.7</v>
       </c>
       <c r="G4">
-        <v>-10.54</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="H4">
-        <v>43.24</v>
+        <v>44.8</v>
       </c>
       <c r="I4">
-        <v>-4.28</v>
+        <v>-1.9</v>
       </c>
       <c r="J4">
-        <v>-7.46</v>
+        <v>-5.61</v>
       </c>
       <c r="K4">
-        <v>27.61</v>
+        <v>29.74</v>
       </c>
       <c r="L4">
-        <v>45.25</v>
+        <v>46.04</v>
       </c>
       <c r="M4">
-        <v>19.17</v>
+        <v>19.8</v>
       </c>
       <c r="N4">
         <v>99</v>
       </c>
       <c r="O4">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P4">
-        <v>373.24</v>
+        <v>371.78</v>
       </c>
       <c r="Q4">
-        <v>386.56</v>
+        <v>385.92</v>
       </c>
       <c r="R4">
-        <v>363.19</v>
+        <v>364.49</v>
       </c>
       <c r="S4">
-        <v>343.61</v>
+        <v>343.92</v>
       </c>
       <c r="T4">
-        <v>7.35</v>
+        <v>9.34</v>
       </c>
       <c r="U4" t="s">
         <v>48</v>
@@ -1251,34 +1282,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>44.73</v>
+        <v>49.66</v>
       </c>
       <c r="Z4">
-        <v>0.92</v>
+        <v>0.7</v>
       </c>
       <c r="AA4">
-        <v>5.53</v>
+        <v>4.56</v>
       </c>
       <c r="AB4">
-        <v>-4.61</v>
+        <v>-3.86</v>
       </c>
       <c r="AC4">
-        <v>6.73</v>
+        <v>24.22</v>
       </c>
       <c r="AD4">
-        <v>3.69</v>
+        <v>10.32</v>
       </c>
       <c r="AE4">
-        <v>12.04</v>
+        <v>12.02</v>
       </c>
       <c r="AF4">
-        <v>-44.01</v>
+        <v>-7.05</v>
       </c>
       <c r="AG4">
-        <v>410.56</v>
+        <v>410.34</v>
       </c>
       <c r="AH4">
-        <v>362.56</v>
+        <v>361.5</v>
       </c>
       <c r="AI4">
         <v>357.72</v>
@@ -1287,7 +1318,7 @@
         <v>50</v>
       </c>
       <c r="AK4">
-        <v>27.78</v>
+        <v>25.77</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1298,10 +1329,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>359</v>
+        <v>363.1</v>
       </c>
       <c r="D5">
-        <v>0.57</v>
+        <v>1.14</v>
       </c>
       <c r="E5">
         <v>421.7</v>
@@ -1310,88 +1341,88 @@
         <v>294.25</v>
       </c>
       <c r="G5">
-        <v>-14.87</v>
+        <v>-13.9</v>
       </c>
       <c r="H5">
-        <v>22.01</v>
+        <v>23.4</v>
       </c>
       <c r="I5">
-        <v>-3.3</v>
+        <v>-1.51</v>
       </c>
       <c r="J5">
-        <v>-9.699999999999999</v>
+        <v>-5.16</v>
       </c>
       <c r="K5">
-        <v>6.72</v>
+        <v>7.27</v>
       </c>
       <c r="L5">
-        <v>2.59</v>
+        <v>4</v>
       </c>
       <c r="M5">
-        <v>6.95</v>
+        <v>6.85</v>
       </c>
       <c r="N5">
         <v>55</v>
       </c>
       <c r="O5">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="P5">
-        <v>363.56</v>
+        <v>362.45</v>
       </c>
       <c r="Q5">
-        <v>377.01</v>
+        <v>375.84</v>
       </c>
       <c r="R5">
-        <v>376.13</v>
+        <v>376.17</v>
       </c>
       <c r="S5">
-        <v>363.64</v>
+        <v>363.46</v>
       </c>
       <c r="T5">
-        <v>-1.28</v>
+        <v>-0.1</v>
       </c>
       <c r="U5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V5" t="s">
         <v>48</v>
       </c>
       <c r="W5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="X5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y5">
-        <v>33.38</v>
+        <v>38.93</v>
       </c>
       <c r="Z5">
-        <v>-4.17</v>
+        <v>-4.4</v>
       </c>
       <c r="AA5">
-        <v>-1.09</v>
+        <v>-1.75</v>
       </c>
       <c r="AB5">
-        <v>-3.09</v>
+        <v>-2.65</v>
       </c>
       <c r="AC5">
-        <v>3.6</v>
+        <v>14.01</v>
       </c>
       <c r="AD5">
-        <v>1.2</v>
+        <v>5.87</v>
       </c>
       <c r="AE5">
-        <v>10.06</v>
+        <v>9.92</v>
       </c>
       <c r="AF5">
-        <v>-41.47</v>
+        <v>-43.49</v>
       </c>
       <c r="AG5">
-        <v>395.73</v>
+        <v>395</v>
       </c>
       <c r="AH5">
-        <v>358.29</v>
+        <v>356.69</v>
       </c>
       <c r="AI5">
         <v>386.7</v>
@@ -1400,7 +1431,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>42.13</v>
+        <v>43.38</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1411,10 +1442,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>392.45</v>
+        <v>400.3</v>
       </c>
       <c r="D6">
-        <v>1.36</v>
+        <v>2</v>
       </c>
       <c r="E6">
         <v>442.7</v>
@@ -1423,46 +1454,46 @@
         <v>279.55</v>
       </c>
       <c r="G6">
-        <v>-11.35</v>
+        <v>-9.58</v>
       </c>
       <c r="H6">
-        <v>40.39</v>
+        <v>43.19</v>
       </c>
       <c r="I6">
-        <v>-1.74</v>
+        <v>2.22</v>
       </c>
       <c r="J6">
-        <v>-6.78</v>
+        <v>-3.19</v>
       </c>
       <c r="K6">
-        <v>13.1</v>
+        <v>14.72</v>
       </c>
       <c r="L6">
-        <v>23.86</v>
+        <v>26.5</v>
       </c>
       <c r="M6">
-        <v>-11.49</v>
+        <v>-10.8</v>
       </c>
       <c r="N6">
         <v>88</v>
       </c>
       <c r="O6">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="P6">
-        <v>391.09</v>
+        <v>392.83</v>
       </c>
       <c r="Q6">
-        <v>401.88</v>
+        <v>401.2</v>
       </c>
       <c r="R6">
-        <v>397.38</v>
+        <v>397.84</v>
       </c>
       <c r="S6">
-        <v>367.23</v>
+        <v>367.55</v>
       </c>
       <c r="T6">
-        <v>6.87</v>
+        <v>8.91</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1477,34 +1508,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>43.75</v>
+        <v>51.39</v>
       </c>
       <c r="Z6">
-        <v>-2.23</v>
+        <v>-1.76</v>
       </c>
       <c r="AA6">
-        <v>0.25</v>
+        <v>-0.16</v>
       </c>
       <c r="AB6">
-        <v>-2.47</v>
+        <v>-1.61</v>
       </c>
       <c r="AC6">
-        <v>13.15</v>
+        <v>41.16</v>
       </c>
       <c r="AD6">
-        <v>6.63</v>
+        <v>19.22</v>
       </c>
       <c r="AE6">
-        <v>11.64</v>
+        <v>11.65</v>
       </c>
       <c r="AF6">
-        <v>-37.04</v>
+        <v>-36.37</v>
       </c>
       <c r="AG6">
-        <v>416.56</v>
+        <v>414.75</v>
       </c>
       <c r="AH6">
-        <v>387.19</v>
+        <v>387.64</v>
       </c>
       <c r="AI6">
         <v>372.35</v>
@@ -1513,7 +1544,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>20.76</v>
+        <v>19.54</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1524,10 +1555,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>665.05</v>
+        <v>653.5</v>
       </c>
       <c r="D7">
-        <v>2.38</v>
+        <v>-1.74</v>
       </c>
       <c r="E7">
         <v>665.05</v>
@@ -1536,46 +1567,46 @@
         <v>506.45</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>-1.74</v>
       </c>
       <c r="H7">
-        <v>31.32</v>
+        <v>29.04</v>
       </c>
       <c r="I7">
-        <v>4.48</v>
+        <v>1.78</v>
       </c>
       <c r="J7">
-        <v>14.84</v>
+        <v>12.17</v>
       </c>
       <c r="K7">
-        <v>8.16</v>
+        <v>4.74</v>
       </c>
       <c r="L7">
-        <v>3.68</v>
+        <v>0.75</v>
       </c>
       <c r="M7">
-        <v>34.98</v>
+        <v>34.08</v>
       </c>
       <c r="N7">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="O7">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="P7">
-        <v>656.3200000000001</v>
+        <v>658.61</v>
       </c>
       <c r="Q7">
-        <v>625.09</v>
+        <v>628.5700000000001</v>
       </c>
       <c r="R7">
-        <v>603.96</v>
+        <v>604.05</v>
       </c>
       <c r="S7">
-        <v>586.1799999999999</v>
+        <v>586.63</v>
       </c>
       <c r="T7">
-        <v>13.45</v>
+        <v>11.4</v>
       </c>
       <c r="U7" t="s">
         <v>48</v>
@@ -1590,43 +1621,43 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>70.15000000000001</v>
+        <v>63.09</v>
       </c>
       <c r="Z7">
-        <v>17.13</v>
+        <v>16.83</v>
       </c>
       <c r="AA7">
-        <v>12.92</v>
+        <v>13.7</v>
       </c>
       <c r="AB7">
-        <v>4.2</v>
+        <v>3.12</v>
       </c>
       <c r="AC7">
-        <v>73.03</v>
+        <v>51.22</v>
       </c>
       <c r="AD7">
-        <v>85.08</v>
+        <v>68.81999999999999</v>
       </c>
       <c r="AE7">
-        <v>18.78</v>
+        <v>19.77</v>
       </c>
       <c r="AF7">
-        <v>104.96</v>
+        <v>91.08</v>
       </c>
       <c r="AG7">
-        <v>672.77</v>
+        <v>673.66</v>
       </c>
       <c r="AH7">
-        <v>577.41</v>
+        <v>583.48</v>
       </c>
       <c r="AI7">
-        <v>605.9</v>
+        <v>606.8</v>
       </c>
       <c r="AJ7" t="s">
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>67.45999999999999</v>
+        <v>68.39</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1637,10 +1668,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>206.59</v>
+        <v>207.91</v>
       </c>
       <c r="D8">
-        <v>-0.83</v>
+        <v>0.64</v>
       </c>
       <c r="E8">
         <v>362.05</v>
@@ -1649,46 +1680,46 @@
         <v>206.59</v>
       </c>
       <c r="G8">
-        <v>-42.94</v>
+        <v>-42.57</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>0.64</v>
       </c>
       <c r="I8">
-        <v>-5.32</v>
+        <v>-1.57</v>
       </c>
       <c r="J8">
-        <v>-9.380000000000001</v>
+        <v>-10.86</v>
       </c>
       <c r="K8">
-        <v>-4.83</v>
+        <v>-3.53</v>
       </c>
       <c r="L8">
-        <v>-40.96</v>
+        <v>-40.53</v>
       </c>
       <c r="M8">
-        <v>-1.52</v>
+        <v>-1.5</v>
       </c>
       <c r="N8">
         <v>12</v>
       </c>
       <c r="O8">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P8">
-        <v>209.43</v>
+        <v>208.77</v>
       </c>
       <c r="Q8">
-        <v>220.39</v>
+        <v>219.23</v>
       </c>
       <c r="R8">
-        <v>225.04</v>
+        <v>224.41</v>
       </c>
       <c r="S8">
-        <v>261.39</v>
+        <v>260.85</v>
       </c>
       <c r="T8">
-        <v>-20.97</v>
+        <v>-20.29</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1703,43 +1734,43 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>29.23</v>
+        <v>32.17</v>
       </c>
       <c r="Z8">
-        <v>-4.45</v>
+        <v>-4.65</v>
       </c>
       <c r="AA8">
-        <v>-2.91</v>
+        <v>-3.26</v>
       </c>
       <c r="AB8">
-        <v>-1.54</v>
+        <v>-1.4</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="AD8">
-        <v>0.39</v>
+        <v>1.72</v>
       </c>
       <c r="AE8">
-        <v>6.24</v>
+        <v>5.97</v>
       </c>
       <c r="AF8">
-        <v>-19.98</v>
+        <v>-28.27</v>
       </c>
       <c r="AG8">
-        <v>235.33</v>
+        <v>234.3</v>
       </c>
       <c r="AH8">
-        <v>205.44</v>
+        <v>204.17</v>
       </c>
       <c r="AI8">
-        <v>226.32</v>
+        <v>225.7</v>
       </c>
       <c r="AJ8" t="s">
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>39.77</v>
+        <v>42.85</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1750,10 +1781,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>3540.9</v>
+        <v>3554.7</v>
       </c>
       <c r="D9">
-        <v>0.09</v>
+        <v>0.39</v>
       </c>
       <c r="E9">
         <v>4497.5</v>
@@ -1762,46 +1793,46 @@
         <v>3308.9</v>
       </c>
       <c r="G9">
-        <v>-21.27</v>
+        <v>-20.96</v>
       </c>
       <c r="H9">
-        <v>7.01</v>
+        <v>7.43</v>
       </c>
       <c r="I9">
-        <v>-0.23</v>
+        <v>0.18</v>
       </c>
       <c r="J9">
-        <v>-1.6</v>
+        <v>-1.5</v>
       </c>
       <c r="K9">
-        <v>-6.1</v>
+        <v>-4.79</v>
       </c>
       <c r="L9">
-        <v>-11.73</v>
+        <v>-13.46</v>
       </c>
       <c r="M9">
-        <v>19.91</v>
+        <v>19.96</v>
       </c>
       <c r="N9">
         <v>23</v>
       </c>
       <c r="O9">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P9">
-        <v>3548.2</v>
+        <v>3549.48</v>
       </c>
       <c r="Q9">
-        <v>3582.78</v>
+        <v>3580.73</v>
       </c>
       <c r="R9">
-        <v>3680.45</v>
+        <v>3672.6</v>
       </c>
       <c r="S9">
-        <v>3691.52</v>
+        <v>3689.5</v>
       </c>
       <c r="T9">
-        <v>-4.08</v>
+        <v>-3.65</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1816,34 +1847,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>36.8</v>
+        <v>40.6</v>
       </c>
       <c r="Z9">
-        <v>-32.28</v>
+        <v>-30.57</v>
       </c>
       <c r="AA9">
-        <v>-33.51</v>
+        <v>-32.92</v>
       </c>
       <c r="AB9">
-        <v>1.23</v>
+        <v>2.35</v>
       </c>
       <c r="AC9">
-        <v>29.28</v>
+        <v>27.73</v>
       </c>
       <c r="AD9">
-        <v>23.35</v>
+        <v>26.53</v>
       </c>
       <c r="AE9">
-        <v>52.37</v>
+        <v>52.49</v>
       </c>
       <c r="AF9">
-        <v>21.59</v>
+        <v>-53.17</v>
       </c>
       <c r="AG9">
-        <v>3646.31</v>
+        <v>3645.14</v>
       </c>
       <c r="AH9">
-        <v>3519.26</v>
+        <v>3516.32</v>
       </c>
       <c r="AI9">
         <v>3684.57</v>
@@ -1852,7 +1883,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>17.74</v>
+        <v>20.16</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1863,10 +1894,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>1623</v>
+        <v>1598</v>
       </c>
       <c r="D10">
-        <v>-0.92</v>
+        <v>-1.54</v>
       </c>
       <c r="E10">
         <v>1768.4</v>
@@ -1875,46 +1906,46 @@
         <v>1326.2</v>
       </c>
       <c r="G10">
-        <v>-8.220000000000001</v>
+        <v>-9.640000000000001</v>
       </c>
       <c r="H10">
-        <v>22.38</v>
+        <v>20.49</v>
       </c>
       <c r="I10">
-        <v>3.31</v>
+        <v>0.82</v>
       </c>
       <c r="J10">
-        <v>-1.55</v>
+        <v>-3.15</v>
       </c>
       <c r="K10">
-        <v>9.119999999999999</v>
+        <v>7.72</v>
       </c>
       <c r="L10">
-        <v>10.71</v>
+        <v>7.26</v>
       </c>
       <c r="M10">
-        <v>5.55</v>
+        <v>5.16</v>
       </c>
       <c r="N10">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="O10">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="P10">
-        <v>1622.98</v>
+        <v>1625.58</v>
       </c>
       <c r="Q10">
-        <v>1614.24</v>
+        <v>1612.53</v>
       </c>
       <c r="R10">
-        <v>1557.3</v>
+        <v>1560.03</v>
       </c>
       <c r="S10">
-        <v>1514.65</v>
+        <v>1515.38</v>
       </c>
       <c r="T10">
-        <v>7.15</v>
+        <v>5.45</v>
       </c>
       <c r="U10" t="s">
         <v>48</v>
@@ -1929,34 +1960,34 @@
         <v>3</v>
       </c>
       <c r="Y10">
-        <v>55.44</v>
+        <v>49.49</v>
       </c>
       <c r="Z10">
-        <v>11.96</v>
+        <v>9.84</v>
       </c>
       <c r="AA10">
-        <v>13.26</v>
+        <v>12.58</v>
       </c>
       <c r="AB10">
-        <v>-1.3</v>
+        <v>-2.74</v>
       </c>
       <c r="AC10">
-        <v>72.17</v>
+        <v>58.49</v>
       </c>
       <c r="AD10">
-        <v>67.81999999999999</v>
+        <v>68.86</v>
       </c>
       <c r="AE10">
-        <v>36.85</v>
+        <v>36.61</v>
       </c>
       <c r="AF10">
-        <v>-40.6</v>
+        <v>-34.57</v>
       </c>
       <c r="AG10">
-        <v>1662.83</v>
+        <v>1660.87</v>
       </c>
       <c r="AH10">
-        <v>1565.64</v>
+        <v>1564.18</v>
       </c>
       <c r="AI10">
         <v>1527.05</v>
@@ -1965,7 +1996,7 @@
         <v>50</v>
       </c>
       <c r="AK10">
-        <v>31.37</v>
+        <v>27.22</v>
       </c>
     </row>
   </sheetData>
@@ -2106,7 +2137,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:F85"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2146,7 +2177,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2165,1313 +2196,1393 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="F4" s="5" t="s">
+      <c r="B5" s="5" t="s">
         <v>66</v>
       </c>
+      <c r="C5" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
+      <c r="A6" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E7" s="3" t="s">
+      <c r="A7" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>71</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B12" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="7">
-        <v>-6.86</v>
-      </c>
-      <c r="D8" s="7">
+      <c r="C12" s="8">
         <v>-6.23</v>
       </c>
-      <c r="E8" s="8">
-        <v>0.63</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="6" t="s">
+      <c r="D12" s="8">
+        <v>-7.49</v>
+      </c>
+      <c r="E12" s="9">
+        <v>-1.26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B13" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="7">
-        <v>-4.95</v>
-      </c>
-      <c r="D9" s="7">
+      <c r="C13" s="8">
         <v>-7.08</v>
       </c>
-      <c r="E9" s="9">
-        <v>-2.13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+      <c r="D13" s="8">
+        <v>-8.84</v>
+      </c>
+      <c r="E13" s="9">
+        <v>-1.76</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B14" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="7">
-        <v>-10.14</v>
-      </c>
-      <c r="D10" s="7">
+      <c r="C14" s="8">
         <v>-7.46</v>
       </c>
-      <c r="E10" s="8">
-        <v>2.68</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="D14" s="8">
+        <v>-5.61</v>
+      </c>
+      <c r="E14" s="10">
+        <v>1.85</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B15" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="7">
-        <v>-10.37</v>
-      </c>
-      <c r="D11" s="7">
+      <c r="C15" s="8">
         <v>-9.699999999999999</v>
       </c>
-      <c r="E11" s="8">
+      <c r="D15" s="8">
+        <v>-5.16</v>
+      </c>
+      <c r="E15" s="10">
+        <v>4.54</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="8">
+        <v>-6.78</v>
+      </c>
+      <c r="D16" s="8">
+        <v>-3.19</v>
+      </c>
+      <c r="E16" s="10">
+        <v>3.59</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="8">
+        <v>14.84</v>
+      </c>
+      <c r="D17" s="8">
+        <v>12.17</v>
+      </c>
+      <c r="E17" s="9">
+        <v>-2.67</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="8">
+        <v>-9.380000000000001</v>
+      </c>
+      <c r="D18" s="8">
+        <v>-10.86</v>
+      </c>
+      <c r="E18" s="9">
+        <v>-1.48</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="8">
+        <v>-1.6</v>
+      </c>
+      <c r="D19" s="8">
+        <v>-1.5</v>
+      </c>
+      <c r="E19" s="10">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" s="8">
+        <v>-1.55</v>
+      </c>
+      <c r="D20" s="8">
+        <v>-3.15</v>
+      </c>
+      <c r="E20" s="9">
+        <v>-1.6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="8">
+        <v>-3.02</v>
+      </c>
+      <c r="D21" s="8">
+        <v>-2.67</v>
+      </c>
+      <c r="E21" s="10">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="8">
+        <v>-6.13</v>
+      </c>
+      <c r="D22" s="8">
+        <v>-5.41</v>
+      </c>
+      <c r="E22" s="10">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="8">
+        <v>-4.28</v>
+      </c>
+      <c r="D23" s="8">
+        <v>-1.9</v>
+      </c>
+      <c r="E23" s="10">
+        <v>2.38</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="8">
+        <v>-3.3</v>
+      </c>
+      <c r="D24" s="8">
+        <v>-1.51</v>
+      </c>
+      <c r="E24" s="10">
+        <v>1.79</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="8">
+        <v>-1.74</v>
+      </c>
+      <c r="D25" s="8">
+        <v>2.22</v>
+      </c>
+      <c r="E25" s="10">
+        <v>3.96</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="8">
+        <v>4.48</v>
+      </c>
+      <c r="D26" s="8">
+        <v>1.78</v>
+      </c>
+      <c r="E26" s="9">
+        <v>-2.7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="8">
+        <v>-5.32</v>
+      </c>
+      <c r="D27" s="8">
+        <v>-1.57</v>
+      </c>
+      <c r="E27" s="10">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="8">
+        <v>-0.23</v>
+      </c>
+      <c r="D28" s="8">
+        <v>0.18</v>
+      </c>
+      <c r="E28" s="10">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="8">
+        <v>3.31</v>
+      </c>
+      <c r="D29" s="8">
+        <v>0.82</v>
+      </c>
+      <c r="E29" s="9">
+        <v>-2.49</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="8">
+        <v>1.53</v>
+      </c>
+      <c r="D30" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="E30" s="9">
+        <v>-0.93</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="8">
+        <v>-0.3</v>
+      </c>
+      <c r="D31" s="8">
+        <v>-4.99</v>
+      </c>
+      <c r="E31" s="9">
+        <v>-4.69</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="8">
+        <v>45.25</v>
+      </c>
+      <c r="D32" s="8">
+        <v>46.04</v>
+      </c>
+      <c r="E32" s="10">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="8">
+        <v>2.59</v>
+      </c>
+      <c r="D33" s="8">
+        <v>4</v>
+      </c>
+      <c r="E33" s="10">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="8">
+        <v>23.86</v>
+      </c>
+      <c r="D34" s="8">
+        <v>26.5</v>
+      </c>
+      <c r="E34" s="10">
+        <v>2.64</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" s="8">
+        <v>3.68</v>
+      </c>
+      <c r="D35" s="8">
+        <v>0.75</v>
+      </c>
+      <c r="E35" s="9">
+        <v>-2.93</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36" s="8">
+        <v>-40.96</v>
+      </c>
+      <c r="D36" s="8">
+        <v>-40.53</v>
+      </c>
+      <c r="E36" s="10">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C37" s="8">
+        <v>-11.73</v>
+      </c>
+      <c r="D37" s="8">
+        <v>-13.46</v>
+      </c>
+      <c r="E37" s="9">
+        <v>-1.73</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C38" s="8">
+        <v>10.71</v>
+      </c>
+      <c r="D38" s="8">
+        <v>7.26</v>
+      </c>
+      <c r="E38" s="9">
+        <v>-3.45</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="8">
+        <v>-15.55</v>
+      </c>
+      <c r="D39" s="8">
+        <v>-15.06</v>
+      </c>
+      <c r="E39" s="10">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="8">
+        <v>5.77</v>
+      </c>
+      <c r="D40" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="E40" s="9">
+        <v>-2.17</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="8">
+        <v>27.61</v>
+      </c>
+      <c r="D41" s="8">
+        <v>29.74</v>
+      </c>
+      <c r="E41" s="10">
+        <v>2.13</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="8">
+        <v>6.72</v>
+      </c>
+      <c r="D42" s="8">
+        <v>7.27</v>
+      </c>
+      <c r="E42" s="10">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="8">
+        <v>13.1</v>
+      </c>
+      <c r="D43" s="8">
+        <v>14.72</v>
+      </c>
+      <c r="E43" s="10">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="8">
+        <v>8.16</v>
+      </c>
+      <c r="D44" s="8">
+        <v>4.74</v>
+      </c>
+      <c r="E44" s="9">
+        <v>-3.42</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="8">
+        <v>-4.83</v>
+      </c>
+      <c r="D45" s="8">
+        <v>-3.53</v>
+      </c>
+      <c r="E45" s="10">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" s="8">
+        <v>-6.1</v>
+      </c>
+      <c r="D46" s="8">
+        <v>-4.79</v>
+      </c>
+      <c r="E46" s="10">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" s="8">
+        <v>9.119999999999999</v>
+      </c>
+      <c r="D47" s="8">
+        <v>7.72</v>
+      </c>
+      <c r="E47" s="9">
+        <v>-1.4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="8">
+        <v>-21.46</v>
+      </c>
+      <c r="D48" s="8">
+        <v>-21.67</v>
+      </c>
+      <c r="E48" s="9">
+        <v>-0.21</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="8">
+        <v>-16.11</v>
+      </c>
+      <c r="D49" s="8">
+        <v>-17.16</v>
+      </c>
+      <c r="E49" s="9">
+        <v>-1.05</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="8">
+        <v>-10.54</v>
+      </c>
+      <c r="D50" s="8">
+        <v>-8.789999999999999</v>
+      </c>
+      <c r="E50" s="10">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="8">
+        <v>-14.87</v>
+      </c>
+      <c r="D51" s="8">
+        <v>-13.9</v>
+      </c>
+      <c r="E51" s="10">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="8">
+        <v>-11.35</v>
+      </c>
+      <c r="D52" s="8">
+        <v>-9.58</v>
+      </c>
+      <c r="E52" s="10">
+        <v>1.77</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53" s="8">
+        <v>0</v>
+      </c>
+      <c r="D53" s="8">
+        <v>-1.74</v>
+      </c>
+      <c r="E53" s="9">
+        <v>-1.74</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54" s="8">
+        <v>-42.94</v>
+      </c>
+      <c r="D54" s="8">
+        <v>-42.57</v>
+      </c>
+      <c r="E54" s="10">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C55" s="8">
+        <v>-21.27</v>
+      </c>
+      <c r="D55" s="8">
+        <v>-20.96</v>
+      </c>
+      <c r="E55" s="10">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C56" s="8">
+        <v>-8.220000000000001</v>
+      </c>
+      <c r="D56" s="8">
+        <v>-9.640000000000001</v>
+      </c>
+      <c r="E56" s="9">
+        <v>-1.42</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="8">
+        <v>385</v>
+      </c>
+      <c r="D57" s="8">
+        <v>383.95</v>
+      </c>
+      <c r="E57" s="9">
+        <v>-1.05</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="8">
+        <v>3190</v>
+      </c>
+      <c r="D58" s="8">
+        <v>3150</v>
+      </c>
+      <c r="E58" s="9">
+        <v>-40</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="8">
+        <v>368.85</v>
+      </c>
+      <c r="D59" s="8">
+        <v>376.05</v>
+      </c>
+      <c r="E59" s="10">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="8">
+        <v>359</v>
+      </c>
+      <c r="D60" s="8">
+        <v>363.1</v>
+      </c>
+      <c r="E60" s="10">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C61" s="8">
+        <v>392.45</v>
+      </c>
+      <c r="D61" s="8">
+        <v>400.3</v>
+      </c>
+      <c r="E61" s="10">
+        <v>7.85</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C62" s="8">
+        <v>665.05</v>
+      </c>
+      <c r="D62" s="8">
+        <v>653.5</v>
+      </c>
+      <c r="E62" s="9">
+        <v>-11.55</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C63" s="8">
+        <v>206.59</v>
+      </c>
+      <c r="D63" s="8">
+        <v>207.91</v>
+      </c>
+      <c r="E63" s="10">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C64" s="8">
+        <v>3540.9</v>
+      </c>
+      <c r="D64" s="8">
+        <v>3554.7</v>
+      </c>
+      <c r="E64" s="10">
+        <v>13.8</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B65" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C65" s="8">
+        <v>1623</v>
+      </c>
+      <c r="D65" s="8">
+        <v>1598</v>
+      </c>
+      <c r="E65" s="9">
+        <v>-25</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C66" s="8">
+        <v>77</v>
+      </c>
+      <c r="D66" s="8">
+        <v>66</v>
+      </c>
+      <c r="E66" s="9">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C67" s="8">
+        <v>66</v>
+      </c>
+      <c r="D67" s="8">
+        <v>77</v>
+      </c>
+      <c r="E67" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="8">
+        <v>24.93</v>
+      </c>
+      <c r="D68" s="8">
+        <v>24.37</v>
+      </c>
+      <c r="E68" s="9">
+        <v>-0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B69" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="8">
+        <v>34.71</v>
+      </c>
+      <c r="D69" s="8">
+        <v>32.01</v>
+      </c>
+      <c r="E69" s="9">
+        <v>-2.7</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B70" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="8">
+        <v>44.73</v>
+      </c>
+      <c r="D70" s="8">
+        <v>49.66</v>
+      </c>
+      <c r="E70" s="10">
+        <v>4.93</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B71" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="8">
+        <v>33.38</v>
+      </c>
+      <c r="D71" s="8">
+        <v>38.93</v>
+      </c>
+      <c r="E71" s="10">
+        <v>5.55</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B72" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C72" s="8">
+        <v>43.75</v>
+      </c>
+      <c r="D72" s="8">
+        <v>51.39</v>
+      </c>
+      <c r="E72" s="10">
+        <v>7.64</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B73" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C73" s="8">
+        <v>70.15000000000001</v>
+      </c>
+      <c r="D73" s="8">
+        <v>63.09</v>
+      </c>
+      <c r="E73" s="9">
+        <v>-7.06</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B74" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C74" s="8">
+        <v>29.23</v>
+      </c>
+      <c r="D74" s="8">
+        <v>32.17</v>
+      </c>
+      <c r="E74" s="10">
+        <v>2.94</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B75" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C75" s="8">
+        <v>36.8</v>
+      </c>
+      <c r="D75" s="8">
+        <v>40.6</v>
+      </c>
+      <c r="E75" s="10">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C76" s="8">
+        <v>55.44</v>
+      </c>
+      <c r="D76" s="8">
+        <v>49.49</v>
+      </c>
+      <c r="E76" s="9">
+        <v>-5.95</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B77" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="8">
+        <v>-55.81</v>
+      </c>
+      <c r="D77" s="8">
+        <v>-24.05</v>
+      </c>
+      <c r="E77" s="10">
+        <v>31.76</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B78" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="8">
+        <v>55.3</v>
+      </c>
+      <c r="D78" s="8">
+        <v>-2.75</v>
+      </c>
+      <c r="E78" s="9">
+        <v>-58.05</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B79" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="8">
+        <v>-44.01</v>
+      </c>
+      <c r="D79" s="8">
+        <v>-7.05</v>
+      </c>
+      <c r="E79" s="10">
+        <v>36.96</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B80" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="8">
+        <v>-41.47</v>
+      </c>
+      <c r="D80" s="8">
+        <v>-43.49</v>
+      </c>
+      <c r="E80" s="9">
+        <v>-2.02</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B81" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81" s="8">
+        <v>-37.04</v>
+      </c>
+      <c r="D81" s="8">
+        <v>-36.37</v>
+      </c>
+      <c r="E81" s="10">
         <v>0.67</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7">
-        <v>-6.99</v>
-      </c>
-      <c r="D12" s="7">
-        <v>-6.78</v>
-      </c>
-      <c r="E12" s="8">
-        <v>0.21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+    <row r="82" spans="1:5">
+      <c r="A82" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="7">
-        <v>13.23</v>
-      </c>
-      <c r="D13" s="7">
-        <v>14.84</v>
-      </c>
-      <c r="E13" s="8">
-        <v>1.61</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="B82" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C82" s="8">
+        <v>104.96</v>
+      </c>
+      <c r="D82" s="8">
+        <v>91.08</v>
+      </c>
+      <c r="E82" s="9">
+        <v>-13.88</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="7">
-        <v>-4.86</v>
-      </c>
-      <c r="D14" s="7">
-        <v>-9.380000000000001</v>
-      </c>
-      <c r="E14" s="9">
-        <v>-4.52</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+      <c r="B83" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C83" s="8">
+        <v>-19.98</v>
+      </c>
+      <c r="D83" s="8">
+        <v>-28.27</v>
+      </c>
+      <c r="E83" s="9">
+        <v>-8.289999999999999</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="7">
-        <v>-2.56</v>
-      </c>
-      <c r="D15" s="7">
-        <v>-1.6</v>
-      </c>
-      <c r="E15" s="8">
-        <v>0.96</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="B84" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C84" s="8">
+        <v>21.59</v>
+      </c>
+      <c r="D84" s="8">
+        <v>-53.17</v>
+      </c>
+      <c r="E84" s="9">
+        <v>-74.76000000000001</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-0.67</v>
-      </c>
-      <c r="D16" s="7">
-        <v>-1.55</v>
-      </c>
-      <c r="E16" s="9">
-        <v>-0.88</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-1.29</v>
-      </c>
-      <c r="D17" s="7">
-        <v>-3.02</v>
-      </c>
-      <c r="E17" s="9">
-        <v>-1.73</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-5.34</v>
-      </c>
-      <c r="D18" s="7">
-        <v>-6.13</v>
-      </c>
-      <c r="E18" s="9">
-        <v>-0.79</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="7">
-        <v>-4.47</v>
-      </c>
-      <c r="D19" s="7">
-        <v>-4.28</v>
-      </c>
-      <c r="E19" s="8">
-        <v>0.19</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="7">
-        <v>-5.21</v>
-      </c>
-      <c r="D20" s="7">
-        <v>-3.3</v>
-      </c>
-      <c r="E20" s="8">
-        <v>1.91</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-3.13</v>
-      </c>
-      <c r="D21" s="7">
-        <v>-1.74</v>
-      </c>
-      <c r="E21" s="8">
-        <v>1.39</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="7">
-        <v>2.05</v>
-      </c>
-      <c r="D22" s="7">
-        <v>4.48</v>
-      </c>
-      <c r="E22" s="8">
-        <v>2.43</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="7">
-        <v>-4.92</v>
-      </c>
-      <c r="D23" s="7">
-        <v>-5.32</v>
-      </c>
-      <c r="E23" s="9">
-        <v>-0.4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="7">
-        <v>-0.39</v>
-      </c>
-      <c r="D24" s="7">
-        <v>-0.23</v>
-      </c>
-      <c r="E24" s="8">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="7">
-        <v>2.38</v>
-      </c>
-      <c r="D25" s="7">
-        <v>3.31</v>
-      </c>
-      <c r="E25" s="8">
-        <v>0.93</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="7">
-        <v>2.03</v>
-      </c>
-      <c r="D26" s="7">
-        <v>1.53</v>
-      </c>
-      <c r="E26" s="9">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="7">
-        <v>-1.1</v>
-      </c>
-      <c r="D27" s="7">
-        <v>-0.3</v>
-      </c>
-      <c r="E27" s="8">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="7">
-        <v>40.64</v>
-      </c>
-      <c r="D28" s="7">
-        <v>45.25</v>
-      </c>
-      <c r="E28" s="8">
-        <v>4.61</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="7">
-        <v>3.58</v>
-      </c>
-      <c r="D29" s="7">
-        <v>2.59</v>
-      </c>
-      <c r="E29" s="9">
-        <v>-0.99</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="7">
-        <v>23.29</v>
-      </c>
-      <c r="D30" s="7">
-        <v>23.86</v>
-      </c>
-      <c r="E30" s="8">
-        <v>0.57</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="7">
-        <v>-0.8</v>
-      </c>
-      <c r="D31" s="7">
-        <v>3.68</v>
-      </c>
-      <c r="E31" s="8">
-        <v>4.48</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="7">
-        <v>-40.8</v>
-      </c>
-      <c r="D32" s="7">
-        <v>-40.96</v>
-      </c>
-      <c r="E32" s="9">
-        <v>-0.16</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="7">
-        <v>-12.27</v>
-      </c>
-      <c r="D33" s="7">
-        <v>-11.73</v>
-      </c>
-      <c r="E33" s="8">
-        <v>0.54</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="7">
-        <v>10.67</v>
-      </c>
-      <c r="D34" s="7">
-        <v>10.71</v>
-      </c>
-      <c r="E34" s="8">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="7">
-        <v>-13.53</v>
-      </c>
-      <c r="D35" s="7">
-        <v>-15.55</v>
-      </c>
-      <c r="E35" s="9">
-        <v>-2.02</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="7">
-        <v>8.23</v>
-      </c>
-      <c r="D36" s="7">
-        <v>5.77</v>
-      </c>
-      <c r="E36" s="9">
-        <v>-2.46</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="7">
-        <v>25.42</v>
-      </c>
-      <c r="D37" s="7">
-        <v>27.61</v>
-      </c>
-      <c r="E37" s="8">
-        <v>2.19</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="7">
-        <v>6.65</v>
-      </c>
-      <c r="D38" s="7">
-        <v>6.72</v>
-      </c>
-      <c r="E38" s="8">
-        <v>0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="7">
-        <v>10.5</v>
-      </c>
-      <c r="D39" s="7">
-        <v>13.1</v>
-      </c>
-      <c r="E39" s="8">
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="7">
-        <v>6.39</v>
-      </c>
-      <c r="D40" s="7">
-        <v>8.16</v>
-      </c>
-      <c r="E40" s="8">
-        <v>1.77</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="7">
-        <v>-1.73</v>
-      </c>
-      <c r="D41" s="7">
-        <v>-4.83</v>
-      </c>
-      <c r="E41" s="9">
-        <v>-3.1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="7">
-        <v>-6.37</v>
-      </c>
-      <c r="D42" s="7">
-        <v>-6.1</v>
-      </c>
-      <c r="E42" s="8">
-        <v>0.27</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="7">
-        <v>11.25</v>
-      </c>
-      <c r="D43" s="7">
-        <v>9.119999999999999</v>
-      </c>
-      <c r="E43" s="9">
-        <v>-2.13</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="7">
-        <v>-20.27</v>
-      </c>
-      <c r="D44" s="7">
-        <v>-21.46</v>
-      </c>
-      <c r="E44" s="9">
-        <v>-1.19</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="7">
-        <v>-14.29</v>
-      </c>
-      <c r="D45" s="7">
-        <v>-16.11</v>
-      </c>
-      <c r="E45" s="9">
-        <v>-1.82</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="7">
-        <v>-11.62</v>
-      </c>
-      <c r="D46" s="7">
-        <v>-10.54</v>
-      </c>
-      <c r="E46" s="8">
-        <v>1.08</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="7">
-        <v>-15.35</v>
-      </c>
-      <c r="D47" s="7">
-        <v>-14.87</v>
-      </c>
-      <c r="E47" s="8">
-        <v>0.48</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="7">
-        <v>-12.54</v>
-      </c>
-      <c r="D48" s="7">
-        <v>-11.35</v>
-      </c>
-      <c r="E48" s="8">
-        <v>1.19</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="7">
-        <v>-2.26</v>
-      </c>
-      <c r="D49" s="7">
-        <v>0</v>
-      </c>
-      <c r="E49" s="8">
-        <v>2.26</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="7">
-        <v>-42.46</v>
-      </c>
-      <c r="D50" s="7">
-        <v>-42.94</v>
-      </c>
-      <c r="E50" s="9">
-        <v>-0.48</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="7">
-        <v>-21.34</v>
-      </c>
-      <c r="D51" s="7">
-        <v>-21.27</v>
-      </c>
-      <c r="E51" s="8">
-        <v>0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C52" s="7">
-        <v>-7.37</v>
-      </c>
-      <c r="D52" s="7">
-        <v>-8.220000000000001</v>
-      </c>
-      <c r="E52" s="9">
-        <v>-0.85</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="7">
-        <v>390.85</v>
-      </c>
-      <c r="D53" s="7">
-        <v>385</v>
-      </c>
-      <c r="E53" s="9">
-        <v>-5.85</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="7">
-        <v>3259</v>
-      </c>
-      <c r="D54" s="7">
-        <v>3190</v>
-      </c>
-      <c r="E54" s="9">
-        <v>-69</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="7">
-        <v>364.4</v>
-      </c>
-      <c r="D55" s="7">
-        <v>368.85</v>
-      </c>
-      <c r="E55" s="8">
-        <v>4.45</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="7">
-        <v>356.95</v>
-      </c>
-      <c r="D56" s="7">
-        <v>359</v>
-      </c>
-      <c r="E56" s="8">
-        <v>2.05</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="7">
-        <v>387.2</v>
-      </c>
-      <c r="D57" s="7">
-        <v>392.45</v>
-      </c>
-      <c r="E57" s="8">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="7">
-        <v>649.6</v>
-      </c>
-      <c r="D58" s="7">
-        <v>665.05</v>
-      </c>
-      <c r="E58" s="8">
-        <v>15.45</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="7">
-        <v>208.31</v>
-      </c>
-      <c r="D59" s="7">
-        <v>206.59</v>
-      </c>
-      <c r="E59" s="9">
-        <v>-1.72</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="7">
-        <v>3537.7</v>
-      </c>
-      <c r="D60" s="7">
-        <v>3540.9</v>
-      </c>
-      <c r="E60" s="8">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C61" s="7">
-        <v>1638</v>
-      </c>
-      <c r="D61" s="7">
-        <v>1623</v>
-      </c>
-      <c r="E61" s="9">
-        <v>-15</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C62" s="7">
-        <v>66</v>
-      </c>
-      <c r="D62" s="7">
-        <v>77</v>
-      </c>
-      <c r="E62" s="8">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C63" s="7">
-        <v>77</v>
-      </c>
-      <c r="D63" s="7">
-        <v>66</v>
-      </c>
-      <c r="E63" s="9">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="7">
-        <v>28.33</v>
-      </c>
-      <c r="D64" s="7">
-        <v>24.93</v>
-      </c>
-      <c r="E64" s="9">
-        <v>-3.4</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="7">
-        <v>40.11</v>
-      </c>
-      <c r="D65" s="7">
-        <v>34.71</v>
-      </c>
-      <c r="E65" s="9">
-        <v>-5.4</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="7">
-        <v>41.44</v>
-      </c>
-      <c r="D66" s="7">
-        <v>44.73</v>
-      </c>
-      <c r="E66" s="8">
-        <v>3.29</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="7">
-        <v>30.45</v>
-      </c>
-      <c r="D67" s="7">
-        <v>33.38</v>
-      </c>
-      <c r="E67" s="8">
-        <v>2.93</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="7">
-        <v>37.66</v>
-      </c>
-      <c r="D68" s="7">
-        <v>43.75</v>
-      </c>
-      <c r="E68" s="8">
-        <v>6.09</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="7">
-        <v>65.33</v>
-      </c>
-      <c r="D69" s="7">
-        <v>70.15000000000001</v>
-      </c>
-      <c r="E69" s="8">
-        <v>4.82</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="7">
-        <v>30.85</v>
-      </c>
-      <c r="D70" s="7">
-        <v>29.23</v>
-      </c>
-      <c r="E70" s="9">
-        <v>-1.62</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B71" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="7">
-        <v>35.92</v>
-      </c>
-      <c r="D71" s="7">
-        <v>36.8</v>
-      </c>
-      <c r="E71" s="8">
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C72" s="7">
-        <v>59.43</v>
-      </c>
-      <c r="D72" s="7">
-        <v>55.44</v>
-      </c>
-      <c r="E72" s="9">
-        <v>-3.99</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B73" s="6" t="s">
+      <c r="B85" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C73" s="7">
-        <v>-39.5</v>
-      </c>
-      <c r="D73" s="7">
-        <v>-55.81</v>
-      </c>
-      <c r="E73" s="9">
-        <v>-16.31</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B74" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="7">
-        <v>0.93</v>
-      </c>
-      <c r="D74" s="7">
-        <v>55.3</v>
-      </c>
-      <c r="E74" s="8">
-        <v>54.37</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B75" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="7">
-        <v>-39.82</v>
-      </c>
-      <c r="D75" s="7">
-        <v>-44.01</v>
-      </c>
-      <c r="E75" s="9">
-        <v>-4.19</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B76" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="7">
-        <v>-17.99</v>
-      </c>
-      <c r="D76" s="7">
-        <v>-41.47</v>
-      </c>
-      <c r="E76" s="9">
-        <v>-23.48</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B77" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="7">
-        <v>-31.7</v>
-      </c>
-      <c r="D77" s="7">
-        <v>-37.04</v>
-      </c>
-      <c r="E77" s="9">
-        <v>-5.34</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B78" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="7">
-        <v>-3.7</v>
-      </c>
-      <c r="D78" s="7">
-        <v>104.96</v>
-      </c>
-      <c r="E78" s="8">
-        <v>108.66</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B79" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="7">
-        <v>7.18</v>
-      </c>
-      <c r="D79" s="7">
-        <v>-19.98</v>
-      </c>
-      <c r="E79" s="9">
-        <v>-27.16</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B80" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="7">
-        <v>107.68</v>
-      </c>
-      <c r="D80" s="7">
-        <v>21.59</v>
-      </c>
-      <c r="E80" s="9">
-        <v>-86.09</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B81" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="7">
-        <v>-8.02</v>
-      </c>
-      <c r="D81" s="7">
+      <c r="C85" s="8">
         <v>-40.6</v>
       </c>
-      <c r="E81" s="9">
-        <v>-32.58</v>
+      <c r="D85" s="8">
+        <v>-34.57</v>
+      </c>
+      <c r="E85" s="10">
+        <v>6.03</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A10:E10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3491,61 +3602,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>79</v>
+      <c r="B1" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="13">
         <v>48.16</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="14">
         <v>9</v>
       </c>
-      <c r="D2" s="12">
-        <v>41.5</v>
-      </c>
-      <c r="E2" s="12">
+      <c r="D2" s="13">
+        <v>42.4</v>
+      </c>
+      <c r="E2" s="13">
         <v>40</v>
       </c>
-      <c r="F2" s="12">
-        <v>-3.9</v>
-      </c>
-      <c r="G2" s="12">
+      <c r="F2" s="13">
+        <v>-3.7</v>
+      </c>
+      <c r="G2" s="13">
         <v>4.9</v>
       </c>
-      <c r="H2" s="12">
+      <c r="H2" s="13">
         <v>55.4</v>
       </c>
-      <c r="I2" s="12">
-        <v>60</v>
+      <c r="I2" s="13">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -3646,61 +3757,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="15" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="15">
-        <v>0.3497999999999999</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0.3446</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0.1991</v>
-      </c>
-      <c r="D2" s="15">
-        <v>0.1917</v>
-      </c>
-      <c r="E2" s="15">
-        <v>0.1224</v>
-      </c>
-      <c r="F2" s="15">
-        <v>0.06950000000000001</v>
-      </c>
-      <c r="G2" s="15">
-        <v>0.0555</v>
-      </c>
-      <c r="H2" s="15">
-        <v>-0.0152</v>
-      </c>
-      <c r="I2" s="15">
-        <v>-0.1149</v>
+      <c r="A2" s="16">
+        <v>0.3421</v>
+      </c>
+      <c r="B2" s="16">
+        <v>0.3408</v>
+      </c>
+      <c r="C2" s="16">
+        <v>0.1996</v>
+      </c>
+      <c r="D2" s="16">
+        <v>0.198</v>
+      </c>
+      <c r="E2" s="16">
+        <v>0.1246</v>
+      </c>
+      <c r="F2" s="16">
+        <v>0.06849999999999999</v>
+      </c>
+      <c r="G2" s="16">
+        <v>0.0516</v>
+      </c>
+      <c r="H2" s="16">
+        <v>-0.015</v>
+      </c>
+      <c r="I2" s="16">
+        <v>-0.108</v>
       </c>
     </row>
   </sheetData>

--- a/MAHINDRA_GROUP_Technical_Metrics.xlsx
+++ b/MAHINDRA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="75">
   <si>
     <t>Symbol</t>
   </si>
@@ -193,64 +193,19 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>43.8 → 51.4</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>43.8</t>
-  </si>
-  <si>
-    <t>51.4</t>
-  </si>
-  <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>29.2 → 32.2</t>
-  </si>
-  <si>
-    <t>29.2</t>
-  </si>
-  <si>
-    <t>32.2</t>
-  </si>
-  <si>
-    <t>RSI Overbought Exit</t>
-  </si>
-  <si>
-    <t>70.2 → 63.1</t>
-  </si>
-  <si>
-    <t>🔵 COOLING</t>
-  </si>
-  <si>
-    <t>70.2</t>
+    <t>RSI Overbought Entry</t>
+  </si>
+  <si>
+    <t>63.1 → 72.1</t>
+  </si>
+  <si>
+    <t>⚠️ CAUTION</t>
   </si>
   <si>
     <t>63.1</t>
   </si>
   <si>
-    <t>Yes → No</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
-  </si>
-  <si>
-    <t>55.4 → 49.5</t>
-  </si>
-  <si>
-    <t>55.4</t>
-  </si>
-  <si>
-    <t>49.5</t>
+    <t>72.1</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -336,14 +291,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF1F4E79"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -383,13 +338,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -465,7 +420,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -473,12 +428,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -990,10 +943,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>383.95</v>
+        <v>385.35</v>
       </c>
       <c r="D2">
-        <v>-0.27</v>
+        <v>0.36</v>
       </c>
       <c r="E2">
         <v>490.2</v>
@@ -1002,25 +955,25 @@
         <v>381.86</v>
       </c>
       <c r="G2">
-        <v>-21.67</v>
+        <v>-21.39</v>
       </c>
       <c r="H2">
-        <v>0.55</v>
+        <v>0.91</v>
       </c>
       <c r="I2">
-        <v>-2.67</v>
+        <v>-1.18</v>
       </c>
       <c r="J2">
-        <v>-7.49</v>
+        <v>-6.08</v>
       </c>
       <c r="K2">
-        <v>-15.06</v>
+        <v>-12</v>
       </c>
       <c r="L2">
-        <v>0.6</v>
+        <v>-2.08</v>
       </c>
       <c r="M2">
-        <v>12.46</v>
+        <v>12.77</v>
       </c>
       <c r="N2">
         <v>34</v>
@@ -1029,19 +982,19 @@
         <v>37</v>
       </c>
       <c r="P2">
-        <v>388.16</v>
+        <v>387.24</v>
       </c>
       <c r="Q2">
-        <v>400.88</v>
+        <v>399.62</v>
       </c>
       <c r="R2">
-        <v>428.45</v>
+        <v>426.73</v>
       </c>
       <c r="S2">
-        <v>436.26</v>
+        <v>436.09</v>
       </c>
       <c r="T2">
-        <v>-11.99</v>
+        <v>-11.64</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1056,43 +1009,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>24.37</v>
+        <v>26.75</v>
       </c>
       <c r="Z2">
-        <v>-11.06</v>
+        <v>-10.95</v>
       </c>
       <c r="AA2">
-        <v>-10.84</v>
+        <v>-10.86</v>
       </c>
       <c r="AB2">
-        <v>-0.22</v>
+        <v>-0.09</v>
       </c>
       <c r="AC2">
-        <v>4.67</v>
+        <v>6.03</v>
       </c>
       <c r="AD2">
-        <v>8.039999999999999</v>
+        <v>6.81</v>
       </c>
       <c r="AE2">
-        <v>8.51</v>
+        <v>8.24</v>
       </c>
       <c r="AF2">
-        <v>-24.05</v>
+        <v>-56</v>
       </c>
       <c r="AG2">
-        <v>419.47</v>
+        <v>418.87</v>
       </c>
       <c r="AH2">
-        <v>382.29</v>
+        <v>380.38</v>
       </c>
       <c r="AI2">
-        <v>411.17</v>
+        <v>409.34</v>
       </c>
       <c r="AJ2" t="s">
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>59.8</v>
+        <v>62.3</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1103,10 +1056,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>3150</v>
+        <v>3170</v>
       </c>
       <c r="D3">
-        <v>-1.25</v>
+        <v>0.63</v>
       </c>
       <c r="E3">
         <v>3802.4</v>
@@ -1115,25 +1068,25 @@
         <v>2931.1</v>
       </c>
       <c r="G3">
-        <v>-17.16</v>
+        <v>-16.63</v>
       </c>
       <c r="H3">
-        <v>7.47</v>
+        <v>8.15</v>
       </c>
       <c r="I3">
-        <v>-5.41</v>
+        <v>-4.92</v>
       </c>
       <c r="J3">
-        <v>-8.84</v>
+        <v>-6.93</v>
       </c>
       <c r="K3">
-        <v>3.6</v>
+        <v>6.88</v>
       </c>
       <c r="L3">
-        <v>-4.99</v>
+        <v>-1.99</v>
       </c>
       <c r="M3">
-        <v>34.21</v>
+        <v>34.25</v>
       </c>
       <c r="N3">
         <v>45</v>
@@ -1142,19 +1095,19 @@
         <v>51</v>
       </c>
       <c r="P3">
-        <v>3243</v>
+        <v>3210.2</v>
       </c>
       <c r="Q3">
-        <v>3380.17</v>
+        <v>3363.57</v>
       </c>
       <c r="R3">
-        <v>3275.51</v>
+        <v>3275.27</v>
       </c>
       <c r="S3">
-        <v>3336.34</v>
+        <v>3333.72</v>
       </c>
       <c r="T3">
-        <v>-5.59</v>
+        <v>-4.91</v>
       </c>
       <c r="U3" t="s">
         <v>48</v>
@@ -1169,43 +1122,43 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>32.01</v>
+        <v>34.74</v>
       </c>
       <c r="Z3">
-        <v>-20.54</v>
+        <v>-29.59</v>
       </c>
       <c r="AA3">
-        <v>17.68</v>
+        <v>8.23</v>
       </c>
       <c r="AB3">
-        <v>-38.22</v>
+        <v>-37.82</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD3">
-        <v>0.3</v>
+        <v>1.09</v>
       </c>
       <c r="AE3">
-        <v>72.95999999999999</v>
+        <v>70.69</v>
       </c>
       <c r="AF3">
-        <v>-2.75</v>
+        <v>-20.35</v>
       </c>
       <c r="AG3">
-        <v>3571.95</v>
+        <v>3568.01</v>
       </c>
       <c r="AH3">
-        <v>3188.39</v>
+        <v>3159.13</v>
       </c>
       <c r="AI3">
-        <v>3398.89</v>
+        <v>3376.81</v>
       </c>
       <c r="AJ3" t="s">
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>43.71</v>
+        <v>47.86</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1216,10 +1169,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>376.05</v>
+        <v>373.65</v>
       </c>
       <c r="D4">
-        <v>1.95</v>
+        <v>-0.64</v>
       </c>
       <c r="E4">
         <v>412.3</v>
@@ -1228,25 +1181,25 @@
         <v>259.7</v>
       </c>
       <c r="G4">
-        <v>-8.789999999999999</v>
+        <v>-9.369999999999999</v>
       </c>
       <c r="H4">
-        <v>44.8</v>
+        <v>43.88</v>
       </c>
       <c r="I4">
-        <v>-1.9</v>
+        <v>-0.78</v>
       </c>
       <c r="J4">
-        <v>-5.61</v>
+        <v>-3.9</v>
       </c>
       <c r="K4">
-        <v>29.74</v>
+        <v>33.09</v>
       </c>
       <c r="L4">
-        <v>46.04</v>
+        <v>43.33</v>
       </c>
       <c r="M4">
-        <v>19.8</v>
+        <v>19.23</v>
       </c>
       <c r="N4">
         <v>99</v>
@@ -1255,19 +1208,19 @@
         <v>86</v>
       </c>
       <c r="P4">
-        <v>371.78</v>
+        <v>371.19</v>
       </c>
       <c r="Q4">
-        <v>385.92</v>
+        <v>384.18</v>
       </c>
       <c r="R4">
-        <v>364.49</v>
+        <v>365.4</v>
       </c>
       <c r="S4">
-        <v>343.92</v>
+        <v>344.17</v>
       </c>
       <c r="T4">
-        <v>9.34</v>
+        <v>8.56</v>
       </c>
       <c r="U4" t="s">
         <v>48</v>
@@ -1282,34 +1235,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>49.66</v>
+        <v>48.12</v>
       </c>
       <c r="Z4">
-        <v>0.7</v>
+        <v>0.33</v>
       </c>
       <c r="AA4">
-        <v>4.56</v>
+        <v>3.72</v>
       </c>
       <c r="AB4">
-        <v>-3.86</v>
+        <v>-3.39</v>
       </c>
       <c r="AC4">
-        <v>24.22</v>
+        <v>38.42</v>
       </c>
       <c r="AD4">
-        <v>10.32</v>
+        <v>23.12</v>
       </c>
       <c r="AE4">
-        <v>12.02</v>
+        <v>11.84</v>
       </c>
       <c r="AF4">
-        <v>-7.05</v>
+        <v>27.05</v>
       </c>
       <c r="AG4">
-        <v>410.34</v>
+        <v>406.73</v>
       </c>
       <c r="AH4">
-        <v>361.5</v>
+        <v>361.63</v>
       </c>
       <c r="AI4">
         <v>357.72</v>
@@ -1318,7 +1271,7 @@
         <v>50</v>
       </c>
       <c r="AK4">
-        <v>25.77</v>
+        <v>23.04</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1329,10 +1282,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>363.1</v>
+        <v>362.4</v>
       </c>
       <c r="D5">
-        <v>1.14</v>
+        <v>-0.19</v>
       </c>
       <c r="E5">
         <v>421.7</v>
@@ -1341,46 +1294,46 @@
         <v>294.25</v>
       </c>
       <c r="G5">
-        <v>-13.9</v>
+        <v>-14.06</v>
       </c>
       <c r="H5">
-        <v>23.4</v>
+        <v>23.16</v>
       </c>
       <c r="I5">
-        <v>-1.51</v>
+        <v>-1.4</v>
       </c>
       <c r="J5">
-        <v>-5.16</v>
+        <v>-6.21</v>
       </c>
       <c r="K5">
-        <v>7.27</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="L5">
-        <v>4</v>
+        <v>3.57</v>
       </c>
       <c r="M5">
-        <v>6.85</v>
+        <v>6.26</v>
       </c>
       <c r="N5">
         <v>55</v>
       </c>
       <c r="O5">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="P5">
-        <v>362.45</v>
+        <v>361.42</v>
       </c>
       <c r="Q5">
-        <v>375.84</v>
+        <v>374.64</v>
       </c>
       <c r="R5">
-        <v>376.17</v>
+        <v>376.2</v>
       </c>
       <c r="S5">
-        <v>363.46</v>
+        <v>363.3</v>
       </c>
       <c r="T5">
-        <v>-0.1</v>
+        <v>-0.25</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1395,34 +1348,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>38.93</v>
+        <v>38.34</v>
       </c>
       <c r="Z5">
-        <v>-4.4</v>
+        <v>-4.58</v>
       </c>
       <c r="AA5">
-        <v>-1.75</v>
+        <v>-2.32</v>
       </c>
       <c r="AB5">
-        <v>-2.65</v>
+        <v>-2.26</v>
       </c>
       <c r="AC5">
-        <v>14.01</v>
+        <v>24.98</v>
       </c>
       <c r="AD5">
-        <v>5.87</v>
+        <v>14.2</v>
       </c>
       <c r="AE5">
-        <v>9.92</v>
+        <v>9.68</v>
       </c>
       <c r="AF5">
-        <v>-43.49</v>
+        <v>-65.7</v>
       </c>
       <c r="AG5">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AH5">
-        <v>356.69</v>
+        <v>355.28</v>
       </c>
       <c r="AI5">
         <v>386.7</v>
@@ -1431,7 +1384,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>43.38</v>
+        <v>42.04</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1442,10 +1395,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>400.3</v>
+        <v>405.35</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>1.26</v>
       </c>
       <c r="E6">
         <v>442.7</v>
@@ -1454,46 +1407,46 @@
         <v>279.55</v>
       </c>
       <c r="G6">
-        <v>-9.58</v>
+        <v>-8.44</v>
       </c>
       <c r="H6">
-        <v>43.19</v>
+        <v>45</v>
       </c>
       <c r="I6">
-        <v>2.22</v>
+        <v>3.21</v>
       </c>
       <c r="J6">
-        <v>-3.19</v>
+        <v>-2.07</v>
       </c>
       <c r="K6">
-        <v>14.72</v>
+        <v>19.94</v>
       </c>
       <c r="L6">
-        <v>26.5</v>
+        <v>26.14</v>
       </c>
       <c r="M6">
-        <v>-10.8</v>
+        <v>-10.35</v>
       </c>
       <c r="N6">
         <v>88</v>
       </c>
       <c r="O6">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P6">
-        <v>392.83</v>
+        <v>395.35</v>
       </c>
       <c r="Q6">
-        <v>401.2</v>
+        <v>401.33</v>
       </c>
       <c r="R6">
-        <v>397.84</v>
+        <v>398.58</v>
       </c>
       <c r="S6">
-        <v>367.55</v>
+        <v>367.94</v>
       </c>
       <c r="T6">
-        <v>8.91</v>
+        <v>10.17</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1508,34 +1461,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>51.39</v>
+        <v>55.57</v>
       </c>
       <c r="Z6">
-        <v>-1.76</v>
+        <v>-0.98</v>
       </c>
       <c r="AA6">
-        <v>-0.16</v>
+        <v>-0.32</v>
       </c>
       <c r="AB6">
-        <v>-1.61</v>
+        <v>-0.66</v>
       </c>
       <c r="AC6">
-        <v>41.16</v>
+        <v>74.48999999999999</v>
       </c>
       <c r="AD6">
-        <v>19.22</v>
+        <v>42.93</v>
       </c>
       <c r="AE6">
-        <v>11.65</v>
+        <v>11.57</v>
       </c>
       <c r="AF6">
-        <v>-36.37</v>
+        <v>-20.14</v>
       </c>
       <c r="AG6">
-        <v>414.75</v>
+        <v>414.99</v>
       </c>
       <c r="AH6">
-        <v>387.64</v>
+        <v>387.66</v>
       </c>
       <c r="AI6">
         <v>372.35</v>
@@ -1544,7 +1497,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>19.54</v>
+        <v>20.82</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1555,58 +1508,58 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>653.5</v>
+        <v>688.1</v>
       </c>
       <c r="D7">
-        <v>-1.74</v>
+        <v>5.29</v>
       </c>
       <c r="E7">
-        <v>665.05</v>
+        <v>688.1</v>
       </c>
       <c r="F7">
         <v>506.45</v>
       </c>
       <c r="G7">
-        <v>-1.74</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>29.04</v>
+        <v>35.87</v>
       </c>
       <c r="I7">
-        <v>1.78</v>
+        <v>3.99</v>
       </c>
       <c r="J7">
-        <v>12.17</v>
+        <v>17.87</v>
       </c>
       <c r="K7">
-        <v>4.74</v>
+        <v>11.92</v>
       </c>
       <c r="L7">
-        <v>0.75</v>
+        <v>4.88</v>
       </c>
       <c r="M7">
-        <v>34.08</v>
+        <v>35.96</v>
       </c>
       <c r="N7">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="O7">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="P7">
-        <v>658.61</v>
+        <v>663.89</v>
       </c>
       <c r="Q7">
-        <v>628.5700000000001</v>
+        <v>633.49</v>
       </c>
       <c r="R7">
-        <v>604.05</v>
+        <v>605.25</v>
       </c>
       <c r="S7">
-        <v>586.63</v>
+        <v>587.25</v>
       </c>
       <c r="T7">
-        <v>11.4</v>
+        <v>17.17</v>
       </c>
       <c r="U7" t="s">
         <v>48</v>
@@ -1621,43 +1574,43 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>63.09</v>
+        <v>72.14</v>
       </c>
       <c r="Z7">
-        <v>16.83</v>
+        <v>19.16</v>
       </c>
       <c r="AA7">
-        <v>13.7</v>
+        <v>14.8</v>
       </c>
       <c r="AB7">
-        <v>3.12</v>
+        <v>4.36</v>
       </c>
       <c r="AC7">
-        <v>51.22</v>
+        <v>63.41</v>
       </c>
       <c r="AD7">
-        <v>68.81999999999999</v>
+        <v>62.55</v>
       </c>
       <c r="AE7">
-        <v>19.77</v>
+        <v>21.53</v>
       </c>
       <c r="AF7">
-        <v>91.08</v>
+        <v>320.45</v>
       </c>
       <c r="AG7">
-        <v>673.66</v>
+        <v>682.0599999999999</v>
       </c>
       <c r="AH7">
-        <v>583.48</v>
+        <v>584.92</v>
       </c>
       <c r="AI7">
-        <v>606.8</v>
+        <v>609.0700000000001</v>
       </c>
       <c r="AJ7" t="s">
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>68.39</v>
+        <v>69.89</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1668,10 +1621,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>207.91</v>
+        <v>207.4</v>
       </c>
       <c r="D8">
-        <v>0.64</v>
+        <v>-0.25</v>
       </c>
       <c r="E8">
         <v>362.05</v>
@@ -1680,46 +1633,46 @@
         <v>206.59</v>
       </c>
       <c r="G8">
-        <v>-42.57</v>
+        <v>-42.72</v>
       </c>
       <c r="H8">
-        <v>0.64</v>
+        <v>0.39</v>
       </c>
       <c r="I8">
-        <v>-1.57</v>
+        <v>-1.89</v>
       </c>
       <c r="J8">
-        <v>-10.86</v>
+        <v>-10.21</v>
       </c>
       <c r="K8">
-        <v>-3.53</v>
+        <v>-1.43</v>
       </c>
       <c r="L8">
-        <v>-40.53</v>
+        <v>-41.25</v>
       </c>
       <c r="M8">
-        <v>-1.5</v>
+        <v>-0.87</v>
       </c>
       <c r="N8">
         <v>12</v>
       </c>
       <c r="O8">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="P8">
-        <v>208.77</v>
+        <v>207.97</v>
       </c>
       <c r="Q8">
-        <v>219.23</v>
+        <v>218.12</v>
       </c>
       <c r="R8">
-        <v>224.41</v>
+        <v>223.76</v>
       </c>
       <c r="S8">
-        <v>260.85</v>
+        <v>260.22</v>
       </c>
       <c r="T8">
-        <v>-20.29</v>
+        <v>-20.3</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1734,34 +1687,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>32.17</v>
+        <v>31.63</v>
       </c>
       <c r="Z8">
-        <v>-4.65</v>
+        <v>-4.8</v>
       </c>
       <c r="AA8">
-        <v>-3.26</v>
+        <v>-3.57</v>
       </c>
       <c r="AB8">
-        <v>-1.4</v>
+        <v>-1.23</v>
       </c>
       <c r="AC8">
-        <v>4.57</v>
+        <v>9.43</v>
       </c>
       <c r="AD8">
-        <v>1.72</v>
+        <v>4.67</v>
       </c>
       <c r="AE8">
-        <v>5.97</v>
+        <v>5.86</v>
       </c>
       <c r="AF8">
-        <v>-28.27</v>
+        <v>57.1</v>
       </c>
       <c r="AG8">
-        <v>234.3</v>
+        <v>233.23</v>
       </c>
       <c r="AH8">
-        <v>204.17</v>
+        <v>203.01</v>
       </c>
       <c r="AI8">
         <v>225.7</v>
@@ -1770,7 +1723,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>42.85</v>
+        <v>42.56</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1781,10 +1734,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>3554.7</v>
+        <v>3557.8</v>
       </c>
       <c r="D9">
-        <v>0.39</v>
+        <v>0.09</v>
       </c>
       <c r="E9">
         <v>4497.5</v>
@@ -1793,25 +1746,25 @@
         <v>3308.9</v>
       </c>
       <c r="G9">
-        <v>-20.96</v>
+        <v>-20.89</v>
       </c>
       <c r="H9">
-        <v>7.43</v>
+        <v>7.52</v>
       </c>
       <c r="I9">
-        <v>0.18</v>
+        <v>0.37</v>
       </c>
       <c r="J9">
-        <v>-1.5</v>
+        <v>-1.06</v>
       </c>
       <c r="K9">
-        <v>-4.79</v>
+        <v>-4.69</v>
       </c>
       <c r="L9">
-        <v>-13.46</v>
+        <v>-12.34</v>
       </c>
       <c r="M9">
-        <v>19.96</v>
+        <v>20.17</v>
       </c>
       <c r="N9">
         <v>23</v>
@@ -1820,19 +1773,19 @@
         <v>36</v>
       </c>
       <c r="P9">
-        <v>3549.48</v>
+        <v>3552.08</v>
       </c>
       <c r="Q9">
-        <v>3580.73</v>
+        <v>3578.6</v>
       </c>
       <c r="R9">
-        <v>3672.6</v>
+        <v>3664.67</v>
       </c>
       <c r="S9">
-        <v>3689.5</v>
+        <v>3687.74</v>
       </c>
       <c r="T9">
-        <v>-3.65</v>
+        <v>-3.52</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1847,34 +1800,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>40.6</v>
+        <v>41.45</v>
       </c>
       <c r="Z9">
-        <v>-30.57</v>
+        <v>-28.63</v>
       </c>
       <c r="AA9">
-        <v>-32.92</v>
+        <v>-32.06</v>
       </c>
       <c r="AB9">
-        <v>2.35</v>
+        <v>3.43</v>
       </c>
       <c r="AC9">
-        <v>27.73</v>
+        <v>52.77</v>
       </c>
       <c r="AD9">
-        <v>26.53</v>
+        <v>36.59</v>
       </c>
       <c r="AE9">
-        <v>52.49</v>
+        <v>58.17</v>
       </c>
       <c r="AF9">
-        <v>-53.17</v>
+        <v>10.08</v>
       </c>
       <c r="AG9">
-        <v>3645.14</v>
+        <v>3643.09</v>
       </c>
       <c r="AH9">
-        <v>3516.32</v>
+        <v>3514.11</v>
       </c>
       <c r="AI9">
         <v>3684.57</v>
@@ -1883,7 +1836,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>20.16</v>
+        <v>25.32</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1894,10 +1847,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>1598</v>
+        <v>1596.9</v>
       </c>
       <c r="D10">
-        <v>-1.54</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E10">
         <v>1768.4</v>
@@ -1906,46 +1859,46 @@
         <v>1326.2</v>
       </c>
       <c r="G10">
-        <v>-9.640000000000001</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="H10">
-        <v>20.49</v>
+        <v>20.41</v>
       </c>
       <c r="I10">
-        <v>0.82</v>
+        <v>-2.68</v>
       </c>
       <c r="J10">
-        <v>-3.15</v>
+        <v>-2.16</v>
       </c>
       <c r="K10">
-        <v>7.72</v>
+        <v>6.22</v>
       </c>
       <c r="L10">
-        <v>7.26</v>
+        <v>6.66</v>
       </c>
       <c r="M10">
-        <v>5.16</v>
+        <v>4.87</v>
       </c>
       <c r="N10">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="O10">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="P10">
-        <v>1625.58</v>
+        <v>1616.78</v>
       </c>
       <c r="Q10">
-        <v>1612.53</v>
+        <v>1610.62</v>
       </c>
       <c r="R10">
-        <v>1560.03</v>
+        <v>1563.22</v>
       </c>
       <c r="S10">
-        <v>1515.38</v>
+        <v>1516.26</v>
       </c>
       <c r="T10">
-        <v>5.45</v>
+        <v>5.32</v>
       </c>
       <c r="U10" t="s">
         <v>48</v>
@@ -1960,34 +1913,34 @@
         <v>3</v>
       </c>
       <c r="Y10">
-        <v>49.49</v>
+        <v>49.24</v>
       </c>
       <c r="Z10">
-        <v>9.84</v>
+        <v>7.97</v>
       </c>
       <c r="AA10">
-        <v>12.58</v>
+        <v>11.66</v>
       </c>
       <c r="AB10">
-        <v>-2.74</v>
+        <v>-3.69</v>
       </c>
       <c r="AC10">
-        <v>58.49</v>
+        <v>40.83</v>
       </c>
       <c r="AD10">
-        <v>68.86</v>
+        <v>57.16</v>
       </c>
       <c r="AE10">
         <v>36.61</v>
       </c>
       <c r="AF10">
-        <v>-34.57</v>
+        <v>-52.97</v>
       </c>
       <c r="AG10">
-        <v>1660.87</v>
+        <v>1658.23</v>
       </c>
       <c r="AH10">
-        <v>1564.18</v>
+        <v>1563.01</v>
       </c>
       <c r="AI10">
         <v>1527.05</v>
@@ -1996,7 +1949,7 @@
         <v>50</v>
       </c>
       <c r="AK10">
-        <v>27.22</v>
+        <v>24.5</v>
       </c>
     </row>
   </sheetData>
@@ -2137,7 +2090,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F85"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2177,7 +2130,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2195,1394 +2148,1294 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>-7.49</v>
+      </c>
+      <c r="D7" s="6">
+        <v>-6.08</v>
+      </c>
+      <c r="E7" s="7">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>-8.84</v>
+      </c>
+      <c r="D8" s="6">
+        <v>-6.93</v>
+      </c>
+      <c r="E8" s="7">
+        <v>1.91</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-5.61</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-3.9</v>
+      </c>
+      <c r="E9" s="7">
+        <v>1.71</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-5.16</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-6.21</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-1.05</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-3.19</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-2.07</v>
+      </c>
+      <c r="E11" s="7">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>12.17</v>
+      </c>
+      <c r="D12" s="6">
+        <v>17.87</v>
+      </c>
+      <c r="E12" s="7">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="5" t="s">
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-10.86</v>
+      </c>
+      <c r="D13" s="6">
+        <v>-10.21</v>
+      </c>
+      <c r="E13" s="7">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-1.5</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-1.06</v>
+      </c>
+      <c r="E14" s="7">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-3.15</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-2.16</v>
+      </c>
+      <c r="E15" s="7">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-2.67</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-1.18</v>
+      </c>
+      <c r="E16" s="7">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-5.41</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-4.92</v>
+      </c>
+      <c r="E17" s="7">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-1.9</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-0.78</v>
+      </c>
+      <c r="E18" s="7">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-1.51</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-1.4</v>
+      </c>
+      <c r="E19" s="7">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>2.22</v>
+      </c>
+      <c r="D20" s="6">
+        <v>3.21</v>
+      </c>
+      <c r="E20" s="7">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="6">
+        <v>1.78</v>
+      </c>
+      <c r="D21" s="6">
+        <v>3.99</v>
+      </c>
+      <c r="E21" s="7">
+        <v>2.21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="6">
+        <v>-1.57</v>
+      </c>
+      <c r="D22" s="6">
+        <v>-1.89</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-0.32</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="6">
+        <v>0.18</v>
+      </c>
+      <c r="D23" s="6">
+        <v>0.37</v>
+      </c>
+      <c r="E23" s="7">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="6">
+        <v>0.82</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-2.68</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-3.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="6">
+        <v>0.6</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-2.08</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-2.68</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>-4.99</v>
+      </c>
+      <c r="D26" s="6">
+        <v>-1.99</v>
+      </c>
+      <c r="E26" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>46.04</v>
+      </c>
+      <c r="D27" s="6">
+        <v>43.33</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-2.71</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="6">
+        <v>4</v>
+      </c>
+      <c r="D28" s="6">
+        <v>3.57</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="6">
+        <v>26.5</v>
+      </c>
+      <c r="D29" s="6">
+        <v>26.14</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-0.36</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="D30" s="6">
+        <v>4.88</v>
+      </c>
+      <c r="E30" s="7">
+        <v>4.13</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-40.53</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-41.25</v>
+      </c>
+      <c r="E31" s="8">
+        <v>-0.72</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-13.46</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-12.34</v>
+      </c>
+      <c r="E32" s="7">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="6">
+        <v>7.26</v>
+      </c>
+      <c r="D33" s="6">
+        <v>6.66</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-15.06</v>
+      </c>
+      <c r="D34" s="6">
+        <v>-12</v>
+      </c>
+      <c r="E34" s="7">
+        <v>3.06</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="6">
+        <v>3.6</v>
+      </c>
+      <c r="D35" s="6">
+        <v>6.88</v>
+      </c>
+      <c r="E35" s="7">
+        <v>3.28</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="6">
+        <v>29.74</v>
+      </c>
+      <c r="D36" s="6">
+        <v>33.09</v>
+      </c>
+      <c r="E36" s="7">
+        <v>3.35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="6">
+        <v>7.27</v>
+      </c>
+      <c r="D37" s="6">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="E37" s="7">
+        <v>1.09</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="6">
+        <v>14.72</v>
+      </c>
+      <c r="D38" s="6">
+        <v>19.94</v>
+      </c>
+      <c r="E38" s="7">
+        <v>5.22</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="6">
+        <v>4.74</v>
+      </c>
+      <c r="D39" s="6">
+        <v>11.92</v>
+      </c>
+      <c r="E39" s="7">
+        <v>7.18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-3.53</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-1.43</v>
+      </c>
+      <c r="E40" s="7">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-4.79</v>
+      </c>
+      <c r="D41" s="6">
+        <v>-4.69</v>
+      </c>
+      <c r="E41" s="7">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="6">
+        <v>7.72</v>
+      </c>
+      <c r="D42" s="6">
+        <v>6.22</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="6">
+        <v>-21.67</v>
+      </c>
+      <c r="D43" s="6">
+        <v>-21.39</v>
+      </c>
+      <c r="E43" s="7">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="6">
+        <v>-17.16</v>
+      </c>
+      <c r="D44" s="6">
+        <v>-16.63</v>
+      </c>
+      <c r="E44" s="7">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-8.789999999999999</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-9.369999999999999</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-0.58</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="6">
+        <v>-13.9</v>
+      </c>
+      <c r="D46" s="6">
+        <v>-14.06</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-0.16</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="6">
+        <v>-9.58</v>
+      </c>
+      <c r="D47" s="6">
+        <v>-8.44</v>
+      </c>
+      <c r="E47" s="7">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="6">
+        <v>-1.74</v>
+      </c>
+      <c r="D48" s="6">
+        <v>0</v>
+      </c>
+      <c r="E48" s="7">
+        <v>1.74</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="6">
+        <v>-42.57</v>
+      </c>
+      <c r="D49" s="6">
+        <v>-42.72</v>
+      </c>
+      <c r="E49" s="8">
+        <v>-0.15</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="6">
+        <v>-20.96</v>
+      </c>
+      <c r="D50" s="6">
+        <v>-20.89</v>
+      </c>
+      <c r="E50" s="7">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="6">
+        <v>-9.640000000000001</v>
+      </c>
+      <c r="D51" s="6">
+        <v>-9.699999999999999</v>
+      </c>
+      <c r="E51" s="8">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="6">
+        <v>383.95</v>
+      </c>
+      <c r="D52" s="6">
+        <v>385.35</v>
+      </c>
+      <c r="E52" s="7">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="6">
+        <v>3150</v>
+      </c>
+      <c r="D53" s="6">
+        <v>3170</v>
+      </c>
+      <c r="E53" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="6">
+        <v>376.05</v>
+      </c>
+      <c r="D54" s="6">
+        <v>373.65</v>
+      </c>
+      <c r="E54" s="8">
+        <v>-2.4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="6">
+        <v>363.1</v>
+      </c>
+      <c r="D55" s="6">
+        <v>362.4</v>
+      </c>
+      <c r="E55" s="8">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="6">
+        <v>400.3</v>
+      </c>
+      <c r="D56" s="6">
+        <v>405.35</v>
+      </c>
+      <c r="E56" s="7">
+        <v>5.05</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="6">
+        <v>653.5</v>
+      </c>
+      <c r="D57" s="6">
+        <v>688.1</v>
+      </c>
+      <c r="E57" s="7">
+        <v>34.6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="6">
+        <v>207.91</v>
+      </c>
+      <c r="D58" s="6">
+        <v>207.4</v>
+      </c>
+      <c r="E58" s="8">
+        <v>-0.51</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="6">
+        <v>3554.7</v>
+      </c>
+      <c r="D59" s="6">
+        <v>3557.8</v>
+      </c>
+      <c r="E59" s="7">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="6">
+        <v>1598</v>
+      </c>
+      <c r="D60" s="6">
+        <v>1596.9</v>
+      </c>
+      <c r="E60" s="8">
+        <v>-1.1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C61" s="6">
         <v>66</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="6" t="s">
+      <c r="D61" s="6">
+        <v>77</v>
+      </c>
+      <c r="E61" s="7">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C62" s="6">
+        <v>77</v>
+      </c>
+      <c r="D62" s="6">
+        <v>66</v>
+      </c>
+      <c r="E62" s="8">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="6">
+        <v>24.37</v>
+      </c>
+      <c r="D63" s="6">
+        <v>26.75</v>
+      </c>
+      <c r="E63" s="7">
+        <v>2.38</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="6">
+        <v>32.01</v>
+      </c>
+      <c r="D64" s="6">
+        <v>34.74</v>
+      </c>
+      <c r="E64" s="7">
+        <v>2.73</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="6">
+        <v>49.66</v>
+      </c>
+      <c r="D65" s="6">
+        <v>48.12</v>
+      </c>
+      <c r="E65" s="8">
+        <v>-1.54</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="6" t="s">
+      <c r="B66" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="6">
+        <v>38.93</v>
+      </c>
+      <c r="D66" s="6">
+        <v>38.34</v>
+      </c>
+      <c r="E66" s="8">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="6">
+        <v>51.39</v>
+      </c>
+      <c r="D67" s="6">
+        <v>55.57</v>
+      </c>
+      <c r="E67" s="7">
+        <v>4.18</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="6">
+        <v>63.09</v>
+      </c>
+      <c r="D68" s="6">
+        <v>72.14</v>
+      </c>
+      <c r="E68" s="7">
+        <v>9.050000000000001</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="6">
+        <v>32.17</v>
+      </c>
+      <c r="D69" s="6">
+        <v>31.63</v>
+      </c>
+      <c r="E69" s="8">
+        <v>-0.54</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="6">
+        <v>40.6</v>
+      </c>
+      <c r="D70" s="6">
+        <v>41.45</v>
+      </c>
+      <c r="E70" s="7">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="6">
+        <v>49.49</v>
+      </c>
+      <c r="D71" s="6">
+        <v>49.24</v>
+      </c>
+      <c r="E71" s="8">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C72" s="6">
+        <v>-24.05</v>
+      </c>
+      <c r="D72" s="6">
+        <v>-56</v>
+      </c>
+      <c r="E72" s="8">
+        <v>-31.95</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="6">
+        <v>-2.75</v>
+      </c>
+      <c r="D73" s="6">
+        <v>-20.35</v>
+      </c>
+      <c r="E73" s="8">
+        <v>-17.6</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="6">
+        <v>-7.05</v>
+      </c>
+      <c r="D74" s="6">
+        <v>27.05</v>
+      </c>
+      <c r="E74" s="7">
+        <v>34.1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="6" t="s">
+      <c r="B75" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="6">
+        <v>-43.49</v>
+      </c>
+      <c r="D75" s="6">
+        <v>-65.7</v>
+      </c>
+      <c r="E75" s="8">
+        <v>-22.21</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="6">
+        <v>-36.37</v>
+      </c>
+      <c r="D76" s="6">
+        <v>-20.14</v>
+      </c>
+      <c r="E76" s="7">
+        <v>16.23</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="6">
+        <v>91.08</v>
+      </c>
+      <c r="D77" s="6">
+        <v>320.45</v>
+      </c>
+      <c r="E77" s="7">
+        <v>229.37</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="6">
+        <v>-28.27</v>
+      </c>
+      <c r="D78" s="6">
+        <v>57.1</v>
+      </c>
+      <c r="E78" s="7">
+        <v>85.37</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="6">
+        <v>-53.17</v>
+      </c>
+      <c r="D79" s="6">
+        <v>10.08</v>
+      </c>
+      <c r="E79" s="7">
+        <v>63.25</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="8">
-        <v>-6.23</v>
-      </c>
-      <c r="D12" s="8">
-        <v>-7.49</v>
-      </c>
-      <c r="E12" s="9">
-        <v>-1.26</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="8">
-        <v>-7.08</v>
-      </c>
-      <c r="D13" s="8">
-        <v>-8.84</v>
-      </c>
-      <c r="E13" s="9">
-        <v>-1.76</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="8">
-        <v>-7.46</v>
-      </c>
-      <c r="D14" s="8">
-        <v>-5.61</v>
-      </c>
-      <c r="E14" s="10">
-        <v>1.85</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="8">
-        <v>-9.699999999999999</v>
-      </c>
-      <c r="D15" s="8">
-        <v>-5.16</v>
-      </c>
-      <c r="E15" s="10">
-        <v>4.54</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="8">
-        <v>-6.78</v>
-      </c>
-      <c r="D16" s="8">
-        <v>-3.19</v>
-      </c>
-      <c r="E16" s="10">
-        <v>3.59</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="8">
-        <v>14.84</v>
-      </c>
-      <c r="D17" s="8">
-        <v>12.17</v>
-      </c>
-      <c r="E17" s="9">
-        <v>-2.67</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="8">
-        <v>-9.380000000000001</v>
-      </c>
-      <c r="D18" s="8">
-        <v>-10.86</v>
-      </c>
-      <c r="E18" s="9">
-        <v>-1.48</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C19" s="8">
-        <v>-1.6</v>
-      </c>
-      <c r="D19" s="8">
-        <v>-1.5</v>
-      </c>
-      <c r="E19" s="10">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C20" s="8">
-        <v>-1.55</v>
-      </c>
-      <c r="D20" s="8">
-        <v>-3.15</v>
-      </c>
-      <c r="E20" s="9">
-        <v>-1.6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="8">
-        <v>-3.02</v>
-      </c>
-      <c r="D21" s="8">
-        <v>-2.67</v>
-      </c>
-      <c r="E21" s="10">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="8">
-        <v>-6.13</v>
-      </c>
-      <c r="D22" s="8">
-        <v>-5.41</v>
-      </c>
-      <c r="E22" s="10">
-        <v>0.72</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="8">
-        <v>-4.28</v>
-      </c>
-      <c r="D23" s="8">
-        <v>-1.9</v>
-      </c>
-      <c r="E23" s="10">
-        <v>2.38</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="8">
-        <v>-3.3</v>
-      </c>
-      <c r="D24" s="8">
-        <v>-1.51</v>
-      </c>
-      <c r="E24" s="10">
-        <v>1.79</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="8">
-        <v>-1.74</v>
-      </c>
-      <c r="D25" s="8">
-        <v>2.22</v>
-      </c>
-      <c r="E25" s="10">
-        <v>3.96</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C26" s="8">
-        <v>4.48</v>
-      </c>
-      <c r="D26" s="8">
-        <v>1.78</v>
-      </c>
-      <c r="E26" s="9">
-        <v>-2.7</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C27" s="8">
-        <v>-5.32</v>
-      </c>
-      <c r="D27" s="8">
-        <v>-1.57</v>
-      </c>
-      <c r="E27" s="10">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C28" s="8">
-        <v>-0.23</v>
-      </c>
-      <c r="D28" s="8">
-        <v>0.18</v>
-      </c>
-      <c r="E28" s="10">
-        <v>0.41</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C29" s="8">
-        <v>3.31</v>
-      </c>
-      <c r="D29" s="8">
-        <v>0.82</v>
-      </c>
-      <c r="E29" s="9">
-        <v>-2.49</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="8">
-        <v>1.53</v>
-      </c>
-      <c r="D30" s="8">
-        <v>0.6</v>
-      </c>
-      <c r="E30" s="9">
-        <v>-0.93</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="8">
-        <v>-0.3</v>
-      </c>
-      <c r="D31" s="8">
-        <v>-4.99</v>
-      </c>
-      <c r="E31" s="9">
-        <v>-4.69</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="8">
-        <v>45.25</v>
-      </c>
-      <c r="D32" s="8">
-        <v>46.04</v>
-      </c>
-      <c r="E32" s="10">
-        <v>0.79</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="8">
-        <v>2.59</v>
-      </c>
-      <c r="D33" s="8">
-        <v>4</v>
-      </c>
-      <c r="E33" s="10">
-        <v>1.41</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="8">
-        <v>23.86</v>
-      </c>
-      <c r="D34" s="8">
-        <v>26.5</v>
-      </c>
-      <c r="E34" s="10">
-        <v>2.64</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C35" s="8">
-        <v>3.68</v>
-      </c>
-      <c r="D35" s="8">
-        <v>0.75</v>
-      </c>
-      <c r="E35" s="9">
-        <v>-2.93</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C36" s="8">
-        <v>-40.96</v>
-      </c>
-      <c r="D36" s="8">
-        <v>-40.53</v>
-      </c>
-      <c r="E36" s="10">
-        <v>0.43</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C37" s="8">
-        <v>-11.73</v>
-      </c>
-      <c r="D37" s="8">
-        <v>-13.46</v>
-      </c>
-      <c r="E37" s="9">
-        <v>-1.73</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C38" s="8">
-        <v>10.71</v>
-      </c>
-      <c r="D38" s="8">
-        <v>7.26</v>
-      </c>
-      <c r="E38" s="9">
-        <v>-3.45</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="8">
-        <v>-15.55</v>
-      </c>
-      <c r="D39" s="8">
-        <v>-15.06</v>
-      </c>
-      <c r="E39" s="10">
-        <v>0.49</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="8">
-        <v>5.77</v>
-      </c>
-      <c r="D40" s="8">
-        <v>3.6</v>
-      </c>
-      <c r="E40" s="9">
-        <v>-2.17</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="8">
-        <v>27.61</v>
-      </c>
-      <c r="D41" s="8">
-        <v>29.74</v>
-      </c>
-      <c r="E41" s="10">
-        <v>2.13</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B42" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="8">
-        <v>6.72</v>
-      </c>
-      <c r="D42" s="8">
-        <v>7.27</v>
-      </c>
-      <c r="E42" s="10">
-        <v>0.55</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="8">
-        <v>13.1</v>
-      </c>
-      <c r="D43" s="8">
-        <v>14.72</v>
-      </c>
-      <c r="E43" s="10">
-        <v>1.62</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B44" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44" s="8">
-        <v>8.16</v>
-      </c>
-      <c r="D44" s="8">
-        <v>4.74</v>
-      </c>
-      <c r="E44" s="9">
-        <v>-3.42</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C45" s="8">
-        <v>-4.83</v>
-      </c>
-      <c r="D45" s="8">
-        <v>-3.53</v>
-      </c>
-      <c r="E45" s="10">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B46" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C46" s="8">
-        <v>-6.1</v>
-      </c>
-      <c r="D46" s="8">
-        <v>-4.79</v>
-      </c>
-      <c r="E46" s="10">
-        <v>1.31</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B47" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C47" s="8">
-        <v>9.119999999999999</v>
-      </c>
-      <c r="D47" s="8">
-        <v>7.72</v>
-      </c>
-      <c r="E47" s="9">
-        <v>-1.4</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B48" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="8">
-        <v>-21.46</v>
-      </c>
-      <c r="D48" s="8">
-        <v>-21.67</v>
-      </c>
-      <c r="E48" s="9">
-        <v>-0.21</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B49" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="8">
-        <v>-16.11</v>
-      </c>
-      <c r="D49" s="8">
-        <v>-17.16</v>
-      </c>
-      <c r="E49" s="9">
-        <v>-1.05</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B50" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="8">
-        <v>-10.54</v>
-      </c>
-      <c r="D50" s="8">
-        <v>-8.789999999999999</v>
-      </c>
-      <c r="E50" s="10">
-        <v>1.75</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B51" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="8">
-        <v>-14.87</v>
-      </c>
-      <c r="D51" s="8">
-        <v>-13.9</v>
-      </c>
-      <c r="E51" s="10">
-        <v>0.97</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B52" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C52" s="8">
-        <v>-11.35</v>
-      </c>
-      <c r="D52" s="8">
-        <v>-9.58</v>
-      </c>
-      <c r="E52" s="10">
-        <v>1.77</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B53" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C53" s="8">
-        <v>0</v>
-      </c>
-      <c r="D53" s="8">
-        <v>-1.74</v>
-      </c>
-      <c r="E53" s="9">
-        <v>-1.74</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B54" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C54" s="8">
-        <v>-42.94</v>
-      </c>
-      <c r="D54" s="8">
-        <v>-42.57</v>
-      </c>
-      <c r="E54" s="10">
-        <v>0.37</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B55" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C55" s="8">
-        <v>-21.27</v>
-      </c>
-      <c r="D55" s="8">
-        <v>-20.96</v>
-      </c>
-      <c r="E55" s="10">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B56" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C56" s="8">
-        <v>-8.220000000000001</v>
-      </c>
-      <c r="D56" s="8">
-        <v>-9.640000000000001</v>
-      </c>
-      <c r="E56" s="9">
-        <v>-1.42</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B57" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="8">
-        <v>385</v>
-      </c>
-      <c r="D57" s="8">
-        <v>383.95</v>
-      </c>
-      <c r="E57" s="9">
-        <v>-1.05</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B58" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="8">
-        <v>3190</v>
-      </c>
-      <c r="D58" s="8">
-        <v>3150</v>
-      </c>
-      <c r="E58" s="9">
-        <v>-40</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B59" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="8">
-        <v>368.85</v>
-      </c>
-      <c r="D59" s="8">
-        <v>376.05</v>
-      </c>
-      <c r="E59" s="10">
-        <v>7.2</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B60" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="8">
-        <v>359</v>
-      </c>
-      <c r="D60" s="8">
-        <v>363.1</v>
-      </c>
-      <c r="E60" s="10">
-        <v>4.1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B61" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C61" s="8">
-        <v>392.45</v>
-      </c>
-      <c r="D61" s="8">
-        <v>400.3</v>
-      </c>
-      <c r="E61" s="10">
-        <v>7.85</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B62" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C62" s="8">
-        <v>665.05</v>
-      </c>
-      <c r="D62" s="8">
-        <v>653.5</v>
-      </c>
-      <c r="E62" s="9">
-        <v>-11.55</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B63" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C63" s="8">
-        <v>206.59</v>
-      </c>
-      <c r="D63" s="8">
-        <v>207.91</v>
-      </c>
-      <c r="E63" s="10">
-        <v>1.32</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B64" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C64" s="8">
-        <v>3540.9</v>
-      </c>
-      <c r="D64" s="8">
-        <v>3554.7</v>
-      </c>
-      <c r="E64" s="10">
-        <v>13.8</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B65" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C65" s="8">
-        <v>1623</v>
-      </c>
-      <c r="D65" s="8">
-        <v>1598</v>
-      </c>
-      <c r="E65" s="9">
-        <v>-25</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B66" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C66" s="8">
-        <v>77</v>
-      </c>
-      <c r="D66" s="8">
-        <v>66</v>
-      </c>
-      <c r="E66" s="9">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B67" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C67" s="8">
-        <v>66</v>
-      </c>
-      <c r="D67" s="8">
-        <v>77</v>
-      </c>
-      <c r="E67" s="10">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B68" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="8">
-        <v>24.93</v>
-      </c>
-      <c r="D68" s="8">
-        <v>24.37</v>
-      </c>
-      <c r="E68" s="9">
-        <v>-0.5600000000000001</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B69" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="8">
-        <v>34.71</v>
-      </c>
-      <c r="D69" s="8">
-        <v>32.01</v>
-      </c>
-      <c r="E69" s="9">
-        <v>-2.7</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B70" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="8">
-        <v>44.73</v>
-      </c>
-      <c r="D70" s="8">
-        <v>49.66</v>
-      </c>
-      <c r="E70" s="10">
-        <v>4.93</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B71" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="8">
-        <v>33.38</v>
-      </c>
-      <c r="D71" s="8">
-        <v>38.93</v>
-      </c>
-      <c r="E71" s="10">
-        <v>5.55</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B72" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C72" s="8">
-        <v>43.75</v>
-      </c>
-      <c r="D72" s="8">
-        <v>51.39</v>
-      </c>
-      <c r="E72" s="10">
-        <v>7.64</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B73" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C73" s="8">
-        <v>70.15000000000001</v>
-      </c>
-      <c r="D73" s="8">
-        <v>63.09</v>
-      </c>
-      <c r="E73" s="9">
-        <v>-7.06</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B74" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C74" s="8">
-        <v>29.23</v>
-      </c>
-      <c r="D74" s="8">
-        <v>32.17</v>
-      </c>
-      <c r="E74" s="10">
-        <v>2.94</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B75" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C75" s="8">
-        <v>36.8</v>
-      </c>
-      <c r="D75" s="8">
-        <v>40.6</v>
-      </c>
-      <c r="E75" s="10">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B76" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C76" s="8">
-        <v>55.44</v>
-      </c>
-      <c r="D76" s="8">
-        <v>49.49</v>
-      </c>
-      <c r="E76" s="9">
-        <v>-5.95</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B77" s="7" t="s">
+      <c r="B80" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C77" s="8">
-        <v>-55.81</v>
-      </c>
-      <c r="D77" s="8">
-        <v>-24.05</v>
-      </c>
-      <c r="E77" s="10">
-        <v>31.76</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B78" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="8">
-        <v>55.3</v>
-      </c>
-      <c r="D78" s="8">
-        <v>-2.75</v>
-      </c>
-      <c r="E78" s="9">
-        <v>-58.05</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B79" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="8">
-        <v>-44.01</v>
-      </c>
-      <c r="D79" s="8">
-        <v>-7.05</v>
-      </c>
-      <c r="E79" s="10">
-        <v>36.96</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B80" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="8">
-        <v>-41.47</v>
-      </c>
-      <c r="D80" s="8">
-        <v>-43.49</v>
-      </c>
-      <c r="E80" s="9">
-        <v>-2.02</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B81" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="8">
-        <v>-37.04</v>
-      </c>
-      <c r="D81" s="8">
-        <v>-36.37</v>
-      </c>
-      <c r="E81" s="10">
-        <v>0.67</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B82" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C82" s="8">
-        <v>104.96</v>
-      </c>
-      <c r="D82" s="8">
-        <v>91.08</v>
-      </c>
-      <c r="E82" s="9">
-        <v>-13.88</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="A83" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B83" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C83" s="8">
-        <v>-19.98</v>
-      </c>
-      <c r="D83" s="8">
-        <v>-28.27</v>
-      </c>
-      <c r="E83" s="9">
-        <v>-8.289999999999999</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5">
-      <c r="A84" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B84" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C84" s="8">
-        <v>21.59</v>
-      </c>
-      <c r="D84" s="8">
-        <v>-53.17</v>
-      </c>
-      <c r="E84" s="9">
-        <v>-74.76000000000001</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5">
-      <c r="A85" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B85" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C85" s="8">
-        <v>-40.6</v>
-      </c>
-      <c r="D85" s="8">
+      <c r="C80" s="6">
         <v>-34.57</v>
       </c>
-      <c r="E85" s="10">
-        <v>6.03</v>
+      <c r="D80" s="6">
+        <v>-52.97</v>
+      </c>
+      <c r="E80" s="8">
+        <v>-18.4</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3602,60 +3455,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="G1" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="H1" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="I1" s="11" t="s">
-        <v>89</v>
+      <c r="B1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="13">
+      <c r="B2" s="11">
         <v>48.16</v>
       </c>
-      <c r="C2" s="14">
+      <c r="C2" s="12">
         <v>9</v>
       </c>
-      <c r="D2" s="13">
-        <v>42.4</v>
-      </c>
-      <c r="E2" s="13">
+      <c r="D2" s="11">
+        <v>44.2</v>
+      </c>
+      <c r="E2" s="11">
         <v>40</v>
       </c>
-      <c r="F2" s="13">
-        <v>-3.7</v>
-      </c>
-      <c r="G2" s="13">
-        <v>4.9</v>
-      </c>
-      <c r="H2" s="13">
+      <c r="F2" s="11">
+        <v>-2.3</v>
+      </c>
+      <c r="G2" s="11">
+        <v>7.6</v>
+      </c>
+      <c r="H2" s="11">
         <v>55.4</v>
       </c>
-      <c r="I2" s="13">
+      <c r="I2" s="11">
         <v>40</v>
       </c>
     </row>
@@ -3757,61 +3610,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G1" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="H1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="I1" s="13" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="16">
-        <v>0.3421</v>
-      </c>
-      <c r="B2" s="16">
-        <v>0.3408</v>
-      </c>
-      <c r="C2" s="16">
-        <v>0.1996</v>
-      </c>
-      <c r="D2" s="16">
-        <v>0.198</v>
-      </c>
-      <c r="E2" s="16">
-        <v>0.1246</v>
-      </c>
-      <c r="F2" s="16">
-        <v>0.06849999999999999</v>
-      </c>
-      <c r="G2" s="16">
-        <v>0.0516</v>
-      </c>
-      <c r="H2" s="16">
-        <v>-0.015</v>
-      </c>
-      <c r="I2" s="16">
-        <v>-0.108</v>
+      <c r="A2" s="14">
+        <v>0.3596</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.3425</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.2017</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.1923</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.1277</v>
+      </c>
+      <c r="F2" s="14">
+        <v>0.0626</v>
+      </c>
+      <c r="G2" s="14">
+        <v>0.0487</v>
+      </c>
+      <c r="H2" s="14">
+        <v>-0.008699999999999999</v>
+      </c>
+      <c r="I2" s="14">
+        <v>-0.1035</v>
       </c>
     </row>
   </sheetData>

--- a/MAHINDRA_GROUP_Technical_Metrics.xlsx
+++ b/MAHINDRA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="75">
   <si>
     <t>Symbol</t>
   </si>
@@ -193,19 +193,19 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Overbought Entry</t>
-  </si>
-  <si>
-    <t>63.1 → 72.1</t>
-  </si>
-  <si>
-    <t>⚠️ CAUTION</t>
-  </si>
-  <si>
-    <t>63.1</t>
-  </si>
-  <si>
-    <t>72.1</t>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>41.5 → 59.6</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>41.5</t>
+  </si>
+  <si>
+    <t>59.6</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -257,7 +257,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -291,13 +291,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -311,7 +304,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -333,12 +326,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF4A6FA5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -431,11 +418,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -444,7 +431,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -943,10 +930,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>385.35</v>
+        <v>383.55</v>
       </c>
       <c r="D2">
-        <v>0.36</v>
+        <v>-0.47</v>
       </c>
       <c r="E2">
         <v>490.2</v>
@@ -955,46 +942,46 @@
         <v>381.86</v>
       </c>
       <c r="G2">
-        <v>-21.39</v>
+        <v>-21.76</v>
       </c>
       <c r="H2">
-        <v>0.91</v>
+        <v>0.44</v>
       </c>
       <c r="I2">
-        <v>-1.18</v>
+        <v>-1.92</v>
       </c>
       <c r="J2">
-        <v>-6.08</v>
+        <v>-6.57</v>
       </c>
       <c r="K2">
-        <v>-12</v>
+        <v>-12.91</v>
       </c>
       <c r="L2">
-        <v>-2.08</v>
+        <v>-2.59</v>
       </c>
       <c r="M2">
-        <v>12.77</v>
+        <v>12.67</v>
       </c>
       <c r="N2">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="O2">
         <v>37</v>
       </c>
       <c r="P2">
-        <v>387.24</v>
+        <v>385.74</v>
       </c>
       <c r="Q2">
-        <v>399.62</v>
+        <v>398.33</v>
       </c>
       <c r="R2">
-        <v>426.73</v>
+        <v>425.23</v>
       </c>
       <c r="S2">
-        <v>436.09</v>
+        <v>435.92</v>
       </c>
       <c r="T2">
-        <v>-11.64</v>
+        <v>-12.01</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1009,34 +996,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>26.75</v>
+        <v>25.63</v>
       </c>
       <c r="Z2">
-        <v>-10.95</v>
+        <v>-10.88</v>
       </c>
       <c r="AA2">
         <v>-10.86</v>
       </c>
       <c r="AB2">
-        <v>-0.09</v>
+        <v>-0.02</v>
       </c>
       <c r="AC2">
-        <v>6.03</v>
+        <v>9.75</v>
       </c>
       <c r="AD2">
-        <v>6.81</v>
+        <v>6.82</v>
       </c>
       <c r="AE2">
-        <v>8.24</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AF2">
-        <v>-56</v>
+        <v>-45.95</v>
       </c>
       <c r="AG2">
-        <v>418.87</v>
+        <v>418.25</v>
       </c>
       <c r="AH2">
-        <v>380.38</v>
+        <v>378.4</v>
       </c>
       <c r="AI2">
         <v>409.34</v>
@@ -1045,7 +1032,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>62.3</v>
+        <v>59.98</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1056,10 +1043,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>3170</v>
+        <v>3160</v>
       </c>
       <c r="D3">
-        <v>0.63</v>
+        <v>-0.32</v>
       </c>
       <c r="E3">
         <v>3802.4</v>
@@ -1068,46 +1055,46 @@
         <v>2931.1</v>
       </c>
       <c r="G3">
-        <v>-16.63</v>
+        <v>-16.89</v>
       </c>
       <c r="H3">
-        <v>8.15</v>
+        <v>7.81</v>
       </c>
       <c r="I3">
-        <v>-4.92</v>
+        <v>-3.72</v>
       </c>
       <c r="J3">
-        <v>-6.93</v>
+        <v>-9.77</v>
       </c>
       <c r="K3">
-        <v>6.88</v>
+        <v>5.68</v>
       </c>
       <c r="L3">
-        <v>-1.99</v>
+        <v>-3.83</v>
       </c>
       <c r="M3">
-        <v>34.25</v>
+        <v>34.18</v>
       </c>
       <c r="N3">
         <v>45</v>
       </c>
       <c r="O3">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="P3">
-        <v>3210.2</v>
+        <v>3185.8</v>
       </c>
       <c r="Q3">
-        <v>3363.57</v>
+        <v>3345.72</v>
       </c>
       <c r="R3">
-        <v>3275.27</v>
+        <v>3276.61</v>
       </c>
       <c r="S3">
-        <v>3333.72</v>
+        <v>3330.91</v>
       </c>
       <c r="T3">
-        <v>-4.91</v>
+        <v>-5.13</v>
       </c>
       <c r="U3" t="s">
         <v>48</v>
@@ -1122,43 +1109,43 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>34.74</v>
+        <v>34</v>
       </c>
       <c r="Z3">
-        <v>-29.59</v>
+        <v>-37.14</v>
       </c>
       <c r="AA3">
-        <v>8.23</v>
+        <v>-0.85</v>
       </c>
       <c r="AB3">
-        <v>-37.82</v>
+        <v>-36.3</v>
       </c>
       <c r="AC3">
-        <v>3.28</v>
+        <v>5.67</v>
       </c>
       <c r="AD3">
-        <v>1.09</v>
+        <v>2.98</v>
       </c>
       <c r="AE3">
-        <v>70.69</v>
+        <v>68</v>
       </c>
       <c r="AF3">
-        <v>-20.35</v>
+        <v>-7.91</v>
       </c>
       <c r="AG3">
-        <v>3568.01</v>
+        <v>3556.01</v>
       </c>
       <c r="AH3">
-        <v>3159.13</v>
+        <v>3135.43</v>
       </c>
       <c r="AI3">
-        <v>3376.81</v>
+        <v>3365.49</v>
       </c>
       <c r="AJ3" t="s">
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>47.86</v>
+        <v>51.45</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1169,58 +1156,58 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>373.65</v>
+        <v>372.35</v>
       </c>
       <c r="D4">
-        <v>-0.64</v>
+        <v>-0.35</v>
       </c>
       <c r="E4">
         <v>412.3</v>
       </c>
       <c r="F4">
-        <v>259.7</v>
+        <v>262.9</v>
       </c>
       <c r="G4">
-        <v>-9.369999999999999</v>
+        <v>-9.69</v>
       </c>
       <c r="H4">
-        <v>43.88</v>
+        <v>41.63</v>
       </c>
       <c r="I4">
-        <v>-0.78</v>
+        <v>-0.17</v>
       </c>
       <c r="J4">
-        <v>-3.9</v>
+        <v>-8.84</v>
       </c>
       <c r="K4">
-        <v>33.09</v>
+        <v>30.65</v>
       </c>
       <c r="L4">
-        <v>43.33</v>
+        <v>43.38</v>
       </c>
       <c r="M4">
-        <v>19.23</v>
+        <v>18.85</v>
       </c>
       <c r="N4">
         <v>99</v>
       </c>
       <c r="O4">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="P4">
-        <v>371.19</v>
+        <v>371.06</v>
       </c>
       <c r="Q4">
-        <v>384.18</v>
+        <v>382.18</v>
       </c>
       <c r="R4">
-        <v>365.4</v>
+        <v>366.53</v>
       </c>
       <c r="S4">
-        <v>344.17</v>
+        <v>344.39</v>
       </c>
       <c r="T4">
-        <v>8.56</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="U4" t="s">
         <v>48</v>
@@ -1235,34 +1222,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>48.12</v>
+        <v>47.27</v>
       </c>
       <c r="Z4">
-        <v>0.33</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AA4">
-        <v>3.72</v>
+        <v>2.96</v>
       </c>
       <c r="AB4">
-        <v>-3.39</v>
+        <v>-3.03</v>
       </c>
       <c r="AC4">
-        <v>38.42</v>
+        <v>44.08</v>
       </c>
       <c r="AD4">
-        <v>23.12</v>
+        <v>35.57</v>
       </c>
       <c r="AE4">
-        <v>11.84</v>
+        <v>11.66</v>
       </c>
       <c r="AF4">
-        <v>27.05</v>
+        <v>-11.85</v>
       </c>
       <c r="AG4">
-        <v>406.73</v>
+        <v>401.02</v>
       </c>
       <c r="AH4">
-        <v>361.63</v>
+        <v>363.35</v>
       </c>
       <c r="AI4">
         <v>357.72</v>
@@ -1271,7 +1258,7 @@
         <v>50</v>
       </c>
       <c r="AK4">
-        <v>23.04</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1282,10 +1269,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>362.4</v>
+        <v>360.15</v>
       </c>
       <c r="D5">
-        <v>-0.19</v>
+        <v>-0.62</v>
       </c>
       <c r="E5">
         <v>421.7</v>
@@ -1294,46 +1281,46 @@
         <v>294.25</v>
       </c>
       <c r="G5">
-        <v>-14.06</v>
+        <v>-14.6</v>
       </c>
       <c r="H5">
-        <v>23.16</v>
+        <v>22.4</v>
       </c>
       <c r="I5">
-        <v>-1.4</v>
+        <v>-1.5</v>
       </c>
       <c r="J5">
-        <v>-6.21</v>
+        <v>-6.83</v>
       </c>
       <c r="K5">
-        <v>8.359999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="L5">
-        <v>3.57</v>
+        <v>1.9</v>
       </c>
       <c r="M5">
-        <v>6.26</v>
+        <v>5.35</v>
       </c>
       <c r="N5">
         <v>55</v>
       </c>
       <c r="O5">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="P5">
-        <v>361.42</v>
+        <v>360.32</v>
       </c>
       <c r="Q5">
-        <v>374.64</v>
+        <v>373.3</v>
       </c>
       <c r="R5">
-        <v>376.2</v>
+        <v>376.06</v>
       </c>
       <c r="S5">
-        <v>363.3</v>
+        <v>363.17</v>
       </c>
       <c r="T5">
-        <v>-0.25</v>
+        <v>-0.83</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1348,34 +1335,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>38.34</v>
+        <v>36.44</v>
       </c>
       <c r="Z5">
-        <v>-4.58</v>
+        <v>-4.85</v>
       </c>
       <c r="AA5">
-        <v>-2.32</v>
+        <v>-2.82</v>
       </c>
       <c r="AB5">
-        <v>-2.26</v>
+        <v>-2.03</v>
       </c>
       <c r="AC5">
-        <v>24.98</v>
+        <v>31.56</v>
       </c>
       <c r="AD5">
-        <v>14.2</v>
+        <v>23.52</v>
       </c>
       <c r="AE5">
-        <v>9.68</v>
+        <v>9.98</v>
       </c>
       <c r="AF5">
-        <v>-65.7</v>
+        <v>-37.33</v>
       </c>
       <c r="AG5">
-        <v>394</v>
+        <v>392.8</v>
       </c>
       <c r="AH5">
-        <v>355.28</v>
+        <v>353.8</v>
       </c>
       <c r="AI5">
         <v>386.7</v>
@@ -1384,7 +1371,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>42.04</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1395,10 +1382,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>405.35</v>
+        <v>403.2</v>
       </c>
       <c r="D6">
-        <v>1.26</v>
+        <v>-0.53</v>
       </c>
       <c r="E6">
         <v>442.7</v>
@@ -1407,25 +1394,25 @@
         <v>279.55</v>
       </c>
       <c r="G6">
-        <v>-8.44</v>
+        <v>-8.92</v>
       </c>
       <c r="H6">
-        <v>45</v>
+        <v>44.23</v>
       </c>
       <c r="I6">
-        <v>3.21</v>
+        <v>3</v>
       </c>
       <c r="J6">
-        <v>-2.07</v>
+        <v>0.12</v>
       </c>
       <c r="K6">
-        <v>19.94</v>
+        <v>16.77</v>
       </c>
       <c r="L6">
-        <v>26.14</v>
+        <v>26.04</v>
       </c>
       <c r="M6">
-        <v>-10.35</v>
+        <v>-10.26</v>
       </c>
       <c r="N6">
         <v>88</v>
@@ -1434,19 +1421,19 @@
         <v>77</v>
       </c>
       <c r="P6">
-        <v>395.35</v>
+        <v>397.7</v>
       </c>
       <c r="Q6">
-        <v>401.33</v>
+        <v>400.92</v>
       </c>
       <c r="R6">
-        <v>398.58</v>
+        <v>399.2</v>
       </c>
       <c r="S6">
-        <v>367.94</v>
+        <v>368.31</v>
       </c>
       <c r="T6">
-        <v>10.17</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1461,34 +1448,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>55.57</v>
+        <v>53.46</v>
       </c>
       <c r="Z6">
-        <v>-0.98</v>
+        <v>-0.52</v>
       </c>
       <c r="AA6">
-        <v>-0.32</v>
+        <v>-0.36</v>
       </c>
       <c r="AB6">
-        <v>-0.66</v>
+        <v>-0.16</v>
       </c>
       <c r="AC6">
-        <v>74.48999999999999</v>
+        <v>91.26000000000001</v>
       </c>
       <c r="AD6">
-        <v>42.93</v>
+        <v>68.97</v>
       </c>
       <c r="AE6">
-        <v>11.57</v>
+        <v>11.49</v>
       </c>
       <c r="AF6">
-        <v>-20.14</v>
+        <v>-2.97</v>
       </c>
       <c r="AG6">
-        <v>414.99</v>
+        <v>413.79</v>
       </c>
       <c r="AH6">
-        <v>387.66</v>
+        <v>388.05</v>
       </c>
       <c r="AI6">
         <v>372.35</v>
@@ -1497,7 +1484,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>20.82</v>
+        <v>22.52</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1508,13 +1495,13 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>688.1</v>
+        <v>688.95</v>
       </c>
       <c r="D7">
-        <v>5.29</v>
+        <v>0.12</v>
       </c>
       <c r="E7">
-        <v>688.1</v>
+        <v>688.95</v>
       </c>
       <c r="F7">
         <v>506.45</v>
@@ -1523,43 +1510,43 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>35.87</v>
+        <v>36.04</v>
       </c>
       <c r="I7">
-        <v>3.99</v>
+        <v>3.88</v>
       </c>
       <c r="J7">
-        <v>17.87</v>
+        <v>16.83</v>
       </c>
       <c r="K7">
-        <v>11.92</v>
+        <v>12.93</v>
       </c>
       <c r="L7">
-        <v>4.88</v>
+        <v>3.94</v>
       </c>
       <c r="M7">
-        <v>35.96</v>
+        <v>36.17</v>
       </c>
       <c r="N7">
         <v>77</v>
       </c>
       <c r="O7">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="P7">
-        <v>663.89</v>
+        <v>669.04</v>
       </c>
       <c r="Q7">
-        <v>633.49</v>
+        <v>637.55</v>
       </c>
       <c r="R7">
-        <v>605.25</v>
+        <v>606.64</v>
       </c>
       <c r="S7">
-        <v>587.25</v>
+        <v>587.87</v>
       </c>
       <c r="T7">
-        <v>17.17</v>
+        <v>17.19</v>
       </c>
       <c r="U7" t="s">
         <v>48</v>
@@ -1574,43 +1561,43 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>72.14</v>
+        <v>72.31999999999999</v>
       </c>
       <c r="Z7">
-        <v>19.16</v>
+        <v>20.84</v>
       </c>
       <c r="AA7">
-        <v>14.8</v>
+        <v>16</v>
       </c>
       <c r="AB7">
-        <v>4.36</v>
+        <v>4.83</v>
       </c>
       <c r="AC7">
-        <v>63.41</v>
+        <v>67.28</v>
       </c>
       <c r="AD7">
-        <v>62.55</v>
+        <v>60.64</v>
       </c>
       <c r="AE7">
-        <v>21.53</v>
+        <v>22.91</v>
       </c>
       <c r="AF7">
-        <v>320.45</v>
+        <v>173.51</v>
       </c>
       <c r="AG7">
-        <v>682.0599999999999</v>
+        <v>690.45</v>
       </c>
       <c r="AH7">
-        <v>584.92</v>
+        <v>584.64</v>
       </c>
       <c r="AI7">
-        <v>609.0700000000001</v>
+        <v>628.66</v>
       </c>
       <c r="AJ7" t="s">
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>69.89</v>
+        <v>71.95999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1621,58 +1608,58 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>207.4</v>
+        <v>205.53</v>
       </c>
       <c r="D8">
-        <v>-0.25</v>
+        <v>-0.9</v>
       </c>
       <c r="E8">
         <v>362.05</v>
       </c>
       <c r="F8">
-        <v>206.59</v>
+        <v>205.53</v>
       </c>
       <c r="G8">
-        <v>-42.72</v>
+        <v>-43.23</v>
       </c>
       <c r="H8">
-        <v>0.39</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <v>-1.89</v>
+        <v>-1.97</v>
       </c>
       <c r="J8">
-        <v>-10.21</v>
+        <v>-10.51</v>
       </c>
       <c r="K8">
-        <v>-1.43</v>
+        <v>-11.06</v>
       </c>
       <c r="L8">
-        <v>-41.25</v>
+        <v>-42.53</v>
       </c>
       <c r="M8">
-        <v>-0.87</v>
+        <v>-1.9</v>
       </c>
       <c r="N8">
         <v>12</v>
       </c>
       <c r="O8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P8">
-        <v>207.97</v>
+        <v>207.15</v>
       </c>
       <c r="Q8">
-        <v>218.12</v>
+        <v>216.88</v>
       </c>
       <c r="R8">
-        <v>223.76</v>
+        <v>223.05</v>
       </c>
       <c r="S8">
-        <v>260.22</v>
+        <v>259.63</v>
       </c>
       <c r="T8">
-        <v>-20.3</v>
+        <v>-20.84</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1687,43 +1674,43 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>31.63</v>
+        <v>29.64</v>
       </c>
       <c r="Z8">
-        <v>-4.8</v>
+        <v>-5.01</v>
       </c>
       <c r="AA8">
-        <v>-3.57</v>
+        <v>-3.85</v>
       </c>
       <c r="AB8">
-        <v>-1.23</v>
+        <v>-1.15</v>
       </c>
       <c r="AC8">
-        <v>9.43</v>
+        <v>10.25</v>
       </c>
       <c r="AD8">
-        <v>4.67</v>
+        <v>8.08</v>
       </c>
       <c r="AE8">
-        <v>5.86</v>
+        <v>5.71</v>
       </c>
       <c r="AF8">
-        <v>57.1</v>
+        <v>-6.44</v>
       </c>
       <c r="AG8">
-        <v>233.23</v>
+        <v>231.85</v>
       </c>
       <c r="AH8">
-        <v>203.01</v>
+        <v>201.92</v>
       </c>
       <c r="AI8">
-        <v>225.7</v>
+        <v>223.82</v>
       </c>
       <c r="AJ8" t="s">
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>42.56</v>
+        <v>43.27</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1734,10 +1721,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>3557.8</v>
+        <v>3648</v>
       </c>
       <c r="D9">
-        <v>0.09</v>
+        <v>2.54</v>
       </c>
       <c r="E9">
         <v>4497.5</v>
@@ -1746,46 +1733,46 @@
         <v>3308.9</v>
       </c>
       <c r="G9">
-        <v>-20.89</v>
+        <v>-18.89</v>
       </c>
       <c r="H9">
-        <v>7.52</v>
+        <v>10.25</v>
       </c>
       <c r="I9">
-        <v>0.37</v>
+        <v>2.2</v>
       </c>
       <c r="J9">
+        <v>1.32</v>
+      </c>
+      <c r="K9">
+        <v>-3.5</v>
+      </c>
+      <c r="L9">
+        <v>-9.35</v>
+      </c>
+      <c r="M9">
+        <v>19.99</v>
+      </c>
+      <c r="N9">
+        <v>34</v>
+      </c>
+      <c r="O9">
+        <v>42</v>
+      </c>
+      <c r="P9">
+        <v>3567.82</v>
+      </c>
+      <c r="Q9">
+        <v>3580.88</v>
+      </c>
+      <c r="R9">
+        <v>3658.41</v>
+      </c>
+      <c r="S9">
+        <v>3687.07</v>
+      </c>
+      <c r="T9">
         <v>-1.06</v>
-      </c>
-      <c r="K9">
-        <v>-4.69</v>
-      </c>
-      <c r="L9">
-        <v>-12.34</v>
-      </c>
-      <c r="M9">
-        <v>20.17</v>
-      </c>
-      <c r="N9">
-        <v>23</v>
-      </c>
-      <c r="O9">
-        <v>36</v>
-      </c>
-      <c r="P9">
-        <v>3552.08</v>
-      </c>
-      <c r="Q9">
-        <v>3578.6</v>
-      </c>
-      <c r="R9">
-        <v>3664.67</v>
-      </c>
-      <c r="S9">
-        <v>3687.74</v>
-      </c>
-      <c r="T9">
-        <v>-3.52</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1800,34 +1787,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>41.45</v>
+        <v>59.59</v>
       </c>
       <c r="Z9">
-        <v>-28.63</v>
+        <v>-19.59</v>
       </c>
       <c r="AA9">
-        <v>-32.06</v>
+        <v>-29.57</v>
       </c>
       <c r="AB9">
-        <v>3.43</v>
+        <v>9.98</v>
       </c>
       <c r="AC9">
-        <v>52.77</v>
+        <v>79.41</v>
       </c>
       <c r="AD9">
-        <v>36.59</v>
+        <v>53.3</v>
       </c>
       <c r="AE9">
-        <v>58.17</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="AF9">
-        <v>10.08</v>
+        <v>378.84</v>
       </c>
       <c r="AG9">
-        <v>3643.09</v>
+        <v>3651.82</v>
       </c>
       <c r="AH9">
-        <v>3514.11</v>
+        <v>3509.95</v>
       </c>
       <c r="AI9">
         <v>3684.57</v>
@@ -1836,7 +1823,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>25.32</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1847,10 +1834,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>1596.9</v>
+        <v>1564</v>
       </c>
       <c r="D10">
-        <v>-0.07000000000000001</v>
+        <v>-2.06</v>
       </c>
       <c r="E10">
         <v>1768.4</v>
@@ -1859,46 +1846,46 @@
         <v>1326.2</v>
       </c>
       <c r="G10">
-        <v>-9.699999999999999</v>
+        <v>-11.56</v>
       </c>
       <c r="H10">
-        <v>20.41</v>
+        <v>17.93</v>
       </c>
       <c r="I10">
-        <v>-2.68</v>
+        <v>-3.93</v>
       </c>
       <c r="J10">
-        <v>-2.16</v>
+        <v>-4.34</v>
       </c>
       <c r="K10">
-        <v>6.22</v>
+        <v>5.41</v>
       </c>
       <c r="L10">
-        <v>6.66</v>
+        <v>4.79</v>
       </c>
       <c r="M10">
-        <v>4.87</v>
+        <v>4.8</v>
       </c>
       <c r="N10">
         <v>66</v>
       </c>
       <c r="O10">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="P10">
-        <v>1616.78</v>
+        <v>1603.98</v>
       </c>
       <c r="Q10">
-        <v>1610.62</v>
+        <v>1606.82</v>
       </c>
       <c r="R10">
-        <v>1563.22</v>
+        <v>1565.83</v>
       </c>
       <c r="S10">
-        <v>1516.26</v>
+        <v>1516.91</v>
       </c>
       <c r="T10">
-        <v>5.32</v>
+        <v>3.1</v>
       </c>
       <c r="U10" t="s">
         <v>48</v>
@@ -1913,34 +1900,34 @@
         <v>3</v>
       </c>
       <c r="Y10">
-        <v>49.24</v>
+        <v>42.34</v>
       </c>
       <c r="Z10">
-        <v>7.97</v>
+        <v>3.79</v>
       </c>
       <c r="AA10">
-        <v>11.66</v>
+        <v>10.08</v>
       </c>
       <c r="AB10">
-        <v>-3.69</v>
+        <v>-6.29</v>
       </c>
       <c r="AC10">
-        <v>40.83</v>
+        <v>18.98</v>
       </c>
       <c r="AD10">
-        <v>57.16</v>
+        <v>39.43</v>
       </c>
       <c r="AE10">
-        <v>36.61</v>
+        <v>37.68</v>
       </c>
       <c r="AF10">
-        <v>-52.97</v>
+        <v>-14.75</v>
       </c>
       <c r="AG10">
-        <v>1658.23</v>
+        <v>1656.64</v>
       </c>
       <c r="AH10">
-        <v>1563.01</v>
+        <v>1557</v>
       </c>
       <c r="AI10">
         <v>1527.05</v>
@@ -1949,7 +1936,7 @@
         <v>50</v>
       </c>
       <c r="AK10">
-        <v>24.5</v>
+        <v>26.9</v>
       </c>
     </row>
   </sheetData>
@@ -2090,7 +2077,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F80"/>
+  <dimension ref="A1:F79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2130,7 +2117,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2182,13 +2169,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="6">
-        <v>-7.49</v>
+        <v>-6.08</v>
       </c>
       <c r="D7" s="6">
-        <v>-6.08</v>
+        <v>-6.57</v>
       </c>
       <c r="E7" s="7">
-        <v>1.41</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2199,13 +2186,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-8.84</v>
+        <v>-6.93</v>
       </c>
       <c r="D8" s="6">
-        <v>-6.93</v>
+        <v>-9.77</v>
       </c>
       <c r="E8" s="7">
-        <v>1.91</v>
+        <v>-2.84</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2216,13 +2203,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-5.61</v>
+        <v>-3.9</v>
       </c>
       <c r="D9" s="6">
-        <v>-3.9</v>
+        <v>-8.84</v>
       </c>
       <c r="E9" s="7">
-        <v>1.71</v>
+        <v>-4.94</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2233,13 +2220,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-5.16</v>
+        <v>-6.21</v>
       </c>
       <c r="D10" s="6">
-        <v>-6.21</v>
-      </c>
-      <c r="E10" s="8">
-        <v>-1.05</v>
+        <v>-6.83</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-0.62</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2250,13 +2237,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-3.19</v>
+        <v>-2.07</v>
       </c>
       <c r="D11" s="6">
-        <v>-2.07</v>
-      </c>
-      <c r="E11" s="7">
-        <v>1.12</v>
+        <v>0.12</v>
+      </c>
+      <c r="E11" s="8">
+        <v>2.19</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2267,13 +2254,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>12.17</v>
+        <v>17.87</v>
       </c>
       <c r="D12" s="6">
-        <v>17.87</v>
+        <v>16.83</v>
       </c>
       <c r="E12" s="7">
-        <v>5.7</v>
+        <v>-1.04</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2284,13 +2271,13 @@
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-10.86</v>
+        <v>-10.21</v>
       </c>
       <c r="D13" s="6">
-        <v>-10.21</v>
+        <v>-10.51</v>
       </c>
       <c r="E13" s="7">
-        <v>0.65</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2301,13 +2288,13 @@
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>-1.5</v>
+        <v>-1.06</v>
       </c>
       <c r="D14" s="6">
-        <v>-1.06</v>
-      </c>
-      <c r="E14" s="7">
-        <v>0.44</v>
+        <v>1.32</v>
+      </c>
+      <c r="E14" s="8">
+        <v>2.38</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2318,13 +2305,13 @@
         <v>9</v>
       </c>
       <c r="C15" s="6">
-        <v>-3.15</v>
+        <v>-2.16</v>
       </c>
       <c r="D15" s="6">
-        <v>-2.16</v>
+        <v>-4.34</v>
       </c>
       <c r="E15" s="7">
-        <v>0.99</v>
+        <v>-2.18</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2335,13 +2322,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>-2.67</v>
+        <v>-1.18</v>
       </c>
       <c r="D16" s="6">
-        <v>-1.18</v>
+        <v>-1.92</v>
       </c>
       <c r="E16" s="7">
-        <v>1.49</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2352,13 +2339,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>-5.41</v>
+        <v>-4.92</v>
       </c>
       <c r="D17" s="6">
-        <v>-4.92</v>
-      </c>
-      <c r="E17" s="7">
-        <v>0.49</v>
+        <v>-3.72</v>
+      </c>
+      <c r="E17" s="8">
+        <v>1.2</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2369,13 +2356,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>-1.9</v>
+        <v>-0.78</v>
       </c>
       <c r="D18" s="6">
-        <v>-0.78</v>
-      </c>
-      <c r="E18" s="7">
-        <v>1.12</v>
+        <v>-0.17</v>
+      </c>
+      <c r="E18" s="8">
+        <v>0.61</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2386,13 +2373,13 @@
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>-1.51</v>
+        <v>-1.4</v>
       </c>
       <c r="D19" s="6">
-        <v>-1.4</v>
+        <v>-1.5</v>
       </c>
       <c r="E19" s="7">
-        <v>0.11</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2403,13 +2390,13 @@
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>2.22</v>
+        <v>3.21</v>
       </c>
       <c r="D20" s="6">
-        <v>3.21</v>
+        <v>3</v>
       </c>
       <c r="E20" s="7">
-        <v>0.99</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2420,13 +2407,13 @@
         <v>8</v>
       </c>
       <c r="C21" s="6">
-        <v>1.78</v>
+        <v>3.99</v>
       </c>
       <c r="D21" s="6">
-        <v>3.99</v>
+        <v>3.88</v>
       </c>
       <c r="E21" s="7">
-        <v>2.21</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2437,13 +2424,13 @@
         <v>8</v>
       </c>
       <c r="C22" s="6">
-        <v>-1.57</v>
+        <v>-1.89</v>
       </c>
       <c r="D22" s="6">
-        <v>-1.89</v>
-      </c>
-      <c r="E22" s="8">
-        <v>-0.32</v>
+        <v>-1.97</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-0.08</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2454,13 +2441,13 @@
         <v>8</v>
       </c>
       <c r="C23" s="6">
-        <v>0.18</v>
+        <v>0.37</v>
       </c>
       <c r="D23" s="6">
-        <v>0.37</v>
-      </c>
-      <c r="E23" s="7">
-        <v>0.19</v>
+        <v>2.2</v>
+      </c>
+      <c r="E23" s="8">
+        <v>1.83</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2471,13 +2458,13 @@
         <v>8</v>
       </c>
       <c r="C24" s="6">
-        <v>0.82</v>
+        <v>-2.68</v>
       </c>
       <c r="D24" s="6">
-        <v>-2.68</v>
-      </c>
-      <c r="E24" s="8">
-        <v>-3.5</v>
+        <v>-3.93</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-1.25</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2488,13 +2475,13 @@
         <v>11</v>
       </c>
       <c r="C25" s="6">
-        <v>0.6</v>
+        <v>-2.08</v>
       </c>
       <c r="D25" s="6">
-        <v>-2.08</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-2.68</v>
+        <v>-2.59</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-0.51</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2505,13 +2492,13 @@
         <v>11</v>
       </c>
       <c r="C26" s="6">
-        <v>-4.99</v>
+        <v>-1.99</v>
       </c>
       <c r="D26" s="6">
-        <v>-1.99</v>
+        <v>-3.83</v>
       </c>
       <c r="E26" s="7">
-        <v>3</v>
+        <v>-1.84</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2522,13 +2509,13 @@
         <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>46.04</v>
+        <v>43.33</v>
       </c>
       <c r="D27" s="6">
-        <v>43.33</v>
+        <v>43.38</v>
       </c>
       <c r="E27" s="8">
-        <v>-2.71</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2539,13 +2526,13 @@
         <v>11</v>
       </c>
       <c r="C28" s="6">
-        <v>4</v>
+        <v>3.57</v>
       </c>
       <c r="D28" s="6">
-        <v>3.57</v>
-      </c>
-      <c r="E28" s="8">
-        <v>-0.43</v>
+        <v>1.9</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-1.67</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2556,13 +2543,13 @@
         <v>11</v>
       </c>
       <c r="C29" s="6">
-        <v>26.5</v>
+        <v>26.14</v>
       </c>
       <c r="D29" s="6">
-        <v>26.14</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-0.36</v>
+        <v>26.04</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-0.1</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2573,13 +2560,13 @@
         <v>11</v>
       </c>
       <c r="C30" s="6">
-        <v>0.75</v>
+        <v>4.88</v>
       </c>
       <c r="D30" s="6">
-        <v>4.88</v>
+        <v>3.94</v>
       </c>
       <c r="E30" s="7">
-        <v>4.13</v>
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2590,13 +2577,13 @@
         <v>11</v>
       </c>
       <c r="C31" s="6">
-        <v>-40.53</v>
+        <v>-41.25</v>
       </c>
       <c r="D31" s="6">
-        <v>-41.25</v>
-      </c>
-      <c r="E31" s="8">
-        <v>-0.72</v>
+        <v>-42.53</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-1.28</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2607,13 +2594,13 @@
         <v>11</v>
       </c>
       <c r="C32" s="6">
-        <v>-13.46</v>
+        <v>-12.34</v>
       </c>
       <c r="D32" s="6">
-        <v>-12.34</v>
-      </c>
-      <c r="E32" s="7">
-        <v>1.12</v>
+        <v>-9.35</v>
+      </c>
+      <c r="E32" s="8">
+        <v>2.99</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2624,13 +2611,13 @@
         <v>11</v>
       </c>
       <c r="C33" s="6">
-        <v>7.26</v>
+        <v>6.66</v>
       </c>
       <c r="D33" s="6">
-        <v>6.66</v>
-      </c>
-      <c r="E33" s="8">
-        <v>-0.6</v>
+        <v>4.79</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-1.87</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2641,13 +2628,13 @@
         <v>10</v>
       </c>
       <c r="C34" s="6">
-        <v>-15.06</v>
+        <v>-12</v>
       </c>
       <c r="D34" s="6">
-        <v>-12</v>
+        <v>-12.91</v>
       </c>
       <c r="E34" s="7">
-        <v>3.06</v>
+        <v>-0.91</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2658,13 +2645,13 @@
         <v>10</v>
       </c>
       <c r="C35" s="6">
-        <v>3.6</v>
+        <v>6.88</v>
       </c>
       <c r="D35" s="6">
-        <v>6.88</v>
+        <v>5.68</v>
       </c>
       <c r="E35" s="7">
-        <v>3.28</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2675,13 +2662,13 @@
         <v>10</v>
       </c>
       <c r="C36" s="6">
-        <v>29.74</v>
+        <v>33.09</v>
       </c>
       <c r="D36" s="6">
-        <v>33.09</v>
+        <v>30.65</v>
       </c>
       <c r="E36" s="7">
-        <v>3.35</v>
+        <v>-2.44</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2692,13 +2679,13 @@
         <v>10</v>
       </c>
       <c r="C37" s="6">
-        <v>7.27</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="D37" s="6">
-        <v>8.359999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="E37" s="7">
-        <v>1.09</v>
+        <v>-0.76</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2709,13 +2696,13 @@
         <v>10</v>
       </c>
       <c r="C38" s="6">
-        <v>14.72</v>
+        <v>19.94</v>
       </c>
       <c r="D38" s="6">
-        <v>19.94</v>
+        <v>16.77</v>
       </c>
       <c r="E38" s="7">
-        <v>5.22</v>
+        <v>-3.17</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2726,13 +2713,13 @@
         <v>10</v>
       </c>
       <c r="C39" s="6">
-        <v>4.74</v>
+        <v>11.92</v>
       </c>
       <c r="D39" s="6">
-        <v>11.92</v>
-      </c>
-      <c r="E39" s="7">
-        <v>7.18</v>
+        <v>12.93</v>
+      </c>
+      <c r="E39" s="8">
+        <v>1.01</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2743,13 +2730,13 @@
         <v>10</v>
       </c>
       <c r="C40" s="6">
-        <v>-3.53</v>
+        <v>-1.43</v>
       </c>
       <c r="D40" s="6">
-        <v>-1.43</v>
+        <v>-11.06</v>
       </c>
       <c r="E40" s="7">
-        <v>2.1</v>
+        <v>-9.630000000000001</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2760,13 +2747,13 @@
         <v>10</v>
       </c>
       <c r="C41" s="6">
-        <v>-4.79</v>
+        <v>-4.69</v>
       </c>
       <c r="D41" s="6">
-        <v>-4.69</v>
-      </c>
-      <c r="E41" s="7">
-        <v>0.1</v>
+        <v>-3.5</v>
+      </c>
+      <c r="E41" s="8">
+        <v>1.19</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2777,13 +2764,13 @@
         <v>10</v>
       </c>
       <c r="C42" s="6">
-        <v>7.72</v>
+        <v>6.22</v>
       </c>
       <c r="D42" s="6">
-        <v>6.22</v>
-      </c>
-      <c r="E42" s="8">
-        <v>-1.5</v>
+        <v>5.41</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2794,13 +2781,13 @@
         <v>6</v>
       </c>
       <c r="C43" s="6">
-        <v>-21.67</v>
+        <v>-21.39</v>
       </c>
       <c r="D43" s="6">
-        <v>-21.39</v>
+        <v>-21.76</v>
       </c>
       <c r="E43" s="7">
-        <v>0.28</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2811,13 +2798,13 @@
         <v>6</v>
       </c>
       <c r="C44" s="6">
-        <v>-17.16</v>
+        <v>-16.63</v>
       </c>
       <c r="D44" s="6">
-        <v>-16.63</v>
+        <v>-16.89</v>
       </c>
       <c r="E44" s="7">
-        <v>0.53</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2828,13 +2815,13 @@
         <v>6</v>
       </c>
       <c r="C45" s="6">
-        <v>-8.789999999999999</v>
+        <v>-9.369999999999999</v>
       </c>
       <c r="D45" s="6">
-        <v>-9.369999999999999</v>
-      </c>
-      <c r="E45" s="8">
-        <v>-0.58</v>
+        <v>-9.69</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-0.32</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2845,13 +2832,13 @@
         <v>6</v>
       </c>
       <c r="C46" s="6">
-        <v>-13.9</v>
+        <v>-14.06</v>
       </c>
       <c r="D46" s="6">
-        <v>-14.06</v>
-      </c>
-      <c r="E46" s="8">
-        <v>-0.16</v>
+        <v>-14.6</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-0.54</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2862,574 +2849,557 @@
         <v>6</v>
       </c>
       <c r="C47" s="6">
-        <v>-9.58</v>
+        <v>-8.44</v>
       </c>
       <c r="D47" s="6">
-        <v>-8.44</v>
+        <v>-8.92</v>
       </c>
       <c r="E47" s="7">
-        <v>1.14</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C48" s="6">
-        <v>-1.74</v>
+        <v>-42.72</v>
       </c>
       <c r="D48" s="6">
-        <v>0</v>
+        <v>-43.23</v>
       </c>
       <c r="E48" s="7">
-        <v>1.74</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C49" s="6">
-        <v>-42.57</v>
+        <v>-20.89</v>
       </c>
       <c r="D49" s="6">
-        <v>-42.72</v>
+        <v>-18.89</v>
       </c>
       <c r="E49" s="8">
-        <v>-0.15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C50" s="6">
-        <v>-20.96</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="D50" s="6">
-        <v>-20.89</v>
+        <v>-11.56</v>
       </c>
       <c r="E50" s="7">
-        <v>0.07000000000000001</v>
+        <v>-1.86</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C51" s="6">
-        <v>-9.640000000000001</v>
+        <v>385.35</v>
       </c>
       <c r="D51" s="6">
-        <v>-9.699999999999999</v>
-      </c>
-      <c r="E51" s="8">
-        <v>-0.06</v>
+        <v>383.55</v>
+      </c>
+      <c r="E51" s="7">
+        <v>-1.8</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C52" s="6">
-        <v>383.95</v>
+        <v>3170</v>
       </c>
       <c r="D52" s="6">
-        <v>385.35</v>
+        <v>3160</v>
       </c>
       <c r="E52" s="7">
-        <v>1.4</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C53" s="6">
-        <v>3150</v>
+        <v>373.65</v>
       </c>
       <c r="D53" s="6">
-        <v>3170</v>
+        <v>372.35</v>
       </c>
       <c r="E53" s="7">
-        <v>20</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C54" s="6">
-        <v>376.05</v>
+        <v>362.4</v>
       </c>
       <c r="D54" s="6">
-        <v>373.65</v>
-      </c>
-      <c r="E54" s="8">
-        <v>-2.4</v>
+        <v>360.15</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-2.25</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C55" s="6">
-        <v>363.1</v>
+        <v>405.35</v>
       </c>
       <c r="D55" s="6">
-        <v>362.4</v>
-      </c>
-      <c r="E55" s="8">
-        <v>-0.7</v>
+        <v>403.2</v>
+      </c>
+      <c r="E55" s="7">
+        <v>-2.15</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C56" s="6">
-        <v>400.3</v>
+        <v>688.1</v>
       </c>
       <c r="D56" s="6">
-        <v>405.35</v>
-      </c>
-      <c r="E56" s="7">
-        <v>5.05</v>
+        <v>688.95</v>
+      </c>
+      <c r="E56" s="8">
+        <v>0.85</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C57" s="6">
-        <v>653.5</v>
+        <v>207.4</v>
       </c>
       <c r="D57" s="6">
-        <v>688.1</v>
+        <v>205.53</v>
       </c>
       <c r="E57" s="7">
-        <v>34.6</v>
+        <v>-1.87</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C58" s="6">
-        <v>207.91</v>
+        <v>3557.8</v>
       </c>
       <c r="D58" s="6">
-        <v>207.4</v>
+        <v>3648</v>
       </c>
       <c r="E58" s="8">
-        <v>-0.51</v>
+        <v>90.2</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C59" s="6">
-        <v>3554.7</v>
+        <v>1596.9</v>
       </c>
       <c r="D59" s="6">
-        <v>3557.8</v>
+        <v>1564</v>
       </c>
       <c r="E59" s="7">
-        <v>3.1</v>
+        <v>-32.9</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C60" s="6">
-        <v>1598</v>
+        <v>34</v>
       </c>
       <c r="D60" s="6">
-        <v>1596.9</v>
-      </c>
-      <c r="E60" s="8">
-        <v>-1.1</v>
+        <v>23</v>
+      </c>
+      <c r="E60" s="7">
+        <v>-11</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C61" s="6">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="D61" s="6">
-        <v>77</v>
-      </c>
-      <c r="E61" s="7">
+        <v>34</v>
+      </c>
+      <c r="E61" s="8">
         <v>11</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C62" s="6">
-        <v>77</v>
+        <v>26.75</v>
       </c>
       <c r="D62" s="6">
-        <v>66</v>
-      </c>
-      <c r="E62" s="8">
-        <v>-11</v>
+        <v>25.63</v>
+      </c>
+      <c r="E62" s="7">
+        <v>-1.12</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C63" s="6">
-        <v>24.37</v>
+        <v>34.74</v>
       </c>
       <c r="D63" s="6">
-        <v>26.75</v>
+        <v>34</v>
       </c>
       <c r="E63" s="7">
-        <v>2.38</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C64" s="6">
-        <v>32.01</v>
+        <v>48.12</v>
       </c>
       <c r="D64" s="6">
-        <v>34.74</v>
+        <v>47.27</v>
       </c>
       <c r="E64" s="7">
-        <v>2.73</v>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C65" s="6">
-        <v>49.66</v>
+        <v>38.34</v>
       </c>
       <c r="D65" s="6">
-        <v>48.12</v>
-      </c>
-      <c r="E65" s="8">
-        <v>-1.54</v>
+        <v>36.44</v>
+      </c>
+      <c r="E65" s="7">
+        <v>-1.9</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C66" s="6">
-        <v>38.93</v>
+        <v>55.57</v>
       </c>
       <c r="D66" s="6">
-        <v>38.34</v>
-      </c>
-      <c r="E66" s="8">
-        <v>-0.59</v>
+        <v>53.46</v>
+      </c>
+      <c r="E66" s="7">
+        <v>-2.11</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C67" s="6">
-        <v>51.39</v>
+        <v>72.14</v>
       </c>
       <c r="D67" s="6">
-        <v>55.57</v>
-      </c>
-      <c r="E67" s="7">
-        <v>4.18</v>
+        <v>72.31999999999999</v>
+      </c>
+      <c r="E67" s="8">
+        <v>0.18</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C68" s="6">
-        <v>63.09</v>
+        <v>31.63</v>
       </c>
       <c r="D68" s="6">
-        <v>72.14</v>
+        <v>29.64</v>
       </c>
       <c r="E68" s="7">
-        <v>9.050000000000001</v>
+        <v>-1.99</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C69" s="6">
-        <v>32.17</v>
+        <v>41.45</v>
       </c>
       <c r="D69" s="6">
-        <v>31.63</v>
+        <v>59.59</v>
       </c>
       <c r="E69" s="8">
-        <v>-0.54</v>
+        <v>18.14</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C70" s="6">
-        <v>40.6</v>
+        <v>49.24</v>
       </c>
       <c r="D70" s="6">
-        <v>41.45</v>
+        <v>42.34</v>
       </c>
       <c r="E70" s="7">
-        <v>0.85</v>
+        <v>-6.9</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C71" s="6">
-        <v>49.49</v>
+        <v>-56</v>
       </c>
       <c r="D71" s="6">
-        <v>49.24</v>
+        <v>-45.95</v>
       </c>
       <c r="E71" s="8">
-        <v>-0.25</v>
+        <v>10.05</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C72" s="6">
-        <v>-24.05</v>
+        <v>-20.35</v>
       </c>
       <c r="D72" s="6">
-        <v>-56</v>
+        <v>-7.91</v>
       </c>
       <c r="E72" s="8">
-        <v>-31.95</v>
+        <v>12.44</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C73" s="6">
-        <v>-2.75</v>
+        <v>27.05</v>
       </c>
       <c r="D73" s="6">
-        <v>-20.35</v>
-      </c>
-      <c r="E73" s="8">
-        <v>-17.6</v>
+        <v>-11.85</v>
+      </c>
+      <c r="E73" s="7">
+        <v>-38.9</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C74" s="6">
-        <v>-7.05</v>
+        <v>-65.7</v>
       </c>
       <c r="D74" s="6">
-        <v>27.05</v>
-      </c>
-      <c r="E74" s="7">
-        <v>34.1</v>
+        <v>-37.33</v>
+      </c>
+      <c r="E74" s="8">
+        <v>28.37</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C75" s="6">
-        <v>-43.49</v>
+        <v>-20.14</v>
       </c>
       <c r="D75" s="6">
-        <v>-65.7</v>
+        <v>-2.97</v>
       </c>
       <c r="E75" s="8">
-        <v>-22.21</v>
+        <v>17.17</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C76" s="6">
-        <v>-36.37</v>
+        <v>320.45</v>
       </c>
       <c r="D76" s="6">
-        <v>-20.14</v>
+        <v>173.51</v>
       </c>
       <c r="E76" s="7">
-        <v>16.23</v>
+        <v>-146.94</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C77" s="6">
-        <v>91.08</v>
+        <v>57.1</v>
       </c>
       <c r="D77" s="6">
-        <v>320.45</v>
+        <v>-6.44</v>
       </c>
       <c r="E77" s="7">
-        <v>229.37</v>
+        <v>-63.54</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C78" s="6">
-        <v>-28.27</v>
+        <v>10.08</v>
       </c>
       <c r="D78" s="6">
-        <v>57.1</v>
-      </c>
-      <c r="E78" s="7">
-        <v>85.37</v>
+        <v>378.84</v>
+      </c>
+      <c r="E78" s="8">
+        <v>368.76</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C79" s="6">
-        <v>-53.17</v>
+        <v>-52.97</v>
       </c>
       <c r="D79" s="6">
-        <v>10.08</v>
-      </c>
-      <c r="E79" s="7">
-        <v>63.25</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="6">
-        <v>-34.57</v>
-      </c>
-      <c r="D80" s="6">
-        <v>-52.97</v>
-      </c>
-      <c r="E80" s="8">
-        <v>-18.4</v>
+        <v>-14.75</v>
+      </c>
+      <c r="E79" s="8">
+        <v>38.22</v>
       </c>
     </row>
   </sheetData>
@@ -3494,16 +3464,16 @@
         <v>9</v>
       </c>
       <c r="D2" s="11">
-        <v>44.2</v>
+        <v>44.5</v>
       </c>
       <c r="E2" s="11">
         <v>40</v>
       </c>
       <c r="F2" s="11">
-        <v>-2.3</v>
+        <v>-3.2</v>
       </c>
       <c r="G2" s="11">
-        <v>7.6</v>
+        <v>5.7</v>
       </c>
       <c r="H2" s="11">
         <v>55.4</v>
@@ -3640,31 +3610,31 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="14">
-        <v>0.3596</v>
+        <v>0.3617</v>
       </c>
       <c r="B2" s="14">
-        <v>0.3425</v>
+        <v>0.3418</v>
       </c>
       <c r="C2" s="14">
-        <v>0.2017</v>
+        <v>0.1999</v>
       </c>
       <c r="D2" s="14">
-        <v>0.1923</v>
+        <v>0.1885</v>
       </c>
       <c r="E2" s="14">
-        <v>0.1277</v>
+        <v>0.1267</v>
       </c>
       <c r="F2" s="14">
-        <v>0.0626</v>
+        <v>0.0535</v>
       </c>
       <c r="G2" s="14">
-        <v>0.0487</v>
+        <v>0.048</v>
       </c>
       <c r="H2" s="14">
-        <v>-0.008699999999999999</v>
+        <v>-0.019</v>
       </c>
       <c r="I2" s="14">
-        <v>-0.1035</v>
+        <v>-0.1026</v>
       </c>
     </row>
   </sheetData>

--- a/MAHINDRA_GROUP_Technical_Metrics.xlsx
+++ b/MAHINDRA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="80">
   <si>
     <t>Symbol</t>
   </si>
@@ -193,19 +193,34 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>41.5 → 59.6</t>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>29.6 → 30.1</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>41.5</t>
-  </si>
-  <si>
-    <t>59.6</t>
+    <t>29.6</t>
+  </si>
+  <si>
+    <t>30.1</t>
+  </si>
+  <si>
+    <t>RSI Overbought Exit</t>
+  </si>
+  <si>
+    <t>72.3 → 67.7</t>
+  </si>
+  <si>
+    <t>🔵 COOLING</t>
+  </si>
+  <si>
+    <t>72.3</t>
+  </si>
+  <si>
+    <t>67.7</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -257,7 +272,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -298,13 +313,20 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF1F4E79"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -332,6 +354,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -407,7 +435,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -415,14 +443,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -431,7 +460,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -930,10 +959,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>383.55</v>
+        <v>383.4</v>
       </c>
       <c r="D2">
-        <v>-0.47</v>
+        <v>-0.04</v>
       </c>
       <c r="E2">
         <v>490.2</v>
@@ -942,46 +971,46 @@
         <v>381.86</v>
       </c>
       <c r="G2">
-        <v>-21.76</v>
+        <v>-21.79</v>
       </c>
       <c r="H2">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="I2">
-        <v>-1.92</v>
+        <v>-1.91</v>
       </c>
       <c r="J2">
-        <v>-6.57</v>
+        <v>-6.37</v>
       </c>
       <c r="K2">
-        <v>-12.91</v>
+        <v>-11.91</v>
       </c>
       <c r="L2">
-        <v>-2.59</v>
+        <v>-0.99</v>
       </c>
       <c r="M2">
-        <v>12.67</v>
+        <v>13.07</v>
       </c>
       <c r="N2">
         <v>23</v>
       </c>
       <c r="O2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P2">
-        <v>385.74</v>
+        <v>384.25</v>
       </c>
       <c r="Q2">
-        <v>398.33</v>
+        <v>396.85</v>
       </c>
       <c r="R2">
-        <v>425.23</v>
+        <v>423.74</v>
       </c>
       <c r="S2">
-        <v>435.92</v>
+        <v>435.79</v>
       </c>
       <c r="T2">
-        <v>-12.01</v>
+        <v>-12.02</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -996,43 +1025,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>25.63</v>
+        <v>25.54</v>
       </c>
       <c r="Z2">
-        <v>-10.88</v>
+        <v>-10.71</v>
       </c>
       <c r="AA2">
-        <v>-10.86</v>
+        <v>-10.83</v>
       </c>
       <c r="AB2">
-        <v>-0.02</v>
+        <v>0.12</v>
       </c>
       <c r="AC2">
-        <v>9.75</v>
+        <v>13.8</v>
       </c>
       <c r="AD2">
-        <v>6.82</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="AE2">
-        <v>8.199999999999999</v>
+        <v>7.89</v>
       </c>
       <c r="AF2">
-        <v>-45.95</v>
+        <v>-69.08</v>
       </c>
       <c r="AG2">
-        <v>418.25</v>
+        <v>416.58</v>
       </c>
       <c r="AH2">
-        <v>378.4</v>
+        <v>377.11</v>
       </c>
       <c r="AI2">
-        <v>409.34</v>
+        <v>408.09</v>
       </c>
       <c r="AJ2" t="s">
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>59.98</v>
+        <v>57.97</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1046,7 +1075,7 @@
         <v>3160</v>
       </c>
       <c r="D3">
-        <v>-0.32</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>3802.4</v>
@@ -1061,40 +1090,40 @@
         <v>7.81</v>
       </c>
       <c r="I3">
-        <v>-3.72</v>
+        <v>-3.04</v>
       </c>
       <c r="J3">
-        <v>-9.77</v>
+        <v>-10.15</v>
       </c>
       <c r="K3">
-        <v>5.68</v>
+        <v>7.03</v>
       </c>
       <c r="L3">
-        <v>-3.83</v>
+        <v>-9.23</v>
       </c>
       <c r="M3">
-        <v>34.18</v>
+        <v>34.13</v>
       </c>
       <c r="N3">
         <v>45</v>
       </c>
       <c r="O3">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="P3">
-        <v>3185.8</v>
+        <v>3166</v>
       </c>
       <c r="Q3">
-        <v>3345.72</v>
+        <v>3330.72</v>
       </c>
       <c r="R3">
-        <v>3276.61</v>
+        <v>3278.43</v>
       </c>
       <c r="S3">
-        <v>3330.91</v>
+        <v>3328.12</v>
       </c>
       <c r="T3">
-        <v>-5.13</v>
+        <v>-5.05</v>
       </c>
       <c r="U3" t="s">
         <v>48</v>
@@ -1112,40 +1141,40 @@
         <v>34</v>
       </c>
       <c r="Z3">
-        <v>-37.14</v>
+        <v>-42.64</v>
       </c>
       <c r="AA3">
-        <v>-0.85</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="AB3">
-        <v>-36.3</v>
+        <v>-33.43</v>
       </c>
       <c r="AC3">
+        <v>8.06</v>
+      </c>
+      <c r="AD3">
         <v>5.67</v>
       </c>
-      <c r="AD3">
-        <v>2.98</v>
-      </c>
       <c r="AE3">
-        <v>68</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="AF3">
-        <v>-7.91</v>
+        <v>-0.12</v>
       </c>
       <c r="AG3">
-        <v>3556.01</v>
+        <v>3549.3</v>
       </c>
       <c r="AH3">
-        <v>3135.43</v>
+        <v>3112.13</v>
       </c>
       <c r="AI3">
-        <v>3365.49</v>
+        <v>3333.36</v>
       </c>
       <c r="AJ3" t="s">
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>51.45</v>
+        <v>55.37</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1156,58 +1185,58 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>372.35</v>
+        <v>374.35</v>
       </c>
       <c r="D4">
-        <v>-0.35</v>
+        <v>0.54</v>
       </c>
       <c r="E4">
         <v>412.3</v>
       </c>
       <c r="F4">
-        <v>262.9</v>
+        <v>268.95</v>
       </c>
       <c r="G4">
-        <v>-9.69</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="H4">
-        <v>41.63</v>
+        <v>39.19</v>
       </c>
       <c r="I4">
-        <v>-0.17</v>
+        <v>2.73</v>
       </c>
       <c r="J4">
-        <v>-8.84</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="K4">
-        <v>30.65</v>
+        <v>35.02</v>
       </c>
       <c r="L4">
-        <v>43.38</v>
+        <v>42.39</v>
       </c>
       <c r="M4">
-        <v>18.85</v>
+        <v>19.27</v>
       </c>
       <c r="N4">
         <v>99</v>
       </c>
       <c r="O4">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P4">
-        <v>371.06</v>
+        <v>373.05</v>
       </c>
       <c r="Q4">
-        <v>382.18</v>
+        <v>380.96</v>
       </c>
       <c r="R4">
-        <v>366.53</v>
+        <v>367.71</v>
       </c>
       <c r="S4">
-        <v>344.39</v>
+        <v>344.52</v>
       </c>
       <c r="T4">
-        <v>8.119999999999999</v>
+        <v>8.66</v>
       </c>
       <c r="U4" t="s">
         <v>48</v>
@@ -1222,34 +1251,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>47.27</v>
+        <v>48.78</v>
       </c>
       <c r="Z4">
-        <v>-0.07000000000000001</v>
+        <v>-0.22</v>
       </c>
       <c r="AA4">
-        <v>2.96</v>
+        <v>2.32</v>
       </c>
       <c r="AB4">
-        <v>-3.03</v>
+        <v>-2.54</v>
       </c>
       <c r="AC4">
-        <v>44.08</v>
+        <v>45.21</v>
       </c>
       <c r="AD4">
-        <v>35.57</v>
+        <v>42.57</v>
       </c>
       <c r="AE4">
-        <v>11.66</v>
+        <v>11.74</v>
       </c>
       <c r="AF4">
-        <v>-11.85</v>
+        <v>50.35</v>
       </c>
       <c r="AG4">
-        <v>401.02</v>
+        <v>398.37</v>
       </c>
       <c r="AH4">
-        <v>363.35</v>
+        <v>363.55</v>
       </c>
       <c r="AI4">
         <v>357.72</v>
@@ -1258,7 +1287,7 @@
         <v>50</v>
       </c>
       <c r="AK4">
-        <v>22.77</v>
+        <v>19.74</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1269,10 +1298,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>360.15</v>
+        <v>366.15</v>
       </c>
       <c r="D5">
-        <v>-0.62</v>
+        <v>1.67</v>
       </c>
       <c r="E5">
         <v>421.7</v>
@@ -1281,46 +1310,46 @@
         <v>294.25</v>
       </c>
       <c r="G5">
-        <v>-14.6</v>
+        <v>-13.17</v>
       </c>
       <c r="H5">
-        <v>22.4</v>
+        <v>24.44</v>
       </c>
       <c r="I5">
-        <v>-1.5</v>
+        <v>2.58</v>
       </c>
       <c r="J5">
-        <v>-6.83</v>
+        <v>-5.35</v>
       </c>
       <c r="K5">
-        <v>7.6</v>
+        <v>12.92</v>
       </c>
       <c r="L5">
-        <v>1.9</v>
+        <v>2.74</v>
       </c>
       <c r="M5">
-        <v>5.35</v>
+        <v>5.99</v>
       </c>
       <c r="N5">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="O5">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="P5">
-        <v>360.32</v>
+        <v>362.16</v>
       </c>
       <c r="Q5">
-        <v>373.3</v>
+        <v>372.48</v>
       </c>
       <c r="R5">
-        <v>376.06</v>
+        <v>376.05</v>
       </c>
       <c r="S5">
-        <v>363.17</v>
+        <v>363.09</v>
       </c>
       <c r="T5">
-        <v>-0.83</v>
+        <v>0.84</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1332,37 +1361,37 @@
         <v>47</v>
       </c>
       <c r="X5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y5">
-        <v>36.44</v>
+        <v>44.37</v>
       </c>
       <c r="Z5">
-        <v>-4.85</v>
+        <v>-4.53</v>
       </c>
       <c r="AA5">
-        <v>-2.82</v>
+        <v>-3.17</v>
       </c>
       <c r="AB5">
-        <v>-2.03</v>
+        <v>-1.36</v>
       </c>
       <c r="AC5">
-        <v>31.56</v>
+        <v>44.8</v>
       </c>
       <c r="AD5">
-        <v>23.52</v>
+        <v>33.78</v>
       </c>
       <c r="AE5">
-        <v>9.98</v>
+        <v>10.17</v>
       </c>
       <c r="AF5">
-        <v>-37.33</v>
+        <v>-36.75</v>
       </c>
       <c r="AG5">
-        <v>392.8</v>
+        <v>391.7</v>
       </c>
       <c r="AH5">
-        <v>353.8</v>
+        <v>353.25</v>
       </c>
       <c r="AI5">
         <v>386.7</v>
@@ -1371,7 +1400,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>42.5</v>
+        <v>42.89</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1382,10 +1411,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>403.2</v>
+        <v>408.85</v>
       </c>
       <c r="D6">
-        <v>-0.53</v>
+        <v>1.4</v>
       </c>
       <c r="E6">
         <v>442.7</v>
@@ -1394,46 +1423,46 @@
         <v>279.55</v>
       </c>
       <c r="G6">
-        <v>-8.92</v>
+        <v>-7.65</v>
       </c>
       <c r="H6">
-        <v>44.23</v>
+        <v>46.25</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>5.59</v>
       </c>
       <c r="J6">
-        <v>0.12</v>
+        <v>-0.61</v>
       </c>
       <c r="K6">
-        <v>16.77</v>
+        <v>20.8</v>
       </c>
       <c r="L6">
-        <v>26.04</v>
+        <v>27.71</v>
       </c>
       <c r="M6">
-        <v>-10.26</v>
+        <v>-10.67</v>
       </c>
       <c r="N6">
         <v>88</v>
       </c>
       <c r="O6">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="P6">
-        <v>397.7</v>
+        <v>402.03</v>
       </c>
       <c r="Q6">
-        <v>400.92</v>
+        <v>400.9</v>
       </c>
       <c r="R6">
-        <v>399.2</v>
+        <v>399.9</v>
       </c>
       <c r="S6">
-        <v>368.31</v>
+        <v>368.7</v>
       </c>
       <c r="T6">
-        <v>9.470000000000001</v>
+        <v>10.89</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1448,34 +1477,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>53.46</v>
+        <v>57.97</v>
       </c>
       <c r="Z6">
-        <v>-0.52</v>
+        <v>0.3</v>
       </c>
       <c r="AA6">
-        <v>-0.36</v>
+        <v>-0.23</v>
       </c>
       <c r="AB6">
-        <v>-0.16</v>
+        <v>0.52</v>
       </c>
       <c r="AC6">
-        <v>91.26000000000001</v>
+        <v>96.08</v>
       </c>
       <c r="AD6">
-        <v>68.97</v>
+        <v>87.28</v>
       </c>
       <c r="AE6">
-        <v>11.49</v>
+        <v>11.3</v>
       </c>
       <c r="AF6">
-        <v>-2.97</v>
+        <v>-5.35</v>
       </c>
       <c r="AG6">
-        <v>413.79</v>
+        <v>413.7</v>
       </c>
       <c r="AH6">
-        <v>388.05</v>
+        <v>388.09</v>
       </c>
       <c r="AI6">
         <v>372.35</v>
@@ -1484,7 +1513,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>22.52</v>
+        <v>23.63</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1495,10 +1524,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>688.95</v>
+        <v>680.65</v>
       </c>
       <c r="D7">
-        <v>0.12</v>
+        <v>-1.2</v>
       </c>
       <c r="E7">
         <v>688.95</v>
@@ -1507,46 +1536,46 @@
         <v>506.45</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>-1.2</v>
       </c>
       <c r="H7">
-        <v>36.04</v>
+        <v>34.4</v>
       </c>
       <c r="I7">
-        <v>3.88</v>
+        <v>4.78</v>
       </c>
       <c r="J7">
-        <v>16.83</v>
+        <v>11.98</v>
       </c>
       <c r="K7">
-        <v>12.93</v>
+        <v>13.71</v>
       </c>
       <c r="L7">
-        <v>3.94</v>
+        <v>5.23</v>
       </c>
       <c r="M7">
-        <v>36.17</v>
+        <v>36</v>
       </c>
       <c r="N7">
         <v>77</v>
       </c>
       <c r="O7">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="P7">
-        <v>669.04</v>
+        <v>675.25</v>
       </c>
       <c r="Q7">
-        <v>637.55</v>
+        <v>641.83</v>
       </c>
       <c r="R7">
-        <v>606.64</v>
+        <v>608.3</v>
       </c>
       <c r="S7">
-        <v>587.87</v>
+        <v>588.42</v>
       </c>
       <c r="T7">
-        <v>17.19</v>
+        <v>15.68</v>
       </c>
       <c r="U7" t="s">
         <v>48</v>
@@ -1561,34 +1590,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>72.31999999999999</v>
+        <v>67.73</v>
       </c>
       <c r="Z7">
-        <v>20.84</v>
+        <v>21.25</v>
       </c>
       <c r="AA7">
-        <v>16</v>
+        <v>17.05</v>
       </c>
       <c r="AB7">
-        <v>4.83</v>
+        <v>4.2</v>
       </c>
       <c r="AC7">
-        <v>67.28</v>
+        <v>75.59</v>
       </c>
       <c r="AD7">
-        <v>60.64</v>
+        <v>68.76000000000001</v>
       </c>
       <c r="AE7">
-        <v>22.91</v>
+        <v>22.61</v>
       </c>
       <c r="AF7">
-        <v>173.51</v>
+        <v>-43.55</v>
       </c>
       <c r="AG7">
-        <v>690.45</v>
+        <v>694.1</v>
       </c>
       <c r="AH7">
-        <v>584.64</v>
+        <v>589.5599999999999</v>
       </c>
       <c r="AI7">
         <v>628.66</v>
@@ -1597,7 +1626,7 @@
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>71.95999999999999</v>
+        <v>73.43000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1608,10 +1637,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>205.53</v>
+        <v>205.71</v>
       </c>
       <c r="D8">
-        <v>-0.9</v>
+        <v>0.09</v>
       </c>
       <c r="E8">
         <v>362.05</v>
@@ -1620,25 +1649,25 @@
         <v>205.53</v>
       </c>
       <c r="G8">
-        <v>-43.23</v>
+        <v>-43.18</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="I8">
-        <v>-1.97</v>
+        <v>-1.25</v>
       </c>
       <c r="J8">
-        <v>-10.51</v>
+        <v>-10.68</v>
       </c>
       <c r="K8">
-        <v>-11.06</v>
+        <v>-12.65</v>
       </c>
       <c r="L8">
-        <v>-42.53</v>
+        <v>-42.89</v>
       </c>
       <c r="M8">
-        <v>-1.9</v>
+        <v>-2.84</v>
       </c>
       <c r="N8">
         <v>12</v>
@@ -1647,19 +1676,19 @@
         <v>7</v>
       </c>
       <c r="P8">
-        <v>207.15</v>
+        <v>206.63</v>
       </c>
       <c r="Q8">
-        <v>216.88</v>
+        <v>215.89</v>
       </c>
       <c r="R8">
-        <v>223.05</v>
+        <v>222.4</v>
       </c>
       <c r="S8">
-        <v>259.63</v>
+        <v>258.99</v>
       </c>
       <c r="T8">
-        <v>-20.84</v>
+        <v>-20.57</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1674,43 +1703,43 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>29.64</v>
+        <v>30.09</v>
       </c>
       <c r="Z8">
-        <v>-5.01</v>
+        <v>-5.1</v>
       </c>
       <c r="AA8">
-        <v>-3.85</v>
+        <v>-4.1</v>
       </c>
       <c r="AB8">
-        <v>-1.15</v>
+        <v>-1</v>
       </c>
       <c r="AC8">
-        <v>10.25</v>
+        <v>7.42</v>
       </c>
       <c r="AD8">
-        <v>8.08</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="AE8">
-        <v>5.71</v>
+        <v>5.54</v>
       </c>
       <c r="AF8">
-        <v>-6.44</v>
+        <v>-8.289999999999999</v>
       </c>
       <c r="AG8">
-        <v>231.85</v>
+        <v>231.06</v>
       </c>
       <c r="AH8">
-        <v>201.92</v>
+        <v>200.72</v>
       </c>
       <c r="AI8">
-        <v>223.82</v>
+        <v>222.99</v>
       </c>
       <c r="AJ8" t="s">
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>43.27</v>
+        <v>43.93</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1721,10 +1750,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>3648</v>
+        <v>3632.6</v>
       </c>
       <c r="D9">
-        <v>2.54</v>
+        <v>-0.42</v>
       </c>
       <c r="E9">
         <v>4497.5</v>
@@ -1733,46 +1762,46 @@
         <v>3308.9</v>
       </c>
       <c r="G9">
-        <v>-18.89</v>
+        <v>-19.23</v>
       </c>
       <c r="H9">
-        <v>10.25</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="I9">
-        <v>2.2</v>
+        <v>2.68</v>
       </c>
       <c r="J9">
-        <v>1.32</v>
+        <v>0.84</v>
       </c>
       <c r="K9">
-        <v>-3.5</v>
+        <v>-3.85</v>
       </c>
       <c r="L9">
-        <v>-9.35</v>
+        <v>-12</v>
       </c>
       <c r="M9">
-        <v>19.99</v>
+        <v>19.58</v>
       </c>
       <c r="N9">
         <v>34</v>
       </c>
       <c r="O9">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="P9">
-        <v>3567.82</v>
+        <v>3586.8</v>
       </c>
       <c r="Q9">
-        <v>3580.88</v>
+        <v>3582.62</v>
       </c>
       <c r="R9">
-        <v>3658.41</v>
+        <v>3651.11</v>
       </c>
       <c r="S9">
-        <v>3687.07</v>
+        <v>3686.56</v>
       </c>
       <c r="T9">
-        <v>-1.06</v>
+        <v>-1.46</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1787,34 +1816,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>59.59</v>
+        <v>56.37</v>
       </c>
       <c r="Z9">
-        <v>-19.59</v>
+        <v>-13.51</v>
       </c>
       <c r="AA9">
-        <v>-29.57</v>
+        <v>-26.36</v>
       </c>
       <c r="AB9">
-        <v>9.98</v>
+        <v>12.85</v>
       </c>
       <c r="AC9">
-        <v>79.41</v>
+        <v>91.87</v>
       </c>
       <c r="AD9">
-        <v>53.3</v>
+        <v>74.68000000000001</v>
       </c>
       <c r="AE9">
-        <v>64.09999999999999</v>
+        <v>63.93</v>
       </c>
       <c r="AF9">
-        <v>378.84</v>
+        <v>16.28</v>
       </c>
       <c r="AG9">
-        <v>3651.82</v>
+        <v>3656.93</v>
       </c>
       <c r="AH9">
-        <v>3509.95</v>
+        <v>3508.31</v>
       </c>
       <c r="AI9">
         <v>3684.57</v>
@@ -1823,7 +1852,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>30.5</v>
+        <v>34.98</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1834,10 +1863,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>1564</v>
+        <v>1559</v>
       </c>
       <c r="D10">
-        <v>-2.06</v>
+        <v>-0.32</v>
       </c>
       <c r="E10">
         <v>1768.4</v>
@@ -1846,46 +1875,46 @@
         <v>1326.2</v>
       </c>
       <c r="G10">
-        <v>-11.56</v>
+        <v>-11.84</v>
       </c>
       <c r="H10">
-        <v>17.93</v>
+        <v>17.55</v>
       </c>
       <c r="I10">
-        <v>-3.93</v>
+        <v>-4.82</v>
       </c>
       <c r="J10">
-        <v>-4.34</v>
+        <v>-4.94</v>
       </c>
       <c r="K10">
-        <v>5.41</v>
+        <v>5.42</v>
       </c>
       <c r="L10">
-        <v>4.79</v>
+        <v>4.99</v>
       </c>
       <c r="M10">
-        <v>4.8</v>
+        <v>4.85</v>
       </c>
       <c r="N10">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="O10">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="P10">
-        <v>1603.98</v>
+        <v>1588.18</v>
       </c>
       <c r="Q10">
-        <v>1606.82</v>
+        <v>1602.62</v>
       </c>
       <c r="R10">
-        <v>1565.83</v>
+        <v>1568.91</v>
       </c>
       <c r="S10">
-        <v>1516.91</v>
+        <v>1517.42</v>
       </c>
       <c r="T10">
-        <v>3.1</v>
+        <v>2.74</v>
       </c>
       <c r="U10" t="s">
         <v>48</v>
@@ -1900,34 +1929,34 @@
         <v>3</v>
       </c>
       <c r="Y10">
-        <v>42.34</v>
+        <v>41.39</v>
       </c>
       <c r="Z10">
-        <v>3.79</v>
+        <v>0.08</v>
       </c>
       <c r="AA10">
-        <v>10.08</v>
+        <v>8.08</v>
       </c>
       <c r="AB10">
-        <v>-6.29</v>
+        <v>-8.01</v>
       </c>
       <c r="AC10">
-        <v>18.98</v>
+        <v>9.23</v>
       </c>
       <c r="AD10">
-        <v>39.43</v>
+        <v>23.01</v>
       </c>
       <c r="AE10">
-        <v>37.68</v>
+        <v>37.02</v>
       </c>
       <c r="AF10">
-        <v>-14.75</v>
+        <v>-27.92</v>
       </c>
       <c r="AG10">
-        <v>1656.64</v>
+        <v>1653.74</v>
       </c>
       <c r="AH10">
-        <v>1557</v>
+        <v>1551.5</v>
       </c>
       <c r="AI10">
         <v>1527.05</v>
@@ -1936,7 +1965,7 @@
         <v>50</v>
       </c>
       <c r="AK10">
-        <v>26.9</v>
+        <v>29.29</v>
       </c>
     </row>
   </sheetData>
@@ -2077,7 +2106,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F79"/>
+  <dimension ref="A1:F78"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2117,7 +2146,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2135,1277 +2164,1263 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+    <row r="4" spans="1:6">
+      <c r="A4" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="C4" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E6" s="3" t="s">
+      <c r="B7" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="7">
+        <v>-6.57</v>
+      </c>
+      <c r="D8" s="7">
+        <v>-6.37</v>
+      </c>
+      <c r="E8" s="8">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-9.77</v>
+      </c>
+      <c r="D9" s="7">
+        <v>-10.15</v>
+      </c>
+      <c r="E9" s="9">
+        <v>-0.38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="7">
+        <v>-8.84</v>
+      </c>
+      <c r="D10" s="7">
+        <v>-9.199999999999999</v>
+      </c>
+      <c r="E10" s="9">
+        <v>-0.36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="7">
+        <v>-6.83</v>
+      </c>
+      <c r="D11" s="7">
+        <v>-5.35</v>
+      </c>
+      <c r="E11" s="8">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="7">
+        <v>0.12</v>
+      </c>
+      <c r="D12" s="7">
+        <v>-0.61</v>
+      </c>
+      <c r="E12" s="9">
+        <v>-0.73</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="7">
+        <v>16.83</v>
+      </c>
+      <c r="D13" s="7">
+        <v>11.98</v>
+      </c>
+      <c r="E13" s="9">
+        <v>-4.85</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="7">
+        <v>-10.51</v>
+      </c>
+      <c r="D14" s="7">
+        <v>-10.68</v>
+      </c>
+      <c r="E14" s="9">
+        <v>-0.17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="7">
+        <v>1.32</v>
+      </c>
+      <c r="D15" s="7">
+        <v>0.84</v>
+      </c>
+      <c r="E15" s="9">
+        <v>-0.48</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-4.34</v>
+      </c>
+      <c r="D16" s="7">
+        <v>-4.94</v>
+      </c>
+      <c r="E16" s="9">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-1.92</v>
+      </c>
+      <c r="D17" s="7">
+        <v>-1.91</v>
+      </c>
+      <c r="E17" s="8">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-3.72</v>
+      </c>
+      <c r="D18" s="7">
+        <v>-3.04</v>
+      </c>
+      <c r="E18" s="8">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="7">
+        <v>-0.17</v>
+      </c>
+      <c r="D19" s="7">
+        <v>2.73</v>
+      </c>
+      <c r="E19" s="8">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="7">
+        <v>-1.5</v>
+      </c>
+      <c r="D20" s="7">
+        <v>2.58</v>
+      </c>
+      <c r="E20" s="8">
+        <v>4.08</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="7">
+        <v>3</v>
+      </c>
+      <c r="D21" s="7">
+        <v>5.59</v>
+      </c>
+      <c r="E21" s="8">
+        <v>2.59</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="7">
+        <v>3.88</v>
+      </c>
+      <c r="D22" s="7">
+        <v>4.78</v>
+      </c>
+      <c r="E22" s="8">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="7">
+        <v>-1.97</v>
+      </c>
+      <c r="D23" s="7">
+        <v>-1.25</v>
+      </c>
+      <c r="E23" s="8">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="7">
+        <v>2.2</v>
+      </c>
+      <c r="D24" s="7">
+        <v>2.68</v>
+      </c>
+      <c r="E24" s="8">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="7">
+        <v>-3.93</v>
+      </c>
+      <c r="D25" s="7">
+        <v>-4.82</v>
+      </c>
+      <c r="E25" s="9">
+        <v>-0.89</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="7">
+        <v>-2.59</v>
+      </c>
+      <c r="D26" s="7">
+        <v>-0.99</v>
+      </c>
+      <c r="E26" s="8">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="7">
+        <v>-3.83</v>
+      </c>
+      <c r="D27" s="7">
+        <v>-9.23</v>
+      </c>
+      <c r="E27" s="9">
+        <v>-5.4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="7">
+        <v>43.38</v>
+      </c>
+      <c r="D28" s="7">
+        <v>42.39</v>
+      </c>
+      <c r="E28" s="9">
+        <v>-0.99</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="7">
+        <v>1.9</v>
+      </c>
+      <c r="D29" s="7">
+        <v>2.74</v>
+      </c>
+      <c r="E29" s="8">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="7">
+        <v>26.04</v>
+      </c>
+      <c r="D30" s="7">
+        <v>27.71</v>
+      </c>
+      <c r="E30" s="8">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="7">
+        <v>3.94</v>
+      </c>
+      <c r="D31" s="7">
+        <v>5.23</v>
+      </c>
+      <c r="E31" s="8">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="7">
+        <v>-42.53</v>
+      </c>
+      <c r="D32" s="7">
+        <v>-42.89</v>
+      </c>
+      <c r="E32" s="9">
+        <v>-0.36</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="7">
+        <v>-9.35</v>
+      </c>
+      <c r="D33" s="7">
+        <v>-12</v>
+      </c>
+      <c r="E33" s="9">
+        <v>-2.65</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="7">
+        <v>4.79</v>
+      </c>
+      <c r="D34" s="7">
+        <v>4.99</v>
+      </c>
+      <c r="E34" s="8">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="7">
+        <v>-12.91</v>
+      </c>
+      <c r="D35" s="7">
+        <v>-11.91</v>
+      </c>
+      <c r="E35" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="7">
+        <v>5.68</v>
+      </c>
+      <c r="D36" s="7">
+        <v>7.03</v>
+      </c>
+      <c r="E36" s="8">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="7">
+        <v>30.65</v>
+      </c>
+      <c r="D37" s="7">
+        <v>35.02</v>
+      </c>
+      <c r="E37" s="8">
+        <v>4.37</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="7">
+        <v>7.6</v>
+      </c>
+      <c r="D38" s="7">
+        <v>12.92</v>
+      </c>
+      <c r="E38" s="8">
+        <v>5.32</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="7">
+        <v>16.77</v>
+      </c>
+      <c r="D39" s="7">
+        <v>20.8</v>
+      </c>
+      <c r="E39" s="8">
+        <v>4.03</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="7">
+        <v>12.93</v>
+      </c>
+      <c r="D40" s="7">
+        <v>13.71</v>
+      </c>
+      <c r="E40" s="8">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="7">
+        <v>-11.06</v>
+      </c>
+      <c r="D41" s="7">
+        <v>-12.65</v>
+      </c>
+      <c r="E41" s="9">
+        <v>-1.59</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="7">
+        <v>-3.5</v>
+      </c>
+      <c r="D42" s="7">
+        <v>-3.85</v>
+      </c>
+      <c r="E42" s="9">
+        <v>-0.35</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="7">
+        <v>5.41</v>
+      </c>
+      <c r="D43" s="7">
+        <v>5.42</v>
+      </c>
+      <c r="E43" s="8">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="7">
+        <v>-21.76</v>
+      </c>
+      <c r="D44" s="7">
+        <v>-21.79</v>
+      </c>
+      <c r="E44" s="9">
+        <v>-0.03</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="7">
+        <v>-9.69</v>
+      </c>
+      <c r="D45" s="7">
+        <v>-9.199999999999999</v>
+      </c>
+      <c r="E45" s="8">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="7">
+        <v>-14.6</v>
+      </c>
+      <c r="D46" s="7">
+        <v>-13.17</v>
+      </c>
+      <c r="E46" s="8">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="7">
+        <v>-8.92</v>
+      </c>
+      <c r="D47" s="7">
+        <v>-7.65</v>
+      </c>
+      <c r="E47" s="8">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="7">
+        <v>0</v>
+      </c>
+      <c r="D48" s="7">
+        <v>-1.2</v>
+      </c>
+      <c r="E48" s="9">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="7">
+        <v>-43.23</v>
+      </c>
+      <c r="D49" s="7">
+        <v>-43.18</v>
+      </c>
+      <c r="E49" s="8">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="7">
+        <v>-18.89</v>
+      </c>
+      <c r="D50" s="7">
+        <v>-19.23</v>
+      </c>
+      <c r="E50" s="9">
+        <v>-0.34</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="7">
+        <v>-11.56</v>
+      </c>
+      <c r="D51" s="7">
+        <v>-11.84</v>
+      </c>
+      <c r="E51" s="9">
+        <v>-0.28</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="7">
+        <v>383.55</v>
+      </c>
+      <c r="D52" s="7">
+        <v>383.4</v>
+      </c>
+      <c r="E52" s="9">
+        <v>-0.15</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="7">
+        <v>372.35</v>
+      </c>
+      <c r="D53" s="7">
+        <v>374.35</v>
+      </c>
+      <c r="E53" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="7">
+        <v>360.15</v>
+      </c>
+      <c r="D54" s="7">
+        <v>366.15</v>
+      </c>
+      <c r="E54" s="8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="7">
+        <v>403.2</v>
+      </c>
+      <c r="D55" s="7">
+        <v>408.85</v>
+      </c>
+      <c r="E55" s="8">
+        <v>5.65</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="7">
+        <v>688.95</v>
+      </c>
+      <c r="D56" s="7">
+        <v>680.65</v>
+      </c>
+      <c r="E56" s="9">
+        <v>-8.300000000000001</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="7">
+        <v>205.53</v>
+      </c>
+      <c r="D57" s="7">
+        <v>205.71</v>
+      </c>
+      <c r="E57" s="8">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="7">
+        <v>3648</v>
+      </c>
+      <c r="D58" s="7">
+        <v>3632.6</v>
+      </c>
+      <c r="E58" s="9">
+        <v>-15.4</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="7">
+        <v>1564</v>
+      </c>
+      <c r="D59" s="7">
+        <v>1559</v>
+      </c>
+      <c r="E59" s="9">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C60" s="7">
+        <v>55</v>
+      </c>
+      <c r="D60" s="7">
         <v>66</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="E60" s="8">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C61" s="7">
+        <v>66</v>
+      </c>
+      <c r="D61" s="7">
+        <v>55</v>
+      </c>
+      <c r="E61" s="9">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="6">
-        <v>-6.08</v>
-      </c>
-      <c r="D7" s="6">
-        <v>-6.57</v>
-      </c>
-      <c r="E7" s="7">
-        <v>-0.49</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="B62" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" s="7">
+        <v>25.63</v>
+      </c>
+      <c r="D62" s="7">
+        <v>25.54</v>
+      </c>
+      <c r="E62" s="9">
+        <v>-0.09</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="7">
+        <v>47.27</v>
+      </c>
+      <c r="D63" s="7">
+        <v>48.78</v>
+      </c>
+      <c r="E63" s="8">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="7">
+        <v>36.44</v>
+      </c>
+      <c r="D64" s="7">
+        <v>44.37</v>
+      </c>
+      <c r="E64" s="8">
+        <v>7.93</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="7">
+        <v>53.46</v>
+      </c>
+      <c r="D65" s="7">
+        <v>57.97</v>
+      </c>
+      <c r="E65" s="8">
+        <v>4.51</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="7">
+        <v>72.31999999999999</v>
+      </c>
+      <c r="D66" s="7">
+        <v>67.73</v>
+      </c>
+      <c r="E66" s="9">
+        <v>-4.59</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="7">
+        <v>29.64</v>
+      </c>
+      <c r="D67" s="7">
+        <v>30.09</v>
+      </c>
+      <c r="E67" s="8">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="7">
+        <v>59.59</v>
+      </c>
+      <c r="D68" s="7">
+        <v>56.37</v>
+      </c>
+      <c r="E68" s="9">
+        <v>-3.22</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="7">
+        <v>42.34</v>
+      </c>
+      <c r="D69" s="7">
+        <v>41.39</v>
+      </c>
+      <c r="E69" s="9">
+        <v>-0.95</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="7">
+        <v>-45.95</v>
+      </c>
+      <c r="D70" s="7">
+        <v>-69.08</v>
+      </c>
+      <c r="E70" s="9">
+        <v>-23.13</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>-6.93</v>
-      </c>
-      <c r="D8" s="6">
-        <v>-9.77</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-2.84</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="B71" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C71" s="7">
+        <v>-7.91</v>
+      </c>
+      <c r="D71" s="7">
+        <v>-0.12</v>
+      </c>
+      <c r="E71" s="8">
+        <v>7.79</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-3.9</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-8.84</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-4.94</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="B72" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C72" s="7">
+        <v>-11.85</v>
+      </c>
+      <c r="D72" s="7">
+        <v>50.35</v>
+      </c>
+      <c r="E72" s="8">
+        <v>62.2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-6.21</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-6.83</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-0.62</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B73" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="7">
+        <v>-37.33</v>
+      </c>
+      <c r="D73" s="7">
+        <v>-36.75</v>
+      </c>
+      <c r="E73" s="8">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-2.07</v>
-      </c>
-      <c r="D11" s="6">
-        <v>0.12</v>
-      </c>
-      <c r="E11" s="8">
-        <v>2.19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B74" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="7">
+        <v>-2.97</v>
+      </c>
+      <c r="D74" s="7">
+        <v>-5.35</v>
+      </c>
+      <c r="E74" s="9">
+        <v>-2.38</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>17.87</v>
-      </c>
-      <c r="D12" s="6">
-        <v>16.83</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-1.04</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B75" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="7">
+        <v>173.51</v>
+      </c>
+      <c r="D75" s="7">
+        <v>-43.55</v>
+      </c>
+      <c r="E75" s="9">
+        <v>-217.06</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-10.21</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-10.51</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-0.3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B76" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="7">
+        <v>-6.44</v>
+      </c>
+      <c r="D76" s="7">
+        <v>-8.289999999999999</v>
+      </c>
+      <c r="E76" s="9">
+        <v>-1.85</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-1.06</v>
-      </c>
-      <c r="D14" s="6">
-        <v>1.32</v>
-      </c>
-      <c r="E14" s="8">
-        <v>2.38</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B77" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="7">
+        <v>378.84</v>
+      </c>
+      <c r="D77" s="7">
+        <v>16.28</v>
+      </c>
+      <c r="E77" s="9">
+        <v>-362.56</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-2.16</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-4.34</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-2.18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-1.18</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-1.92</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-0.74</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-4.92</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-3.72</v>
-      </c>
-      <c r="E17" s="8">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-0.78</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-0.17</v>
-      </c>
-      <c r="E18" s="8">
-        <v>0.61</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-1.4</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-1.5</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-0.1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>3.21</v>
-      </c>
-      <c r="D20" s="6">
-        <v>3</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-0.21</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6">
-        <v>3.99</v>
-      </c>
-      <c r="D21" s="6">
-        <v>3.88</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-0.11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-1.89</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-1.97</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-0.08</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="6">
-        <v>0.37</v>
-      </c>
-      <c r="D23" s="6">
-        <v>2.2</v>
-      </c>
-      <c r="E23" s="8">
-        <v>1.83</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-2.68</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-3.93</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-1.25</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-2.08</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-2.59</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-0.51</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>-1.99</v>
-      </c>
-      <c r="D26" s="6">
-        <v>-3.83</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-1.84</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>43.33</v>
-      </c>
-      <c r="D27" s="6">
-        <v>43.38</v>
-      </c>
-      <c r="E27" s="8">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="6">
-        <v>3.57</v>
-      </c>
-      <c r="D28" s="6">
-        <v>1.9</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-1.67</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="6">
-        <v>26.14</v>
-      </c>
-      <c r="D29" s="6">
-        <v>26.04</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-0.1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="6">
-        <v>4.88</v>
-      </c>
-      <c r="D30" s="6">
-        <v>3.94</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-0.9399999999999999</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-41.25</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-42.53</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-1.28</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-12.34</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-9.35</v>
-      </c>
-      <c r="E32" s="8">
-        <v>2.99</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="6">
-        <v>6.66</v>
-      </c>
-      <c r="D33" s="6">
-        <v>4.79</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-1.87</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="6">
-        <v>-12</v>
-      </c>
-      <c r="D34" s="6">
-        <v>-12.91</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-0.91</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="6">
-        <v>6.88</v>
-      </c>
-      <c r="D35" s="6">
-        <v>5.68</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-1.2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="6">
-        <v>33.09</v>
-      </c>
-      <c r="D36" s="6">
-        <v>30.65</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-2.44</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="6">
-        <v>8.359999999999999</v>
-      </c>
-      <c r="D37" s="6">
-        <v>7.6</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-0.76</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="6">
-        <v>19.94</v>
-      </c>
-      <c r="D38" s="6">
-        <v>16.77</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-3.17</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="6">
-        <v>11.92</v>
-      </c>
-      <c r="D39" s="6">
-        <v>12.93</v>
-      </c>
-      <c r="E39" s="8">
-        <v>1.01</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-1.43</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-11.06</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-9.630000000000001</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="6">
-        <v>-4.69</v>
-      </c>
-      <c r="D41" s="6">
-        <v>-3.5</v>
-      </c>
-      <c r="E41" s="8">
-        <v>1.19</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="6">
-        <v>6.22</v>
-      </c>
-      <c r="D42" s="6">
-        <v>5.41</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-0.8100000000000001</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="6">
-        <v>-21.39</v>
-      </c>
-      <c r="D43" s="6">
-        <v>-21.76</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-0.37</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="6">
-        <v>-16.63</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-16.89</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-0.26</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-9.369999999999999</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-9.69</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-0.32</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-14.06</v>
-      </c>
-      <c r="D46" s="6">
-        <v>-14.6</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-0.54</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="6">
-        <v>-8.44</v>
-      </c>
-      <c r="D47" s="6">
-        <v>-8.92</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-0.48</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="6">
-        <v>-42.72</v>
-      </c>
-      <c r="D48" s="6">
-        <v>-43.23</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-0.51</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="6">
-        <v>-20.89</v>
-      </c>
-      <c r="D49" s="6">
-        <v>-18.89</v>
-      </c>
-      <c r="E49" s="8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="6">
-        <v>-9.699999999999999</v>
-      </c>
-      <c r="D50" s="6">
-        <v>-11.56</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-1.86</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C51" s="6">
-        <v>385.35</v>
-      </c>
-      <c r="D51" s="6">
-        <v>383.55</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-1.8</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="6">
-        <v>3170</v>
-      </c>
-      <c r="D52" s="6">
-        <v>3160</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="6">
-        <v>373.65</v>
-      </c>
-      <c r="D53" s="6">
-        <v>372.35</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-1.3</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="6">
-        <v>362.4</v>
-      </c>
-      <c r="D54" s="6">
-        <v>360.15</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-2.25</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="6">
-        <v>405.35</v>
-      </c>
-      <c r="D55" s="6">
-        <v>403.2</v>
-      </c>
-      <c r="E55" s="7">
-        <v>-2.15</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="6">
-        <v>688.1</v>
-      </c>
-      <c r="D56" s="6">
-        <v>688.95</v>
-      </c>
-      <c r="E56" s="8">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="6">
-        <v>207.4</v>
-      </c>
-      <c r="D57" s="6">
-        <v>205.53</v>
-      </c>
-      <c r="E57" s="7">
-        <v>-1.87</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="6">
-        <v>3557.8</v>
-      </c>
-      <c r="D58" s="6">
-        <v>3648</v>
-      </c>
-      <c r="E58" s="8">
-        <v>90.2</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="6">
-        <v>1596.9</v>
-      </c>
-      <c r="D59" s="6">
-        <v>1564</v>
-      </c>
-      <c r="E59" s="7">
-        <v>-32.9</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C60" s="6">
-        <v>34</v>
-      </c>
-      <c r="D60" s="6">
-        <v>23</v>
-      </c>
-      <c r="E60" s="7">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C61" s="6">
-        <v>23</v>
-      </c>
-      <c r="D61" s="6">
-        <v>34</v>
-      </c>
-      <c r="E61" s="8">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C62" s="6">
-        <v>26.75</v>
-      </c>
-      <c r="D62" s="6">
-        <v>25.63</v>
-      </c>
-      <c r="E62" s="7">
-        <v>-1.12</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C63" s="6">
-        <v>34.74</v>
-      </c>
-      <c r="D63" s="6">
-        <v>34</v>
-      </c>
-      <c r="E63" s="7">
-        <v>-0.74</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="6">
-        <v>48.12</v>
-      </c>
-      <c r="D64" s="6">
-        <v>47.27</v>
-      </c>
-      <c r="E64" s="7">
-        <v>-0.85</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="6">
-        <v>38.34</v>
-      </c>
-      <c r="D65" s="6">
-        <v>36.44</v>
-      </c>
-      <c r="E65" s="7">
-        <v>-1.9</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="6">
-        <v>55.57</v>
-      </c>
-      <c r="D66" s="6">
-        <v>53.46</v>
-      </c>
-      <c r="E66" s="7">
-        <v>-2.11</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="6">
-        <v>72.14</v>
-      </c>
-      <c r="D67" s="6">
-        <v>72.31999999999999</v>
-      </c>
-      <c r="E67" s="8">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="6">
-        <v>31.63</v>
-      </c>
-      <c r="D68" s="6">
-        <v>29.64</v>
-      </c>
-      <c r="E68" s="7">
-        <v>-1.99</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="6">
-        <v>41.45</v>
-      </c>
-      <c r="D69" s="6">
-        <v>59.59</v>
-      </c>
-      <c r="E69" s="8">
-        <v>18.14</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="6">
-        <v>49.24</v>
-      </c>
-      <c r="D70" s="6">
-        <v>42.34</v>
-      </c>
-      <c r="E70" s="7">
-        <v>-6.9</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B71" s="5" t="s">
+      <c r="B78" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C71" s="6">
-        <v>-56</v>
-      </c>
-      <c r="D71" s="6">
-        <v>-45.95</v>
-      </c>
-      <c r="E71" s="8">
-        <v>10.05</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C72" s="6">
-        <v>-20.35</v>
-      </c>
-      <c r="D72" s="6">
-        <v>-7.91</v>
-      </c>
-      <c r="E72" s="8">
-        <v>12.44</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C73" s="6">
-        <v>27.05</v>
-      </c>
-      <c r="D73" s="6">
-        <v>-11.85</v>
-      </c>
-      <c r="E73" s="7">
-        <v>-38.9</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="6">
-        <v>-65.7</v>
-      </c>
-      <c r="D74" s="6">
-        <v>-37.33</v>
-      </c>
-      <c r="E74" s="8">
-        <v>28.37</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="6">
-        <v>-20.14</v>
-      </c>
-      <c r="D75" s="6">
-        <v>-2.97</v>
-      </c>
-      <c r="E75" s="8">
-        <v>17.17</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="6">
-        <v>320.45</v>
-      </c>
-      <c r="D76" s="6">
-        <v>173.51</v>
-      </c>
-      <c r="E76" s="7">
-        <v>-146.94</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="6">
-        <v>57.1</v>
-      </c>
-      <c r="D77" s="6">
-        <v>-6.44</v>
-      </c>
-      <c r="E77" s="7">
-        <v>-63.54</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="6">
-        <v>10.08</v>
-      </c>
-      <c r="D78" s="6">
-        <v>378.84</v>
-      </c>
-      <c r="E78" s="8">
-        <v>368.76</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="6">
-        <v>-52.97</v>
-      </c>
-      <c r="D79" s="6">
+      <c r="C78" s="7">
         <v>-14.75</v>
       </c>
-      <c r="E79" s="8">
-        <v>38.22</v>
+      <c r="D78" s="7">
+        <v>-27.92</v>
+      </c>
+      <c r="E78" s="9">
+        <v>-13.17</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3425,60 +3440,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="G1" s="9" t="s">
+      <c r="B1" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="C1" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="D1" s="10" t="s">
         <v>74</v>
       </c>
+      <c r="E1" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="11">
-        <v>48.16</v>
-      </c>
-      <c r="C2" s="12">
+      <c r="B2" s="12">
+        <v>56.16</v>
+      </c>
+      <c r="C2" s="13">
         <v>9</v>
       </c>
-      <c r="D2" s="11">
-        <v>44.5</v>
-      </c>
-      <c r="E2" s="11">
-        <v>40</v>
-      </c>
-      <c r="F2" s="11">
-        <v>-3.2</v>
-      </c>
-      <c r="G2" s="11">
-        <v>5.7</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="D2" s="12">
+        <v>45.1</v>
+      </c>
+      <c r="E2" s="12">
+        <v>60</v>
+      </c>
+      <c r="F2" s="12">
+        <v>-3.8</v>
+      </c>
+      <c r="G2" s="12">
+        <v>7.4</v>
+      </c>
+      <c r="H2" s="12">
         <v>55.4</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="12">
         <v>40</v>
       </c>
     </row>
@@ -3580,61 +3595,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="14" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="14">
-        <v>0.3617</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.3418</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.1999</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.1885</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.1267</v>
-      </c>
-      <c r="F2" s="14">
-        <v>0.0535</v>
-      </c>
-      <c r="G2" s="14">
-        <v>0.048</v>
-      </c>
-      <c r="H2" s="14">
-        <v>-0.019</v>
-      </c>
-      <c r="I2" s="14">
-        <v>-0.1026</v>
+      <c r="A2" s="15">
+        <v>0.36</v>
+      </c>
+      <c r="B2" s="15">
+        <v>0.3413</v>
+      </c>
+      <c r="C2" s="15">
+        <v>0.1958</v>
+      </c>
+      <c r="D2" s="15">
+        <v>0.1927</v>
+      </c>
+      <c r="E2" s="15">
+        <v>0.1307</v>
+      </c>
+      <c r="F2" s="15">
+        <v>0.0599</v>
+      </c>
+      <c r="G2" s="15">
+        <v>0.04849999999999999</v>
+      </c>
+      <c r="H2" s="15">
+        <v>-0.0284</v>
+      </c>
+      <c r="I2" s="15">
+        <v>-0.1067</v>
       </c>
     </row>
   </sheetData>

--- a/MAHINDRA_GROUP_Technical_Metrics.xlsx
+++ b/MAHINDRA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="75">
   <si>
     <t>Symbol</t>
   </si>
@@ -193,34 +193,19 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>29.6 → 30.1</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>29.6</t>
-  </si>
-  <si>
-    <t>30.1</t>
-  </si>
-  <si>
-    <t>RSI Overbought Exit</t>
-  </si>
-  <si>
-    <t>72.3 → 67.7</t>
-  </si>
-  <si>
-    <t>🔵 COOLING</t>
-  </si>
-  <si>
-    <t>72.3</t>
-  </si>
-  <si>
-    <t>67.7</t>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>56.4 → 49.3</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>56.4</t>
+  </si>
+  <si>
+    <t>49.3</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -272,7 +257,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -306,27 +291,20 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF1F4E79"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -353,19 +331,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -435,7 +407,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -443,15 +415,14 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -460,7 +431,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -959,58 +930,58 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>383.4</v>
+        <v>381.65</v>
       </c>
       <c r="D2">
-        <v>-0.04</v>
+        <v>-0.46</v>
       </c>
       <c r="E2">
         <v>490.2</v>
       </c>
       <c r="F2">
-        <v>381.86</v>
+        <v>381.65</v>
       </c>
       <c r="G2">
-        <v>-21.79</v>
+        <v>-22.14</v>
       </c>
       <c r="H2">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>-1.91</v>
+        <v>-0.87</v>
       </c>
       <c r="J2">
-        <v>-6.37</v>
+        <v>-7.59</v>
       </c>
       <c r="K2">
-        <v>-11.91</v>
+        <v>-12.49</v>
       </c>
       <c r="L2">
-        <v>-0.99</v>
+        <v>-1.69</v>
       </c>
       <c r="M2">
-        <v>13.07</v>
+        <v>11.3</v>
       </c>
       <c r="N2">
         <v>23</v>
       </c>
       <c r="O2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P2">
-        <v>384.25</v>
+        <v>383.58</v>
       </c>
       <c r="Q2">
-        <v>396.85</v>
+        <v>395.34</v>
       </c>
       <c r="R2">
-        <v>423.74</v>
+        <v>422.19</v>
       </c>
       <c r="S2">
-        <v>435.79</v>
+        <v>435.65</v>
       </c>
       <c r="T2">
-        <v>-12.02</v>
+        <v>-12.39</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1025,43 +996,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>25.54</v>
+        <v>24.39</v>
       </c>
       <c r="Z2">
-        <v>-10.71</v>
+        <v>-10.6</v>
       </c>
       <c r="AA2">
-        <v>-10.83</v>
+        <v>-10.79</v>
       </c>
       <c r="AB2">
-        <v>0.12</v>
+        <v>0.19</v>
       </c>
       <c r="AC2">
-        <v>13.8</v>
+        <v>7.87</v>
       </c>
       <c r="AD2">
-        <v>9.859999999999999</v>
+        <v>10.48</v>
       </c>
       <c r="AE2">
-        <v>7.89</v>
+        <v>7.72</v>
       </c>
       <c r="AF2">
-        <v>-69.08</v>
+        <v>-35.44</v>
       </c>
       <c r="AG2">
-        <v>416.58</v>
+        <v>414.89</v>
       </c>
       <c r="AH2">
-        <v>377.11</v>
+        <v>375.79</v>
       </c>
       <c r="AI2">
-        <v>408.09</v>
+        <v>406.9</v>
       </c>
       <c r="AJ2" t="s">
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>57.97</v>
+        <v>57.05</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1072,10 +1043,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>3160</v>
+        <v>3150</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>-0.32</v>
       </c>
       <c r="E3">
         <v>3802.4</v>
@@ -1084,25 +1055,25 @@
         <v>2931.1</v>
       </c>
       <c r="G3">
-        <v>-16.89</v>
+        <v>-17.16</v>
       </c>
       <c r="H3">
-        <v>7.81</v>
+        <v>7.47</v>
       </c>
       <c r="I3">
-        <v>-3.04</v>
+        <v>-1.25</v>
       </c>
       <c r="J3">
-        <v>-10.15</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="K3">
-        <v>7.03</v>
+        <v>4.97</v>
       </c>
       <c r="L3">
-        <v>-9.23</v>
+        <v>-11.55</v>
       </c>
       <c r="M3">
-        <v>34.13</v>
+        <v>34.18</v>
       </c>
       <c r="N3">
         <v>45</v>
@@ -1111,19 +1082,19 @@
         <v>42</v>
       </c>
       <c r="P3">
-        <v>3166</v>
+        <v>3158</v>
       </c>
       <c r="Q3">
-        <v>3330.72</v>
+        <v>3318.03</v>
       </c>
       <c r="R3">
-        <v>3278.43</v>
+        <v>3279.49</v>
       </c>
       <c r="S3">
-        <v>3328.12</v>
+        <v>3325.12</v>
       </c>
       <c r="T3">
-        <v>-5.05</v>
+        <v>-5.27</v>
       </c>
       <c r="U3" t="s">
         <v>48</v>
@@ -1138,43 +1109,43 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>34</v>
+        <v>33.19</v>
       </c>
       <c r="Z3">
-        <v>-42.64</v>
+        <v>-47.25</v>
       </c>
       <c r="AA3">
-        <v>-9.210000000000001</v>
+        <v>-16.82</v>
       </c>
       <c r="AB3">
-        <v>-33.43</v>
+        <v>-30.44</v>
       </c>
       <c r="AC3">
-        <v>8.06</v>
+        <v>6.2</v>
       </c>
       <c r="AD3">
-        <v>5.67</v>
+        <v>6.64</v>
       </c>
       <c r="AE3">
-        <v>67.90000000000001</v>
+        <v>66.05</v>
       </c>
       <c r="AF3">
-        <v>-0.12</v>
+        <v>-40.17</v>
       </c>
       <c r="AG3">
-        <v>3549.3</v>
+        <v>3547.95</v>
       </c>
       <c r="AH3">
-        <v>3112.13</v>
+        <v>3088.12</v>
       </c>
       <c r="AI3">
-        <v>3333.36</v>
+        <v>3332.81</v>
       </c>
       <c r="AJ3" t="s">
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>55.37</v>
+        <v>58.76</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1185,10 +1156,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>374.35</v>
+        <v>363.75</v>
       </c>
       <c r="D4">
-        <v>0.54</v>
+        <v>-2.83</v>
       </c>
       <c r="E4">
         <v>412.3</v>
@@ -1197,46 +1168,46 @@
         <v>268.95</v>
       </c>
       <c r="G4">
-        <v>-9.199999999999999</v>
+        <v>-11.78</v>
       </c>
       <c r="H4">
-        <v>39.19</v>
+        <v>35.25</v>
       </c>
       <c r="I4">
-        <v>2.73</v>
+        <v>-1.38</v>
       </c>
       <c r="J4">
-        <v>-9.199999999999999</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="K4">
-        <v>35.02</v>
+        <v>31.94</v>
       </c>
       <c r="L4">
-        <v>42.39</v>
+        <v>35.07</v>
       </c>
       <c r="M4">
-        <v>19.27</v>
+        <v>18.66</v>
       </c>
       <c r="N4">
         <v>99</v>
       </c>
       <c r="O4">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="P4">
-        <v>373.05</v>
+        <v>372.03</v>
       </c>
       <c r="Q4">
-        <v>380.96</v>
+        <v>379.36</v>
       </c>
       <c r="R4">
-        <v>367.71</v>
+        <v>368.68</v>
       </c>
       <c r="S4">
-        <v>344.52</v>
+        <v>344.63</v>
       </c>
       <c r="T4">
-        <v>8.66</v>
+        <v>5.55</v>
       </c>
       <c r="U4" t="s">
         <v>48</v>
@@ -1251,34 +1222,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>48.78</v>
+        <v>41.93</v>
       </c>
       <c r="Z4">
-        <v>-0.22</v>
+        <v>-1.18</v>
       </c>
       <c r="AA4">
-        <v>2.32</v>
+        <v>1.62</v>
       </c>
       <c r="AB4">
-        <v>-2.54</v>
+        <v>-2.8</v>
       </c>
       <c r="AC4">
-        <v>45.21</v>
+        <v>32.23</v>
       </c>
       <c r="AD4">
-        <v>42.57</v>
+        <v>40.51</v>
       </c>
       <c r="AE4">
-        <v>11.74</v>
+        <v>11.77</v>
       </c>
       <c r="AF4">
-        <v>50.35</v>
+        <v>30.45</v>
       </c>
       <c r="AG4">
-        <v>398.37</v>
+        <v>396.91</v>
       </c>
       <c r="AH4">
-        <v>363.55</v>
+        <v>361.8</v>
       </c>
       <c r="AI4">
         <v>357.72</v>
@@ -1287,7 +1258,7 @@
         <v>50</v>
       </c>
       <c r="AK4">
-        <v>19.74</v>
+        <v>19.48</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1298,10 +1269,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>366.15</v>
+        <v>370.1</v>
       </c>
       <c r="D5">
-        <v>1.67</v>
+        <v>1.08</v>
       </c>
       <c r="E5">
         <v>421.7</v>
@@ -1310,25 +1281,25 @@
         <v>294.25</v>
       </c>
       <c r="G5">
-        <v>-13.17</v>
+        <v>-12.24</v>
       </c>
       <c r="H5">
-        <v>24.44</v>
+        <v>25.78</v>
       </c>
       <c r="I5">
-        <v>2.58</v>
+        <v>3.09</v>
       </c>
       <c r="J5">
-        <v>-5.35</v>
+        <v>-3.28</v>
       </c>
       <c r="K5">
-        <v>12.92</v>
+        <v>16.04</v>
       </c>
       <c r="L5">
-        <v>2.74</v>
+        <v>1.83</v>
       </c>
       <c r="M5">
-        <v>5.99</v>
+        <v>6.13</v>
       </c>
       <c r="N5">
         <v>66</v>
@@ -1337,19 +1308,19 @@
         <v>60</v>
       </c>
       <c r="P5">
-        <v>362.16</v>
+        <v>364.38</v>
       </c>
       <c r="Q5">
-        <v>372.48</v>
+        <v>371.84</v>
       </c>
       <c r="R5">
-        <v>376.05</v>
+        <v>376</v>
       </c>
       <c r="S5">
-        <v>363.09</v>
+        <v>363</v>
       </c>
       <c r="T5">
-        <v>0.84</v>
+        <v>1.96</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1364,34 +1335,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>44.37</v>
+        <v>48.88</v>
       </c>
       <c r="Z5">
-        <v>-4.53</v>
+        <v>-3.91</v>
       </c>
       <c r="AA5">
-        <v>-3.17</v>
+        <v>-3.31</v>
       </c>
       <c r="AB5">
-        <v>-1.36</v>
+        <v>-0.6</v>
       </c>
       <c r="AC5">
-        <v>44.8</v>
+        <v>65.16</v>
       </c>
       <c r="AD5">
-        <v>33.78</v>
+        <v>47.17</v>
       </c>
       <c r="AE5">
-        <v>10.17</v>
+        <v>10.28</v>
       </c>
       <c r="AF5">
-        <v>-36.75</v>
+        <v>49.33</v>
       </c>
       <c r="AG5">
-        <v>391.7</v>
+        <v>390.45</v>
       </c>
       <c r="AH5">
-        <v>353.25</v>
+        <v>353.23</v>
       </c>
       <c r="AI5">
         <v>386.7</v>
@@ -1400,7 +1371,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>42.89</v>
+        <v>40.05</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1411,10 +1382,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>408.85</v>
+        <v>401.75</v>
       </c>
       <c r="D6">
-        <v>1.4</v>
+        <v>-1.74</v>
       </c>
       <c r="E6">
         <v>442.7</v>
@@ -1423,46 +1394,46 @@
         <v>279.55</v>
       </c>
       <c r="G6">
-        <v>-7.65</v>
+        <v>-9.25</v>
       </c>
       <c r="H6">
-        <v>46.25</v>
+        <v>43.71</v>
       </c>
       <c r="I6">
-        <v>5.59</v>
+        <v>2.37</v>
       </c>
       <c r="J6">
-        <v>-0.61</v>
+        <v>-1.86</v>
       </c>
       <c r="K6">
-        <v>20.8</v>
+        <v>20.97</v>
       </c>
       <c r="L6">
-        <v>27.71</v>
+        <v>25.27</v>
       </c>
       <c r="M6">
-        <v>-10.67</v>
+        <v>-10.66</v>
       </c>
       <c r="N6">
         <v>88</v>
       </c>
       <c r="O6">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="P6">
-        <v>402.03</v>
+        <v>403.89</v>
       </c>
       <c r="Q6">
-        <v>400.9</v>
+        <v>400.64</v>
       </c>
       <c r="R6">
-        <v>399.9</v>
+        <v>400.5</v>
       </c>
       <c r="S6">
-        <v>368.7</v>
+        <v>369.11</v>
       </c>
       <c r="T6">
-        <v>10.89</v>
+        <v>8.84</v>
       </c>
       <c r="U6" t="s">
         <v>48</v>
@@ -1477,34 +1448,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>57.97</v>
+        <v>51.25</v>
       </c>
       <c r="Z6">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AA6">
-        <v>-0.23</v>
+        <v>-0.11</v>
       </c>
       <c r="AB6">
-        <v>0.52</v>
+        <v>0.47</v>
       </c>
       <c r="AC6">
-        <v>96.08</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="AD6">
-        <v>87.28</v>
+        <v>90.79000000000001</v>
       </c>
       <c r="AE6">
-        <v>11.3</v>
+        <v>11.46</v>
       </c>
       <c r="AF6">
-        <v>-5.35</v>
+        <v>-14.87</v>
       </c>
       <c r="AG6">
-        <v>413.7</v>
+        <v>413.13</v>
       </c>
       <c r="AH6">
-        <v>388.09</v>
+        <v>388.14</v>
       </c>
       <c r="AI6">
         <v>372.35</v>
@@ -1513,7 +1484,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>23.63</v>
+        <v>25.64</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1524,10 +1495,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>680.65</v>
+        <v>676.2</v>
       </c>
       <c r="D7">
-        <v>-1.2</v>
+        <v>-0.65</v>
       </c>
       <c r="E7">
         <v>688.95</v>
@@ -1536,46 +1507,46 @@
         <v>506.45</v>
       </c>
       <c r="G7">
-        <v>-1.2</v>
+        <v>-1.85</v>
       </c>
       <c r="H7">
-        <v>34.4</v>
+        <v>33.52</v>
       </c>
       <c r="I7">
-        <v>4.78</v>
+        <v>1.68</v>
       </c>
       <c r="J7">
-        <v>11.98</v>
+        <v>13.65</v>
       </c>
       <c r="K7">
         <v>13.71</v>
       </c>
       <c r="L7">
-        <v>5.23</v>
+        <v>6.72</v>
       </c>
       <c r="M7">
-        <v>36</v>
+        <v>35.74</v>
       </c>
       <c r="N7">
         <v>77</v>
       </c>
       <c r="O7">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="P7">
-        <v>675.25</v>
+        <v>677.48</v>
       </c>
       <c r="Q7">
-        <v>641.83</v>
+        <v>645.14</v>
       </c>
       <c r="R7">
-        <v>608.3</v>
+        <v>609.9</v>
       </c>
       <c r="S7">
-        <v>588.42</v>
+        <v>588.9400000000001</v>
       </c>
       <c r="T7">
-        <v>15.68</v>
+        <v>14.82</v>
       </c>
       <c r="U7" t="s">
         <v>48</v>
@@ -1590,34 +1561,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>67.73</v>
+        <v>65.33</v>
       </c>
       <c r="Z7">
-        <v>21.25</v>
+        <v>20.98</v>
       </c>
       <c r="AA7">
-        <v>17.05</v>
+        <v>17.84</v>
       </c>
       <c r="AB7">
-        <v>4.2</v>
+        <v>3.14</v>
       </c>
       <c r="AC7">
-        <v>75.59</v>
+        <v>54.01</v>
       </c>
       <c r="AD7">
-        <v>68.76000000000001</v>
+        <v>65.63</v>
       </c>
       <c r="AE7">
-        <v>22.61</v>
+        <v>22.03</v>
       </c>
       <c r="AF7">
-        <v>-43.55</v>
+        <v>-53.85</v>
       </c>
       <c r="AG7">
-        <v>694.1</v>
+        <v>697.3</v>
       </c>
       <c r="AH7">
-        <v>589.5599999999999</v>
+        <v>592.99</v>
       </c>
       <c r="AI7">
         <v>628.66</v>
@@ -1626,7 +1597,7 @@
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>73.43000000000001</v>
+        <v>72.01000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1637,58 +1608,58 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>205.71</v>
+        <v>199.36</v>
       </c>
       <c r="D8">
-        <v>0.09</v>
+        <v>-3.09</v>
       </c>
       <c r="E8">
         <v>362.05</v>
       </c>
       <c r="F8">
-        <v>205.53</v>
+        <v>199.36</v>
       </c>
       <c r="G8">
-        <v>-43.18</v>
+        <v>-44.94</v>
       </c>
       <c r="H8">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <v>-1.25</v>
+        <v>-3.5</v>
       </c>
       <c r="J8">
-        <v>-10.68</v>
+        <v>-11.62</v>
       </c>
       <c r="K8">
-        <v>-12.65</v>
+        <v>-13.58</v>
       </c>
       <c r="L8">
-        <v>-42.89</v>
+        <v>-44.32</v>
       </c>
       <c r="M8">
-        <v>-2.84</v>
+        <v>-3.05</v>
       </c>
       <c r="N8">
         <v>12</v>
       </c>
       <c r="O8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P8">
-        <v>206.63</v>
+        <v>205.18</v>
       </c>
       <c r="Q8">
-        <v>215.89</v>
+        <v>214.61</v>
       </c>
       <c r="R8">
-        <v>222.4</v>
+        <v>221.65</v>
       </c>
       <c r="S8">
-        <v>258.99</v>
+        <v>258.33</v>
       </c>
       <c r="T8">
-        <v>-20.57</v>
+        <v>-22.83</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1703,43 +1674,43 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>30.09</v>
+        <v>24.15</v>
       </c>
       <c r="Z8">
-        <v>-5.1</v>
+        <v>-5.62</v>
       </c>
       <c r="AA8">
-        <v>-4.1</v>
+        <v>-4.41</v>
       </c>
       <c r="AB8">
-        <v>-1</v>
+        <v>-1.21</v>
       </c>
       <c r="AC8">
-        <v>7.42</v>
+        <v>2.57</v>
       </c>
       <c r="AD8">
-        <v>9.029999999999999</v>
+        <v>6.74</v>
       </c>
       <c r="AE8">
-        <v>5.54</v>
+        <v>5.69</v>
       </c>
       <c r="AF8">
-        <v>-8.289999999999999</v>
+        <v>155.72</v>
       </c>
       <c r="AG8">
-        <v>231.06</v>
+        <v>230.85</v>
       </c>
       <c r="AH8">
-        <v>200.72</v>
+        <v>198.37</v>
       </c>
       <c r="AI8">
-        <v>222.99</v>
+        <v>219.93</v>
       </c>
       <c r="AJ8" t="s">
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>43.93</v>
+        <v>46.86</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1750,10 +1721,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>3632.6</v>
+        <v>3594.3</v>
       </c>
       <c r="D9">
-        <v>-0.42</v>
+        <v>-1.05</v>
       </c>
       <c r="E9">
         <v>4497.5</v>
@@ -1762,46 +1733,46 @@
         <v>3308.9</v>
       </c>
       <c r="G9">
-        <v>-19.23</v>
+        <v>-20.08</v>
       </c>
       <c r="H9">
-        <v>9.779999999999999</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="I9">
-        <v>2.68</v>
+        <v>1.51</v>
       </c>
       <c r="J9">
-        <v>0.84</v>
+        <v>-0.1</v>
       </c>
       <c r="K9">
-        <v>-3.85</v>
+        <v>-2.51</v>
       </c>
       <c r="L9">
-        <v>-12</v>
+        <v>-14.21</v>
       </c>
       <c r="M9">
-        <v>19.58</v>
+        <v>19.56</v>
       </c>
       <c r="N9">
         <v>34</v>
       </c>
       <c r="O9">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P9">
-        <v>3586.8</v>
+        <v>3597.48</v>
       </c>
       <c r="Q9">
-        <v>3582.62</v>
+        <v>3581.89</v>
       </c>
       <c r="R9">
-        <v>3651.11</v>
+        <v>3642.23</v>
       </c>
       <c r="S9">
-        <v>3686.56</v>
+        <v>3685.83</v>
       </c>
       <c r="T9">
-        <v>-1.46</v>
+        <v>-2.48</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1816,34 +1787,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>56.37</v>
+        <v>49.26</v>
       </c>
       <c r="Z9">
-        <v>-13.51</v>
+        <v>-11.65</v>
       </c>
       <c r="AA9">
-        <v>-26.36</v>
+        <v>-23.41</v>
       </c>
       <c r="AB9">
-        <v>12.85</v>
+        <v>11.77</v>
       </c>
       <c r="AC9">
-        <v>91.87</v>
+        <v>82.2</v>
       </c>
       <c r="AD9">
-        <v>74.68000000000001</v>
+        <v>84.48999999999999</v>
       </c>
       <c r="AE9">
-        <v>63.93</v>
+        <v>64.15000000000001</v>
       </c>
       <c r="AF9">
-        <v>16.28</v>
+        <v>26.46</v>
       </c>
       <c r="AG9">
-        <v>3656.93</v>
+        <v>3655.39</v>
       </c>
       <c r="AH9">
-        <v>3508.31</v>
+        <v>3508.39</v>
       </c>
       <c r="AI9">
         <v>3684.57</v>
@@ -1852,7 +1823,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>34.98</v>
+        <v>35.3</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1863,10 +1834,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>1559</v>
+        <v>1508</v>
       </c>
       <c r="D10">
-        <v>-0.32</v>
+        <v>-3.27</v>
       </c>
       <c r="E10">
         <v>1768.4</v>
@@ -1875,46 +1846,46 @@
         <v>1326.2</v>
       </c>
       <c r="G10">
-        <v>-11.84</v>
+        <v>-14.73</v>
       </c>
       <c r="H10">
-        <v>17.55</v>
+        <v>13.71</v>
       </c>
       <c r="I10">
-        <v>-4.82</v>
+        <v>-7.09</v>
       </c>
       <c r="J10">
-        <v>-4.94</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="K10">
-        <v>5.42</v>
+        <v>2.93</v>
       </c>
       <c r="L10">
-        <v>4.99</v>
+        <v>3.1</v>
       </c>
       <c r="M10">
-        <v>4.85</v>
+        <v>4.07</v>
       </c>
       <c r="N10">
         <v>55</v>
       </c>
       <c r="O10">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="P10">
-        <v>1588.18</v>
+        <v>1565.18</v>
       </c>
       <c r="Q10">
-        <v>1602.62</v>
+        <v>1596.77</v>
       </c>
       <c r="R10">
-        <v>1568.91</v>
+        <v>1572.55</v>
       </c>
       <c r="S10">
-        <v>1517.42</v>
+        <v>1517.65</v>
       </c>
       <c r="T10">
-        <v>2.74</v>
+        <v>-0.64</v>
       </c>
       <c r="U10" t="s">
         <v>48</v>
@@ -1926,46 +1897,46 @@
         <v>48</v>
       </c>
       <c r="X10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y10">
-        <v>41.39</v>
+        <v>33.21</v>
       </c>
       <c r="Z10">
-        <v>0.08</v>
+        <v>-6.9</v>
       </c>
       <c r="AA10">
-        <v>8.08</v>
+        <v>5.09</v>
       </c>
       <c r="AB10">
-        <v>-8.01</v>
+        <v>-11.99</v>
       </c>
       <c r="AC10">
-        <v>9.23</v>
+        <v>0</v>
       </c>
       <c r="AD10">
-        <v>23.01</v>
+        <v>9.4</v>
       </c>
       <c r="AE10">
-        <v>37.02</v>
+        <v>38.73</v>
       </c>
       <c r="AF10">
-        <v>-27.92</v>
+        <v>-37.51</v>
       </c>
       <c r="AG10">
-        <v>1653.74</v>
+        <v>1661.95</v>
       </c>
       <c r="AH10">
-        <v>1551.5</v>
+        <v>1531.59</v>
       </c>
       <c r="AI10">
-        <v>1527.05</v>
+        <v>1630.7</v>
       </c>
       <c r="AJ10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AK10">
-        <v>29.29</v>
+        <v>33.84</v>
       </c>
     </row>
   </sheetData>
@@ -2106,7 +2077,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:F77"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2146,7 +2117,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2164,1263 +2135,1243 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>-6.37</v>
+      </c>
+      <c r="D7" s="6">
+        <v>-7.59</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-1.22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>-10.15</v>
+      </c>
+      <c r="D8" s="6">
+        <v>-8.960000000000001</v>
+      </c>
+      <c r="E8" s="8">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-9.199999999999999</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-8.789999999999999</v>
+      </c>
+      <c r="E9" s="8">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-5.35</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-3.28</v>
+      </c>
+      <c r="E10" s="8">
+        <v>2.07</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-0.61</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-1.86</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-1.25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="6" t="s">
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>11.98</v>
+      </c>
+      <c r="D12" s="6">
+        <v>13.65</v>
+      </c>
+      <c r="E12" s="8">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-10.68</v>
+      </c>
+      <c r="D13" s="6">
+        <v>-11.62</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="6">
+        <v>0.84</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-0.1</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-4.94</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-8.220000000000001</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-3.28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="7">
-        <v>-6.57</v>
-      </c>
-      <c r="D8" s="7">
-        <v>-6.37</v>
-      </c>
-      <c r="E8" s="8">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="6" t="s">
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-1.91</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-0.87</v>
+      </c>
+      <c r="E16" s="8">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-9.77</v>
-      </c>
-      <c r="D9" s="7">
-        <v>-10.15</v>
-      </c>
-      <c r="E9" s="9">
-        <v>-0.38</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-3.04</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-1.25</v>
+      </c>
+      <c r="E17" s="8">
+        <v>1.79</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7">
-        <v>-8.84</v>
-      </c>
-      <c r="D10" s="7">
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>2.73</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-1.38</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-4.11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>2.58</v>
+      </c>
+      <c r="D19" s="6">
+        <v>3.09</v>
+      </c>
+      <c r="E19" s="8">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>5.59</v>
+      </c>
+      <c r="D20" s="6">
+        <v>2.37</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-3.22</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="6">
+        <v>4.78</v>
+      </c>
+      <c r="D21" s="6">
+        <v>1.68</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-3.1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="6">
+        <v>-1.25</v>
+      </c>
+      <c r="D22" s="6">
+        <v>-3.5</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-2.25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="6">
+        <v>2.68</v>
+      </c>
+      <c r="D23" s="6">
+        <v>1.51</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-1.17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-4.82</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-7.09</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-2.27</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-0.99</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-1.69</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>-9.23</v>
+      </c>
+      <c r="D26" s="6">
+        <v>-11.55</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-2.32</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>42.39</v>
+      </c>
+      <c r="D27" s="6">
+        <v>35.07</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-7.32</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="6">
+        <v>2.74</v>
+      </c>
+      <c r="D28" s="6">
+        <v>1.83</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="6">
+        <v>27.71</v>
+      </c>
+      <c r="D29" s="6">
+        <v>25.27</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-2.44</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="6">
+        <v>5.23</v>
+      </c>
+      <c r="D30" s="6">
+        <v>6.72</v>
+      </c>
+      <c r="E30" s="8">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-42.89</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-44.32</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-1.43</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-12</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-14.21</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-2.21</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="6">
+        <v>4.99</v>
+      </c>
+      <c r="D33" s="6">
+        <v>3.1</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-1.89</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-11.91</v>
+      </c>
+      <c r="D34" s="6">
+        <v>-12.49</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-0.58</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="6">
+        <v>7.03</v>
+      </c>
+      <c r="D35" s="6">
+        <v>4.97</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-2.06</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="6">
+        <v>35.02</v>
+      </c>
+      <c r="D36" s="6">
+        <v>31.94</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-3.08</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="6">
+        <v>12.92</v>
+      </c>
+      <c r="D37" s="6">
+        <v>16.04</v>
+      </c>
+      <c r="E37" s="8">
+        <v>3.12</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="6">
+        <v>20.8</v>
+      </c>
+      <c r="D38" s="6">
+        <v>20.97</v>
+      </c>
+      <c r="E38" s="8">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-12.65</v>
+      </c>
+      <c r="D39" s="6">
+        <v>-13.58</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-0.93</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-3.85</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-2.51</v>
+      </c>
+      <c r="E40" s="8">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="6">
+        <v>5.42</v>
+      </c>
+      <c r="D41" s="6">
+        <v>2.93</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-2.49</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="6">
+        <v>-21.79</v>
+      </c>
+      <c r="D42" s="6">
+        <v>-22.14</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-0.35</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="6">
+        <v>-16.89</v>
+      </c>
+      <c r="D43" s="6">
+        <v>-17.16</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-0.27</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="6">
         <v>-9.199999999999999</v>
       </c>
-      <c r="E10" s="9">
-        <v>-0.36</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="D44" s="6">
+        <v>-11.78</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-2.58</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7">
-        <v>-6.83</v>
-      </c>
-      <c r="D11" s="7">
+      <c r="B45" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-13.17</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-12.24</v>
+      </c>
+      <c r="E45" s="8">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="6">
+        <v>-7.65</v>
+      </c>
+      <c r="D46" s="6">
+        <v>-9.25</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-1.6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="6">
+        <v>-1.2</v>
+      </c>
+      <c r="D47" s="6">
+        <v>-1.85</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-0.65</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="6">
+        <v>-43.18</v>
+      </c>
+      <c r="D48" s="6">
+        <v>-44.94</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-1.76</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="6">
+        <v>-19.23</v>
+      </c>
+      <c r="D49" s="6">
+        <v>-20.08</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-0.85</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="6">
+        <v>-11.84</v>
+      </c>
+      <c r="D50" s="6">
+        <v>-14.73</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-2.89</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C51" s="6">
+        <v>383.4</v>
+      </c>
+      <c r="D51" s="6">
+        <v>381.65</v>
+      </c>
+      <c r="E51" s="7">
+        <v>-1.75</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="6">
+        <v>3160</v>
+      </c>
+      <c r="D52" s="6">
+        <v>3150</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="6">
+        <v>374.35</v>
+      </c>
+      <c r="D53" s="6">
+        <v>363.75</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-10.6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="6">
+        <v>366.15</v>
+      </c>
+      <c r="D54" s="6">
+        <v>370.1</v>
+      </c>
+      <c r="E54" s="8">
+        <v>3.95</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="6">
+        <v>408.85</v>
+      </c>
+      <c r="D55" s="6">
+        <v>401.75</v>
+      </c>
+      <c r="E55" s="7">
+        <v>-7.1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="6">
+        <v>680.65</v>
+      </c>
+      <c r="D56" s="6">
+        <v>676.2</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-4.45</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="6">
+        <v>205.71</v>
+      </c>
+      <c r="D57" s="6">
+        <v>199.36</v>
+      </c>
+      <c r="E57" s="7">
+        <v>-6.35</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="6">
+        <v>3632.6</v>
+      </c>
+      <c r="D58" s="6">
+        <v>3594.3</v>
+      </c>
+      <c r="E58" s="7">
+        <v>-38.3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="6">
+        <v>1559</v>
+      </c>
+      <c r="D59" s="6">
+        <v>1508</v>
+      </c>
+      <c r="E59" s="7">
+        <v>-51</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C60" s="6">
+        <v>25.54</v>
+      </c>
+      <c r="D60" s="6">
+        <v>24.39</v>
+      </c>
+      <c r="E60" s="7">
+        <v>-1.15</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" s="6">
+        <v>34</v>
+      </c>
+      <c r="D61" s="6">
+        <v>33.19</v>
+      </c>
+      <c r="E61" s="7">
+        <v>-0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" s="6">
+        <v>48.78</v>
+      </c>
+      <c r="D62" s="6">
+        <v>41.93</v>
+      </c>
+      <c r="E62" s="7">
+        <v>-6.85</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="6">
+        <v>44.37</v>
+      </c>
+      <c r="D63" s="6">
+        <v>48.88</v>
+      </c>
+      <c r="E63" s="8">
+        <v>4.51</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="6">
+        <v>57.97</v>
+      </c>
+      <c r="D64" s="6">
+        <v>51.25</v>
+      </c>
+      <c r="E64" s="7">
+        <v>-6.72</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="6">
+        <v>67.73</v>
+      </c>
+      <c r="D65" s="6">
+        <v>65.33</v>
+      </c>
+      <c r="E65" s="7">
+        <v>-2.4</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="6">
+        <v>30.09</v>
+      </c>
+      <c r="D66" s="6">
+        <v>24.15</v>
+      </c>
+      <c r="E66" s="7">
+        <v>-5.94</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="6">
+        <v>56.37</v>
+      </c>
+      <c r="D67" s="6">
+        <v>49.26</v>
+      </c>
+      <c r="E67" s="7">
+        <v>-7.11</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="6">
+        <v>41.39</v>
+      </c>
+      <c r="D68" s="6">
+        <v>33.21</v>
+      </c>
+      <c r="E68" s="7">
+        <v>-8.18</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C69" s="6">
+        <v>-69.08</v>
+      </c>
+      <c r="D69" s="6">
+        <v>-35.44</v>
+      </c>
+      <c r="E69" s="8">
+        <v>33.64</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="6">
+        <v>-0.12</v>
+      </c>
+      <c r="D70" s="6">
+        <v>-40.17</v>
+      </c>
+      <c r="E70" s="7">
+        <v>-40.05</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C71" s="6">
+        <v>50.35</v>
+      </c>
+      <c r="D71" s="6">
+        <v>30.45</v>
+      </c>
+      <c r="E71" s="7">
+        <v>-19.9</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C72" s="6">
+        <v>-36.75</v>
+      </c>
+      <c r="D72" s="6">
+        <v>49.33</v>
+      </c>
+      <c r="E72" s="8">
+        <v>86.08</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="6">
         <v>-5.35</v>
       </c>
-      <c r="E11" s="8">
-        <v>1.48</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7">
-        <v>0.12</v>
-      </c>
-      <c r="D12" s="7">
-        <v>-0.61</v>
-      </c>
-      <c r="E12" s="9">
-        <v>-0.73</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+      <c r="D73" s="6">
+        <v>-14.87</v>
+      </c>
+      <c r="E73" s="7">
+        <v>-9.52</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="7">
-        <v>16.83</v>
-      </c>
-      <c r="D13" s="7">
-        <v>11.98</v>
-      </c>
-      <c r="E13" s="9">
-        <v>-4.85</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="B74" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="6">
+        <v>-43.55</v>
+      </c>
+      <c r="D74" s="6">
+        <v>-53.85</v>
+      </c>
+      <c r="E74" s="7">
+        <v>-10.3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="7">
-        <v>-10.51</v>
-      </c>
-      <c r="D14" s="7">
-        <v>-10.68</v>
-      </c>
-      <c r="E14" s="9">
-        <v>-0.17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+      <c r="B75" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="6">
+        <v>-8.289999999999999</v>
+      </c>
+      <c r="D75" s="6">
+        <v>155.72</v>
+      </c>
+      <c r="E75" s="8">
+        <v>164.01</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="7">
-        <v>1.32</v>
-      </c>
-      <c r="D15" s="7">
-        <v>0.84</v>
-      </c>
-      <c r="E15" s="9">
-        <v>-0.48</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="B76" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="6">
+        <v>16.28</v>
+      </c>
+      <c r="D76" s="6">
+        <v>26.46</v>
+      </c>
+      <c r="E76" s="8">
+        <v>10.18</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-4.34</v>
-      </c>
-      <c r="D16" s="7">
-        <v>-4.94</v>
-      </c>
-      <c r="E16" s="9">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-1.92</v>
-      </c>
-      <c r="D17" s="7">
-        <v>-1.91</v>
-      </c>
-      <c r="E17" s="8">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-3.72</v>
-      </c>
-      <c r="D18" s="7">
-        <v>-3.04</v>
-      </c>
-      <c r="E18" s="8">
-        <v>0.68</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="7">
-        <v>-0.17</v>
-      </c>
-      <c r="D19" s="7">
-        <v>2.73</v>
-      </c>
-      <c r="E19" s="8">
-        <v>2.9</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="7">
-        <v>-1.5</v>
-      </c>
-      <c r="D20" s="7">
-        <v>2.58</v>
-      </c>
-      <c r="E20" s="8">
-        <v>4.08</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="7">
-        <v>3</v>
-      </c>
-      <c r="D21" s="7">
-        <v>5.59</v>
-      </c>
-      <c r="E21" s="8">
-        <v>2.59</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="7">
-        <v>3.88</v>
-      </c>
-      <c r="D22" s="7">
-        <v>4.78</v>
-      </c>
-      <c r="E22" s="8">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="7">
-        <v>-1.97</v>
-      </c>
-      <c r="D23" s="7">
-        <v>-1.25</v>
-      </c>
-      <c r="E23" s="8">
-        <v>0.72</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="7">
-        <v>2.2</v>
-      </c>
-      <c r="D24" s="7">
-        <v>2.68</v>
-      </c>
-      <c r="E24" s="8">
-        <v>0.48</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="7">
-        <v>-3.93</v>
-      </c>
-      <c r="D25" s="7">
-        <v>-4.82</v>
-      </c>
-      <c r="E25" s="9">
-        <v>-0.89</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="7">
-        <v>-2.59</v>
-      </c>
-      <c r="D26" s="7">
-        <v>-0.99</v>
-      </c>
-      <c r="E26" s="8">
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="7">
-        <v>-3.83</v>
-      </c>
-      <c r="D27" s="7">
-        <v>-9.23</v>
-      </c>
-      <c r="E27" s="9">
-        <v>-5.4</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="7">
-        <v>43.38</v>
-      </c>
-      <c r="D28" s="7">
-        <v>42.39</v>
-      </c>
-      <c r="E28" s="9">
-        <v>-0.99</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="7">
-        <v>1.9</v>
-      </c>
-      <c r="D29" s="7">
-        <v>2.74</v>
-      </c>
-      <c r="E29" s="8">
-        <v>0.84</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="7">
-        <v>26.04</v>
-      </c>
-      <c r="D30" s="7">
-        <v>27.71</v>
-      </c>
-      <c r="E30" s="8">
-        <v>1.67</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="7">
-        <v>3.94</v>
-      </c>
-      <c r="D31" s="7">
-        <v>5.23</v>
-      </c>
-      <c r="E31" s="8">
-        <v>1.29</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="7">
-        <v>-42.53</v>
-      </c>
-      <c r="D32" s="7">
-        <v>-42.89</v>
-      </c>
-      <c r="E32" s="9">
-        <v>-0.36</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="7">
-        <v>-9.35</v>
-      </c>
-      <c r="D33" s="7">
-        <v>-12</v>
-      </c>
-      <c r="E33" s="9">
-        <v>-2.65</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="7">
-        <v>4.79</v>
-      </c>
-      <c r="D34" s="7">
-        <v>4.99</v>
-      </c>
-      <c r="E34" s="8">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="7">
-        <v>-12.91</v>
-      </c>
-      <c r="D35" s="7">
-        <v>-11.91</v>
-      </c>
-      <c r="E35" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="7">
-        <v>5.68</v>
-      </c>
-      <c r="D36" s="7">
-        <v>7.03</v>
-      </c>
-      <c r="E36" s="8">
-        <v>1.35</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="7">
-        <v>30.65</v>
-      </c>
-      <c r="D37" s="7">
-        <v>35.02</v>
-      </c>
-      <c r="E37" s="8">
-        <v>4.37</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="7">
-        <v>7.6</v>
-      </c>
-      <c r="D38" s="7">
-        <v>12.92</v>
-      </c>
-      <c r="E38" s="8">
-        <v>5.32</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="7">
-        <v>16.77</v>
-      </c>
-      <c r="D39" s="7">
-        <v>20.8</v>
-      </c>
-      <c r="E39" s="8">
-        <v>4.03</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="7">
-        <v>12.93</v>
-      </c>
-      <c r="D40" s="7">
-        <v>13.71</v>
-      </c>
-      <c r="E40" s="8">
-        <v>0.78</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="7">
-        <v>-11.06</v>
-      </c>
-      <c r="D41" s="7">
-        <v>-12.65</v>
-      </c>
-      <c r="E41" s="9">
-        <v>-1.59</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="7">
-        <v>-3.5</v>
-      </c>
-      <c r="D42" s="7">
-        <v>-3.85</v>
-      </c>
-      <c r="E42" s="9">
-        <v>-0.35</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="7">
-        <v>5.41</v>
-      </c>
-      <c r="D43" s="7">
-        <v>5.42</v>
-      </c>
-      <c r="E43" s="8">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="7">
-        <v>-21.76</v>
-      </c>
-      <c r="D44" s="7">
-        <v>-21.79</v>
-      </c>
-      <c r="E44" s="9">
-        <v>-0.03</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="7">
-        <v>-9.69</v>
-      </c>
-      <c r="D45" s="7">
-        <v>-9.199999999999999</v>
-      </c>
-      <c r="E45" s="8">
-        <v>0.49</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="7">
-        <v>-14.6</v>
-      </c>
-      <c r="D46" s="7">
-        <v>-13.17</v>
-      </c>
-      <c r="E46" s="8">
-        <v>1.43</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="7">
-        <v>-8.92</v>
-      </c>
-      <c r="D47" s="7">
-        <v>-7.65</v>
-      </c>
-      <c r="E47" s="8">
-        <v>1.27</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="7">
-        <v>0</v>
-      </c>
-      <c r="D48" s="7">
-        <v>-1.2</v>
-      </c>
-      <c r="E48" s="9">
-        <v>-1.2</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="7">
-        <v>-43.23</v>
-      </c>
-      <c r="D49" s="7">
-        <v>-43.18</v>
-      </c>
-      <c r="E49" s="8">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="7">
-        <v>-18.89</v>
-      </c>
-      <c r="D50" s="7">
-        <v>-19.23</v>
-      </c>
-      <c r="E50" s="9">
-        <v>-0.34</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="7">
-        <v>-11.56</v>
-      </c>
-      <c r="D51" s="7">
-        <v>-11.84</v>
-      </c>
-      <c r="E51" s="9">
-        <v>-0.28</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="7">
-        <v>383.55</v>
-      </c>
-      <c r="D52" s="7">
-        <v>383.4</v>
-      </c>
-      <c r="E52" s="9">
-        <v>-0.15</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="7">
-        <v>372.35</v>
-      </c>
-      <c r="D53" s="7">
-        <v>374.35</v>
-      </c>
-      <c r="E53" s="8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="7">
-        <v>360.15</v>
-      </c>
-      <c r="D54" s="7">
-        <v>366.15</v>
-      </c>
-      <c r="E54" s="8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="7">
-        <v>403.2</v>
-      </c>
-      <c r="D55" s="7">
-        <v>408.85</v>
-      </c>
-      <c r="E55" s="8">
-        <v>5.65</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="7">
-        <v>688.95</v>
-      </c>
-      <c r="D56" s="7">
-        <v>680.65</v>
-      </c>
-      <c r="E56" s="9">
-        <v>-8.300000000000001</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="7">
-        <v>205.53</v>
-      </c>
-      <c r="D57" s="7">
-        <v>205.71</v>
-      </c>
-      <c r="E57" s="8">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="7">
-        <v>3648</v>
-      </c>
-      <c r="D58" s="7">
-        <v>3632.6</v>
-      </c>
-      <c r="E58" s="9">
-        <v>-15.4</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="7">
-        <v>1564</v>
-      </c>
-      <c r="D59" s="7">
-        <v>1559</v>
-      </c>
-      <c r="E59" s="9">
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C60" s="7">
-        <v>55</v>
-      </c>
-      <c r="D60" s="7">
-        <v>66</v>
-      </c>
-      <c r="E60" s="8">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C61" s="7">
-        <v>66</v>
-      </c>
-      <c r="D61" s="7">
-        <v>55</v>
-      </c>
-      <c r="E61" s="9">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C62" s="7">
-        <v>25.63</v>
-      </c>
-      <c r="D62" s="7">
-        <v>25.54</v>
-      </c>
-      <c r="E62" s="9">
-        <v>-0.09</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C63" s="7">
-        <v>47.27</v>
-      </c>
-      <c r="D63" s="7">
-        <v>48.78</v>
-      </c>
-      <c r="E63" s="8">
-        <v>1.51</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="7">
-        <v>36.44</v>
-      </c>
-      <c r="D64" s="7">
-        <v>44.37</v>
-      </c>
-      <c r="E64" s="8">
-        <v>7.93</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="7">
-        <v>53.46</v>
-      </c>
-      <c r="D65" s="7">
-        <v>57.97</v>
-      </c>
-      <c r="E65" s="8">
-        <v>4.51</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="7">
-        <v>72.31999999999999</v>
-      </c>
-      <c r="D66" s="7">
-        <v>67.73</v>
-      </c>
-      <c r="E66" s="9">
-        <v>-4.59</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="7">
-        <v>29.64</v>
-      </c>
-      <c r="D67" s="7">
-        <v>30.09</v>
-      </c>
-      <c r="E67" s="8">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="7">
-        <v>59.59</v>
-      </c>
-      <c r="D68" s="7">
-        <v>56.37</v>
-      </c>
-      <c r="E68" s="9">
-        <v>-3.22</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="7">
-        <v>42.34</v>
-      </c>
-      <c r="D69" s="7">
-        <v>41.39</v>
-      </c>
-      <c r="E69" s="9">
-        <v>-0.95</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B70" s="6" t="s">
+      <c r="B77" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C70" s="7">
-        <v>-45.95</v>
-      </c>
-      <c r="D70" s="7">
-        <v>-69.08</v>
-      </c>
-      <c r="E70" s="9">
-        <v>-23.13</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B71" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C71" s="7">
-        <v>-7.91</v>
-      </c>
-      <c r="D71" s="7">
-        <v>-0.12</v>
-      </c>
-      <c r="E71" s="8">
-        <v>7.79</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C72" s="7">
-        <v>-11.85</v>
-      </c>
-      <c r="D72" s="7">
-        <v>50.35</v>
-      </c>
-      <c r="E72" s="8">
-        <v>62.2</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C73" s="7">
-        <v>-37.33</v>
-      </c>
-      <c r="D73" s="7">
-        <v>-36.75</v>
-      </c>
-      <c r="E73" s="8">
-        <v>0.58</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B74" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="7">
-        <v>-2.97</v>
-      </c>
-      <c r="D74" s="7">
-        <v>-5.35</v>
-      </c>
-      <c r="E74" s="9">
-        <v>-2.38</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B75" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="7">
-        <v>173.51</v>
-      </c>
-      <c r="D75" s="7">
-        <v>-43.55</v>
-      </c>
-      <c r="E75" s="9">
-        <v>-217.06</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B76" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="7">
-        <v>-6.44</v>
-      </c>
-      <c r="D76" s="7">
-        <v>-8.289999999999999</v>
-      </c>
-      <c r="E76" s="9">
-        <v>-1.85</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B77" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="7">
-        <v>378.84</v>
-      </c>
-      <c r="D77" s="7">
-        <v>16.28</v>
-      </c>
-      <c r="E77" s="9">
-        <v>-362.56</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B78" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="7">
-        <v>-14.75</v>
-      </c>
-      <c r="D78" s="7">
+      <c r="C77" s="6">
         <v>-27.92</v>
       </c>
-      <c r="E78" s="9">
-        <v>-13.17</v>
+      <c r="D77" s="6">
+        <v>-37.51</v>
+      </c>
+      <c r="E77" s="7">
+        <v>-9.59</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3440,60 +3391,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="H1" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="I1" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="E1" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>79</v>
-      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="12">
-        <v>56.16</v>
-      </c>
-      <c r="C2" s="13">
+      <c r="B2" s="11">
+        <v>48.16</v>
+      </c>
+      <c r="C2" s="12">
         <v>9</v>
       </c>
-      <c r="D2" s="12">
-        <v>45.1</v>
-      </c>
-      <c r="E2" s="12">
-        <v>60</v>
-      </c>
-      <c r="F2" s="12">
-        <v>-3.8</v>
-      </c>
-      <c r="G2" s="12">
-        <v>7.4</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="D2" s="11">
+        <v>41.3</v>
+      </c>
+      <c r="E2" s="11">
+        <v>40</v>
+      </c>
+      <c r="F2" s="11">
+        <v>-4.1</v>
+      </c>
+      <c r="G2" s="11">
+        <v>6.9</v>
+      </c>
+      <c r="H2" s="11">
         <v>55.4</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="11">
         <v>40</v>
       </c>
     </row>
@@ -3595,61 +3546,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="13" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="15">
-        <v>0.36</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0.3413</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0.1958</v>
-      </c>
-      <c r="D2" s="15">
-        <v>0.1927</v>
-      </c>
-      <c r="E2" s="15">
-        <v>0.1307</v>
-      </c>
-      <c r="F2" s="15">
-        <v>0.0599</v>
-      </c>
-      <c r="G2" s="15">
-        <v>0.04849999999999999</v>
-      </c>
-      <c r="H2" s="15">
-        <v>-0.0284</v>
-      </c>
-      <c r="I2" s="15">
-        <v>-0.1067</v>
+      <c r="A2" s="14">
+        <v>0.3574</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.3418</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.1956</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.1866</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.113</v>
+      </c>
+      <c r="F2" s="14">
+        <v>0.0613</v>
+      </c>
+      <c r="G2" s="14">
+        <v>0.0407</v>
+      </c>
+      <c r="H2" s="14">
+        <v>-0.0305</v>
+      </c>
+      <c r="I2" s="14">
+        <v>-0.1066</v>
       </c>
     </row>
   </sheetData>

--- a/MAHINDRA_GROUP_Technical_Metrics.xlsx
+++ b/MAHINDRA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="82">
   <si>
     <t>Symbol</t>
   </si>
@@ -193,19 +193,40 @@
     <t>Curr Value</t>
   </si>
   <si>
+    <t>RSI Overbought Entry</t>
+  </si>
+  <si>
+    <t>65.3 → 74.6</t>
+  </si>
+  <si>
+    <t>⚠️ CAUTION</t>
+  </si>
+  <si>
+    <t>65.3</t>
+  </si>
+  <si>
+    <t>74.6</t>
+  </si>
+  <si>
+    <t>Yes → No</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
+  </si>
+  <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>56.4 → 49.3</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>56.4</t>
-  </si>
-  <si>
-    <t>49.3</t>
+    <t>51.2 → 49.8</t>
+  </si>
+  <si>
+    <t>51.2</t>
+  </si>
+  <si>
+    <t>49.8</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -257,7 +278,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -291,6 +312,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -304,7 +332,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -326,6 +354,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF4A6FA5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -407,7 +441,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -415,14 +449,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -431,7 +466,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -930,10 +965,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>381.65</v>
+        <v>381.8</v>
       </c>
       <c r="D2">
-        <v>-0.46</v>
+        <v>0.04</v>
       </c>
       <c r="E2">
         <v>490.2</v>
@@ -942,46 +977,46 @@
         <v>381.65</v>
       </c>
       <c r="G2">
-        <v>-22.14</v>
+        <v>-22.11</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="I2">
-        <v>-0.87</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="J2">
-        <v>-7.59</v>
+        <v>-7.26</v>
       </c>
       <c r="K2">
-        <v>-12.49</v>
+        <v>-15.29</v>
       </c>
       <c r="L2">
-        <v>-1.69</v>
+        <v>-4.36</v>
       </c>
       <c r="M2">
-        <v>11.3</v>
+        <v>11.73</v>
       </c>
       <c r="N2">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="O2">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="P2">
-        <v>383.58</v>
+        <v>383.15</v>
       </c>
       <c r="Q2">
-        <v>395.34</v>
+        <v>394</v>
       </c>
       <c r="R2">
-        <v>422.19</v>
+        <v>420.35</v>
       </c>
       <c r="S2">
-        <v>435.65</v>
+        <v>435.53</v>
       </c>
       <c r="T2">
-        <v>-12.39</v>
+        <v>-12.34</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -996,43 +1031,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>24.39</v>
+        <v>24.7</v>
       </c>
       <c r="Z2">
-        <v>-10.6</v>
+        <v>-10.38</v>
       </c>
       <c r="AA2">
-        <v>-10.79</v>
+        <v>-10.71</v>
       </c>
       <c r="AB2">
-        <v>0.19</v>
+        <v>0.33</v>
       </c>
       <c r="AC2">
-        <v>7.87</v>
+        <v>5.73</v>
       </c>
       <c r="AD2">
-        <v>10.48</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="AE2">
-        <v>7.72</v>
+        <v>7.57</v>
       </c>
       <c r="AF2">
-        <v>-35.44</v>
+        <v>28.97</v>
       </c>
       <c r="AG2">
-        <v>414.89</v>
+        <v>413.4</v>
       </c>
       <c r="AH2">
-        <v>375.79</v>
+        <v>374.61</v>
       </c>
       <c r="AI2">
-        <v>406.9</v>
+        <v>406.13</v>
       </c>
       <c r="AJ2" t="s">
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>57.05</v>
+        <v>56.47</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1043,10 +1078,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>3150</v>
+        <v>3123.8</v>
       </c>
       <c r="D3">
-        <v>-0.32</v>
+        <v>-0.83</v>
       </c>
       <c r="E3">
         <v>3802.4</v>
@@ -1055,46 +1090,46 @@
         <v>2931.1</v>
       </c>
       <c r="G3">
-        <v>-17.16</v>
+        <v>-17.85</v>
       </c>
       <c r="H3">
-        <v>7.47</v>
+        <v>6.57</v>
       </c>
       <c r="I3">
-        <v>-1.25</v>
+        <v>-0.83</v>
       </c>
       <c r="J3">
-        <v>-8.960000000000001</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="K3">
-        <v>4.97</v>
+        <v>2.66</v>
       </c>
       <c r="L3">
-        <v>-11.55</v>
+        <v>-12.28</v>
       </c>
       <c r="M3">
-        <v>34.18</v>
+        <v>34.21</v>
       </c>
       <c r="N3">
         <v>45</v>
       </c>
       <c r="O3">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="P3">
-        <v>3158</v>
+        <v>3152.76</v>
       </c>
       <c r="Q3">
-        <v>3318.03</v>
+        <v>3302.82</v>
       </c>
       <c r="R3">
-        <v>3279.49</v>
+        <v>3278.46</v>
       </c>
       <c r="S3">
-        <v>3325.12</v>
+        <v>3322.29</v>
       </c>
       <c r="T3">
-        <v>-5.27</v>
+        <v>-5.97</v>
       </c>
       <c r="U3" t="s">
         <v>48</v>
@@ -1109,43 +1144,43 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>33.19</v>
+        <v>31.09</v>
       </c>
       <c r="Z3">
-        <v>-47.25</v>
+        <v>-52.42</v>
       </c>
       <c r="AA3">
-        <v>-16.82</v>
+        <v>-23.94</v>
       </c>
       <c r="AB3">
-        <v>-30.44</v>
+        <v>-28.48</v>
       </c>
       <c r="AC3">
-        <v>6.2</v>
+        <v>3.81</v>
       </c>
       <c r="AD3">
-        <v>6.64</v>
+        <v>6.02</v>
       </c>
       <c r="AE3">
-        <v>66.05</v>
+        <v>65.06999999999999</v>
       </c>
       <c r="AF3">
-        <v>-40.17</v>
+        <v>26.07</v>
       </c>
       <c r="AG3">
-        <v>3547.95</v>
+        <v>3542.13</v>
       </c>
       <c r="AH3">
-        <v>3088.12</v>
+        <v>3063.5</v>
       </c>
       <c r="AI3">
-        <v>3332.81</v>
+        <v>3317.51</v>
       </c>
       <c r="AJ3" t="s">
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>58.76</v>
+        <v>62.01</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1156,10 +1191,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>363.75</v>
+        <v>359.25</v>
       </c>
       <c r="D4">
-        <v>-2.83</v>
+        <v>-1.24</v>
       </c>
       <c r="E4">
         <v>412.3</v>
@@ -1168,46 +1203,46 @@
         <v>268.95</v>
       </c>
       <c r="G4">
-        <v>-11.78</v>
+        <v>-12.87</v>
       </c>
       <c r="H4">
-        <v>35.25</v>
+        <v>33.58</v>
       </c>
       <c r="I4">
-        <v>-1.38</v>
+        <v>-4.47</v>
       </c>
       <c r="J4">
-        <v>-8.789999999999999</v>
+        <v>-9.25</v>
       </c>
       <c r="K4">
-        <v>31.94</v>
+        <v>23.43</v>
       </c>
       <c r="L4">
-        <v>35.07</v>
+        <v>33.4</v>
       </c>
       <c r="M4">
-        <v>18.66</v>
+        <v>18.26</v>
       </c>
       <c r="N4">
         <v>99</v>
       </c>
       <c r="O4">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P4">
-        <v>372.03</v>
+        <v>368.67</v>
       </c>
       <c r="Q4">
-        <v>379.36</v>
+        <v>377.5</v>
       </c>
       <c r="R4">
-        <v>368.68</v>
+        <v>369.5</v>
       </c>
       <c r="S4">
-        <v>344.63</v>
+        <v>344.64</v>
       </c>
       <c r="T4">
-        <v>5.55</v>
+        <v>4.24</v>
       </c>
       <c r="U4" t="s">
         <v>48</v>
@@ -1222,34 +1257,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>41.93</v>
+        <v>39.4</v>
       </c>
       <c r="Z4">
-        <v>-1.18</v>
+        <v>-2.28</v>
       </c>
       <c r="AA4">
-        <v>1.62</v>
+        <v>0.84</v>
       </c>
       <c r="AB4">
-        <v>-2.8</v>
+        <v>-3.12</v>
       </c>
       <c r="AC4">
-        <v>32.23</v>
+        <v>19.85</v>
       </c>
       <c r="AD4">
-        <v>40.51</v>
+        <v>32.43</v>
       </c>
       <c r="AE4">
-        <v>11.77</v>
+        <v>11.53</v>
       </c>
       <c r="AF4">
-        <v>30.45</v>
+        <v>30.93</v>
       </c>
       <c r="AG4">
-        <v>396.91</v>
+        <v>395.32</v>
       </c>
       <c r="AH4">
-        <v>361.8</v>
+        <v>359.68</v>
       </c>
       <c r="AI4">
         <v>357.72</v>
@@ -1258,7 +1293,7 @@
         <v>50</v>
       </c>
       <c r="AK4">
-        <v>19.48</v>
+        <v>20.93</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1269,10 +1304,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>370.1</v>
+        <v>359.65</v>
       </c>
       <c r="D5">
-        <v>1.08</v>
+        <v>-2.82</v>
       </c>
       <c r="E5">
         <v>421.7</v>
@@ -1281,46 +1316,46 @@
         <v>294.25</v>
       </c>
       <c r="G5">
-        <v>-12.24</v>
+        <v>-14.71</v>
       </c>
       <c r="H5">
-        <v>25.78</v>
+        <v>22.23</v>
       </c>
       <c r="I5">
-        <v>3.09</v>
+        <v>-0.95</v>
       </c>
       <c r="J5">
-        <v>-3.28</v>
+        <v>-6.06</v>
       </c>
       <c r="K5">
-        <v>16.04</v>
+        <v>9.5</v>
       </c>
       <c r="L5">
-        <v>1.83</v>
+        <v>-3.06</v>
       </c>
       <c r="M5">
-        <v>6.13</v>
+        <v>5.37</v>
       </c>
       <c r="N5">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="O5">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="P5">
-        <v>364.38</v>
+        <v>363.69</v>
       </c>
       <c r="Q5">
-        <v>371.84</v>
+        <v>370.63</v>
       </c>
       <c r="R5">
-        <v>376</v>
+        <v>375.75</v>
       </c>
       <c r="S5">
-        <v>363</v>
+        <v>362.83</v>
       </c>
       <c r="T5">
-        <v>1.96</v>
+        <v>-0.88</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1332,37 +1367,37 @@
         <v>47</v>
       </c>
       <c r="X5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y5">
-        <v>48.88</v>
+        <v>39.7</v>
       </c>
       <c r="Z5">
-        <v>-3.91</v>
+        <v>-4.21</v>
       </c>
       <c r="AA5">
-        <v>-3.31</v>
+        <v>-3.49</v>
       </c>
       <c r="AB5">
-        <v>-0.6</v>
+        <v>-0.72</v>
       </c>
       <c r="AC5">
-        <v>65.16</v>
+        <v>71.26000000000001</v>
       </c>
       <c r="AD5">
-        <v>47.17</v>
+        <v>60.41</v>
       </c>
       <c r="AE5">
-        <v>10.28</v>
+        <v>10.41</v>
       </c>
       <c r="AF5">
-        <v>49.33</v>
+        <v>-33.86</v>
       </c>
       <c r="AG5">
-        <v>390.45</v>
+        <v>389.12</v>
       </c>
       <c r="AH5">
-        <v>353.23</v>
+        <v>352.15</v>
       </c>
       <c r="AI5">
         <v>386.7</v>
@@ -1371,7 +1406,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>40.05</v>
+        <v>38.91</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1382,10 +1417,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>401.75</v>
+        <v>400.1</v>
       </c>
       <c r="D6">
-        <v>-1.74</v>
+        <v>-0.41</v>
       </c>
       <c r="E6">
         <v>442.7</v>
@@ -1394,25 +1429,25 @@
         <v>279.55</v>
       </c>
       <c r="G6">
-        <v>-9.25</v>
+        <v>-9.619999999999999</v>
       </c>
       <c r="H6">
-        <v>43.71</v>
+        <v>43.12</v>
       </c>
       <c r="I6">
-        <v>2.37</v>
+        <v>-0.05</v>
       </c>
       <c r="J6">
-        <v>-1.86</v>
+        <v>-1.68</v>
       </c>
       <c r="K6">
-        <v>20.97</v>
+        <v>18.48</v>
       </c>
       <c r="L6">
-        <v>25.27</v>
+        <v>24.62</v>
       </c>
       <c r="M6">
-        <v>-10.66</v>
+        <v>-10.43</v>
       </c>
       <c r="N6">
         <v>88</v>
@@ -1421,61 +1456,61 @@
         <v>76</v>
       </c>
       <c r="P6">
-        <v>403.89</v>
+        <v>403.85</v>
       </c>
       <c r="Q6">
-        <v>400.64</v>
+        <v>400.34</v>
       </c>
       <c r="R6">
-        <v>400.5</v>
+        <v>400.78</v>
       </c>
       <c r="S6">
-        <v>369.11</v>
+        <v>369.53</v>
       </c>
       <c r="T6">
-        <v>8.84</v>
+        <v>8.27</v>
       </c>
       <c r="U6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V6" t="s">
         <v>48</v>
       </c>
       <c r="W6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="X6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y6">
-        <v>51.25</v>
+        <v>49.8</v>
       </c>
       <c r="Z6">
-        <v>0.36</v>
+        <v>0.28</v>
       </c>
       <c r="AA6">
-        <v>-0.11</v>
+        <v>-0.03</v>
       </c>
       <c r="AB6">
-        <v>0.47</v>
+        <v>0.31</v>
       </c>
       <c r="AC6">
-        <v>85.04000000000001</v>
+        <v>75.56</v>
       </c>
       <c r="AD6">
-        <v>90.79000000000001</v>
+        <v>85.56</v>
       </c>
       <c r="AE6">
-        <v>11.46</v>
+        <v>11.17</v>
       </c>
       <c r="AF6">
-        <v>-14.87</v>
+        <v>-38.02</v>
       </c>
       <c r="AG6">
-        <v>413.13</v>
+        <v>412.57</v>
       </c>
       <c r="AH6">
-        <v>388.14</v>
+        <v>388.11</v>
       </c>
       <c r="AI6">
         <v>372.35</v>
@@ -1484,7 +1519,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>25.64</v>
+        <v>25.65</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1495,58 +1530,58 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>676.2</v>
+        <v>718.95</v>
       </c>
       <c r="D7">
-        <v>-0.65</v>
+        <v>6.32</v>
       </c>
       <c r="E7">
-        <v>688.95</v>
+        <v>718.95</v>
       </c>
       <c r="F7">
         <v>506.45</v>
       </c>
       <c r="G7">
-        <v>-1.85</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>33.52</v>
+        <v>41.96</v>
       </c>
       <c r="I7">
-        <v>1.68</v>
+        <v>10.02</v>
       </c>
       <c r="J7">
-        <v>13.65</v>
+        <v>17.87</v>
       </c>
       <c r="K7">
-        <v>13.71</v>
+        <v>16.5</v>
       </c>
       <c r="L7">
-        <v>6.72</v>
+        <v>12.85</v>
       </c>
       <c r="M7">
-        <v>35.74</v>
+        <v>36.86</v>
       </c>
       <c r="N7">
         <v>77</v>
       </c>
       <c r="O7">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="P7">
-        <v>677.48</v>
+        <v>690.5700000000001</v>
       </c>
       <c r="Q7">
-        <v>645.14</v>
+        <v>650.49</v>
       </c>
       <c r="R7">
-        <v>609.9</v>
+        <v>612.1799999999999</v>
       </c>
       <c r="S7">
-        <v>588.9400000000001</v>
+        <v>589.6799999999999</v>
       </c>
       <c r="T7">
-        <v>14.82</v>
+        <v>21.92</v>
       </c>
       <c r="U7" t="s">
         <v>48</v>
@@ -1561,34 +1596,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>65.33</v>
+        <v>74.62</v>
       </c>
       <c r="Z7">
-        <v>20.98</v>
+        <v>23.94</v>
       </c>
       <c r="AA7">
-        <v>17.84</v>
+        <v>19.06</v>
       </c>
       <c r="AB7">
-        <v>3.14</v>
+        <v>4.88</v>
       </c>
       <c r="AC7">
-        <v>54.01</v>
+        <v>57.51</v>
       </c>
       <c r="AD7">
-        <v>65.63</v>
+        <v>62.37</v>
       </c>
       <c r="AE7">
-        <v>22.03</v>
+        <v>24.06</v>
       </c>
       <c r="AF7">
-        <v>-53.85</v>
+        <v>245.57</v>
       </c>
       <c r="AG7">
-        <v>697.3</v>
+        <v>709.78</v>
       </c>
       <c r="AH7">
-        <v>592.99</v>
+        <v>591.2</v>
       </c>
       <c r="AI7">
         <v>628.66</v>
@@ -1597,7 +1632,7 @@
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>72.01000000000001</v>
+        <v>72.84</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1608,58 +1643,58 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>199.36</v>
+        <v>196.57</v>
       </c>
       <c r="D8">
-        <v>-3.09</v>
+        <v>-1.4</v>
       </c>
       <c r="E8">
         <v>362.05</v>
       </c>
       <c r="F8">
-        <v>199.36</v>
+        <v>196.57</v>
       </c>
       <c r="G8">
-        <v>-44.94</v>
+        <v>-45.71</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
       <c r="I8">
-        <v>-3.5</v>
+        <v>-5.45</v>
       </c>
       <c r="J8">
-        <v>-11.62</v>
+        <v>-12.59</v>
       </c>
       <c r="K8">
-        <v>-13.58</v>
+        <v>-16.52</v>
       </c>
       <c r="L8">
-        <v>-44.32</v>
+        <v>-44.16</v>
       </c>
       <c r="M8">
-        <v>-3.05</v>
+        <v>-3.47</v>
       </c>
       <c r="N8">
         <v>12</v>
       </c>
       <c r="O8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P8">
-        <v>205.18</v>
+        <v>202.91</v>
       </c>
       <c r="Q8">
-        <v>214.61</v>
+        <v>213.25</v>
       </c>
       <c r="R8">
-        <v>221.65</v>
+        <v>220.84</v>
       </c>
       <c r="S8">
-        <v>258.33</v>
+        <v>257.72</v>
       </c>
       <c r="T8">
-        <v>-22.83</v>
+        <v>-23.73</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1674,43 +1709,43 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>24.15</v>
+        <v>22.09</v>
       </c>
       <c r="Z8">
-        <v>-5.62</v>
+        <v>-6.19</v>
       </c>
       <c r="AA8">
-        <v>-4.41</v>
+        <v>-4.76</v>
       </c>
       <c r="AB8">
-        <v>-1.21</v>
+        <v>-1.42</v>
       </c>
       <c r="AC8">
-        <v>2.57</v>
+        <v>1.74</v>
       </c>
       <c r="AD8">
-        <v>6.74</v>
+        <v>3.91</v>
       </c>
       <c r="AE8">
-        <v>5.69</v>
+        <v>5.83</v>
       </c>
       <c r="AF8">
-        <v>155.72</v>
+        <v>183.21</v>
       </c>
       <c r="AG8">
-        <v>230.85</v>
+        <v>230.75</v>
       </c>
       <c r="AH8">
-        <v>198.37</v>
+        <v>195.74</v>
       </c>
       <c r="AI8">
-        <v>219.93</v>
+        <v>214.31</v>
       </c>
       <c r="AJ8" t="s">
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>46.86</v>
+        <v>50.74</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1721,10 +1756,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>3594.3</v>
+        <v>3551</v>
       </c>
       <c r="D9">
-        <v>-1.05</v>
+        <v>-1.2</v>
       </c>
       <c r="E9">
         <v>4497.5</v>
@@ -1733,46 +1768,46 @@
         <v>3308.9</v>
       </c>
       <c r="G9">
-        <v>-20.08</v>
+        <v>-21.05</v>
       </c>
       <c r="H9">
-        <v>8.630000000000001</v>
+        <v>7.32</v>
       </c>
       <c r="I9">
-        <v>1.51</v>
+        <v>-0.1</v>
       </c>
       <c r="J9">
-        <v>-0.1</v>
+        <v>-1.6</v>
       </c>
       <c r="K9">
-        <v>-2.51</v>
+        <v>-4.12</v>
       </c>
       <c r="L9">
-        <v>-14.21</v>
+        <v>-19.45</v>
       </c>
       <c r="M9">
-        <v>19.56</v>
+        <v>19.61</v>
       </c>
       <c r="N9">
+        <v>23</v>
+      </c>
+      <c r="O9">
         <v>34</v>
       </c>
-      <c r="O9">
-        <v>38</v>
-      </c>
       <c r="P9">
-        <v>3597.48</v>
+        <v>3596.74</v>
       </c>
       <c r="Q9">
-        <v>3581.89</v>
+        <v>3578.53</v>
       </c>
       <c r="R9">
-        <v>3642.23</v>
+        <v>3631.18</v>
       </c>
       <c r="S9">
-        <v>3685.83</v>
+        <v>3685.01</v>
       </c>
       <c r="T9">
-        <v>-2.48</v>
+        <v>-3.64</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1787,34 +1822,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>49.26</v>
+        <v>42.71</v>
       </c>
       <c r="Z9">
-        <v>-11.65</v>
+        <v>-13.51</v>
       </c>
       <c r="AA9">
-        <v>-23.41</v>
+        <v>-21.43</v>
       </c>
       <c r="AB9">
-        <v>11.77</v>
+        <v>7.92</v>
       </c>
       <c r="AC9">
-        <v>82.2</v>
+        <v>60</v>
       </c>
       <c r="AD9">
-        <v>84.48999999999999</v>
+        <v>78.02</v>
       </c>
       <c r="AE9">
-        <v>64.15000000000001</v>
+        <v>63.74</v>
       </c>
       <c r="AF9">
-        <v>26.46</v>
+        <v>2.72</v>
       </c>
       <c r="AG9">
-        <v>3655.39</v>
+        <v>3651.18</v>
       </c>
       <c r="AH9">
-        <v>3508.39</v>
+        <v>3505.88</v>
       </c>
       <c r="AI9">
         <v>3684.57</v>
@@ -1823,7 +1858,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>35.3</v>
+        <v>32.74</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1834,10 +1869,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>1508</v>
+        <v>1525.8</v>
       </c>
       <c r="D10">
-        <v>-3.27</v>
+        <v>1.18</v>
       </c>
       <c r="E10">
         <v>1768.4</v>
@@ -1846,46 +1881,46 @@
         <v>1326.2</v>
       </c>
       <c r="G10">
-        <v>-14.73</v>
+        <v>-13.72</v>
       </c>
       <c r="H10">
-        <v>13.71</v>
+        <v>15.05</v>
       </c>
       <c r="I10">
-        <v>-7.09</v>
+        <v>-4.52</v>
       </c>
       <c r="J10">
-        <v>-8.220000000000001</v>
+        <v>-6.1</v>
       </c>
       <c r="K10">
-        <v>2.93</v>
+        <v>6.76</v>
       </c>
       <c r="L10">
-        <v>3.1</v>
+        <v>5.55</v>
       </c>
       <c r="M10">
-        <v>4.07</v>
+        <v>4.38</v>
       </c>
       <c r="N10">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="O10">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="P10">
-        <v>1565.18</v>
+        <v>1550.74</v>
       </c>
       <c r="Q10">
-        <v>1596.77</v>
+        <v>1591.11</v>
       </c>
       <c r="R10">
-        <v>1572.55</v>
+        <v>1574.64</v>
       </c>
       <c r="S10">
-        <v>1517.65</v>
+        <v>1517.81</v>
       </c>
       <c r="T10">
-        <v>-0.64</v>
+        <v>0.53</v>
       </c>
       <c r="U10" t="s">
         <v>48</v>
@@ -1897,37 +1932,37 @@
         <v>48</v>
       </c>
       <c r="X10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y10">
-        <v>33.21</v>
+        <v>37.83</v>
       </c>
       <c r="Z10">
-        <v>-6.9</v>
+        <v>-10.87</v>
       </c>
       <c r="AA10">
-        <v>5.09</v>
+        <v>1.89</v>
       </c>
       <c r="AB10">
-        <v>-11.99</v>
+        <v>-12.77</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AD10">
-        <v>9.4</v>
+        <v>4.93</v>
       </c>
       <c r="AE10">
-        <v>38.73</v>
+        <v>39.3</v>
       </c>
       <c r="AF10">
-        <v>-37.51</v>
+        <v>-33.01</v>
       </c>
       <c r="AG10">
-        <v>1661.95</v>
+        <v>1660.38</v>
       </c>
       <c r="AH10">
-        <v>1531.59</v>
+        <v>1521.84</v>
       </c>
       <c r="AI10">
         <v>1630.7</v>
@@ -1936,7 +1971,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>33.84</v>
+        <v>35.4</v>
       </c>
     </row>
   </sheetData>
@@ -2077,7 +2112,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F77"/>
+  <dimension ref="A1:F85"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2117,7 +2152,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2135,1243 +2170,1388 @@
         <v>61</v>
       </c>
     </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="D5" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E6" s="3" t="s">
+      <c r="B9" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="7">
+        <v>-7.59</v>
+      </c>
+      <c r="D10" s="7">
+        <v>-7.26</v>
+      </c>
+      <c r="E10" s="8">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="7">
+        <v>-8.960000000000001</v>
+      </c>
+      <c r="D11" s="7">
+        <v>-8.220000000000001</v>
+      </c>
+      <c r="E11" s="8">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="7">
+        <v>-8.789999999999999</v>
+      </c>
+      <c r="D12" s="7">
+        <v>-9.25</v>
+      </c>
+      <c r="E12" s="9">
+        <v>-0.46</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="7">
+        <v>-3.28</v>
+      </c>
+      <c r="D13" s="7">
+        <v>-6.06</v>
+      </c>
+      <c r="E13" s="9">
+        <v>-2.78</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="7">
+        <v>-1.86</v>
+      </c>
+      <c r="D14" s="7">
+        <v>-1.68</v>
+      </c>
+      <c r="E14" s="8">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="7">
+        <v>13.65</v>
+      </c>
+      <c r="D15" s="7">
+        <v>17.87</v>
+      </c>
+      <c r="E15" s="8">
+        <v>4.22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-11.62</v>
+      </c>
+      <c r="D16" s="7">
+        <v>-12.59</v>
+      </c>
+      <c r="E16" s="9">
+        <v>-0.97</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-0.1</v>
+      </c>
+      <c r="D17" s="7">
+        <v>-1.6</v>
+      </c>
+      <c r="E17" s="9">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-8.220000000000001</v>
+      </c>
+      <c r="D18" s="7">
+        <v>-6.1</v>
+      </c>
+      <c r="E18" s="8">
+        <v>2.12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="7">
+        <v>-0.87</v>
+      </c>
+      <c r="D19" s="7">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="E19" s="8">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="7">
+        <v>-1.25</v>
+      </c>
+      <c r="D20" s="7">
+        <v>-0.83</v>
+      </c>
+      <c r="E20" s="8">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-1.38</v>
+      </c>
+      <c r="D21" s="7">
+        <v>-4.47</v>
+      </c>
+      <c r="E21" s="9">
+        <v>-3.09</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="7">
+        <v>3.09</v>
+      </c>
+      <c r="D22" s="7">
+        <v>-0.95</v>
+      </c>
+      <c r="E22" s="9">
+        <v>-4.04</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="7">
+        <v>2.37</v>
+      </c>
+      <c r="D23" s="7">
+        <v>-0.05</v>
+      </c>
+      <c r="E23" s="9">
+        <v>-2.42</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="7">
+        <v>1.68</v>
+      </c>
+      <c r="D24" s="7">
+        <v>10.02</v>
+      </c>
+      <c r="E24" s="8">
+        <v>8.34</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="7">
+        <v>-3.5</v>
+      </c>
+      <c r="D25" s="7">
+        <v>-5.45</v>
+      </c>
+      <c r="E25" s="9">
+        <v>-1.95</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="7">
+        <v>1.51</v>
+      </c>
+      <c r="D26" s="7">
+        <v>-0.1</v>
+      </c>
+      <c r="E26" s="9">
+        <v>-1.61</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="7">
+        <v>-7.09</v>
+      </c>
+      <c r="D27" s="7">
+        <v>-4.52</v>
+      </c>
+      <c r="E27" s="8">
+        <v>2.57</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="7">
+        <v>-1.69</v>
+      </c>
+      <c r="D28" s="7">
+        <v>-4.36</v>
+      </c>
+      <c r="E28" s="9">
+        <v>-2.67</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="7">
+        <v>-11.55</v>
+      </c>
+      <c r="D29" s="7">
+        <v>-12.28</v>
+      </c>
+      <c r="E29" s="9">
+        <v>-0.73</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="7">
+        <v>35.07</v>
+      </c>
+      <c r="D30" s="7">
+        <v>33.4</v>
+      </c>
+      <c r="E30" s="9">
+        <v>-1.67</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="7">
+        <v>1.83</v>
+      </c>
+      <c r="D31" s="7">
+        <v>-3.06</v>
+      </c>
+      <c r="E31" s="9">
+        <v>-4.89</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="7">
+        <v>25.27</v>
+      </c>
+      <c r="D32" s="7">
+        <v>24.62</v>
+      </c>
+      <c r="E32" s="9">
+        <v>-0.65</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="7">
+        <v>6.72</v>
+      </c>
+      <c r="D33" s="7">
+        <v>12.85</v>
+      </c>
+      <c r="E33" s="8">
+        <v>6.13</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="7">
+        <v>-44.32</v>
+      </c>
+      <c r="D34" s="7">
+        <v>-44.16</v>
+      </c>
+      <c r="E34" s="8">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" s="7">
+        <v>-14.21</v>
+      </c>
+      <c r="D35" s="7">
+        <v>-19.45</v>
+      </c>
+      <c r="E35" s="9">
+        <v>-5.24</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36" s="7">
+        <v>3.1</v>
+      </c>
+      <c r="D36" s="7">
+        <v>5.55</v>
+      </c>
+      <c r="E36" s="8">
+        <v>2.45</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="7">
+        <v>-12.49</v>
+      </c>
+      <c r="D37" s="7">
+        <v>-15.29</v>
+      </c>
+      <c r="E37" s="9">
+        <v>-2.8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="7">
+        <v>4.97</v>
+      </c>
+      <c r="D38" s="7">
+        <v>2.66</v>
+      </c>
+      <c r="E38" s="9">
+        <v>-2.31</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="7">
+        <v>31.94</v>
+      </c>
+      <c r="D39" s="7">
+        <v>23.43</v>
+      </c>
+      <c r="E39" s="9">
+        <v>-8.51</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="7">
+        <v>16.04</v>
+      </c>
+      <c r="D40" s="7">
+        <v>9.5</v>
+      </c>
+      <c r="E40" s="9">
+        <v>-6.54</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="7">
+        <v>20.97</v>
+      </c>
+      <c r="D41" s="7">
+        <v>18.48</v>
+      </c>
+      <c r="E41" s="9">
+        <v>-2.49</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="7">
+        <v>13.71</v>
+      </c>
+      <c r="D42" s="7">
+        <v>16.5</v>
+      </c>
+      <c r="E42" s="8">
+        <v>2.79</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="7">
+        <v>-13.58</v>
+      </c>
+      <c r="D43" s="7">
+        <v>-16.52</v>
+      </c>
+      <c r="E43" s="9">
+        <v>-2.94</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="7">
+        <v>-2.51</v>
+      </c>
+      <c r="D44" s="7">
+        <v>-4.12</v>
+      </c>
+      <c r="E44" s="9">
+        <v>-1.61</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="7">
+        <v>2.93</v>
+      </c>
+      <c r="D45" s="7">
+        <v>6.76</v>
+      </c>
+      <c r="E45" s="8">
+        <v>3.83</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="7">
+        <v>-22.14</v>
+      </c>
+      <c r="D46" s="7">
+        <v>-22.11</v>
+      </c>
+      <c r="E46" s="8">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="7">
+        <v>-17.16</v>
+      </c>
+      <c r="D47" s="7">
+        <v>-17.85</v>
+      </c>
+      <c r="E47" s="9">
+        <v>-0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="7">
+        <v>-11.78</v>
+      </c>
+      <c r="D48" s="7">
+        <v>-12.87</v>
+      </c>
+      <c r="E48" s="9">
+        <v>-1.09</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="7">
+        <v>-12.24</v>
+      </c>
+      <c r="D49" s="7">
+        <v>-14.71</v>
+      </c>
+      <c r="E49" s="9">
+        <v>-2.47</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="7">
+        <v>-9.25</v>
+      </c>
+      <c r="D50" s="7">
+        <v>-9.619999999999999</v>
+      </c>
+      <c r="E50" s="9">
+        <v>-0.37</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="7">
+        <v>-1.85</v>
+      </c>
+      <c r="D51" s="7">
+        <v>0</v>
+      </c>
+      <c r="E51" s="8">
+        <v>1.85</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="7">
+        <v>-44.94</v>
+      </c>
+      <c r="D52" s="7">
+        <v>-45.71</v>
+      </c>
+      <c r="E52" s="9">
+        <v>-0.77</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53" s="7">
+        <v>-20.08</v>
+      </c>
+      <c r="D53" s="7">
+        <v>-21.05</v>
+      </c>
+      <c r="E53" s="9">
+        <v>-0.97</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54" s="7">
+        <v>-14.73</v>
+      </c>
+      <c r="D54" s="7">
+        <v>-13.72</v>
+      </c>
+      <c r="E54" s="8">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="7">
+        <v>381.65</v>
+      </c>
+      <c r="D55" s="7">
+        <v>381.8</v>
+      </c>
+      <c r="E55" s="8">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="7">
+        <v>3150</v>
+      </c>
+      <c r="D56" s="7">
+        <v>3123.8</v>
+      </c>
+      <c r="E56" s="9">
+        <v>-26.2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="7">
+        <v>363.75</v>
+      </c>
+      <c r="D57" s="7">
+        <v>359.25</v>
+      </c>
+      <c r="E57" s="9">
+        <v>-4.5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="7">
+        <v>370.1</v>
+      </c>
+      <c r="D58" s="7">
+        <v>359.65</v>
+      </c>
+      <c r="E58" s="9">
+        <v>-10.45</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="7">
+        <v>401.75</v>
+      </c>
+      <c r="D59" s="7">
+        <v>400.1</v>
+      </c>
+      <c r="E59" s="9">
+        <v>-1.65</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="7">
+        <v>676.2</v>
+      </c>
+      <c r="D60" s="7">
+        <v>718.95</v>
+      </c>
+      <c r="E60" s="8">
+        <v>42.75</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C61" s="7">
+        <v>199.36</v>
+      </c>
+      <c r="D61" s="7">
+        <v>196.57</v>
+      </c>
+      <c r="E61" s="9">
+        <v>-2.79</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C62" s="7">
+        <v>3594.3</v>
+      </c>
+      <c r="D62" s="7">
+        <v>3551</v>
+      </c>
+      <c r="E62" s="9">
+        <v>-43.3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C63" s="7">
+        <v>1508</v>
+      </c>
+      <c r="D63" s="7">
+        <v>1525.8</v>
+      </c>
+      <c r="E63" s="8">
+        <v>17.8</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C64" s="7">
+        <v>23</v>
+      </c>
+      <c r="D64" s="7">
+        <v>34</v>
+      </c>
+      <c r="E64" s="8">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C65" s="7">
         <v>66</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="D65" s="7">
+        <v>55</v>
+      </c>
+      <c r="E65" s="9">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C66" s="7">
+        <v>34</v>
+      </c>
+      <c r="D66" s="7">
+        <v>23</v>
+      </c>
+      <c r="E66" s="9">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C67" s="7">
+        <v>55</v>
+      </c>
+      <c r="D67" s="7">
+        <v>66</v>
+      </c>
+      <c r="E67" s="8">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="6">
-        <v>-6.37</v>
-      </c>
-      <c r="D7" s="6">
-        <v>-7.59</v>
-      </c>
-      <c r="E7" s="7">
-        <v>-1.22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="B68" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="7">
+        <v>24.39</v>
+      </c>
+      <c r="D68" s="7">
+        <v>24.7</v>
+      </c>
+      <c r="E68" s="8">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>-10.15</v>
-      </c>
-      <c r="D8" s="6">
-        <v>-8.960000000000001</v>
-      </c>
-      <c r="E8" s="8">
-        <v>1.19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="B69" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="7">
+        <v>33.19</v>
+      </c>
+      <c r="D69" s="7">
+        <v>31.09</v>
+      </c>
+      <c r="E69" s="9">
+        <v>-2.1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-9.199999999999999</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-8.789999999999999</v>
-      </c>
-      <c r="E9" s="8">
-        <v>0.41</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="B70" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="7">
+        <v>41.93</v>
+      </c>
+      <c r="D70" s="7">
+        <v>39.4</v>
+      </c>
+      <c r="E70" s="9">
+        <v>-2.53</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-5.35</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-3.28</v>
-      </c>
-      <c r="E10" s="8">
-        <v>2.07</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B71" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="7">
+        <v>48.88</v>
+      </c>
+      <c r="D71" s="7">
+        <v>39.7</v>
+      </c>
+      <c r="E71" s="9">
+        <v>-9.18</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-0.61</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-1.86</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-1.25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B72" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C72" s="7">
+        <v>51.25</v>
+      </c>
+      <c r="D72" s="7">
+        <v>49.8</v>
+      </c>
+      <c r="E72" s="9">
+        <v>-1.45</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>11.98</v>
-      </c>
-      <c r="D12" s="6">
-        <v>13.65</v>
-      </c>
-      <c r="E12" s="8">
-        <v>1.67</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B73" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C73" s="7">
+        <v>65.33</v>
+      </c>
+      <c r="D73" s="7">
+        <v>74.62</v>
+      </c>
+      <c r="E73" s="8">
+        <v>9.289999999999999</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-10.68</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-11.62</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-0.9399999999999999</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B74" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C74" s="7">
+        <v>24.15</v>
+      </c>
+      <c r="D74" s="7">
+        <v>22.09</v>
+      </c>
+      <c r="E74" s="9">
+        <v>-2.06</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="6">
-        <v>0.84</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-0.1</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-0.9399999999999999</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B75" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C75" s="7">
+        <v>49.26</v>
+      </c>
+      <c r="D75" s="7">
+        <v>42.71</v>
+      </c>
+      <c r="E75" s="9">
+        <v>-6.55</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-4.94</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-8.220000000000001</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-3.28</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B76" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C76" s="7">
+        <v>33.21</v>
+      </c>
+      <c r="D76" s="7">
+        <v>37.83</v>
+      </c>
+      <c r="E76" s="8">
+        <v>4.62</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-1.91</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-0.87</v>
-      </c>
-      <c r="E16" s="8">
-        <v>1.04</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B77" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="7">
+        <v>-35.44</v>
+      </c>
+      <c r="D77" s="7">
+        <v>28.97</v>
+      </c>
+      <c r="E77" s="8">
+        <v>64.41</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-3.04</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-1.25</v>
-      </c>
-      <c r="E17" s="8">
-        <v>1.79</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B78" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="7">
+        <v>-40.17</v>
+      </c>
+      <c r="D78" s="7">
+        <v>26.07</v>
+      </c>
+      <c r="E78" s="8">
+        <v>66.23999999999999</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>2.73</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-1.38</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-4.11</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B79" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="7">
+        <v>30.45</v>
+      </c>
+      <c r="D79" s="7">
+        <v>30.93</v>
+      </c>
+      <c r="E79" s="8">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>2.58</v>
-      </c>
-      <c r="D19" s="6">
-        <v>3.09</v>
-      </c>
-      <c r="E19" s="8">
-        <v>0.51</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B80" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="7">
+        <v>49.33</v>
+      </c>
+      <c r="D80" s="7">
+        <v>-33.86</v>
+      </c>
+      <c r="E80" s="9">
+        <v>-83.19</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>5.59</v>
-      </c>
-      <c r="D20" s="6">
-        <v>2.37</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-3.22</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B81" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81" s="7">
+        <v>-14.87</v>
+      </c>
+      <c r="D81" s="7">
+        <v>-38.02</v>
+      </c>
+      <c r="E81" s="9">
+        <v>-23.15</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6">
-        <v>4.78</v>
-      </c>
-      <c r="D21" s="6">
-        <v>1.68</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-3.1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B82" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C82" s="7">
+        <v>-53.85</v>
+      </c>
+      <c r="D82" s="7">
+        <v>245.57</v>
+      </c>
+      <c r="E82" s="8">
+        <v>299.42</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-1.25</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-3.5</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-2.25</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B83" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C83" s="7">
+        <v>155.72</v>
+      </c>
+      <c r="D83" s="7">
+        <v>183.21</v>
+      </c>
+      <c r="E83" s="8">
+        <v>27.49</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="6">
-        <v>2.68</v>
-      </c>
-      <c r="D23" s="6">
-        <v>1.51</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-1.17</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B84" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C84" s="7">
+        <v>26.46</v>
+      </c>
+      <c r="D84" s="7">
+        <v>2.72</v>
+      </c>
+      <c r="E84" s="9">
+        <v>-23.74</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-4.82</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-7.09</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-2.27</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-0.99</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-1.69</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-0.7</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>-9.23</v>
-      </c>
-      <c r="D26" s="6">
-        <v>-11.55</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-2.32</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>42.39</v>
-      </c>
-      <c r="D27" s="6">
-        <v>35.07</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-7.32</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="6">
-        <v>2.74</v>
-      </c>
-      <c r="D28" s="6">
-        <v>1.83</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-0.91</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="6">
-        <v>27.71</v>
-      </c>
-      <c r="D29" s="6">
-        <v>25.27</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-2.44</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="6">
-        <v>5.23</v>
-      </c>
-      <c r="D30" s="6">
-        <v>6.72</v>
-      </c>
-      <c r="E30" s="8">
-        <v>1.49</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-42.89</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-44.32</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-1.43</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-12</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-14.21</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-2.21</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="6">
-        <v>4.99</v>
-      </c>
-      <c r="D33" s="6">
-        <v>3.1</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-1.89</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="6">
-        <v>-11.91</v>
-      </c>
-      <c r="D34" s="6">
-        <v>-12.49</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-0.58</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="6">
-        <v>7.03</v>
-      </c>
-      <c r="D35" s="6">
-        <v>4.97</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-2.06</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="6">
-        <v>35.02</v>
-      </c>
-      <c r="D36" s="6">
-        <v>31.94</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-3.08</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="6">
-        <v>12.92</v>
-      </c>
-      <c r="D37" s="6">
-        <v>16.04</v>
-      </c>
-      <c r="E37" s="8">
-        <v>3.12</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="6">
-        <v>20.8</v>
-      </c>
-      <c r="D38" s="6">
-        <v>20.97</v>
-      </c>
-      <c r="E38" s="8">
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="6">
-        <v>-12.65</v>
-      </c>
-      <c r="D39" s="6">
-        <v>-13.58</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-0.93</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-3.85</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-2.51</v>
-      </c>
-      <c r="E40" s="8">
-        <v>1.34</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="6">
-        <v>5.42</v>
-      </c>
-      <c r="D41" s="6">
-        <v>2.93</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-2.49</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="6">
-        <v>-21.79</v>
-      </c>
-      <c r="D42" s="6">
-        <v>-22.14</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-0.35</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="6">
-        <v>-16.89</v>
-      </c>
-      <c r="D43" s="6">
-        <v>-17.16</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-0.27</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="6">
-        <v>-9.199999999999999</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-11.78</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-2.58</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-13.17</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-12.24</v>
-      </c>
-      <c r="E45" s="8">
-        <v>0.93</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-7.65</v>
-      </c>
-      <c r="D46" s="6">
-        <v>-9.25</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-1.6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="6">
-        <v>-1.2</v>
-      </c>
-      <c r="D47" s="6">
-        <v>-1.85</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-0.65</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="6">
-        <v>-43.18</v>
-      </c>
-      <c r="D48" s="6">
-        <v>-44.94</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-1.76</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="6">
-        <v>-19.23</v>
-      </c>
-      <c r="D49" s="6">
-        <v>-20.08</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-0.85</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="6">
-        <v>-11.84</v>
-      </c>
-      <c r="D50" s="6">
-        <v>-14.73</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-2.89</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C51" s="6">
-        <v>383.4</v>
-      </c>
-      <c r="D51" s="6">
-        <v>381.65</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-1.75</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="6">
-        <v>3160</v>
-      </c>
-      <c r="D52" s="6">
-        <v>3150</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="6">
-        <v>374.35</v>
-      </c>
-      <c r="D53" s="6">
-        <v>363.75</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-10.6</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="6">
-        <v>366.15</v>
-      </c>
-      <c r="D54" s="6">
-        <v>370.1</v>
-      </c>
-      <c r="E54" s="8">
-        <v>3.95</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="6">
-        <v>408.85</v>
-      </c>
-      <c r="D55" s="6">
-        <v>401.75</v>
-      </c>
-      <c r="E55" s="7">
-        <v>-7.1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="6">
-        <v>680.65</v>
-      </c>
-      <c r="D56" s="6">
-        <v>676.2</v>
-      </c>
-      <c r="E56" s="7">
-        <v>-4.45</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="6">
-        <v>205.71</v>
-      </c>
-      <c r="D57" s="6">
-        <v>199.36</v>
-      </c>
-      <c r="E57" s="7">
-        <v>-6.35</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="6">
-        <v>3632.6</v>
-      </c>
-      <c r="D58" s="6">
-        <v>3594.3</v>
-      </c>
-      <c r="E58" s="7">
-        <v>-38.3</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="6">
-        <v>1559</v>
-      </c>
-      <c r="D59" s="6">
-        <v>1508</v>
-      </c>
-      <c r="E59" s="7">
-        <v>-51</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C60" s="6">
-        <v>25.54</v>
-      </c>
-      <c r="D60" s="6">
-        <v>24.39</v>
-      </c>
-      <c r="E60" s="7">
-        <v>-1.15</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C61" s="6">
-        <v>34</v>
-      </c>
-      <c r="D61" s="6">
-        <v>33.19</v>
-      </c>
-      <c r="E61" s="7">
-        <v>-0.8100000000000001</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C62" s="6">
-        <v>48.78</v>
-      </c>
-      <c r="D62" s="6">
-        <v>41.93</v>
-      </c>
-      <c r="E62" s="7">
-        <v>-6.85</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C63" s="6">
-        <v>44.37</v>
-      </c>
-      <c r="D63" s="6">
-        <v>48.88</v>
-      </c>
-      <c r="E63" s="8">
-        <v>4.51</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="6">
-        <v>57.97</v>
-      </c>
-      <c r="D64" s="6">
-        <v>51.25</v>
-      </c>
-      <c r="E64" s="7">
-        <v>-6.72</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="6">
-        <v>67.73</v>
-      </c>
-      <c r="D65" s="6">
-        <v>65.33</v>
-      </c>
-      <c r="E65" s="7">
-        <v>-2.4</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="6">
-        <v>30.09</v>
-      </c>
-      <c r="D66" s="6">
-        <v>24.15</v>
-      </c>
-      <c r="E66" s="7">
-        <v>-5.94</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="6">
-        <v>56.37</v>
-      </c>
-      <c r="D67" s="6">
-        <v>49.26</v>
-      </c>
-      <c r="E67" s="7">
-        <v>-7.11</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="6">
-        <v>41.39</v>
-      </c>
-      <c r="D68" s="6">
-        <v>33.21</v>
-      </c>
-      <c r="E68" s="7">
-        <v>-8.18</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B69" s="5" t="s">
+      <c r="B85" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C69" s="6">
-        <v>-69.08</v>
-      </c>
-      <c r="D69" s="6">
-        <v>-35.44</v>
-      </c>
-      <c r="E69" s="8">
-        <v>33.64</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C70" s="6">
-        <v>-0.12</v>
-      </c>
-      <c r="D70" s="6">
-        <v>-40.17</v>
-      </c>
-      <c r="E70" s="7">
-        <v>-40.05</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C71" s="6">
-        <v>50.35</v>
-      </c>
-      <c r="D71" s="6">
-        <v>30.45</v>
-      </c>
-      <c r="E71" s="7">
-        <v>-19.9</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C72" s="6">
-        <v>-36.75</v>
-      </c>
-      <c r="D72" s="6">
-        <v>49.33</v>
-      </c>
-      <c r="E72" s="8">
-        <v>86.08</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C73" s="6">
-        <v>-5.35</v>
-      </c>
-      <c r="D73" s="6">
-        <v>-14.87</v>
-      </c>
-      <c r="E73" s="7">
-        <v>-9.52</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="6">
-        <v>-43.55</v>
-      </c>
-      <c r="D74" s="6">
-        <v>-53.85</v>
-      </c>
-      <c r="E74" s="7">
-        <v>-10.3</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="6">
-        <v>-8.289999999999999</v>
-      </c>
-      <c r="D75" s="6">
-        <v>155.72</v>
-      </c>
-      <c r="E75" s="8">
-        <v>164.01</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="6">
-        <v>16.28</v>
-      </c>
-      <c r="D76" s="6">
-        <v>26.46</v>
-      </c>
-      <c r="E76" s="8">
-        <v>10.18</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="6">
-        <v>-27.92</v>
-      </c>
-      <c r="D77" s="6">
+      <c r="C85" s="7">
         <v>-37.51</v>
       </c>
-      <c r="E77" s="7">
-        <v>-9.59</v>
+      <c r="D85" s="7">
+        <v>-33.01</v>
+      </c>
+      <c r="E85" s="8">
+        <v>4.5</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A8:E8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3391,61 +3571,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="I1" s="9" t="s">
+      <c r="B1" s="10" t="s">
         <v>74</v>
       </c>
+      <c r="C1" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="12">
         <v>48.16</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="13">
         <v>9</v>
       </c>
-      <c r="D2" s="11">
-        <v>41.3</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="12">
+        <v>40.2</v>
+      </c>
+      <c r="E2" s="12">
         <v>40</v>
       </c>
-      <c r="F2" s="11">
-        <v>-4.1</v>
-      </c>
-      <c r="G2" s="11">
-        <v>6.9</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="12">
+        <v>-3.9</v>
+      </c>
+      <c r="G2" s="12">
+        <v>4.6</v>
+      </c>
+      <c r="H2" s="12">
         <v>55.4</v>
       </c>
-      <c r="I2" s="11">
-        <v>40</v>
+      <c r="I2" s="12">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -3546,61 +3726,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="14" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="14">
-        <v>0.3574</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.3418</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.1956</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.1866</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.113</v>
-      </c>
-      <c r="F2" s="14">
-        <v>0.0613</v>
-      </c>
-      <c r="G2" s="14">
-        <v>0.0407</v>
-      </c>
-      <c r="H2" s="14">
-        <v>-0.0305</v>
-      </c>
-      <c r="I2" s="14">
-        <v>-0.1066</v>
+      <c r="A2" s="15">
+        <v>0.3686</v>
+      </c>
+      <c r="B2" s="15">
+        <v>0.3421</v>
+      </c>
+      <c r="C2" s="15">
+        <v>0.1961</v>
+      </c>
+      <c r="D2" s="15">
+        <v>0.1826</v>
+      </c>
+      <c r="E2" s="15">
+        <v>0.1173</v>
+      </c>
+      <c r="F2" s="15">
+        <v>0.0537</v>
+      </c>
+      <c r="G2" s="15">
+        <v>0.0438</v>
+      </c>
+      <c r="H2" s="15">
+        <v>-0.0347</v>
+      </c>
+      <c r="I2" s="15">
+        <v>-0.1043</v>
       </c>
     </row>
   </sheetData>

--- a/MAHINDRA_GROUP_Technical_Metrics.xlsx
+++ b/MAHINDRA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="66">
   <si>
     <t>Symbol</t>
   </si>
@@ -178,55 +178,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Overbought Entry</t>
-  </si>
-  <si>
-    <t>65.3 → 74.6</t>
-  </si>
-  <si>
-    <t>⚠️ CAUTION</t>
-  </si>
-  <si>
-    <t>65.3</t>
-  </si>
-  <si>
-    <t>74.6</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>51.2 → 49.8</t>
-  </si>
-  <si>
-    <t>51.2</t>
-  </si>
-  <si>
-    <t>49.8</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -278,7 +230,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -312,7 +264,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -324,15 +276,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -359,19 +304,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -441,23 +380,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -466,7 +403,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -965,58 +902,58 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>381.8</v>
+        <v>379.65</v>
       </c>
       <c r="D2">
-        <v>0.04</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="E2">
         <v>490.2</v>
       </c>
       <c r="F2">
-        <v>381.65</v>
+        <v>379.65</v>
       </c>
       <c r="G2">
-        <v>-22.11</v>
+        <v>-22.55</v>
       </c>
       <c r="H2">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>-0.5600000000000001</v>
+        <v>-1.48</v>
       </c>
       <c r="J2">
-        <v>-7.26</v>
+        <v>-7.09</v>
       </c>
       <c r="K2">
-        <v>-15.29</v>
+        <v>-18.32</v>
       </c>
       <c r="L2">
-        <v>-4.36</v>
+        <v>-4.77</v>
       </c>
       <c r="M2">
-        <v>11.73</v>
+        <v>11.6</v>
       </c>
       <c r="N2">
+        <v>23</v>
+      </c>
+      <c r="O2">
         <v>34</v>
       </c>
-      <c r="O2">
-        <v>35</v>
-      </c>
       <c r="P2">
-        <v>383.15</v>
+        <v>382.01</v>
       </c>
       <c r="Q2">
-        <v>394</v>
+        <v>392.6</v>
       </c>
       <c r="R2">
-        <v>420.35</v>
+        <v>418.52</v>
       </c>
       <c r="S2">
-        <v>435.53</v>
+        <v>435.4</v>
       </c>
       <c r="T2">
-        <v>-12.34</v>
+        <v>-12.81</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1031,43 +968,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>24.7</v>
+        <v>23.23</v>
       </c>
       <c r="Z2">
-        <v>-10.38</v>
+        <v>-10.26</v>
       </c>
       <c r="AA2">
-        <v>-10.71</v>
+        <v>-10.62</v>
       </c>
       <c r="AB2">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="AC2">
-        <v>5.73</v>
+        <v>1.68</v>
       </c>
       <c r="AD2">
-        <v>9.130000000000001</v>
+        <v>5.09</v>
       </c>
       <c r="AE2">
-        <v>7.57</v>
+        <v>7.44</v>
       </c>
       <c r="AF2">
-        <v>28.97</v>
+        <v>-58.19</v>
       </c>
       <c r="AG2">
-        <v>413.4</v>
+        <v>411.87</v>
       </c>
       <c r="AH2">
-        <v>374.61</v>
+        <v>373.32</v>
       </c>
       <c r="AI2">
-        <v>406.13</v>
+        <v>400.84</v>
       </c>
       <c r="AJ2" t="s">
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>56.47</v>
+        <v>57.88</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1078,10 +1015,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>3123.8</v>
+        <v>3107</v>
       </c>
       <c r="D3">
-        <v>-0.83</v>
+        <v>-0.54</v>
       </c>
       <c r="E3">
         <v>3802.4</v>
@@ -1090,46 +1027,46 @@
         <v>2931.1</v>
       </c>
       <c r="G3">
-        <v>-17.85</v>
+        <v>-18.29</v>
       </c>
       <c r="H3">
-        <v>6.57</v>
+        <v>6</v>
       </c>
       <c r="I3">
-        <v>-0.83</v>
+        <v>-1.99</v>
       </c>
       <c r="J3">
-        <v>-8.220000000000001</v>
+        <v>-9.369999999999999</v>
       </c>
       <c r="K3">
-        <v>2.66</v>
+        <v>-0.87</v>
       </c>
       <c r="L3">
-        <v>-12.28</v>
+        <v>-15.94</v>
       </c>
       <c r="M3">
-        <v>34.21</v>
+        <v>34.04</v>
       </c>
       <c r="N3">
         <v>45</v>
       </c>
       <c r="O3">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P3">
-        <v>3152.76</v>
+        <v>3140.16</v>
       </c>
       <c r="Q3">
-        <v>3302.82</v>
+        <v>3286.75</v>
       </c>
       <c r="R3">
-        <v>3278.46</v>
+        <v>3277.86</v>
       </c>
       <c r="S3">
-        <v>3322.29</v>
+        <v>3319.48</v>
       </c>
       <c r="T3">
-        <v>-5.97</v>
+        <v>-6.4</v>
       </c>
       <c r="U3" t="s">
         <v>48</v>
@@ -1144,43 +1081,43 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>31.09</v>
+        <v>29.79</v>
       </c>
       <c r="Z3">
-        <v>-52.42</v>
+        <v>-57.21</v>
       </c>
       <c r="AA3">
-        <v>-23.94</v>
+        <v>-30.59</v>
       </c>
       <c r="AB3">
-        <v>-28.48</v>
+        <v>-26.62</v>
       </c>
       <c r="AC3">
+        <v>1.42</v>
+      </c>
+      <c r="AD3">
         <v>3.81</v>
       </c>
-      <c r="AD3">
-        <v>6.02</v>
-      </c>
       <c r="AE3">
-        <v>65.06999999999999</v>
+        <v>64.36</v>
       </c>
       <c r="AF3">
-        <v>26.07</v>
+        <v>-23.43</v>
       </c>
       <c r="AG3">
-        <v>3542.13</v>
+        <v>3533.62</v>
       </c>
       <c r="AH3">
-        <v>3063.5</v>
+        <v>3039.88</v>
       </c>
       <c r="AI3">
-        <v>3317.51</v>
+        <v>3289.73</v>
       </c>
       <c r="AJ3" t="s">
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>62.01</v>
+        <v>65.18000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1191,58 +1128,58 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>359.25</v>
+        <v>356.15</v>
       </c>
       <c r="D4">
-        <v>-1.24</v>
+        <v>-0.86</v>
       </c>
       <c r="E4">
         <v>412.3</v>
       </c>
       <c r="F4">
-        <v>268.95</v>
+        <v>269.25</v>
       </c>
       <c r="G4">
-        <v>-12.87</v>
+        <v>-13.62</v>
       </c>
       <c r="H4">
-        <v>33.58</v>
+        <v>32.27</v>
       </c>
       <c r="I4">
-        <v>-4.47</v>
+        <v>-4.68</v>
       </c>
       <c r="J4">
-        <v>-9.25</v>
+        <v>-10.15</v>
       </c>
       <c r="K4">
-        <v>23.43</v>
+        <v>19.57</v>
       </c>
       <c r="L4">
-        <v>33.4</v>
+        <v>32.42</v>
       </c>
       <c r="M4">
-        <v>18.26</v>
+        <v>18.04</v>
       </c>
       <c r="N4">
         <v>99</v>
       </c>
       <c r="O4">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P4">
-        <v>368.67</v>
+        <v>365.17</v>
       </c>
       <c r="Q4">
-        <v>377.5</v>
+        <v>375.8</v>
       </c>
       <c r="R4">
-        <v>369.5</v>
+        <v>369.94</v>
       </c>
       <c r="S4">
-        <v>344.64</v>
+        <v>344.62</v>
       </c>
       <c r="T4">
-        <v>4.24</v>
+        <v>3.35</v>
       </c>
       <c r="U4" t="s">
         <v>48</v>
@@ -1257,43 +1194,43 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>39.4</v>
+        <v>37.71</v>
       </c>
       <c r="Z4">
-        <v>-2.28</v>
+        <v>-3.36</v>
       </c>
       <c r="AA4">
-        <v>0.84</v>
+        <v>0</v>
       </c>
       <c r="AB4">
-        <v>-3.12</v>
+        <v>-3.36</v>
       </c>
       <c r="AC4">
-        <v>19.85</v>
+        <v>1.23</v>
       </c>
       <c r="AD4">
-        <v>32.43</v>
+        <v>17.77</v>
       </c>
       <c r="AE4">
-        <v>11.53</v>
+        <v>11.26</v>
       </c>
       <c r="AF4">
-        <v>30.93</v>
+        <v>14.57</v>
       </c>
       <c r="AG4">
-        <v>395.32</v>
+        <v>394.98</v>
       </c>
       <c r="AH4">
-        <v>359.68</v>
+        <v>356.62</v>
       </c>
       <c r="AI4">
-        <v>357.72</v>
+        <v>388.35</v>
       </c>
       <c r="AJ4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AK4">
-        <v>20.93</v>
+        <v>23.41</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1304,10 +1241,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>359.65</v>
+        <v>353.05</v>
       </c>
       <c r="D5">
-        <v>-2.82</v>
+        <v>-1.84</v>
       </c>
       <c r="E5">
         <v>421.7</v>
@@ -1316,46 +1253,46 @@
         <v>294.25</v>
       </c>
       <c r="G5">
-        <v>-14.71</v>
+        <v>-16.28</v>
       </c>
       <c r="H5">
-        <v>22.23</v>
+        <v>19.98</v>
       </c>
       <c r="I5">
-        <v>-0.95</v>
+        <v>-2.58</v>
       </c>
       <c r="J5">
-        <v>-6.06</v>
+        <v>-8</v>
       </c>
       <c r="K5">
-        <v>9.5</v>
+        <v>5.8</v>
       </c>
       <c r="L5">
-        <v>-3.06</v>
+        <v>-4.76</v>
       </c>
       <c r="M5">
-        <v>5.37</v>
+        <v>4.98</v>
       </c>
       <c r="N5">
         <v>55</v>
       </c>
       <c r="O5">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="P5">
-        <v>363.69</v>
+        <v>361.82</v>
       </c>
       <c r="Q5">
-        <v>370.63</v>
+        <v>369.04</v>
       </c>
       <c r="R5">
-        <v>375.75</v>
+        <v>375.41</v>
       </c>
       <c r="S5">
-        <v>362.83</v>
+        <v>362.64</v>
       </c>
       <c r="T5">
-        <v>-0.88</v>
+        <v>-2.64</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1370,43 +1307,43 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>39.7</v>
+        <v>35.2</v>
       </c>
       <c r="Z5">
-        <v>-4.21</v>
+        <v>-4.93</v>
       </c>
       <c r="AA5">
-        <v>-3.49</v>
+        <v>-3.78</v>
       </c>
       <c r="AB5">
-        <v>-0.72</v>
+        <v>-1.15</v>
       </c>
       <c r="AC5">
-        <v>71.26000000000001</v>
+        <v>56.19</v>
       </c>
       <c r="AD5">
-        <v>60.41</v>
+        <v>64.2</v>
       </c>
       <c r="AE5">
-        <v>10.41</v>
+        <v>10.44</v>
       </c>
       <c r="AF5">
-        <v>-33.86</v>
+        <v>3.03</v>
       </c>
       <c r="AG5">
-        <v>389.12</v>
+        <v>387.84</v>
       </c>
       <c r="AH5">
-        <v>352.15</v>
+        <v>350.24</v>
       </c>
       <c r="AI5">
-        <v>386.7</v>
+        <v>385.87</v>
       </c>
       <c r="AJ5" t="s">
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>38.91</v>
+        <v>40.65</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1417,10 +1354,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>400.1</v>
+        <v>397.2</v>
       </c>
       <c r="D6">
-        <v>-0.41</v>
+        <v>-0.72</v>
       </c>
       <c r="E6">
         <v>442.7</v>
@@ -1429,46 +1366,46 @@
         <v>279.55</v>
       </c>
       <c r="G6">
-        <v>-9.619999999999999</v>
+        <v>-10.28</v>
       </c>
       <c r="H6">
-        <v>43.12</v>
+        <v>42.09</v>
       </c>
       <c r="I6">
-        <v>-0.05</v>
+        <v>-2.01</v>
       </c>
       <c r="J6">
-        <v>-1.68</v>
+        <v>-2.17</v>
       </c>
       <c r="K6">
-        <v>18.48</v>
+        <v>14.07</v>
       </c>
       <c r="L6">
-        <v>24.62</v>
+        <v>23.01</v>
       </c>
       <c r="M6">
-        <v>-10.43</v>
+        <v>-10.56</v>
       </c>
       <c r="N6">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="O6">
         <v>76</v>
       </c>
       <c r="P6">
-        <v>403.85</v>
+        <v>402.22</v>
       </c>
       <c r="Q6">
-        <v>400.34</v>
+        <v>399.93</v>
       </c>
       <c r="R6">
-        <v>400.78</v>
+        <v>400.83</v>
       </c>
       <c r="S6">
-        <v>369.53</v>
+        <v>369.91</v>
       </c>
       <c r="T6">
-        <v>8.27</v>
+        <v>7.38</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1483,34 +1420,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>49.8</v>
+        <v>47.28</v>
       </c>
       <c r="Z6">
-        <v>0.28</v>
+        <v>-0.02</v>
       </c>
       <c r="AA6">
         <v>-0.03</v>
       </c>
       <c r="AB6">
-        <v>0.31</v>
+        <v>0.01</v>
       </c>
       <c r="AC6">
-        <v>75.56</v>
+        <v>58</v>
       </c>
       <c r="AD6">
-        <v>85.56</v>
+        <v>72.87</v>
       </c>
       <c r="AE6">
-        <v>11.17</v>
+        <v>10.91</v>
       </c>
       <c r="AF6">
-        <v>-38.02</v>
+        <v>-22.18</v>
       </c>
       <c r="AG6">
-        <v>412.57</v>
+        <v>411.98</v>
       </c>
       <c r="AH6">
-        <v>388.11</v>
+        <v>387.87</v>
       </c>
       <c r="AI6">
         <v>372.35</v>
@@ -1519,7 +1456,7 @@
         <v>50</v>
       </c>
       <c r="AK6">
-        <v>25.65</v>
+        <v>22.86</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1530,13 +1467,13 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>718.95</v>
+        <v>728.9</v>
       </c>
       <c r="D7">
-        <v>6.32</v>
+        <v>1.38</v>
       </c>
       <c r="E7">
-        <v>718.95</v>
+        <v>728.9</v>
       </c>
       <c r="F7">
         <v>506.45</v>
@@ -1545,43 +1482,43 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>41.96</v>
+        <v>43.92</v>
       </c>
       <c r="I7">
-        <v>10.02</v>
+        <v>5.93</v>
       </c>
       <c r="J7">
-        <v>17.87</v>
+        <v>19.1</v>
       </c>
       <c r="K7">
-        <v>16.5</v>
+        <v>15.71</v>
       </c>
       <c r="L7">
-        <v>12.85</v>
+        <v>14.13</v>
       </c>
       <c r="M7">
-        <v>36.86</v>
+        <v>37.21</v>
       </c>
       <c r="N7">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="O7">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="P7">
-        <v>690.5700000000001</v>
+        <v>698.73</v>
       </c>
       <c r="Q7">
-        <v>650.49</v>
+        <v>656.3099999999999</v>
       </c>
       <c r="R7">
-        <v>612.1799999999999</v>
+        <v>614.55</v>
       </c>
       <c r="S7">
-        <v>589.6799999999999</v>
+        <v>590.39</v>
       </c>
       <c r="T7">
-        <v>21.92</v>
+        <v>23.46</v>
       </c>
       <c r="U7" t="s">
         <v>48</v>
@@ -1596,43 +1533,43 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>74.62</v>
+        <v>76.22</v>
       </c>
       <c r="Z7">
-        <v>23.94</v>
+        <v>26.78</v>
       </c>
       <c r="AA7">
-        <v>19.06</v>
+        <v>20.6</v>
       </c>
       <c r="AB7">
-        <v>4.88</v>
+        <v>6.18</v>
       </c>
       <c r="AC7">
-        <v>57.51</v>
+        <v>71.02</v>
       </c>
       <c r="AD7">
-        <v>62.37</v>
+        <v>60.85</v>
       </c>
       <c r="AE7">
-        <v>24.06</v>
+        <v>24.54</v>
       </c>
       <c r="AF7">
-        <v>245.57</v>
+        <v>150.35</v>
       </c>
       <c r="AG7">
-        <v>709.78</v>
+        <v>722.36</v>
       </c>
       <c r="AH7">
-        <v>591.2</v>
+        <v>590.26</v>
       </c>
       <c r="AI7">
-        <v>628.66</v>
+        <v>649.01</v>
       </c>
       <c r="AJ7" t="s">
         <v>50</v>
       </c>
       <c r="AK7">
-        <v>72.84</v>
+        <v>73.95999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1643,10 +1580,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>196.57</v>
+        <v>196.73</v>
       </c>
       <c r="D8">
-        <v>-1.4</v>
+        <v>0.08</v>
       </c>
       <c r="E8">
         <v>362.05</v>
@@ -1655,46 +1592,46 @@
         <v>196.57</v>
       </c>
       <c r="G8">
-        <v>-45.71</v>
+        <v>-45.66</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="I8">
-        <v>-5.45</v>
+        <v>-5.14</v>
       </c>
       <c r="J8">
-        <v>-12.59</v>
+        <v>-12.13</v>
       </c>
       <c r="K8">
-        <v>-16.52</v>
+        <v>-15.5</v>
       </c>
       <c r="L8">
-        <v>-44.16</v>
+        <v>-44.73</v>
       </c>
       <c r="M8">
-        <v>-3.47</v>
+        <v>-3.45</v>
       </c>
       <c r="N8">
         <v>12</v>
       </c>
       <c r="O8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P8">
-        <v>202.91</v>
+        <v>200.78</v>
       </c>
       <c r="Q8">
-        <v>213.25</v>
+        <v>211.75</v>
       </c>
       <c r="R8">
-        <v>220.84</v>
+        <v>220.04</v>
       </c>
       <c r="S8">
-        <v>257.72</v>
+        <v>257.12</v>
       </c>
       <c r="T8">
-        <v>-23.73</v>
+        <v>-23.49</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1709,34 +1646,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>22.09</v>
+        <v>22.5</v>
       </c>
       <c r="Z8">
-        <v>-6.19</v>
+        <v>-6.55</v>
       </c>
       <c r="AA8">
-        <v>-4.76</v>
+        <v>-5.12</v>
       </c>
       <c r="AB8">
-        <v>-1.42</v>
+        <v>-1.43</v>
       </c>
       <c r="AC8">
-        <v>1.74</v>
+        <v>0.68</v>
       </c>
       <c r="AD8">
-        <v>3.91</v>
+        <v>1.66</v>
       </c>
       <c r="AE8">
-        <v>5.83</v>
+        <v>5.84</v>
       </c>
       <c r="AF8">
-        <v>183.21</v>
+        <v>10.87</v>
       </c>
       <c r="AG8">
-        <v>230.75</v>
+        <v>229.55</v>
       </c>
       <c r="AH8">
-        <v>195.74</v>
+        <v>193.95</v>
       </c>
       <c r="AI8">
         <v>214.31</v>
@@ -1745,7 +1682,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>50.74</v>
+        <v>54.09</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1756,10 +1693,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>3551</v>
+        <v>3576</v>
       </c>
       <c r="D9">
-        <v>-1.2</v>
+        <v>0.7</v>
       </c>
       <c r="E9">
         <v>4497.5</v>
@@ -1768,46 +1705,46 @@
         <v>3308.9</v>
       </c>
       <c r="G9">
-        <v>-21.05</v>
+        <v>-20.49</v>
       </c>
       <c r="H9">
-        <v>7.32</v>
+        <v>8.07</v>
       </c>
       <c r="I9">
-        <v>-0.1</v>
+        <v>0.51</v>
       </c>
       <c r="J9">
-        <v>-1.6</v>
+        <v>-1.17</v>
       </c>
       <c r="K9">
-        <v>-4.12</v>
+        <v>-6.53</v>
       </c>
       <c r="L9">
-        <v>-19.45</v>
+        <v>-19.11</v>
       </c>
       <c r="M9">
-        <v>19.61</v>
+        <v>19.77</v>
       </c>
       <c r="N9">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="O9">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="P9">
-        <v>3596.74</v>
+        <v>3600.38</v>
       </c>
       <c r="Q9">
-        <v>3578.53</v>
+        <v>3575.42</v>
       </c>
       <c r="R9">
-        <v>3631.18</v>
+        <v>3623.9</v>
       </c>
       <c r="S9">
-        <v>3685.01</v>
+        <v>3684.75</v>
       </c>
       <c r="T9">
-        <v>-3.64</v>
+        <v>-2.95</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1822,34 +1759,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>42.71</v>
+        <v>47.09</v>
       </c>
       <c r="Z9">
-        <v>-13.51</v>
+        <v>-12.82</v>
       </c>
       <c r="AA9">
-        <v>-21.43</v>
+        <v>-19.71</v>
       </c>
       <c r="AB9">
-        <v>7.92</v>
+        <v>6.89</v>
       </c>
       <c r="AC9">
-        <v>60</v>
+        <v>47.78</v>
       </c>
       <c r="AD9">
-        <v>78.02</v>
+        <v>63.32</v>
       </c>
       <c r="AE9">
-        <v>63.74</v>
+        <v>63.54</v>
       </c>
       <c r="AF9">
-        <v>2.72</v>
+        <v>13.08</v>
       </c>
       <c r="AG9">
-        <v>3651.18</v>
+        <v>3642.42</v>
       </c>
       <c r="AH9">
-        <v>3505.88</v>
+        <v>3508.42</v>
       </c>
       <c r="AI9">
         <v>3684.57</v>
@@ -1858,7 +1795,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>32.74</v>
+        <v>29.63</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1869,10 +1806,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>1525.8</v>
+        <v>1541</v>
       </c>
       <c r="D10">
-        <v>1.18</v>
+        <v>1</v>
       </c>
       <c r="E10">
         <v>1768.4</v>
@@ -1881,46 +1818,46 @@
         <v>1326.2</v>
       </c>
       <c r="G10">
-        <v>-13.72</v>
+        <v>-12.86</v>
       </c>
       <c r="H10">
-        <v>15.05</v>
+        <v>16.2</v>
       </c>
       <c r="I10">
-        <v>-4.52</v>
+        <v>-3.5</v>
       </c>
       <c r="J10">
-        <v>-6.1</v>
+        <v>-5.98</v>
       </c>
       <c r="K10">
-        <v>6.76</v>
+        <v>8.09</v>
       </c>
       <c r="L10">
-        <v>5.55</v>
+        <v>3.93</v>
       </c>
       <c r="M10">
-        <v>4.38</v>
+        <v>4.58</v>
       </c>
       <c r="N10">
         <v>66</v>
       </c>
       <c r="O10">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="P10">
-        <v>1550.74</v>
+        <v>1539.56</v>
       </c>
       <c r="Q10">
-        <v>1591.11</v>
+        <v>1586.52</v>
       </c>
       <c r="R10">
-        <v>1574.64</v>
+        <v>1577.26</v>
       </c>
       <c r="S10">
-        <v>1517.81</v>
+        <v>1518.04</v>
       </c>
       <c r="T10">
-        <v>0.53</v>
+        <v>1.51</v>
       </c>
       <c r="U10" t="s">
         <v>48</v>
@@ -1935,34 +1872,34 @@
         <v>3</v>
       </c>
       <c r="Y10">
-        <v>37.83</v>
+        <v>41.54</v>
       </c>
       <c r="Z10">
-        <v>-10.87</v>
+        <v>-12.65</v>
       </c>
       <c r="AA10">
-        <v>1.89</v>
+        <v>-1.01</v>
       </c>
       <c r="AB10">
-        <v>-12.77</v>
+        <v>-11.63</v>
       </c>
       <c r="AC10">
-        <v>5.55</v>
+        <v>15.58</v>
       </c>
       <c r="AD10">
-        <v>4.93</v>
+        <v>7.04</v>
       </c>
       <c r="AE10">
-        <v>39.3</v>
+        <v>39.25</v>
       </c>
       <c r="AF10">
-        <v>-33.01</v>
+        <v>1.03</v>
       </c>
       <c r="AG10">
-        <v>1660.38</v>
+        <v>1656.32</v>
       </c>
       <c r="AH10">
-        <v>1521.84</v>
+        <v>1516.72</v>
       </c>
       <c r="AI10">
         <v>1630.7</v>
@@ -1971,7 +1908,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>35.4</v>
+        <v>34.73</v>
       </c>
     </row>
   </sheetData>
@@ -2112,7 +2049,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F85"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2132,1426 +2069,1314 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>68</v>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>-7.26</v>
+      </c>
+      <c r="D7" s="5">
+        <v>-7.09</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0.17</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
+      <c r="A8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>-8.220000000000001</v>
+      </c>
+      <c r="D8" s="5">
+        <v>-9.369999999999999</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-1.15</v>
+      </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="3" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>73</v>
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>-9.25</v>
+      </c>
+      <c r="D9" s="5">
+        <v>-10.15</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-0.9</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5">
+        <v>-6.06</v>
+      </c>
+      <c r="D10" s="5">
+        <v>-8</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-1.94</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-1.68</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-2.17</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-0.49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="5">
+        <v>17.87</v>
+      </c>
+      <c r="D12" s="5">
+        <v>19.1</v>
+      </c>
+      <c r="E12" s="6">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="5">
+        <v>-12.59</v>
+      </c>
+      <c r="D13" s="5">
+        <v>-12.13</v>
+      </c>
+      <c r="E13" s="6">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-1.6</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-1.17</v>
+      </c>
+      <c r="E14" s="6">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-6.1</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-5.98</v>
+      </c>
+      <c r="E15" s="6">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7">
-        <v>-7.59</v>
-      </c>
-      <c r="D10" s="7">
-        <v>-7.26</v>
-      </c>
-      <c r="E10" s="8">
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-1.48</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-0.92</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7">
-        <v>-8.960000000000001</v>
-      </c>
-      <c r="D11" s="7">
-        <v>-8.220000000000001</v>
-      </c>
-      <c r="E11" s="8">
-        <v>0.74</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="B17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-0.83</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-1.99</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-1.16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7">
-        <v>-8.789999999999999</v>
-      </c>
-      <c r="D12" s="7">
-        <v>-9.25</v>
-      </c>
-      <c r="E12" s="9">
-        <v>-0.46</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+      <c r="B18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-4.47</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-4.68</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-0.21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="7">
-        <v>-3.28</v>
-      </c>
-      <c r="D13" s="7">
-        <v>-6.06</v>
-      </c>
-      <c r="E13" s="9">
-        <v>-2.78</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="B19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-0.95</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-2.58</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-1.63</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="7">
-        <v>-1.86</v>
-      </c>
-      <c r="D14" s="7">
-        <v>-1.68</v>
-      </c>
-      <c r="E14" s="8">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+      <c r="B20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-0.05</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-2.01</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-1.96</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="7">
-        <v>13.65</v>
-      </c>
-      <c r="D15" s="7">
-        <v>17.87</v>
-      </c>
-      <c r="E15" s="8">
-        <v>4.22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="B21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="5">
+        <v>10.02</v>
+      </c>
+      <c r="D21" s="5">
+        <v>5.93</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-4.09</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-11.62</v>
-      </c>
-      <c r="D16" s="7">
-        <v>-12.59</v>
-      </c>
-      <c r="E16" s="9">
-        <v>-0.97</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+      <c r="B22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="5">
+        <v>-5.45</v>
+      </c>
+      <c r="D22" s="5">
+        <v>-5.14</v>
+      </c>
+      <c r="E22" s="6">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="7">
+      <c r="B23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="5">
         <v>-0.1</v>
       </c>
-      <c r="D17" s="7">
-        <v>-1.6</v>
-      </c>
-      <c r="E17" s="9">
-        <v>-1.5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
+      <c r="D23" s="5">
+        <v>0.51</v>
+      </c>
+      <c r="E23" s="6">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-8.220000000000001</v>
-      </c>
-      <c r="D18" s="7">
-        <v>-6.1</v>
-      </c>
-      <c r="E18" s="8">
-        <v>2.12</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
+      <c r="B24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-4.52</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-3.5</v>
+      </c>
+      <c r="E24" s="6">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="7">
+      <c r="B25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="5">
+        <v>-4.36</v>
+      </c>
+      <c r="D25" s="5">
+        <v>-4.77</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-0.41</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="5">
+        <v>-12.28</v>
+      </c>
+      <c r="D26" s="5">
+        <v>-15.94</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-3.66</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="5">
+        <v>33.4</v>
+      </c>
+      <c r="D27" s="5">
+        <v>32.42</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-0.98</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="5">
+        <v>-3.06</v>
+      </c>
+      <c r="D28" s="5">
+        <v>-4.76</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-1.7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="5">
+        <v>24.62</v>
+      </c>
+      <c r="D29" s="5">
+        <v>23.01</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-1.61</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="5">
+        <v>12.85</v>
+      </c>
+      <c r="D30" s="5">
+        <v>14.13</v>
+      </c>
+      <c r="E30" s="6">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-44.16</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-44.73</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-0.57</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="5">
+        <v>-19.45</v>
+      </c>
+      <c r="D32" s="5">
+        <v>-19.11</v>
+      </c>
+      <c r="E32" s="6">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="5">
+        <v>5.55</v>
+      </c>
+      <c r="D33" s="5">
+        <v>3.93</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-1.62</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="5">
+        <v>-15.29</v>
+      </c>
+      <c r="D34" s="5">
+        <v>-18.32</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-3.03</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="5">
+        <v>2.66</v>
+      </c>
+      <c r="D35" s="5">
         <v>-0.87</v>
       </c>
-      <c r="D19" s="7">
-        <v>-0.5600000000000001</v>
-      </c>
-      <c r="E19" s="8">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
+      <c r="E35" s="7">
+        <v>-3.53</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="5">
+        <v>23.43</v>
+      </c>
+      <c r="D36" s="5">
+        <v>19.57</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-3.86</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="5">
+        <v>9.5</v>
+      </c>
+      <c r="D37" s="5">
+        <v>5.8</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-3.7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="5">
+        <v>18.48</v>
+      </c>
+      <c r="D38" s="5">
+        <v>14.07</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-4.41</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="5">
+        <v>16.5</v>
+      </c>
+      <c r="D39" s="5">
+        <v>15.71</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-0.79</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="5">
+        <v>-16.52</v>
+      </c>
+      <c r="D40" s="5">
+        <v>-15.5</v>
+      </c>
+      <c r="E40" s="6">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="5">
+        <v>-4.12</v>
+      </c>
+      <c r="D41" s="5">
+        <v>-6.53</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-2.41</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="5">
+        <v>6.76</v>
+      </c>
+      <c r="D42" s="5">
+        <v>8.09</v>
+      </c>
+      <c r="E42" s="6">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="5">
+        <v>-22.11</v>
+      </c>
+      <c r="D43" s="5">
+        <v>-22.55</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-0.44</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="7">
-        <v>-1.25</v>
-      </c>
-      <c r="D20" s="7">
-        <v>-0.83</v>
-      </c>
-      <c r="E20" s="8">
-        <v>0.42</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
+      <c r="B44" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="5">
+        <v>-17.85</v>
+      </c>
+      <c r="D44" s="5">
+        <v>-18.29</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-0.44</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-1.38</v>
-      </c>
-      <c r="D21" s="7">
-        <v>-4.47</v>
-      </c>
-      <c r="E21" s="9">
-        <v>-3.09</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
+      <c r="B45" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="5">
+        <v>-12.87</v>
+      </c>
+      <c r="D45" s="5">
+        <v>-13.62</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="7">
-        <v>3.09</v>
-      </c>
-      <c r="D22" s="7">
-        <v>-0.95</v>
-      </c>
-      <c r="E22" s="9">
-        <v>-4.04</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
+      <c r="B46" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="5">
+        <v>-14.71</v>
+      </c>
+      <c r="D46" s="5">
+        <v>-16.28</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-1.57</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="7">
-        <v>2.37</v>
-      </c>
-      <c r="D23" s="7">
-        <v>-0.05</v>
-      </c>
-      <c r="E23" s="9">
-        <v>-2.42</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
+      <c r="B47" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="5">
+        <v>-9.619999999999999</v>
+      </c>
+      <c r="D47" s="5">
+        <v>-10.28</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-0.66</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="5">
+        <v>-45.71</v>
+      </c>
+      <c r="D48" s="5">
+        <v>-45.66</v>
+      </c>
+      <c r="E48" s="6">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="5">
+        <v>-21.05</v>
+      </c>
+      <c r="D49" s="5">
+        <v>-20.49</v>
+      </c>
+      <c r="E49" s="6">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="5">
+        <v>-13.72</v>
+      </c>
+      <c r="D50" s="5">
+        <v>-12.86</v>
+      </c>
+      <c r="E50" s="6">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C51" s="5">
+        <v>381.8</v>
+      </c>
+      <c r="D51" s="5">
+        <v>379.65</v>
+      </c>
+      <c r="E51" s="7">
+        <v>-2.15</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="5">
+        <v>3123.8</v>
+      </c>
+      <c r="D52" s="5">
+        <v>3107</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-16.8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="5">
+        <v>359.25</v>
+      </c>
+      <c r="D53" s="5">
+        <v>356.15</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-3.1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="5">
+        <v>359.65</v>
+      </c>
+      <c r="D54" s="5">
+        <v>353.05</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-6.6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="5">
+        <v>400.1</v>
+      </c>
+      <c r="D55" s="5">
+        <v>397.2</v>
+      </c>
+      <c r="E55" s="7">
+        <v>-2.9</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="7">
-        <v>1.68</v>
-      </c>
-      <c r="D24" s="7">
-        <v>10.02</v>
-      </c>
-      <c r="E24" s="8">
-        <v>8.34</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
+      <c r="B56" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="5">
+        <v>718.95</v>
+      </c>
+      <c r="D56" s="5">
+        <v>728.9</v>
+      </c>
+      <c r="E56" s="6">
+        <v>9.949999999999999</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="7">
-        <v>-3.5</v>
-      </c>
-      <c r="D25" s="7">
-        <v>-5.45</v>
-      </c>
-      <c r="E25" s="9">
-        <v>-1.95</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
+      <c r="B57" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="5">
+        <v>196.57</v>
+      </c>
+      <c r="D57" s="5">
+        <v>196.73</v>
+      </c>
+      <c r="E57" s="6">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C26" s="7">
-        <v>1.51</v>
-      </c>
-      <c r="D26" s="7">
-        <v>-0.1</v>
-      </c>
-      <c r="E26" s="9">
-        <v>-1.61</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
+      <c r="B58" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="5">
+        <v>3551</v>
+      </c>
+      <c r="D58" s="5">
+        <v>3576</v>
+      </c>
+      <c r="E58" s="6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C27" s="7">
-        <v>-7.09</v>
-      </c>
-      <c r="D27" s="7">
-        <v>-4.52</v>
-      </c>
-      <c r="E27" s="8">
-        <v>2.57</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
+      <c r="B59" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="5">
+        <v>1525.8</v>
+      </c>
+      <c r="D59" s="5">
+        <v>1541</v>
+      </c>
+      <c r="E59" s="6">
+        <v>15.2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B60" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C60" s="5">
+        <v>34</v>
+      </c>
+      <c r="D60" s="5">
+        <v>23</v>
+      </c>
+      <c r="E60" s="7">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C61" s="5">
+        <v>88</v>
+      </c>
+      <c r="D61" s="5">
+        <v>77</v>
+      </c>
+      <c r="E61" s="7">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C62" s="5">
+        <v>77</v>
+      </c>
+      <c r="D62" s="5">
+        <v>88</v>
+      </c>
+      <c r="E62" s="6">
         <v>11</v>
       </c>
-      <c r="C28" s="7">
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C63" s="5">
+        <v>23</v>
+      </c>
+      <c r="D63" s="5">
+        <v>34</v>
+      </c>
+      <c r="E63" s="6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="5">
+        <v>24.7</v>
+      </c>
+      <c r="D64" s="5">
+        <v>23.23</v>
+      </c>
+      <c r="E64" s="7">
+        <v>-1.47</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="5">
+        <v>31.09</v>
+      </c>
+      <c r="D65" s="5">
+        <v>29.79</v>
+      </c>
+      <c r="E65" s="7">
+        <v>-1.3</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="5">
+        <v>39.4</v>
+      </c>
+      <c r="D66" s="5">
+        <v>37.71</v>
+      </c>
+      <c r="E66" s="7">
         <v>-1.69</v>
       </c>
-      <c r="D28" s="7">
-        <v>-4.36</v>
-      </c>
-      <c r="E28" s="9">
-        <v>-2.67</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="5">
+        <v>39.7</v>
+      </c>
+      <c r="D67" s="5">
+        <v>35.2</v>
+      </c>
+      <c r="E67" s="7">
+        <v>-4.5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="5">
+        <v>49.8</v>
+      </c>
+      <c r="D68" s="5">
+        <v>47.28</v>
+      </c>
+      <c r="E68" s="7">
+        <v>-2.52</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="5">
+        <v>74.62</v>
+      </c>
+      <c r="D69" s="5">
+        <v>76.22</v>
+      </c>
+      <c r="E69" s="6">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="5">
+        <v>22.09</v>
+      </c>
+      <c r="D70" s="5">
+        <v>22.5</v>
+      </c>
+      <c r="E70" s="6">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="5">
+        <v>42.71</v>
+      </c>
+      <c r="D71" s="5">
+        <v>47.09</v>
+      </c>
+      <c r="E71" s="6">
+        <v>4.38</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C72" s="5">
+        <v>37.83</v>
+      </c>
+      <c r="D72" s="5">
+        <v>41.54</v>
+      </c>
+      <c r="E72" s="6">
+        <v>3.71</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="5">
+        <v>28.97</v>
+      </c>
+      <c r="D73" s="5">
+        <v>-58.19</v>
+      </c>
+      <c r="E73" s="7">
+        <v>-87.16</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="7">
-        <v>-11.55</v>
-      </c>
-      <c r="D29" s="7">
-        <v>-12.28</v>
-      </c>
-      <c r="E29" s="9">
-        <v>-0.73</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
+      <c r="B74" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="5">
+        <v>26.07</v>
+      </c>
+      <c r="D74" s="5">
+        <v>-23.43</v>
+      </c>
+      <c r="E74" s="7">
+        <v>-49.5</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="7">
-        <v>35.07</v>
-      </c>
-      <c r="D30" s="7">
-        <v>33.4</v>
-      </c>
-      <c r="E30" s="9">
-        <v>-1.67</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
+      <c r="B75" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="5">
+        <v>30.93</v>
+      </c>
+      <c r="D75" s="5">
+        <v>14.57</v>
+      </c>
+      <c r="E75" s="7">
+        <v>-16.36</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B31" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="7">
-        <v>1.83</v>
-      </c>
-      <c r="D31" s="7">
-        <v>-3.06</v>
-      </c>
-      <c r="E31" s="9">
-        <v>-4.89</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
+      <c r="B76" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="5">
+        <v>-33.86</v>
+      </c>
+      <c r="D76" s="5">
+        <v>3.03</v>
+      </c>
+      <c r="E76" s="6">
+        <v>36.89</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="7">
-        <v>25.27</v>
-      </c>
-      <c r="D32" s="7">
-        <v>24.62</v>
-      </c>
-      <c r="E32" s="9">
-        <v>-0.65</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
+      <c r="B77" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="5">
+        <v>-38.02</v>
+      </c>
+      <c r="D77" s="5">
+        <v>-22.18</v>
+      </c>
+      <c r="E77" s="6">
+        <v>15.84</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B33" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="7">
-        <v>6.72</v>
-      </c>
-      <c r="D33" s="7">
-        <v>12.85</v>
-      </c>
-      <c r="E33" s="8">
-        <v>6.13</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
+      <c r="B78" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="5">
+        <v>245.57</v>
+      </c>
+      <c r="D78" s="5">
+        <v>150.35</v>
+      </c>
+      <c r="E78" s="7">
+        <v>-95.22</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B34" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="7">
-        <v>-44.32</v>
-      </c>
-      <c r="D34" s="7">
-        <v>-44.16</v>
-      </c>
-      <c r="E34" s="8">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
+      <c r="B79" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="5">
+        <v>183.21</v>
+      </c>
+      <c r="D79" s="5">
+        <v>10.87</v>
+      </c>
+      <c r="E79" s="7">
+        <v>-172.34</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B35" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C35" s="7">
-        <v>-14.21</v>
-      </c>
-      <c r="D35" s="7">
-        <v>-19.45</v>
-      </c>
-      <c r="E35" s="9">
-        <v>-5.24</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
+      <c r="B80" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="5">
+        <v>2.72</v>
+      </c>
+      <c r="D80" s="5">
+        <v>13.08</v>
+      </c>
+      <c r="E80" s="6">
+        <v>10.36</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B36" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C36" s="7">
-        <v>3.1</v>
-      </c>
-      <c r="D36" s="7">
-        <v>5.55</v>
-      </c>
-      <c r="E36" s="8">
-        <v>2.45</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="7">
-        <v>-12.49</v>
-      </c>
-      <c r="D37" s="7">
-        <v>-15.29</v>
-      </c>
-      <c r="E37" s="9">
-        <v>-2.8</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="7">
-        <v>4.97</v>
-      </c>
-      <c r="D38" s="7">
-        <v>2.66</v>
-      </c>
-      <c r="E38" s="9">
-        <v>-2.31</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="7">
-        <v>31.94</v>
-      </c>
-      <c r="D39" s="7">
-        <v>23.43</v>
-      </c>
-      <c r="E39" s="9">
-        <v>-8.51</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="7">
-        <v>16.04</v>
-      </c>
-      <c r="D40" s="7">
-        <v>9.5</v>
-      </c>
-      <c r="E40" s="9">
-        <v>-6.54</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="7">
-        <v>20.97</v>
-      </c>
-      <c r="D41" s="7">
-        <v>18.48</v>
-      </c>
-      <c r="E41" s="9">
-        <v>-2.49</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="7">
-        <v>13.71</v>
-      </c>
-      <c r="D42" s="7">
-        <v>16.5</v>
-      </c>
-      <c r="E42" s="8">
-        <v>2.79</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="7">
-        <v>-13.58</v>
-      </c>
-      <c r="D43" s="7">
-        <v>-16.52</v>
-      </c>
-      <c r="E43" s="9">
-        <v>-2.94</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44" s="7">
-        <v>-2.51</v>
-      </c>
-      <c r="D44" s="7">
-        <v>-4.12</v>
-      </c>
-      <c r="E44" s="9">
-        <v>-1.61</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C45" s="7">
-        <v>2.93</v>
-      </c>
-      <c r="D45" s="7">
-        <v>6.76</v>
-      </c>
-      <c r="E45" s="8">
-        <v>3.83</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="7">
-        <v>-22.14</v>
-      </c>
-      <c r="D46" s="7">
-        <v>-22.11</v>
-      </c>
-      <c r="E46" s="8">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="7">
-        <v>-17.16</v>
-      </c>
-      <c r="D47" s="7">
-        <v>-17.85</v>
-      </c>
-      <c r="E47" s="9">
-        <v>-0.6899999999999999</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="7">
-        <v>-11.78</v>
-      </c>
-      <c r="D48" s="7">
-        <v>-12.87</v>
-      </c>
-      <c r="E48" s="9">
-        <v>-1.09</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="7">
-        <v>-12.24</v>
-      </c>
-      <c r="D49" s="7">
-        <v>-14.71</v>
-      </c>
-      <c r="E49" s="9">
-        <v>-2.47</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="7">
-        <v>-9.25</v>
-      </c>
-      <c r="D50" s="7">
-        <v>-9.619999999999999</v>
-      </c>
-      <c r="E50" s="9">
-        <v>-0.37</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="7">
-        <v>-1.85</v>
-      </c>
-      <c r="D51" s="7">
-        <v>0</v>
-      </c>
-      <c r="E51" s="8">
-        <v>1.85</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C52" s="7">
-        <v>-44.94</v>
-      </c>
-      <c r="D52" s="7">
-        <v>-45.71</v>
-      </c>
-      <c r="E52" s="9">
-        <v>-0.77</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C53" s="7">
-        <v>-20.08</v>
-      </c>
-      <c r="D53" s="7">
-        <v>-21.05</v>
-      </c>
-      <c r="E53" s="9">
-        <v>-0.97</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C54" s="7">
-        <v>-14.73</v>
-      </c>
-      <c r="D54" s="7">
-        <v>-13.72</v>
-      </c>
-      <c r="E54" s="8">
-        <v>1.01</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="7">
-        <v>381.65</v>
-      </c>
-      <c r="D55" s="7">
-        <v>381.8</v>
-      </c>
-      <c r="E55" s="8">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="7">
-        <v>3150</v>
-      </c>
-      <c r="D56" s="7">
-        <v>3123.8</v>
-      </c>
-      <c r="E56" s="9">
-        <v>-26.2</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="7">
-        <v>363.75</v>
-      </c>
-      <c r="D57" s="7">
-        <v>359.25</v>
-      </c>
-      <c r="E57" s="9">
-        <v>-4.5</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="7">
-        <v>370.1</v>
-      </c>
-      <c r="D58" s="7">
-        <v>359.65</v>
-      </c>
-      <c r="E58" s="9">
-        <v>-10.45</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="7">
-        <v>401.75</v>
-      </c>
-      <c r="D59" s="7">
-        <v>400.1</v>
-      </c>
-      <c r="E59" s="9">
-        <v>-1.65</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="7">
-        <v>676.2</v>
-      </c>
-      <c r="D60" s="7">
-        <v>718.95</v>
-      </c>
-      <c r="E60" s="8">
-        <v>42.75</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C61" s="7">
-        <v>199.36</v>
-      </c>
-      <c r="D61" s="7">
-        <v>196.57</v>
-      </c>
-      <c r="E61" s="9">
-        <v>-2.79</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C62" s="7">
-        <v>3594.3</v>
-      </c>
-      <c r="D62" s="7">
-        <v>3551</v>
-      </c>
-      <c r="E62" s="9">
-        <v>-43.3</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C63" s="7">
-        <v>1508</v>
-      </c>
-      <c r="D63" s="7">
-        <v>1525.8</v>
-      </c>
-      <c r="E63" s="8">
-        <v>17.8</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C64" s="7">
-        <v>23</v>
-      </c>
-      <c r="D64" s="7">
-        <v>34</v>
-      </c>
-      <c r="E64" s="8">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C65" s="7">
-        <v>66</v>
-      </c>
-      <c r="D65" s="7">
-        <v>55</v>
-      </c>
-      <c r="E65" s="9">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C66" s="7">
-        <v>34</v>
-      </c>
-      <c r="D66" s="7">
-        <v>23</v>
-      </c>
-      <c r="E66" s="9">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C67" s="7">
-        <v>55</v>
-      </c>
-      <c r="D67" s="7">
-        <v>66</v>
-      </c>
-      <c r="E67" s="8">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="7">
-        <v>24.39</v>
-      </c>
-      <c r="D68" s="7">
-        <v>24.7</v>
-      </c>
-      <c r="E68" s="8">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="7">
-        <v>33.19</v>
-      </c>
-      <c r="D69" s="7">
-        <v>31.09</v>
-      </c>
-      <c r="E69" s="9">
-        <v>-2.1</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="7">
-        <v>41.93</v>
-      </c>
-      <c r="D70" s="7">
-        <v>39.4</v>
-      </c>
-      <c r="E70" s="9">
-        <v>-2.53</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B71" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="7">
-        <v>48.88</v>
-      </c>
-      <c r="D71" s="7">
-        <v>39.7</v>
-      </c>
-      <c r="E71" s="9">
-        <v>-9.18</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C72" s="7">
-        <v>51.25</v>
-      </c>
-      <c r="D72" s="7">
-        <v>49.8</v>
-      </c>
-      <c r="E72" s="9">
-        <v>-1.45</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C73" s="7">
-        <v>65.33</v>
-      </c>
-      <c r="D73" s="7">
-        <v>74.62</v>
-      </c>
-      <c r="E73" s="8">
-        <v>9.289999999999999</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B74" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C74" s="7">
-        <v>24.15</v>
-      </c>
-      <c r="D74" s="7">
-        <v>22.09</v>
-      </c>
-      <c r="E74" s="9">
-        <v>-2.06</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B75" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C75" s="7">
-        <v>49.26</v>
-      </c>
-      <c r="D75" s="7">
-        <v>42.71</v>
-      </c>
-      <c r="E75" s="9">
-        <v>-6.55</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B76" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C76" s="7">
-        <v>33.21</v>
-      </c>
-      <c r="D76" s="7">
-        <v>37.83</v>
-      </c>
-      <c r="E76" s="8">
-        <v>4.62</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B77" s="6" t="s">
+      <c r="B81" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C77" s="7">
-        <v>-35.44</v>
-      </c>
-      <c r="D77" s="7">
-        <v>28.97</v>
-      </c>
-      <c r="E77" s="8">
-        <v>64.41</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B78" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="7">
-        <v>-40.17</v>
-      </c>
-      <c r="D78" s="7">
-        <v>26.07</v>
-      </c>
-      <c r="E78" s="8">
-        <v>66.23999999999999</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B79" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="7">
-        <v>30.45</v>
-      </c>
-      <c r="D79" s="7">
-        <v>30.93</v>
-      </c>
-      <c r="E79" s="8">
-        <v>0.48</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B80" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="7">
-        <v>49.33</v>
-      </c>
-      <c r="D80" s="7">
-        <v>-33.86</v>
-      </c>
-      <c r="E80" s="9">
-        <v>-83.19</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B81" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="7">
-        <v>-14.87</v>
-      </c>
-      <c r="D81" s="7">
-        <v>-38.02</v>
-      </c>
-      <c r="E81" s="9">
-        <v>-23.15</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B82" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C82" s="7">
-        <v>-53.85</v>
-      </c>
-      <c r="D82" s="7">
-        <v>245.57</v>
-      </c>
-      <c r="E82" s="8">
-        <v>299.42</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="A83" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B83" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C83" s="7">
-        <v>155.72</v>
-      </c>
-      <c r="D83" s="7">
-        <v>183.21</v>
-      </c>
-      <c r="E83" s="8">
-        <v>27.49</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5">
-      <c r="A84" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B84" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C84" s="7">
-        <v>26.46</v>
-      </c>
-      <c r="D84" s="7">
-        <v>2.72</v>
-      </c>
-      <c r="E84" s="9">
-        <v>-23.74</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5">
-      <c r="A85" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B85" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C85" s="7">
-        <v>-37.51</v>
-      </c>
-      <c r="D85" s="7">
+      <c r="C81" s="5">
         <v>-33.01</v>
       </c>
-      <c r="E85" s="8">
-        <v>4.5</v>
+      <c r="D81" s="5">
+        <v>1.03</v>
+      </c>
+      <c r="E81" s="6">
+        <v>34.04</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3571,60 +3396,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>81</v>
+      <c r="B1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="10">
         <v>48.16</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="11">
         <v>9</v>
       </c>
-      <c r="D2" s="12">
-        <v>40.2</v>
-      </c>
-      <c r="E2" s="12">
+      <c r="D2" s="10">
+        <v>40.1</v>
+      </c>
+      <c r="E2" s="10">
         <v>40</v>
       </c>
-      <c r="F2" s="12">
-        <v>-3.9</v>
-      </c>
-      <c r="G2" s="12">
-        <v>4.6</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="F2" s="10">
+        <v>-4.1</v>
+      </c>
+      <c r="G2" s="10">
+        <v>2.4</v>
+      </c>
+      <c r="H2" s="10">
         <v>55.4</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="10">
         <v>30</v>
       </c>
     </row>
@@ -3726,61 +3551,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="12" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="15">
-        <v>0.3686</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0.3421</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0.1961</v>
-      </c>
-      <c r="D2" s="15">
-        <v>0.1826</v>
-      </c>
-      <c r="E2" s="15">
-        <v>0.1173</v>
-      </c>
-      <c r="F2" s="15">
-        <v>0.0537</v>
-      </c>
-      <c r="G2" s="15">
-        <v>0.0438</v>
-      </c>
-      <c r="H2" s="15">
-        <v>-0.0347</v>
-      </c>
-      <c r="I2" s="15">
-        <v>-0.1043</v>
+      <c r="A2" s="13">
+        <v>0.3721</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.3404</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.1977</v>
+      </c>
+      <c r="D2" s="13">
+        <v>0.1804</v>
+      </c>
+      <c r="E2" s="13">
+        <v>0.116</v>
+      </c>
+      <c r="F2" s="13">
+        <v>0.0498</v>
+      </c>
+      <c r="G2" s="13">
+        <v>0.0458</v>
+      </c>
+      <c r="H2" s="13">
+        <v>-0.0345</v>
+      </c>
+      <c r="I2" s="13">
+        <v>-0.1056</v>
       </c>
     </row>
   </sheetData>
